--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B444A77C-F821-4DFE-8B41-5A097B450B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A25A275-5D4D-46AB-95FB-23AFC20F9338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="1473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="1475">
   <si>
     <t>trigger</t>
   </si>
@@ -4323,9 +4323,6 @@
     <t>calcified granulomas</t>
   </si>
   <si>
-    <t>enlm</t>
-  </si>
-  <si>
     <t>enlargement</t>
   </si>
   <si>
@@ -4447,6 +4444,15 @@
   </si>
   <si>
     <t>ent</t>
+  </si>
+  <si>
+    <t>enla</t>
+  </si>
+  <si>
+    <t>enca</t>
+  </si>
+  <si>
+    <t>encasement</t>
   </si>
 </sst>
 </file>
@@ -4515,10 +4521,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B742" totalsRowShown="0">
-  <autoFilter ref="A1:B742" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B742">
-    <sortCondition ref="A1:A742"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B743" totalsRowShown="0">
+  <autoFilter ref="A1:B743" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B743">
+    <sortCondition ref="A1:A743"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4791,7 +4797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B742"/>
+  <dimension ref="A1:B743"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -5152,7 +5158,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="B45" t="s">
         <v>1346</v>
@@ -5352,10 +5358,10 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B70" t="s">
         <v>1449</v>
-      </c>
-      <c r="B70" t="s">
-        <v>1450</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
@@ -5688,10 +5694,10 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B112" t="s">
         <v>1461</v>
-      </c>
-      <c r="B112" t="s">
-        <v>1462</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
@@ -6032,10 +6038,10 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B155" t="s">
         <v>1447</v>
-      </c>
-      <c r="B155" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
@@ -6243,7 +6249,7 @@
         <v>211</v>
       </c>
       <c r="B181" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
@@ -6251,7 +6257,7 @@
         <v>213</v>
       </c>
       <c r="B182" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
@@ -6520,159 +6526,159 @@
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>815</v>
+        <v>1473</v>
       </c>
       <c r="B216" t="s">
-        <v>816</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>130</v>
+        <v>815</v>
       </c>
       <c r="B217" t="s">
-        <v>417</v>
+        <v>816</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>321</v>
+        <v>130</v>
       </c>
       <c r="B218" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>1431</v>
+        <v>321</v>
       </c>
       <c r="B219" t="s">
-        <v>1432</v>
+        <v>418</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>863</v>
+        <v>1472</v>
       </c>
       <c r="B220" t="s">
-        <v>864</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>1435</v>
+        <v>863</v>
       </c>
       <c r="B221" t="s">
-        <v>1436</v>
+        <v>864</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>1303</v>
+        <v>1434</v>
       </c>
       <c r="B222" t="s">
-        <v>1304</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>183</v>
+        <v>1471</v>
       </c>
       <c r="B223" t="s">
-        <v>419</v>
+        <v>887</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>1141</v>
+        <v>1303</v>
       </c>
       <c r="B224" t="s">
-        <v>1142</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>1143</v>
+        <v>183</v>
       </c>
       <c r="B225" t="s">
-        <v>1144</v>
+        <v>419</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>1425</v>
+        <v>1141</v>
       </c>
       <c r="B226" t="s">
-        <v>1426</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>1383</v>
+        <v>1143</v>
       </c>
       <c r="B227" t="s">
-        <v>1384</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>1472</v>
+        <v>1425</v>
       </c>
       <c r="B228" t="s">
-        <v>887</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>32</v>
+        <v>1383</v>
       </c>
       <c r="B229" t="s">
-        <v>420</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B230" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>1293</v>
+        <v>35</v>
       </c>
       <c r="B231" t="s">
-        <v>1294</v>
+        <v>421</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>1219</v>
+        <v>1293</v>
       </c>
       <c r="B232" t="s">
-        <v>1220</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>760</v>
+        <v>1219</v>
       </c>
       <c r="B233" t="s">
-        <v>1004</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>169</v>
+        <v>760</v>
       </c>
       <c r="B234" t="s">
-        <v>422</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B235" t="s">
         <v>422</v>
@@ -6680,591 +6686,591 @@
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>1005</v>
+        <v>170</v>
       </c>
       <c r="B236" t="s">
-        <v>761</v>
+        <v>422</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>1423</v>
+        <v>1005</v>
       </c>
       <c r="B237" t="s">
-        <v>1424</v>
+        <v>761</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>178</v>
+        <v>1423</v>
       </c>
       <c r="B238" t="s">
-        <v>423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="B239" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>238</v>
+        <v>111</v>
       </c>
       <c r="B240" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="B241" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B242" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="B243" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>663</v>
+        <v>179</v>
       </c>
       <c r="B244" t="s">
-        <v>718</v>
+        <v>428</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>97</v>
+        <v>663</v>
       </c>
       <c r="B245" t="s">
-        <v>429</v>
+        <v>718</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B246" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>242</v>
+        <v>110</v>
       </c>
       <c r="B247" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B248" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="B249" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>1421</v>
+        <v>177</v>
       </c>
       <c r="B250" t="s">
-        <v>1422</v>
+        <v>433</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>182</v>
+        <v>1421</v>
       </c>
       <c r="B251" t="s">
-        <v>434</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>1098</v>
+        <v>182</v>
       </c>
       <c r="B252" t="s">
-        <v>1099</v>
+        <v>434</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>972</v>
+        <v>1098</v>
       </c>
       <c r="B253" t="s">
-        <v>973</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B254" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>1184</v>
+        <v>974</v>
       </c>
       <c r="B255" t="s">
-        <v>1185</v>
+        <v>975</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>1363</v>
+        <v>1184</v>
       </c>
       <c r="B256" t="s">
-        <v>1364</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>1187</v>
+        <v>1363</v>
       </c>
       <c r="B257" t="s">
-        <v>1188</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>253</v>
+        <v>1187</v>
       </c>
       <c r="B258" t="s">
-        <v>435</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="B259" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>783</v>
+        <v>34</v>
       </c>
       <c r="B260" t="s">
-        <v>784</v>
+        <v>436</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>180</v>
+        <v>783</v>
       </c>
       <c r="B261" t="s">
-        <v>437</v>
+        <v>784</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>1335</v>
+        <v>180</v>
       </c>
       <c r="B262" t="s">
-        <v>1404</v>
+        <v>437</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B263" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>1455</v>
+        <v>1334</v>
       </c>
       <c r="B264" t="s">
-        <v>1456</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>275</v>
+        <v>1454</v>
       </c>
       <c r="B265" t="s">
-        <v>438</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>853</v>
+        <v>275</v>
       </c>
       <c r="B266" t="s">
-        <v>854</v>
+        <v>438</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>116</v>
+        <v>853</v>
       </c>
       <c r="B267" t="s">
-        <v>439</v>
+        <v>854</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="B268" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>1409</v>
+        <v>208</v>
       </c>
       <c r="B269" t="s">
-        <v>1410</v>
+        <v>440</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>1207</v>
+        <v>1409</v>
       </c>
       <c r="B270" t="s">
-        <v>1208</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>1048</v>
+        <v>1207</v>
       </c>
       <c r="B271" t="s">
-        <v>1049</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>118</v>
+        <v>1048</v>
       </c>
       <c r="B272" t="s">
-        <v>441</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>637</v>
+        <v>118</v>
       </c>
       <c r="B273" t="s">
-        <v>719</v>
+        <v>441</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>1319</v>
+        <v>637</v>
       </c>
       <c r="B274" t="s">
-        <v>1320</v>
+        <v>719</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>811</v>
+        <v>1319</v>
       </c>
       <c r="B275" t="s">
-        <v>812</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>298</v>
+        <v>811</v>
       </c>
       <c r="B276" t="s">
-        <v>442</v>
+        <v>812</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>639</v>
+        <v>298</v>
       </c>
       <c r="B277" t="s">
-        <v>720</v>
+        <v>442</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B278" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>1030</v>
+        <v>640</v>
       </c>
       <c r="B279" t="s">
-        <v>1031</v>
+        <v>721</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>90</v>
+        <v>1030</v>
       </c>
       <c r="B280" t="s">
-        <v>443</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B281" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B282" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>1064</v>
+        <v>89</v>
       </c>
       <c r="B283" t="s">
-        <v>1065</v>
+        <v>445</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>23</v>
+        <v>1064</v>
       </c>
       <c r="B284" t="s">
-        <v>1124</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>1413</v>
+        <v>23</v>
       </c>
       <c r="B285" t="s">
-        <v>1414</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>5</v>
+        <v>1413</v>
       </c>
       <c r="B286" t="s">
-        <v>6</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>1128</v>
+        <v>5</v>
       </c>
       <c r="B287" t="s">
-        <v>1129</v>
+        <v>6</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>126</v>
+        <v>1128</v>
       </c>
       <c r="B288" t="s">
-        <v>446</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>1387</v>
+        <v>126</v>
       </c>
       <c r="B289" t="s">
-        <v>1388</v>
+        <v>446</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>128</v>
+        <v>1387</v>
       </c>
       <c r="B290" t="s">
-        <v>447</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B291" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B292" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B293" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>277</v>
+        <v>119</v>
       </c>
       <c r="B294" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>1066</v>
+        <v>277</v>
       </c>
       <c r="B295" t="s">
-        <v>1067</v>
+        <v>451</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>9</v>
+        <v>1066</v>
       </c>
       <c r="B296" t="s">
-        <v>10</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="B297" t="s">
-        <v>452</v>
+        <v>10</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B298" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="B299" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="B300" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>1374</v>
+        <v>262</v>
       </c>
       <c r="B301" t="s">
-        <v>1375</v>
+        <v>455</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>77</v>
+        <v>1374</v>
       </c>
       <c r="B302" t="s">
-        <v>456</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>933</v>
+        <v>77</v>
       </c>
       <c r="B303" t="s">
-        <v>934</v>
+        <v>456</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>1158</v>
+        <v>933</v>
       </c>
       <c r="B304" t="s">
-        <v>1159</v>
+        <v>934</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>168</v>
+        <v>1158</v>
       </c>
       <c r="B305" t="s">
-        <v>457</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>1347</v>
+        <v>168</v>
       </c>
       <c r="B306" t="s">
-        <v>1348</v>
+        <v>457</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>1357</v>
+        <v>1347</v>
       </c>
       <c r="B307" t="s">
-        <v>1358</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>1400</v>
+        <v>1357</v>
       </c>
       <c r="B308" t="s">
-        <v>1354</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>1353</v>
+        <v>1400</v>
       </c>
       <c r="B309" t="s">
         <v>1354</v>
@@ -7272,39 +7278,39 @@
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>167</v>
+        <v>1353</v>
       </c>
       <c r="B310" t="s">
-        <v>458</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>1349</v>
+        <v>167</v>
       </c>
       <c r="B311" t="s">
-        <v>1350</v>
+        <v>458</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>1355</v>
+        <v>1349</v>
       </c>
       <c r="B312" t="s">
-        <v>1356</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>1382</v>
+        <v>1355</v>
       </c>
       <c r="B313" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>1351</v>
+        <v>1382</v>
       </c>
       <c r="B314" t="s">
         <v>1352</v>
@@ -7312,199 +7318,199 @@
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>831</v>
+        <v>1351</v>
       </c>
       <c r="B315" t="s">
-        <v>832</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>787</v>
+        <v>831</v>
       </c>
       <c r="B316" t="s">
-        <v>788</v>
+        <v>832</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>304</v>
+        <v>787</v>
       </c>
       <c r="B317" t="s">
-        <v>459</v>
+        <v>788</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>754</v>
+        <v>304</v>
       </c>
       <c r="B318" t="s">
-        <v>755</v>
+        <v>459</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>892</v>
+        <v>754</v>
       </c>
       <c r="B319" t="s">
-        <v>893</v>
+        <v>755</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>1389</v>
+        <v>892</v>
       </c>
       <c r="B320" t="s">
-        <v>1390</v>
+        <v>893</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>648</v>
+        <v>1389</v>
       </c>
       <c r="B321" t="s">
-        <v>722</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>86</v>
+        <v>648</v>
       </c>
       <c r="B322" t="s">
-        <v>460</v>
+        <v>722</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B323" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="B324" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B325" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B326" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>251</v>
+        <v>158</v>
       </c>
       <c r="B327" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="B328" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>325</v>
+        <v>285</v>
       </c>
       <c r="B329" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>1369</v>
+        <v>325</v>
       </c>
       <c r="B330" t="s">
-        <v>1370</v>
+        <v>467</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>326</v>
+        <v>1369</v>
       </c>
       <c r="B331" t="s">
-        <v>468</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>229</v>
+        <v>326</v>
       </c>
       <c r="B332" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>55</v>
+        <v>229</v>
       </c>
       <c r="B333" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>653</v>
+        <v>55</v>
       </c>
       <c r="B334" t="s">
-        <v>723</v>
+        <v>470</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>235</v>
+        <v>653</v>
       </c>
       <c r="B335" t="s">
-        <v>471</v>
+        <v>723</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="B336" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="B337" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>762</v>
+        <v>236</v>
       </c>
       <c r="B338" t="s">
-        <v>763</v>
+        <v>473</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>1006</v>
+        <v>762</v>
       </c>
       <c r="B339" t="s">
         <v>763</v>
@@ -7512,631 +7518,631 @@
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>164</v>
+        <v>1006</v>
       </c>
       <c r="B340" t="s">
-        <v>474</v>
+        <v>763</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>1469</v>
+        <v>164</v>
       </c>
       <c r="B341" t="s">
-        <v>1467</v>
+        <v>474</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>201</v>
+        <v>1468</v>
       </c>
       <c r="B342" t="s">
-        <v>475</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B343" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>313</v>
+        <v>204</v>
       </c>
       <c r="B344" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>869</v>
+        <v>313</v>
       </c>
       <c r="B345" t="s">
-        <v>870</v>
+        <v>477</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>992</v>
+        <v>869</v>
       </c>
       <c r="B346" t="s">
-        <v>993</v>
+        <v>870</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>1322</v>
+        <v>992</v>
       </c>
       <c r="B347" t="s">
-        <v>1323</v>
+        <v>993</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>258</v>
+        <v>1322</v>
       </c>
       <c r="B348" t="s">
-        <v>478</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>978</v>
+        <v>258</v>
       </c>
       <c r="B349" t="s">
-        <v>979</v>
+        <v>478</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>1361</v>
+        <v>978</v>
       </c>
       <c r="B350" t="s">
-        <v>1362</v>
+        <v>979</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>160</v>
+        <v>1361</v>
       </c>
       <c r="B351" t="s">
-        <v>479</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>688</v>
+        <v>160</v>
       </c>
       <c r="B352" t="s">
-        <v>724</v>
+        <v>479</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>1152</v>
+        <v>688</v>
       </c>
       <c r="B353" t="s">
-        <v>1153</v>
+        <v>724</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>756</v>
+        <v>1152</v>
       </c>
       <c r="B354" t="s">
-        <v>757</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>890</v>
+        <v>756</v>
       </c>
       <c r="B355" t="s">
-        <v>891</v>
+        <v>757</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B356" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>184</v>
+        <v>888</v>
       </c>
       <c r="B357" t="s">
-        <v>480</v>
+        <v>889</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>244</v>
+        <v>184</v>
       </c>
       <c r="B358" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B359" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>1265</v>
+        <v>243</v>
       </c>
       <c r="B360" t="s">
-        <v>1270</v>
+        <v>482</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>682</v>
+        <v>1265</v>
       </c>
       <c r="B361" t="s">
-        <v>725</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>1266</v>
+        <v>682</v>
       </c>
       <c r="B362" t="s">
-        <v>1271</v>
+        <v>725</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>683</v>
+        <v>1266</v>
       </c>
       <c r="B363" t="s">
-        <v>726</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>1267</v>
+        <v>683</v>
       </c>
       <c r="B364" t="s">
-        <v>1272</v>
+        <v>726</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>684</v>
+        <v>1267</v>
       </c>
       <c r="B365" t="s">
-        <v>727</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>1268</v>
+        <v>684</v>
       </c>
       <c r="B366" t="s">
-        <v>1273</v>
+        <v>727</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>685</v>
+        <v>1268</v>
       </c>
       <c r="B367" t="s">
-        <v>728</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>1269</v>
+        <v>685</v>
       </c>
       <c r="B368" t="s">
-        <v>1274</v>
+        <v>728</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>686</v>
+        <v>1269</v>
       </c>
       <c r="B369" t="s">
-        <v>729</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>1178</v>
+        <v>686</v>
       </c>
       <c r="B370" t="s">
-        <v>1179</v>
+        <v>729</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>280</v>
+        <v>1178</v>
       </c>
       <c r="B371" t="s">
-        <v>483</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B372" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>49</v>
+        <v>281</v>
       </c>
       <c r="B373" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B374" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="B375" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>1443</v>
+        <v>136</v>
       </c>
       <c r="B376" t="s">
-        <v>1444</v>
+        <v>488</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>72</v>
+        <v>1442</v>
       </c>
       <c r="B377" t="s">
-        <v>487</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>1176</v>
+        <v>72</v>
       </c>
       <c r="B378" t="s">
-        <v>1177</v>
+        <v>487</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>221</v>
+        <v>1176</v>
       </c>
       <c r="B379" t="s">
-        <v>489</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>1180</v>
+        <v>221</v>
       </c>
       <c r="B380" t="s">
-        <v>1181</v>
+        <v>489</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>15</v>
+        <v>1180</v>
       </c>
       <c r="B381" t="s">
-        <v>16</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>1052</v>
+        <v>15</v>
       </c>
       <c r="B382" t="s">
-        <v>1053</v>
+        <v>16</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>915</v>
+        <v>1052</v>
       </c>
       <c r="B383" t="s">
-        <v>916</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>108</v>
+        <v>915</v>
       </c>
       <c r="B384" t="s">
-        <v>490</v>
+        <v>916</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>241</v>
+        <v>108</v>
       </c>
       <c r="B385" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>327</v>
+        <v>241</v>
       </c>
       <c r="B386" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>1092</v>
+        <v>327</v>
       </c>
       <c r="B387" t="s">
-        <v>1093</v>
+        <v>492</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>1044</v>
+        <v>1092</v>
       </c>
       <c r="B388" t="s">
-        <v>1045</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>121</v>
+        <v>1044</v>
       </c>
       <c r="B389" t="s">
-        <v>493</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>746</v>
+        <v>121</v>
       </c>
       <c r="B390" t="s">
-        <v>747</v>
+        <v>493</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>777</v>
+        <v>746</v>
       </c>
       <c r="B391" t="s">
-        <v>778</v>
+        <v>747</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>134</v>
+        <v>777</v>
       </c>
       <c r="B392" t="s">
-        <v>494</v>
+        <v>778</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="B393" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>1299</v>
+        <v>63</v>
       </c>
       <c r="B394" t="s">
-        <v>1300</v>
+        <v>495</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>224</v>
+        <v>1299</v>
       </c>
       <c r="B395" t="s">
-        <v>496</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>25</v>
+        <v>224</v>
       </c>
       <c r="B396" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B397" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>207</v>
+        <v>26</v>
       </c>
       <c r="B398" t="s">
-        <v>1121</v>
+        <v>498</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>955</v>
+        <v>207</v>
       </c>
       <c r="B399" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>1101</v>
+        <v>955</v>
       </c>
       <c r="B400" t="s">
-        <v>1102</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>206</v>
+        <v>1101</v>
       </c>
       <c r="B401" t="s">
-        <v>1123</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B402" t="s">
-        <v>499</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B403" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="B404" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>659</v>
+        <v>145</v>
       </c>
       <c r="B405" t="s">
-        <v>730</v>
+        <v>501</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>171</v>
+        <v>659</v>
       </c>
       <c r="B406" t="s">
-        <v>502</v>
+        <v>730</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>1080</v>
+        <v>171</v>
       </c>
       <c r="B407" t="s">
-        <v>1081</v>
+        <v>502</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>263</v>
+        <v>1080</v>
       </c>
       <c r="B408" t="s">
-        <v>503</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>1082</v>
+        <v>263</v>
       </c>
       <c r="B409" t="s">
-        <v>1083</v>
+        <v>503</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>80</v>
+        <v>1082</v>
       </c>
       <c r="B410" t="s">
-        <v>504</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B411" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>191</v>
+        <v>65</v>
       </c>
       <c r="B412" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="B413" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>192</v>
+        <v>123</v>
       </c>
       <c r="B414" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="B415" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B416" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>1186</v>
+        <v>233</v>
       </c>
       <c r="B417" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>31</v>
+        <v>1186</v>
       </c>
       <c r="B418" t="s">
         <v>511</v>
@@ -8144,367 +8150,367 @@
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B419" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B420" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B421" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>1441</v>
+        <v>71</v>
       </c>
       <c r="B422" t="s">
-        <v>1442</v>
+        <v>514</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>306</v>
+        <v>1440</v>
       </c>
       <c r="B423" t="s">
-        <v>515</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>222</v>
+        <v>306</v>
       </c>
       <c r="B424" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>278</v>
+        <v>222</v>
       </c>
       <c r="B425" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B426" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>1391</v>
+        <v>279</v>
       </c>
       <c r="B427" t="s">
-        <v>1392</v>
+        <v>519</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>827</v>
+        <v>1391</v>
       </c>
       <c r="B428" t="s">
-        <v>828</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>48</v>
+        <v>827</v>
       </c>
       <c r="B429" t="s">
-        <v>520</v>
+        <v>828</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="B430" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="B431" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>1373</v>
+        <v>52</v>
       </c>
       <c r="B432" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>223</v>
+        <v>1373</v>
       </c>
       <c r="B433" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>1086</v>
+        <v>223</v>
       </c>
       <c r="B434" t="s">
-        <v>1087</v>
+        <v>523</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>1097</v>
+        <v>1086</v>
       </c>
       <c r="B435" t="s">
-        <v>1100</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>1042</v>
+        <v>1097</v>
       </c>
       <c r="B436" t="s">
-        <v>1043</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>96</v>
+        <v>1042</v>
       </c>
       <c r="B437" t="s">
-        <v>524</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>248</v>
+        <v>96</v>
       </c>
       <c r="B438" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B439" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>94</v>
+        <v>249</v>
       </c>
       <c r="B440" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>1056</v>
+        <v>94</v>
       </c>
       <c r="B441" t="s">
-        <v>1057</v>
+        <v>527</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>212</v>
+        <v>1056</v>
       </c>
       <c r="B442" t="s">
-        <v>528</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>1211</v>
+        <v>212</v>
       </c>
       <c r="B443" t="s">
-        <v>1212</v>
+        <v>528</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>911</v>
+        <v>1211</v>
       </c>
       <c r="B444" t="s">
-        <v>912</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="B445" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="B446" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>329</v>
+        <v>913</v>
       </c>
       <c r="B447" t="s">
-        <v>529</v>
+        <v>914</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>1415</v>
+        <v>329</v>
       </c>
       <c r="B448" t="s">
-        <v>1416</v>
+        <v>529</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="B449" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>1058</v>
+        <v>1417</v>
       </c>
       <c r="B450" t="s">
-        <v>1059</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>990</v>
+        <v>1058</v>
       </c>
       <c r="B451" t="s">
-        <v>991</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>1401</v>
+        <v>990</v>
       </c>
       <c r="B452" t="s">
-        <v>1402</v>
+        <v>991</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>986</v>
+        <v>1401</v>
       </c>
       <c r="B453" t="s">
-        <v>987</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="B454" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>82</v>
+        <v>988</v>
       </c>
       <c r="B455" t="s">
-        <v>530</v>
+        <v>989</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>768</v>
+        <v>82</v>
       </c>
       <c r="B456" t="s">
-        <v>769</v>
+        <v>530</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>197</v>
+        <v>768</v>
       </c>
       <c r="B457" t="s">
-        <v>531</v>
+        <v>769</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>650</v>
+        <v>197</v>
       </c>
       <c r="B458" t="s">
-        <v>731</v>
+        <v>531</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>1439</v>
+        <v>650</v>
       </c>
       <c r="B459" t="s">
-        <v>1440</v>
+        <v>731</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>1344</v>
+        <v>1438</v>
       </c>
       <c r="B460" t="s">
-        <v>1345</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>817</v>
+        <v>1344</v>
       </c>
       <c r="B461" t="s">
-        <v>818</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>1060</v>
+        <v>817</v>
       </c>
       <c r="B462" t="s">
-        <v>1061</v>
+        <v>818</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>3</v>
+        <v>1060</v>
       </c>
       <c r="B463" t="s">
-        <v>4</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>953</v>
+        <v>3</v>
       </c>
       <c r="B464" t="s">
         <v>4</v>
@@ -8512,7 +8518,7 @@
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B465" t="s">
         <v>4</v>
@@ -8520,1615 +8526,1615 @@
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>660</v>
+        <v>954</v>
       </c>
       <c r="B466" t="s">
-        <v>732</v>
+        <v>4</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>1291</v>
+        <v>660</v>
       </c>
       <c r="B467" t="s">
-        <v>1292</v>
+        <v>732</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>766</v>
+        <v>1291</v>
       </c>
       <c r="B468" t="s">
-        <v>767</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>85</v>
+        <v>766</v>
       </c>
       <c r="B469" t="s">
-        <v>532</v>
+        <v>767</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>1054</v>
+        <v>85</v>
       </c>
       <c r="B470" t="s">
-        <v>1055</v>
+        <v>532</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>825</v>
+        <v>1054</v>
       </c>
       <c r="B471" t="s">
-        <v>826</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>805</v>
+        <v>825</v>
       </c>
       <c r="B472" t="s">
-        <v>806</v>
+        <v>826</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>187</v>
+        <v>805</v>
       </c>
       <c r="B473" t="s">
-        <v>533</v>
+        <v>806</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>823</v>
+        <v>187</v>
       </c>
       <c r="B474" t="s">
-        <v>824</v>
+        <v>533</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>929</v>
+        <v>823</v>
       </c>
       <c r="B475" t="s">
-        <v>1118</v>
+        <v>824</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>1445</v>
+        <v>929</v>
       </c>
       <c r="B476" t="s">
-        <v>1446</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>859</v>
+        <v>1444</v>
       </c>
       <c r="B477" t="s">
-        <v>860</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>1433</v>
+        <v>859</v>
       </c>
       <c r="B478" t="s">
-        <v>1434</v>
+        <v>860</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>1038</v>
+        <v>1432</v>
       </c>
       <c r="B479" t="s">
-        <v>1039</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>794</v>
+        <v>1038</v>
       </c>
       <c r="B480" t="s">
-        <v>1119</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B481" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>13</v>
+        <v>793</v>
       </c>
       <c r="B482" t="s">
-        <v>14</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>813</v>
+        <v>13</v>
       </c>
       <c r="B483" t="s">
-        <v>814</v>
+        <v>14</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>1221</v>
+        <v>813</v>
       </c>
       <c r="B484" t="s">
-        <v>1222</v>
+        <v>814</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>186</v>
+        <v>1221</v>
       </c>
       <c r="B485" t="s">
-        <v>534</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>807</v>
+        <v>186</v>
       </c>
       <c r="B486" t="s">
-        <v>808</v>
+        <v>534</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>319</v>
+        <v>807</v>
       </c>
       <c r="B487" t="s">
-        <v>535</v>
+        <v>808</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>652</v>
+        <v>319</v>
       </c>
       <c r="B488" t="s">
-        <v>733</v>
+        <v>535</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>851</v>
+        <v>652</v>
       </c>
       <c r="B489" t="s">
-        <v>852</v>
+        <v>733</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>654</v>
+        <v>851</v>
       </c>
       <c r="B490" t="s">
-        <v>734</v>
+        <v>852</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="B491" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>1193</v>
+        <v>649</v>
       </c>
       <c r="B492" t="s">
-        <v>1194</v>
+        <v>735</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>256</v>
+        <v>1193</v>
       </c>
       <c r="B493" t="s">
-        <v>536</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B494" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B495" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>188</v>
+        <v>261</v>
       </c>
       <c r="B496" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B497" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>931</v>
+        <v>190</v>
       </c>
       <c r="B498" t="s">
-        <v>932</v>
+        <v>540</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>1025</v>
+        <v>931</v>
       </c>
       <c r="B499" t="s">
-        <v>1026</v>
+        <v>932</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>1209</v>
+        <v>1025</v>
       </c>
       <c r="B500" t="s">
-        <v>1210</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>209</v>
+        <v>1209</v>
       </c>
       <c r="B501" t="s">
-        <v>541</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>1411</v>
+        <v>209</v>
       </c>
       <c r="B502" t="s">
-        <v>1412</v>
+        <v>541</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>1301</v>
+        <v>1411</v>
       </c>
       <c r="B503" t="s">
-        <v>1302</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>847</v>
+        <v>1301</v>
       </c>
       <c r="B504" t="s">
-        <v>848</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>143</v>
+        <v>847</v>
       </c>
       <c r="B505" t="s">
-        <v>542</v>
+        <v>848</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B506" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>1189</v>
+        <v>140</v>
       </c>
       <c r="B507" t="s">
-        <v>1190</v>
+        <v>543</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>1289</v>
+        <v>1189</v>
       </c>
       <c r="B508" t="s">
-        <v>1290</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>254</v>
+        <v>1289</v>
       </c>
       <c r="B509" t="s">
-        <v>544</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>330</v>
+        <v>254</v>
       </c>
       <c r="B510" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="B511" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="B512" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>73</v>
+        <v>234</v>
       </c>
       <c r="B513" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>341</v>
+        <v>73</v>
       </c>
       <c r="B514" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>308</v>
+        <v>341</v>
       </c>
       <c r="B515" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>839</v>
+        <v>308</v>
       </c>
       <c r="B516" t="s">
-        <v>840</v>
+        <v>550</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B517" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>220</v>
+        <v>841</v>
       </c>
       <c r="B518" t="s">
-        <v>551</v>
+        <v>842</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>904</v>
+        <v>220</v>
       </c>
       <c r="B519" t="s">
-        <v>905</v>
+        <v>551</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>1367</v>
+        <v>904</v>
       </c>
       <c r="B520" t="s">
-        <v>1368</v>
+        <v>905</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>958</v>
+        <v>1367</v>
       </c>
       <c r="B521" t="s">
-        <v>959</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>1174</v>
+        <v>958</v>
       </c>
       <c r="B522" t="s">
-        <v>1175</v>
+        <v>959</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>227</v>
+        <v>1174</v>
       </c>
       <c r="B523" t="s">
-        <v>552</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>333</v>
+        <v>227</v>
       </c>
       <c r="B524" t="s">
-        <v>1147</v>
+        <v>552</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>966</v>
+        <v>333</v>
       </c>
       <c r="B525" t="s">
-        <v>967</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>774</v>
+        <v>966</v>
       </c>
       <c r="B526" t="s">
-        <v>775</v>
+        <v>967</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>294</v>
+        <v>774</v>
       </c>
       <c r="B527" t="s">
-        <v>553</v>
+        <v>775</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>947</v>
+        <v>294</v>
       </c>
       <c r="B528" t="s">
-        <v>948</v>
+        <v>553</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>338</v>
+        <v>947</v>
       </c>
       <c r="B529" t="s">
-        <v>554</v>
+        <v>948</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>776</v>
+        <v>338</v>
       </c>
       <c r="B530" t="s">
-        <v>775</v>
+        <v>554</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>1305</v>
+        <v>776</v>
       </c>
       <c r="B531" t="s">
-        <v>1306</v>
+        <v>775</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>339</v>
+        <v>1305</v>
       </c>
       <c r="B532" t="s">
-        <v>555</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B533" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>641</v>
+        <v>340</v>
       </c>
       <c r="B534" t="s">
-        <v>736</v>
+        <v>556</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>39</v>
+        <v>641</v>
       </c>
       <c r="B535" t="s">
-        <v>557</v>
+        <v>736</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B536" t="s">
-        <v>1117</v>
+        <v>557</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>342</v>
+        <v>38</v>
       </c>
       <c r="B537" t="s">
-        <v>558</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>107</v>
+        <v>342</v>
       </c>
       <c r="B538" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>1419</v>
+        <v>107</v>
       </c>
       <c r="B539" t="s">
-        <v>1420</v>
+        <v>559</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>1023</v>
+        <v>1419</v>
       </c>
       <c r="B540" t="s">
-        <v>1024</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>898</v>
+        <v>1023</v>
       </c>
       <c r="B541" t="s">
-        <v>899</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>117</v>
+        <v>898</v>
       </c>
       <c r="B542" t="s">
-        <v>560</v>
+        <v>899</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>1019</v>
+        <v>117</v>
       </c>
       <c r="B543" t="s">
-        <v>1020</v>
+        <v>560</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>98</v>
+        <v>1019</v>
       </c>
       <c r="B544" t="s">
-        <v>561</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B545" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>662</v>
+        <v>99</v>
       </c>
       <c r="B546" t="s">
-        <v>737</v>
+        <v>562</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>1095</v>
+        <v>662</v>
       </c>
       <c r="B547" t="s">
-        <v>1018</v>
+        <v>737</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>819</v>
+        <v>1095</v>
       </c>
       <c r="B548" t="s">
-        <v>820</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>113</v>
+        <v>819</v>
       </c>
       <c r="B549" t="s">
-        <v>563</v>
+        <v>820</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>885</v>
+        <v>113</v>
       </c>
       <c r="B550" t="s">
-        <v>886</v>
+        <v>563</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>45</v>
+        <v>885</v>
       </c>
       <c r="B551" t="s">
-        <v>1116</v>
+        <v>886</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>290</v>
+        <v>45</v>
       </c>
       <c r="B552" t="s">
-        <v>564</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B553" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>47</v>
+        <v>299</v>
       </c>
       <c r="B554" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>843</v>
+        <v>47</v>
       </c>
       <c r="B555" t="s">
-        <v>844</v>
+        <v>566</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>51</v>
+        <v>843</v>
       </c>
       <c r="B556" t="s">
-        <v>567</v>
+        <v>844</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>867</v>
+        <v>51</v>
       </c>
       <c r="B557" t="s">
-        <v>868</v>
+        <v>567</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>114</v>
+        <v>867</v>
       </c>
       <c r="B558" t="s">
-        <v>568</v>
+        <v>868</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>849</v>
+        <v>114</v>
       </c>
       <c r="B559" t="s">
-        <v>850</v>
+        <v>568</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>144</v>
+        <v>849</v>
       </c>
       <c r="B560" t="s">
-        <v>569</v>
+        <v>850</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>1072</v>
+        <v>144</v>
       </c>
       <c r="B561" t="s">
-        <v>1073</v>
+        <v>569</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>176</v>
+        <v>1072</v>
       </c>
       <c r="B562" t="s">
-        <v>570</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>315</v>
+        <v>176</v>
       </c>
       <c r="B563" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>29</v>
+        <v>315</v>
       </c>
       <c r="B564" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>1012</v>
+        <v>29</v>
       </c>
       <c r="B565" t="s">
-        <v>1013</v>
+        <v>572</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>1217</v>
+        <v>1012</v>
       </c>
       <c r="B566" t="s">
-        <v>1218</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>293</v>
+        <v>1217</v>
       </c>
       <c r="B567" t="s">
-        <v>573</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>976</v>
+        <v>293</v>
       </c>
       <c r="B568" t="s">
-        <v>977</v>
+        <v>573</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>1453</v>
+        <v>976</v>
       </c>
       <c r="B569" t="s">
-        <v>1454</v>
+        <v>977</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>301</v>
+        <v>1452</v>
       </c>
       <c r="B570" t="s">
-        <v>574</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>998</v>
+        <v>301</v>
       </c>
       <c r="B571" t="s">
-        <v>999</v>
+        <v>574</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="B572" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>75</v>
+        <v>1002</v>
       </c>
       <c r="B573" t="s">
-        <v>575</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B574" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B575" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>328</v>
+        <v>78</v>
       </c>
       <c r="B576" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>1398</v>
+        <v>328</v>
       </c>
       <c r="B577" t="s">
-        <v>1399</v>
+        <v>578</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>1295</v>
+        <v>1398</v>
       </c>
       <c r="B578" t="s">
-        <v>1296</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>748</v>
+        <v>1295</v>
       </c>
       <c r="B579" t="s">
-        <v>749</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>801</v>
+        <v>748</v>
       </c>
       <c r="B580" t="s">
-        <v>802</v>
+        <v>749</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>1308</v>
+        <v>801</v>
       </c>
       <c r="B581" t="s">
-        <v>1309</v>
+        <v>802</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>135</v>
+        <v>1308</v>
       </c>
       <c r="B582" t="s">
-        <v>579</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>1172</v>
+        <v>135</v>
       </c>
       <c r="B583" t="s">
-        <v>1173</v>
+        <v>579</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>1032</v>
+        <v>1172</v>
       </c>
       <c r="B584" t="s">
-        <v>1033</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>215</v>
+        <v>1032</v>
       </c>
       <c r="B585" t="s">
-        <v>580</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>930</v>
+        <v>215</v>
       </c>
       <c r="B586" t="s">
-        <v>1132</v>
+        <v>580</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>216</v>
+        <v>930</v>
       </c>
       <c r="B587" t="s">
-        <v>1114</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>316</v>
+        <v>216</v>
       </c>
       <c r="B588" t="s">
-        <v>581</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>1074</v>
+        <v>316</v>
       </c>
       <c r="B589" t="s">
-        <v>1075</v>
+        <v>581</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>214</v>
+        <v>1074</v>
       </c>
       <c r="B590" t="s">
-        <v>1115</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>994</v>
+        <v>214</v>
       </c>
       <c r="B591" t="s">
-        <v>995</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="B592" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>225</v>
+        <v>996</v>
       </c>
       <c r="B593" t="s">
-        <v>582</v>
+        <v>997</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>1385</v>
+        <v>225</v>
       </c>
       <c r="B594" t="s">
-        <v>1386</v>
+        <v>582</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>943</v>
+        <v>1385</v>
       </c>
       <c r="B595" t="s">
-        <v>944</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>1090</v>
+        <v>943</v>
       </c>
       <c r="B596" t="s">
-        <v>1091</v>
+        <v>944</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>1040</v>
+        <v>1090</v>
       </c>
       <c r="B597" t="s">
-        <v>1041</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>93</v>
+        <v>1040</v>
       </c>
       <c r="B598" t="s">
-        <v>583</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="B599" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>779</v>
+        <v>120</v>
       </c>
       <c r="B600" t="s">
-        <v>780</v>
+        <v>584</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>133</v>
+        <v>779</v>
       </c>
       <c r="B601" t="s">
-        <v>585</v>
+        <v>780</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="B602" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>1297</v>
+        <v>62</v>
       </c>
       <c r="B603" t="s">
-        <v>1298</v>
+        <v>586</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>66</v>
+        <v>1297</v>
       </c>
       <c r="B604" t="s">
-        <v>587</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>821</v>
+        <v>66</v>
       </c>
       <c r="B605" t="s">
-        <v>822</v>
+        <v>587</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>945</v>
+        <v>821</v>
       </c>
       <c r="B606" t="s">
-        <v>946</v>
+        <v>822</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>1201</v>
+        <v>945</v>
       </c>
       <c r="B607" t="s">
-        <v>1202</v>
+        <v>946</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>1310</v>
+        <v>1201</v>
       </c>
       <c r="B608" t="s">
-        <v>1311</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>79</v>
+        <v>1310</v>
       </c>
       <c r="B609" t="s">
-        <v>588</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B610" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="B611" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>1170</v>
+        <v>122</v>
       </c>
       <c r="B612" t="s">
-        <v>1171</v>
+        <v>590</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>181</v>
+        <v>1170</v>
       </c>
       <c r="B613" t="s">
-        <v>591</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>797</v>
+        <v>181</v>
       </c>
       <c r="B614" t="s">
-        <v>798</v>
+        <v>591</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>1275</v>
+        <v>797</v>
       </c>
       <c r="B615" t="s">
-        <v>1280</v>
+        <v>798</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>687</v>
+        <v>1275</v>
       </c>
       <c r="B616" t="s">
-        <v>738</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>1276</v>
+        <v>687</v>
       </c>
       <c r="B617" t="s">
-        <v>1281</v>
+        <v>738</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B618" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="B619" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="B620" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>1137</v>
+        <v>1279</v>
       </c>
       <c r="B621" t="s">
-        <v>1138</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="B622" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
-        <v>284</v>
+        <v>1135</v>
       </c>
       <c r="B623" t="s">
-        <v>592</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
-        <v>968</v>
+        <v>284</v>
       </c>
       <c r="B624" t="s">
-        <v>969</v>
+        <v>592</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
-        <v>1205</v>
+        <v>968</v>
       </c>
       <c r="B625" t="s">
-        <v>1206</v>
+        <v>969</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
-        <v>837</v>
+        <v>1205</v>
       </c>
       <c r="B626" t="s">
-        <v>838</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>283</v>
+        <v>837</v>
       </c>
       <c r="B627" t="s">
-        <v>593</v>
+        <v>838</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
-        <v>879</v>
+        <v>283</v>
       </c>
       <c r="B628" t="s">
-        <v>880</v>
+        <v>593</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>1166</v>
+        <v>879</v>
       </c>
       <c r="B629" t="s">
-        <v>1167</v>
+        <v>880</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>752</v>
+        <v>1166</v>
       </c>
       <c r="B630" t="s">
-        <v>753</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>1070</v>
+        <v>752</v>
       </c>
       <c r="B631" t="s">
-        <v>1071</v>
+        <v>753</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>67</v>
+        <v>1070</v>
       </c>
       <c r="B632" t="s">
-        <v>594</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B633" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
-        <v>1380</v>
+        <v>68</v>
       </c>
       <c r="B634" t="s">
-        <v>1381</v>
+        <v>595</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
-        <v>95</v>
+        <v>1380</v>
       </c>
       <c r="B635" t="s">
-        <v>596</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
-        <v>289</v>
+        <v>95</v>
       </c>
       <c r="B636" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B637" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="B638" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
-        <v>193</v>
+        <v>264</v>
       </c>
       <c r="B639" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
-        <v>1340</v>
+        <v>193</v>
       </c>
       <c r="B640" t="s">
-        <v>1341</v>
+        <v>600</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>896</v>
+        <v>1340</v>
       </c>
       <c r="B641" t="s">
-        <v>897</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
-        <v>44</v>
+        <v>896</v>
       </c>
       <c r="B642" t="s">
-        <v>1113</v>
+        <v>897</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
-        <v>1062</v>
+        <v>44</v>
       </c>
       <c r="B643" t="s">
-        <v>1063</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
-        <v>323</v>
+        <v>1062</v>
       </c>
       <c r="B644" t="s">
-        <v>601</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B645" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
-        <v>845</v>
+        <v>324</v>
       </c>
       <c r="B646" t="s">
-        <v>846</v>
+        <v>602</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
-        <v>883</v>
+        <v>845</v>
       </c>
       <c r="B647" t="s">
-        <v>884</v>
+        <v>846</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
-        <v>1223</v>
+        <v>883</v>
       </c>
       <c r="B648" t="s">
-        <v>1224</v>
+        <v>884</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
-        <v>865</v>
+        <v>1223</v>
       </c>
       <c r="B649" t="s">
-        <v>866</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
-        <v>33</v>
+        <v>865</v>
       </c>
       <c r="B650" t="s">
-        <v>603</v>
+        <v>866</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B651" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>1130</v>
+        <v>36</v>
       </c>
       <c r="B652" t="s">
-        <v>1131</v>
+        <v>604</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
-        <v>309</v>
+        <v>1130</v>
       </c>
       <c r="B653" t="s">
-        <v>605</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
       <c r="B654" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
-        <v>302</v>
+        <v>257</v>
       </c>
       <c r="B655" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
-        <v>228</v>
+        <v>302</v>
       </c>
       <c r="B656" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c r="B657" t="s">
-        <v>18</v>
+        <v>608</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
-        <v>651</v>
+        <v>17</v>
       </c>
       <c r="B658" t="s">
-        <v>739</v>
+        <v>18</v>
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
-        <v>1407</v>
+        <v>651</v>
       </c>
       <c r="B659" t="s">
-        <v>1408</v>
+        <v>739</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
-        <v>781</v>
+        <v>1407</v>
       </c>
       <c r="B660" t="s">
-        <v>782</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
-        <v>142</v>
+        <v>781</v>
       </c>
       <c r="B661" t="s">
-        <v>609</v>
+        <v>782</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
-        <v>1164</v>
+        <v>142</v>
       </c>
       <c r="B662" t="s">
-        <v>1165</v>
+        <v>609</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
-        <v>951</v>
+        <v>1164</v>
       </c>
       <c r="B663" t="s">
-        <v>952</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
-        <v>54</v>
+        <v>951</v>
       </c>
       <c r="B664" t="s">
-        <v>610</v>
+        <v>952</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
-        <v>265</v>
+        <v>54</v>
       </c>
       <c r="B665" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
-        <v>971</v>
+        <v>265</v>
       </c>
       <c r="B666" t="s">
-        <v>970</v>
+        <v>611</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
-        <v>1397</v>
+        <v>971</v>
       </c>
       <c r="B667" t="s">
         <v>970</v>
@@ -10136,601 +10142,609 @@
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
-        <v>56</v>
+        <v>1397</v>
       </c>
       <c r="B668" t="s">
-        <v>612</v>
+        <v>970</v>
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
-        <v>1203</v>
+        <v>56</v>
       </c>
       <c r="B669" t="s">
-        <v>1204</v>
+        <v>612</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
-        <v>185</v>
+        <v>1203</v>
       </c>
       <c r="B670" t="s">
-        <v>613</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="B671" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="B672" t="s">
-        <v>1333</v>
+        <v>614</v>
       </c>
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
-        <v>1331</v>
+        <v>43</v>
       </c>
       <c r="B673" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
-        <v>1457</v>
+        <v>1331</v>
       </c>
       <c r="B674" t="s">
-        <v>1459</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B675" t="s">
         <v>1458</v>
-      </c>
-      <c r="B675" t="s">
-        <v>1460</v>
       </c>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
-        <v>40</v>
+        <v>1457</v>
       </c>
       <c r="B676" t="s">
-        <v>1112</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
-        <v>1329</v>
+        <v>40</v>
       </c>
       <c r="B677" t="s">
-        <v>1330</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
-        <v>1156</v>
+        <v>1329</v>
       </c>
       <c r="B678" t="s">
-        <v>1157</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
-        <v>165</v>
+        <v>1156</v>
       </c>
       <c r="B679" t="s">
-        <v>615</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
-        <v>1285</v>
+        <v>165</v>
       </c>
       <c r="B680" t="s">
-        <v>1286</v>
+        <v>615</v>
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="B681" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
-        <v>12</v>
+        <v>1287</v>
       </c>
       <c r="B682" t="s">
-        <v>11</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
-        <v>250</v>
+        <v>12</v>
       </c>
       <c r="B683" t="s">
-        <v>616</v>
+        <v>11</v>
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="B684" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
-        <v>1034</v>
+        <v>27</v>
       </c>
       <c r="B685" t="s">
-        <v>1035</v>
+        <v>617</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
-        <v>28</v>
+        <v>1034</v>
       </c>
       <c r="B686" t="s">
-        <v>618</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
-        <v>1191</v>
+        <v>28</v>
       </c>
       <c r="B687" t="s">
-        <v>1192</v>
+        <v>618</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
-        <v>255</v>
+        <v>1191</v>
       </c>
       <c r="B688" t="s">
-        <v>619</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
-        <v>1321</v>
+        <v>255</v>
       </c>
       <c r="B689" t="s">
-        <v>1326</v>
+        <v>619</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
-        <v>791</v>
+        <v>1321</v>
       </c>
       <c r="B690" t="s">
-        <v>792</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
-        <v>267</v>
+        <v>791</v>
       </c>
       <c r="B691" t="s">
-        <v>620</v>
+        <v>792</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
-        <v>657</v>
+        <v>267</v>
       </c>
       <c r="B692" t="s">
-        <v>740</v>
+        <v>620</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B693" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
-        <v>139</v>
+        <v>658</v>
       </c>
       <c r="B694" t="s">
-        <v>621</v>
+        <v>741</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="B695" t="s">
-        <v>2</v>
+        <v>621</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="B696" t="s">
-        <v>622</v>
+        <v>2</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
-        <v>1336</v>
+        <v>105</v>
       </c>
       <c r="B697" t="s">
-        <v>1337</v>
+        <v>622</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
-        <v>1028</v>
+        <v>1336</v>
       </c>
       <c r="B698" t="s">
-        <v>1111</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
-        <v>861</v>
+        <v>1028</v>
       </c>
       <c r="B699" t="s">
-        <v>862</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
-        <v>1437</v>
+        <v>861</v>
       </c>
       <c r="B700" t="s">
-        <v>1438</v>
+        <v>862</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
-        <v>1029</v>
+        <v>1436</v>
       </c>
       <c r="B701" t="s">
-        <v>1110</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
-        <v>292</v>
+        <v>1029</v>
       </c>
       <c r="B702" t="s">
-        <v>623</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
-        <v>8</v>
+        <v>292</v>
       </c>
       <c r="B703" t="s">
-        <v>11</v>
+        <v>623</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
-        <v>334</v>
+        <v>8</v>
       </c>
       <c r="B704" t="s">
-        <v>624</v>
+        <v>11</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
-        <v>1378</v>
+        <v>334</v>
       </c>
       <c r="B705" t="s">
-        <v>1379</v>
+        <v>624</v>
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
-        <v>1338</v>
+        <v>1378</v>
       </c>
       <c r="B706" t="s">
-        <v>1339</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
-        <v>331</v>
+        <v>1338</v>
       </c>
       <c r="B707" t="s">
-        <v>625</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="B708" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
-        <v>318</v>
+        <v>259</v>
       </c>
       <c r="B709" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
-        <v>855</v>
+        <v>318</v>
       </c>
       <c r="B710" t="s">
-        <v>856</v>
+        <v>627</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
-        <v>1160</v>
+        <v>855</v>
       </c>
       <c r="B711" t="s">
-        <v>1161</v>
+        <v>856</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
-        <v>268</v>
+        <v>1160</v>
       </c>
       <c r="B712" t="s">
-        <v>628</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B713" t="s">
-        <v>1105</v>
+        <v>628</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B714" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A715" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B715" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A716" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B716" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B717" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B718" t="s">
-        <v>1104</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
-        <v>92</v>
+        <v>272</v>
       </c>
       <c r="B719" t="s">
-        <v>629</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
-        <v>200</v>
+        <v>92</v>
       </c>
       <c r="B720" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B721" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
-        <v>1213</v>
+        <v>203</v>
       </c>
       <c r="B722" t="s">
-        <v>1214</v>
+        <v>631</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
-        <v>172</v>
+        <v>1213</v>
       </c>
       <c r="B723" t="s">
-        <v>632</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
-        <v>1470</v>
+        <v>172</v>
       </c>
       <c r="B724" t="s">
-        <v>1471</v>
+        <v>632</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B725" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A726" t="s">
         <v>689</v>
       </c>
-      <c r="B725" t="s">
+      <c r="B726" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="726" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A726" t="s">
+    <row r="727" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A727" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B727" s="1" t="s">
         <v>1465</v>
-      </c>
-      <c r="B726" s="1" t="s">
-        <v>1466</v>
-      </c>
-    </row>
-    <row r="727" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A727" t="s">
-        <v>252</v>
-      </c>
-      <c r="B727" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
-        <v>690</v>
+        <v>252</v>
       </c>
       <c r="B728" t="s">
-        <v>743</v>
+        <v>633</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
-        <v>189</v>
+        <v>690</v>
       </c>
       <c r="B729" t="s">
-        <v>1406</v>
+        <v>743</v>
       </c>
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A730" t="s">
-        <v>984</v>
+        <v>189</v>
       </c>
       <c r="B730" t="s">
-        <v>985</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
-        <v>311</v>
+        <v>984</v>
       </c>
       <c r="B731" t="s">
-        <v>634</v>
+        <v>985</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B732" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
-        <v>1027</v>
+        <v>312</v>
       </c>
       <c r="B733" t="s">
-        <v>1464</v>
+        <v>635</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B734" t="s">
         <v>1463</v>
-      </c>
-      <c r="B734" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
-        <v>1000</v>
+        <v>1462</v>
       </c>
       <c r="B735" t="s">
-        <v>1001</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
-        <v>81</v>
+        <v>1000</v>
       </c>
       <c r="B736" t="s">
-        <v>636</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A737" t="s">
-        <v>647</v>
+        <v>81</v>
       </c>
       <c r="B737" t="s">
-        <v>744</v>
+        <v>636</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
-        <v>917</v>
+        <v>647</v>
       </c>
       <c r="B738" t="s">
-        <v>918</v>
+        <v>744</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
-        <v>638</v>
+        <v>917</v>
       </c>
       <c r="B739" t="s">
-        <v>745</v>
+        <v>918</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A740" t="s">
-        <v>964</v>
+        <v>638</v>
       </c>
       <c r="B740" t="s">
-        <v>965</v>
+        <v>745</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
-        <v>1148</v>
+        <v>964</v>
       </c>
       <c r="B741" t="s">
-        <v>1149</v>
+        <v>965</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B742" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A743" t="s">
         <v>1376</v>
       </c>
-      <c r="B742" t="s">
+      <c r="B743" t="s">
         <v>1377</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A25A275-5D4D-46AB-95FB-23AFC20F9338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29D6600-9B72-4B6A-896F-8D1443D7C657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1233,9 +1233,6 @@
     <t>contralateral</t>
   </si>
   <si>
-    <t>centrilobular nodules with tree in bud pattern</t>
-  </si>
-  <si>
     <t>collapse consolidation</t>
   </si>
   <si>
@@ -3972,9 +3969,6 @@
     <t>cpe</t>
   </si>
   <si>
-    <t>Centriacinar and paraseptal emphysematous changes</t>
-  </si>
-  <si>
     <t>empc</t>
   </si>
   <si>
@@ -4453,6 +4447,12 @@
   </si>
   <si>
     <t>encasement</t>
+  </si>
+  <si>
+    <t>Centrilobular and paraseptal emphysematous changes</t>
+  </si>
+  <si>
+    <t>centrilobular nodules giving tree in bud pattern</t>
   </si>
 </sst>
 </file>
@@ -4822,50 +4822,50 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B3" t="s">
         <v>1182</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>938</v>
+      </c>
+      <c r="B4" t="s">
         <v>939</v>
-      </c>
-      <c r="B4" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>936</v>
+      </c>
+      <c r="B5" t="s">
         <v>937</v>
-      </c>
-      <c r="B5" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>940</v>
+      </c>
+      <c r="B6" t="s">
         <v>941</v>
-      </c>
-      <c r="B6" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>948</v>
+      </c>
+      <c r="B7" t="s">
         <v>949</v>
-      </c>
-      <c r="B7" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>899</v>
+      </c>
+      <c r="B8" t="s">
         <v>900</v>
-      </c>
-      <c r="B8" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -4878,18 +4878,18 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>918</v>
+      </c>
+      <c r="B10" t="s">
         <v>919</v>
-      </c>
-      <c r="B10" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>920</v>
+      </c>
+      <c r="B11" t="s">
         <v>921</v>
-      </c>
-      <c r="B11" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -4905,15 +4905,15 @@
         <v>307</v>
       </c>
       <c r="B13" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>876</v>
+      </c>
+      <c r="B14" t="s">
         <v>877</v>
-      </c>
-      <c r="B14" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -4926,58 +4926,58 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>901</v>
+      </c>
+      <c r="B16" t="s">
         <v>902</v>
-      </c>
-      <c r="B16" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>798</v>
+      </c>
+      <c r="B17" t="s">
         <v>799</v>
-      </c>
-      <c r="B17" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>979</v>
+      </c>
+      <c r="B18" t="s">
         <v>980</v>
-      </c>
-      <c r="B18" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B19" t="s">
         <v>1050</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>872</v>
+      </c>
+      <c r="B20" t="s">
         <v>873</v>
-      </c>
-      <c r="B20" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>763</v>
+      </c>
+      <c r="B21" t="s">
         <v>764</v>
-      </c>
-      <c r="B21" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B22" t="s">
         <v>1046</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
@@ -5014,26 +5014,26 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B27" t="s">
         <v>1021</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B28" t="s">
         <v>1014</v>
-      </c>
-      <c r="B28" t="s">
-        <v>1015</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B29" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
@@ -5046,18 +5046,18 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B31" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B32" t="s">
         <v>1168</v>
-      </c>
-      <c r="B32" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
@@ -5086,10 +5086,10 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B36" t="s">
         <v>1016</v>
-      </c>
-      <c r="B36" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
@@ -5118,10 +5118,10 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
+        <v>905</v>
+      </c>
+      <c r="B40" t="s">
         <v>906</v>
-      </c>
-      <c r="B40" t="s">
-        <v>907</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
@@ -5134,42 +5134,42 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B42" t="s">
         <v>1199</v>
-      </c>
-      <c r="B42" t="s">
-        <v>1200</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B43" t="s">
         <v>1196</v>
-      </c>
-      <c r="B43" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B44" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="B45" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B46" t="s">
         <v>1010</v>
-      </c>
-      <c r="B46" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
@@ -5217,15 +5217,15 @@
         <v>246</v>
       </c>
       <c r="B52" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B53" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
@@ -5238,34 +5238,34 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
+        <v>856</v>
+      </c>
+      <c r="B55" t="s">
         <v>857</v>
-      </c>
-      <c r="B55" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
+        <v>981</v>
+      </c>
+      <c r="B56" t="s">
         <v>982</v>
-      </c>
-      <c r="B56" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
+        <v>769</v>
+      </c>
+      <c r="B57" t="s">
         <v>770</v>
-      </c>
-      <c r="B57" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
+        <v>771</v>
+      </c>
+      <c r="B58" t="s">
         <v>772</v>
-      </c>
-      <c r="B58" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
@@ -5278,10 +5278,10 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B60" t="s">
         <v>1133</v>
-      </c>
-      <c r="B60" t="s">
-        <v>1134</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
@@ -5310,10 +5310,10 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
+        <v>784</v>
+      </c>
+      <c r="B64" t="s">
         <v>785</v>
-      </c>
-      <c r="B64" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
@@ -5326,10 +5326,10 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
+        <v>757</v>
+      </c>
+      <c r="B66" t="s">
         <v>758</v>
-      </c>
-      <c r="B66" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
@@ -5358,42 +5358,42 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="B70" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
+        <v>880</v>
+      </c>
+      <c r="B71" t="s">
         <v>881</v>
-      </c>
-      <c r="B71" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="B72" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B73" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="B74" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
@@ -5406,10 +5406,10 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B76" t="s">
         <v>1215</v>
-      </c>
-      <c r="B76" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
@@ -5422,138 +5422,138 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B78" t="s">
         <v>1008</v>
-      </c>
-      <c r="B78" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B79" t="s">
         <v>1225</v>
-      </c>
-      <c r="B79" t="s">
-        <v>1226</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B80" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B81" t="s">
         <v>1227</v>
-      </c>
-      <c r="B81" t="s">
-        <v>1228</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B82" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B83" t="s">
         <v>1229</v>
-      </c>
-      <c r="B83" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B84" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B85" t="s">
         <v>1231</v>
-      </c>
-      <c r="B85" t="s">
-        <v>1232</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B86" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B87" t="s">
         <v>1233</v>
-      </c>
-      <c r="B87" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B88" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="B89" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B90" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="B91" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B92" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="B93" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
+        <v>870</v>
+      </c>
+      <c r="B94" t="s">
         <v>871</v>
-      </c>
-      <c r="B94" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
@@ -5622,10 +5622,10 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
+        <v>893</v>
+      </c>
+      <c r="B103" t="s">
         <v>894</v>
-      </c>
-      <c r="B103" t="s">
-        <v>895</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
@@ -5646,10 +5646,10 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B106" t="s">
         <v>1145</v>
-      </c>
-      <c r="B106" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
@@ -5681,23 +5681,23 @@
         <v>41</v>
       </c>
       <c r="B110" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B111" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B112" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
@@ -5742,18 +5742,18 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="B118" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B119" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
@@ -5782,26 +5782,26 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B123" t="s">
         <v>1162</v>
-      </c>
-      <c r="B123" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
+        <v>874</v>
+      </c>
+      <c r="B124" t="s">
         <v>875</v>
-      </c>
-      <c r="B124" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
+        <v>802</v>
+      </c>
+      <c r="B125" t="s">
         <v>803</v>
-      </c>
-      <c r="B125" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
@@ -5814,10 +5814,10 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="B127" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
@@ -5846,10 +5846,10 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
+        <v>961</v>
+      </c>
+      <c r="B131" t="s">
         <v>962</v>
-      </c>
-      <c r="B131" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
@@ -5862,18 +5862,18 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
+        <v>959</v>
+      </c>
+      <c r="B133" t="s">
         <v>960</v>
-      </c>
-      <c r="B133" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="B134" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
@@ -5905,7 +5905,7 @@
         <v>104</v>
       </c>
       <c r="B138" t="s">
-        <v>401</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
@@ -5913,7 +5913,7 @@
         <v>163</v>
       </c>
       <c r="B139" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
@@ -5921,7 +5921,7 @@
         <v>101</v>
       </c>
       <c r="B140" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
@@ -5929,31 +5929,31 @@
         <v>102</v>
       </c>
       <c r="B141" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="B142" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
+        <v>924</v>
+      </c>
+      <c r="B143" t="s">
         <v>925</v>
-      </c>
-      <c r="B143" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
+        <v>922</v>
+      </c>
+      <c r="B144" t="s">
         <v>923</v>
-      </c>
-      <c r="B144" t="s">
-        <v>924</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
@@ -5961,279 +5961,279 @@
         <v>162</v>
       </c>
       <c r="B145" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B146" t="s">
         <v>1139</v>
-      </c>
-      <c r="B146" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="B147" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
+        <v>832</v>
+      </c>
+      <c r="B148" t="s">
         <v>833</v>
-      </c>
-      <c r="B148" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
+        <v>834</v>
+      </c>
+      <c r="B149" t="s">
         <v>835</v>
-      </c>
-      <c r="B149" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="B150" t="s">
-        <v>1314</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B151" t="s">
         <v>1076</v>
-      </c>
-      <c r="B151" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B152" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B153" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
+        <v>934</v>
+      </c>
+      <c r="B154" t="s">
         <v>935</v>
-      </c>
-      <c r="B154" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="B155" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="B156" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B157" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="B158" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B159" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B160" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B161" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="B162" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B163" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B164" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B165" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="B166" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B167" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="B168" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B169" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="B170" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B171" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="B172" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B173" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="B174" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B175" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B176" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B177" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B178" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B179" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
@@ -6241,7 +6241,7 @@
         <v>175</v>
       </c>
       <c r="B180" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
@@ -6249,7 +6249,7 @@
         <v>211</v>
       </c>
       <c r="B181" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
@@ -6257,31 +6257,31 @@
         <v>213</v>
       </c>
       <c r="B182" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B183" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="B184" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B185" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
@@ -6289,7 +6289,7 @@
         <v>149</v>
       </c>
       <c r="B186" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
@@ -6297,7 +6297,7 @@
         <v>247</v>
       </c>
       <c r="B187" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
@@ -6305,7 +6305,7 @@
         <v>245</v>
       </c>
       <c r="B188" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
@@ -6313,15 +6313,15 @@
         <v>335</v>
       </c>
       <c r="B189" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B190" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
@@ -6329,7 +6329,7 @@
         <v>91</v>
       </c>
       <c r="B191" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
@@ -6337,39 +6337,39 @@
         <v>266</v>
       </c>
       <c r="B192" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B193" t="s">
         <v>1088</v>
-      </c>
-      <c r="B193" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
+        <v>794</v>
+      </c>
+      <c r="B194" t="s">
         <v>795</v>
-      </c>
-      <c r="B194" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B195" t="s">
         <v>1154</v>
-      </c>
-      <c r="B195" t="s">
-        <v>1155</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="B196" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
@@ -6377,23 +6377,23 @@
         <v>295</v>
       </c>
       <c r="B197" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B198" t="s">
         <v>1078</v>
-      </c>
-      <c r="B198" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B199" t="s">
         <v>1084</v>
-      </c>
-      <c r="B199" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
@@ -6401,63 +6401,63 @@
         <v>151</v>
       </c>
       <c r="B200" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
+        <v>955</v>
+      </c>
+      <c r="B201" t="s">
         <v>956</v>
-      </c>
-      <c r="B201" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
+        <v>808</v>
+      </c>
+      <c r="B202" t="s">
         <v>809</v>
-      </c>
-      <c r="B202" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
+        <v>926</v>
+      </c>
+      <c r="B203" t="s">
         <v>927</v>
-      </c>
-      <c r="B203" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
+        <v>828</v>
+      </c>
+      <c r="B204" t="s">
         <v>829</v>
-      </c>
-      <c r="B204" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
+        <v>788</v>
+      </c>
+      <c r="B205" t="s">
         <v>789</v>
-      </c>
-      <c r="B205" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="B206" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
+        <v>749</v>
+      </c>
+      <c r="B207" t="s">
         <v>750</v>
-      </c>
-      <c r="B207" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
@@ -6465,15 +6465,15 @@
         <v>100</v>
       </c>
       <c r="B208" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B209" t="s">
         <v>1036</v>
-      </c>
-      <c r="B209" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
@@ -6481,7 +6481,7 @@
         <v>154</v>
       </c>
       <c r="B210" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
@@ -6489,7 +6489,7 @@
         <v>157</v>
       </c>
       <c r="B211" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
@@ -6497,47 +6497,47 @@
         <v>24</v>
       </c>
       <c r="B212" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B213" t="s">
         <v>1150</v>
-      </c>
-      <c r="B213" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B214" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B215" t="s">
         <v>1068</v>
-      </c>
-      <c r="B215" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="B216" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
+        <v>814</v>
+      </c>
+      <c r="B217" t="s">
         <v>815</v>
-      </c>
-      <c r="B217" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
@@ -6545,7 +6545,7 @@
         <v>130</v>
       </c>
       <c r="B218" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
@@ -6553,47 +6553,47 @@
         <v>321</v>
       </c>
       <c r="B219" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="B220" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
+        <v>862</v>
+      </c>
+      <c r="B221" t="s">
         <v>863</v>
-      </c>
-      <c r="B221" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="B222" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="B223" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B224" t="s">
         <v>1303</v>
-      </c>
-      <c r="B224" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
@@ -6601,39 +6601,39 @@
         <v>183</v>
       </c>
       <c r="B225" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B226" t="s">
         <v>1141</v>
-      </c>
-      <c r="B226" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B227" t="s">
         <v>1143</v>
-      </c>
-      <c r="B227" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="B228" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="B229" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
@@ -6641,7 +6641,7 @@
         <v>32</v>
       </c>
       <c r="B230" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
@@ -6649,31 +6649,31 @@
         <v>35</v>
       </c>
       <c r="B231" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B232" t="s">
         <v>1293</v>
-      </c>
-      <c r="B232" t="s">
-        <v>1294</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B233" t="s">
         <v>1219</v>
-      </c>
-      <c r="B233" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B234" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
@@ -6681,7 +6681,7 @@
         <v>169</v>
       </c>
       <c r="B235" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
@@ -6689,23 +6689,23 @@
         <v>170</v>
       </c>
       <c r="B236" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B237" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="B238" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
@@ -6713,7 +6713,7 @@
         <v>178</v>
       </c>
       <c r="B239" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
@@ -6721,7 +6721,7 @@
         <v>111</v>
       </c>
       <c r="B240" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
@@ -6729,7 +6729,7 @@
         <v>238</v>
       </c>
       <c r="B241" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
@@ -6737,7 +6737,7 @@
         <v>106</v>
       </c>
       <c r="B242" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
@@ -6745,7 +6745,7 @@
         <v>109</v>
       </c>
       <c r="B243" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
@@ -6753,15 +6753,15 @@
         <v>179</v>
       </c>
       <c r="B244" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B245" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
@@ -6769,7 +6769,7 @@
         <v>97</v>
       </c>
       <c r="B246" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
@@ -6777,7 +6777,7 @@
         <v>110</v>
       </c>
       <c r="B247" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
@@ -6785,7 +6785,7 @@
         <v>242</v>
       </c>
       <c r="B248" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
@@ -6793,7 +6793,7 @@
         <v>226</v>
       </c>
       <c r="B249" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
@@ -6801,15 +6801,15 @@
         <v>177</v>
       </c>
       <c r="B250" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="B251" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
@@ -6817,55 +6817,55 @@
         <v>182</v>
       </c>
       <c r="B252" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B253" t="s">
         <v>1098</v>
-      </c>
-      <c r="B253" t="s">
-        <v>1099</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
+        <v>971</v>
+      </c>
+      <c r="B254" t="s">
         <v>972</v>
-      </c>
-      <c r="B254" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
+        <v>973</v>
+      </c>
+      <c r="B255" t="s">
         <v>974</v>
-      </c>
-      <c r="B255" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B256" t="s">
         <v>1184</v>
-      </c>
-      <c r="B256" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B257" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B258" t="s">
         <v>1187</v>
-      </c>
-      <c r="B258" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
@@ -6873,7 +6873,7 @@
         <v>253</v>
       </c>
       <c r="B259" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
@@ -6881,15 +6881,15 @@
         <v>34</v>
       </c>
       <c r="B260" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
+        <v>782</v>
+      </c>
+      <c r="B261" t="s">
         <v>783</v>
-      </c>
-      <c r="B261" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
@@ -6897,31 +6897,31 @@
         <v>180</v>
       </c>
       <c r="B262" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="B263" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="B264" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="B265" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
@@ -6929,15 +6929,15 @@
         <v>275</v>
       </c>
       <c r="B266" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
+        <v>852</v>
+      </c>
+      <c r="B267" t="s">
         <v>853</v>
-      </c>
-      <c r="B267" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
@@ -6945,7 +6945,7 @@
         <v>116</v>
       </c>
       <c r="B268" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
@@ -6953,31 +6953,31 @@
         <v>208</v>
       </c>
       <c r="B269" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="B270" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B271" t="s">
         <v>1207</v>
-      </c>
-      <c r="B271" t="s">
-        <v>1208</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B272" t="s">
         <v>1048</v>
-      </c>
-      <c r="B272" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
@@ -6985,31 +6985,31 @@
         <v>118</v>
       </c>
       <c r="B273" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B274" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="B275" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
+        <v>810</v>
+      </c>
+      <c r="B276" t="s">
         <v>811</v>
-      </c>
-      <c r="B276" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
@@ -7017,31 +7017,31 @@
         <v>298</v>
       </c>
       <c r="B277" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B278" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B279" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B280" t="s">
         <v>1030</v>
-      </c>
-      <c r="B280" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
@@ -7049,7 +7049,7 @@
         <v>90</v>
       </c>
       <c r="B281" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
@@ -7057,7 +7057,7 @@
         <v>88</v>
       </c>
       <c r="B282" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
@@ -7065,15 +7065,15 @@
         <v>89</v>
       </c>
       <c r="B283" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B284" t="s">
         <v>1064</v>
-      </c>
-      <c r="B284" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
@@ -7081,15 +7081,15 @@
         <v>23</v>
       </c>
       <c r="B285" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="B286" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
@@ -7102,10 +7102,10 @@
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B288" t="s">
         <v>1128</v>
-      </c>
-      <c r="B288" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
@@ -7113,15 +7113,15 @@
         <v>126</v>
       </c>
       <c r="B289" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="B290" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
@@ -7129,7 +7129,7 @@
         <v>128</v>
       </c>
       <c r="B291" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
@@ -7137,7 +7137,7 @@
         <v>131</v>
       </c>
       <c r="B292" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
@@ -7145,7 +7145,7 @@
         <v>132</v>
       </c>
       <c r="B293" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
@@ -7153,7 +7153,7 @@
         <v>119</v>
       </c>
       <c r="B294" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
@@ -7161,15 +7161,15 @@
         <v>277</v>
       </c>
       <c r="B295" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B296" t="s">
         <v>1066</v>
-      </c>
-      <c r="B296" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
@@ -7185,7 +7185,7 @@
         <v>129</v>
       </c>
       <c r="B298" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
@@ -7193,7 +7193,7 @@
         <v>127</v>
       </c>
       <c r="B299" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
@@ -7201,7 +7201,7 @@
         <v>173</v>
       </c>
       <c r="B300" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
@@ -7209,15 +7209,15 @@
         <v>262</v>
       </c>
       <c r="B301" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="B302" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
@@ -7225,23 +7225,23 @@
         <v>77</v>
       </c>
       <c r="B303" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
+        <v>932</v>
+      </c>
+      <c r="B304" t="s">
         <v>933</v>
-      </c>
-      <c r="B304" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B305" t="s">
         <v>1158</v>
-      </c>
-      <c r="B305" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
@@ -7249,39 +7249,39 @@
         <v>168</v>
       </c>
       <c r="B306" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="B307" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="B308" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B309" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="B310" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
@@ -7289,55 +7289,55 @@
         <v>167</v>
       </c>
       <c r="B311" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="B312" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="B313" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B314" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="B315" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
+        <v>830</v>
+      </c>
+      <c r="B316" t="s">
         <v>831</v>
-      </c>
-      <c r="B316" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
+        <v>786</v>
+      </c>
+      <c r="B317" t="s">
         <v>787</v>
-      </c>
-      <c r="B317" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
@@ -7345,39 +7345,39 @@
         <v>304</v>
       </c>
       <c r="B318" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
+        <v>753</v>
+      </c>
+      <c r="B319" t="s">
         <v>754</v>
-      </c>
-      <c r="B319" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
+        <v>891</v>
+      </c>
+      <c r="B320" t="s">
         <v>892</v>
-      </c>
-      <c r="B320" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="B321" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B322" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
@@ -7385,7 +7385,7 @@
         <v>86</v>
       </c>
       <c r="B323" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
@@ -7393,7 +7393,7 @@
         <v>87</v>
       </c>
       <c r="B324" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
@@ -7401,7 +7401,7 @@
         <v>153</v>
       </c>
       <c r="B325" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
@@ -7409,7 +7409,7 @@
         <v>156</v>
       </c>
       <c r="B326" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
@@ -7417,7 +7417,7 @@
         <v>158</v>
       </c>
       <c r="B327" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
@@ -7425,7 +7425,7 @@
         <v>251</v>
       </c>
       <c r="B328" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
@@ -7433,7 +7433,7 @@
         <v>285</v>
       </c>
       <c r="B329" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
@@ -7441,15 +7441,15 @@
         <v>325</v>
       </c>
       <c r="B330" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="B331" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
@@ -7457,7 +7457,7 @@
         <v>326</v>
       </c>
       <c r="B332" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
@@ -7465,7 +7465,7 @@
         <v>229</v>
       </c>
       <c r="B333" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
@@ -7473,15 +7473,15 @@
         <v>55</v>
       </c>
       <c r="B334" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B335" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
@@ -7489,7 +7489,7 @@
         <v>235</v>
       </c>
       <c r="B336" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
@@ -7497,7 +7497,7 @@
         <v>57</v>
       </c>
       <c r="B337" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
@@ -7505,23 +7505,23 @@
         <v>236</v>
       </c>
       <c r="B338" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
+        <v>761</v>
+      </c>
+      <c r="B339" t="s">
         <v>762</v>
-      </c>
-      <c r="B339" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B340" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
@@ -7529,15 +7529,15 @@
         <v>164</v>
       </c>
       <c r="B341" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="B342" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
@@ -7545,7 +7545,7 @@
         <v>201</v>
       </c>
       <c r="B343" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
@@ -7553,7 +7553,7 @@
         <v>204</v>
       </c>
       <c r="B344" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
@@ -7561,31 +7561,31 @@
         <v>313</v>
       </c>
       <c r="B345" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
+        <v>868</v>
+      </c>
+      <c r="B346" t="s">
         <v>869</v>
-      </c>
-      <c r="B346" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
+        <v>991</v>
+      </c>
+      <c r="B347" t="s">
         <v>992</v>
-      </c>
-      <c r="B347" t="s">
-        <v>993</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="B348" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
@@ -7593,23 +7593,23 @@
         <v>258</v>
       </c>
       <c r="B349" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
+        <v>977</v>
+      </c>
+      <c r="B350" t="s">
         <v>978</v>
-      </c>
-      <c r="B350" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="B351" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
@@ -7617,47 +7617,47 @@
         <v>160</v>
       </c>
       <c r="B352" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B353" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B354" t="s">
         <v>1152</v>
-      </c>
-      <c r="B354" t="s">
-        <v>1153</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
+        <v>755</v>
+      </c>
+      <c r="B355" t="s">
         <v>756</v>
-      </c>
-      <c r="B355" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
+        <v>889</v>
+      </c>
+      <c r="B356" t="s">
         <v>890</v>
-      </c>
-      <c r="B356" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
+        <v>887</v>
+      </c>
+      <c r="B357" t="s">
         <v>888</v>
-      </c>
-      <c r="B357" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
@@ -7665,7 +7665,7 @@
         <v>184</v>
       </c>
       <c r="B358" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
@@ -7673,7 +7673,7 @@
         <v>244</v>
       </c>
       <c r="B359" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
@@ -7681,95 +7681,95 @@
         <v>243</v>
       </c>
       <c r="B360" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="B361" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B362" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="B363" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B364" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="B365" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B366" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B367" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B368" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="B369" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B370" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B371" t="s">
         <v>1178</v>
-      </c>
-      <c r="B371" t="s">
-        <v>1179</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
@@ -7777,7 +7777,7 @@
         <v>280</v>
       </c>
       <c r="B372" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
@@ -7785,7 +7785,7 @@
         <v>281</v>
       </c>
       <c r="B373" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
@@ -7793,7 +7793,7 @@
         <v>49</v>
       </c>
       <c r="B374" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
@@ -7801,7 +7801,7 @@
         <v>53</v>
       </c>
       <c r="B375" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
@@ -7809,15 +7809,15 @@
         <v>136</v>
       </c>
       <c r="B376" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="B377" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
@@ -7825,15 +7825,15 @@
         <v>72</v>
       </c>
       <c r="B378" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B379" t="s">
         <v>1176</v>
-      </c>
-      <c r="B379" t="s">
-        <v>1177</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
@@ -7841,15 +7841,15 @@
         <v>221</v>
       </c>
       <c r="B380" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B381" t="s">
         <v>1180</v>
-      </c>
-      <c r="B381" t="s">
-        <v>1181</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
@@ -7862,18 +7862,18 @@
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B383" t="s">
         <v>1052</v>
-      </c>
-      <c r="B383" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
+        <v>914</v>
+      </c>
+      <c r="B384" t="s">
         <v>915</v>
-      </c>
-      <c r="B384" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
@@ -7881,7 +7881,7 @@
         <v>108</v>
       </c>
       <c r="B385" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
@@ -7889,7 +7889,7 @@
         <v>241</v>
       </c>
       <c r="B386" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
@@ -7897,23 +7897,23 @@
         <v>327</v>
       </c>
       <c r="B387" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B388" t="s">
         <v>1092</v>
-      </c>
-      <c r="B388" t="s">
-        <v>1093</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B389" t="s">
         <v>1044</v>
-      </c>
-      <c r="B389" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
@@ -7921,23 +7921,23 @@
         <v>121</v>
       </c>
       <c r="B390" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
+        <v>745</v>
+      </c>
+      <c r="B391" t="s">
         <v>746</v>
-      </c>
-      <c r="B391" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
+        <v>776</v>
+      </c>
+      <c r="B392" t="s">
         <v>777</v>
-      </c>
-      <c r="B392" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
@@ -7945,7 +7945,7 @@
         <v>134</v>
       </c>
       <c r="B393" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
@@ -7953,15 +7953,15 @@
         <v>63</v>
       </c>
       <c r="B394" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B395" t="s">
         <v>1299</v>
-      </c>
-      <c r="B395" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
@@ -7969,7 +7969,7 @@
         <v>224</v>
       </c>
       <c r="B396" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
@@ -7977,7 +7977,7 @@
         <v>25</v>
       </c>
       <c r="B397" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
@@ -7985,7 +7985,7 @@
         <v>26</v>
       </c>
       <c r="B398" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
@@ -7993,23 +7993,23 @@
         <v>207</v>
       </c>
       <c r="B399" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B400" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B401" t="s">
         <v>1101</v>
-      </c>
-      <c r="B401" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
@@ -8017,7 +8017,7 @@
         <v>206</v>
       </c>
       <c r="B402" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
@@ -8025,7 +8025,7 @@
         <v>202</v>
       </c>
       <c r="B403" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
@@ -8033,7 +8033,7 @@
         <v>205</v>
       </c>
       <c r="B404" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
@@ -8041,15 +8041,15 @@
         <v>145</v>
       </c>
       <c r="B405" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B406" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
@@ -8057,15 +8057,15 @@
         <v>171</v>
       </c>
       <c r="B407" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B408" t="s">
         <v>1080</v>
-      </c>
-      <c r="B408" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
@@ -8073,15 +8073,15 @@
         <v>263</v>
       </c>
       <c r="B409" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B410" t="s">
         <v>1082</v>
-      </c>
-      <c r="B410" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
@@ -8089,7 +8089,7 @@
         <v>80</v>
       </c>
       <c r="B411" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
@@ -8097,7 +8097,7 @@
         <v>65</v>
       </c>
       <c r="B412" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
@@ -8105,7 +8105,7 @@
         <v>191</v>
       </c>
       <c r="B413" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
@@ -8113,7 +8113,7 @@
         <v>123</v>
       </c>
       <c r="B414" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
@@ -8121,7 +8121,7 @@
         <v>192</v>
       </c>
       <c r="B415" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
@@ -8129,7 +8129,7 @@
         <v>231</v>
       </c>
       <c r="B416" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
@@ -8137,15 +8137,15 @@
         <v>233</v>
       </c>
       <c r="B417" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B418" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
@@ -8153,7 +8153,7 @@
         <v>31</v>
       </c>
       <c r="B419" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
@@ -8161,7 +8161,7 @@
         <v>30</v>
       </c>
       <c r="B420" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
@@ -8169,7 +8169,7 @@
         <v>37</v>
       </c>
       <c r="B421" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
@@ -8177,15 +8177,15 @@
         <v>71</v>
       </c>
       <c r="B422" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="B423" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
@@ -8193,7 +8193,7 @@
         <v>306</v>
       </c>
       <c r="B424" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
@@ -8201,7 +8201,7 @@
         <v>222</v>
       </c>
       <c r="B425" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
@@ -8209,7 +8209,7 @@
         <v>278</v>
       </c>
       <c r="B426" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
@@ -8217,23 +8217,23 @@
         <v>279</v>
       </c>
       <c r="B427" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="B428" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
+        <v>826</v>
+      </c>
+      <c r="B429" t="s">
         <v>827</v>
-      </c>
-      <c r="B429" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
@@ -8241,7 +8241,7 @@
         <v>48</v>
       </c>
       <c r="B430" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
@@ -8249,7 +8249,7 @@
         <v>146</v>
       </c>
       <c r="B431" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
@@ -8257,15 +8257,15 @@
         <v>52</v>
       </c>
       <c r="B432" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="B433" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
@@ -8273,31 +8273,31 @@
         <v>223</v>
       </c>
       <c r="B434" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B435" t="s">
         <v>1086</v>
-      </c>
-      <c r="B435" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B436" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B437" t="s">
         <v>1042</v>
-      </c>
-      <c r="B437" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
@@ -8305,7 +8305,7 @@
         <v>96</v>
       </c>
       <c r="B438" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
@@ -8313,7 +8313,7 @@
         <v>248</v>
       </c>
       <c r="B439" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
@@ -8321,7 +8321,7 @@
         <v>249</v>
       </c>
       <c r="B440" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
@@ -8329,15 +8329,15 @@
         <v>94</v>
       </c>
       <c r="B441" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B442" t="s">
         <v>1056</v>
-      </c>
-      <c r="B442" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
@@ -8345,39 +8345,39 @@
         <v>212</v>
       </c>
       <c r="B443" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B444" t="s">
         <v>1211</v>
-      </c>
-      <c r="B444" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
+        <v>910</v>
+      </c>
+      <c r="B445" t="s">
         <v>911</v>
-      </c>
-      <c r="B445" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
+        <v>908</v>
+      </c>
+      <c r="B446" t="s">
         <v>909</v>
-      </c>
-      <c r="B446" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
+        <v>912</v>
+      </c>
+      <c r="B447" t="s">
         <v>913</v>
-      </c>
-      <c r="B447" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
@@ -8385,63 +8385,63 @@
         <v>329</v>
       </c>
       <c r="B448" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="B449" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="B450" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B451" t="s">
         <v>1058</v>
-      </c>
-      <c r="B451" t="s">
-        <v>1059</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
+        <v>989</v>
+      </c>
+      <c r="B452" t="s">
         <v>990</v>
-      </c>
-      <c r="B452" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="B453" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
+        <v>985</v>
+      </c>
+      <c r="B454" t="s">
         <v>986</v>
-      </c>
-      <c r="B454" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
+        <v>987</v>
+      </c>
+      <c r="B455" t="s">
         <v>988</v>
-      </c>
-      <c r="B455" t="s">
-        <v>989</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
@@ -8449,15 +8449,15 @@
         <v>82</v>
       </c>
       <c r="B456" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
+        <v>767</v>
+      </c>
+      <c r="B457" t="s">
         <v>768</v>
-      </c>
-      <c r="B457" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
@@ -8465,47 +8465,47 @@
         <v>197</v>
       </c>
       <c r="B458" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B459" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="B460" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="B461" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
+        <v>816</v>
+      </c>
+      <c r="B462" t="s">
         <v>817</v>
-      </c>
-      <c r="B462" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B463" t="s">
         <v>1060</v>
-      </c>
-      <c r="B463" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
@@ -8518,7 +8518,7 @@
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B465" t="s">
         <v>4</v>
@@ -8526,7 +8526,7 @@
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B466" t="s">
         <v>4</v>
@@ -8534,26 +8534,26 @@
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B467" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B468" t="s">
         <v>1291</v>
-      </c>
-      <c r="B468" t="s">
-        <v>1292</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
+        <v>765</v>
+      </c>
+      <c r="B469" t="s">
         <v>766</v>
-      </c>
-      <c r="B469" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
@@ -8561,31 +8561,31 @@
         <v>85</v>
       </c>
       <c r="B470" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B471" t="s">
         <v>1054</v>
-      </c>
-      <c r="B471" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
+        <v>824</v>
+      </c>
+      <c r="B472" t="s">
         <v>825</v>
-      </c>
-      <c r="B472" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
+        <v>804</v>
+      </c>
+      <c r="B473" t="s">
         <v>805</v>
-      </c>
-      <c r="B473" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
@@ -8593,71 +8593,71 @@
         <v>187</v>
       </c>
       <c r="B474" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
+        <v>822</v>
+      </c>
+      <c r="B475" t="s">
         <v>823</v>
-      </c>
-      <c r="B475" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B476" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="B477" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
+        <v>858</v>
+      </c>
+      <c r="B478" t="s">
         <v>859</v>
-      </c>
-      <c r="B478" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="B479" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B480" t="s">
         <v>1038</v>
-      </c>
-      <c r="B480" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B481" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B482" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
@@ -8670,18 +8670,18 @@
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
+        <v>812</v>
+      </c>
+      <c r="B484" t="s">
         <v>813</v>
-      </c>
-      <c r="B484" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B485" t="s">
         <v>1221</v>
-      </c>
-      <c r="B485" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
@@ -8689,15 +8689,15 @@
         <v>186</v>
       </c>
       <c r="B486" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
+        <v>806</v>
+      </c>
+      <c r="B487" t="s">
         <v>807</v>
-      </c>
-      <c r="B487" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
@@ -8705,47 +8705,47 @@
         <v>319</v>
       </c>
       <c r="B488" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B489" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
+        <v>850</v>
+      </c>
+      <c r="B490" t="s">
         <v>851</v>
-      </c>
-      <c r="B490" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B491" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B492" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B493" t="s">
         <v>1193</v>
-      </c>
-      <c r="B493" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
@@ -8753,7 +8753,7 @@
         <v>256</v>
       </c>
       <c r="B494" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
@@ -8761,7 +8761,7 @@
         <v>260</v>
       </c>
       <c r="B495" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
@@ -8769,7 +8769,7 @@
         <v>261</v>
       </c>
       <c r="B496" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
@@ -8777,7 +8777,7 @@
         <v>188</v>
       </c>
       <c r="B497" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
@@ -8785,31 +8785,31 @@
         <v>190</v>
       </c>
       <c r="B498" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
+        <v>930</v>
+      </c>
+      <c r="B499" t="s">
         <v>931</v>
-      </c>
-      <c r="B499" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B500" t="s">
         <v>1025</v>
-      </c>
-      <c r="B500" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B501" t="s">
         <v>1209</v>
-      </c>
-      <c r="B501" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
@@ -8817,31 +8817,31 @@
         <v>209</v>
       </c>
       <c r="B502" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="B503" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B504" t="s">
         <v>1301</v>
-      </c>
-      <c r="B504" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
+        <v>846</v>
+      </c>
+      <c r="B505" t="s">
         <v>847</v>
-      </c>
-      <c r="B505" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
@@ -8849,7 +8849,7 @@
         <v>143</v>
       </c>
       <c r="B506" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
@@ -8857,23 +8857,23 @@
         <v>140</v>
       </c>
       <c r="B507" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B508" t="s">
         <v>1189</v>
-      </c>
-      <c r="B508" t="s">
-        <v>1190</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B509" t="s">
         <v>1289</v>
-      </c>
-      <c r="B509" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
@@ -8881,7 +8881,7 @@
         <v>254</v>
       </c>
       <c r="B510" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
@@ -8889,7 +8889,7 @@
         <v>330</v>
       </c>
       <c r="B511" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
@@ -8897,7 +8897,7 @@
         <v>210</v>
       </c>
       <c r="B512" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
@@ -8905,7 +8905,7 @@
         <v>234</v>
       </c>
       <c r="B513" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
@@ -8913,7 +8913,7 @@
         <v>73</v>
       </c>
       <c r="B514" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
@@ -8921,7 +8921,7 @@
         <v>341</v>
       </c>
       <c r="B515" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
@@ -8929,23 +8929,23 @@
         <v>308</v>
       </c>
       <c r="B516" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
+        <v>838</v>
+      </c>
+      <c r="B517" t="s">
         <v>839</v>
-      </c>
-      <c r="B517" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
+        <v>840</v>
+      </c>
+      <c r="B518" t="s">
         <v>841</v>
-      </c>
-      <c r="B518" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
@@ -8953,39 +8953,39 @@
         <v>220</v>
       </c>
       <c r="B519" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
+        <v>903</v>
+      </c>
+      <c r="B520" t="s">
         <v>904</v>
-      </c>
-      <c r="B520" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="B521" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
+        <v>957</v>
+      </c>
+      <c r="B522" t="s">
         <v>958</v>
-      </c>
-      <c r="B522" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B523" t="s">
         <v>1174</v>
-      </c>
-      <c r="B523" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
@@ -8993,7 +8993,7 @@
         <v>227</v>
       </c>
       <c r="B524" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
@@ -9001,23 +9001,23 @@
         <v>333</v>
       </c>
       <c r="B525" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
+        <v>965</v>
+      </c>
+      <c r="B526" t="s">
         <v>966</v>
-      </c>
-      <c r="B526" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
+        <v>773</v>
+      </c>
+      <c r="B527" t="s">
         <v>774</v>
-      </c>
-      <c r="B527" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
@@ -9025,15 +9025,15 @@
         <v>294</v>
       </c>
       <c r="B528" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
+        <v>946</v>
+      </c>
+      <c r="B529" t="s">
         <v>947</v>
-      </c>
-      <c r="B529" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
@@ -9041,23 +9041,23 @@
         <v>338</v>
       </c>
       <c r="B530" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B531" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B532" t="s">
         <v>1305</v>
-      </c>
-      <c r="B532" t="s">
-        <v>1306</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
@@ -9065,7 +9065,7 @@
         <v>339</v>
       </c>
       <c r="B533" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
@@ -9073,15 +9073,15 @@
         <v>340</v>
       </c>
       <c r="B534" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B535" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
@@ -9089,7 +9089,7 @@
         <v>39</v>
       </c>
       <c r="B536" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
@@ -9097,7 +9097,7 @@
         <v>38</v>
       </c>
       <c r="B537" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
@@ -9105,7 +9105,7 @@
         <v>342</v>
       </c>
       <c r="B538" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
@@ -9113,31 +9113,31 @@
         <v>107</v>
       </c>
       <c r="B539" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="B540" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B541" t="s">
         <v>1023</v>
-      </c>
-      <c r="B541" t="s">
-        <v>1024</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
+        <v>897</v>
+      </c>
+      <c r="B542" t="s">
         <v>898</v>
-      </c>
-      <c r="B542" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
@@ -9145,15 +9145,15 @@
         <v>117</v>
       </c>
       <c r="B543" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B544" t="s">
         <v>1019</v>
-      </c>
-      <c r="B544" t="s">
-        <v>1020</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
@@ -9161,7 +9161,7 @@
         <v>98</v>
       </c>
       <c r="B545" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
@@ -9169,31 +9169,31 @@
         <v>99</v>
       </c>
       <c r="B546" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B547" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B548" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
+        <v>818</v>
+      </c>
+      <c r="B549" t="s">
         <v>819</v>
-      </c>
-      <c r="B549" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
@@ -9201,15 +9201,15 @@
         <v>113</v>
       </c>
       <c r="B550" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
+        <v>884</v>
+      </c>
+      <c r="B551" t="s">
         <v>885</v>
-      </c>
-      <c r="B551" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
@@ -9217,7 +9217,7 @@
         <v>45</v>
       </c>
       <c r="B552" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
@@ -9225,7 +9225,7 @@
         <v>290</v>
       </c>
       <c r="B553" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
@@ -9233,7 +9233,7 @@
         <v>299</v>
       </c>
       <c r="B554" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
@@ -9241,15 +9241,15 @@
         <v>47</v>
       </c>
       <c r="B555" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
+        <v>842</v>
+      </c>
+      <c r="B556" t="s">
         <v>843</v>
-      </c>
-      <c r="B556" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
@@ -9257,15 +9257,15 @@
         <v>51</v>
       </c>
       <c r="B557" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
+        <v>866</v>
+      </c>
+      <c r="B558" t="s">
         <v>867</v>
-      </c>
-      <c r="B558" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
@@ -9273,15 +9273,15 @@
         <v>114</v>
       </c>
       <c r="B559" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
+        <v>848</v>
+      </c>
+      <c r="B560" t="s">
         <v>849</v>
-      </c>
-      <c r="B560" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
@@ -9289,15 +9289,15 @@
         <v>144</v>
       </c>
       <c r="B561" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B562" t="s">
         <v>1072</v>
-      </c>
-      <c r="B562" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
@@ -9305,7 +9305,7 @@
         <v>176</v>
       </c>
       <c r="B563" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
@@ -9313,7 +9313,7 @@
         <v>315</v>
       </c>
       <c r="B564" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
@@ -9321,23 +9321,23 @@
         <v>29</v>
       </c>
       <c r="B565" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B566" t="s">
         <v>1012</v>
-      </c>
-      <c r="B566" t="s">
-        <v>1013</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B567" t="s">
         <v>1217</v>
-      </c>
-      <c r="B567" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
@@ -9345,23 +9345,23 @@
         <v>293</v>
       </c>
       <c r="B568" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
+        <v>975</v>
+      </c>
+      <c r="B569" t="s">
         <v>976</v>
-      </c>
-      <c r="B569" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="B570" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
@@ -9369,23 +9369,23 @@
         <v>301</v>
       </c>
       <c r="B571" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
+        <v>997</v>
+      </c>
+      <c r="B572" t="s">
         <v>998</v>
-      </c>
-      <c r="B572" t="s">
-        <v>999</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B573" t="s">
         <v>1002</v>
-      </c>
-      <c r="B573" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
@@ -9393,7 +9393,7 @@
         <v>75</v>
       </c>
       <c r="B574" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
@@ -9401,7 +9401,7 @@
         <v>76</v>
       </c>
       <c r="B575" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
@@ -9409,7 +9409,7 @@
         <v>78</v>
       </c>
       <c r="B576" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
@@ -9417,47 +9417,47 @@
         <v>328</v>
       </c>
       <c r="B577" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="B578" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B579" t="s">
         <v>1295</v>
-      </c>
-      <c r="B579" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
+        <v>747</v>
+      </c>
+      <c r="B580" t="s">
         <v>748</v>
-      </c>
-      <c r="B580" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
+        <v>800</v>
+      </c>
+      <c r="B581" t="s">
         <v>801</v>
-      </c>
-      <c r="B581" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B582" t="s">
         <v>1308</v>
-      </c>
-      <c r="B582" t="s">
-        <v>1309</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
@@ -9465,23 +9465,23 @@
         <v>135</v>
       </c>
       <c r="B583" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B584" t="s">
         <v>1172</v>
-      </c>
-      <c r="B584" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B585" t="s">
         <v>1032</v>
-      </c>
-      <c r="B585" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
@@ -9489,15 +9489,15 @@
         <v>215</v>
       </c>
       <c r="B586" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B587" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
@@ -9505,7 +9505,7 @@
         <v>216</v>
       </c>
       <c r="B588" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
@@ -9513,15 +9513,15 @@
         <v>316</v>
       </c>
       <c r="B589" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B590" t="s">
         <v>1074</v>
-      </c>
-      <c r="B590" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
@@ -9529,23 +9529,23 @@
         <v>214</v>
       </c>
       <c r="B591" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
+        <v>993</v>
+      </c>
+      <c r="B592" t="s">
         <v>994</v>
-      </c>
-      <c r="B592" t="s">
-        <v>995</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
+        <v>995</v>
+      </c>
+      <c r="B593" t="s">
         <v>996</v>
-      </c>
-      <c r="B593" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
@@ -9553,39 +9553,39 @@
         <v>225</v>
       </c>
       <c r="B594" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="B595" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
+        <v>942</v>
+      </c>
+      <c r="B596" t="s">
         <v>943</v>
-      </c>
-      <c r="B596" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B597" t="s">
         <v>1090</v>
-      </c>
-      <c r="B597" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B598" t="s">
         <v>1040</v>
-      </c>
-      <c r="B598" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
@@ -9593,7 +9593,7 @@
         <v>93</v>
       </c>
       <c r="B599" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
@@ -9601,15 +9601,15 @@
         <v>120</v>
       </c>
       <c r="B600" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
+        <v>778</v>
+      </c>
+      <c r="B601" t="s">
         <v>779</v>
-      </c>
-      <c r="B601" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
@@ -9617,7 +9617,7 @@
         <v>133</v>
       </c>
       <c r="B602" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
@@ -9625,15 +9625,15 @@
         <v>62</v>
       </c>
       <c r="B603" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B604" t="s">
         <v>1297</v>
-      </c>
-      <c r="B604" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
@@ -9641,39 +9641,39 @@
         <v>66</v>
       </c>
       <c r="B605" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
+        <v>820</v>
+      </c>
+      <c r="B606" t="s">
         <v>821</v>
-      </c>
-      <c r="B606" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
+        <v>944</v>
+      </c>
+      <c r="B607" t="s">
         <v>945</v>
-      </c>
-      <c r="B607" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B608" t="s">
         <v>1201</v>
-      </c>
-      <c r="B608" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B609" t="s">
         <v>1310</v>
-      </c>
-      <c r="B609" t="s">
-        <v>1311</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
@@ -9681,7 +9681,7 @@
         <v>79</v>
       </c>
       <c r="B610" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
@@ -9689,7 +9689,7 @@
         <v>64</v>
       </c>
       <c r="B611" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
@@ -9697,15 +9697,15 @@
         <v>122</v>
       </c>
       <c r="B612" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B613" t="s">
         <v>1170</v>
-      </c>
-      <c r="B613" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
@@ -9713,79 +9713,79 @@
         <v>181</v>
       </c>
       <c r="B614" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
+        <v>796</v>
+      </c>
+      <c r="B615" t="s">
         <v>797</v>
-      </c>
-      <c r="B615" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="B616" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B617" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="B618" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B619" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="B620" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="B621" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B622" t="s">
         <v>1137</v>
-      </c>
-      <c r="B622" t="s">
-        <v>1138</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B623" t="s">
         <v>1135</v>
-      </c>
-      <c r="B623" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.35">
@@ -9793,31 +9793,31 @@
         <v>284</v>
       </c>
       <c r="B624" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
+        <v>967</v>
+      </c>
+      <c r="B625" t="s">
         <v>968</v>
-      </c>
-      <c r="B625" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B626" t="s">
         <v>1205</v>
-      </c>
-      <c r="B626" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
+        <v>836</v>
+      </c>
+      <c r="B627" t="s">
         <v>837</v>
-      </c>
-      <c r="B627" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.35">
@@ -9825,39 +9825,39 @@
         <v>283</v>
       </c>
       <c r="B628" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
+        <v>878</v>
+      </c>
+      <c r="B629" t="s">
         <v>879</v>
-      </c>
-      <c r="B629" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B630" t="s">
         <v>1166</v>
-      </c>
-      <c r="B630" t="s">
-        <v>1167</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
+        <v>751</v>
+      </c>
+      <c r="B631" t="s">
         <v>752</v>
-      </c>
-      <c r="B631" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B632" t="s">
         <v>1070</v>
-      </c>
-      <c r="B632" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
@@ -9865,7 +9865,7 @@
         <v>67</v>
       </c>
       <c r="B633" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.35">
@@ -9873,15 +9873,15 @@
         <v>68</v>
       </c>
       <c r="B634" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="B635" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.35">
@@ -9889,7 +9889,7 @@
         <v>95</v>
       </c>
       <c r="B636" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.35">
@@ -9897,7 +9897,7 @@
         <v>289</v>
       </c>
       <c r="B637" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.35">
@@ -9905,7 +9905,7 @@
         <v>297</v>
       </c>
       <c r="B638" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.35">
@@ -9913,7 +9913,7 @@
         <v>264</v>
       </c>
       <c r="B639" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.35">
@@ -9921,23 +9921,23 @@
         <v>193</v>
       </c>
       <c r="B640" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="B641" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
+        <v>895</v>
+      </c>
+      <c r="B642" t="s">
         <v>896</v>
-      </c>
-      <c r="B642" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.35">
@@ -9945,15 +9945,15 @@
         <v>44</v>
       </c>
       <c r="B643" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B644" t="s">
         <v>1062</v>
-      </c>
-      <c r="B644" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.35">
@@ -9961,7 +9961,7 @@
         <v>323</v>
       </c>
       <c r="B645" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.35">
@@ -9969,39 +9969,39 @@
         <v>324</v>
       </c>
       <c r="B646" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
+        <v>844</v>
+      </c>
+      <c r="B647" t="s">
         <v>845</v>
-      </c>
-      <c r="B647" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
+        <v>882</v>
+      </c>
+      <c r="B648" t="s">
         <v>883</v>
-      </c>
-      <c r="B648" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B649" t="s">
         <v>1223</v>
-      </c>
-      <c r="B649" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
+        <v>864</v>
+      </c>
+      <c r="B650" t="s">
         <v>865</v>
-      </c>
-      <c r="B650" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.35">
@@ -10009,7 +10009,7 @@
         <v>33</v>
       </c>
       <c r="B651" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.35">
@@ -10017,15 +10017,15 @@
         <v>36</v>
       </c>
       <c r="B652" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B653" t="s">
         <v>1130</v>
-      </c>
-      <c r="B653" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.35">
@@ -10033,7 +10033,7 @@
         <v>309</v>
       </c>
       <c r="B654" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.35">
@@ -10041,7 +10041,7 @@
         <v>257</v>
       </c>
       <c r="B655" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.35">
@@ -10049,7 +10049,7 @@
         <v>302</v>
       </c>
       <c r="B656" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.35">
@@ -10057,7 +10057,7 @@
         <v>228</v>
       </c>
       <c r="B657" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.35">
@@ -10070,26 +10070,26 @@
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B659" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="B660" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
+        <v>780</v>
+      </c>
+      <c r="B661" t="s">
         <v>781</v>
-      </c>
-      <c r="B661" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.35">
@@ -10097,23 +10097,23 @@
         <v>142</v>
       </c>
       <c r="B662" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B663" t="s">
         <v>1164</v>
-      </c>
-      <c r="B663" t="s">
-        <v>1165</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
+        <v>950</v>
+      </c>
+      <c r="B664" t="s">
         <v>951</v>
-      </c>
-      <c r="B664" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.35">
@@ -10121,7 +10121,7 @@
         <v>54</v>
       </c>
       <c r="B665" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.35">
@@ -10129,23 +10129,23 @@
         <v>265</v>
       </c>
       <c r="B666" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B667" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="B668" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.35">
@@ -10153,15 +10153,15 @@
         <v>56</v>
       </c>
       <c r="B669" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B670" t="s">
         <v>1203</v>
-      </c>
-      <c r="B670" t="s">
-        <v>1204</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.35">
@@ -10169,7 +10169,7 @@
         <v>185</v>
       </c>
       <c r="B671" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.35">
@@ -10177,7 +10177,7 @@
         <v>159</v>
       </c>
       <c r="B672" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.35">
@@ -10185,31 +10185,31 @@
         <v>43</v>
       </c>
       <c r="B673" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="B674" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B675" t="s">
         <v>1456</v>
-      </c>
-      <c r="B675" t="s">
-        <v>1458</v>
       </c>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B676" t="s">
         <v>1457</v>
-      </c>
-      <c r="B676" t="s">
-        <v>1459</v>
       </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.35">
@@ -10217,23 +10217,23 @@
         <v>40</v>
       </c>
       <c r="B677" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="B678" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B679" t="s">
         <v>1156</v>
-      </c>
-      <c r="B679" t="s">
-        <v>1157</v>
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.35">
@@ -10241,23 +10241,23 @@
         <v>165</v>
       </c>
       <c r="B680" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B681" t="s">
         <v>1285</v>
-      </c>
-      <c r="B681" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B682" t="s">
         <v>1287</v>
-      </c>
-      <c r="B682" t="s">
-        <v>1288</v>
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.35">
@@ -10273,7 +10273,7 @@
         <v>250</v>
       </c>
       <c r="B684" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.35">
@@ -10281,15 +10281,15 @@
         <v>27</v>
       </c>
       <c r="B685" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B686" t="s">
         <v>1034</v>
-      </c>
-      <c r="B686" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.35">
@@ -10297,15 +10297,15 @@
         <v>28</v>
       </c>
       <c r="B687" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B688" t="s">
         <v>1191</v>
-      </c>
-      <c r="B688" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.35">
@@ -10313,23 +10313,23 @@
         <v>255</v>
       </c>
       <c r="B689" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="B690" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
+        <v>790</v>
+      </c>
+      <c r="B691" t="s">
         <v>791</v>
-      </c>
-      <c r="B691" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.35">
@@ -10337,23 +10337,23 @@
         <v>267</v>
       </c>
       <c r="B692" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B693" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B694" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.35">
@@ -10361,7 +10361,7 @@
         <v>139</v>
       </c>
       <c r="B695" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.35">
@@ -10377,47 +10377,47 @@
         <v>105</v>
       </c>
       <c r="B697" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="B698" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B699" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
+        <v>860</v>
+      </c>
+      <c r="B700" t="s">
         <v>861</v>
-      </c>
-      <c r="B700" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="B701" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B702" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.35">
@@ -10425,7 +10425,7 @@
         <v>292</v>
       </c>
       <c r="B703" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.35">
@@ -10441,23 +10441,23 @@
         <v>334</v>
       </c>
       <c r="B705" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="B706" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="B707" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.35">
@@ -10465,7 +10465,7 @@
         <v>331</v>
       </c>
       <c r="B708" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.35">
@@ -10473,7 +10473,7 @@
         <v>259</v>
       </c>
       <c r="B709" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.35">
@@ -10481,23 +10481,23 @@
         <v>318</v>
       </c>
       <c r="B710" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
+        <v>854</v>
+      </c>
+      <c r="B711" t="s">
         <v>855</v>
-      </c>
-      <c r="B711" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B712" t="s">
         <v>1160</v>
-      </c>
-      <c r="B712" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.35">
@@ -10505,7 +10505,7 @@
         <v>268</v>
       </c>
       <c r="B713" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.35">
@@ -10513,7 +10513,7 @@
         <v>271</v>
       </c>
       <c r="B714" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.35">
@@ -10521,7 +10521,7 @@
         <v>274</v>
       </c>
       <c r="B715" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.35">
@@ -10529,7 +10529,7 @@
         <v>270</v>
       </c>
       <c r="B716" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.35">
@@ -10537,7 +10537,7 @@
         <v>273</v>
       </c>
       <c r="B717" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.35">
@@ -10545,7 +10545,7 @@
         <v>269</v>
       </c>
       <c r="B718" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.35">
@@ -10553,7 +10553,7 @@
         <v>272</v>
       </c>
       <c r="B719" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.35">
@@ -10561,7 +10561,7 @@
         <v>92</v>
       </c>
       <c r="B720" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.35">
@@ -10569,7 +10569,7 @@
         <v>200</v>
       </c>
       <c r="B721" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.35">
@@ -10577,15 +10577,15 @@
         <v>203</v>
       </c>
       <c r="B722" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B723" t="s">
         <v>1213</v>
-      </c>
-      <c r="B723" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.35">
@@ -10593,31 +10593,31 @@
         <v>172</v>
       </c>
       <c r="B724" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="B725" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B726" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="727" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="B727" s="1" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.35">
@@ -10625,15 +10625,15 @@
         <v>252</v>
       </c>
       <c r="B728" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B729" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.35">
@@ -10641,15 +10641,15 @@
         <v>189</v>
       </c>
       <c r="B730" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
+        <v>983</v>
+      </c>
+      <c r="B731" t="s">
         <v>984</v>
-      </c>
-      <c r="B731" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.35">
@@ -10657,7 +10657,7 @@
         <v>311</v>
       </c>
       <c r="B732" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.35">
@@ -10665,31 +10665,31 @@
         <v>312</v>
       </c>
       <c r="B733" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B734" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="B735" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
+        <v>999</v>
+      </c>
+      <c r="B736" t="s">
         <v>1000</v>
-      </c>
-      <c r="B736" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.35">
@@ -10697,55 +10697,55 @@
         <v>81</v>
       </c>
       <c r="B737" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B738" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
+        <v>916</v>
+      </c>
+      <c r="B739" t="s">
         <v>917</v>
-      </c>
-      <c r="B739" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A740" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B740" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
+        <v>963</v>
+      </c>
+      <c r="B741" t="s">
         <v>964</v>
-      </c>
-      <c r="B741" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B742" t="s">
         <v>1148</v>
-      </c>
-      <c r="B742" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="B743" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
     </row>
   </sheetData>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29D6600-9B72-4B6A-896F-8D1443D7C657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0343EC7C-6A54-40A9-BB48-BE5861DD0E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="1475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1492" uniqueCount="1481">
   <si>
     <t>trigger</t>
   </si>
@@ -3336,9 +3336,6 @@
     <t>loss of fat plane</t>
   </si>
   <si>
-    <t>Multiple tiny T2 high signal intensity foci noted in  bilateral frontoparietal lobe which are suppressed on FLAIR , likely Virchow Robin spaces</t>
-  </si>
-  <si>
     <t>Urinary bladder is partially filled with Foley's in situ</t>
   </si>
   <si>
@@ -3363,9 +3360,6 @@
     <t>T2 high signal intensity noted in bilateral maxillary sinus - suggestive of sinusitis</t>
   </si>
   <si>
-    <t>Discrete and confluent T2/FLAIR high signal intensities are noted in bilateral periventricular white matter and centrum semi-ovale</t>
-  </si>
-  <si>
     <t>Mucosal thickening noted in bilateral maxillary sinus - suggestive of sinusitis</t>
   </si>
   <si>
@@ -3378,9 +3372,6 @@
     <t>Soft tissue density with convex outward margin is noted in right maxillary sinus – polyp/ retention cyst</t>
   </si>
   <si>
-    <t>There is fluid signal intensity noted in the pituitary fossa suggestive of partial empty sella</t>
-  </si>
-  <si>
     <t>No septations, solid component or calcification noted within</t>
   </si>
   <si>
@@ -4453,6 +4444,33 @@
   </si>
   <si>
     <t>centrilobular nodules giving tree in bud pattern</t>
+  </si>
+  <si>
+    <t>t2fl</t>
+  </si>
+  <si>
+    <t>T2/FLAIR</t>
+  </si>
+  <si>
+    <t>t2st</t>
+  </si>
+  <si>
+    <t>T2/STIR</t>
+  </si>
+  <si>
+    <t>There is fluid signal intensity noted in the pituitary fossa with flattening of the pituitary gland, suggestive of partial empty sella</t>
+  </si>
+  <si>
+    <t>Multiple tiny T2 hyperintense FLAIR suppressed foci noted in  bilateral frontoparietal lobes, likely Virchow Robin spaces</t>
+  </si>
+  <si>
+    <t>Multiple discrete and confluent T2/FLAIR high signal intensities are noted in bilateral periventricular white matter and centrum semi-ovale</t>
+  </si>
+  <si>
+    <t>dishx</t>
+  </si>
+  <si>
+    <t>Multilevel flowing anterolateral ossification/bridging osteophytes along the thoracic spine involving multiple contiguous vertebral levels, with relative preservation of the intervertebral disc spaces. Findings are suggestive of diffuse idiopathic skeletal hyperostosis (DISH)</t>
   </si>
 </sst>
 </file>
@@ -4521,10 +4539,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B743" totalsRowShown="0">
-  <autoFilter ref="A1:B743" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B743">
-    <sortCondition ref="A1:A743"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B746" totalsRowShown="0">
+  <autoFilter ref="A1:B746" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B746">
+    <sortCondition ref="A1:A746"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4797,7 +4815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B743"/>
+  <dimension ref="A1:B746"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -4822,10 +4840,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="B3" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -5054,10 +5072,10 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="B32" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
@@ -5134,18 +5152,18 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="B42" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="B43" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
@@ -5158,10 +5176,10 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="B45" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
@@ -5217,7 +5235,7 @@
         <v>246</v>
       </c>
       <c r="B52" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
@@ -5278,10 +5296,10 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="B60" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
@@ -5358,10 +5376,10 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
       <c r="B70" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
@@ -5374,10 +5392,10 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="B72" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
@@ -5390,10 +5408,10 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B74" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
@@ -5406,10 +5424,10 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="B76" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
@@ -5430,10 +5448,10 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="B79" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
@@ -5446,10 +5464,10 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="B81" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
@@ -5462,10 +5480,10 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="B83" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
@@ -5478,10 +5496,10 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="B85" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
@@ -5494,10 +5512,10 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="B87" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
@@ -5510,10 +5528,10 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B89" t="s">
         <v>1234</v>
-      </c>
-      <c r="B89" t="s">
-        <v>1237</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
@@ -5526,10 +5544,10 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B91" t="s">
         <v>1235</v>
-      </c>
-      <c r="B91" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
@@ -5542,10 +5560,10 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B93" t="s">
         <v>1236</v>
-      </c>
-      <c r="B93" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
@@ -5646,10 +5664,10 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="B106" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
@@ -5681,7 +5699,7 @@
         <v>41</v>
       </c>
       <c r="B110" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
@@ -5694,10 +5712,10 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="B112" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
@@ -5742,10 +5760,10 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="B118" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
@@ -5782,10 +5800,10 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="B123" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
@@ -5814,10 +5832,10 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
       <c r="B127" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
@@ -5870,10 +5888,10 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B134" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
@@ -5905,7 +5923,7 @@
         <v>104</v>
       </c>
       <c r="B138" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
@@ -5929,12 +5947,12 @@
         <v>102</v>
       </c>
       <c r="B141" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="B142" t="s">
         <v>403</v>
@@ -5966,18 +5984,18 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="B146" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>1369</v>
+        <v>1366</v>
       </c>
       <c r="B147" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
@@ -5998,10 +6016,10 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="B150" t="s">
-        <v>1473</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
@@ -6038,34 +6056,34 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="B155" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>1363</v>
+        <v>1360</v>
       </c>
       <c r="B156" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="B157" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="B158" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
@@ -6078,10 +6096,10 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="B160" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
@@ -6094,10 +6112,10 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="B162" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
@@ -6110,10 +6128,10 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="B164" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
@@ -6126,10 +6144,10 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="B166" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
@@ -6142,10 +6160,10 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="B168" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
@@ -6158,10 +6176,10 @@
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="B170" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
@@ -6174,10 +6192,10 @@
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="B172" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
@@ -6190,10 +6208,10 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="B174" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
@@ -6206,10 +6224,10 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="B176" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
@@ -6222,10 +6240,10 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="B178" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
@@ -6249,7 +6267,7 @@
         <v>211</v>
       </c>
       <c r="B181" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
@@ -6257,28 +6275,28 @@
         <v>213</v>
       </c>
       <c r="B182" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="B183" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
       <c r="B184" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="B185" t="s">
         <v>406</v>
@@ -6289,7 +6307,7 @@
         <v>149</v>
       </c>
       <c r="B186" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
@@ -6305,7 +6323,7 @@
         <v>245</v>
       </c>
       <c r="B188" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
@@ -6342,351 +6360,351 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>1087</v>
+        <v>1479</v>
       </c>
       <c r="B193" t="s">
-        <v>1088</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>794</v>
+        <v>1087</v>
       </c>
       <c r="B194" t="s">
-        <v>795</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>1153</v>
+        <v>794</v>
       </c>
       <c r="B195" t="s">
-        <v>1154</v>
+        <v>795</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>1340</v>
+        <v>1150</v>
       </c>
       <c r="B196" t="s">
-        <v>1341</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>295</v>
+        <v>1337</v>
       </c>
       <c r="B197" t="s">
-        <v>411</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>1077</v>
+        <v>295</v>
       </c>
       <c r="B198" t="s">
-        <v>1078</v>
+        <v>411</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="B199" t="s">
-        <v>1084</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>151</v>
+        <v>1083</v>
       </c>
       <c r="B200" t="s">
-        <v>412</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>955</v>
+        <v>151</v>
       </c>
       <c r="B201" t="s">
-        <v>956</v>
+        <v>412</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>808</v>
+        <v>955</v>
       </c>
       <c r="B202" t="s">
-        <v>809</v>
+        <v>956</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>926</v>
+        <v>808</v>
       </c>
       <c r="B203" t="s">
-        <v>927</v>
+        <v>809</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>828</v>
+        <v>926</v>
       </c>
       <c r="B204" t="s">
-        <v>829</v>
+        <v>927</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>788</v>
+        <v>828</v>
       </c>
       <c r="B205" t="s">
-        <v>789</v>
+        <v>829</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>1425</v>
+        <v>788</v>
       </c>
       <c r="B206" t="s">
-        <v>1426</v>
+        <v>789</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>749</v>
+        <v>1422</v>
       </c>
       <c r="B207" t="s">
-        <v>750</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>100</v>
+        <v>749</v>
       </c>
       <c r="B208" t="s">
-        <v>413</v>
+        <v>750</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>1035</v>
+        <v>100</v>
       </c>
       <c r="B209" t="s">
-        <v>1036</v>
+        <v>413</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>154</v>
+        <v>1035</v>
       </c>
       <c r="B210" t="s">
-        <v>414</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B211" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="B212" t="s">
-        <v>1124</v>
+        <v>415</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>1149</v>
+        <v>24</v>
       </c>
       <c r="B213" t="s">
-        <v>1150</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>1313</v>
+        <v>1146</v>
       </c>
       <c r="B214" t="s">
-        <v>1314</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>1067</v>
+        <v>1310</v>
       </c>
       <c r="B215" t="s">
-        <v>1068</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>1471</v>
+        <v>1067</v>
       </c>
       <c r="B216" t="s">
-        <v>1472</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>814</v>
+        <v>1468</v>
       </c>
       <c r="B217" t="s">
-        <v>815</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>130</v>
+        <v>814</v>
       </c>
       <c r="B218" t="s">
-        <v>416</v>
+        <v>815</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>321</v>
+        <v>130</v>
       </c>
       <c r="B219" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>1470</v>
+        <v>321</v>
       </c>
       <c r="B220" t="s">
-        <v>1429</v>
+        <v>417</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>862</v>
+        <v>1467</v>
       </c>
       <c r="B221" t="s">
-        <v>863</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>1432</v>
+        <v>862</v>
       </c>
       <c r="B222" t="s">
-        <v>1433</v>
+        <v>863</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>1469</v>
+        <v>1429</v>
       </c>
       <c r="B223" t="s">
-        <v>886</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>1302</v>
+        <v>1466</v>
       </c>
       <c r="B224" t="s">
-        <v>1303</v>
+        <v>886</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>183</v>
+        <v>1299</v>
       </c>
       <c r="B225" t="s">
-        <v>418</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>1140</v>
+        <v>183</v>
       </c>
       <c r="B226" t="s">
-        <v>1141</v>
+        <v>418</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>1142</v>
+        <v>1137</v>
       </c>
       <c r="B227" t="s">
-        <v>1143</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>1423</v>
+        <v>1139</v>
       </c>
       <c r="B228" t="s">
-        <v>1424</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>1381</v>
+        <v>1420</v>
       </c>
       <c r="B229" t="s">
-        <v>1382</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>32</v>
+        <v>1378</v>
       </c>
       <c r="B230" t="s">
-        <v>419</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B231" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>1292</v>
+        <v>35</v>
       </c>
       <c r="B232" t="s">
-        <v>1293</v>
+        <v>420</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>1218</v>
+        <v>1289</v>
       </c>
       <c r="B233" t="s">
-        <v>1219</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>759</v>
+        <v>1215</v>
       </c>
       <c r="B234" t="s">
-        <v>1003</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>169</v>
+        <v>759</v>
       </c>
       <c r="B235" t="s">
-        <v>421</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B236" t="s">
         <v>421</v>
@@ -6694,831 +6712,831 @@
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>1004</v>
+        <v>170</v>
       </c>
       <c r="B237" t="s">
-        <v>760</v>
+        <v>421</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>1421</v>
+        <v>1004</v>
       </c>
       <c r="B238" t="s">
-        <v>1422</v>
+        <v>760</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>178</v>
+        <v>1418</v>
       </c>
       <c r="B239" t="s">
-        <v>422</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="B240" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>238</v>
+        <v>111</v>
       </c>
       <c r="B241" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="B242" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B243" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="B244" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>662</v>
+        <v>179</v>
       </c>
       <c r="B245" t="s">
-        <v>717</v>
+        <v>427</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>97</v>
+        <v>662</v>
       </c>
       <c r="B246" t="s">
-        <v>428</v>
+        <v>717</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B247" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>242</v>
+        <v>110</v>
       </c>
       <c r="B248" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B249" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="B250" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>1419</v>
+        <v>177</v>
       </c>
       <c r="B251" t="s">
-        <v>1420</v>
+        <v>432</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>182</v>
+        <v>1416</v>
       </c>
       <c r="B252" t="s">
-        <v>433</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>1097</v>
+        <v>182</v>
       </c>
       <c r="B253" t="s">
-        <v>1098</v>
+        <v>433</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>971</v>
+        <v>1097</v>
       </c>
       <c r="B254" t="s">
-        <v>972</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B255" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>1183</v>
+        <v>973</v>
       </c>
       <c r="B256" t="s">
-        <v>1184</v>
+        <v>974</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>1361</v>
+        <v>1180</v>
       </c>
       <c r="B257" t="s">
-        <v>1362</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>1186</v>
+        <v>1358</v>
       </c>
       <c r="B258" t="s">
-        <v>1187</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>253</v>
+        <v>1183</v>
       </c>
       <c r="B259" t="s">
-        <v>434</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="B260" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>782</v>
+        <v>34</v>
       </c>
       <c r="B261" t="s">
-        <v>783</v>
+        <v>435</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>180</v>
+        <v>782</v>
       </c>
       <c r="B262" t="s">
-        <v>436</v>
+        <v>783</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>1333</v>
+        <v>180</v>
       </c>
       <c r="B263" t="s">
-        <v>1402</v>
+        <v>436</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="B264" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>1452</v>
+        <v>1329</v>
       </c>
       <c r="B265" t="s">
-        <v>1453</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>275</v>
+        <v>1449</v>
       </c>
       <c r="B266" t="s">
-        <v>437</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>852</v>
+        <v>275</v>
       </c>
       <c r="B267" t="s">
-        <v>853</v>
+        <v>437</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>116</v>
+        <v>852</v>
       </c>
       <c r="B268" t="s">
-        <v>438</v>
+        <v>853</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="B269" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>1407</v>
+        <v>208</v>
       </c>
       <c r="B270" t="s">
-        <v>1408</v>
+        <v>439</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>1206</v>
+        <v>1404</v>
       </c>
       <c r="B271" t="s">
-        <v>1207</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>1047</v>
+        <v>1203</v>
       </c>
       <c r="B272" t="s">
-        <v>1048</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>118</v>
+        <v>1047</v>
       </c>
       <c r="B273" t="s">
-        <v>440</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>636</v>
+        <v>118</v>
       </c>
       <c r="B274" t="s">
-        <v>718</v>
+        <v>440</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>1317</v>
+        <v>636</v>
       </c>
       <c r="B275" t="s">
-        <v>1318</v>
+        <v>718</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>810</v>
+        <v>1314</v>
       </c>
       <c r="B276" t="s">
-        <v>811</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>298</v>
+        <v>810</v>
       </c>
       <c r="B277" t="s">
-        <v>441</v>
+        <v>811</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>638</v>
+        <v>298</v>
       </c>
       <c r="B278" t="s">
-        <v>719</v>
+        <v>441</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B279" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>1029</v>
+        <v>639</v>
       </c>
       <c r="B280" t="s">
-        <v>1030</v>
+        <v>720</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>90</v>
+        <v>1029</v>
       </c>
       <c r="B281" t="s">
-        <v>442</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B282" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B283" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>1063</v>
+        <v>89</v>
       </c>
       <c r="B284" t="s">
-        <v>1064</v>
+        <v>444</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>23</v>
+        <v>1063</v>
       </c>
       <c r="B285" t="s">
-        <v>1123</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>1411</v>
+        <v>23</v>
       </c>
       <c r="B286" t="s">
-        <v>1412</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>5</v>
+        <v>1408</v>
       </c>
       <c r="B287" t="s">
-        <v>6</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>1127</v>
+        <v>5</v>
       </c>
       <c r="B288" t="s">
-        <v>1128</v>
+        <v>6</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>126</v>
+        <v>1124</v>
       </c>
       <c r="B289" t="s">
-        <v>445</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>1385</v>
+        <v>126</v>
       </c>
       <c r="B290" t="s">
-        <v>1386</v>
+        <v>445</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>128</v>
+        <v>1382</v>
       </c>
       <c r="B291" t="s">
-        <v>446</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B292" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B293" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B294" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>277</v>
+        <v>119</v>
       </c>
       <c r="B295" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>1065</v>
+        <v>277</v>
       </c>
       <c r="B296" t="s">
-        <v>1066</v>
+        <v>450</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>9</v>
+        <v>1065</v>
       </c>
       <c r="B297" t="s">
-        <v>10</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="B298" t="s">
-        <v>451</v>
+        <v>10</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B299" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="B300" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="B301" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>1372</v>
+        <v>262</v>
       </c>
       <c r="B302" t="s">
-        <v>1373</v>
+        <v>454</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>77</v>
+        <v>1369</v>
       </c>
       <c r="B303" t="s">
-        <v>455</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>932</v>
+        <v>77</v>
       </c>
       <c r="B304" t="s">
-        <v>933</v>
+        <v>455</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>1157</v>
+        <v>932</v>
       </c>
       <c r="B305" t="s">
-        <v>1158</v>
+        <v>933</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>168</v>
+        <v>1154</v>
       </c>
       <c r="B306" t="s">
-        <v>456</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>1345</v>
+        <v>168</v>
       </c>
       <c r="B307" t="s">
-        <v>1346</v>
+        <v>456</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>1355</v>
+        <v>1342</v>
       </c>
       <c r="B308" t="s">
-        <v>1356</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>1398</v>
+        <v>1352</v>
       </c>
       <c r="B309" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>1351</v>
+        <v>1395</v>
       </c>
       <c r="B310" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>167</v>
+        <v>1348</v>
       </c>
       <c r="B311" t="s">
-        <v>457</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>1347</v>
+        <v>167</v>
       </c>
       <c r="B312" t="s">
-        <v>1348</v>
+        <v>457</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>1353</v>
+        <v>1344</v>
       </c>
       <c r="B313" t="s">
-        <v>1354</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>1380</v>
+        <v>1350</v>
       </c>
       <c r="B314" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>1349</v>
+        <v>1377</v>
       </c>
       <c r="B315" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>830</v>
+        <v>1346</v>
       </c>
       <c r="B316" t="s">
-        <v>831</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>786</v>
+        <v>830</v>
       </c>
       <c r="B317" t="s">
-        <v>787</v>
+        <v>831</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>304</v>
+        <v>786</v>
       </c>
       <c r="B318" t="s">
-        <v>458</v>
+        <v>787</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>753</v>
+        <v>304</v>
       </c>
       <c r="B319" t="s">
-        <v>754</v>
+        <v>458</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>891</v>
+        <v>753</v>
       </c>
       <c r="B320" t="s">
-        <v>892</v>
+        <v>754</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>1387</v>
+        <v>891</v>
       </c>
       <c r="B321" t="s">
-        <v>1388</v>
+        <v>892</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>647</v>
+        <v>1384</v>
       </c>
       <c r="B322" t="s">
-        <v>721</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>86</v>
+        <v>647</v>
       </c>
       <c r="B323" t="s">
-        <v>459</v>
+        <v>721</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B324" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="B325" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B326" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B327" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>251</v>
+        <v>158</v>
       </c>
       <c r="B328" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="B329" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>325</v>
+        <v>285</v>
       </c>
       <c r="B330" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>1367</v>
+        <v>325</v>
       </c>
       <c r="B331" t="s">
-        <v>1368</v>
+        <v>466</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>326</v>
+        <v>1364</v>
       </c>
       <c r="B332" t="s">
-        <v>467</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>229</v>
+        <v>326</v>
       </c>
       <c r="B333" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>55</v>
+        <v>229</v>
       </c>
       <c r="B334" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>652</v>
+        <v>55</v>
       </c>
       <c r="B335" t="s">
-        <v>722</v>
+        <v>469</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>235</v>
+        <v>652</v>
       </c>
       <c r="B336" t="s">
-        <v>470</v>
+        <v>722</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="B337" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="B338" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>761</v>
+        <v>236</v>
       </c>
       <c r="B339" t="s">
-        <v>762</v>
+        <v>472</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>1005</v>
+        <v>761</v>
       </c>
       <c r="B340" t="s">
         <v>762</v>
@@ -7526,631 +7544,631 @@
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>164</v>
+        <v>1005</v>
       </c>
       <c r="B341" t="s">
-        <v>473</v>
+        <v>762</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>1466</v>
+        <v>164</v>
       </c>
       <c r="B342" t="s">
-        <v>1464</v>
+        <v>473</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>201</v>
+        <v>1463</v>
       </c>
       <c r="B343" t="s">
-        <v>474</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B344" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>313</v>
+        <v>204</v>
       </c>
       <c r="B345" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>868</v>
+        <v>313</v>
       </c>
       <c r="B346" t="s">
-        <v>869</v>
+        <v>476</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>991</v>
+        <v>868</v>
       </c>
       <c r="B347" t="s">
-        <v>992</v>
+        <v>869</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>1320</v>
+        <v>991</v>
       </c>
       <c r="B348" t="s">
-        <v>1321</v>
+        <v>992</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>258</v>
+        <v>1317</v>
       </c>
       <c r="B349" t="s">
-        <v>477</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>977</v>
+        <v>258</v>
       </c>
       <c r="B350" t="s">
-        <v>978</v>
+        <v>477</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>1359</v>
+        <v>977</v>
       </c>
       <c r="B351" t="s">
-        <v>1360</v>
+        <v>978</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>160</v>
+        <v>1356</v>
       </c>
       <c r="B352" t="s">
-        <v>478</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>687</v>
+        <v>160</v>
       </c>
       <c r="B353" t="s">
-        <v>723</v>
+        <v>478</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>1151</v>
+        <v>687</v>
       </c>
       <c r="B354" t="s">
-        <v>1152</v>
+        <v>723</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>755</v>
+        <v>1148</v>
       </c>
       <c r="B355" t="s">
-        <v>756</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>889</v>
+        <v>755</v>
       </c>
       <c r="B356" t="s">
-        <v>890</v>
+        <v>756</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B357" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>184</v>
+        <v>887</v>
       </c>
       <c r="B358" t="s">
-        <v>479</v>
+        <v>888</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>244</v>
+        <v>184</v>
       </c>
       <c r="B359" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B360" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>1264</v>
+        <v>243</v>
       </c>
       <c r="B361" t="s">
-        <v>1269</v>
+        <v>481</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>681</v>
+        <v>1261</v>
       </c>
       <c r="B362" t="s">
-        <v>724</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>1265</v>
+        <v>681</v>
       </c>
       <c r="B363" t="s">
-        <v>1270</v>
+        <v>724</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>682</v>
+        <v>1262</v>
       </c>
       <c r="B364" t="s">
-        <v>725</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>1266</v>
+        <v>682</v>
       </c>
       <c r="B365" t="s">
-        <v>1271</v>
+        <v>725</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>683</v>
+        <v>1263</v>
       </c>
       <c r="B366" t="s">
-        <v>726</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>1267</v>
+        <v>683</v>
       </c>
       <c r="B367" t="s">
-        <v>1272</v>
+        <v>726</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>684</v>
+        <v>1264</v>
       </c>
       <c r="B368" t="s">
-        <v>727</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>1268</v>
+        <v>684</v>
       </c>
       <c r="B369" t="s">
-        <v>1273</v>
+        <v>727</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>685</v>
+        <v>1265</v>
       </c>
       <c r="B370" t="s">
-        <v>728</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>1177</v>
+        <v>685</v>
       </c>
       <c r="B371" t="s">
-        <v>1178</v>
+        <v>728</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>280</v>
+        <v>1174</v>
       </c>
       <c r="B372" t="s">
-        <v>482</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B373" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>49</v>
+        <v>281</v>
       </c>
       <c r="B374" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B375" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="B376" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>1440</v>
+        <v>136</v>
       </c>
       <c r="B377" t="s">
-        <v>1441</v>
+        <v>487</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>72</v>
+        <v>1437</v>
       </c>
       <c r="B378" t="s">
-        <v>486</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>1175</v>
+        <v>72</v>
       </c>
       <c r="B379" t="s">
-        <v>1176</v>
+        <v>486</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>221</v>
+        <v>1172</v>
       </c>
       <c r="B380" t="s">
-        <v>488</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>1179</v>
+        <v>221</v>
       </c>
       <c r="B381" t="s">
-        <v>1180</v>
+        <v>488</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>15</v>
+        <v>1176</v>
       </c>
       <c r="B382" t="s">
-        <v>16</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>1051</v>
+        <v>15</v>
       </c>
       <c r="B383" t="s">
-        <v>1052</v>
+        <v>16</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>914</v>
+        <v>1051</v>
       </c>
       <c r="B384" t="s">
-        <v>915</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>108</v>
+        <v>914</v>
       </c>
       <c r="B385" t="s">
-        <v>489</v>
+        <v>915</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>241</v>
+        <v>108</v>
       </c>
       <c r="B386" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>327</v>
+        <v>241</v>
       </c>
       <c r="B387" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>1091</v>
+        <v>327</v>
       </c>
       <c r="B388" t="s">
-        <v>1092</v>
+        <v>491</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>1043</v>
+        <v>1091</v>
       </c>
       <c r="B389" t="s">
-        <v>1044</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>121</v>
+        <v>1043</v>
       </c>
       <c r="B390" t="s">
-        <v>492</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>745</v>
+        <v>121</v>
       </c>
       <c r="B391" t="s">
-        <v>746</v>
+        <v>492</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>776</v>
+        <v>745</v>
       </c>
       <c r="B392" t="s">
-        <v>777</v>
+        <v>746</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>134</v>
+        <v>776</v>
       </c>
       <c r="B393" t="s">
-        <v>493</v>
+        <v>777</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="B394" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>1298</v>
+        <v>63</v>
       </c>
       <c r="B395" t="s">
-        <v>1299</v>
+        <v>494</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>224</v>
+        <v>1295</v>
       </c>
       <c r="B396" t="s">
-        <v>495</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>25</v>
+        <v>224</v>
       </c>
       <c r="B397" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B398" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>207</v>
+        <v>26</v>
       </c>
       <c r="B399" t="s">
-        <v>1120</v>
+        <v>497</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>954</v>
+        <v>207</v>
       </c>
       <c r="B400" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>1100</v>
+        <v>954</v>
       </c>
       <c r="B401" t="s">
-        <v>1101</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>206</v>
+        <v>1100</v>
       </c>
       <c r="B402" t="s">
-        <v>1122</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B403" t="s">
-        <v>498</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B404" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="B405" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>658</v>
+        <v>145</v>
       </c>
       <c r="B406" t="s">
-        <v>729</v>
+        <v>500</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>171</v>
+        <v>658</v>
       </c>
       <c r="B407" t="s">
-        <v>501</v>
+        <v>729</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>1079</v>
+        <v>171</v>
       </c>
       <c r="B408" t="s">
-        <v>1080</v>
+        <v>501</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>263</v>
+        <v>1079</v>
       </c>
       <c r="B409" t="s">
-        <v>502</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>1081</v>
+        <v>263</v>
       </c>
       <c r="B410" t="s">
-        <v>1082</v>
+        <v>502</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>80</v>
+        <v>1081</v>
       </c>
       <c r="B411" t="s">
-        <v>503</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B412" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>191</v>
+        <v>65</v>
       </c>
       <c r="B413" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="B414" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>192</v>
+        <v>123</v>
       </c>
       <c r="B415" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="B416" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B417" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>1185</v>
+        <v>233</v>
       </c>
       <c r="B418" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>31</v>
+        <v>1182</v>
       </c>
       <c r="B419" t="s">
         <v>510</v>
@@ -8158,367 +8176,367 @@
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B420" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B421" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B422" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>1438</v>
+        <v>71</v>
       </c>
       <c r="B423" t="s">
-        <v>1439</v>
+        <v>513</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>306</v>
+        <v>1435</v>
       </c>
       <c r="B424" t="s">
-        <v>514</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>222</v>
+        <v>306</v>
       </c>
       <c r="B425" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>278</v>
+        <v>222</v>
       </c>
       <c r="B426" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B427" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>1389</v>
+        <v>279</v>
       </c>
       <c r="B428" t="s">
-        <v>1390</v>
+        <v>518</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>826</v>
+        <v>1386</v>
       </c>
       <c r="B429" t="s">
-        <v>827</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>48</v>
+        <v>826</v>
       </c>
       <c r="B430" t="s">
-        <v>519</v>
+        <v>827</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="B431" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="B432" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>1371</v>
+        <v>52</v>
       </c>
       <c r="B433" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>223</v>
+        <v>1368</v>
       </c>
       <c r="B434" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>1085</v>
+        <v>223</v>
       </c>
       <c r="B435" t="s">
-        <v>1086</v>
+        <v>522</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>1096</v>
+        <v>1085</v>
       </c>
       <c r="B436" t="s">
-        <v>1099</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>1041</v>
+        <v>1096</v>
       </c>
       <c r="B437" t="s">
-        <v>1042</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>96</v>
+        <v>1041</v>
       </c>
       <c r="B438" t="s">
-        <v>523</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>248</v>
+        <v>96</v>
       </c>
       <c r="B439" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B440" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>94</v>
+        <v>249</v>
       </c>
       <c r="B441" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>1055</v>
+        <v>94</v>
       </c>
       <c r="B442" t="s">
-        <v>1056</v>
+        <v>526</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>212</v>
+        <v>1055</v>
       </c>
       <c r="B443" t="s">
-        <v>527</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>1210</v>
+        <v>212</v>
       </c>
       <c r="B444" t="s">
-        <v>1211</v>
+        <v>527</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>910</v>
+        <v>1207</v>
       </c>
       <c r="B445" t="s">
-        <v>911</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B446" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="B447" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>329</v>
+        <v>912</v>
       </c>
       <c r="B448" t="s">
-        <v>528</v>
+        <v>913</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>1413</v>
+        <v>329</v>
       </c>
       <c r="B449" t="s">
-        <v>1414</v>
+        <v>528</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>1415</v>
+        <v>1410</v>
       </c>
       <c r="B450" t="s">
-        <v>1416</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>1057</v>
+        <v>1412</v>
       </c>
       <c r="B451" t="s">
-        <v>1058</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>989</v>
+        <v>1057</v>
       </c>
       <c r="B452" t="s">
-        <v>990</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>1399</v>
+        <v>989</v>
       </c>
       <c r="B453" t="s">
-        <v>1400</v>
+        <v>990</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>985</v>
+        <v>1396</v>
       </c>
       <c r="B454" t="s">
-        <v>986</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="B455" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>82</v>
+        <v>987</v>
       </c>
       <c r="B456" t="s">
-        <v>529</v>
+        <v>988</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>767</v>
+        <v>82</v>
       </c>
       <c r="B457" t="s">
-        <v>768</v>
+        <v>529</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>197</v>
+        <v>767</v>
       </c>
       <c r="B458" t="s">
-        <v>530</v>
+        <v>768</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>649</v>
+        <v>197</v>
       </c>
       <c r="B459" t="s">
-        <v>730</v>
+        <v>530</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>1436</v>
+        <v>649</v>
       </c>
       <c r="B460" t="s">
-        <v>1437</v>
+        <v>730</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>1342</v>
+        <v>1433</v>
       </c>
       <c r="B461" t="s">
-        <v>1343</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>816</v>
+        <v>1339</v>
       </c>
       <c r="B462" t="s">
-        <v>817</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>1059</v>
+        <v>816</v>
       </c>
       <c r="B463" t="s">
-        <v>1060</v>
+        <v>817</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>3</v>
+        <v>1059</v>
       </c>
       <c r="B464" t="s">
-        <v>4</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>952</v>
+        <v>3</v>
       </c>
       <c r="B465" t="s">
         <v>4</v>
@@ -8526,7 +8544,7 @@
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B466" t="s">
         <v>4</v>
@@ -8534,1615 +8552,1615 @@
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>659</v>
+        <v>953</v>
       </c>
       <c r="B467" t="s">
-        <v>731</v>
+        <v>4</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>1290</v>
+        <v>659</v>
       </c>
       <c r="B468" t="s">
-        <v>1291</v>
+        <v>731</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>765</v>
+        <v>1287</v>
       </c>
       <c r="B469" t="s">
-        <v>766</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>85</v>
+        <v>765</v>
       </c>
       <c r="B470" t="s">
-        <v>531</v>
+        <v>766</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>1053</v>
+        <v>85</v>
       </c>
       <c r="B471" t="s">
-        <v>1054</v>
+        <v>531</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>824</v>
+        <v>1053</v>
       </c>
       <c r="B472" t="s">
-        <v>825</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>804</v>
+        <v>824</v>
       </c>
       <c r="B473" t="s">
-        <v>805</v>
+        <v>825</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>187</v>
+        <v>804</v>
       </c>
       <c r="B474" t="s">
-        <v>532</v>
+        <v>805</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>822</v>
+        <v>187</v>
       </c>
       <c r="B475" t="s">
-        <v>823</v>
+        <v>532</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>928</v>
+        <v>822</v>
       </c>
       <c r="B476" t="s">
-        <v>1117</v>
+        <v>823</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>1442</v>
+        <v>928</v>
       </c>
       <c r="B477" t="s">
-        <v>1443</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>858</v>
+        <v>1439</v>
       </c>
       <c r="B478" t="s">
-        <v>859</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>1430</v>
+        <v>858</v>
       </c>
       <c r="B479" t="s">
-        <v>1431</v>
+        <v>859</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>1037</v>
+        <v>1427</v>
       </c>
       <c r="B480" t="s">
-        <v>1038</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>793</v>
+        <v>1037</v>
       </c>
       <c r="B481" t="s">
-        <v>1118</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B482" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>13</v>
+        <v>792</v>
       </c>
       <c r="B483" t="s">
-        <v>14</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>812</v>
+        <v>13</v>
       </c>
       <c r="B484" t="s">
-        <v>813</v>
+        <v>14</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>1220</v>
+        <v>812</v>
       </c>
       <c r="B485" t="s">
-        <v>1221</v>
+        <v>813</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>186</v>
+        <v>1217</v>
       </c>
       <c r="B486" t="s">
-        <v>533</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>806</v>
+        <v>186</v>
       </c>
       <c r="B487" t="s">
-        <v>807</v>
+        <v>533</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>319</v>
+        <v>806</v>
       </c>
       <c r="B488" t="s">
-        <v>534</v>
+        <v>807</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>651</v>
+        <v>319</v>
       </c>
       <c r="B489" t="s">
-        <v>732</v>
+        <v>534</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>850</v>
+        <v>651</v>
       </c>
       <c r="B490" t="s">
-        <v>851</v>
+        <v>732</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>653</v>
+        <v>850</v>
       </c>
       <c r="B491" t="s">
-        <v>733</v>
+        <v>851</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="B492" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>1192</v>
+        <v>648</v>
       </c>
       <c r="B493" t="s">
-        <v>1193</v>
+        <v>734</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>256</v>
+        <v>1189</v>
       </c>
       <c r="B494" t="s">
-        <v>535</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B495" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B496" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>188</v>
+        <v>261</v>
       </c>
       <c r="B497" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B498" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>930</v>
+        <v>190</v>
       </c>
       <c r="B499" t="s">
-        <v>931</v>
+        <v>539</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>1024</v>
+        <v>930</v>
       </c>
       <c r="B500" t="s">
-        <v>1025</v>
+        <v>931</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>1208</v>
+        <v>1024</v>
       </c>
       <c r="B501" t="s">
-        <v>1209</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>209</v>
+        <v>1205</v>
       </c>
       <c r="B502" t="s">
-        <v>540</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>1409</v>
+        <v>209</v>
       </c>
       <c r="B503" t="s">
-        <v>1410</v>
+        <v>540</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>1300</v>
+        <v>1406</v>
       </c>
       <c r="B504" t="s">
-        <v>1301</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>846</v>
+        <v>1297</v>
       </c>
       <c r="B505" t="s">
-        <v>847</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>143</v>
+        <v>846</v>
       </c>
       <c r="B506" t="s">
-        <v>541</v>
+        <v>847</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B507" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>1188</v>
+        <v>140</v>
       </c>
       <c r="B508" t="s">
-        <v>1189</v>
+        <v>542</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>1288</v>
+        <v>1185</v>
       </c>
       <c r="B509" t="s">
-        <v>1289</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>254</v>
+        <v>1285</v>
       </c>
       <c r="B510" t="s">
-        <v>543</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>330</v>
+        <v>254</v>
       </c>
       <c r="B511" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="B512" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="B513" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>73</v>
+        <v>234</v>
       </c>
       <c r="B514" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>341</v>
+        <v>73</v>
       </c>
       <c r="B515" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>308</v>
+        <v>341</v>
       </c>
       <c r="B516" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>838</v>
+        <v>308</v>
       </c>
       <c r="B517" t="s">
-        <v>839</v>
+        <v>549</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B518" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>220</v>
+        <v>840</v>
       </c>
       <c r="B519" t="s">
-        <v>550</v>
+        <v>841</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>903</v>
+        <v>220</v>
       </c>
       <c r="B520" t="s">
-        <v>904</v>
+        <v>550</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>1365</v>
+        <v>903</v>
       </c>
       <c r="B521" t="s">
-        <v>1366</v>
+        <v>904</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>957</v>
+        <v>1362</v>
       </c>
       <c r="B522" t="s">
-        <v>958</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>1173</v>
+        <v>957</v>
       </c>
       <c r="B523" t="s">
-        <v>1174</v>
+        <v>958</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>227</v>
+        <v>1170</v>
       </c>
       <c r="B524" t="s">
-        <v>551</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>333</v>
+        <v>227</v>
       </c>
       <c r="B525" t="s">
-        <v>1146</v>
+        <v>551</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>965</v>
+        <v>333</v>
       </c>
       <c r="B526" t="s">
-        <v>966</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>773</v>
+        <v>965</v>
       </c>
       <c r="B527" t="s">
-        <v>774</v>
+        <v>966</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>294</v>
+        <v>773</v>
       </c>
       <c r="B528" t="s">
-        <v>552</v>
+        <v>774</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>946</v>
+        <v>294</v>
       </c>
       <c r="B529" t="s">
-        <v>947</v>
+        <v>552</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>338</v>
+        <v>946</v>
       </c>
       <c r="B530" t="s">
-        <v>553</v>
+        <v>947</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>775</v>
+        <v>338</v>
       </c>
       <c r="B531" t="s">
-        <v>774</v>
+        <v>553</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>1304</v>
+        <v>775</v>
       </c>
       <c r="B532" t="s">
-        <v>1305</v>
+        <v>774</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>339</v>
+        <v>1301</v>
       </c>
       <c r="B533" t="s">
-        <v>554</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B534" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>640</v>
+        <v>340</v>
       </c>
       <c r="B535" t="s">
-        <v>735</v>
+        <v>555</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>39</v>
+        <v>640</v>
       </c>
       <c r="B536" t="s">
-        <v>556</v>
+        <v>735</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B537" t="s">
-        <v>1116</v>
+        <v>556</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>342</v>
+        <v>38</v>
       </c>
       <c r="B538" t="s">
-        <v>557</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>107</v>
+        <v>342</v>
       </c>
       <c r="B539" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>1417</v>
+        <v>107</v>
       </c>
       <c r="B540" t="s">
-        <v>1418</v>
+        <v>558</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>1022</v>
+        <v>1414</v>
       </c>
       <c r="B541" t="s">
-        <v>1023</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>897</v>
+        <v>1022</v>
       </c>
       <c r="B542" t="s">
-        <v>898</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>117</v>
+        <v>897</v>
       </c>
       <c r="B543" t="s">
-        <v>559</v>
+        <v>898</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>1018</v>
+        <v>117</v>
       </c>
       <c r="B544" t="s">
-        <v>1019</v>
+        <v>559</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>98</v>
+        <v>1018</v>
       </c>
       <c r="B545" t="s">
-        <v>560</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B546" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>661</v>
+        <v>99</v>
       </c>
       <c r="B547" t="s">
-        <v>736</v>
+        <v>561</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>1094</v>
+        <v>661</v>
       </c>
       <c r="B548" t="s">
-        <v>1017</v>
+        <v>736</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>818</v>
+        <v>1094</v>
       </c>
       <c r="B549" t="s">
-        <v>819</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>113</v>
+        <v>818</v>
       </c>
       <c r="B550" t="s">
-        <v>562</v>
+        <v>819</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>884</v>
+        <v>113</v>
       </c>
       <c r="B551" t="s">
-        <v>885</v>
+        <v>562</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>45</v>
+        <v>884</v>
       </c>
       <c r="B552" t="s">
-        <v>1115</v>
+        <v>885</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>290</v>
+        <v>45</v>
       </c>
       <c r="B553" t="s">
-        <v>563</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B554" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>47</v>
+        <v>299</v>
       </c>
       <c r="B555" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>842</v>
+        <v>47</v>
       </c>
       <c r="B556" t="s">
-        <v>843</v>
+        <v>565</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>51</v>
+        <v>842</v>
       </c>
       <c r="B557" t="s">
-        <v>566</v>
+        <v>843</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>866</v>
+        <v>51</v>
       </c>
       <c r="B558" t="s">
-        <v>867</v>
+        <v>566</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>114</v>
+        <v>866</v>
       </c>
       <c r="B559" t="s">
-        <v>567</v>
+        <v>867</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>848</v>
+        <v>114</v>
       </c>
       <c r="B560" t="s">
-        <v>849</v>
+        <v>567</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>144</v>
+        <v>848</v>
       </c>
       <c r="B561" t="s">
-        <v>568</v>
+        <v>849</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>1071</v>
+        <v>144</v>
       </c>
       <c r="B562" t="s">
-        <v>1072</v>
+        <v>568</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>176</v>
+        <v>1071</v>
       </c>
       <c r="B563" t="s">
-        <v>569</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>315</v>
+        <v>176</v>
       </c>
       <c r="B564" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>29</v>
+        <v>315</v>
       </c>
       <c r="B565" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>1011</v>
+        <v>29</v>
       </c>
       <c r="B566" t="s">
-        <v>1012</v>
+        <v>571</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>1216</v>
+        <v>1011</v>
       </c>
       <c r="B567" t="s">
-        <v>1217</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>293</v>
+        <v>1213</v>
       </c>
       <c r="B568" t="s">
-        <v>572</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>975</v>
+        <v>293</v>
       </c>
       <c r="B569" t="s">
-        <v>976</v>
+        <v>572</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>1450</v>
+        <v>975</v>
       </c>
       <c r="B570" t="s">
-        <v>1451</v>
+        <v>976</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>301</v>
+        <v>1447</v>
       </c>
       <c r="B571" t="s">
-        <v>573</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>997</v>
+        <v>301</v>
       </c>
       <c r="B572" t="s">
-        <v>998</v>
+        <v>573</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="B573" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>75</v>
+        <v>1001</v>
       </c>
       <c r="B574" t="s">
-        <v>574</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B575" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B576" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>328</v>
+        <v>78</v>
       </c>
       <c r="B577" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>1396</v>
+        <v>328</v>
       </c>
       <c r="B578" t="s">
-        <v>1397</v>
+        <v>577</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>1294</v>
+        <v>1393</v>
       </c>
       <c r="B579" t="s">
-        <v>1295</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>747</v>
+        <v>1291</v>
       </c>
       <c r="B580" t="s">
-        <v>748</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>800</v>
+        <v>747</v>
       </c>
       <c r="B581" t="s">
-        <v>801</v>
+        <v>748</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>1307</v>
+        <v>800</v>
       </c>
       <c r="B582" t="s">
-        <v>1308</v>
+        <v>801</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>135</v>
+        <v>1304</v>
       </c>
       <c r="B583" t="s">
-        <v>578</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>1171</v>
+        <v>135</v>
       </c>
       <c r="B584" t="s">
-        <v>1172</v>
+        <v>578</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>1031</v>
+        <v>1168</v>
       </c>
       <c r="B585" t="s">
-        <v>1032</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>215</v>
+        <v>1031</v>
       </c>
       <c r="B586" t="s">
-        <v>579</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>929</v>
+        <v>215</v>
       </c>
       <c r="B587" t="s">
-        <v>1131</v>
+        <v>579</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>216</v>
+        <v>929</v>
       </c>
       <c r="B588" t="s">
-        <v>1113</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>316</v>
+        <v>216</v>
       </c>
       <c r="B589" t="s">
-        <v>580</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>1073</v>
+        <v>316</v>
       </c>
       <c r="B590" t="s">
-        <v>1074</v>
+        <v>580</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>214</v>
+        <v>1073</v>
       </c>
       <c r="B591" t="s">
-        <v>1114</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>993</v>
+        <v>214</v>
       </c>
       <c r="B592" t="s">
-        <v>994</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B593" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>225</v>
+        <v>995</v>
       </c>
       <c r="B594" t="s">
-        <v>581</v>
+        <v>996</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>1383</v>
+        <v>225</v>
       </c>
       <c r="B595" t="s">
-        <v>1384</v>
+        <v>581</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>942</v>
+        <v>1380</v>
       </c>
       <c r="B596" t="s">
-        <v>943</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>1089</v>
+        <v>942</v>
       </c>
       <c r="B597" t="s">
-        <v>1090</v>
+        <v>943</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>1039</v>
+        <v>1089</v>
       </c>
       <c r="B598" t="s">
-        <v>1040</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>93</v>
+        <v>1039</v>
       </c>
       <c r="B599" t="s">
-        <v>582</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="B600" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>778</v>
+        <v>120</v>
       </c>
       <c r="B601" t="s">
-        <v>779</v>
+        <v>583</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>133</v>
+        <v>778</v>
       </c>
       <c r="B602" t="s">
-        <v>584</v>
+        <v>779</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="B603" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>1296</v>
+        <v>62</v>
       </c>
       <c r="B604" t="s">
-        <v>1297</v>
+        <v>585</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>66</v>
+        <v>1293</v>
       </c>
       <c r="B605" t="s">
-        <v>586</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>820</v>
+        <v>66</v>
       </c>
       <c r="B606" t="s">
-        <v>821</v>
+        <v>586</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>944</v>
+        <v>820</v>
       </c>
       <c r="B607" t="s">
-        <v>945</v>
+        <v>821</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>1200</v>
+        <v>944</v>
       </c>
       <c r="B608" t="s">
-        <v>1201</v>
+        <v>945</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>1309</v>
+        <v>1197</v>
       </c>
       <c r="B609" t="s">
-        <v>1310</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>79</v>
+        <v>1306</v>
       </c>
       <c r="B610" t="s">
-        <v>587</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B611" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="B612" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>1169</v>
+        <v>122</v>
       </c>
       <c r="B613" t="s">
-        <v>1170</v>
+        <v>589</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>181</v>
+        <v>1166</v>
       </c>
       <c r="B614" t="s">
-        <v>590</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>796</v>
+        <v>181</v>
       </c>
       <c r="B615" t="s">
-        <v>797</v>
+        <v>590</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>1274</v>
+        <v>796</v>
       </c>
       <c r="B616" t="s">
-        <v>1279</v>
+        <v>797</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>686</v>
+        <v>1271</v>
       </c>
       <c r="B617" t="s">
-        <v>737</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>1275</v>
+        <v>686</v>
       </c>
       <c r="B618" t="s">
-        <v>1280</v>
+        <v>737</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="B619" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="B620" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="B621" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
-        <v>1136</v>
+        <v>1275</v>
       </c>
       <c r="B622" t="s">
-        <v>1137</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B623" t="s">
         <v>1134</v>
-      </c>
-      <c r="B623" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
-        <v>284</v>
+        <v>1131</v>
       </c>
       <c r="B624" t="s">
-        <v>591</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
-        <v>967</v>
+        <v>284</v>
       </c>
       <c r="B625" t="s">
-        <v>968</v>
+        <v>591</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
-        <v>1204</v>
+        <v>967</v>
       </c>
       <c r="B626" t="s">
-        <v>1205</v>
+        <v>968</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>836</v>
+        <v>1201</v>
       </c>
       <c r="B627" t="s">
-        <v>837</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
-        <v>283</v>
+        <v>836</v>
       </c>
       <c r="B628" t="s">
-        <v>592</v>
+        <v>837</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>878</v>
+        <v>283</v>
       </c>
       <c r="B629" t="s">
-        <v>879</v>
+        <v>592</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>1165</v>
+        <v>878</v>
       </c>
       <c r="B630" t="s">
-        <v>1166</v>
+        <v>879</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>751</v>
+        <v>1162</v>
       </c>
       <c r="B631" t="s">
-        <v>752</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>1069</v>
+        <v>751</v>
       </c>
       <c r="B632" t="s">
-        <v>1070</v>
+        <v>752</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
-        <v>67</v>
+        <v>1069</v>
       </c>
       <c r="B633" t="s">
-        <v>593</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B634" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
-        <v>1378</v>
+        <v>68</v>
       </c>
       <c r="B635" t="s">
-        <v>1379</v>
+        <v>594</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
-        <v>95</v>
+        <v>1375</v>
       </c>
       <c r="B636" t="s">
-        <v>595</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
-        <v>289</v>
+        <v>95</v>
       </c>
       <c r="B637" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B638" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="B639" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
-        <v>193</v>
+        <v>264</v>
       </c>
       <c r="B640" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>1338</v>
+        <v>193</v>
       </c>
       <c r="B641" t="s">
-        <v>1339</v>
+        <v>599</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
-        <v>895</v>
+        <v>1335</v>
       </c>
       <c r="B642" t="s">
-        <v>896</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
-        <v>44</v>
+        <v>895</v>
       </c>
       <c r="B643" t="s">
-        <v>1112</v>
+        <v>896</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
-        <v>1061</v>
+        <v>44</v>
       </c>
       <c r="B644" t="s">
-        <v>1062</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
-        <v>323</v>
+        <v>1061</v>
       </c>
       <c r="B645" t="s">
-        <v>600</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B646" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
-        <v>844</v>
+        <v>324</v>
       </c>
       <c r="B647" t="s">
-        <v>845</v>
+        <v>601</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
-        <v>882</v>
+        <v>844</v>
       </c>
       <c r="B648" t="s">
-        <v>883</v>
+        <v>845</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
-        <v>1222</v>
+        <v>882</v>
       </c>
       <c r="B649" t="s">
-        <v>1223</v>
+        <v>883</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
-        <v>864</v>
+        <v>1219</v>
       </c>
       <c r="B650" t="s">
-        <v>865</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
-        <v>33</v>
+        <v>864</v>
       </c>
       <c r="B651" t="s">
-        <v>602</v>
+        <v>865</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B652" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
-        <v>1129</v>
+        <v>36</v>
       </c>
       <c r="B653" t="s">
-        <v>1130</v>
+        <v>603</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
-        <v>309</v>
+        <v>1126</v>
       </c>
       <c r="B654" t="s">
-        <v>604</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
       <c r="B655" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
-        <v>302</v>
+        <v>257</v>
       </c>
       <c r="B656" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
-        <v>228</v>
+        <v>302</v>
       </c>
       <c r="B657" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c r="B658" t="s">
-        <v>18</v>
+        <v>607</v>
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
-        <v>650</v>
+        <v>17</v>
       </c>
       <c r="B659" t="s">
-        <v>738</v>
+        <v>18</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
-        <v>1405</v>
+        <v>650</v>
       </c>
       <c r="B660" t="s">
-        <v>1406</v>
+        <v>738</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
-        <v>780</v>
+        <v>1402</v>
       </c>
       <c r="B661" t="s">
-        <v>781</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
-        <v>142</v>
+        <v>780</v>
       </c>
       <c r="B662" t="s">
-        <v>608</v>
+        <v>781</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
-        <v>1163</v>
+        <v>142</v>
       </c>
       <c r="B663" t="s">
-        <v>1164</v>
+        <v>608</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
-        <v>950</v>
+        <v>1160</v>
       </c>
       <c r="B664" t="s">
-        <v>951</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
-        <v>54</v>
+        <v>950</v>
       </c>
       <c r="B665" t="s">
-        <v>609</v>
+        <v>951</v>
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
-        <v>265</v>
+        <v>54</v>
       </c>
       <c r="B666" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
-        <v>970</v>
+        <v>265</v>
       </c>
       <c r="B667" t="s">
-        <v>969</v>
+        <v>610</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
-        <v>1395</v>
+        <v>970</v>
       </c>
       <c r="B668" t="s">
         <v>969</v>
@@ -10150,271 +10168,271 @@
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
-        <v>56</v>
+        <v>1392</v>
       </c>
       <c r="B669" t="s">
-        <v>611</v>
+        <v>969</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
-        <v>1202</v>
+        <v>56</v>
       </c>
       <c r="B670" t="s">
-        <v>1203</v>
+        <v>611</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
-        <v>185</v>
+        <v>1199</v>
       </c>
       <c r="B671" t="s">
-        <v>612</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="B672" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="B673" t="s">
-        <v>1331</v>
+        <v>613</v>
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
-        <v>1329</v>
+        <v>43</v>
       </c>
       <c r="B674" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
-        <v>1454</v>
+        <v>1326</v>
       </c>
       <c r="B675" t="s">
-        <v>1456</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
       <c r="B676" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
-        <v>40</v>
+        <v>1452</v>
       </c>
       <c r="B677" t="s">
-        <v>1111</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
-        <v>1327</v>
+        <v>40</v>
       </c>
       <c r="B678" t="s">
-        <v>1328</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
-        <v>1155</v>
+        <v>1324</v>
       </c>
       <c r="B679" t="s">
-        <v>1156</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
-        <v>165</v>
+        <v>1152</v>
       </c>
       <c r="B680" t="s">
-        <v>614</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
-        <v>1284</v>
+        <v>165</v>
       </c>
       <c r="B681" t="s">
-        <v>1285</v>
+        <v>614</v>
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
-        <v>1286</v>
+        <v>1281</v>
       </c>
       <c r="B682" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
-        <v>12</v>
+        <v>1283</v>
       </c>
       <c r="B683" t="s">
-        <v>11</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
-        <v>250</v>
+        <v>1472</v>
       </c>
       <c r="B684" t="s">
-        <v>615</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
-        <v>27</v>
+        <v>1474</v>
       </c>
       <c r="B685" t="s">
-        <v>616</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
-        <v>1033</v>
+        <v>12</v>
       </c>
       <c r="B686" t="s">
-        <v>1034</v>
+        <v>11</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
-        <v>28</v>
+        <v>250</v>
       </c>
       <c r="B687" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
-        <v>1190</v>
+        <v>27</v>
       </c>
       <c r="B688" t="s">
-        <v>1191</v>
+        <v>616</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
-        <v>255</v>
+        <v>1033</v>
       </c>
       <c r="B689" t="s">
-        <v>618</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
-        <v>1319</v>
+        <v>28</v>
       </c>
       <c r="B690" t="s">
-        <v>1324</v>
+        <v>617</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
-        <v>790</v>
+        <v>1187</v>
       </c>
       <c r="B691" t="s">
-        <v>791</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="B692" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
-        <v>656</v>
+        <v>1316</v>
       </c>
       <c r="B693" t="s">
-        <v>739</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
-        <v>657</v>
+        <v>790</v>
       </c>
       <c r="B694" t="s">
-        <v>740</v>
+        <v>791</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
-        <v>139</v>
+        <v>267</v>
       </c>
       <c r="B695" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
-        <v>7</v>
+        <v>656</v>
       </c>
       <c r="B696" t="s">
-        <v>2</v>
+        <v>739</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
-        <v>105</v>
+        <v>657</v>
       </c>
       <c r="B697" t="s">
-        <v>621</v>
+        <v>740</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
-        <v>1334</v>
+        <v>139</v>
       </c>
       <c r="B698" t="s">
-        <v>1335</v>
+        <v>620</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
-        <v>1027</v>
+        <v>7</v>
       </c>
       <c r="B699" t="s">
-        <v>1110</v>
+        <v>2</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
-        <v>860</v>
+        <v>105</v>
       </c>
       <c r="B700" t="s">
-        <v>861</v>
+        <v>621</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
-        <v>1434</v>
+        <v>1331</v>
       </c>
       <c r="B701" t="s">
-        <v>1435</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B702" t="s">
         <v>1109</v>
@@ -10422,330 +10440,354 @@
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
-        <v>292</v>
+        <v>860</v>
       </c>
       <c r="B703" t="s">
-        <v>622</v>
+        <v>861</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
-        <v>8</v>
+        <v>1431</v>
       </c>
       <c r="B704" t="s">
-        <v>11</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
-        <v>334</v>
+        <v>1028</v>
       </c>
       <c r="B705" t="s">
-        <v>623</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
-        <v>1376</v>
+        <v>292</v>
       </c>
       <c r="B706" t="s">
-        <v>1377</v>
+        <v>622</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
-        <v>1336</v>
+        <v>8</v>
       </c>
       <c r="B707" t="s">
-        <v>1337</v>
+        <v>11</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B708" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
-        <v>259</v>
+        <v>1373</v>
       </c>
       <c r="B709" t="s">
-        <v>625</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
-        <v>318</v>
+        <v>1333</v>
       </c>
       <c r="B710" t="s">
-        <v>626</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
-        <v>854</v>
+        <v>331</v>
       </c>
       <c r="B711" t="s">
-        <v>855</v>
+        <v>624</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
-        <v>1159</v>
+        <v>259</v>
       </c>
       <c r="B712" t="s">
-        <v>1160</v>
+        <v>625</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
-        <v>268</v>
+        <v>318</v>
       </c>
       <c r="B713" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
-        <v>271</v>
+        <v>854</v>
       </c>
       <c r="B714" t="s">
-        <v>1104</v>
+        <v>855</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A715" t="s">
-        <v>274</v>
+        <v>1156</v>
       </c>
       <c r="B715" t="s">
-        <v>1105</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A716" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B716" t="s">
-        <v>1106</v>
+        <v>627</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B717" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B718" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B719" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
-        <v>92</v>
+        <v>273</v>
       </c>
       <c r="B720" t="s">
-        <v>628</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
-        <v>200</v>
+        <v>269</v>
       </c>
       <c r="B721" t="s">
-        <v>629</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
-        <v>203</v>
+        <v>272</v>
       </c>
       <c r="B722" t="s">
-        <v>630</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
-        <v>1212</v>
+        <v>92</v>
       </c>
       <c r="B723" t="s">
-        <v>1213</v>
+        <v>628</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="B724" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
-        <v>1467</v>
+        <v>203</v>
       </c>
       <c r="B725" t="s">
-        <v>1468</v>
+        <v>630</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
-        <v>688</v>
+        <v>1209</v>
       </c>
       <c r="B726" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="727" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
-        <v>1462</v>
-      </c>
-      <c r="B727" s="1" t="s">
-        <v>1463</v>
+        <v>172</v>
+      </c>
+      <c r="B727" t="s">
+        <v>631</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
-        <v>252</v>
+        <v>1464</v>
       </c>
       <c r="B728" t="s">
-        <v>632</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B729" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="730" spans="1:2" x14ac:dyDescent="0.35">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A730" t="s">
-        <v>189</v>
-      </c>
-      <c r="B730" t="s">
-        <v>1404</v>
+        <v>1459</v>
+      </c>
+      <c r="B730" s="1" t="s">
+        <v>1460</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
-        <v>983</v>
+        <v>252</v>
       </c>
       <c r="B731" t="s">
-        <v>984</v>
+        <v>632</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
-        <v>311</v>
+        <v>689</v>
       </c>
       <c r="B732" t="s">
-        <v>633</v>
+        <v>742</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
-        <v>312</v>
+        <v>189</v>
       </c>
       <c r="B733" t="s">
-        <v>634</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
-        <v>1026</v>
+        <v>983</v>
       </c>
       <c r="B734" t="s">
-        <v>1461</v>
+        <v>984</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
-        <v>1460</v>
+        <v>311</v>
       </c>
       <c r="B735" t="s">
-        <v>1102</v>
+        <v>633</v>
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
-        <v>999</v>
+        <v>312</v>
       </c>
       <c r="B736" t="s">
-        <v>1000</v>
+        <v>634</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A737" t="s">
-        <v>81</v>
+        <v>1026</v>
       </c>
       <c r="B737" t="s">
-        <v>635</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
-        <v>646</v>
+        <v>1457</v>
       </c>
       <c r="B738" t="s">
-        <v>743</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
-        <v>916</v>
+        <v>999</v>
       </c>
       <c r="B739" t="s">
-        <v>917</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A740" t="s">
-        <v>637</v>
+        <v>81</v>
       </c>
       <c r="B740" t="s">
-        <v>744</v>
+        <v>635</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
-        <v>963</v>
+        <v>646</v>
       </c>
       <c r="B741" t="s">
-        <v>964</v>
+        <v>743</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
-        <v>1147</v>
+        <v>916</v>
       </c>
       <c r="B742" t="s">
-        <v>1148</v>
+        <v>917</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
-        <v>1374</v>
+        <v>637</v>
       </c>
       <c r="B743" t="s">
-        <v>1375</v>
+        <v>744</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A744" t="s">
+        <v>963</v>
+      </c>
+      <c r="B744" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A745" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B745" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A746" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B746" t="s">
+        <v>1372</v>
       </c>
     </row>
   </sheetData>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0343EC7C-6A54-40A9-BB48-BE5861DD0E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE1D93F9-99BA-4D93-BAFB-044E519E7B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4362,9 +4362,6 @@
     <t>bloom</t>
   </si>
   <si>
-    <t>No blooming seen on SWI</t>
-  </si>
-  <si>
     <t xml:space="preserve">disc desiccation changes </t>
   </si>
   <si>
@@ -4461,9 +4458,6 @@
     <t>There is fluid signal intensity noted in the pituitary fossa with flattening of the pituitary gland, suggestive of partial empty sella</t>
   </si>
   <si>
-    <t>Multiple tiny T2 hyperintense FLAIR suppressed foci noted in  bilateral frontoparietal lobes, likely Virchow Robin spaces</t>
-  </si>
-  <si>
     <t>Multiple discrete and confluent T2/FLAIR high signal intensities are noted in bilateral periventricular white matter and centrum semi-ovale</t>
   </si>
   <si>
@@ -4471,6 +4465,12 @@
   </si>
   <si>
     <t>Multilevel flowing anterolateral ossification/bridging osteophytes along the thoracic spine involving multiple contiguous vertebral levels, with relative preservation of the intervertebral disc spaces. Findings are suggestive of diffuse idiopathic skeletal hyperostosis (DISH)</t>
+  </si>
+  <si>
+    <t>No blooming seen on SWI/GRE</t>
+  </si>
+  <si>
+    <t>Multiple tiny T2 hyperintense FLAIR suppressed foci without gliotic rim noted in  bilateral frontoparietal lobes, likely Virchow Robin spaces</t>
   </si>
 </sst>
 </file>
@@ -5176,7 +5176,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="B45" t="s">
         <v>1341</v>
@@ -5379,7 +5379,7 @@
         <v>1443</v>
       </c>
       <c r="B70" t="s">
-        <v>1444</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
@@ -5712,10 +5712,10 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B112" t="s">
         <v>1455</v>
-      </c>
-      <c r="B112" t="s">
-        <v>1456</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
@@ -5923,7 +5923,7 @@
         <v>104</v>
       </c>
       <c r="B138" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
@@ -6019,7 +6019,7 @@
         <v>1309</v>
       </c>
       <c r="B150" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
@@ -6267,7 +6267,7 @@
         <v>211</v>
       </c>
       <c r="B181" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
@@ -6275,7 +6275,7 @@
         <v>213</v>
       </c>
       <c r="B182" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
@@ -6360,10 +6360,10 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="B193" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
@@ -6552,10 +6552,10 @@
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B217" t="s">
         <v>1468</v>
-      </c>
-      <c r="B217" t="s">
-        <v>1469</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
@@ -6584,7 +6584,7 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="B221" t="s">
         <v>1426</v>
@@ -6608,7 +6608,7 @@
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="B224" t="s">
         <v>886</v>
@@ -6944,10 +6944,10 @@
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B266" t="s">
         <v>1449</v>
-      </c>
-      <c r="B266" t="s">
-        <v>1450</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
@@ -7560,10 +7560,10 @@
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="B343" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
@@ -9123,7 +9123,7 @@
         <v>38</v>
       </c>
       <c r="B538" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
@@ -9384,10 +9384,10 @@
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B571" t="s">
         <v>1447</v>
-      </c>
-      <c r="B571" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
@@ -10224,18 +10224,18 @@
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="B676" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="B677" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.35">
@@ -10243,7 +10243,7 @@
         <v>40</v>
       </c>
       <c r="B678" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.35">
@@ -10288,18 +10288,18 @@
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B684" t="s">
         <v>1472</v>
-      </c>
-      <c r="B684" t="s">
-        <v>1473</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B685" t="s">
         <v>1474</v>
-      </c>
-      <c r="B685" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.35">
@@ -10640,10 +10640,10 @@
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B728" t="s">
         <v>1464</v>
-      </c>
-      <c r="B728" t="s">
-        <v>1465</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.35">
@@ -10656,10 +10656,10 @@
     </row>
     <row r="730" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A730" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B730" s="1" t="s">
         <v>1459</v>
-      </c>
-      <c r="B730" s="1" t="s">
-        <v>1460</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.35">
@@ -10715,15 +10715,15 @@
         <v>1026</v>
       </c>
       <c r="B737" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="B738" t="s">
-        <v>1477</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.35">

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE1D93F9-99BA-4D93-BAFB-044E519E7B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DF13C7-6F26-446B-AD9F-4BF78A61661F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1492" uniqueCount="1481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="1487">
   <si>
     <t>trigger</t>
   </si>
@@ -4458,9 +4458,6 @@
     <t>There is fluid signal intensity noted in the pituitary fossa with flattening of the pituitary gland, suggestive of partial empty sella</t>
   </si>
   <si>
-    <t>Multiple discrete and confluent T2/FLAIR high signal intensities are noted in bilateral periventricular white matter and centrum semi-ovale</t>
-  </si>
-  <si>
     <t>dishx</t>
   </si>
   <si>
@@ -4471,6 +4468,27 @@
   </si>
   <si>
     <t>Multiple tiny T2 hyperintense FLAIR suppressed foci without gliotic rim noted in  bilateral frontoparietal lobes, likely Virchow Robin spaces</t>
+  </si>
+  <si>
+    <t>chrif</t>
+  </si>
+  <si>
+    <t>Well-defined T2 high FLAIR suppressed signal intensity with surrounding gliotic rim is noted in</t>
+  </si>
+  <si>
+    <t>nswmh</t>
+  </si>
+  <si>
+    <t>Multiple discrete T2/FLAIR hyperintensities are noted in subcortical and deep white matter of bilateral frontoparietal lobes. No restriction of diffusion on DWI</t>
+  </si>
+  <si>
+    <t>nswm</t>
+  </si>
+  <si>
+    <t>Non-specific white matter hyperintensities in bilateral frontoparietal lobes</t>
+  </si>
+  <si>
+    <t>Multiple discrete and confluent T2/FLAIR high signal intensities are noted in bilateral periventricular white matter and centrum semi-ovale. No restriction of diffusion on DWI</t>
   </si>
 </sst>
 </file>
@@ -4539,10 +4557,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B746" totalsRowShown="0">
-  <autoFilter ref="A1:B746" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B746">
-    <sortCondition ref="A1:A746"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B749" totalsRowShown="0">
+  <autoFilter ref="A1:B749" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B749">
+    <sortCondition ref="A1:A749"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4815,7 +4833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B746"/>
+  <dimension ref="A1:B749"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -5379,7 +5397,7 @@
         <v>1443</v>
       </c>
       <c r="B70" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
@@ -5824,895 +5842,895 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>152</v>
+        <v>1480</v>
       </c>
       <c r="B126" t="s">
-        <v>393</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>1303</v>
+        <v>152</v>
       </c>
       <c r="B127" t="s">
-        <v>1308</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>124</v>
+        <v>1303</v>
       </c>
       <c r="B128" t="s">
-        <v>395</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B129" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="B130" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>961</v>
+        <v>155</v>
       </c>
       <c r="B131" t="s">
-        <v>962</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>84</v>
+        <v>961</v>
       </c>
       <c r="B132" t="s">
-        <v>397</v>
+        <v>962</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>959</v>
+        <v>84</v>
       </c>
       <c r="B133" t="s">
-        <v>960</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>1390</v>
+        <v>959</v>
       </c>
       <c r="B134" t="s">
-        <v>1391</v>
+        <v>960</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>103</v>
+        <v>1390</v>
       </c>
       <c r="B135" t="s">
-        <v>398</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>198</v>
+        <v>103</v>
       </c>
       <c r="B136" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>314</v>
+        <v>198</v>
       </c>
       <c r="B137" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>104</v>
+        <v>314</v>
       </c>
       <c r="B138" t="s">
-        <v>1470</v>
+        <v>400</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="B139" t="s">
-        <v>401</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="B140" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B141" t="s">
-        <v>1323</v>
+        <v>402</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>1322</v>
+        <v>102</v>
       </c>
       <c r="B142" t="s">
-        <v>403</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>924</v>
+        <v>1322</v>
       </c>
       <c r="B143" t="s">
-        <v>925</v>
+        <v>403</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B144" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>162</v>
+        <v>922</v>
       </c>
       <c r="B145" t="s">
-        <v>404</v>
+        <v>923</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>1135</v>
+        <v>162</v>
       </c>
       <c r="B146" t="s">
-        <v>1136</v>
+        <v>404</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>1366</v>
+        <v>1135</v>
       </c>
       <c r="B147" t="s">
-        <v>1367</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>832</v>
+        <v>1366</v>
       </c>
       <c r="B148" t="s">
-        <v>833</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B149" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>1309</v>
+        <v>834</v>
       </c>
       <c r="B150" t="s">
-        <v>1469</v>
+        <v>835</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>1075</v>
+        <v>1309</v>
       </c>
       <c r="B151" t="s">
-        <v>1076</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>660</v>
+        <v>1075</v>
       </c>
       <c r="B152" t="s">
-        <v>703</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>641</v>
+        <v>660</v>
       </c>
       <c r="B153" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>934</v>
+        <v>641</v>
       </c>
       <c r="B154" t="s">
-        <v>935</v>
+        <v>704</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>1441</v>
+        <v>934</v>
       </c>
       <c r="B155" t="s">
-        <v>1442</v>
+        <v>935</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>1360</v>
+        <v>1441</v>
       </c>
       <c r="B156" t="s">
-        <v>1361</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>1237</v>
+        <v>1360</v>
       </c>
       <c r="B157" t="s">
-        <v>1249</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>1246</v>
+        <v>1237</v>
       </c>
       <c r="B158" t="s">
-        <v>1258</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>678</v>
+        <v>1246</v>
       </c>
       <c r="B159" t="s">
-        <v>705</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>1247</v>
+        <v>678</v>
       </c>
       <c r="B160" t="s">
-        <v>1259</v>
+        <v>705</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>679</v>
+        <v>1247</v>
       </c>
       <c r="B161" t="s">
-        <v>706</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>1248</v>
+        <v>679</v>
       </c>
       <c r="B162" t="s">
-        <v>1260</v>
+        <v>706</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>680</v>
+        <v>1248</v>
       </c>
       <c r="B163" t="s">
-        <v>707</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>1238</v>
+        <v>680</v>
       </c>
       <c r="B164" t="s">
-        <v>1250</v>
+        <v>707</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>670</v>
+        <v>1238</v>
       </c>
       <c r="B165" t="s">
-        <v>708</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>1239</v>
+        <v>670</v>
       </c>
       <c r="B166" t="s">
-        <v>1251</v>
+        <v>708</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>671</v>
+        <v>1239</v>
       </c>
       <c r="B167" t="s">
-        <v>709</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>1240</v>
+        <v>671</v>
       </c>
       <c r="B168" t="s">
-        <v>1252</v>
+        <v>709</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>672</v>
+        <v>1240</v>
       </c>
       <c r="B169" t="s">
-        <v>710</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>1241</v>
+        <v>672</v>
       </c>
       <c r="B170" t="s">
-        <v>1253</v>
+        <v>710</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>673</v>
+        <v>1241</v>
       </c>
       <c r="B171" t="s">
-        <v>711</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>1242</v>
+        <v>673</v>
       </c>
       <c r="B172" t="s">
-        <v>1254</v>
+        <v>711</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>674</v>
+        <v>1242</v>
       </c>
       <c r="B173" t="s">
-        <v>712</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>1243</v>
+        <v>674</v>
       </c>
       <c r="B174" t="s">
-        <v>1255</v>
+        <v>712</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>675</v>
+        <v>1243</v>
       </c>
       <c r="B175" t="s">
-        <v>713</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>1244</v>
+        <v>675</v>
       </c>
       <c r="B176" t="s">
-        <v>1256</v>
+        <v>713</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>676</v>
+        <v>1244</v>
       </c>
       <c r="B177" t="s">
-        <v>714</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>1245</v>
+        <v>676</v>
       </c>
       <c r="B178" t="s">
-        <v>1257</v>
+        <v>714</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>677</v>
+        <v>1245</v>
       </c>
       <c r="B179" t="s">
-        <v>715</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>175</v>
+        <v>677</v>
       </c>
       <c r="B180" t="s">
-        <v>405</v>
+        <v>715</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="B181" t="s">
-        <v>1444</v>
+        <v>405</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B182" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>1319</v>
+        <v>213</v>
       </c>
       <c r="B183" t="s">
-        <v>1320</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>1354</v>
+        <v>1319</v>
       </c>
       <c r="B184" t="s">
-        <v>1355</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>1191</v>
+        <v>1354</v>
       </c>
       <c r="B185" t="s">
-        <v>406</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>149</v>
+        <v>1191</v>
       </c>
       <c r="B186" t="s">
-        <v>1194</v>
+        <v>406</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>247</v>
+        <v>149</v>
       </c>
       <c r="B187" t="s">
-        <v>407</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B188" t="s">
-        <v>1398</v>
+        <v>407</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>335</v>
+        <v>245</v>
       </c>
       <c r="B189" t="s">
-        <v>408</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>645</v>
+        <v>335</v>
       </c>
       <c r="B190" t="s">
-        <v>716</v>
+        <v>408</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>91</v>
+        <v>645</v>
       </c>
       <c r="B191" t="s">
-        <v>409</v>
+        <v>716</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>266</v>
+        <v>91</v>
       </c>
       <c r="B192" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>1477</v>
+        <v>266</v>
       </c>
       <c r="B193" t="s">
-        <v>1478</v>
+        <v>410</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>1087</v>
+        <v>1476</v>
       </c>
       <c r="B194" t="s">
-        <v>1088</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>794</v>
+        <v>1087</v>
       </c>
       <c r="B195" t="s">
-        <v>795</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>1150</v>
+        <v>794</v>
       </c>
       <c r="B196" t="s">
-        <v>1151</v>
+        <v>795</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>1337</v>
+        <v>1150</v>
       </c>
       <c r="B197" t="s">
-        <v>1338</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>295</v>
+        <v>1337</v>
       </c>
       <c r="B198" t="s">
-        <v>411</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>1077</v>
+        <v>295</v>
       </c>
       <c r="B199" t="s">
-        <v>1078</v>
+        <v>411</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="B200" t="s">
-        <v>1084</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>151</v>
+        <v>1083</v>
       </c>
       <c r="B201" t="s">
-        <v>412</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>955</v>
+        <v>151</v>
       </c>
       <c r="B202" t="s">
-        <v>956</v>
+        <v>412</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>808</v>
+        <v>955</v>
       </c>
       <c r="B203" t="s">
-        <v>809</v>
+        <v>956</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>926</v>
+        <v>808</v>
       </c>
       <c r="B204" t="s">
-        <v>927</v>
+        <v>809</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>828</v>
+        <v>926</v>
       </c>
       <c r="B205" t="s">
-        <v>829</v>
+        <v>927</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>788</v>
+        <v>828</v>
       </c>
       <c r="B206" t="s">
-        <v>789</v>
+        <v>829</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>1422</v>
+        <v>788</v>
       </c>
       <c r="B207" t="s">
-        <v>1423</v>
+        <v>789</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>749</v>
+        <v>1422</v>
       </c>
       <c r="B208" t="s">
-        <v>750</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>100</v>
+        <v>749</v>
       </c>
       <c r="B209" t="s">
-        <v>413</v>
+        <v>750</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>1035</v>
+        <v>100</v>
       </c>
       <c r="B210" t="s">
-        <v>1036</v>
+        <v>413</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>154</v>
+        <v>1035</v>
       </c>
       <c r="B211" t="s">
-        <v>414</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B212" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="B213" t="s">
-        <v>1121</v>
+        <v>415</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>1146</v>
+        <v>24</v>
       </c>
       <c r="B214" t="s">
-        <v>1147</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>1310</v>
+        <v>1146</v>
       </c>
       <c r="B215" t="s">
-        <v>1311</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>1067</v>
+        <v>1310</v>
       </c>
       <c r="B216" t="s">
-        <v>1068</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>1467</v>
+        <v>1067</v>
       </c>
       <c r="B217" t="s">
-        <v>1468</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>814</v>
+        <v>1467</v>
       </c>
       <c r="B218" t="s">
-        <v>815</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>130</v>
+        <v>814</v>
       </c>
       <c r="B219" t="s">
-        <v>416</v>
+        <v>815</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>321</v>
+        <v>130</v>
       </c>
       <c r="B220" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>1466</v>
+        <v>321</v>
       </c>
       <c r="B221" t="s">
-        <v>1426</v>
+        <v>417</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>862</v>
+        <v>1466</v>
       </c>
       <c r="B222" t="s">
-        <v>863</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>1429</v>
+        <v>862</v>
       </c>
       <c r="B223" t="s">
-        <v>1430</v>
+        <v>863</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>1465</v>
+        <v>1429</v>
       </c>
       <c r="B224" t="s">
-        <v>886</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>1299</v>
+        <v>1465</v>
       </c>
       <c r="B225" t="s">
-        <v>1300</v>
+        <v>886</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>183</v>
+        <v>1299</v>
       </c>
       <c r="B226" t="s">
-        <v>418</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>1137</v>
+        <v>183</v>
       </c>
       <c r="B227" t="s">
-        <v>1138</v>
+        <v>418</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B228" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>1420</v>
+        <v>1139</v>
       </c>
       <c r="B229" t="s">
-        <v>1421</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>1378</v>
+        <v>1420</v>
       </c>
       <c r="B230" t="s">
-        <v>1379</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>32</v>
+        <v>1378</v>
       </c>
       <c r="B231" t="s">
-        <v>419</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B232" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>1289</v>
+        <v>35</v>
       </c>
       <c r="B233" t="s">
-        <v>1290</v>
+        <v>420</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>1215</v>
+        <v>1289</v>
       </c>
       <c r="B234" t="s">
-        <v>1216</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>759</v>
+        <v>1215</v>
       </c>
       <c r="B235" t="s">
-        <v>1003</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>169</v>
+        <v>759</v>
       </c>
       <c r="B236" t="s">
-        <v>421</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B237" t="s">
         <v>421</v>
@@ -6720,591 +6738,591 @@
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>1004</v>
+        <v>170</v>
       </c>
       <c r="B238" t="s">
-        <v>760</v>
+        <v>421</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>1418</v>
+        <v>1004</v>
       </c>
       <c r="B239" t="s">
-        <v>1419</v>
+        <v>760</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>178</v>
+        <v>1418</v>
       </c>
       <c r="B240" t="s">
-        <v>422</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="B241" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>238</v>
+        <v>111</v>
       </c>
       <c r="B242" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="B243" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B244" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="B245" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>662</v>
+        <v>179</v>
       </c>
       <c r="B246" t="s">
-        <v>717</v>
+        <v>427</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>97</v>
+        <v>662</v>
       </c>
       <c r="B247" t="s">
-        <v>428</v>
+        <v>717</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B248" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>242</v>
+        <v>110</v>
       </c>
       <c r="B249" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B250" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="B251" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>1416</v>
+        <v>177</v>
       </c>
       <c r="B252" t="s">
-        <v>1417</v>
+        <v>432</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>182</v>
+        <v>1416</v>
       </c>
       <c r="B253" t="s">
-        <v>433</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>1097</v>
+        <v>182</v>
       </c>
       <c r="B254" t="s">
-        <v>1098</v>
+        <v>433</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>971</v>
+        <v>1097</v>
       </c>
       <c r="B255" t="s">
-        <v>972</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B256" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>1180</v>
+        <v>973</v>
       </c>
       <c r="B257" t="s">
-        <v>1181</v>
+        <v>974</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>1358</v>
+        <v>1180</v>
       </c>
       <c r="B258" t="s">
-        <v>1359</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>1183</v>
+        <v>1358</v>
       </c>
       <c r="B259" t="s">
-        <v>1184</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>253</v>
+        <v>1183</v>
       </c>
       <c r="B260" t="s">
-        <v>434</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="B261" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>782</v>
+        <v>34</v>
       </c>
       <c r="B262" t="s">
-        <v>783</v>
+        <v>435</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>180</v>
+        <v>782</v>
       </c>
       <c r="B263" t="s">
-        <v>436</v>
+        <v>783</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>1330</v>
+        <v>180</v>
       </c>
       <c r="B264" t="s">
-        <v>1399</v>
+        <v>436</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B265" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>1448</v>
+        <v>1329</v>
       </c>
       <c r="B266" t="s">
-        <v>1449</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>275</v>
+        <v>1448</v>
       </c>
       <c r="B267" t="s">
-        <v>437</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>852</v>
+        <v>275</v>
       </c>
       <c r="B268" t="s">
-        <v>853</v>
+        <v>437</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>116</v>
+        <v>852</v>
       </c>
       <c r="B269" t="s">
-        <v>438</v>
+        <v>853</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="B270" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>1404</v>
+        <v>208</v>
       </c>
       <c r="B271" t="s">
-        <v>1405</v>
+        <v>439</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>1203</v>
+        <v>1404</v>
       </c>
       <c r="B272" t="s">
-        <v>1204</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>1047</v>
+        <v>1203</v>
       </c>
       <c r="B273" t="s">
-        <v>1048</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>118</v>
+        <v>1047</v>
       </c>
       <c r="B274" t="s">
-        <v>440</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>636</v>
+        <v>118</v>
       </c>
       <c r="B275" t="s">
-        <v>718</v>
+        <v>440</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>1314</v>
+        <v>636</v>
       </c>
       <c r="B276" t="s">
-        <v>1315</v>
+        <v>718</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>810</v>
+        <v>1314</v>
       </c>
       <c r="B277" t="s">
-        <v>811</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>298</v>
+        <v>810</v>
       </c>
       <c r="B278" t="s">
-        <v>441</v>
+        <v>811</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>638</v>
+        <v>298</v>
       </c>
       <c r="B279" t="s">
-        <v>719</v>
+        <v>441</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B280" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>1029</v>
+        <v>639</v>
       </c>
       <c r="B281" t="s">
-        <v>1030</v>
+        <v>720</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>90</v>
+        <v>1029</v>
       </c>
       <c r="B282" t="s">
-        <v>442</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B283" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B284" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>1063</v>
+        <v>89</v>
       </c>
       <c r="B285" t="s">
-        <v>1064</v>
+        <v>444</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>23</v>
+        <v>1063</v>
       </c>
       <c r="B286" t="s">
-        <v>1120</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>1408</v>
+        <v>23</v>
       </c>
       <c r="B287" t="s">
-        <v>1409</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>5</v>
+        <v>1408</v>
       </c>
       <c r="B288" t="s">
-        <v>6</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>1124</v>
+        <v>5</v>
       </c>
       <c r="B289" t="s">
-        <v>1125</v>
+        <v>6</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>126</v>
+        <v>1124</v>
       </c>
       <c r="B290" t="s">
-        <v>445</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>1382</v>
+        <v>126</v>
       </c>
       <c r="B291" t="s">
-        <v>1383</v>
+        <v>445</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>128</v>
+        <v>1382</v>
       </c>
       <c r="B292" t="s">
-        <v>446</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B293" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B294" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B295" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>277</v>
+        <v>119</v>
       </c>
       <c r="B296" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>1065</v>
+        <v>277</v>
       </c>
       <c r="B297" t="s">
-        <v>1066</v>
+        <v>450</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>9</v>
+        <v>1065</v>
       </c>
       <c r="B298" t="s">
-        <v>10</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="B299" t="s">
-        <v>451</v>
+        <v>10</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B300" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="B301" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="B302" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>1369</v>
+        <v>262</v>
       </c>
       <c r="B303" t="s">
-        <v>1370</v>
+        <v>454</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>77</v>
+        <v>1369</v>
       </c>
       <c r="B304" t="s">
-        <v>455</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>932</v>
+        <v>77</v>
       </c>
       <c r="B305" t="s">
-        <v>933</v>
+        <v>455</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>1154</v>
+        <v>932</v>
       </c>
       <c r="B306" t="s">
-        <v>1155</v>
+        <v>933</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>168</v>
+        <v>1154</v>
       </c>
       <c r="B307" t="s">
-        <v>456</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>1342</v>
+        <v>168</v>
       </c>
       <c r="B308" t="s">
-        <v>1343</v>
+        <v>456</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>1352</v>
+        <v>1342</v>
       </c>
       <c r="B309" t="s">
-        <v>1353</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>1395</v>
+        <v>1352</v>
       </c>
       <c r="B310" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>1348</v>
+        <v>1395</v>
       </c>
       <c r="B311" t="s">
         <v>1349</v>
@@ -7312,39 +7330,39 @@
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>167</v>
+        <v>1348</v>
       </c>
       <c r="B312" t="s">
-        <v>457</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>1344</v>
+        <v>167</v>
       </c>
       <c r="B313" t="s">
-        <v>1345</v>
+        <v>457</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>1350</v>
+        <v>1344</v>
       </c>
       <c r="B314" t="s">
-        <v>1351</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>1377</v>
+        <v>1350</v>
       </c>
       <c r="B315" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>1346</v>
+        <v>1377</v>
       </c>
       <c r="B316" t="s">
         <v>1347</v>
@@ -7352,199 +7370,199 @@
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>830</v>
+        <v>1346</v>
       </c>
       <c r="B317" t="s">
-        <v>831</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>786</v>
+        <v>830</v>
       </c>
       <c r="B318" t="s">
-        <v>787</v>
+        <v>831</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>304</v>
+        <v>786</v>
       </c>
       <c r="B319" t="s">
-        <v>458</v>
+        <v>787</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>753</v>
+        <v>304</v>
       </c>
       <c r="B320" t="s">
-        <v>754</v>
+        <v>458</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>891</v>
+        <v>753</v>
       </c>
       <c r="B321" t="s">
-        <v>892</v>
+        <v>754</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>1384</v>
+        <v>891</v>
       </c>
       <c r="B322" t="s">
-        <v>1385</v>
+        <v>892</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>647</v>
+        <v>1384</v>
       </c>
       <c r="B323" t="s">
-        <v>721</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>86</v>
+        <v>647</v>
       </c>
       <c r="B324" t="s">
-        <v>459</v>
+        <v>721</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B325" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="B326" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B327" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B328" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>251</v>
+        <v>158</v>
       </c>
       <c r="B329" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="B330" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>325</v>
+        <v>285</v>
       </c>
       <c r="B331" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>1364</v>
+        <v>325</v>
       </c>
       <c r="B332" t="s">
-        <v>1365</v>
+        <v>466</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>326</v>
+        <v>1364</v>
       </c>
       <c r="B333" t="s">
-        <v>467</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>229</v>
+        <v>326</v>
       </c>
       <c r="B334" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>55</v>
+        <v>229</v>
       </c>
       <c r="B335" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>652</v>
+        <v>55</v>
       </c>
       <c r="B336" t="s">
-        <v>722</v>
+        <v>469</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>235</v>
+        <v>652</v>
       </c>
       <c r="B337" t="s">
-        <v>470</v>
+        <v>722</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="B338" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="B339" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>761</v>
+        <v>236</v>
       </c>
       <c r="B340" t="s">
-        <v>762</v>
+        <v>472</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>1005</v>
+        <v>761</v>
       </c>
       <c r="B341" t="s">
         <v>762</v>
@@ -7552,631 +7570,631 @@
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>164</v>
+        <v>1005</v>
       </c>
       <c r="B342" t="s">
-        <v>473</v>
+        <v>762</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>1462</v>
+        <v>164</v>
       </c>
       <c r="B343" t="s">
-        <v>1460</v>
+        <v>473</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>201</v>
+        <v>1462</v>
       </c>
       <c r="B344" t="s">
-        <v>474</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B345" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>313</v>
+        <v>204</v>
       </c>
       <c r="B346" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>868</v>
+        <v>313</v>
       </c>
       <c r="B347" t="s">
-        <v>869</v>
+        <v>476</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>991</v>
+        <v>868</v>
       </c>
       <c r="B348" t="s">
-        <v>992</v>
+        <v>869</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>1317</v>
+        <v>991</v>
       </c>
       <c r="B349" t="s">
-        <v>1318</v>
+        <v>992</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>258</v>
+        <v>1317</v>
       </c>
       <c r="B350" t="s">
-        <v>477</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>977</v>
+        <v>258</v>
       </c>
       <c r="B351" t="s">
-        <v>978</v>
+        <v>477</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>1356</v>
+        <v>977</v>
       </c>
       <c r="B352" t="s">
-        <v>1357</v>
+        <v>978</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>160</v>
+        <v>1356</v>
       </c>
       <c r="B353" t="s">
-        <v>478</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>687</v>
+        <v>160</v>
       </c>
       <c r="B354" t="s">
-        <v>723</v>
+        <v>478</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>1148</v>
+        <v>687</v>
       </c>
       <c r="B355" t="s">
-        <v>1149</v>
+        <v>723</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>755</v>
+        <v>1148</v>
       </c>
       <c r="B356" t="s">
-        <v>756</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>889</v>
+        <v>755</v>
       </c>
       <c r="B357" t="s">
-        <v>890</v>
+        <v>756</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B358" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>184</v>
+        <v>887</v>
       </c>
       <c r="B359" t="s">
-        <v>479</v>
+        <v>888</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>244</v>
+        <v>184</v>
       </c>
       <c r="B360" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B361" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>1261</v>
+        <v>243</v>
       </c>
       <c r="B362" t="s">
-        <v>1266</v>
+        <v>481</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>681</v>
+        <v>1261</v>
       </c>
       <c r="B363" t="s">
-        <v>724</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>1262</v>
+        <v>681</v>
       </c>
       <c r="B364" t="s">
-        <v>1267</v>
+        <v>724</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>682</v>
+        <v>1262</v>
       </c>
       <c r="B365" t="s">
-        <v>725</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>1263</v>
+        <v>682</v>
       </c>
       <c r="B366" t="s">
-        <v>1268</v>
+        <v>725</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>683</v>
+        <v>1263</v>
       </c>
       <c r="B367" t="s">
-        <v>726</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>1264</v>
+        <v>683</v>
       </c>
       <c r="B368" t="s">
-        <v>1269</v>
+        <v>726</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>684</v>
+        <v>1264</v>
       </c>
       <c r="B369" t="s">
-        <v>727</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>1265</v>
+        <v>684</v>
       </c>
       <c r="B370" t="s">
-        <v>1270</v>
+        <v>727</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>685</v>
+        <v>1265</v>
       </c>
       <c r="B371" t="s">
-        <v>728</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>1174</v>
+        <v>685</v>
       </c>
       <c r="B372" t="s">
-        <v>1175</v>
+        <v>728</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>280</v>
+        <v>1174</v>
       </c>
       <c r="B373" t="s">
-        <v>482</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B374" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>49</v>
+        <v>281</v>
       </c>
       <c r="B375" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B376" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="B377" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>1437</v>
+        <v>136</v>
       </c>
       <c r="B378" t="s">
-        <v>1438</v>
+        <v>487</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>72</v>
+        <v>1437</v>
       </c>
       <c r="B379" t="s">
-        <v>486</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>1172</v>
+        <v>72</v>
       </c>
       <c r="B380" t="s">
-        <v>1173</v>
+        <v>486</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>221</v>
+        <v>1172</v>
       </c>
       <c r="B381" t="s">
-        <v>488</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>1176</v>
+        <v>221</v>
       </c>
       <c r="B382" t="s">
-        <v>1177</v>
+        <v>488</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>15</v>
+        <v>1176</v>
       </c>
       <c r="B383" t="s">
-        <v>16</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>1051</v>
+        <v>15</v>
       </c>
       <c r="B384" t="s">
-        <v>1052</v>
+        <v>16</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>914</v>
+        <v>1051</v>
       </c>
       <c r="B385" t="s">
-        <v>915</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>108</v>
+        <v>914</v>
       </c>
       <c r="B386" t="s">
-        <v>489</v>
+        <v>915</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>241</v>
+        <v>108</v>
       </c>
       <c r="B387" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>327</v>
+        <v>241</v>
       </c>
       <c r="B388" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>1091</v>
+        <v>327</v>
       </c>
       <c r="B389" t="s">
-        <v>1092</v>
+        <v>491</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>1043</v>
+        <v>1091</v>
       </c>
       <c r="B390" t="s">
-        <v>1044</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>121</v>
+        <v>1043</v>
       </c>
       <c r="B391" t="s">
-        <v>492</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>745</v>
+        <v>121</v>
       </c>
       <c r="B392" t="s">
-        <v>746</v>
+        <v>492</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>776</v>
+        <v>745</v>
       </c>
       <c r="B393" t="s">
-        <v>777</v>
+        <v>746</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>134</v>
+        <v>776</v>
       </c>
       <c r="B394" t="s">
-        <v>493</v>
+        <v>777</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="B395" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>1295</v>
+        <v>63</v>
       </c>
       <c r="B396" t="s">
-        <v>1296</v>
+        <v>494</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>224</v>
+        <v>1295</v>
       </c>
       <c r="B397" t="s">
-        <v>495</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>25</v>
+        <v>224</v>
       </c>
       <c r="B398" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B399" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>207</v>
+        <v>26</v>
       </c>
       <c r="B400" t="s">
-        <v>1117</v>
+        <v>497</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>954</v>
+        <v>207</v>
       </c>
       <c r="B401" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>1100</v>
+        <v>954</v>
       </c>
       <c r="B402" t="s">
-        <v>1101</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>206</v>
+        <v>1100</v>
       </c>
       <c r="B403" t="s">
-        <v>1119</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B404" t="s">
-        <v>498</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B405" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="B406" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>658</v>
+        <v>145</v>
       </c>
       <c r="B407" t="s">
-        <v>729</v>
+        <v>500</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>171</v>
+        <v>658</v>
       </c>
       <c r="B408" t="s">
-        <v>501</v>
+        <v>729</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>1079</v>
+        <v>171</v>
       </c>
       <c r="B409" t="s">
-        <v>1080</v>
+        <v>501</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>263</v>
+        <v>1079</v>
       </c>
       <c r="B410" t="s">
-        <v>502</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>1081</v>
+        <v>263</v>
       </c>
       <c r="B411" t="s">
-        <v>1082</v>
+        <v>502</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>80</v>
+        <v>1081</v>
       </c>
       <c r="B412" t="s">
-        <v>503</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B413" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>191</v>
+        <v>65</v>
       </c>
       <c r="B414" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="B415" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>192</v>
+        <v>123</v>
       </c>
       <c r="B416" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="B417" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B418" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>1182</v>
+        <v>233</v>
       </c>
       <c r="B419" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>31</v>
+        <v>1182</v>
       </c>
       <c r="B420" t="s">
         <v>510</v>
@@ -8184,367 +8202,367 @@
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B421" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B422" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B423" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>1435</v>
+        <v>71</v>
       </c>
       <c r="B424" t="s">
-        <v>1436</v>
+        <v>513</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>306</v>
+        <v>1435</v>
       </c>
       <c r="B425" t="s">
-        <v>514</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>222</v>
+        <v>306</v>
       </c>
       <c r="B426" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>278</v>
+        <v>222</v>
       </c>
       <c r="B427" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B428" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>1386</v>
+        <v>279</v>
       </c>
       <c r="B429" t="s">
-        <v>1387</v>
+        <v>518</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>826</v>
+        <v>1386</v>
       </c>
       <c r="B430" t="s">
-        <v>827</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>48</v>
+        <v>826</v>
       </c>
       <c r="B431" t="s">
-        <v>519</v>
+        <v>827</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="B432" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="B433" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>1368</v>
+        <v>52</v>
       </c>
       <c r="B434" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>223</v>
+        <v>1368</v>
       </c>
       <c r="B435" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>1085</v>
+        <v>223</v>
       </c>
       <c r="B436" t="s">
-        <v>1086</v>
+        <v>522</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>1096</v>
+        <v>1085</v>
       </c>
       <c r="B437" t="s">
-        <v>1099</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>1041</v>
+        <v>1096</v>
       </c>
       <c r="B438" t="s">
-        <v>1042</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>96</v>
+        <v>1041</v>
       </c>
       <c r="B439" t="s">
-        <v>523</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>248</v>
+        <v>96</v>
       </c>
       <c r="B440" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B441" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>94</v>
+        <v>249</v>
       </c>
       <c r="B442" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>1055</v>
+        <v>94</v>
       </c>
       <c r="B443" t="s">
-        <v>1056</v>
+        <v>526</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>212</v>
+        <v>1055</v>
       </c>
       <c r="B444" t="s">
-        <v>527</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>1207</v>
+        <v>212</v>
       </c>
       <c r="B445" t="s">
-        <v>1208</v>
+        <v>527</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>910</v>
+        <v>1207</v>
       </c>
       <c r="B446" t="s">
-        <v>911</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B447" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="B448" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>329</v>
+        <v>912</v>
       </c>
       <c r="B449" t="s">
-        <v>528</v>
+        <v>913</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>1410</v>
+        <v>329</v>
       </c>
       <c r="B450" t="s">
-        <v>1411</v>
+        <v>528</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="B451" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>1057</v>
+        <v>1412</v>
       </c>
       <c r="B452" t="s">
-        <v>1058</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>989</v>
+        <v>1057</v>
       </c>
       <c r="B453" t="s">
-        <v>990</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>1396</v>
+        <v>989</v>
       </c>
       <c r="B454" t="s">
-        <v>1397</v>
+        <v>990</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>985</v>
+        <v>1396</v>
       </c>
       <c r="B455" t="s">
-        <v>986</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="B456" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>82</v>
+        <v>987</v>
       </c>
       <c r="B457" t="s">
-        <v>529</v>
+        <v>988</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>767</v>
+        <v>82</v>
       </c>
       <c r="B458" t="s">
-        <v>768</v>
+        <v>529</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>197</v>
+        <v>767</v>
       </c>
       <c r="B459" t="s">
-        <v>530</v>
+        <v>768</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>649</v>
+        <v>197</v>
       </c>
       <c r="B460" t="s">
-        <v>730</v>
+        <v>530</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>1433</v>
+        <v>649</v>
       </c>
       <c r="B461" t="s">
-        <v>1434</v>
+        <v>730</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>1339</v>
+        <v>1433</v>
       </c>
       <c r="B462" t="s">
-        <v>1340</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>816</v>
+        <v>1339</v>
       </c>
       <c r="B463" t="s">
-        <v>817</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>1059</v>
+        <v>816</v>
       </c>
       <c r="B464" t="s">
-        <v>1060</v>
+        <v>817</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>3</v>
+        <v>1059</v>
       </c>
       <c r="B465" t="s">
-        <v>4</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>952</v>
+        <v>3</v>
       </c>
       <c r="B466" t="s">
         <v>4</v>
@@ -8552,7 +8570,7 @@
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B467" t="s">
         <v>4</v>
@@ -8560,2233 +8578,2257 @@
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>659</v>
+        <v>953</v>
       </c>
       <c r="B468" t="s">
-        <v>731</v>
+        <v>4</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>1287</v>
+        <v>659</v>
       </c>
       <c r="B469" t="s">
-        <v>1288</v>
+        <v>731</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>765</v>
+        <v>1287</v>
       </c>
       <c r="B470" t="s">
-        <v>766</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>85</v>
+        <v>765</v>
       </c>
       <c r="B471" t="s">
-        <v>531</v>
+        <v>766</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>1053</v>
+        <v>85</v>
       </c>
       <c r="B472" t="s">
-        <v>1054</v>
+        <v>531</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>824</v>
+        <v>1053</v>
       </c>
       <c r="B473" t="s">
-        <v>825</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>804</v>
+        <v>824</v>
       </c>
       <c r="B474" t="s">
-        <v>805</v>
+        <v>825</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>187</v>
+        <v>804</v>
       </c>
       <c r="B475" t="s">
-        <v>532</v>
+        <v>805</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>822</v>
+        <v>187</v>
       </c>
       <c r="B476" t="s">
-        <v>823</v>
+        <v>532</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>928</v>
+        <v>822</v>
       </c>
       <c r="B477" t="s">
-        <v>1114</v>
+        <v>823</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>1439</v>
+        <v>928</v>
       </c>
       <c r="B478" t="s">
-        <v>1440</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>858</v>
+        <v>1439</v>
       </c>
       <c r="B479" t="s">
-        <v>859</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>1427</v>
+        <v>858</v>
       </c>
       <c r="B480" t="s">
-        <v>1428</v>
+        <v>859</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>1037</v>
+        <v>1427</v>
       </c>
       <c r="B481" t="s">
-        <v>1038</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>793</v>
+        <v>1037</v>
       </c>
       <c r="B482" t="s">
-        <v>1115</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B483" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>13</v>
+        <v>792</v>
       </c>
       <c r="B484" t="s">
-        <v>14</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>812</v>
+        <v>1484</v>
       </c>
       <c r="B485" t="s">
-        <v>813</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>1217</v>
+        <v>1482</v>
       </c>
       <c r="B486" t="s">
-        <v>1218</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>186</v>
+        <v>13</v>
       </c>
       <c r="B487" t="s">
-        <v>533</v>
+        <v>14</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="B488" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>319</v>
+        <v>1217</v>
       </c>
       <c r="B489" t="s">
-        <v>534</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>651</v>
+        <v>186</v>
       </c>
       <c r="B490" t="s">
-        <v>732</v>
+        <v>533</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>850</v>
+        <v>806</v>
       </c>
       <c r="B491" t="s">
-        <v>851</v>
+        <v>807</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>653</v>
+        <v>319</v>
       </c>
       <c r="B492" t="s">
-        <v>733</v>
+        <v>534</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B493" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>1189</v>
+        <v>850</v>
       </c>
       <c r="B494" t="s">
-        <v>1190</v>
+        <v>851</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>256</v>
+        <v>653</v>
       </c>
       <c r="B495" t="s">
-        <v>535</v>
+        <v>733</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>260</v>
+        <v>648</v>
       </c>
       <c r="B496" t="s">
-        <v>536</v>
+        <v>734</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>261</v>
+        <v>1189</v>
       </c>
       <c r="B497" t="s">
-        <v>537</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="B498" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="B499" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>930</v>
+        <v>261</v>
       </c>
       <c r="B500" t="s">
-        <v>931</v>
+        <v>537</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>1024</v>
+        <v>188</v>
       </c>
       <c r="B501" t="s">
-        <v>1025</v>
+        <v>538</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>1205</v>
+        <v>190</v>
       </c>
       <c r="B502" t="s">
-        <v>1206</v>
+        <v>539</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>209</v>
+        <v>930</v>
       </c>
       <c r="B503" t="s">
-        <v>540</v>
+        <v>931</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>1406</v>
+        <v>1024</v>
       </c>
       <c r="B504" t="s">
-        <v>1407</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>1297</v>
+        <v>1205</v>
       </c>
       <c r="B505" t="s">
-        <v>1298</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>846</v>
+        <v>209</v>
       </c>
       <c r="B506" t="s">
-        <v>847</v>
+        <v>540</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>143</v>
+        <v>1406</v>
       </c>
       <c r="B507" t="s">
-        <v>541</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>140</v>
+        <v>1297</v>
       </c>
       <c r="B508" t="s">
-        <v>542</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>1185</v>
+        <v>846</v>
       </c>
       <c r="B509" t="s">
-        <v>1186</v>
+        <v>847</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>1285</v>
+        <v>143</v>
       </c>
       <c r="B510" t="s">
-        <v>1286</v>
+        <v>541</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>254</v>
+        <v>140</v>
       </c>
       <c r="B511" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>330</v>
+        <v>1185</v>
       </c>
       <c r="B512" t="s">
-        <v>544</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>210</v>
+        <v>1285</v>
       </c>
       <c r="B513" t="s">
-        <v>545</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="B514" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>73</v>
+        <v>330</v>
       </c>
       <c r="B515" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>341</v>
+        <v>210</v>
       </c>
       <c r="B516" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>308</v>
+        <v>234</v>
       </c>
       <c r="B517" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>838</v>
+        <v>73</v>
       </c>
       <c r="B518" t="s">
-        <v>839</v>
+        <v>547</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>840</v>
+        <v>341</v>
       </c>
       <c r="B519" t="s">
-        <v>841</v>
+        <v>548</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>220</v>
+        <v>308</v>
       </c>
       <c r="B520" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>903</v>
+        <v>838</v>
       </c>
       <c r="B521" t="s">
-        <v>904</v>
+        <v>839</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>1362</v>
+        <v>840</v>
       </c>
       <c r="B522" t="s">
-        <v>1363</v>
+        <v>841</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>957</v>
+        <v>220</v>
       </c>
       <c r="B523" t="s">
-        <v>958</v>
+        <v>550</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>1170</v>
+        <v>903</v>
       </c>
       <c r="B524" t="s">
-        <v>1171</v>
+        <v>904</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>227</v>
+        <v>1362</v>
       </c>
       <c r="B525" t="s">
-        <v>551</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>333</v>
+        <v>957</v>
       </c>
       <c r="B526" t="s">
-        <v>1143</v>
+        <v>958</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>965</v>
+        <v>1170</v>
       </c>
       <c r="B527" t="s">
-        <v>966</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>773</v>
+        <v>227</v>
       </c>
       <c r="B528" t="s">
-        <v>774</v>
+        <v>551</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>294</v>
+        <v>333</v>
       </c>
       <c r="B529" t="s">
-        <v>552</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>946</v>
+        <v>965</v>
       </c>
       <c r="B530" t="s">
-        <v>947</v>
+        <v>966</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>338</v>
+        <v>773</v>
       </c>
       <c r="B531" t="s">
-        <v>553</v>
+        <v>774</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>775</v>
+        <v>294</v>
       </c>
       <c r="B532" t="s">
-        <v>774</v>
+        <v>552</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>1301</v>
+        <v>946</v>
       </c>
       <c r="B533" t="s">
-        <v>1302</v>
+        <v>947</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B534" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>340</v>
+        <v>775</v>
       </c>
       <c r="B535" t="s">
-        <v>555</v>
+        <v>774</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>640</v>
+        <v>1301</v>
       </c>
       <c r="B536" t="s">
-        <v>735</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>39</v>
+        <v>339</v>
       </c>
       <c r="B537" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>38</v>
+        <v>340</v>
       </c>
       <c r="B538" t="s">
-        <v>1475</v>
+        <v>555</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>342</v>
+        <v>640</v>
       </c>
       <c r="B539" t="s">
-        <v>557</v>
+        <v>735</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="B540" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>1414</v>
+        <v>38</v>
       </c>
       <c r="B541" t="s">
-        <v>1415</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>1022</v>
+        <v>342</v>
       </c>
       <c r="B542" t="s">
-        <v>1023</v>
+        <v>557</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>897</v>
+        <v>107</v>
       </c>
       <c r="B543" t="s">
-        <v>898</v>
+        <v>558</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>117</v>
+        <v>1414</v>
       </c>
       <c r="B544" t="s">
-        <v>559</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="B545" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>98</v>
+        <v>897</v>
       </c>
       <c r="B546" t="s">
-        <v>560</v>
+        <v>898</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="B547" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>661</v>
+        <v>1018</v>
       </c>
       <c r="B548" t="s">
-        <v>736</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>1094</v>
+        <v>98</v>
       </c>
       <c r="B549" t="s">
-        <v>1017</v>
+        <v>560</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>818</v>
+        <v>99</v>
       </c>
       <c r="B550" t="s">
-        <v>819</v>
+        <v>561</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>113</v>
+        <v>661</v>
       </c>
       <c r="B551" t="s">
-        <v>562</v>
+        <v>736</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>884</v>
+        <v>1094</v>
       </c>
       <c r="B552" t="s">
-        <v>885</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>45</v>
+        <v>818</v>
       </c>
       <c r="B553" t="s">
-        <v>1113</v>
+        <v>819</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>290</v>
+        <v>113</v>
       </c>
       <c r="B554" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>299</v>
+        <v>884</v>
       </c>
       <c r="B555" t="s">
-        <v>564</v>
+        <v>885</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B556" t="s">
-        <v>565</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>842</v>
+        <v>290</v>
       </c>
       <c r="B557" t="s">
-        <v>843</v>
+        <v>563</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>51</v>
+        <v>299</v>
       </c>
       <c r="B558" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>866</v>
+        <v>47</v>
       </c>
       <c r="B559" t="s">
-        <v>867</v>
+        <v>565</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>114</v>
+        <v>842</v>
       </c>
       <c r="B560" t="s">
-        <v>567</v>
+        <v>843</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>848</v>
+        <v>51</v>
       </c>
       <c r="B561" t="s">
-        <v>849</v>
+        <v>566</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>144</v>
+        <v>866</v>
       </c>
       <c r="B562" t="s">
-        <v>568</v>
+        <v>867</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>1071</v>
+        <v>114</v>
       </c>
       <c r="B563" t="s">
-        <v>1072</v>
+        <v>567</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>176</v>
+        <v>848</v>
       </c>
       <c r="B564" t="s">
-        <v>569</v>
+        <v>849</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>315</v>
+        <v>144</v>
       </c>
       <c r="B565" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>29</v>
+        <v>1071</v>
       </c>
       <c r="B566" t="s">
-        <v>571</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>1011</v>
+        <v>176</v>
       </c>
       <c r="B567" t="s">
-        <v>1012</v>
+        <v>569</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>1213</v>
+        <v>315</v>
       </c>
       <c r="B568" t="s">
-        <v>1214</v>
+        <v>570</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>293</v>
+        <v>29</v>
       </c>
       <c r="B569" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>975</v>
+        <v>1011</v>
       </c>
       <c r="B570" t="s">
-        <v>976</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>1446</v>
+        <v>1213</v>
       </c>
       <c r="B571" t="s">
-        <v>1447</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B572" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>997</v>
+        <v>975</v>
       </c>
       <c r="B573" t="s">
-        <v>998</v>
+        <v>976</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>1001</v>
+        <v>1446</v>
       </c>
       <c r="B574" t="s">
-        <v>1002</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>75</v>
+        <v>301</v>
       </c>
       <c r="B575" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>76</v>
+        <v>997</v>
       </c>
       <c r="B576" t="s">
-        <v>575</v>
+        <v>998</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>78</v>
+        <v>1001</v>
       </c>
       <c r="B577" t="s">
-        <v>576</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>328</v>
+        <v>75</v>
       </c>
       <c r="B578" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>1393</v>
+        <v>76</v>
       </c>
       <c r="B579" t="s">
-        <v>1394</v>
+        <v>575</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>1291</v>
+        <v>78</v>
       </c>
       <c r="B580" t="s">
-        <v>1292</v>
+        <v>576</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>747</v>
+        <v>328</v>
       </c>
       <c r="B581" t="s">
-        <v>748</v>
+        <v>577</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>800</v>
+        <v>1393</v>
       </c>
       <c r="B582" t="s">
-        <v>801</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>1304</v>
+        <v>1291</v>
       </c>
       <c r="B583" t="s">
-        <v>1305</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>135</v>
+        <v>747</v>
       </c>
       <c r="B584" t="s">
-        <v>578</v>
+        <v>748</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>1168</v>
+        <v>800</v>
       </c>
       <c r="B585" t="s">
-        <v>1169</v>
+        <v>801</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>1031</v>
+        <v>1304</v>
       </c>
       <c r="B586" t="s">
-        <v>1032</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>215</v>
+        <v>135</v>
       </c>
       <c r="B587" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>929</v>
+        <v>1168</v>
       </c>
       <c r="B588" t="s">
-        <v>1128</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>216</v>
+        <v>1031</v>
       </c>
       <c r="B589" t="s">
-        <v>1111</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>316</v>
+        <v>215</v>
       </c>
       <c r="B590" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>1073</v>
+        <v>929</v>
       </c>
       <c r="B591" t="s">
-        <v>1074</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B592" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>993</v>
+        <v>316</v>
       </c>
       <c r="B593" t="s">
-        <v>994</v>
+        <v>580</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>995</v>
+        <v>1073</v>
       </c>
       <c r="B594" t="s">
-        <v>996</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="B595" t="s">
-        <v>581</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>1380</v>
+        <v>993</v>
       </c>
       <c r="B596" t="s">
-        <v>1381</v>
+        <v>994</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>942</v>
+        <v>995</v>
       </c>
       <c r="B597" t="s">
-        <v>943</v>
+        <v>996</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>1089</v>
+        <v>225</v>
       </c>
       <c r="B598" t="s">
-        <v>1090</v>
+        <v>581</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>1039</v>
+        <v>1380</v>
       </c>
       <c r="B599" t="s">
-        <v>1040</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>93</v>
+        <v>942</v>
       </c>
       <c r="B600" t="s">
-        <v>582</v>
+        <v>943</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>120</v>
+        <v>1089</v>
       </c>
       <c r="B601" t="s">
-        <v>583</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>778</v>
+        <v>1039</v>
       </c>
       <c r="B602" t="s">
-        <v>779</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="B603" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="B604" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>1293</v>
+        <v>778</v>
       </c>
       <c r="B605" t="s">
-        <v>1294</v>
+        <v>779</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="B606" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>820</v>
+        <v>62</v>
       </c>
       <c r="B607" t="s">
-        <v>821</v>
+        <v>585</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>944</v>
+        <v>1293</v>
       </c>
       <c r="B608" t="s">
-        <v>945</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>1197</v>
+        <v>66</v>
       </c>
       <c r="B609" t="s">
-        <v>1198</v>
+        <v>586</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>1306</v>
+        <v>820</v>
       </c>
       <c r="B610" t="s">
-        <v>1307</v>
+        <v>821</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>79</v>
+        <v>944</v>
       </c>
       <c r="B611" t="s">
-        <v>587</v>
+        <v>945</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>64</v>
+        <v>1197</v>
       </c>
       <c r="B612" t="s">
-        <v>588</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>122</v>
+        <v>1306</v>
       </c>
       <c r="B613" t="s">
-        <v>589</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>1166</v>
+        <v>79</v>
       </c>
       <c r="B614" t="s">
-        <v>1167</v>
+        <v>587</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>181</v>
+        <v>64</v>
       </c>
       <c r="B615" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>796</v>
+        <v>122</v>
       </c>
       <c r="B616" t="s">
-        <v>797</v>
+        <v>589</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>1271</v>
+        <v>1166</v>
       </c>
       <c r="B617" t="s">
-        <v>1276</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>686</v>
+        <v>181</v>
       </c>
       <c r="B618" t="s">
-        <v>737</v>
+        <v>590</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>1272</v>
+        <v>796</v>
       </c>
       <c r="B619" t="s">
-        <v>1277</v>
+        <v>797</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="B620" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>1274</v>
+        <v>686</v>
       </c>
       <c r="B621" t="s">
-        <v>1279</v>
+        <v>737</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="B622" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
-        <v>1133</v>
+        <v>1273</v>
       </c>
       <c r="B623" t="s">
-        <v>1134</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
-        <v>1131</v>
+        <v>1274</v>
       </c>
       <c r="B624" t="s">
-        <v>1132</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
-        <v>284</v>
+        <v>1275</v>
       </c>
       <c r="B625" t="s">
-        <v>591</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
-        <v>967</v>
+        <v>1133</v>
       </c>
       <c r="B626" t="s">
-        <v>968</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>1201</v>
+        <v>1131</v>
       </c>
       <c r="B627" t="s">
-        <v>1202</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
-        <v>836</v>
+        <v>284</v>
       </c>
       <c r="B628" t="s">
-        <v>837</v>
+        <v>591</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>283</v>
+        <v>967</v>
       </c>
       <c r="B629" t="s">
-        <v>592</v>
+        <v>968</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>878</v>
+        <v>1201</v>
       </c>
       <c r="B630" t="s">
-        <v>879</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>1162</v>
+        <v>836</v>
       </c>
       <c r="B631" t="s">
-        <v>1163</v>
+        <v>837</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>751</v>
+        <v>283</v>
       </c>
       <c r="B632" t="s">
-        <v>752</v>
+        <v>592</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
-        <v>1069</v>
+        <v>878</v>
       </c>
       <c r="B633" t="s">
-        <v>1070</v>
+        <v>879</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
-        <v>67</v>
+        <v>1162</v>
       </c>
       <c r="B634" t="s">
-        <v>593</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
-        <v>68</v>
+        <v>751</v>
       </c>
       <c r="B635" t="s">
-        <v>594</v>
+        <v>752</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
-        <v>1375</v>
+        <v>1069</v>
       </c>
       <c r="B636" t="s">
-        <v>1376</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="B637" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
-        <v>289</v>
+        <v>68</v>
       </c>
       <c r="B638" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
-        <v>297</v>
+        <v>1375</v>
       </c>
       <c r="B639" t="s">
-        <v>597</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
-        <v>264</v>
+        <v>95</v>
       </c>
       <c r="B640" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>193</v>
+        <v>289</v>
       </c>
       <c r="B641" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
-        <v>1335</v>
+        <v>297</v>
       </c>
       <c r="B642" t="s">
-        <v>1336</v>
+        <v>597</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
-        <v>895</v>
+        <v>264</v>
       </c>
       <c r="B643" t="s">
-        <v>896</v>
+        <v>598</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
-        <v>44</v>
+        <v>193</v>
       </c>
       <c r="B644" t="s">
-        <v>1110</v>
+        <v>599</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
-        <v>1061</v>
+        <v>1335</v>
       </c>
       <c r="B645" t="s">
-        <v>1062</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
-        <v>323</v>
+        <v>895</v>
       </c>
       <c r="B646" t="s">
-        <v>600</v>
+        <v>896</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
-        <v>324</v>
+        <v>44</v>
       </c>
       <c r="B647" t="s">
-        <v>601</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
-        <v>844</v>
+        <v>1061</v>
       </c>
       <c r="B648" t="s">
-        <v>845</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
-        <v>882</v>
+        <v>323</v>
       </c>
       <c r="B649" t="s">
-        <v>883</v>
+        <v>600</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
-        <v>1219</v>
+        <v>324</v>
       </c>
       <c r="B650" t="s">
-        <v>1220</v>
+        <v>601</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
-        <v>864</v>
+        <v>844</v>
       </c>
       <c r="B651" t="s">
-        <v>865</v>
+        <v>845</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>33</v>
+        <v>882</v>
       </c>
       <c r="B652" t="s">
-        <v>602</v>
+        <v>883</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
-        <v>36</v>
+        <v>1219</v>
       </c>
       <c r="B653" t="s">
-        <v>603</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
-        <v>1126</v>
+        <v>864</v>
       </c>
       <c r="B654" t="s">
-        <v>1127</v>
+        <v>865</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
-        <v>309</v>
+        <v>33</v>
       </c>
       <c r="B655" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
-        <v>257</v>
+        <v>36</v>
       </c>
       <c r="B656" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
-        <v>302</v>
+        <v>1126</v>
       </c>
       <c r="B657" t="s">
-        <v>606</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
-        <v>228</v>
+        <v>309</v>
       </c>
       <c r="B658" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
-        <v>17</v>
+        <v>257</v>
       </c>
       <c r="B659" t="s">
-        <v>18</v>
+        <v>605</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
-        <v>650</v>
+        <v>302</v>
       </c>
       <c r="B660" t="s">
-        <v>738</v>
+        <v>606</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
-        <v>1402</v>
+        <v>228</v>
       </c>
       <c r="B661" t="s">
-        <v>1403</v>
+        <v>607</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
-        <v>780</v>
+        <v>17</v>
       </c>
       <c r="B662" t="s">
-        <v>781</v>
+        <v>18</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
-        <v>142</v>
+        <v>650</v>
       </c>
       <c r="B663" t="s">
-        <v>608</v>
+        <v>738</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
-        <v>1160</v>
+        <v>1402</v>
       </c>
       <c r="B664" t="s">
-        <v>1161</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
-        <v>950</v>
+        <v>780</v>
       </c>
       <c r="B665" t="s">
-        <v>951</v>
+        <v>781</v>
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="B666" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
-        <v>265</v>
+        <v>1160</v>
       </c>
       <c r="B667" t="s">
-        <v>610</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="B668" t="s">
-        <v>969</v>
+        <v>951</v>
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
-        <v>1392</v>
+        <v>54</v>
       </c>
       <c r="B669" t="s">
-        <v>969</v>
+        <v>609</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
-        <v>56</v>
+        <v>265</v>
       </c>
       <c r="B670" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
-        <v>1199</v>
+        <v>970</v>
       </c>
       <c r="B671" t="s">
-        <v>1200</v>
+        <v>969</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
-        <v>185</v>
+        <v>1392</v>
       </c>
       <c r="B672" t="s">
-        <v>612</v>
+        <v>969</v>
       </c>
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="B673" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
-        <v>43</v>
+        <v>1199</v>
       </c>
       <c r="B674" t="s">
-        <v>1328</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
-        <v>1326</v>
+        <v>185</v>
       </c>
       <c r="B675" t="s">
-        <v>1327</v>
+        <v>612</v>
       </c>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
-        <v>1450</v>
+        <v>159</v>
       </c>
       <c r="B676" t="s">
-        <v>1452</v>
+        <v>613</v>
       </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
-        <v>1451</v>
+        <v>43</v>
       </c>
       <c r="B677" t="s">
-        <v>1453</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
-        <v>40</v>
+        <v>1326</v>
       </c>
       <c r="B678" t="s">
-        <v>1476</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
-        <v>1324</v>
+        <v>1450</v>
       </c>
       <c r="B679" t="s">
-        <v>1325</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
-        <v>1152</v>
+        <v>1451</v>
       </c>
       <c r="B680" t="s">
-        <v>1153</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
-        <v>165</v>
+        <v>40</v>
       </c>
       <c r="B681" t="s">
-        <v>614</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
-        <v>1281</v>
+        <v>1324</v>
       </c>
       <c r="B682" t="s">
-        <v>1282</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
-        <v>1283</v>
+        <v>1152</v>
       </c>
       <c r="B683" t="s">
-        <v>1284</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
-        <v>1471</v>
+        <v>165</v>
       </c>
       <c r="B684" t="s">
-        <v>1472</v>
+        <v>614</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
-        <v>1473</v>
+        <v>1281</v>
       </c>
       <c r="B685" t="s">
-        <v>1474</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
-        <v>12</v>
+        <v>1283</v>
       </c>
       <c r="B686" t="s">
-        <v>11</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
-        <v>250</v>
+        <v>1471</v>
       </c>
       <c r="B687" t="s">
-        <v>615</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
-        <v>27</v>
+        <v>1473</v>
       </c>
       <c r="B688" t="s">
-        <v>616</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
-        <v>1033</v>
+        <v>12</v>
       </c>
       <c r="B689" t="s">
-        <v>1034</v>
+        <v>11</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
-        <v>28</v>
+        <v>250</v>
       </c>
       <c r="B690" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
-        <v>1187</v>
+        <v>27</v>
       </c>
       <c r="B691" t="s">
-        <v>1188</v>
+        <v>616</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
-        <v>255</v>
+        <v>1033</v>
       </c>
       <c r="B692" t="s">
-        <v>618</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
-        <v>1316</v>
+        <v>28</v>
       </c>
       <c r="B693" t="s">
-        <v>1321</v>
+        <v>617</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
-        <v>790</v>
+        <v>1187</v>
       </c>
       <c r="B694" t="s">
-        <v>791</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="B695" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
-        <v>656</v>
+        <v>1316</v>
       </c>
       <c r="B696" t="s">
-        <v>739</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
-        <v>657</v>
+        <v>790</v>
       </c>
       <c r="B697" t="s">
-        <v>740</v>
+        <v>791</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
-        <v>139</v>
+        <v>267</v>
       </c>
       <c r="B698" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
-        <v>7</v>
+        <v>656</v>
       </c>
       <c r="B699" t="s">
-        <v>2</v>
+        <v>739</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
-        <v>105</v>
+        <v>657</v>
       </c>
       <c r="B700" t="s">
-        <v>621</v>
+        <v>740</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
-        <v>1331</v>
+        <v>139</v>
       </c>
       <c r="B701" t="s">
-        <v>1332</v>
+        <v>620</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
-        <v>1027</v>
+        <v>7</v>
       </c>
       <c r="B702" t="s">
-        <v>1109</v>
+        <v>2</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
-        <v>860</v>
+        <v>105</v>
       </c>
       <c r="B703" t="s">
-        <v>861</v>
+        <v>621</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
-        <v>1431</v>
+        <v>1331</v>
       </c>
       <c r="B704" t="s">
-        <v>1432</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B705" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
-        <v>292</v>
+        <v>860</v>
       </c>
       <c r="B706" t="s">
-        <v>622</v>
+        <v>861</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
-        <v>8</v>
+        <v>1431</v>
       </c>
       <c r="B707" t="s">
-        <v>11</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
-        <v>334</v>
+        <v>1028</v>
       </c>
       <c r="B708" t="s">
-        <v>623</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
-        <v>1373</v>
+        <v>292</v>
       </c>
       <c r="B709" t="s">
-        <v>1374</v>
+        <v>622</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
-        <v>1333</v>
+        <v>8</v>
       </c>
       <c r="B710" t="s">
-        <v>1334</v>
+        <v>11</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B711" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
-        <v>259</v>
+        <v>1373</v>
       </c>
       <c r="B712" t="s">
-        <v>625</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
-        <v>318</v>
+        <v>1333</v>
       </c>
       <c r="B713" t="s">
-        <v>626</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
-        <v>854</v>
+        <v>331</v>
       </c>
       <c r="B714" t="s">
-        <v>855</v>
+        <v>624</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A715" t="s">
-        <v>1156</v>
+        <v>259</v>
       </c>
       <c r="B715" t="s">
-        <v>1157</v>
+        <v>625</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A716" t="s">
-        <v>268</v>
+        <v>318</v>
       </c>
       <c r="B716" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
-        <v>271</v>
+        <v>854</v>
       </c>
       <c r="B717" t="s">
-        <v>1103</v>
+        <v>855</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
-        <v>274</v>
+        <v>1156</v>
       </c>
       <c r="B718" t="s">
-        <v>1104</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B719" t="s">
-        <v>1105</v>
+        <v>627</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B720" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B721" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B722" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
-        <v>92</v>
+        <v>273</v>
       </c>
       <c r="B723" t="s">
-        <v>628</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
-        <v>200</v>
+        <v>269</v>
       </c>
       <c r="B724" t="s">
-        <v>629</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
-        <v>203</v>
+        <v>272</v>
       </c>
       <c r="B725" t="s">
-        <v>630</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
-        <v>1209</v>
+        <v>92</v>
       </c>
       <c r="B726" t="s">
-        <v>1210</v>
+        <v>628</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="B727" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
-        <v>1463</v>
+        <v>203</v>
       </c>
       <c r="B728" t="s">
-        <v>1464</v>
+        <v>630</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
-        <v>688</v>
+        <v>1209</v>
       </c>
       <c r="B729" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="730" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A730" t="s">
-        <v>1458</v>
-      </c>
-      <c r="B730" s="1" t="s">
-        <v>1459</v>
+        <v>172</v>
+      </c>
+      <c r="B730" t="s">
+        <v>631</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
-        <v>252</v>
+        <v>1463</v>
       </c>
       <c r="B731" t="s">
-        <v>632</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B732" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="733" spans="1:2" x14ac:dyDescent="0.35">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
-        <v>189</v>
-      </c>
-      <c r="B733" t="s">
-        <v>1401</v>
+        <v>1458</v>
+      </c>
+      <c r="B733" s="1" t="s">
+        <v>1459</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
-        <v>983</v>
+        <v>252</v>
       </c>
       <c r="B734" t="s">
-        <v>984</v>
+        <v>632</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
-        <v>311</v>
+        <v>689</v>
       </c>
       <c r="B735" t="s">
-        <v>633</v>
+        <v>742</v>
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
-        <v>312</v>
+        <v>189</v>
       </c>
       <c r="B736" t="s">
-        <v>634</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A737" t="s">
-        <v>1026</v>
+        <v>983</v>
       </c>
       <c r="B737" t="s">
-        <v>1457</v>
+        <v>984</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
-        <v>1456</v>
+        <v>311</v>
       </c>
       <c r="B738" t="s">
-        <v>1480</v>
+        <v>633</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
-        <v>999</v>
+        <v>312</v>
       </c>
       <c r="B739" t="s">
-        <v>1000</v>
+        <v>634</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A740" t="s">
-        <v>81</v>
+        <v>1026</v>
       </c>
       <c r="B740" t="s">
-        <v>635</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
-        <v>646</v>
+        <v>1456</v>
       </c>
       <c r="B741" t="s">
-        <v>743</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
-        <v>916</v>
+        <v>999</v>
       </c>
       <c r="B742" t="s">
-        <v>917</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
-        <v>637</v>
+        <v>81</v>
       </c>
       <c r="B743" t="s">
-        <v>744</v>
+        <v>635</v>
       </c>
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A744" t="s">
-        <v>963</v>
+        <v>646</v>
       </c>
       <c r="B744" t="s">
-        <v>964</v>
+        <v>743</v>
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A745" t="s">
-        <v>1144</v>
+        <v>916</v>
       </c>
       <c r="B745" t="s">
-        <v>1145</v>
+        <v>917</v>
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A746" t="s">
+        <v>637</v>
+      </c>
+      <c r="B746" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A747" t="s">
+        <v>963</v>
+      </c>
+      <c r="B747" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A748" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B748" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A749" t="s">
         <v>1371</v>
       </c>
-      <c r="B746" t="s">
+      <c r="B749" t="s">
         <v>1372</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DF13C7-6F26-446B-AD9F-4BF78A61661F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5A4E01-CD1B-4831-9775-3995363E1D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="1487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="1489">
   <si>
     <t>trigger</t>
   </si>
@@ -4489,6 +4489,12 @@
   </si>
   <si>
     <t>Multiple discrete and confluent T2/FLAIR high signal intensities are noted in bilateral periventricular white matter and centrum semi-ovale. No restriction of diffusion on DWI</t>
+  </si>
+  <si>
+    <t>fdf</t>
+  </si>
+  <si>
+    <t>facilitated diffusion on DWI</t>
   </si>
 </sst>
 </file>
@@ -4557,10 +4563,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B749" totalsRowShown="0">
-  <autoFilter ref="A1:B749" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B749">
-    <sortCondition ref="A1:A749"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B750" totalsRowShown="0">
+  <autoFilter ref="A1:B750" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B750">
+    <sortCondition ref="A1:A750"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4833,7 +4839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B749"/>
+  <dimension ref="A1:B750"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -6818,519 +6824,519 @@
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>97</v>
+        <v>1487</v>
       </c>
       <c r="B248" t="s">
-        <v>428</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B249" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>242</v>
+        <v>110</v>
       </c>
       <c r="B250" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B251" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="B252" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>1416</v>
+        <v>177</v>
       </c>
       <c r="B253" t="s">
-        <v>1417</v>
+        <v>432</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>182</v>
+        <v>1416</v>
       </c>
       <c r="B254" t="s">
-        <v>433</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>1097</v>
+        <v>182</v>
       </c>
       <c r="B255" t="s">
-        <v>1098</v>
+        <v>433</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>971</v>
+        <v>1097</v>
       </c>
       <c r="B256" t="s">
-        <v>972</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B257" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>1180</v>
+        <v>973</v>
       </c>
       <c r="B258" t="s">
-        <v>1181</v>
+        <v>974</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>1358</v>
+        <v>1180</v>
       </c>
       <c r="B259" t="s">
-        <v>1359</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>1183</v>
+        <v>1358</v>
       </c>
       <c r="B260" t="s">
-        <v>1184</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>253</v>
+        <v>1183</v>
       </c>
       <c r="B261" t="s">
-        <v>434</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="B262" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>782</v>
+        <v>34</v>
       </c>
       <c r="B263" t="s">
-        <v>783</v>
+        <v>435</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>180</v>
+        <v>782</v>
       </c>
       <c r="B264" t="s">
-        <v>436</v>
+        <v>783</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>1330</v>
+        <v>180</v>
       </c>
       <c r="B265" t="s">
-        <v>1399</v>
+        <v>436</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B266" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>1448</v>
+        <v>1329</v>
       </c>
       <c r="B267" t="s">
-        <v>1449</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>275</v>
+        <v>1448</v>
       </c>
       <c r="B268" t="s">
-        <v>437</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>852</v>
+        <v>275</v>
       </c>
       <c r="B269" t="s">
-        <v>853</v>
+        <v>437</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>116</v>
+        <v>852</v>
       </c>
       <c r="B270" t="s">
-        <v>438</v>
+        <v>853</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="B271" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>1404</v>
+        <v>208</v>
       </c>
       <c r="B272" t="s">
-        <v>1405</v>
+        <v>439</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>1203</v>
+        <v>1404</v>
       </c>
       <c r="B273" t="s">
-        <v>1204</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>1047</v>
+        <v>1203</v>
       </c>
       <c r="B274" t="s">
-        <v>1048</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>118</v>
+        <v>1047</v>
       </c>
       <c r="B275" t="s">
-        <v>440</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>636</v>
+        <v>118</v>
       </c>
       <c r="B276" t="s">
-        <v>718</v>
+        <v>440</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>1314</v>
+        <v>636</v>
       </c>
       <c r="B277" t="s">
-        <v>1315</v>
+        <v>718</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>810</v>
+        <v>1314</v>
       </c>
       <c r="B278" t="s">
-        <v>811</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>298</v>
+        <v>810</v>
       </c>
       <c r="B279" t="s">
-        <v>441</v>
+        <v>811</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>638</v>
+        <v>298</v>
       </c>
       <c r="B280" t="s">
-        <v>719</v>
+        <v>441</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B281" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>1029</v>
+        <v>639</v>
       </c>
       <c r="B282" t="s">
-        <v>1030</v>
+        <v>720</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>90</v>
+        <v>1029</v>
       </c>
       <c r="B283" t="s">
-        <v>442</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B284" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B285" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>1063</v>
+        <v>89</v>
       </c>
       <c r="B286" t="s">
-        <v>1064</v>
+        <v>444</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>23</v>
+        <v>1063</v>
       </c>
       <c r="B287" t="s">
-        <v>1120</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>1408</v>
+        <v>23</v>
       </c>
       <c r="B288" t="s">
-        <v>1409</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>5</v>
+        <v>1408</v>
       </c>
       <c r="B289" t="s">
-        <v>6</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>1124</v>
+        <v>5</v>
       </c>
       <c r="B290" t="s">
-        <v>1125</v>
+        <v>6</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>126</v>
+        <v>1124</v>
       </c>
       <c r="B291" t="s">
-        <v>445</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>1382</v>
+        <v>126</v>
       </c>
       <c r="B292" t="s">
-        <v>1383</v>
+        <v>445</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>128</v>
+        <v>1382</v>
       </c>
       <c r="B293" t="s">
-        <v>446</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B294" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B295" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B296" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>277</v>
+        <v>119</v>
       </c>
       <c r="B297" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>1065</v>
+        <v>277</v>
       </c>
       <c r="B298" t="s">
-        <v>1066</v>
+        <v>450</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>9</v>
+        <v>1065</v>
       </c>
       <c r="B299" t="s">
-        <v>10</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="B300" t="s">
-        <v>451</v>
+        <v>10</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B301" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="B302" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="B303" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>1369</v>
+        <v>262</v>
       </c>
       <c r="B304" t="s">
-        <v>1370</v>
+        <v>454</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>77</v>
+        <v>1369</v>
       </c>
       <c r="B305" t="s">
-        <v>455</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>932</v>
+        <v>77</v>
       </c>
       <c r="B306" t="s">
-        <v>933</v>
+        <v>455</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>1154</v>
+        <v>932</v>
       </c>
       <c r="B307" t="s">
-        <v>1155</v>
+        <v>933</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>168</v>
+        <v>1154</v>
       </c>
       <c r="B308" t="s">
-        <v>456</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>1342</v>
+        <v>168</v>
       </c>
       <c r="B309" t="s">
-        <v>1343</v>
+        <v>456</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>1352</v>
+        <v>1342</v>
       </c>
       <c r="B310" t="s">
-        <v>1353</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>1395</v>
+        <v>1352</v>
       </c>
       <c r="B311" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>1348</v>
+        <v>1395</v>
       </c>
       <c r="B312" t="s">
         <v>1349</v>
@@ -7338,39 +7344,39 @@
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>167</v>
+        <v>1348</v>
       </c>
       <c r="B313" t="s">
-        <v>457</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>1344</v>
+        <v>167</v>
       </c>
       <c r="B314" t="s">
-        <v>1345</v>
+        <v>457</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>1350</v>
+        <v>1344</v>
       </c>
       <c r="B315" t="s">
-        <v>1351</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>1377</v>
+        <v>1350</v>
       </c>
       <c r="B316" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>1346</v>
+        <v>1377</v>
       </c>
       <c r="B317" t="s">
         <v>1347</v>
@@ -7378,199 +7384,199 @@
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>830</v>
+        <v>1346</v>
       </c>
       <c r="B318" t="s">
-        <v>831</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>786</v>
+        <v>830</v>
       </c>
       <c r="B319" t="s">
-        <v>787</v>
+        <v>831</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>304</v>
+        <v>786</v>
       </c>
       <c r="B320" t="s">
-        <v>458</v>
+        <v>787</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>753</v>
+        <v>304</v>
       </c>
       <c r="B321" t="s">
-        <v>754</v>
+        <v>458</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>891</v>
+        <v>753</v>
       </c>
       <c r="B322" t="s">
-        <v>892</v>
+        <v>754</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>1384</v>
+        <v>891</v>
       </c>
       <c r="B323" t="s">
-        <v>1385</v>
+        <v>892</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>647</v>
+        <v>1384</v>
       </c>
       <c r="B324" t="s">
-        <v>721</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>86</v>
+        <v>647</v>
       </c>
       <c r="B325" t="s">
-        <v>459</v>
+        <v>721</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B326" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="B327" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B328" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B329" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>251</v>
+        <v>158</v>
       </c>
       <c r="B330" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="B331" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>325</v>
+        <v>285</v>
       </c>
       <c r="B332" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>1364</v>
+        <v>325</v>
       </c>
       <c r="B333" t="s">
-        <v>1365</v>
+        <v>466</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>326</v>
+        <v>1364</v>
       </c>
       <c r="B334" t="s">
-        <v>467</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>229</v>
+        <v>326</v>
       </c>
       <c r="B335" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>55</v>
+        <v>229</v>
       </c>
       <c r="B336" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>652</v>
+        <v>55</v>
       </c>
       <c r="B337" t="s">
-        <v>722</v>
+        <v>469</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>235</v>
+        <v>652</v>
       </c>
       <c r="B338" t="s">
-        <v>470</v>
+        <v>722</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="B339" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="B340" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>761</v>
+        <v>236</v>
       </c>
       <c r="B341" t="s">
-        <v>762</v>
+        <v>472</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>1005</v>
+        <v>761</v>
       </c>
       <c r="B342" t="s">
         <v>762</v>
@@ -7578,631 +7584,631 @@
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>164</v>
+        <v>1005</v>
       </c>
       <c r="B343" t="s">
-        <v>473</v>
+        <v>762</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>1462</v>
+        <v>164</v>
       </c>
       <c r="B344" t="s">
-        <v>1460</v>
+        <v>473</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>201</v>
+        <v>1462</v>
       </c>
       <c r="B345" t="s">
-        <v>474</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B346" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>313</v>
+        <v>204</v>
       </c>
       <c r="B347" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>868</v>
+        <v>313</v>
       </c>
       <c r="B348" t="s">
-        <v>869</v>
+        <v>476</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>991</v>
+        <v>868</v>
       </c>
       <c r="B349" t="s">
-        <v>992</v>
+        <v>869</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>1317</v>
+        <v>991</v>
       </c>
       <c r="B350" t="s">
-        <v>1318</v>
+        <v>992</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>258</v>
+        <v>1317</v>
       </c>
       <c r="B351" t="s">
-        <v>477</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>977</v>
+        <v>258</v>
       </c>
       <c r="B352" t="s">
-        <v>978</v>
+        <v>477</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>1356</v>
+        <v>977</v>
       </c>
       <c r="B353" t="s">
-        <v>1357</v>
+        <v>978</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>160</v>
+        <v>1356</v>
       </c>
       <c r="B354" t="s">
-        <v>478</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>687</v>
+        <v>160</v>
       </c>
       <c r="B355" t="s">
-        <v>723</v>
+        <v>478</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>1148</v>
+        <v>687</v>
       </c>
       <c r="B356" t="s">
-        <v>1149</v>
+        <v>723</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>755</v>
+        <v>1148</v>
       </c>
       <c r="B357" t="s">
-        <v>756</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>889</v>
+        <v>755</v>
       </c>
       <c r="B358" t="s">
-        <v>890</v>
+        <v>756</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B359" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>184</v>
+        <v>887</v>
       </c>
       <c r="B360" t="s">
-        <v>479</v>
+        <v>888</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>244</v>
+        <v>184</v>
       </c>
       <c r="B361" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B362" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>1261</v>
+        <v>243</v>
       </c>
       <c r="B363" t="s">
-        <v>1266</v>
+        <v>481</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>681</v>
+        <v>1261</v>
       </c>
       <c r="B364" t="s">
-        <v>724</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>1262</v>
+        <v>681</v>
       </c>
       <c r="B365" t="s">
-        <v>1267</v>
+        <v>724</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>682</v>
+        <v>1262</v>
       </c>
       <c r="B366" t="s">
-        <v>725</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>1263</v>
+        <v>682</v>
       </c>
       <c r="B367" t="s">
-        <v>1268</v>
+        <v>725</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>683</v>
+        <v>1263</v>
       </c>
       <c r="B368" t="s">
-        <v>726</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>1264</v>
+        <v>683</v>
       </c>
       <c r="B369" t="s">
-        <v>1269</v>
+        <v>726</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>684</v>
+        <v>1264</v>
       </c>
       <c r="B370" t="s">
-        <v>727</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>1265</v>
+        <v>684</v>
       </c>
       <c r="B371" t="s">
-        <v>1270</v>
+        <v>727</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>685</v>
+        <v>1265</v>
       </c>
       <c r="B372" t="s">
-        <v>728</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>1174</v>
+        <v>685</v>
       </c>
       <c r="B373" t="s">
-        <v>1175</v>
+        <v>728</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>280</v>
+        <v>1174</v>
       </c>
       <c r="B374" t="s">
-        <v>482</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B375" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>49</v>
+        <v>281</v>
       </c>
       <c r="B376" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B377" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="B378" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>1437</v>
+        <v>136</v>
       </c>
       <c r="B379" t="s">
-        <v>1438</v>
+        <v>487</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>72</v>
+        <v>1437</v>
       </c>
       <c r="B380" t="s">
-        <v>486</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>1172</v>
+        <v>72</v>
       </c>
       <c r="B381" t="s">
-        <v>1173</v>
+        <v>486</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>221</v>
+        <v>1172</v>
       </c>
       <c r="B382" t="s">
-        <v>488</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>1176</v>
+        <v>221</v>
       </c>
       <c r="B383" t="s">
-        <v>1177</v>
+        <v>488</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>15</v>
+        <v>1176</v>
       </c>
       <c r="B384" t="s">
-        <v>16</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>1051</v>
+        <v>15</v>
       </c>
       <c r="B385" t="s">
-        <v>1052</v>
+        <v>16</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>914</v>
+        <v>1051</v>
       </c>
       <c r="B386" t="s">
-        <v>915</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>108</v>
+        <v>914</v>
       </c>
       <c r="B387" t="s">
-        <v>489</v>
+        <v>915</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>241</v>
+        <v>108</v>
       </c>
       <c r="B388" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>327</v>
+        <v>241</v>
       </c>
       <c r="B389" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>1091</v>
+        <v>327</v>
       </c>
       <c r="B390" t="s">
-        <v>1092</v>
+        <v>491</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>1043</v>
+        <v>1091</v>
       </c>
       <c r="B391" t="s">
-        <v>1044</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>121</v>
+        <v>1043</v>
       </c>
       <c r="B392" t="s">
-        <v>492</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>745</v>
+        <v>121</v>
       </c>
       <c r="B393" t="s">
-        <v>746</v>
+        <v>492</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>776</v>
+        <v>745</v>
       </c>
       <c r="B394" t="s">
-        <v>777</v>
+        <v>746</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>134</v>
+        <v>776</v>
       </c>
       <c r="B395" t="s">
-        <v>493</v>
+        <v>777</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="B396" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>1295</v>
+        <v>63</v>
       </c>
       <c r="B397" t="s">
-        <v>1296</v>
+        <v>494</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>224</v>
+        <v>1295</v>
       </c>
       <c r="B398" t="s">
-        <v>495</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>25</v>
+        <v>224</v>
       </c>
       <c r="B399" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B400" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>207</v>
+        <v>26</v>
       </c>
       <c r="B401" t="s">
-        <v>1117</v>
+        <v>497</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>954</v>
+        <v>207</v>
       </c>
       <c r="B402" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>1100</v>
+        <v>954</v>
       </c>
       <c r="B403" t="s">
-        <v>1101</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>206</v>
+        <v>1100</v>
       </c>
       <c r="B404" t="s">
-        <v>1119</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B405" t="s">
-        <v>498</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B406" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="B407" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>658</v>
+        <v>145</v>
       </c>
       <c r="B408" t="s">
-        <v>729</v>
+        <v>500</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>171</v>
+        <v>658</v>
       </c>
       <c r="B409" t="s">
-        <v>501</v>
+        <v>729</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>1079</v>
+        <v>171</v>
       </c>
       <c r="B410" t="s">
-        <v>1080</v>
+        <v>501</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>263</v>
+        <v>1079</v>
       </c>
       <c r="B411" t="s">
-        <v>502</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>1081</v>
+        <v>263</v>
       </c>
       <c r="B412" t="s">
-        <v>1082</v>
+        <v>502</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>80</v>
+        <v>1081</v>
       </c>
       <c r="B413" t="s">
-        <v>503</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B414" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>191</v>
+        <v>65</v>
       </c>
       <c r="B415" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="B416" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>192</v>
+        <v>123</v>
       </c>
       <c r="B417" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="B418" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B419" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>1182</v>
+        <v>233</v>
       </c>
       <c r="B420" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>31</v>
+        <v>1182</v>
       </c>
       <c r="B421" t="s">
         <v>510</v>
@@ -8210,367 +8216,367 @@
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B422" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B423" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B424" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>1435</v>
+        <v>71</v>
       </c>
       <c r="B425" t="s">
-        <v>1436</v>
+        <v>513</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>306</v>
+        <v>1435</v>
       </c>
       <c r="B426" t="s">
-        <v>514</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>222</v>
+        <v>306</v>
       </c>
       <c r="B427" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>278</v>
+        <v>222</v>
       </c>
       <c r="B428" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B429" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>1386</v>
+        <v>279</v>
       </c>
       <c r="B430" t="s">
-        <v>1387</v>
+        <v>518</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>826</v>
+        <v>1386</v>
       </c>
       <c r="B431" t="s">
-        <v>827</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>48</v>
+        <v>826</v>
       </c>
       <c r="B432" t="s">
-        <v>519</v>
+        <v>827</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="B433" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="B434" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>1368</v>
+        <v>52</v>
       </c>
       <c r="B435" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>223</v>
+        <v>1368</v>
       </c>
       <c r="B436" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>1085</v>
+        <v>223</v>
       </c>
       <c r="B437" t="s">
-        <v>1086</v>
+        <v>522</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>1096</v>
+        <v>1085</v>
       </c>
       <c r="B438" t="s">
-        <v>1099</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>1041</v>
+        <v>1096</v>
       </c>
       <c r="B439" t="s">
-        <v>1042</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>96</v>
+        <v>1041</v>
       </c>
       <c r="B440" t="s">
-        <v>523</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>248</v>
+        <v>96</v>
       </c>
       <c r="B441" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B442" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>94</v>
+        <v>249</v>
       </c>
       <c r="B443" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>1055</v>
+        <v>94</v>
       </c>
       <c r="B444" t="s">
-        <v>1056</v>
+        <v>526</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>212</v>
+        <v>1055</v>
       </c>
       <c r="B445" t="s">
-        <v>527</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>1207</v>
+        <v>212</v>
       </c>
       <c r="B446" t="s">
-        <v>1208</v>
+        <v>527</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>910</v>
+        <v>1207</v>
       </c>
       <c r="B447" t="s">
-        <v>911</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B448" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="B449" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>329</v>
+        <v>912</v>
       </c>
       <c r="B450" t="s">
-        <v>528</v>
+        <v>913</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>1410</v>
+        <v>329</v>
       </c>
       <c r="B451" t="s">
-        <v>1411</v>
+        <v>528</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="B452" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>1057</v>
+        <v>1412</v>
       </c>
       <c r="B453" t="s">
-        <v>1058</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>989</v>
+        <v>1057</v>
       </c>
       <c r="B454" t="s">
-        <v>990</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>1396</v>
+        <v>989</v>
       </c>
       <c r="B455" t="s">
-        <v>1397</v>
+        <v>990</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>985</v>
+        <v>1396</v>
       </c>
       <c r="B456" t="s">
-        <v>986</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="B457" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>82</v>
+        <v>987</v>
       </c>
       <c r="B458" t="s">
-        <v>529</v>
+        <v>988</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>767</v>
+        <v>82</v>
       </c>
       <c r="B459" t="s">
-        <v>768</v>
+        <v>529</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>197</v>
+        <v>767</v>
       </c>
       <c r="B460" t="s">
-        <v>530</v>
+        <v>768</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>649</v>
+        <v>197</v>
       </c>
       <c r="B461" t="s">
-        <v>730</v>
+        <v>530</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>1433</v>
+        <v>649</v>
       </c>
       <c r="B462" t="s">
-        <v>1434</v>
+        <v>730</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>1339</v>
+        <v>1433</v>
       </c>
       <c r="B463" t="s">
-        <v>1340</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>816</v>
+        <v>1339</v>
       </c>
       <c r="B464" t="s">
-        <v>817</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>1059</v>
+        <v>816</v>
       </c>
       <c r="B465" t="s">
-        <v>1060</v>
+        <v>817</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>3</v>
+        <v>1059</v>
       </c>
       <c r="B466" t="s">
-        <v>4</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>952</v>
+        <v>3</v>
       </c>
       <c r="B467" t="s">
         <v>4</v>
@@ -8578,7 +8584,7 @@
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B468" t="s">
         <v>4</v>
@@ -8586,1631 +8592,1631 @@
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>659</v>
+        <v>953</v>
       </c>
       <c r="B469" t="s">
-        <v>731</v>
+        <v>4</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>1287</v>
+        <v>659</v>
       </c>
       <c r="B470" t="s">
-        <v>1288</v>
+        <v>731</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>765</v>
+        <v>1287</v>
       </c>
       <c r="B471" t="s">
-        <v>766</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>85</v>
+        <v>765</v>
       </c>
       <c r="B472" t="s">
-        <v>531</v>
+        <v>766</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>1053</v>
+        <v>85</v>
       </c>
       <c r="B473" t="s">
-        <v>1054</v>
+        <v>531</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>824</v>
+        <v>1053</v>
       </c>
       <c r="B474" t="s">
-        <v>825</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>804</v>
+        <v>824</v>
       </c>
       <c r="B475" t="s">
-        <v>805</v>
+        <v>825</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>187</v>
+        <v>804</v>
       </c>
       <c r="B476" t="s">
-        <v>532</v>
+        <v>805</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>822</v>
+        <v>187</v>
       </c>
       <c r="B477" t="s">
-        <v>823</v>
+        <v>532</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>928</v>
+        <v>822</v>
       </c>
       <c r="B478" t="s">
-        <v>1114</v>
+        <v>823</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>1439</v>
+        <v>928</v>
       </c>
       <c r="B479" t="s">
-        <v>1440</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>858</v>
+        <v>1439</v>
       </c>
       <c r="B480" t="s">
-        <v>859</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>1427</v>
+        <v>858</v>
       </c>
       <c r="B481" t="s">
-        <v>1428</v>
+        <v>859</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>1037</v>
+        <v>1427</v>
       </c>
       <c r="B482" t="s">
-        <v>1038</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>793</v>
+        <v>1037</v>
       </c>
       <c r="B483" t="s">
-        <v>1115</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B484" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>1484</v>
+        <v>792</v>
       </c>
       <c r="B485" t="s">
-        <v>1485</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="B486" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>13</v>
+        <v>1482</v>
       </c>
       <c r="B487" t="s">
-        <v>14</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>812</v>
+        <v>13</v>
       </c>
       <c r="B488" t="s">
-        <v>813</v>
+        <v>14</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>1217</v>
+        <v>812</v>
       </c>
       <c r="B489" t="s">
-        <v>1218</v>
+        <v>813</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>186</v>
+        <v>1217</v>
       </c>
       <c r="B490" t="s">
-        <v>533</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>806</v>
+        <v>186</v>
       </c>
       <c r="B491" t="s">
-        <v>807</v>
+        <v>533</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>319</v>
+        <v>806</v>
       </c>
       <c r="B492" t="s">
-        <v>534</v>
+        <v>807</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>651</v>
+        <v>319</v>
       </c>
       <c r="B493" t="s">
-        <v>732</v>
+        <v>534</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>850</v>
+        <v>651</v>
       </c>
       <c r="B494" t="s">
-        <v>851</v>
+        <v>732</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>653</v>
+        <v>850</v>
       </c>
       <c r="B495" t="s">
-        <v>733</v>
+        <v>851</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="B496" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>1189</v>
+        <v>648</v>
       </c>
       <c r="B497" t="s">
-        <v>1190</v>
+        <v>734</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>256</v>
+        <v>1189</v>
       </c>
       <c r="B498" t="s">
-        <v>535</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B499" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B500" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>188</v>
+        <v>261</v>
       </c>
       <c r="B501" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B502" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>930</v>
+        <v>190</v>
       </c>
       <c r="B503" t="s">
-        <v>931</v>
+        <v>539</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>1024</v>
+        <v>930</v>
       </c>
       <c r="B504" t="s">
-        <v>1025</v>
+        <v>931</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>1205</v>
+        <v>1024</v>
       </c>
       <c r="B505" t="s">
-        <v>1206</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>209</v>
+        <v>1205</v>
       </c>
       <c r="B506" t="s">
-        <v>540</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>1406</v>
+        <v>209</v>
       </c>
       <c r="B507" t="s">
-        <v>1407</v>
+        <v>540</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>1297</v>
+        <v>1406</v>
       </c>
       <c r="B508" t="s">
-        <v>1298</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>846</v>
+        <v>1297</v>
       </c>
       <c r="B509" t="s">
-        <v>847</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>143</v>
+        <v>846</v>
       </c>
       <c r="B510" t="s">
-        <v>541</v>
+        <v>847</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B511" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>1185</v>
+        <v>140</v>
       </c>
       <c r="B512" t="s">
-        <v>1186</v>
+        <v>542</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>1285</v>
+        <v>1185</v>
       </c>
       <c r="B513" t="s">
-        <v>1286</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>254</v>
+        <v>1285</v>
       </c>
       <c r="B514" t="s">
-        <v>543</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>330</v>
+        <v>254</v>
       </c>
       <c r="B515" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="B516" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="B517" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>73</v>
+        <v>234</v>
       </c>
       <c r="B518" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>341</v>
+        <v>73</v>
       </c>
       <c r="B519" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>308</v>
+        <v>341</v>
       </c>
       <c r="B520" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>838</v>
+        <v>308</v>
       </c>
       <c r="B521" t="s">
-        <v>839</v>
+        <v>549</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B522" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>220</v>
+        <v>840</v>
       </c>
       <c r="B523" t="s">
-        <v>550</v>
+        <v>841</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>903</v>
+        <v>220</v>
       </c>
       <c r="B524" t="s">
-        <v>904</v>
+        <v>550</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>1362</v>
+        <v>903</v>
       </c>
       <c r="B525" t="s">
-        <v>1363</v>
+        <v>904</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>957</v>
+        <v>1362</v>
       </c>
       <c r="B526" t="s">
-        <v>958</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>1170</v>
+        <v>957</v>
       </c>
       <c r="B527" t="s">
-        <v>1171</v>
+        <v>958</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>227</v>
+        <v>1170</v>
       </c>
       <c r="B528" t="s">
-        <v>551</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>333</v>
+        <v>227</v>
       </c>
       <c r="B529" t="s">
-        <v>1143</v>
+        <v>551</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>965</v>
+        <v>333</v>
       </c>
       <c r="B530" t="s">
-        <v>966</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>773</v>
+        <v>965</v>
       </c>
       <c r="B531" t="s">
-        <v>774</v>
+        <v>966</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>294</v>
+        <v>773</v>
       </c>
       <c r="B532" t="s">
-        <v>552</v>
+        <v>774</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>946</v>
+        <v>294</v>
       </c>
       <c r="B533" t="s">
-        <v>947</v>
+        <v>552</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>338</v>
+        <v>946</v>
       </c>
       <c r="B534" t="s">
-        <v>553</v>
+        <v>947</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>775</v>
+        <v>338</v>
       </c>
       <c r="B535" t="s">
-        <v>774</v>
+        <v>553</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>1301</v>
+        <v>775</v>
       </c>
       <c r="B536" t="s">
-        <v>1302</v>
+        <v>774</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>339</v>
+        <v>1301</v>
       </c>
       <c r="B537" t="s">
-        <v>554</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B538" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>640</v>
+        <v>340</v>
       </c>
       <c r="B539" t="s">
-        <v>735</v>
+        <v>555</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>39</v>
+        <v>640</v>
       </c>
       <c r="B540" t="s">
-        <v>556</v>
+        <v>735</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B541" t="s">
-        <v>1475</v>
+        <v>556</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>342</v>
+        <v>38</v>
       </c>
       <c r="B542" t="s">
-        <v>557</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>107</v>
+        <v>342</v>
       </c>
       <c r="B543" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>1414</v>
+        <v>107</v>
       </c>
       <c r="B544" t="s">
-        <v>1415</v>
+        <v>558</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>1022</v>
+        <v>1414</v>
       </c>
       <c r="B545" t="s">
-        <v>1023</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>897</v>
+        <v>1022</v>
       </c>
       <c r="B546" t="s">
-        <v>898</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>117</v>
+        <v>897</v>
       </c>
       <c r="B547" t="s">
-        <v>559</v>
+        <v>898</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>1018</v>
+        <v>117</v>
       </c>
       <c r="B548" t="s">
-        <v>1019</v>
+        <v>559</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>98</v>
+        <v>1018</v>
       </c>
       <c r="B549" t="s">
-        <v>560</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B550" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>661</v>
+        <v>99</v>
       </c>
       <c r="B551" t="s">
-        <v>736</v>
+        <v>561</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>1094</v>
+        <v>661</v>
       </c>
       <c r="B552" t="s">
-        <v>1017</v>
+        <v>736</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>818</v>
+        <v>1094</v>
       </c>
       <c r="B553" t="s">
-        <v>819</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>113</v>
+        <v>818</v>
       </c>
       <c r="B554" t="s">
-        <v>562</v>
+        <v>819</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>884</v>
+        <v>113</v>
       </c>
       <c r="B555" t="s">
-        <v>885</v>
+        <v>562</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>45</v>
+        <v>884</v>
       </c>
       <c r="B556" t="s">
-        <v>1113</v>
+        <v>885</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>290</v>
+        <v>45</v>
       </c>
       <c r="B557" t="s">
-        <v>563</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B558" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>47</v>
+        <v>299</v>
       </c>
       <c r="B559" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>842</v>
+        <v>47</v>
       </c>
       <c r="B560" t="s">
-        <v>843</v>
+        <v>565</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>51</v>
+        <v>842</v>
       </c>
       <c r="B561" t="s">
-        <v>566</v>
+        <v>843</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>866</v>
+        <v>51</v>
       </c>
       <c r="B562" t="s">
-        <v>867</v>
+        <v>566</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>114</v>
+        <v>866</v>
       </c>
       <c r="B563" t="s">
-        <v>567</v>
+        <v>867</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>848</v>
+        <v>114</v>
       </c>
       <c r="B564" t="s">
-        <v>849</v>
+        <v>567</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>144</v>
+        <v>848</v>
       </c>
       <c r="B565" t="s">
-        <v>568</v>
+        <v>849</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>1071</v>
+        <v>144</v>
       </c>
       <c r="B566" t="s">
-        <v>1072</v>
+        <v>568</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>176</v>
+        <v>1071</v>
       </c>
       <c r="B567" t="s">
-        <v>569</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>315</v>
+        <v>176</v>
       </c>
       <c r="B568" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>29</v>
+        <v>315</v>
       </c>
       <c r="B569" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>1011</v>
+        <v>29</v>
       </c>
       <c r="B570" t="s">
-        <v>1012</v>
+        <v>571</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>1213</v>
+        <v>1011</v>
       </c>
       <c r="B571" t="s">
-        <v>1214</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>293</v>
+        <v>1213</v>
       </c>
       <c r="B572" t="s">
-        <v>572</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>975</v>
+        <v>293</v>
       </c>
       <c r="B573" t="s">
-        <v>976</v>
+        <v>572</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>1446</v>
+        <v>975</v>
       </c>
       <c r="B574" t="s">
-        <v>1447</v>
+        <v>976</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>301</v>
+        <v>1446</v>
       </c>
       <c r="B575" t="s">
-        <v>573</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>997</v>
+        <v>301</v>
       </c>
       <c r="B576" t="s">
-        <v>998</v>
+        <v>573</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="B577" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>75</v>
+        <v>1001</v>
       </c>
       <c r="B578" t="s">
-        <v>574</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B579" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B580" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>328</v>
+        <v>78</v>
       </c>
       <c r="B581" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>1393</v>
+        <v>328</v>
       </c>
       <c r="B582" t="s">
-        <v>1394</v>
+        <v>577</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>1291</v>
+        <v>1393</v>
       </c>
       <c r="B583" t="s">
-        <v>1292</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>747</v>
+        <v>1291</v>
       </c>
       <c r="B584" t="s">
-        <v>748</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>800</v>
+        <v>747</v>
       </c>
       <c r="B585" t="s">
-        <v>801</v>
+        <v>748</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>1304</v>
+        <v>800</v>
       </c>
       <c r="B586" t="s">
-        <v>1305</v>
+        <v>801</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>135</v>
+        <v>1304</v>
       </c>
       <c r="B587" t="s">
-        <v>578</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>1168</v>
+        <v>135</v>
       </c>
       <c r="B588" t="s">
-        <v>1169</v>
+        <v>578</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>1031</v>
+        <v>1168</v>
       </c>
       <c r="B589" t="s">
-        <v>1032</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>215</v>
+        <v>1031</v>
       </c>
       <c r="B590" t="s">
-        <v>579</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>929</v>
+        <v>215</v>
       </c>
       <c r="B591" t="s">
-        <v>1128</v>
+        <v>579</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>216</v>
+        <v>929</v>
       </c>
       <c r="B592" t="s">
-        <v>1111</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>316</v>
+        <v>216</v>
       </c>
       <c r="B593" t="s">
-        <v>580</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>1073</v>
+        <v>316</v>
       </c>
       <c r="B594" t="s">
-        <v>1074</v>
+        <v>580</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>214</v>
+        <v>1073</v>
       </c>
       <c r="B595" t="s">
-        <v>1112</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>993</v>
+        <v>214</v>
       </c>
       <c r="B596" t="s">
-        <v>994</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B597" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>225</v>
+        <v>995</v>
       </c>
       <c r="B598" t="s">
-        <v>581</v>
+        <v>996</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>1380</v>
+        <v>225</v>
       </c>
       <c r="B599" t="s">
-        <v>1381</v>
+        <v>581</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>942</v>
+        <v>1380</v>
       </c>
       <c r="B600" t="s">
-        <v>943</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>1089</v>
+        <v>942</v>
       </c>
       <c r="B601" t="s">
-        <v>1090</v>
+        <v>943</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>1039</v>
+        <v>1089</v>
       </c>
       <c r="B602" t="s">
-        <v>1040</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>93</v>
+        <v>1039</v>
       </c>
       <c r="B603" t="s">
-        <v>582</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="B604" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>778</v>
+        <v>120</v>
       </c>
       <c r="B605" t="s">
-        <v>779</v>
+        <v>583</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>133</v>
+        <v>778</v>
       </c>
       <c r="B606" t="s">
-        <v>584</v>
+        <v>779</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="B607" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>1293</v>
+        <v>62</v>
       </c>
       <c r="B608" t="s">
-        <v>1294</v>
+        <v>585</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>66</v>
+        <v>1293</v>
       </c>
       <c r="B609" t="s">
-        <v>586</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>820</v>
+        <v>66</v>
       </c>
       <c r="B610" t="s">
-        <v>821</v>
+        <v>586</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>944</v>
+        <v>820</v>
       </c>
       <c r="B611" t="s">
-        <v>945</v>
+        <v>821</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>1197</v>
+        <v>944</v>
       </c>
       <c r="B612" t="s">
-        <v>1198</v>
+        <v>945</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>1306</v>
+        <v>1197</v>
       </c>
       <c r="B613" t="s">
-        <v>1307</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>79</v>
+        <v>1306</v>
       </c>
       <c r="B614" t="s">
-        <v>587</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B615" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="B616" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>1166</v>
+        <v>122</v>
       </c>
       <c r="B617" t="s">
-        <v>1167</v>
+        <v>589</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>181</v>
+        <v>1166</v>
       </c>
       <c r="B618" t="s">
-        <v>590</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>796</v>
+        <v>181</v>
       </c>
       <c r="B619" t="s">
-        <v>797</v>
+        <v>590</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>1271</v>
+        <v>796</v>
       </c>
       <c r="B620" t="s">
-        <v>1276</v>
+        <v>797</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>686</v>
+        <v>1271</v>
       </c>
       <c r="B621" t="s">
-        <v>737</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
-        <v>1272</v>
+        <v>686</v>
       </c>
       <c r="B622" t="s">
-        <v>1277</v>
+        <v>737</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="B623" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="B624" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="B625" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
-        <v>1133</v>
+        <v>1275</v>
       </c>
       <c r="B626" t="s">
-        <v>1134</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="B627" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
-        <v>284</v>
+        <v>1131</v>
       </c>
       <c r="B628" t="s">
-        <v>591</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>967</v>
+        <v>284</v>
       </c>
       <c r="B629" t="s">
-        <v>968</v>
+        <v>591</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>1201</v>
+        <v>967</v>
       </c>
       <c r="B630" t="s">
-        <v>1202</v>
+        <v>968</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>836</v>
+        <v>1201</v>
       </c>
       <c r="B631" t="s">
-        <v>837</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>283</v>
+        <v>836</v>
       </c>
       <c r="B632" t="s">
-        <v>592</v>
+        <v>837</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
-        <v>878</v>
+        <v>283</v>
       </c>
       <c r="B633" t="s">
-        <v>879</v>
+        <v>592</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
-        <v>1162</v>
+        <v>878</v>
       </c>
       <c r="B634" t="s">
-        <v>1163</v>
+        <v>879</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
-        <v>751</v>
+        <v>1162</v>
       </c>
       <c r="B635" t="s">
-        <v>752</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
-        <v>1069</v>
+        <v>751</v>
       </c>
       <c r="B636" t="s">
-        <v>1070</v>
+        <v>752</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
-        <v>67</v>
+        <v>1069</v>
       </c>
       <c r="B637" t="s">
-        <v>593</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B638" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
-        <v>1375</v>
+        <v>68</v>
       </c>
       <c r="B639" t="s">
-        <v>1376</v>
+        <v>594</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
-        <v>95</v>
+        <v>1375</v>
       </c>
       <c r="B640" t="s">
-        <v>595</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>289</v>
+        <v>95</v>
       </c>
       <c r="B641" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B642" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="B643" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
-        <v>193</v>
+        <v>264</v>
       </c>
       <c r="B644" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
-        <v>1335</v>
+        <v>193</v>
       </c>
       <c r="B645" t="s">
-        <v>1336</v>
+        <v>599</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
-        <v>895</v>
+        <v>1335</v>
       </c>
       <c r="B646" t="s">
-        <v>896</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
-        <v>44</v>
+        <v>895</v>
       </c>
       <c r="B647" t="s">
-        <v>1110</v>
+        <v>896</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
-        <v>1061</v>
+        <v>44</v>
       </c>
       <c r="B648" t="s">
-        <v>1062</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
-        <v>323</v>
+        <v>1061</v>
       </c>
       <c r="B649" t="s">
-        <v>600</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B650" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
-        <v>844</v>
+        <v>324</v>
       </c>
       <c r="B651" t="s">
-        <v>845</v>
+        <v>601</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>882</v>
+        <v>844</v>
       </c>
       <c r="B652" t="s">
-        <v>883</v>
+        <v>845</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
-        <v>1219</v>
+        <v>882</v>
       </c>
       <c r="B653" t="s">
-        <v>1220</v>
+        <v>883</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
-        <v>864</v>
+        <v>1219</v>
       </c>
       <c r="B654" t="s">
-        <v>865</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
-        <v>33</v>
+        <v>864</v>
       </c>
       <c r="B655" t="s">
-        <v>602</v>
+        <v>865</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B656" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
-        <v>1126</v>
+        <v>36</v>
       </c>
       <c r="B657" t="s">
-        <v>1127</v>
+        <v>603</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
-        <v>309</v>
+        <v>1126</v>
       </c>
       <c r="B658" t="s">
-        <v>604</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
       <c r="B659" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
-        <v>302</v>
+        <v>257</v>
       </c>
       <c r="B660" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
-        <v>228</v>
+        <v>302</v>
       </c>
       <c r="B661" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c r="B662" t="s">
-        <v>18</v>
+        <v>607</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
-        <v>650</v>
+        <v>17</v>
       </c>
       <c r="B663" t="s">
-        <v>738</v>
+        <v>18</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
-        <v>1402</v>
+        <v>650</v>
       </c>
       <c r="B664" t="s">
-        <v>1403</v>
+        <v>738</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
-        <v>780</v>
+        <v>1402</v>
       </c>
       <c r="B665" t="s">
-        <v>781</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
-        <v>142</v>
+        <v>780</v>
       </c>
       <c r="B666" t="s">
-        <v>608</v>
+        <v>781</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
-        <v>1160</v>
+        <v>142</v>
       </c>
       <c r="B667" t="s">
-        <v>1161</v>
+        <v>608</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
-        <v>950</v>
+        <v>1160</v>
       </c>
       <c r="B668" t="s">
-        <v>951</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
-        <v>54</v>
+        <v>950</v>
       </c>
       <c r="B669" t="s">
-        <v>609</v>
+        <v>951</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
-        <v>265</v>
+        <v>54</v>
       </c>
       <c r="B670" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
-        <v>970</v>
+        <v>265</v>
       </c>
       <c r="B671" t="s">
-        <v>969</v>
+        <v>610</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
-        <v>1392</v>
+        <v>970</v>
       </c>
       <c r="B672" t="s">
         <v>969</v>
@@ -10218,617 +10224,625 @@
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
-        <v>56</v>
+        <v>1392</v>
       </c>
       <c r="B673" t="s">
-        <v>611</v>
+        <v>969</v>
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
-        <v>1199</v>
+        <v>56</v>
       </c>
       <c r="B674" t="s">
-        <v>1200</v>
+        <v>611</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
-        <v>185</v>
+        <v>1199</v>
       </c>
       <c r="B675" t="s">
-        <v>612</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="B676" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="B677" t="s">
-        <v>1328</v>
+        <v>613</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
-        <v>1326</v>
+        <v>43</v>
       </c>
       <c r="B678" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
-        <v>1450</v>
+        <v>1326</v>
       </c>
       <c r="B679" t="s">
-        <v>1452</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="B680" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
-        <v>40</v>
+        <v>1451</v>
       </c>
       <c r="B681" t="s">
-        <v>1486</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
-        <v>1324</v>
+        <v>40</v>
       </c>
       <c r="B682" t="s">
-        <v>1325</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
-        <v>1152</v>
+        <v>1324</v>
       </c>
       <c r="B683" t="s">
-        <v>1153</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
-        <v>165</v>
+        <v>1152</v>
       </c>
       <c r="B684" t="s">
-        <v>614</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
-        <v>1281</v>
+        <v>165</v>
       </c>
       <c r="B685" t="s">
-        <v>1282</v>
+        <v>614</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="B686" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
-        <v>1471</v>
+        <v>1283</v>
       </c>
       <c r="B687" t="s">
-        <v>1472</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="B688" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
-        <v>12</v>
+        <v>1473</v>
       </c>
       <c r="B689" t="s">
-        <v>11</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
-        <v>250</v>
+        <v>12</v>
       </c>
       <c r="B690" t="s">
-        <v>615</v>
+        <v>11</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="B691" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
-        <v>1033</v>
+        <v>27</v>
       </c>
       <c r="B692" t="s">
-        <v>1034</v>
+        <v>616</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
-        <v>28</v>
+        <v>1033</v>
       </c>
       <c r="B693" t="s">
-        <v>617</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
-        <v>1187</v>
+        <v>28</v>
       </c>
       <c r="B694" t="s">
-        <v>1188</v>
+        <v>617</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
-        <v>255</v>
+        <v>1187</v>
       </c>
       <c r="B695" t="s">
-        <v>618</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
-        <v>1316</v>
+        <v>255</v>
       </c>
       <c r="B696" t="s">
-        <v>1321</v>
+        <v>618</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
-        <v>790</v>
+        <v>1316</v>
       </c>
       <c r="B697" t="s">
-        <v>791</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
-        <v>267</v>
+        <v>790</v>
       </c>
       <c r="B698" t="s">
-        <v>619</v>
+        <v>791</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
-        <v>656</v>
+        <v>267</v>
       </c>
       <c r="B699" t="s">
-        <v>739</v>
+        <v>619</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B700" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
-        <v>139</v>
+        <v>657</v>
       </c>
       <c r="B701" t="s">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="B702" t="s">
-        <v>2</v>
+        <v>620</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="B703" t="s">
-        <v>621</v>
+        <v>2</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
-        <v>1331</v>
+        <v>105</v>
       </c>
       <c r="B704" t="s">
-        <v>1332</v>
+        <v>621</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
-        <v>1027</v>
+        <v>1331</v>
       </c>
       <c r="B705" t="s">
-        <v>1109</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
-        <v>860</v>
+        <v>1027</v>
       </c>
       <c r="B706" t="s">
-        <v>861</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
-        <v>1431</v>
+        <v>860</v>
       </c>
       <c r="B707" t="s">
-        <v>1432</v>
+        <v>861</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
-        <v>1028</v>
+        <v>1431</v>
       </c>
       <c r="B708" t="s">
-        <v>1108</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
-        <v>292</v>
+        <v>1028</v>
       </c>
       <c r="B709" t="s">
-        <v>622</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
-        <v>8</v>
+        <v>292</v>
       </c>
       <c r="B710" t="s">
-        <v>11</v>
+        <v>622</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
-        <v>334</v>
+        <v>8</v>
       </c>
       <c r="B711" t="s">
-        <v>623</v>
+        <v>11</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
-        <v>1373</v>
+        <v>334</v>
       </c>
       <c r="B712" t="s">
-        <v>1374</v>
+        <v>623</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
-        <v>1333</v>
+        <v>1373</v>
       </c>
       <c r="B713" t="s">
-        <v>1334</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
-        <v>331</v>
+        <v>1333</v>
       </c>
       <c r="B714" t="s">
-        <v>624</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A715" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="B715" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A716" t="s">
-        <v>318</v>
+        <v>259</v>
       </c>
       <c r="B716" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
-        <v>854</v>
+        <v>318</v>
       </c>
       <c r="B717" t="s">
-        <v>855</v>
+        <v>626</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
-        <v>1156</v>
+        <v>854</v>
       </c>
       <c r="B718" t="s">
-        <v>1157</v>
+        <v>855</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
-        <v>268</v>
+        <v>1156</v>
       </c>
       <c r="B719" t="s">
-        <v>627</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B720" t="s">
-        <v>1103</v>
+        <v>627</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B721" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B722" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B723" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B724" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B725" t="s">
-        <v>1102</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
-        <v>92</v>
+        <v>272</v>
       </c>
       <c r="B726" t="s">
-        <v>628</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
-        <v>200</v>
+        <v>92</v>
       </c>
       <c r="B727" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B728" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
-        <v>1209</v>
+        <v>203</v>
       </c>
       <c r="B729" t="s">
-        <v>1210</v>
+        <v>630</v>
       </c>
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A730" t="s">
-        <v>172</v>
+        <v>1209</v>
       </c>
       <c r="B730" t="s">
-        <v>631</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
-        <v>1463</v>
+        <v>172</v>
       </c>
       <c r="B731" t="s">
-        <v>1464</v>
+        <v>631</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B732" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A733" t="s">
         <v>688</v>
       </c>
-      <c r="B732" t="s">
+      <c r="B733" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="733" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A733" t="s">
+    <row r="734" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A734" t="s">
         <v>1458</v>
       </c>
-      <c r="B733" s="1" t="s">
+      <c r="B734" s="1" t="s">
         <v>1459</v>
-      </c>
-    </row>
-    <row r="734" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A734" t="s">
-        <v>252</v>
-      </c>
-      <c r="B734" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
-        <v>689</v>
+        <v>252</v>
       </c>
       <c r="B735" t="s">
-        <v>742</v>
+        <v>632</v>
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
-        <v>189</v>
+        <v>689</v>
       </c>
       <c r="B736" t="s">
-        <v>1401</v>
+        <v>742</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A737" t="s">
-        <v>983</v>
+        <v>189</v>
       </c>
       <c r="B737" t="s">
-        <v>984</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
-        <v>311</v>
+        <v>983</v>
       </c>
       <c r="B738" t="s">
-        <v>633</v>
+        <v>984</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B739" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A740" t="s">
-        <v>1026</v>
+        <v>312</v>
       </c>
       <c r="B740" t="s">
-        <v>1457</v>
+        <v>634</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
-        <v>1456</v>
+        <v>1026</v>
       </c>
       <c r="B741" t="s">
-        <v>1479</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
-        <v>999</v>
+        <v>1456</v>
       </c>
       <c r="B742" t="s">
-        <v>1000</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
-        <v>81</v>
+        <v>999</v>
       </c>
       <c r="B743" t="s">
-        <v>635</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A744" t="s">
-        <v>646</v>
+        <v>81</v>
       </c>
       <c r="B744" t="s">
-        <v>743</v>
+        <v>635</v>
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A745" t="s">
-        <v>916</v>
+        <v>646</v>
       </c>
       <c r="B745" t="s">
-        <v>917</v>
+        <v>743</v>
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A746" t="s">
-        <v>637</v>
+        <v>916</v>
       </c>
       <c r="B746" t="s">
-        <v>744</v>
+        <v>917</v>
       </c>
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A747" t="s">
-        <v>963</v>
+        <v>637</v>
       </c>
       <c r="B747" t="s">
-        <v>964</v>
+        <v>744</v>
       </c>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A748" t="s">
-        <v>1144</v>
+        <v>963</v>
       </c>
       <c r="B748" t="s">
-        <v>1145</v>
+        <v>964</v>
       </c>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A749" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B749" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A750" t="s">
         <v>1371</v>
       </c>
-      <c r="B749" t="s">
+      <c r="B750" t="s">
         <v>1372</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5A4E01-CD1B-4831-9775-3995363E1D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C766FC-3360-4ECC-A3F6-0090352371EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="1489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="1493">
   <si>
     <t>trigger</t>
   </si>
@@ -4359,9 +4359,6 @@
     <t>cavum septum pellucidum et vergae</t>
   </si>
   <si>
-    <t>bloom</t>
-  </si>
-  <si>
     <t xml:space="preserve">disc desiccation changes </t>
   </si>
   <si>
@@ -4464,9 +4461,6 @@
     <t>Multilevel flowing anterolateral ossification/bridging osteophytes along the thoracic spine involving multiple contiguous vertebral levels, with relative preservation of the intervertebral disc spaces. Findings are suggestive of diffuse idiopathic skeletal hyperostosis (DISH)</t>
   </si>
   <si>
-    <t>No blooming seen on SWI/GRE</t>
-  </si>
-  <si>
     <t>Multiple tiny T2 hyperintense FLAIR suppressed foci without gliotic rim noted in  bilateral frontoparietal lobes, likely Virchow Robin spaces</t>
   </si>
   <si>
@@ -4495,6 +4489,24 @@
   </si>
   <si>
     <t>facilitated diffusion on DWI</t>
+  </si>
+  <si>
+    <t>blooms</t>
+  </si>
+  <si>
+    <t>No blooming seen on SWI</t>
+  </si>
+  <si>
+    <t>bloomg</t>
+  </si>
+  <si>
+    <t>No blooming seen on GRE</t>
+  </si>
+  <si>
+    <t>mast</t>
+  </si>
+  <si>
+    <t>T2 high signal intensity noted in bilateral mastoid air cells - suggestive of mastoiditis</t>
   </si>
 </sst>
 </file>
@@ -4563,10 +4575,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B750" totalsRowShown="0">
-  <autoFilter ref="A1:B750" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B750">
-    <sortCondition ref="A1:A750"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B752" totalsRowShown="0">
+  <autoFilter ref="A1:B752" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B752">
+    <sortCondition ref="A1:A752"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4839,7 +4851,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B750"/>
+  <dimension ref="A1:B752"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -5200,7 +5212,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="B45" t="s">
         <v>1341</v>
@@ -5400,1351 +5412,1351 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>1443</v>
+        <v>1489</v>
       </c>
       <c r="B70" t="s">
-        <v>1478</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>880</v>
+        <v>1487</v>
       </c>
       <c r="B71" t="s">
-        <v>881</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>1312</v>
+        <v>880</v>
       </c>
       <c r="B72" t="s">
-        <v>1313</v>
+        <v>881</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>654</v>
+        <v>1312</v>
       </c>
       <c r="B73" t="s">
-        <v>693</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>1388</v>
+        <v>654</v>
       </c>
       <c r="B74" t="s">
-        <v>1389</v>
+        <v>693</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>237</v>
+        <v>1388</v>
       </c>
       <c r="B75" t="s">
-        <v>372</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>1211</v>
+        <v>237</v>
       </c>
       <c r="B76" t="s">
-        <v>1212</v>
+        <v>372</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>60</v>
+        <v>1211</v>
       </c>
       <c r="B77" t="s">
-        <v>373</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>1007</v>
+        <v>60</v>
       </c>
       <c r="B78" t="s">
-        <v>1008</v>
+        <v>373</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>1221</v>
+        <v>1007</v>
       </c>
       <c r="B79" t="s">
-        <v>1222</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>663</v>
+        <v>1221</v>
       </c>
       <c r="B80" t="s">
-        <v>694</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>1223</v>
+        <v>663</v>
       </c>
       <c r="B81" t="s">
-        <v>1224</v>
+        <v>694</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>664</v>
+        <v>1223</v>
       </c>
       <c r="B82" t="s">
-        <v>695</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>1225</v>
+        <v>664</v>
       </c>
       <c r="B83" t="s">
-        <v>1226</v>
+        <v>695</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>665</v>
+        <v>1225</v>
       </c>
       <c r="B84" t="s">
-        <v>696</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>1227</v>
+        <v>665</v>
       </c>
       <c r="B85" t="s">
-        <v>1228</v>
+        <v>696</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>666</v>
+        <v>1227</v>
       </c>
       <c r="B86" t="s">
-        <v>697</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>1229</v>
+        <v>666</v>
       </c>
       <c r="B87" t="s">
-        <v>1230</v>
+        <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>667</v>
+        <v>1229</v>
       </c>
       <c r="B88" t="s">
-        <v>698</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>1231</v>
+        <v>667</v>
       </c>
       <c r="B89" t="s">
-        <v>1234</v>
+        <v>698</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>668</v>
+        <v>1231</v>
       </c>
       <c r="B90" t="s">
-        <v>699</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>1232</v>
+        <v>668</v>
       </c>
       <c r="B91" t="s">
-        <v>1235</v>
+        <v>699</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>669</v>
+        <v>1232</v>
       </c>
       <c r="B92" t="s">
-        <v>700</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>1233</v>
+        <v>669</v>
       </c>
       <c r="B93" t="s">
-        <v>1236</v>
+        <v>700</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>870</v>
+        <v>1233</v>
       </c>
       <c r="B94" t="s">
-        <v>871</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>320</v>
+        <v>870</v>
       </c>
       <c r="B95" t="s">
-        <v>374</v>
+        <v>871</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>194</v>
+        <v>320</v>
       </c>
       <c r="B96" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="B97" t="s">
-        <v>22</v>
+        <v>375</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B98" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="B99" t="s">
-        <v>376</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>287</v>
+        <v>196</v>
       </c>
       <c r="B100" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B101" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>336</v>
+        <v>286</v>
       </c>
       <c r="B102" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>893</v>
+        <v>336</v>
       </c>
       <c r="B103" t="s">
-        <v>894</v>
+        <v>379</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>305</v>
+        <v>893</v>
       </c>
       <c r="B104" t="s">
-        <v>380</v>
+        <v>894</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="B105" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>1141</v>
+        <v>322</v>
       </c>
       <c r="B106" t="s">
-        <v>1142</v>
+        <v>381</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>276</v>
+        <v>1141</v>
       </c>
       <c r="B107" t="s">
-        <v>382</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>332</v>
+        <v>276</v>
       </c>
       <c r="B108" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>42</v>
+        <v>332</v>
       </c>
       <c r="B109" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B110" t="s">
-        <v>1122</v>
+        <v>384</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>644</v>
+        <v>41</v>
       </c>
       <c r="B111" t="s">
-        <v>701</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>1454</v>
+        <v>644</v>
       </c>
       <c r="B112" t="s">
-        <v>1455</v>
+        <v>701</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>217</v>
+        <v>1453</v>
       </c>
       <c r="B113" t="s">
-        <v>385</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>288</v>
+        <v>217</v>
       </c>
       <c r="B114" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>218</v>
+        <v>288</v>
       </c>
       <c r="B115" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>296</v>
+        <v>218</v>
       </c>
       <c r="B116" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>199</v>
+        <v>296</v>
       </c>
       <c r="B117" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>1424</v>
+        <v>199</v>
       </c>
       <c r="B118" t="s">
-        <v>1425</v>
+        <v>389</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>643</v>
+        <v>1424</v>
       </c>
       <c r="B119" t="s">
-        <v>702</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>112</v>
+        <v>643</v>
       </c>
       <c r="B120" t="s">
-        <v>390</v>
+        <v>702</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="B121" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="B122" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>1158</v>
+        <v>115</v>
       </c>
       <c r="B123" t="s">
-        <v>1159</v>
+        <v>392</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>874</v>
+        <v>1158</v>
       </c>
       <c r="B124" t="s">
-        <v>875</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>802</v>
+        <v>874</v>
       </c>
       <c r="B125" t="s">
-        <v>803</v>
+        <v>875</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>1480</v>
+        <v>802</v>
       </c>
       <c r="B126" t="s">
-        <v>1481</v>
+        <v>803</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>152</v>
+        <v>1478</v>
       </c>
       <c r="B127" t="s">
-        <v>393</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>1303</v>
+        <v>152</v>
       </c>
       <c r="B128" t="s">
-        <v>1308</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>124</v>
+        <v>1303</v>
       </c>
       <c r="B129" t="s">
-        <v>395</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B130" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="B131" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>961</v>
+        <v>155</v>
       </c>
       <c r="B132" t="s">
-        <v>962</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>84</v>
+        <v>961</v>
       </c>
       <c r="B133" t="s">
-        <v>397</v>
+        <v>962</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>959</v>
+        <v>84</v>
       </c>
       <c r="B134" t="s">
-        <v>960</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>1390</v>
+        <v>959</v>
       </c>
       <c r="B135" t="s">
-        <v>1391</v>
+        <v>960</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>103</v>
+        <v>1390</v>
       </c>
       <c r="B136" t="s">
-        <v>398</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>198</v>
+        <v>103</v>
       </c>
       <c r="B137" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>314</v>
+        <v>198</v>
       </c>
       <c r="B138" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>104</v>
+        <v>314</v>
       </c>
       <c r="B139" t="s">
-        <v>1470</v>
+        <v>400</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="B140" t="s">
-        <v>401</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="B141" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B142" t="s">
-        <v>1323</v>
+        <v>402</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>1322</v>
+        <v>102</v>
       </c>
       <c r="B143" t="s">
-        <v>403</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>924</v>
+        <v>1322</v>
       </c>
       <c r="B144" t="s">
-        <v>925</v>
+        <v>403</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B145" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>162</v>
+        <v>922</v>
       </c>
       <c r="B146" t="s">
-        <v>404</v>
+        <v>923</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>1135</v>
+        <v>162</v>
       </c>
       <c r="B147" t="s">
-        <v>1136</v>
+        <v>404</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>1366</v>
+        <v>1135</v>
       </c>
       <c r="B148" t="s">
-        <v>1367</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>832</v>
+        <v>1366</v>
       </c>
       <c r="B149" t="s">
-        <v>833</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B150" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>1309</v>
+        <v>834</v>
       </c>
       <c r="B151" t="s">
-        <v>1469</v>
+        <v>835</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>1075</v>
+        <v>1309</v>
       </c>
       <c r="B152" t="s">
-        <v>1076</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>660</v>
+        <v>1075</v>
       </c>
       <c r="B153" t="s">
-        <v>703</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>641</v>
+        <v>660</v>
       </c>
       <c r="B154" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>934</v>
+        <v>641</v>
       </c>
       <c r="B155" t="s">
-        <v>935</v>
+        <v>704</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>1441</v>
+        <v>934</v>
       </c>
       <c r="B156" t="s">
-        <v>1442</v>
+        <v>935</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>1360</v>
+        <v>1441</v>
       </c>
       <c r="B157" t="s">
-        <v>1361</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>1237</v>
+        <v>1360</v>
       </c>
       <c r="B158" t="s">
-        <v>1249</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>1246</v>
+        <v>1237</v>
       </c>
       <c r="B159" t="s">
-        <v>1258</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>678</v>
+        <v>1246</v>
       </c>
       <c r="B160" t="s">
-        <v>705</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>1247</v>
+        <v>678</v>
       </c>
       <c r="B161" t="s">
-        <v>1259</v>
+        <v>705</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>679</v>
+        <v>1247</v>
       </c>
       <c r="B162" t="s">
-        <v>706</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>1248</v>
+        <v>679</v>
       </c>
       <c r="B163" t="s">
-        <v>1260</v>
+        <v>706</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>680</v>
+        <v>1248</v>
       </c>
       <c r="B164" t="s">
-        <v>707</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>1238</v>
+        <v>680</v>
       </c>
       <c r="B165" t="s">
-        <v>1250</v>
+        <v>707</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>670</v>
+        <v>1238</v>
       </c>
       <c r="B166" t="s">
-        <v>708</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>1239</v>
+        <v>670</v>
       </c>
       <c r="B167" t="s">
-        <v>1251</v>
+        <v>708</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>671</v>
+        <v>1239</v>
       </c>
       <c r="B168" t="s">
-        <v>709</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>1240</v>
+        <v>671</v>
       </c>
       <c r="B169" t="s">
-        <v>1252</v>
+        <v>709</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>672</v>
+        <v>1240</v>
       </c>
       <c r="B170" t="s">
-        <v>710</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>1241</v>
+        <v>672</v>
       </c>
       <c r="B171" t="s">
-        <v>1253</v>
+        <v>710</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>673</v>
+        <v>1241</v>
       </c>
       <c r="B172" t="s">
-        <v>711</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>1242</v>
+        <v>673</v>
       </c>
       <c r="B173" t="s">
-        <v>1254</v>
+        <v>711</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>674</v>
+        <v>1242</v>
       </c>
       <c r="B174" t="s">
-        <v>712</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>1243</v>
+        <v>674</v>
       </c>
       <c r="B175" t="s">
-        <v>1255</v>
+        <v>712</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>675</v>
+        <v>1243</v>
       </c>
       <c r="B176" t="s">
-        <v>713</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>1244</v>
+        <v>675</v>
       </c>
       <c r="B177" t="s">
-        <v>1256</v>
+        <v>713</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>676</v>
+        <v>1244</v>
       </c>
       <c r="B178" t="s">
-        <v>714</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>1245</v>
+        <v>676</v>
       </c>
       <c r="B179" t="s">
-        <v>1257</v>
+        <v>714</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>677</v>
+        <v>1245</v>
       </c>
       <c r="B180" t="s">
-        <v>715</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>175</v>
+        <v>677</v>
       </c>
       <c r="B181" t="s">
-        <v>405</v>
+        <v>715</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="B182" t="s">
-        <v>1444</v>
+        <v>405</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B183" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>1319</v>
+        <v>213</v>
       </c>
       <c r="B184" t="s">
-        <v>1320</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>1354</v>
+        <v>1319</v>
       </c>
       <c r="B185" t="s">
-        <v>1355</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>1191</v>
+        <v>1354</v>
       </c>
       <c r="B186" t="s">
-        <v>406</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>149</v>
+        <v>1191</v>
       </c>
       <c r="B187" t="s">
-        <v>1194</v>
+        <v>406</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>247</v>
+        <v>149</v>
       </c>
       <c r="B188" t="s">
-        <v>407</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B189" t="s">
-        <v>1398</v>
+        <v>407</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>335</v>
+        <v>245</v>
       </c>
       <c r="B190" t="s">
-        <v>408</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>645</v>
+        <v>335</v>
       </c>
       <c r="B191" t="s">
-        <v>716</v>
+        <v>408</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>91</v>
+        <v>645</v>
       </c>
       <c r="B192" t="s">
-        <v>409</v>
+        <v>716</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>266</v>
+        <v>91</v>
       </c>
       <c r="B193" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>1476</v>
+        <v>266</v>
       </c>
       <c r="B194" t="s">
-        <v>1477</v>
+        <v>410</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>1087</v>
+        <v>1475</v>
       </c>
       <c r="B195" t="s">
-        <v>1088</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>794</v>
+        <v>1087</v>
       </c>
       <c r="B196" t="s">
-        <v>795</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>1150</v>
+        <v>794</v>
       </c>
       <c r="B197" t="s">
-        <v>1151</v>
+        <v>795</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>1337</v>
+        <v>1150</v>
       </c>
       <c r="B198" t="s">
-        <v>1338</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>295</v>
+        <v>1337</v>
       </c>
       <c r="B199" t="s">
-        <v>411</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>1077</v>
+        <v>295</v>
       </c>
       <c r="B200" t="s">
-        <v>1078</v>
+        <v>411</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="B201" t="s">
-        <v>1084</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>151</v>
+        <v>1083</v>
       </c>
       <c r="B202" t="s">
-        <v>412</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>955</v>
+        <v>151</v>
       </c>
       <c r="B203" t="s">
-        <v>956</v>
+        <v>412</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>808</v>
+        <v>955</v>
       </c>
       <c r="B204" t="s">
-        <v>809</v>
+        <v>956</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>926</v>
+        <v>808</v>
       </c>
       <c r="B205" t="s">
-        <v>927</v>
+        <v>809</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>828</v>
+        <v>926</v>
       </c>
       <c r="B206" t="s">
-        <v>829</v>
+        <v>927</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>788</v>
+        <v>828</v>
       </c>
       <c r="B207" t="s">
-        <v>789</v>
+        <v>829</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>1422</v>
+        <v>788</v>
       </c>
       <c r="B208" t="s">
-        <v>1423</v>
+        <v>789</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>749</v>
+        <v>1422</v>
       </c>
       <c r="B209" t="s">
-        <v>750</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>100</v>
+        <v>749</v>
       </c>
       <c r="B210" t="s">
-        <v>413</v>
+        <v>750</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>1035</v>
+        <v>100</v>
       </c>
       <c r="B211" t="s">
-        <v>1036</v>
+        <v>413</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>154</v>
+        <v>1035</v>
       </c>
       <c r="B212" t="s">
-        <v>414</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B213" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="B214" t="s">
-        <v>1121</v>
+        <v>415</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>1146</v>
+        <v>24</v>
       </c>
       <c r="B215" t="s">
-        <v>1147</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>1310</v>
+        <v>1146</v>
       </c>
       <c r="B216" t="s">
-        <v>1311</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>1067</v>
+        <v>1310</v>
       </c>
       <c r="B217" t="s">
-        <v>1068</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>1467</v>
+        <v>1067</v>
       </c>
       <c r="B218" t="s">
-        <v>1468</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>814</v>
+        <v>1466</v>
       </c>
       <c r="B219" t="s">
-        <v>815</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>130</v>
+        <v>814</v>
       </c>
       <c r="B220" t="s">
-        <v>416</v>
+        <v>815</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>321</v>
+        <v>130</v>
       </c>
       <c r="B221" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>1466</v>
+        <v>321</v>
       </c>
       <c r="B222" t="s">
-        <v>1426</v>
+        <v>417</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>862</v>
+        <v>1465</v>
       </c>
       <c r="B223" t="s">
-        <v>863</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>1429</v>
+        <v>862</v>
       </c>
       <c r="B224" t="s">
-        <v>1430</v>
+        <v>863</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>1465</v>
+        <v>1429</v>
       </c>
       <c r="B225" t="s">
-        <v>886</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>1299</v>
+        <v>1464</v>
       </c>
       <c r="B226" t="s">
-        <v>1300</v>
+        <v>886</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>183</v>
+        <v>1299</v>
       </c>
       <c r="B227" t="s">
-        <v>418</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>1137</v>
+        <v>183</v>
       </c>
       <c r="B228" t="s">
-        <v>1138</v>
+        <v>418</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B229" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>1420</v>
+        <v>1139</v>
       </c>
       <c r="B230" t="s">
-        <v>1421</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>1378</v>
+        <v>1420</v>
       </c>
       <c r="B231" t="s">
-        <v>1379</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>32</v>
+        <v>1378</v>
       </c>
       <c r="B232" t="s">
-        <v>419</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B233" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>1289</v>
+        <v>35</v>
       </c>
       <c r="B234" t="s">
-        <v>1290</v>
+        <v>420</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>1215</v>
+        <v>1289</v>
       </c>
       <c r="B235" t="s">
-        <v>1216</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>759</v>
+        <v>1215</v>
       </c>
       <c r="B236" t="s">
-        <v>1003</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>169</v>
+        <v>759</v>
       </c>
       <c r="B237" t="s">
-        <v>421</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B238" t="s">
         <v>421</v>
@@ -6752,599 +6764,599 @@
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>1004</v>
+        <v>170</v>
       </c>
       <c r="B239" t="s">
-        <v>760</v>
+        <v>421</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>1418</v>
+        <v>1004</v>
       </c>
       <c r="B240" t="s">
-        <v>1419</v>
+        <v>760</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>178</v>
+        <v>1418</v>
       </c>
       <c r="B241" t="s">
-        <v>422</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="B242" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>238</v>
+        <v>111</v>
       </c>
       <c r="B243" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="B244" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B245" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="B246" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>662</v>
+        <v>179</v>
       </c>
       <c r="B247" t="s">
-        <v>717</v>
+        <v>427</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>1487</v>
+        <v>662</v>
       </c>
       <c r="B248" t="s">
-        <v>1488</v>
+        <v>717</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>97</v>
+        <v>1485</v>
       </c>
       <c r="B249" t="s">
-        <v>428</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B250" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>242</v>
+        <v>110</v>
       </c>
       <c r="B251" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B252" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="B253" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>1416</v>
+        <v>177</v>
       </c>
       <c r="B254" t="s">
-        <v>1417</v>
+        <v>432</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>182</v>
+        <v>1416</v>
       </c>
       <c r="B255" t="s">
-        <v>433</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>1097</v>
+        <v>182</v>
       </c>
       <c r="B256" t="s">
-        <v>1098</v>
+        <v>433</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>971</v>
+        <v>1097</v>
       </c>
       <c r="B257" t="s">
-        <v>972</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B258" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>1180</v>
+        <v>973</v>
       </c>
       <c r="B259" t="s">
-        <v>1181</v>
+        <v>974</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>1358</v>
+        <v>1180</v>
       </c>
       <c r="B260" t="s">
-        <v>1359</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>1183</v>
+        <v>1358</v>
       </c>
       <c r="B261" t="s">
-        <v>1184</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>253</v>
+        <v>1183</v>
       </c>
       <c r="B262" t="s">
-        <v>434</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="B263" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>782</v>
+        <v>34</v>
       </c>
       <c r="B264" t="s">
-        <v>783</v>
+        <v>435</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>180</v>
+        <v>782</v>
       </c>
       <c r="B265" t="s">
-        <v>436</v>
+        <v>783</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>1330</v>
+        <v>180</v>
       </c>
       <c r="B266" t="s">
-        <v>1399</v>
+        <v>436</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B267" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>1448</v>
+        <v>1329</v>
       </c>
       <c r="B268" t="s">
-        <v>1449</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>275</v>
+        <v>1447</v>
       </c>
       <c r="B269" t="s">
-        <v>437</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>852</v>
+        <v>275</v>
       </c>
       <c r="B270" t="s">
-        <v>853</v>
+        <v>437</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>116</v>
+        <v>852</v>
       </c>
       <c r="B271" t="s">
-        <v>438</v>
+        <v>853</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="B272" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>1404</v>
+        <v>208</v>
       </c>
       <c r="B273" t="s">
-        <v>1405</v>
+        <v>439</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>1203</v>
+        <v>1404</v>
       </c>
       <c r="B274" t="s">
-        <v>1204</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>1047</v>
+        <v>1203</v>
       </c>
       <c r="B275" t="s">
-        <v>1048</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>118</v>
+        <v>1047</v>
       </c>
       <c r="B276" t="s">
-        <v>440</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>636</v>
+        <v>118</v>
       </c>
       <c r="B277" t="s">
-        <v>718</v>
+        <v>440</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>1314</v>
+        <v>636</v>
       </c>
       <c r="B278" t="s">
-        <v>1315</v>
+        <v>718</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>810</v>
+        <v>1314</v>
       </c>
       <c r="B279" t="s">
-        <v>811</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>298</v>
+        <v>810</v>
       </c>
       <c r="B280" t="s">
-        <v>441</v>
+        <v>811</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>638</v>
+        <v>298</v>
       </c>
       <c r="B281" t="s">
-        <v>719</v>
+        <v>441</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B282" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>1029</v>
+        <v>639</v>
       </c>
       <c r="B283" t="s">
-        <v>1030</v>
+        <v>720</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>90</v>
+        <v>1029</v>
       </c>
       <c r="B284" t="s">
-        <v>442</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B285" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B286" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>1063</v>
+        <v>89</v>
       </c>
       <c r="B287" t="s">
-        <v>1064</v>
+        <v>444</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>23</v>
+        <v>1063</v>
       </c>
       <c r="B288" t="s">
-        <v>1120</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>1408</v>
+        <v>23</v>
       </c>
       <c r="B289" t="s">
-        <v>1409</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>5</v>
+        <v>1408</v>
       </c>
       <c r="B290" t="s">
-        <v>6</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>1124</v>
+        <v>5</v>
       </c>
       <c r="B291" t="s">
-        <v>1125</v>
+        <v>6</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>126</v>
+        <v>1124</v>
       </c>
       <c r="B292" t="s">
-        <v>445</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>1382</v>
+        <v>126</v>
       </c>
       <c r="B293" t="s">
-        <v>1383</v>
+        <v>445</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>128</v>
+        <v>1382</v>
       </c>
       <c r="B294" t="s">
-        <v>446</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B295" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B296" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B297" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>277</v>
+        <v>119</v>
       </c>
       <c r="B298" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>1065</v>
+        <v>277</v>
       </c>
       <c r="B299" t="s">
-        <v>1066</v>
+        <v>450</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>9</v>
+        <v>1065</v>
       </c>
       <c r="B300" t="s">
-        <v>10</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="B301" t="s">
-        <v>451</v>
+        <v>10</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B302" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="B303" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="B304" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>1369</v>
+        <v>262</v>
       </c>
       <c r="B305" t="s">
-        <v>1370</v>
+        <v>454</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>77</v>
+        <v>1369</v>
       </c>
       <c r="B306" t="s">
-        <v>455</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>932</v>
+        <v>77</v>
       </c>
       <c r="B307" t="s">
-        <v>933</v>
+        <v>455</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>1154</v>
+        <v>932</v>
       </c>
       <c r="B308" t="s">
-        <v>1155</v>
+        <v>933</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>168</v>
+        <v>1154</v>
       </c>
       <c r="B309" t="s">
-        <v>456</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>1342</v>
+        <v>168</v>
       </c>
       <c r="B310" t="s">
-        <v>1343</v>
+        <v>456</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>1352</v>
+        <v>1342</v>
       </c>
       <c r="B311" t="s">
-        <v>1353</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>1395</v>
+        <v>1352</v>
       </c>
       <c r="B312" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>1348</v>
+        <v>1395</v>
       </c>
       <c r="B313" t="s">
         <v>1349</v>
@@ -7352,39 +7364,39 @@
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>167</v>
+        <v>1348</v>
       </c>
       <c r="B314" t="s">
-        <v>457</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>1344</v>
+        <v>167</v>
       </c>
       <c r="B315" t="s">
-        <v>1345</v>
+        <v>457</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>1350</v>
+        <v>1344</v>
       </c>
       <c r="B316" t="s">
-        <v>1351</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>1377</v>
+        <v>1350</v>
       </c>
       <c r="B317" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>1346</v>
+        <v>1377</v>
       </c>
       <c r="B318" t="s">
         <v>1347</v>
@@ -7392,199 +7404,199 @@
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>830</v>
+        <v>1346</v>
       </c>
       <c r="B319" t="s">
-        <v>831</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>786</v>
+        <v>830</v>
       </c>
       <c r="B320" t="s">
-        <v>787</v>
+        <v>831</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>304</v>
+        <v>786</v>
       </c>
       <c r="B321" t="s">
-        <v>458</v>
+        <v>787</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>753</v>
+        <v>304</v>
       </c>
       <c r="B322" t="s">
-        <v>754</v>
+        <v>458</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>891</v>
+        <v>753</v>
       </c>
       <c r="B323" t="s">
-        <v>892</v>
+        <v>754</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>1384</v>
+        <v>891</v>
       </c>
       <c r="B324" t="s">
-        <v>1385</v>
+        <v>892</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>647</v>
+        <v>1384</v>
       </c>
       <c r="B325" t="s">
-        <v>721</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>86</v>
+        <v>647</v>
       </c>
       <c r="B326" t="s">
-        <v>459</v>
+        <v>721</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B327" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="B328" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B329" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B330" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>251</v>
+        <v>158</v>
       </c>
       <c r="B331" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="B332" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>325</v>
+        <v>285</v>
       </c>
       <c r="B333" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>1364</v>
+        <v>325</v>
       </c>
       <c r="B334" t="s">
-        <v>1365</v>
+        <v>466</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>326</v>
+        <v>1364</v>
       </c>
       <c r="B335" t="s">
-        <v>467</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>229</v>
+        <v>326</v>
       </c>
       <c r="B336" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>55</v>
+        <v>229</v>
       </c>
       <c r="B337" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>652</v>
+        <v>55</v>
       </c>
       <c r="B338" t="s">
-        <v>722</v>
+        <v>469</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>235</v>
+        <v>652</v>
       </c>
       <c r="B339" t="s">
-        <v>470</v>
+        <v>722</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="B340" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="B341" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>761</v>
+        <v>236</v>
       </c>
       <c r="B342" t="s">
-        <v>762</v>
+        <v>472</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>1005</v>
+        <v>761</v>
       </c>
       <c r="B343" t="s">
         <v>762</v>
@@ -7592,631 +7604,631 @@
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>164</v>
+        <v>1005</v>
       </c>
       <c r="B344" t="s">
-        <v>473</v>
+        <v>762</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>1462</v>
+        <v>164</v>
       </c>
       <c r="B345" t="s">
-        <v>1460</v>
+        <v>473</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>201</v>
+        <v>1461</v>
       </c>
       <c r="B346" t="s">
-        <v>474</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B347" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>313</v>
+        <v>204</v>
       </c>
       <c r="B348" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>868</v>
+        <v>313</v>
       </c>
       <c r="B349" t="s">
-        <v>869</v>
+        <v>476</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>991</v>
+        <v>868</v>
       </c>
       <c r="B350" t="s">
-        <v>992</v>
+        <v>869</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>1317</v>
+        <v>991</v>
       </c>
       <c r="B351" t="s">
-        <v>1318</v>
+        <v>992</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>258</v>
+        <v>1317</v>
       </c>
       <c r="B352" t="s">
-        <v>477</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>977</v>
+        <v>258</v>
       </c>
       <c r="B353" t="s">
-        <v>978</v>
+        <v>477</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>1356</v>
+        <v>977</v>
       </c>
       <c r="B354" t="s">
-        <v>1357</v>
+        <v>978</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>160</v>
+        <v>1356</v>
       </c>
       <c r="B355" t="s">
-        <v>478</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>687</v>
+        <v>160</v>
       </c>
       <c r="B356" t="s">
-        <v>723</v>
+        <v>478</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>1148</v>
+        <v>687</v>
       </c>
       <c r="B357" t="s">
-        <v>1149</v>
+        <v>723</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>755</v>
+        <v>1148</v>
       </c>
       <c r="B358" t="s">
-        <v>756</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>889</v>
+        <v>755</v>
       </c>
       <c r="B359" t="s">
-        <v>890</v>
+        <v>756</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B360" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>184</v>
+        <v>887</v>
       </c>
       <c r="B361" t="s">
-        <v>479</v>
+        <v>888</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>244</v>
+        <v>184</v>
       </c>
       <c r="B362" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B363" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>1261</v>
+        <v>243</v>
       </c>
       <c r="B364" t="s">
-        <v>1266</v>
+        <v>481</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>681</v>
+        <v>1261</v>
       </c>
       <c r="B365" t="s">
-        <v>724</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>1262</v>
+        <v>681</v>
       </c>
       <c r="B366" t="s">
-        <v>1267</v>
+        <v>724</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>682</v>
+        <v>1262</v>
       </c>
       <c r="B367" t="s">
-        <v>725</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>1263</v>
+        <v>682</v>
       </c>
       <c r="B368" t="s">
-        <v>1268</v>
+        <v>725</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>683</v>
+        <v>1263</v>
       </c>
       <c r="B369" t="s">
-        <v>726</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>1264</v>
+        <v>683</v>
       </c>
       <c r="B370" t="s">
-        <v>1269</v>
+        <v>726</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>684</v>
+        <v>1264</v>
       </c>
       <c r="B371" t="s">
-        <v>727</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>1265</v>
+        <v>684</v>
       </c>
       <c r="B372" t="s">
-        <v>1270</v>
+        <v>727</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>685</v>
+        <v>1265</v>
       </c>
       <c r="B373" t="s">
-        <v>728</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>1174</v>
+        <v>685</v>
       </c>
       <c r="B374" t="s">
-        <v>1175</v>
+        <v>728</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>280</v>
+        <v>1174</v>
       </c>
       <c r="B375" t="s">
-        <v>482</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B376" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>49</v>
+        <v>281</v>
       </c>
       <c r="B377" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B378" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="B379" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>1437</v>
+        <v>136</v>
       </c>
       <c r="B380" t="s">
-        <v>1438</v>
+        <v>487</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>72</v>
+        <v>1437</v>
       </c>
       <c r="B381" t="s">
-        <v>486</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>1172</v>
+        <v>72</v>
       </c>
       <c r="B382" t="s">
-        <v>1173</v>
+        <v>486</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>221</v>
+        <v>1172</v>
       </c>
       <c r="B383" t="s">
-        <v>488</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>1176</v>
+        <v>221</v>
       </c>
       <c r="B384" t="s">
-        <v>1177</v>
+        <v>488</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>15</v>
+        <v>1176</v>
       </c>
       <c r="B385" t="s">
-        <v>16</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>1051</v>
+        <v>15</v>
       </c>
       <c r="B386" t="s">
-        <v>1052</v>
+        <v>16</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>914</v>
+        <v>1051</v>
       </c>
       <c r="B387" t="s">
-        <v>915</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>108</v>
+        <v>914</v>
       </c>
       <c r="B388" t="s">
-        <v>489</v>
+        <v>915</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>241</v>
+        <v>108</v>
       </c>
       <c r="B389" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>327</v>
+        <v>241</v>
       </c>
       <c r="B390" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>1091</v>
+        <v>327</v>
       </c>
       <c r="B391" t="s">
-        <v>1092</v>
+        <v>491</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>1043</v>
+        <v>1091</v>
       </c>
       <c r="B392" t="s">
-        <v>1044</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>121</v>
+        <v>1043</v>
       </c>
       <c r="B393" t="s">
-        <v>492</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>745</v>
+        <v>121</v>
       </c>
       <c r="B394" t="s">
-        <v>746</v>
+        <v>492</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>776</v>
+        <v>745</v>
       </c>
       <c r="B395" t="s">
-        <v>777</v>
+        <v>746</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>134</v>
+        <v>776</v>
       </c>
       <c r="B396" t="s">
-        <v>493</v>
+        <v>777</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="B397" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>1295</v>
+        <v>63</v>
       </c>
       <c r="B398" t="s">
-        <v>1296</v>
+        <v>494</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>224</v>
+        <v>1295</v>
       </c>
       <c r="B399" t="s">
-        <v>495</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>25</v>
+        <v>224</v>
       </c>
       <c r="B400" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B401" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>207</v>
+        <v>26</v>
       </c>
       <c r="B402" t="s">
-        <v>1117</v>
+        <v>497</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>954</v>
+        <v>207</v>
       </c>
       <c r="B403" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>1100</v>
+        <v>954</v>
       </c>
       <c r="B404" t="s">
-        <v>1101</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>206</v>
+        <v>1100</v>
       </c>
       <c r="B405" t="s">
-        <v>1119</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B406" t="s">
-        <v>498</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B407" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="B408" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>658</v>
+        <v>145</v>
       </c>
       <c r="B409" t="s">
-        <v>729</v>
+        <v>500</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>171</v>
+        <v>658</v>
       </c>
       <c r="B410" t="s">
-        <v>501</v>
+        <v>729</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>1079</v>
+        <v>171</v>
       </c>
       <c r="B411" t="s">
-        <v>1080</v>
+        <v>501</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>263</v>
+        <v>1079</v>
       </c>
       <c r="B412" t="s">
-        <v>502</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>1081</v>
+        <v>263</v>
       </c>
       <c r="B413" t="s">
-        <v>1082</v>
+        <v>502</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>80</v>
+        <v>1081</v>
       </c>
       <c r="B414" t="s">
-        <v>503</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B415" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>191</v>
+        <v>65</v>
       </c>
       <c r="B416" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="B417" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>192</v>
+        <v>123</v>
       </c>
       <c r="B418" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="B419" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B420" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>1182</v>
+        <v>233</v>
       </c>
       <c r="B421" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>31</v>
+        <v>1182</v>
       </c>
       <c r="B422" t="s">
         <v>510</v>
@@ -8224,375 +8236,375 @@
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B423" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>37</v>
+        <v>1491</v>
       </c>
       <c r="B424" t="s">
-        <v>512</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="B425" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>1435</v>
+        <v>37</v>
       </c>
       <c r="B426" t="s">
-        <v>1436</v>
+        <v>512</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>306</v>
+        <v>71</v>
       </c>
       <c r="B427" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>222</v>
+        <v>1435</v>
       </c>
       <c r="B428" t="s">
-        <v>515</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="B429" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>279</v>
+        <v>222</v>
       </c>
       <c r="B430" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>1386</v>
+        <v>278</v>
       </c>
       <c r="B431" t="s">
-        <v>1387</v>
+        <v>517</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>826</v>
+        <v>279</v>
       </c>
       <c r="B432" t="s">
-        <v>827</v>
+        <v>518</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>48</v>
+        <v>1386</v>
       </c>
       <c r="B433" t="s">
-        <v>519</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>146</v>
+        <v>826</v>
       </c>
       <c r="B434" t="s">
-        <v>520</v>
+        <v>827</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B435" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>1368</v>
+        <v>146</v>
       </c>
       <c r="B436" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>223</v>
+        <v>52</v>
       </c>
       <c r="B437" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>1085</v>
+        <v>1368</v>
       </c>
       <c r="B438" t="s">
-        <v>1086</v>
+        <v>516</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>1096</v>
+        <v>223</v>
       </c>
       <c r="B439" t="s">
-        <v>1099</v>
+        <v>522</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>1041</v>
+        <v>1085</v>
       </c>
       <c r="B440" t="s">
-        <v>1042</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>96</v>
+        <v>1096</v>
       </c>
       <c r="B441" t="s">
-        <v>523</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>248</v>
+        <v>1041</v>
       </c>
       <c r="B442" t="s">
-        <v>524</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>249</v>
+        <v>96</v>
       </c>
       <c r="B443" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>94</v>
+        <v>248</v>
       </c>
       <c r="B444" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>1055</v>
+        <v>249</v>
       </c>
       <c r="B445" t="s">
-        <v>1056</v>
+        <v>525</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>212</v>
+        <v>94</v>
       </c>
       <c r="B446" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>1207</v>
+        <v>1055</v>
       </c>
       <c r="B447" t="s">
-        <v>1208</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>910</v>
+        <v>212</v>
       </c>
       <c r="B448" t="s">
-        <v>911</v>
+        <v>527</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>908</v>
+        <v>1207</v>
       </c>
       <c r="B449" t="s">
-        <v>909</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B450" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>329</v>
+        <v>908</v>
       </c>
       <c r="B451" t="s">
-        <v>528</v>
+        <v>909</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>1410</v>
+        <v>912</v>
       </c>
       <c r="B452" t="s">
-        <v>1411</v>
+        <v>913</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>1412</v>
+        <v>329</v>
       </c>
       <c r="B453" t="s">
-        <v>1413</v>
+        <v>528</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>1057</v>
+        <v>1410</v>
       </c>
       <c r="B454" t="s">
-        <v>1058</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>989</v>
+        <v>1412</v>
       </c>
       <c r="B455" t="s">
-        <v>990</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>1396</v>
+        <v>1057</v>
       </c>
       <c r="B456" t="s">
-        <v>1397</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="B457" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>987</v>
+        <v>1396</v>
       </c>
       <c r="B458" t="s">
-        <v>988</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>82</v>
+        <v>985</v>
       </c>
       <c r="B459" t="s">
-        <v>529</v>
+        <v>986</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>767</v>
+        <v>987</v>
       </c>
       <c r="B460" t="s">
-        <v>768</v>
+        <v>988</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="B461" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>649</v>
+        <v>767</v>
       </c>
       <c r="B462" t="s">
-        <v>730</v>
+        <v>768</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>1433</v>
+        <v>197</v>
       </c>
       <c r="B463" t="s">
-        <v>1434</v>
+        <v>530</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>1339</v>
+        <v>649</v>
       </c>
       <c r="B464" t="s">
-        <v>1340</v>
+        <v>730</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>816</v>
+        <v>1433</v>
       </c>
       <c r="B465" t="s">
-        <v>817</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>1059</v>
+        <v>1339</v>
       </c>
       <c r="B466" t="s">
-        <v>1060</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>3</v>
+        <v>816</v>
       </c>
       <c r="B467" t="s">
-        <v>4</v>
+        <v>817</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>952</v>
+        <v>1059</v>
       </c>
       <c r="B468" t="s">
-        <v>4</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>953</v>
+        <v>3</v>
       </c>
       <c r="B469" t="s">
         <v>4</v>
@@ -8600,2249 +8612,2265 @@
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>659</v>
+        <v>952</v>
       </c>
       <c r="B470" t="s">
-        <v>731</v>
+        <v>4</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>1287</v>
+        <v>953</v>
       </c>
       <c r="B471" t="s">
-        <v>1288</v>
+        <v>4</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>765</v>
+        <v>659</v>
       </c>
       <c r="B472" t="s">
-        <v>766</v>
+        <v>731</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>85</v>
+        <v>1287</v>
       </c>
       <c r="B473" t="s">
-        <v>531</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>1053</v>
+        <v>765</v>
       </c>
       <c r="B474" t="s">
-        <v>1054</v>
+        <v>766</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>824</v>
+        <v>85</v>
       </c>
       <c r="B475" t="s">
-        <v>825</v>
+        <v>531</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>804</v>
+        <v>1053</v>
       </c>
       <c r="B476" t="s">
-        <v>805</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>187</v>
+        <v>824</v>
       </c>
       <c r="B477" t="s">
-        <v>532</v>
+        <v>825</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>822</v>
+        <v>804</v>
       </c>
       <c r="B478" t="s">
-        <v>823</v>
+        <v>805</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>928</v>
+        <v>187</v>
       </c>
       <c r="B479" t="s">
-        <v>1114</v>
+        <v>532</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>1439</v>
+        <v>822</v>
       </c>
       <c r="B480" t="s">
-        <v>1440</v>
+        <v>823</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>858</v>
+        <v>928</v>
       </c>
       <c r="B481" t="s">
-        <v>859</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>1427</v>
+        <v>1439</v>
       </c>
       <c r="B482" t="s">
-        <v>1428</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>1037</v>
+        <v>858</v>
       </c>
       <c r="B483" t="s">
-        <v>1038</v>
+        <v>859</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>793</v>
+        <v>1427</v>
       </c>
       <c r="B484" t="s">
-        <v>1115</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>792</v>
+        <v>1037</v>
       </c>
       <c r="B485" t="s">
-        <v>1116</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>1484</v>
+        <v>793</v>
       </c>
       <c r="B486" t="s">
-        <v>1485</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>1482</v>
+        <v>792</v>
       </c>
       <c r="B487" t="s">
-        <v>1483</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>13</v>
+        <v>1482</v>
       </c>
       <c r="B488" t="s">
-        <v>14</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>812</v>
+        <v>1480</v>
       </c>
       <c r="B489" t="s">
-        <v>813</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>1217</v>
+        <v>13</v>
       </c>
       <c r="B490" t="s">
-        <v>1218</v>
+        <v>14</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>186</v>
+        <v>812</v>
       </c>
       <c r="B491" t="s">
-        <v>533</v>
+        <v>813</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>806</v>
+        <v>1217</v>
       </c>
       <c r="B492" t="s">
-        <v>807</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>319</v>
+        <v>186</v>
       </c>
       <c r="B493" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>651</v>
+        <v>806</v>
       </c>
       <c r="B494" t="s">
-        <v>732</v>
+        <v>807</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>850</v>
+        <v>319</v>
       </c>
       <c r="B495" t="s">
-        <v>851</v>
+        <v>534</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B496" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>648</v>
+        <v>850</v>
       </c>
       <c r="B497" t="s">
-        <v>734</v>
+        <v>851</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>1189</v>
+        <v>653</v>
       </c>
       <c r="B498" t="s">
-        <v>1190</v>
+        <v>733</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="B499" t="s">
-        <v>535</v>
+        <v>734</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>260</v>
+        <v>1189</v>
       </c>
       <c r="B500" t="s">
-        <v>536</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B501" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>188</v>
+        <v>260</v>
       </c>
       <c r="B502" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>190</v>
+        <v>261</v>
       </c>
       <c r="B503" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>930</v>
+        <v>188</v>
       </c>
       <c r="B504" t="s">
-        <v>931</v>
+        <v>538</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>1024</v>
+        <v>190</v>
       </c>
       <c r="B505" t="s">
-        <v>1025</v>
+        <v>539</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>1205</v>
+        <v>930</v>
       </c>
       <c r="B506" t="s">
-        <v>1206</v>
+        <v>931</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>209</v>
+        <v>1024</v>
       </c>
       <c r="B507" t="s">
-        <v>540</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>1406</v>
+        <v>1205</v>
       </c>
       <c r="B508" t="s">
-        <v>1407</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>1297</v>
+        <v>209</v>
       </c>
       <c r="B509" t="s">
-        <v>1298</v>
+        <v>540</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>846</v>
+        <v>1406</v>
       </c>
       <c r="B510" t="s">
-        <v>847</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>143</v>
+        <v>1297</v>
       </c>
       <c r="B511" t="s">
-        <v>541</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>140</v>
+        <v>846</v>
       </c>
       <c r="B512" t="s">
-        <v>542</v>
+        <v>847</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>1185</v>
+        <v>143</v>
       </c>
       <c r="B513" t="s">
-        <v>1186</v>
+        <v>541</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>1285</v>
+        <v>140</v>
       </c>
       <c r="B514" t="s">
-        <v>1286</v>
+        <v>542</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>254</v>
+        <v>1185</v>
       </c>
       <c r="B515" t="s">
-        <v>543</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>330</v>
+        <v>1285</v>
       </c>
       <c r="B516" t="s">
-        <v>544</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>210</v>
+        <v>254</v>
       </c>
       <c r="B517" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>234</v>
+        <v>330</v>
       </c>
       <c r="B518" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>73</v>
+        <v>210</v>
       </c>
       <c r="B519" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>341</v>
+        <v>234</v>
       </c>
       <c r="B520" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>308</v>
+        <v>73</v>
       </c>
       <c r="B521" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>838</v>
+        <v>341</v>
       </c>
       <c r="B522" t="s">
-        <v>839</v>
+        <v>548</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>840</v>
+        <v>308</v>
       </c>
       <c r="B523" t="s">
-        <v>841</v>
+        <v>549</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>220</v>
+        <v>838</v>
       </c>
       <c r="B524" t="s">
-        <v>550</v>
+        <v>839</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>903</v>
+        <v>840</v>
       </c>
       <c r="B525" t="s">
-        <v>904</v>
+        <v>841</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>1362</v>
+        <v>220</v>
       </c>
       <c r="B526" t="s">
-        <v>1363</v>
+        <v>550</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>957</v>
+        <v>903</v>
       </c>
       <c r="B527" t="s">
-        <v>958</v>
+        <v>904</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>1170</v>
+        <v>1362</v>
       </c>
       <c r="B528" t="s">
-        <v>1171</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>227</v>
+        <v>957</v>
       </c>
       <c r="B529" t="s">
-        <v>551</v>
+        <v>958</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>333</v>
+        <v>1170</v>
       </c>
       <c r="B530" t="s">
-        <v>1143</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>965</v>
+        <v>227</v>
       </c>
       <c r="B531" t="s">
-        <v>966</v>
+        <v>551</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>773</v>
+        <v>333</v>
       </c>
       <c r="B532" t="s">
-        <v>774</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>294</v>
+        <v>965</v>
       </c>
       <c r="B533" t="s">
-        <v>552</v>
+        <v>966</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>946</v>
+        <v>773</v>
       </c>
       <c r="B534" t="s">
-        <v>947</v>
+        <v>774</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>338</v>
+        <v>294</v>
       </c>
       <c r="B535" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>775</v>
+        <v>946</v>
       </c>
       <c r="B536" t="s">
-        <v>774</v>
+        <v>947</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>1301</v>
+        <v>338</v>
       </c>
       <c r="B537" t="s">
-        <v>1302</v>
+        <v>553</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>339</v>
+        <v>775</v>
       </c>
       <c r="B538" t="s">
-        <v>554</v>
+        <v>774</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>340</v>
+        <v>1301</v>
       </c>
       <c r="B539" t="s">
-        <v>555</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>640</v>
+        <v>339</v>
       </c>
       <c r="B540" t="s">
-        <v>735</v>
+        <v>554</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>39</v>
+        <v>340</v>
       </c>
       <c r="B541" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>38</v>
+        <v>640</v>
       </c>
       <c r="B542" t="s">
-        <v>1475</v>
+        <v>735</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>342</v>
+        <v>39</v>
       </c>
       <c r="B543" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="B544" t="s">
-        <v>558</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>1414</v>
+        <v>342</v>
       </c>
       <c r="B545" t="s">
-        <v>1415</v>
+        <v>557</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>1022</v>
+        <v>107</v>
       </c>
       <c r="B546" t="s">
-        <v>1023</v>
+        <v>558</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>897</v>
+        <v>1414</v>
       </c>
       <c r="B547" t="s">
-        <v>898</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>117</v>
+        <v>1022</v>
       </c>
       <c r="B548" t="s">
-        <v>559</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>1018</v>
+        <v>897</v>
       </c>
       <c r="B549" t="s">
-        <v>1019</v>
+        <v>898</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="B550" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>99</v>
+        <v>1018</v>
       </c>
       <c r="B551" t="s">
-        <v>561</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>661</v>
+        <v>98</v>
       </c>
       <c r="B552" t="s">
-        <v>736</v>
+        <v>560</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>1094</v>
+        <v>99</v>
       </c>
       <c r="B553" t="s">
-        <v>1017</v>
+        <v>561</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>818</v>
+        <v>661</v>
       </c>
       <c r="B554" t="s">
-        <v>819</v>
+        <v>736</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>113</v>
+        <v>1094</v>
       </c>
       <c r="B555" t="s">
-        <v>562</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>884</v>
+        <v>818</v>
       </c>
       <c r="B556" t="s">
-        <v>885</v>
+        <v>819</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="B557" t="s">
-        <v>1113</v>
+        <v>562</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>290</v>
+        <v>884</v>
       </c>
       <c r="B558" t="s">
-        <v>563</v>
+        <v>885</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>299</v>
+        <v>45</v>
       </c>
       <c r="B559" t="s">
-        <v>564</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>47</v>
+        <v>290</v>
       </c>
       <c r="B560" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>842</v>
+        <v>299</v>
       </c>
       <c r="B561" t="s">
-        <v>843</v>
+        <v>564</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B562" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>866</v>
+        <v>842</v>
       </c>
       <c r="B563" t="s">
-        <v>867</v>
+        <v>843</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="B564" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>848</v>
+        <v>866</v>
       </c>
       <c r="B565" t="s">
-        <v>849</v>
+        <v>867</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="B566" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>1071</v>
+        <v>848</v>
       </c>
       <c r="B567" t="s">
-        <v>1072</v>
+        <v>849</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="B568" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>315</v>
+        <v>1071</v>
       </c>
       <c r="B569" t="s">
-        <v>570</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>29</v>
+        <v>176</v>
       </c>
       <c r="B570" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>1011</v>
+        <v>315</v>
       </c>
       <c r="B571" t="s">
-        <v>1012</v>
+        <v>570</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>1213</v>
+        <v>29</v>
       </c>
       <c r="B572" t="s">
-        <v>1214</v>
+        <v>571</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>293</v>
+        <v>1011</v>
       </c>
       <c r="B573" t="s">
-        <v>572</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>975</v>
+        <v>1213</v>
       </c>
       <c r="B574" t="s">
-        <v>976</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>1446</v>
+        <v>293</v>
       </c>
       <c r="B575" t="s">
-        <v>1447</v>
+        <v>572</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>301</v>
+        <v>975</v>
       </c>
       <c r="B576" t="s">
-        <v>573</v>
+        <v>976</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>997</v>
+        <v>1445</v>
       </c>
       <c r="B577" t="s">
-        <v>998</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>1001</v>
+        <v>301</v>
       </c>
       <c r="B578" t="s">
-        <v>1002</v>
+        <v>573</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>75</v>
+        <v>997</v>
       </c>
       <c r="B579" t="s">
-        <v>574</v>
+        <v>998</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>76</v>
+        <v>1001</v>
       </c>
       <c r="B580" t="s">
-        <v>575</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B581" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>328</v>
+        <v>76</v>
       </c>
       <c r="B582" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>1393</v>
+        <v>78</v>
       </c>
       <c r="B583" t="s">
-        <v>1394</v>
+        <v>576</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>1291</v>
+        <v>328</v>
       </c>
       <c r="B584" t="s">
-        <v>1292</v>
+        <v>577</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>747</v>
+        <v>1393</v>
       </c>
       <c r="B585" t="s">
-        <v>748</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>800</v>
+        <v>1291</v>
       </c>
       <c r="B586" t="s">
-        <v>801</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>1304</v>
+        <v>747</v>
       </c>
       <c r="B587" t="s">
-        <v>1305</v>
+        <v>748</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>135</v>
+        <v>800</v>
       </c>
       <c r="B588" t="s">
-        <v>578</v>
+        <v>801</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>1168</v>
+        <v>1304</v>
       </c>
       <c r="B589" t="s">
-        <v>1169</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>1031</v>
+        <v>135</v>
       </c>
       <c r="B590" t="s">
-        <v>1032</v>
+        <v>578</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>215</v>
+        <v>1168</v>
       </c>
       <c r="B591" t="s">
-        <v>579</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>929</v>
+        <v>1031</v>
       </c>
       <c r="B592" t="s">
-        <v>1128</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B593" t="s">
-        <v>1111</v>
+        <v>579</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>316</v>
+        <v>929</v>
       </c>
       <c r="B594" t="s">
-        <v>580</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>1073</v>
+        <v>216</v>
       </c>
       <c r="B595" t="s">
-        <v>1074</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>214</v>
+        <v>316</v>
       </c>
       <c r="B596" t="s">
-        <v>1112</v>
+        <v>580</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>993</v>
+        <v>1073</v>
       </c>
       <c r="B597" t="s">
-        <v>994</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>995</v>
+        <v>214</v>
       </c>
       <c r="B598" t="s">
-        <v>996</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>225</v>
+        <v>993</v>
       </c>
       <c r="B599" t="s">
-        <v>581</v>
+        <v>994</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>1380</v>
+        <v>995</v>
       </c>
       <c r="B600" t="s">
-        <v>1381</v>
+        <v>996</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>942</v>
+        <v>225</v>
       </c>
       <c r="B601" t="s">
-        <v>943</v>
+        <v>581</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>1089</v>
+        <v>1380</v>
       </c>
       <c r="B602" t="s">
-        <v>1090</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>1039</v>
+        <v>942</v>
       </c>
       <c r="B603" t="s">
-        <v>1040</v>
+        <v>943</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>93</v>
+        <v>1089</v>
       </c>
       <c r="B604" t="s">
-        <v>582</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>120</v>
+        <v>1039</v>
       </c>
       <c r="B605" t="s">
-        <v>583</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>778</v>
+        <v>93</v>
       </c>
       <c r="B606" t="s">
-        <v>779</v>
+        <v>582</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="B607" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>62</v>
+        <v>778</v>
       </c>
       <c r="B608" t="s">
-        <v>585</v>
+        <v>779</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>1293</v>
+        <v>133</v>
       </c>
       <c r="B609" t="s">
-        <v>1294</v>
+        <v>584</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B610" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>820</v>
+        <v>1293</v>
       </c>
       <c r="B611" t="s">
-        <v>821</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>944</v>
+        <v>66</v>
       </c>
       <c r="B612" t="s">
-        <v>945</v>
+        <v>586</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>1197</v>
+        <v>820</v>
       </c>
       <c r="B613" t="s">
-        <v>1198</v>
+        <v>821</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>1306</v>
+        <v>944</v>
       </c>
       <c r="B614" t="s">
-        <v>1307</v>
+        <v>945</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>79</v>
+        <v>1197</v>
       </c>
       <c r="B615" t="s">
-        <v>587</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>64</v>
+        <v>1306</v>
       </c>
       <c r="B616" t="s">
-        <v>588</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="B617" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>1166</v>
+        <v>64</v>
       </c>
       <c r="B618" t="s">
-        <v>1167</v>
+        <v>588</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>181</v>
+        <v>122</v>
       </c>
       <c r="B619" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>796</v>
+        <v>1166</v>
       </c>
       <c r="B620" t="s">
-        <v>797</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>1271</v>
+        <v>181</v>
       </c>
       <c r="B621" t="s">
-        <v>1276</v>
+        <v>590</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
-        <v>686</v>
+        <v>796</v>
       </c>
       <c r="B622" t="s">
-        <v>737</v>
+        <v>797</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="B623" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
-        <v>1273</v>
+        <v>686</v>
       </c>
       <c r="B624" t="s">
-        <v>1278</v>
+        <v>737</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="B625" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="B626" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>1133</v>
+        <v>1274</v>
       </c>
       <c r="B627" t="s">
-        <v>1134</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
-        <v>1131</v>
+        <v>1275</v>
       </c>
       <c r="B628" t="s">
-        <v>1132</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>284</v>
+        <v>1133</v>
       </c>
       <c r="B629" t="s">
-        <v>591</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>967</v>
+        <v>1131</v>
       </c>
       <c r="B630" t="s">
-        <v>968</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>1201</v>
+        <v>284</v>
       </c>
       <c r="B631" t="s">
-        <v>1202</v>
+        <v>591</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>836</v>
+        <v>967</v>
       </c>
       <c r="B632" t="s">
-        <v>837</v>
+        <v>968</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
-        <v>283</v>
+        <v>1201</v>
       </c>
       <c r="B633" t="s">
-        <v>592</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
-        <v>878</v>
+        <v>836</v>
       </c>
       <c r="B634" t="s">
-        <v>879</v>
+        <v>837</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
-        <v>1162</v>
+        <v>283</v>
       </c>
       <c r="B635" t="s">
-        <v>1163</v>
+        <v>592</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
-        <v>751</v>
+        <v>878</v>
       </c>
       <c r="B636" t="s">
-        <v>752</v>
+        <v>879</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
-        <v>1069</v>
+        <v>1162</v>
       </c>
       <c r="B637" t="s">
-        <v>1070</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
-        <v>67</v>
+        <v>751</v>
       </c>
       <c r="B638" t="s">
-        <v>593</v>
+        <v>752</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
-        <v>68</v>
+        <v>1069</v>
       </c>
       <c r="B639" t="s">
-        <v>594</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
-        <v>1375</v>
+        <v>67</v>
       </c>
       <c r="B640" t="s">
-        <v>1376</v>
+        <v>593</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="B641" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
-        <v>289</v>
+        <v>1375</v>
       </c>
       <c r="B642" t="s">
-        <v>596</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
-        <v>297</v>
+        <v>95</v>
       </c>
       <c r="B643" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="B644" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
-        <v>193</v>
+        <v>297</v>
       </c>
       <c r="B645" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
-        <v>1335</v>
+        <v>264</v>
       </c>
       <c r="B646" t="s">
-        <v>1336</v>
+        <v>598</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
-        <v>895</v>
+        <v>193</v>
       </c>
       <c r="B647" t="s">
-        <v>896</v>
+        <v>599</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
-        <v>44</v>
+        <v>1335</v>
       </c>
       <c r="B648" t="s">
-        <v>1110</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
-        <v>1061</v>
+        <v>895</v>
       </c>
       <c r="B649" t="s">
-        <v>1062</v>
+        <v>896</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
-        <v>323</v>
+        <v>44</v>
       </c>
       <c r="B650" t="s">
-        <v>600</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
-        <v>324</v>
+        <v>1061</v>
       </c>
       <c r="B651" t="s">
-        <v>601</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>844</v>
+        <v>323</v>
       </c>
       <c r="B652" t="s">
-        <v>845</v>
+        <v>600</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
-        <v>882</v>
+        <v>324</v>
       </c>
       <c r="B653" t="s">
-        <v>883</v>
+        <v>601</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
-        <v>1219</v>
+        <v>844</v>
       </c>
       <c r="B654" t="s">
-        <v>1220</v>
+        <v>845</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
-        <v>864</v>
+        <v>882</v>
       </c>
       <c r="B655" t="s">
-        <v>865</v>
+        <v>883</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
-        <v>33</v>
+        <v>1219</v>
       </c>
       <c r="B656" t="s">
-        <v>602</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
-        <v>36</v>
+        <v>864</v>
       </c>
       <c r="B657" t="s">
-        <v>603</v>
+        <v>865</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
-        <v>1126</v>
+        <v>33</v>
       </c>
       <c r="B658" t="s">
-        <v>1127</v>
+        <v>602</v>
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
-        <v>309</v>
+        <v>36</v>
       </c>
       <c r="B659" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
-        <v>257</v>
+        <v>1126</v>
       </c>
       <c r="B660" t="s">
-        <v>605</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B661" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="B662" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
-        <v>17</v>
+        <v>302</v>
       </c>
       <c r="B663" t="s">
-        <v>18</v>
+        <v>606</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
-        <v>650</v>
+        <v>228</v>
       </c>
       <c r="B664" t="s">
-        <v>738</v>
+        <v>607</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
-        <v>1402</v>
+        <v>17</v>
       </c>
       <c r="B665" t="s">
-        <v>1403</v>
+        <v>18</v>
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
-        <v>780</v>
+        <v>650</v>
       </c>
       <c r="B666" t="s">
-        <v>781</v>
+        <v>738</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
-        <v>142</v>
+        <v>1402</v>
       </c>
       <c r="B667" t="s">
-        <v>608</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
-        <v>1160</v>
+        <v>780</v>
       </c>
       <c r="B668" t="s">
-        <v>1161</v>
+        <v>781</v>
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
-        <v>950</v>
+        <v>142</v>
       </c>
       <c r="B669" t="s">
-        <v>951</v>
+        <v>608</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
-        <v>54</v>
+        <v>1160</v>
       </c>
       <c r="B670" t="s">
-        <v>609</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
-        <v>265</v>
+        <v>950</v>
       </c>
       <c r="B671" t="s">
-        <v>610</v>
+        <v>951</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
-        <v>970</v>
+        <v>54</v>
       </c>
       <c r="B672" t="s">
-        <v>969</v>
+        <v>609</v>
       </c>
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
-        <v>1392</v>
+        <v>265</v>
       </c>
       <c r="B673" t="s">
-        <v>969</v>
+        <v>610</v>
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
-        <v>56</v>
+        <v>970</v>
       </c>
       <c r="B674" t="s">
-        <v>611</v>
+        <v>969</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
-        <v>1199</v>
+        <v>1392</v>
       </c>
       <c r="B675" t="s">
-        <v>1200</v>
+        <v>969</v>
       </c>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
-        <v>185</v>
+        <v>56</v>
       </c>
       <c r="B676" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
-        <v>159</v>
+        <v>1199</v>
       </c>
       <c r="B677" t="s">
-        <v>613</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
-        <v>43</v>
+        <v>185</v>
       </c>
       <c r="B678" t="s">
-        <v>1328</v>
+        <v>612</v>
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
-        <v>1326</v>
+        <v>159</v>
       </c>
       <c r="B679" t="s">
-        <v>1327</v>
+        <v>613</v>
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
-        <v>1450</v>
+        <v>43</v>
       </c>
       <c r="B680" t="s">
-        <v>1452</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
-        <v>1451</v>
+        <v>1326</v>
       </c>
       <c r="B681" t="s">
-        <v>1453</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
-        <v>40</v>
+        <v>1449</v>
       </c>
       <c r="B682" t="s">
-        <v>1486</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
-        <v>1324</v>
+        <v>1450</v>
       </c>
       <c r="B683" t="s">
-        <v>1325</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
-        <v>1152</v>
+        <v>40</v>
       </c>
       <c r="B684" t="s">
-        <v>1153</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
-        <v>165</v>
+        <v>1324</v>
       </c>
       <c r="B685" t="s">
-        <v>614</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
-        <v>1281</v>
+        <v>1152</v>
       </c>
       <c r="B686" t="s">
-        <v>1282</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
-        <v>1283</v>
+        <v>165</v>
       </c>
       <c r="B687" t="s">
-        <v>1284</v>
+        <v>614</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
-        <v>1471</v>
+        <v>1281</v>
       </c>
       <c r="B688" t="s">
-        <v>1472</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
-        <v>1473</v>
+        <v>1283</v>
       </c>
       <c r="B689" t="s">
-        <v>1474</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
-        <v>12</v>
+        <v>1470</v>
       </c>
       <c r="B690" t="s">
-        <v>11</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
-        <v>250</v>
+        <v>1472</v>
       </c>
       <c r="B691" t="s">
-        <v>615</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B692" t="s">
-        <v>616</v>
+        <v>11</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
-        <v>1033</v>
+        <v>250</v>
       </c>
       <c r="B693" t="s">
-        <v>1034</v>
+        <v>615</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B694" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
-        <v>1187</v>
+        <v>1033</v>
       </c>
       <c r="B695" t="s">
-        <v>1188</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
-        <v>255</v>
+        <v>28</v>
       </c>
       <c r="B696" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
-        <v>1316</v>
+        <v>1187</v>
       </c>
       <c r="B697" t="s">
-        <v>1321</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
-        <v>790</v>
+        <v>255</v>
       </c>
       <c r="B698" t="s">
-        <v>791</v>
+        <v>618</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
-        <v>267</v>
+        <v>1316</v>
       </c>
       <c r="B699" t="s">
-        <v>619</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
-        <v>656</v>
+        <v>790</v>
       </c>
       <c r="B700" t="s">
-        <v>739</v>
+        <v>791</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
-        <v>657</v>
+        <v>267</v>
       </c>
       <c r="B701" t="s">
-        <v>740</v>
+        <v>619</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
-        <v>139</v>
+        <v>656</v>
       </c>
       <c r="B702" t="s">
-        <v>620</v>
+        <v>739</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
-        <v>7</v>
+        <v>657</v>
       </c>
       <c r="B703" t="s">
-        <v>2</v>
+        <v>740</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="B704" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
-        <v>1331</v>
+        <v>7</v>
       </c>
       <c r="B705" t="s">
-        <v>1332</v>
+        <v>2</v>
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
-        <v>1027</v>
+        <v>105</v>
       </c>
       <c r="B706" t="s">
-        <v>1109</v>
+        <v>621</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
-        <v>860</v>
+        <v>1331</v>
       </c>
       <c r="B707" t="s">
-        <v>861</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
-        <v>1431</v>
+        <v>1027</v>
       </c>
       <c r="B708" t="s">
-        <v>1432</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
-        <v>1028</v>
+        <v>860</v>
       </c>
       <c r="B709" t="s">
-        <v>1108</v>
+        <v>861</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
-        <v>292</v>
+        <v>1431</v>
       </c>
       <c r="B710" t="s">
-        <v>622</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
-        <v>8</v>
+        <v>1028</v>
       </c>
       <c r="B711" t="s">
-        <v>11</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
-        <v>334</v>
+        <v>292</v>
       </c>
       <c r="B712" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
-        <v>1373</v>
+        <v>8</v>
       </c>
       <c r="B713" t="s">
-        <v>1374</v>
+        <v>11</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
-        <v>1333</v>
+        <v>334</v>
       </c>
       <c r="B714" t="s">
-        <v>1334</v>
+        <v>623</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A715" t="s">
-        <v>331</v>
+        <v>1373</v>
       </c>
       <c r="B715" t="s">
-        <v>624</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A716" t="s">
-        <v>259</v>
+        <v>1333</v>
       </c>
       <c r="B716" t="s">
-        <v>625</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="B717" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
-        <v>854</v>
+        <v>259</v>
       </c>
       <c r="B718" t="s">
-        <v>855</v>
+        <v>625</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
-        <v>1156</v>
+        <v>318</v>
       </c>
       <c r="B719" t="s">
-        <v>1157</v>
+        <v>626</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
-        <v>268</v>
+        <v>854</v>
       </c>
       <c r="B720" t="s">
-        <v>627</v>
+        <v>855</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
-        <v>271</v>
+        <v>1156</v>
       </c>
       <c r="B721" t="s">
-        <v>1103</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B722" t="s">
-        <v>1104</v>
+        <v>627</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B723" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B724" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B725" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B726" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
-        <v>92</v>
+        <v>269</v>
       </c>
       <c r="B727" t="s">
-        <v>628</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
-        <v>200</v>
+        <v>272</v>
       </c>
       <c r="B728" t="s">
-        <v>629</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
-        <v>203</v>
+        <v>92</v>
       </c>
       <c r="B729" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A730" t="s">
-        <v>1209</v>
+        <v>200</v>
       </c>
       <c r="B730" t="s">
-        <v>1210</v>
+        <v>629</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="B731" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
-        <v>1463</v>
+        <v>1209</v>
       </c>
       <c r="B732" t="s">
-        <v>1464</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
-        <v>688</v>
+        <v>172</v>
       </c>
       <c r="B733" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="734" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
-        <v>1458</v>
-      </c>
-      <c r="B734" s="1" t="s">
-        <v>1459</v>
+        <v>1462</v>
+      </c>
+      <c r="B734" t="s">
+        <v>1463</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
-        <v>252</v>
+        <v>688</v>
       </c>
       <c r="B735" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="736" spans="1:2" x14ac:dyDescent="0.35">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
-        <v>689</v>
-      </c>
-      <c r="B736" t="s">
-        <v>742</v>
+        <v>1457</v>
+      </c>
+      <c r="B736" s="1" t="s">
+        <v>1458</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A737" t="s">
-        <v>189</v>
+        <v>252</v>
       </c>
       <c r="B737" t="s">
-        <v>1401</v>
+        <v>632</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
-        <v>983</v>
+        <v>689</v>
       </c>
       <c r="B738" t="s">
-        <v>984</v>
+        <v>742</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
-        <v>311</v>
+        <v>189</v>
       </c>
       <c r="B739" t="s">
-        <v>633</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A740" t="s">
-        <v>312</v>
+        <v>983</v>
       </c>
       <c r="B740" t="s">
-        <v>634</v>
+        <v>984</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
-        <v>1026</v>
+        <v>311</v>
       </c>
       <c r="B741" t="s">
-        <v>1457</v>
+        <v>633</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
-        <v>1456</v>
+        <v>312</v>
       </c>
       <c r="B742" t="s">
-        <v>1479</v>
+        <v>634</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
-        <v>999</v>
+        <v>1026</v>
       </c>
       <c r="B743" t="s">
-        <v>1000</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A744" t="s">
-        <v>81</v>
+        <v>1455</v>
       </c>
       <c r="B744" t="s">
-        <v>635</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A745" t="s">
-        <v>646</v>
+        <v>999</v>
       </c>
       <c r="B745" t="s">
-        <v>743</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A746" t="s">
-        <v>916</v>
+        <v>81</v>
       </c>
       <c r="B746" t="s">
-        <v>917</v>
+        <v>635</v>
       </c>
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A747" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="B747" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A748" t="s">
-        <v>963</v>
+        <v>916</v>
       </c>
       <c r="B748" t="s">
-        <v>964</v>
+        <v>917</v>
       </c>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A749" t="s">
-        <v>1144</v>
+        <v>637</v>
       </c>
       <c r="B749" t="s">
-        <v>1145</v>
+        <v>744</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A750" t="s">
+        <v>963</v>
+      </c>
+      <c r="B750" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A751" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B751" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A752" t="s">
         <v>1371</v>
       </c>
-      <c r="B750" t="s">
+      <c r="B752" t="s">
         <v>1372</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C766FC-3360-4ECC-A3F6-0090352371EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F10EF7F-B81C-488F-8D25-531C3157DE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="1493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="1499">
   <si>
     <t>trigger</t>
   </si>
@@ -1698,9 +1698,6 @@
     <t>peripancreatic</t>
   </si>
   <si>
-    <t>partially empty sella</t>
-  </si>
-  <si>
     <t>patchy fibrosis</t>
   </si>
   <si>
@@ -4452,9 +4449,6 @@
     <t>T2/STIR</t>
   </si>
   <si>
-    <t>There is fluid signal intensity noted in the pituitary fossa with flattening of the pituitary gland, suggestive of partial empty sella</t>
-  </si>
-  <si>
     <t>dishx</t>
   </si>
   <si>
@@ -4507,6 +4501,30 @@
   </si>
   <si>
     <t>T2 high signal intensity noted in bilateral mastoid air cells - suggestive of mastoiditis</t>
+  </si>
+  <si>
+    <t>There is partial fluid signal intensity noted in the pituitary fossa with mild flattening of the pituitary gland, suggestive of partial empty sella</t>
+  </si>
+  <si>
+    <t>es</t>
+  </si>
+  <si>
+    <t>empty sella</t>
+  </si>
+  <si>
+    <t>ess</t>
+  </si>
+  <si>
+    <t>There is fluid signal intensity noted in the pituitary fossa with marked flattening of the pituitary gland, suggestive of empty sella</t>
+  </si>
+  <si>
+    <t>coc</t>
+  </si>
+  <si>
+    <t>corpus callosum</t>
+  </si>
+  <si>
+    <t>partial empty sella</t>
   </si>
 </sst>
 </file>
@@ -4575,10 +4593,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B752" totalsRowShown="0">
-  <autoFilter ref="A1:B752" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B752">
-    <sortCondition ref="A1:A752"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B755" totalsRowShown="0">
+  <autoFilter ref="A1:B755" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B755">
+    <sortCondition ref="A1:A755"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4851,7 +4869,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B752"/>
+  <dimension ref="A1:B755"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -4876,50 +4894,50 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B3" t="s">
         <v>1178</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1179</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>937</v>
+      </c>
+      <c r="B4" t="s">
         <v>938</v>
-      </c>
-      <c r="B4" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>935</v>
+      </c>
+      <c r="B5" t="s">
         <v>936</v>
-      </c>
-      <c r="B5" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>939</v>
+      </c>
+      <c r="B6" t="s">
         <v>940</v>
-      </c>
-      <c r="B6" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>947</v>
+      </c>
+      <c r="B7" t="s">
         <v>948</v>
-      </c>
-      <c r="B7" t="s">
-        <v>949</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>898</v>
+      </c>
+      <c r="B8" t="s">
         <v>899</v>
-      </c>
-      <c r="B8" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -4932,18 +4950,18 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>917</v>
+      </c>
+      <c r="B10" t="s">
         <v>918</v>
-      </c>
-      <c r="B10" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>919</v>
+      </c>
+      <c r="B11" t="s">
         <v>920</v>
-      </c>
-      <c r="B11" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -4959,15 +4977,15 @@
         <v>307</v>
       </c>
       <c r="B13" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>875</v>
+      </c>
+      <c r="B14" t="s">
         <v>876</v>
-      </c>
-      <c r="B14" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -4980,58 +4998,58 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>900</v>
+      </c>
+      <c r="B16" t="s">
         <v>901</v>
-      </c>
-      <c r="B16" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>797</v>
+      </c>
+      <c r="B17" t="s">
         <v>798</v>
-      </c>
-      <c r="B17" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>978</v>
+      </c>
+      <c r="B18" t="s">
         <v>979</v>
-      </c>
-      <c r="B18" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B19" t="s">
         <v>1049</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>871</v>
+      </c>
+      <c r="B20" t="s">
         <v>872</v>
-      </c>
-      <c r="B20" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>762</v>
+      </c>
+      <c r="B21" t="s">
         <v>763</v>
-      </c>
-      <c r="B21" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B22" t="s">
         <v>1045</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
@@ -5068,26 +5086,26 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B27" t="s">
         <v>1020</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B28" t="s">
         <v>1013</v>
-      </c>
-      <c r="B28" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B29" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
@@ -5100,18 +5118,18 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B31" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B32" t="s">
         <v>1164</v>
-      </c>
-      <c r="B32" t="s">
-        <v>1165</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
@@ -5140,10 +5158,10 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B36" t="s">
         <v>1015</v>
-      </c>
-      <c r="B36" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
@@ -5172,10 +5190,10 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
+        <v>904</v>
+      </c>
+      <c r="B40" t="s">
         <v>905</v>
-      </c>
-      <c r="B40" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
@@ -5188,42 +5206,42 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B42" t="s">
         <v>1195</v>
-      </c>
-      <c r="B42" t="s">
-        <v>1196</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B43" t="s">
         <v>1192</v>
-      </c>
-      <c r="B43" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B44" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="B45" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B46" t="s">
         <v>1009</v>
-      </c>
-      <c r="B46" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
@@ -5271,15 +5289,15 @@
         <v>246</v>
       </c>
       <c r="B52" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B53" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
@@ -5292,34 +5310,34 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
+        <v>855</v>
+      </c>
+      <c r="B55" t="s">
         <v>856</v>
-      </c>
-      <c r="B55" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
+        <v>980</v>
+      </c>
+      <c r="B56" t="s">
         <v>981</v>
-      </c>
-      <c r="B56" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
+        <v>768</v>
+      </c>
+      <c r="B57" t="s">
         <v>769</v>
-      </c>
-      <c r="B57" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
+        <v>770</v>
+      </c>
+      <c r="B58" t="s">
         <v>771</v>
-      </c>
-      <c r="B58" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
@@ -5332,10 +5350,10 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B60" t="s">
         <v>1129</v>
-      </c>
-      <c r="B60" t="s">
-        <v>1130</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
@@ -5364,10 +5382,10 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
+        <v>783</v>
+      </c>
+      <c r="B64" t="s">
         <v>784</v>
-      </c>
-      <c r="B64" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
@@ -5380,10 +5398,10 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
+        <v>756</v>
+      </c>
+      <c r="B66" t="s">
         <v>757</v>
-      </c>
-      <c r="B66" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
@@ -5412,50 +5430,50 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="B70" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="B71" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
+        <v>879</v>
+      </c>
+      <c r="B72" t="s">
         <v>880</v>
-      </c>
-      <c r="B72" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B73" t="s">
         <v>1312</v>
-      </c>
-      <c r="B73" t="s">
-        <v>1313</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B74" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B75" t="s">
         <v>1388</v>
-      </c>
-      <c r="B75" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
@@ -5468,10 +5486,10 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B77" t="s">
         <v>1211</v>
-      </c>
-      <c r="B77" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
@@ -5484,138 +5502,138 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B79" t="s">
         <v>1007</v>
-      </c>
-      <c r="B79" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B80" t="s">
         <v>1221</v>
-      </c>
-      <c r="B80" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B81" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B82" t="s">
         <v>1223</v>
-      </c>
-      <c r="B82" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B83" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B84" t="s">
         <v>1225</v>
-      </c>
-      <c r="B84" t="s">
-        <v>1226</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B85" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B86" t="s">
         <v>1227</v>
-      </c>
-      <c r="B86" t="s">
-        <v>1228</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B87" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B88" t="s">
         <v>1229</v>
-      </c>
-      <c r="B88" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B89" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="B90" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B91" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="B92" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B93" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="B94" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
+        <v>869</v>
+      </c>
+      <c r="B95" t="s">
         <v>870</v>
-      </c>
-      <c r="B95" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
@@ -5684,10 +5702,10 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
+        <v>892</v>
+      </c>
+      <c r="B104" t="s">
         <v>893</v>
-      </c>
-      <c r="B104" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
@@ -5708,10 +5726,10 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B107" t="s">
         <v>1141</v>
-      </c>
-      <c r="B107" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
@@ -5743,23 +5761,23 @@
         <v>41</v>
       </c>
       <c r="B111" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B112" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B113" t="s">
         <v>1453</v>
-      </c>
-      <c r="B113" t="s">
-        <v>1454</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
@@ -5804,18 +5822,18 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B119" t="s">
         <v>1424</v>
-      </c>
-      <c r="B119" t="s">
-        <v>1425</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B120" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
@@ -5844,34 +5862,34 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B124" t="s">
         <v>1158</v>
-      </c>
-      <c r="B124" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
+        <v>873</v>
+      </c>
+      <c r="B125" t="s">
         <v>874</v>
-      </c>
-      <c r="B125" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
+        <v>801</v>
+      </c>
+      <c r="B126" t="s">
         <v>802</v>
-      </c>
-      <c r="B126" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="B127" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
@@ -5884,10 +5902,10 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="B129" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
@@ -5916,10 +5934,10 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
+        <v>960</v>
+      </c>
+      <c r="B133" t="s">
         <v>961</v>
-      </c>
-      <c r="B133" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
@@ -5932,18 +5950,18 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
+        <v>958</v>
+      </c>
+      <c r="B135" t="s">
         <v>959</v>
-      </c>
-      <c r="B135" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B136" t="s">
         <v>1390</v>
-      </c>
-      <c r="B136" t="s">
-        <v>1391</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
@@ -5975,4572 +5993,4572 @@
         <v>104</v>
       </c>
       <c r="B140" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>163</v>
+        <v>1496</v>
       </c>
       <c r="B141" t="s">
-        <v>401</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="B142" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B143" t="s">
-        <v>1323</v>
+        <v>402</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
+        <v>102</v>
+      </c>
+      <c r="B144" t="s">
         <v>1322</v>
-      </c>
-      <c r="B144" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>924</v>
+        <v>1321</v>
       </c>
       <c r="B145" t="s">
-        <v>925</v>
+        <v>403</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B146" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>162</v>
+        <v>921</v>
       </c>
       <c r="B147" t="s">
-        <v>404</v>
+        <v>922</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>1135</v>
+        <v>162</v>
       </c>
       <c r="B148" t="s">
-        <v>1136</v>
+        <v>404</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>1366</v>
+        <v>1134</v>
       </c>
       <c r="B149" t="s">
-        <v>1367</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>832</v>
+        <v>1365</v>
       </c>
       <c r="B150" t="s">
-        <v>833</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="B151" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>1309</v>
+        <v>833</v>
       </c>
       <c r="B152" t="s">
-        <v>1468</v>
+        <v>834</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>1075</v>
+        <v>1308</v>
       </c>
       <c r="B153" t="s">
-        <v>1076</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>660</v>
+        <v>1074</v>
       </c>
       <c r="B154" t="s">
-        <v>703</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>641</v>
+        <v>659</v>
       </c>
       <c r="B155" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>934</v>
+        <v>640</v>
       </c>
       <c r="B156" t="s">
-        <v>935</v>
+        <v>703</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>1441</v>
+        <v>933</v>
       </c>
       <c r="B157" t="s">
-        <v>1442</v>
+        <v>934</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>1360</v>
+        <v>1440</v>
       </c>
       <c r="B158" t="s">
-        <v>1361</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>1237</v>
+        <v>1359</v>
       </c>
       <c r="B159" t="s">
-        <v>1249</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>1246</v>
+        <v>1236</v>
       </c>
       <c r="B160" t="s">
-        <v>1258</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>678</v>
+        <v>1245</v>
       </c>
       <c r="B161" t="s">
-        <v>705</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>1247</v>
+        <v>677</v>
       </c>
       <c r="B162" t="s">
-        <v>1259</v>
+        <v>704</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>679</v>
+        <v>1246</v>
       </c>
       <c r="B163" t="s">
-        <v>706</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>1248</v>
+        <v>678</v>
       </c>
       <c r="B164" t="s">
-        <v>1260</v>
+        <v>705</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>680</v>
+        <v>1247</v>
       </c>
       <c r="B165" t="s">
-        <v>707</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>1238</v>
+        <v>679</v>
       </c>
       <c r="B166" t="s">
-        <v>1250</v>
+        <v>706</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>670</v>
+        <v>1237</v>
       </c>
       <c r="B167" t="s">
-        <v>708</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>1239</v>
+        <v>669</v>
       </c>
       <c r="B168" t="s">
-        <v>1251</v>
+        <v>707</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>671</v>
+        <v>1238</v>
       </c>
       <c r="B169" t="s">
-        <v>709</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>1240</v>
+        <v>670</v>
       </c>
       <c r="B170" t="s">
-        <v>1252</v>
+        <v>708</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>672</v>
+        <v>1239</v>
       </c>
       <c r="B171" t="s">
-        <v>710</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>1241</v>
+        <v>671</v>
       </c>
       <c r="B172" t="s">
-        <v>1253</v>
+        <v>709</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>673</v>
+        <v>1240</v>
       </c>
       <c r="B173" t="s">
-        <v>711</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>1242</v>
+        <v>672</v>
       </c>
       <c r="B174" t="s">
-        <v>1254</v>
+        <v>710</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>674</v>
+        <v>1241</v>
       </c>
       <c r="B175" t="s">
-        <v>712</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>1243</v>
+        <v>673</v>
       </c>
       <c r="B176" t="s">
-        <v>1255</v>
+        <v>711</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>675</v>
+        <v>1242</v>
       </c>
       <c r="B177" t="s">
-        <v>713</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>1244</v>
+        <v>674</v>
       </c>
       <c r="B178" t="s">
-        <v>1256</v>
+        <v>712</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>676</v>
+        <v>1243</v>
       </c>
       <c r="B179" t="s">
-        <v>714</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>1245</v>
+        <v>675</v>
       </c>
       <c r="B180" t="s">
-        <v>1257</v>
+        <v>713</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>677</v>
+        <v>1244</v>
       </c>
       <c r="B181" t="s">
-        <v>715</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>175</v>
+        <v>676</v>
       </c>
       <c r="B182" t="s">
-        <v>405</v>
+        <v>714</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="B183" t="s">
-        <v>1443</v>
+        <v>405</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B184" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>1319</v>
+        <v>213</v>
       </c>
       <c r="B185" t="s">
-        <v>1320</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>1354</v>
+        <v>1318</v>
       </c>
       <c r="B186" t="s">
-        <v>1355</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>1191</v>
+        <v>1353</v>
       </c>
       <c r="B187" t="s">
-        <v>406</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>149</v>
+        <v>1190</v>
       </c>
       <c r="B188" t="s">
-        <v>1194</v>
+        <v>406</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>247</v>
+        <v>149</v>
       </c>
       <c r="B189" t="s">
-        <v>407</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B190" t="s">
-        <v>1398</v>
+        <v>407</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>335</v>
+        <v>245</v>
       </c>
       <c r="B191" t="s">
-        <v>408</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>645</v>
+        <v>335</v>
       </c>
       <c r="B192" t="s">
-        <v>716</v>
+        <v>408</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>91</v>
+        <v>644</v>
       </c>
       <c r="B193" t="s">
-        <v>409</v>
+        <v>715</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>266</v>
+        <v>91</v>
       </c>
       <c r="B194" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>1475</v>
+        <v>266</v>
       </c>
       <c r="B195" t="s">
-        <v>1476</v>
+        <v>410</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>1087</v>
+        <v>1473</v>
       </c>
       <c r="B196" t="s">
-        <v>1088</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>794</v>
+        <v>1086</v>
       </c>
       <c r="B197" t="s">
-        <v>795</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>1150</v>
+        <v>793</v>
       </c>
       <c r="B198" t="s">
-        <v>1151</v>
+        <v>794</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>1337</v>
+        <v>1149</v>
       </c>
       <c r="B199" t="s">
-        <v>1338</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>295</v>
+        <v>1336</v>
       </c>
       <c r="B200" t="s">
-        <v>411</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>1077</v>
+        <v>295</v>
       </c>
       <c r="B201" t="s">
-        <v>1078</v>
+        <v>411</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>1083</v>
+        <v>1076</v>
       </c>
       <c r="B202" t="s">
-        <v>1084</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>151</v>
+        <v>1082</v>
       </c>
       <c r="B203" t="s">
-        <v>412</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>955</v>
+        <v>151</v>
       </c>
       <c r="B204" t="s">
-        <v>956</v>
+        <v>412</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>808</v>
+        <v>954</v>
       </c>
       <c r="B205" t="s">
-        <v>809</v>
+        <v>955</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>926</v>
+        <v>807</v>
       </c>
       <c r="B206" t="s">
-        <v>927</v>
+        <v>808</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>828</v>
+        <v>925</v>
       </c>
       <c r="B207" t="s">
-        <v>829</v>
+        <v>926</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>788</v>
+        <v>827</v>
       </c>
       <c r="B208" t="s">
-        <v>789</v>
+        <v>828</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>1422</v>
+        <v>787</v>
       </c>
       <c r="B209" t="s">
-        <v>1423</v>
+        <v>788</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>749</v>
+        <v>1421</v>
       </c>
       <c r="B210" t="s">
-        <v>750</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>100</v>
+        <v>748</v>
       </c>
       <c r="B211" t="s">
-        <v>413</v>
+        <v>749</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>1035</v>
+        <v>100</v>
       </c>
       <c r="B212" t="s">
-        <v>1036</v>
+        <v>413</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>154</v>
+        <v>1034</v>
       </c>
       <c r="B213" t="s">
-        <v>414</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B214" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="B215" t="s">
-        <v>1121</v>
+        <v>415</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>1146</v>
+        <v>24</v>
       </c>
       <c r="B216" t="s">
-        <v>1147</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>1310</v>
+        <v>1145</v>
       </c>
       <c r="B217" t="s">
-        <v>1311</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>1067</v>
+        <v>1309</v>
       </c>
       <c r="B218" t="s">
-        <v>1068</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>1466</v>
+        <v>1066</v>
       </c>
       <c r="B219" t="s">
-        <v>1467</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>814</v>
+        <v>1465</v>
       </c>
       <c r="B220" t="s">
-        <v>815</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>130</v>
+        <v>813</v>
       </c>
       <c r="B221" t="s">
-        <v>416</v>
+        <v>814</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>321</v>
+        <v>130</v>
       </c>
       <c r="B222" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>1465</v>
+        <v>321</v>
       </c>
       <c r="B223" t="s">
-        <v>1426</v>
+        <v>417</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>862</v>
+        <v>1464</v>
       </c>
       <c r="B224" t="s">
-        <v>863</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>1429</v>
+        <v>861</v>
       </c>
       <c r="B225" t="s">
-        <v>1430</v>
+        <v>862</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>1464</v>
+        <v>1428</v>
       </c>
       <c r="B226" t="s">
-        <v>886</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>1299</v>
+        <v>1463</v>
       </c>
       <c r="B227" t="s">
-        <v>1300</v>
+        <v>885</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>183</v>
+        <v>1298</v>
       </c>
       <c r="B228" t="s">
-        <v>418</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>1137</v>
+        <v>183</v>
       </c>
       <c r="B229" t="s">
-        <v>1138</v>
+        <v>418</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="B230" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>1420</v>
+        <v>1138</v>
       </c>
       <c r="B231" t="s">
-        <v>1421</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>1378</v>
+        <v>1419</v>
       </c>
       <c r="B232" t="s">
-        <v>1379</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>32</v>
+        <v>1492</v>
       </c>
       <c r="B233" t="s">
-        <v>419</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>35</v>
+        <v>1377</v>
       </c>
       <c r="B234" t="s">
-        <v>420</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>1289</v>
+        <v>1494</v>
       </c>
       <c r="B235" t="s">
-        <v>1290</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>1215</v>
+        <v>32</v>
       </c>
       <c r="B236" t="s">
-        <v>1216</v>
+        <v>419</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>759</v>
+        <v>35</v>
       </c>
       <c r="B237" t="s">
-        <v>1003</v>
+        <v>420</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>169</v>
+        <v>1288</v>
       </c>
       <c r="B238" t="s">
-        <v>421</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>170</v>
+        <v>1214</v>
       </c>
       <c r="B239" t="s">
-        <v>421</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>1004</v>
+        <v>758</v>
       </c>
       <c r="B240" t="s">
-        <v>760</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>1418</v>
+        <v>169</v>
       </c>
       <c r="B241" t="s">
-        <v>1419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B242" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>111</v>
+        <v>1003</v>
       </c>
       <c r="B243" t="s">
-        <v>423</v>
+        <v>759</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>238</v>
+        <v>1417</v>
       </c>
       <c r="B244" t="s">
-        <v>424</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="B245" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B246" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>179</v>
+        <v>238</v>
       </c>
       <c r="B247" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>662</v>
+        <v>106</v>
       </c>
       <c r="B248" t="s">
-        <v>717</v>
+        <v>425</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>1485</v>
+        <v>109</v>
       </c>
       <c r="B249" t="s">
-        <v>1486</v>
+        <v>426</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>97</v>
+        <v>179</v>
       </c>
       <c r="B250" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>110</v>
+        <v>661</v>
       </c>
       <c r="B251" t="s">
-        <v>429</v>
+        <v>716</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>242</v>
+        <v>1483</v>
       </c>
       <c r="B252" t="s">
-        <v>430</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>226</v>
+        <v>97</v>
       </c>
       <c r="B253" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>177</v>
+        <v>110</v>
       </c>
       <c r="B254" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>1416</v>
+        <v>242</v>
       </c>
       <c r="B255" t="s">
-        <v>1417</v>
+        <v>430</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>182</v>
+        <v>226</v>
       </c>
       <c r="B256" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>1097</v>
+        <v>177</v>
       </c>
       <c r="B257" t="s">
-        <v>1098</v>
+        <v>432</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>971</v>
+        <v>1415</v>
       </c>
       <c r="B258" t="s">
-        <v>972</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>973</v>
+        <v>182</v>
       </c>
       <c r="B259" t="s">
-        <v>974</v>
+        <v>433</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>1180</v>
+        <v>1096</v>
       </c>
       <c r="B260" t="s">
-        <v>1181</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>1358</v>
+        <v>970</v>
       </c>
       <c r="B261" t="s">
-        <v>1359</v>
+        <v>971</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>1183</v>
+        <v>972</v>
       </c>
       <c r="B262" t="s">
-        <v>1184</v>
+        <v>973</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>253</v>
+        <v>1179</v>
       </c>
       <c r="B263" t="s">
-        <v>434</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>34</v>
+        <v>1357</v>
       </c>
       <c r="B264" t="s">
-        <v>435</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>782</v>
+        <v>1182</v>
       </c>
       <c r="B265" t="s">
-        <v>783</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>180</v>
+        <v>253</v>
       </c>
       <c r="B266" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>1330</v>
+        <v>34</v>
       </c>
       <c r="B267" t="s">
-        <v>1399</v>
+        <v>435</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>1329</v>
+        <v>781</v>
       </c>
       <c r="B268" t="s">
-        <v>1400</v>
+        <v>782</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>1447</v>
+        <v>180</v>
       </c>
       <c r="B269" t="s">
-        <v>1448</v>
+        <v>436</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>275</v>
+        <v>1329</v>
       </c>
       <c r="B270" t="s">
-        <v>437</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>852</v>
+        <v>1328</v>
       </c>
       <c r="B271" t="s">
-        <v>853</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>116</v>
+        <v>1446</v>
       </c>
       <c r="B272" t="s">
-        <v>438</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>208</v>
+        <v>275</v>
       </c>
       <c r="B273" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>1404</v>
+        <v>851</v>
       </c>
       <c r="B274" t="s">
-        <v>1405</v>
+        <v>852</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>1203</v>
+        <v>116</v>
       </c>
       <c r="B275" t="s">
-        <v>1204</v>
+        <v>438</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>1047</v>
+        <v>208</v>
       </c>
       <c r="B276" t="s">
-        <v>1048</v>
+        <v>439</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>118</v>
+        <v>1403</v>
       </c>
       <c r="B277" t="s">
-        <v>440</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>636</v>
+        <v>1202</v>
       </c>
       <c r="B278" t="s">
-        <v>718</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>1314</v>
+        <v>1046</v>
       </c>
       <c r="B279" t="s">
-        <v>1315</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>810</v>
+        <v>118</v>
       </c>
       <c r="B280" t="s">
-        <v>811</v>
+        <v>440</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>298</v>
+        <v>635</v>
       </c>
       <c r="B281" t="s">
-        <v>441</v>
+        <v>717</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>638</v>
+        <v>1313</v>
       </c>
       <c r="B282" t="s">
-        <v>719</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>639</v>
+        <v>809</v>
       </c>
       <c r="B283" t="s">
-        <v>720</v>
+        <v>810</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>1029</v>
+        <v>298</v>
       </c>
       <c r="B284" t="s">
-        <v>1030</v>
+        <v>441</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>90</v>
+        <v>637</v>
       </c>
       <c r="B285" t="s">
-        <v>442</v>
+        <v>718</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>88</v>
+        <v>638</v>
       </c>
       <c r="B286" t="s">
-        <v>443</v>
+        <v>719</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>89</v>
+        <v>1028</v>
       </c>
       <c r="B287" t="s">
-        <v>444</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>1063</v>
+        <v>90</v>
       </c>
       <c r="B288" t="s">
-        <v>1064</v>
+        <v>442</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="B289" t="s">
-        <v>1120</v>
+        <v>443</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>1408</v>
+        <v>89</v>
       </c>
       <c r="B290" t="s">
-        <v>1409</v>
+        <v>444</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>5</v>
+        <v>1062</v>
       </c>
       <c r="B291" t="s">
-        <v>6</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>1124</v>
+        <v>23</v>
       </c>
       <c r="B292" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>126</v>
+        <v>1407</v>
       </c>
       <c r="B293" t="s">
-        <v>445</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>1382</v>
+        <v>5</v>
       </c>
       <c r="B294" t="s">
-        <v>1383</v>
+        <v>6</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>128</v>
+        <v>1123</v>
       </c>
       <c r="B295" t="s">
-        <v>446</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B296" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>132</v>
+        <v>1381</v>
       </c>
       <c r="B297" t="s">
-        <v>448</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B298" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>277</v>
+        <v>131</v>
       </c>
       <c r="B299" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>1065</v>
+        <v>132</v>
       </c>
       <c r="B300" t="s">
-        <v>1066</v>
+        <v>448</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>9</v>
+        <v>119</v>
       </c>
       <c r="B301" t="s">
-        <v>10</v>
+        <v>449</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>129</v>
+        <v>277</v>
       </c>
       <c r="B302" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>127</v>
+        <v>1064</v>
       </c>
       <c r="B303" t="s">
-        <v>452</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>173</v>
+        <v>9</v>
       </c>
       <c r="B304" t="s">
-        <v>453</v>
+        <v>10</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>262</v>
+        <v>129</v>
       </c>
       <c r="B305" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>1369</v>
+        <v>127</v>
       </c>
       <c r="B306" t="s">
-        <v>1370</v>
+        <v>452</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>77</v>
+        <v>173</v>
       </c>
       <c r="B307" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>932</v>
+        <v>262</v>
       </c>
       <c r="B308" t="s">
-        <v>933</v>
+        <v>454</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>1154</v>
+        <v>1368</v>
       </c>
       <c r="B309" t="s">
-        <v>1155</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c r="B310" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>1342</v>
+        <v>931</v>
       </c>
       <c r="B311" t="s">
-        <v>1343</v>
+        <v>932</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>1352</v>
+        <v>1153</v>
       </c>
       <c r="B312" t="s">
-        <v>1353</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>1395</v>
+        <v>168</v>
       </c>
       <c r="B313" t="s">
-        <v>1349</v>
+        <v>456</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>1348</v>
+        <v>1341</v>
       </c>
       <c r="B314" t="s">
-        <v>1349</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>167</v>
+        <v>1351</v>
       </c>
       <c r="B315" t="s">
-        <v>457</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>1344</v>
+        <v>1394</v>
       </c>
       <c r="B316" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="B317" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>1377</v>
+        <v>167</v>
       </c>
       <c r="B318" t="s">
-        <v>1347</v>
+        <v>457</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="B319" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>830</v>
+        <v>1349</v>
       </c>
       <c r="B320" t="s">
-        <v>831</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>786</v>
+        <v>1376</v>
       </c>
       <c r="B321" t="s">
-        <v>787</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>304</v>
+        <v>1345</v>
       </c>
       <c r="B322" t="s">
-        <v>458</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>753</v>
+        <v>829</v>
       </c>
       <c r="B323" t="s">
-        <v>754</v>
+        <v>830</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>891</v>
+        <v>785</v>
       </c>
       <c r="B324" t="s">
-        <v>892</v>
+        <v>786</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>1384</v>
+        <v>304</v>
       </c>
       <c r="B325" t="s">
-        <v>1385</v>
+        <v>458</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>647</v>
+        <v>752</v>
       </c>
       <c r="B326" t="s">
-        <v>721</v>
+        <v>753</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>86</v>
+        <v>890</v>
       </c>
       <c r="B327" t="s">
-        <v>459</v>
+        <v>891</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>87</v>
+        <v>1383</v>
       </c>
       <c r="B328" t="s">
-        <v>460</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>153</v>
+        <v>646</v>
       </c>
       <c r="B329" t="s">
-        <v>461</v>
+        <v>720</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>156</v>
+        <v>86</v>
       </c>
       <c r="B330" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>158</v>
+        <v>87</v>
       </c>
       <c r="B331" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>251</v>
+        <v>153</v>
       </c>
       <c r="B332" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>285</v>
+        <v>156</v>
       </c>
       <c r="B333" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>325</v>
+        <v>158</v>
       </c>
       <c r="B334" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>1364</v>
+        <v>251</v>
       </c>
       <c r="B335" t="s">
-        <v>1365</v>
+        <v>464</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>326</v>
+        <v>285</v>
       </c>
       <c r="B336" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>229</v>
+        <v>325</v>
       </c>
       <c r="B337" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>55</v>
+        <v>1363</v>
       </c>
       <c r="B338" t="s">
-        <v>469</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>652</v>
+        <v>326</v>
       </c>
       <c r="B339" t="s">
-        <v>722</v>
+        <v>467</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B340" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B341" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>236</v>
+        <v>651</v>
       </c>
       <c r="B342" t="s">
-        <v>472</v>
+        <v>721</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>761</v>
+        <v>235</v>
       </c>
       <c r="B343" t="s">
-        <v>762</v>
+        <v>470</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>1005</v>
+        <v>57</v>
       </c>
       <c r="B344" t="s">
-        <v>762</v>
+        <v>471</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>164</v>
+        <v>236</v>
       </c>
       <c r="B345" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>1461</v>
+        <v>760</v>
       </c>
       <c r="B346" t="s">
-        <v>1459</v>
+        <v>761</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>201</v>
+        <v>1004</v>
       </c>
       <c r="B347" t="s">
-        <v>474</v>
+        <v>761</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>204</v>
+        <v>164</v>
       </c>
       <c r="B348" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>313</v>
+        <v>1460</v>
       </c>
       <c r="B349" t="s">
-        <v>476</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>868</v>
+        <v>201</v>
       </c>
       <c r="B350" t="s">
-        <v>869</v>
+        <v>474</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>991</v>
+        <v>204</v>
       </c>
       <c r="B351" t="s">
-        <v>992</v>
+        <v>475</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>1317</v>
+        <v>313</v>
       </c>
       <c r="B352" t="s">
-        <v>1318</v>
+        <v>476</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>258</v>
+        <v>867</v>
       </c>
       <c r="B353" t="s">
-        <v>477</v>
+        <v>868</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>977</v>
+        <v>990</v>
       </c>
       <c r="B354" t="s">
-        <v>978</v>
+        <v>991</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>1356</v>
+        <v>1316</v>
       </c>
       <c r="B355" t="s">
-        <v>1357</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>160</v>
+        <v>258</v>
       </c>
       <c r="B356" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>687</v>
+        <v>976</v>
       </c>
       <c r="B357" t="s">
-        <v>723</v>
+        <v>977</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>1148</v>
+        <v>1355</v>
       </c>
       <c r="B358" t="s">
-        <v>1149</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>755</v>
+        <v>160</v>
       </c>
       <c r="B359" t="s">
-        <v>756</v>
+        <v>478</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>889</v>
+        <v>686</v>
       </c>
       <c r="B360" t="s">
-        <v>890</v>
+        <v>722</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>887</v>
+        <v>1147</v>
       </c>
       <c r="B361" t="s">
-        <v>888</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>184</v>
+        <v>754</v>
       </c>
       <c r="B362" t="s">
-        <v>479</v>
+        <v>755</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>244</v>
+        <v>888</v>
       </c>
       <c r="B363" t="s">
-        <v>480</v>
+        <v>889</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>243</v>
+        <v>886</v>
       </c>
       <c r="B364" t="s">
-        <v>481</v>
+        <v>887</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>1261</v>
+        <v>184</v>
       </c>
       <c r="B365" t="s">
-        <v>1266</v>
+        <v>479</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>681</v>
+        <v>244</v>
       </c>
       <c r="B366" t="s">
-        <v>724</v>
+        <v>480</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>1262</v>
+        <v>243</v>
       </c>
       <c r="B367" t="s">
-        <v>1267</v>
+        <v>481</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>682</v>
+        <v>1260</v>
       </c>
       <c r="B368" t="s">
-        <v>725</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>1263</v>
+        <v>680</v>
       </c>
       <c r="B369" t="s">
-        <v>1268</v>
+        <v>723</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>683</v>
+        <v>1261</v>
       </c>
       <c r="B370" t="s">
-        <v>726</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>1264</v>
+        <v>681</v>
       </c>
       <c r="B371" t="s">
-        <v>1269</v>
+        <v>724</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>684</v>
+        <v>1262</v>
       </c>
       <c r="B372" t="s">
-        <v>727</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>1265</v>
+        <v>682</v>
       </c>
       <c r="B373" t="s">
-        <v>1270</v>
+        <v>725</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>685</v>
+        <v>1263</v>
       </c>
       <c r="B374" t="s">
-        <v>728</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>1174</v>
+        <v>683</v>
       </c>
       <c r="B375" t="s">
-        <v>1175</v>
+        <v>726</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>280</v>
+        <v>1264</v>
       </c>
       <c r="B376" t="s">
-        <v>482</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>281</v>
+        <v>684</v>
       </c>
       <c r="B377" t="s">
-        <v>483</v>
+        <v>727</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>49</v>
+        <v>1173</v>
       </c>
       <c r="B378" t="s">
-        <v>484</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>53</v>
+        <v>280</v>
       </c>
       <c r="B379" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>136</v>
+        <v>281</v>
       </c>
       <c r="B380" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>1437</v>
+        <v>49</v>
       </c>
       <c r="B381" t="s">
-        <v>1438</v>
+        <v>484</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="B382" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>1172</v>
+        <v>136</v>
       </c>
       <c r="B383" t="s">
-        <v>1173</v>
+        <v>487</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>221</v>
+        <v>1436</v>
       </c>
       <c r="B384" t="s">
-        <v>488</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>1176</v>
+        <v>72</v>
       </c>
       <c r="B385" t="s">
-        <v>1177</v>
+        <v>486</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>15</v>
+        <v>1171</v>
       </c>
       <c r="B386" t="s">
-        <v>16</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>1051</v>
+        <v>221</v>
       </c>
       <c r="B387" t="s">
-        <v>1052</v>
+        <v>488</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>914</v>
+        <v>1175</v>
       </c>
       <c r="B388" t="s">
-        <v>915</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="B389" t="s">
-        <v>489</v>
+        <v>16</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>241</v>
+        <v>1050</v>
       </c>
       <c r="B390" t="s">
-        <v>490</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>327</v>
+        <v>913</v>
       </c>
       <c r="B391" t="s">
-        <v>491</v>
+        <v>914</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>1091</v>
+        <v>108</v>
       </c>
       <c r="B392" t="s">
-        <v>1092</v>
+        <v>489</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>1043</v>
+        <v>241</v>
       </c>
       <c r="B393" t="s">
-        <v>1044</v>
+        <v>490</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>121</v>
+        <v>327</v>
       </c>
       <c r="B394" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>745</v>
+        <v>1090</v>
       </c>
       <c r="B395" t="s">
-        <v>746</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>776</v>
+        <v>1042</v>
       </c>
       <c r="B396" t="s">
-        <v>777</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="B397" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>63</v>
+        <v>744</v>
       </c>
       <c r="B398" t="s">
-        <v>494</v>
+        <v>745</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>1295</v>
+        <v>775</v>
       </c>
       <c r="B399" t="s">
-        <v>1296</v>
+        <v>776</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>224</v>
+        <v>134</v>
       </c>
       <c r="B400" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="B401" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>26</v>
+        <v>1294</v>
       </c>
       <c r="B402" t="s">
-        <v>497</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="B403" t="s">
-        <v>1117</v>
+        <v>495</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>954</v>
+        <v>25</v>
       </c>
       <c r="B404" t="s">
-        <v>1118</v>
+        <v>496</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>1100</v>
+        <v>26</v>
       </c>
       <c r="B405" t="s">
-        <v>1101</v>
+        <v>497</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B406" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>202</v>
+        <v>953</v>
       </c>
       <c r="B407" t="s">
-        <v>498</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>205</v>
+        <v>1099</v>
       </c>
       <c r="B408" t="s">
-        <v>499</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="B409" t="s">
-        <v>500</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>658</v>
+        <v>202</v>
       </c>
       <c r="B410" t="s">
-        <v>729</v>
+        <v>498</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="B411" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>1079</v>
+        <v>145</v>
       </c>
       <c r="B412" t="s">
-        <v>1080</v>
+        <v>500</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>263</v>
+        <v>657</v>
       </c>
       <c r="B413" t="s">
-        <v>502</v>
+        <v>728</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>1081</v>
+        <v>171</v>
       </c>
       <c r="B414" t="s">
-        <v>1082</v>
+        <v>501</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>80</v>
+        <v>1078</v>
       </c>
       <c r="B415" t="s">
-        <v>503</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>65</v>
+        <v>263</v>
       </c>
       <c r="B416" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>191</v>
+        <v>1080</v>
       </c>
       <c r="B417" t="s">
-        <v>505</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="B418" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>192</v>
+        <v>65</v>
       </c>
       <c r="B419" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="B420" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>233</v>
+        <v>123</v>
       </c>
       <c r="B421" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>1182</v>
+        <v>192</v>
       </c>
       <c r="B422" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>31</v>
+        <v>231</v>
       </c>
       <c r="B423" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>1491</v>
+        <v>233</v>
       </c>
       <c r="B424" t="s">
-        <v>1492</v>
+        <v>509</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>30</v>
+        <v>1181</v>
       </c>
       <c r="B425" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B426" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>71</v>
+        <v>1489</v>
       </c>
       <c r="B427" t="s">
-        <v>513</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>1435</v>
+        <v>30</v>
       </c>
       <c r="B428" t="s">
-        <v>1436</v>
+        <v>511</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>306</v>
+        <v>37</v>
       </c>
       <c r="B429" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>222</v>
+        <v>71</v>
       </c>
       <c r="B430" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>278</v>
+        <v>1434</v>
       </c>
       <c r="B431" t="s">
-        <v>517</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="B432" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>1386</v>
+        <v>222</v>
       </c>
       <c r="B433" t="s">
-        <v>1387</v>
+        <v>515</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>826</v>
+        <v>278</v>
       </c>
       <c r="B434" t="s">
-        <v>827</v>
+        <v>517</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>48</v>
+        <v>279</v>
       </c>
       <c r="B435" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>146</v>
+        <v>1385</v>
       </c>
       <c r="B436" t="s">
-        <v>520</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>52</v>
+        <v>825</v>
       </c>
       <c r="B437" t="s">
-        <v>521</v>
+        <v>826</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>1368</v>
+        <v>48</v>
       </c>
       <c r="B438" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>223</v>
+        <v>146</v>
       </c>
       <c r="B439" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>1085</v>
+        <v>52</v>
       </c>
       <c r="B440" t="s">
-        <v>1086</v>
+        <v>521</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>1096</v>
+        <v>1367</v>
       </c>
       <c r="B441" t="s">
-        <v>1099</v>
+        <v>516</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>1041</v>
+        <v>223</v>
       </c>
       <c r="B442" t="s">
-        <v>1042</v>
+        <v>522</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>96</v>
+        <v>1084</v>
       </c>
       <c r="B443" t="s">
-        <v>523</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>248</v>
+        <v>1095</v>
       </c>
       <c r="B444" t="s">
-        <v>524</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>249</v>
+        <v>1040</v>
       </c>
       <c r="B445" t="s">
-        <v>525</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B446" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>1055</v>
+        <v>248</v>
       </c>
       <c r="B447" t="s">
-        <v>1056</v>
+        <v>524</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="B448" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>1207</v>
+        <v>94</v>
       </c>
       <c r="B449" t="s">
-        <v>1208</v>
+        <v>526</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>910</v>
+        <v>1054</v>
       </c>
       <c r="B450" t="s">
-        <v>911</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>908</v>
+        <v>212</v>
       </c>
       <c r="B451" t="s">
-        <v>909</v>
+        <v>527</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>912</v>
+        <v>1206</v>
       </c>
       <c r="B452" t="s">
-        <v>913</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>329</v>
+        <v>909</v>
       </c>
       <c r="B453" t="s">
-        <v>528</v>
+        <v>910</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>1410</v>
+        <v>907</v>
       </c>
       <c r="B454" t="s">
-        <v>1411</v>
+        <v>908</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>1412</v>
+        <v>911</v>
       </c>
       <c r="B455" t="s">
-        <v>1413</v>
+        <v>912</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>1057</v>
+        <v>329</v>
       </c>
       <c r="B456" t="s">
-        <v>1058</v>
+        <v>528</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>989</v>
+        <v>1409</v>
       </c>
       <c r="B457" t="s">
-        <v>990</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>1396</v>
+        <v>1411</v>
       </c>
       <c r="B458" t="s">
-        <v>1397</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>985</v>
+        <v>1056</v>
       </c>
       <c r="B459" t="s">
-        <v>986</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B460" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>82</v>
+        <v>1395</v>
       </c>
       <c r="B461" t="s">
-        <v>529</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>767</v>
+        <v>984</v>
       </c>
       <c r="B462" t="s">
-        <v>768</v>
+        <v>985</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>197</v>
+        <v>986</v>
       </c>
       <c r="B463" t="s">
-        <v>530</v>
+        <v>987</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>649</v>
+        <v>82</v>
       </c>
       <c r="B464" t="s">
-        <v>730</v>
+        <v>529</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>1433</v>
+        <v>766</v>
       </c>
       <c r="B465" t="s">
-        <v>1434</v>
+        <v>767</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>1339</v>
+        <v>197</v>
       </c>
       <c r="B466" t="s">
-        <v>1340</v>
+        <v>530</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>816</v>
+        <v>648</v>
       </c>
       <c r="B467" t="s">
-        <v>817</v>
+        <v>729</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>1059</v>
+        <v>1432</v>
       </c>
       <c r="B468" t="s">
-        <v>1060</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>3</v>
+        <v>1338</v>
       </c>
       <c r="B469" t="s">
-        <v>4</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>952</v>
+        <v>815</v>
       </c>
       <c r="B470" t="s">
-        <v>4</v>
+        <v>816</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>953</v>
+        <v>1058</v>
       </c>
       <c r="B471" t="s">
-        <v>4</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>659</v>
+        <v>3</v>
       </c>
       <c r="B472" t="s">
-        <v>731</v>
+        <v>4</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>1287</v>
+        <v>951</v>
       </c>
       <c r="B473" t="s">
-        <v>1288</v>
+        <v>4</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>765</v>
+        <v>952</v>
       </c>
       <c r="B474" t="s">
-        <v>766</v>
+        <v>4</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>85</v>
+        <v>658</v>
       </c>
       <c r="B475" t="s">
-        <v>531</v>
+        <v>730</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>1053</v>
+        <v>1286</v>
       </c>
       <c r="B476" t="s">
-        <v>1054</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>824</v>
+        <v>764</v>
       </c>
       <c r="B477" t="s">
-        <v>825</v>
+        <v>765</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>804</v>
+        <v>85</v>
       </c>
       <c r="B478" t="s">
-        <v>805</v>
+        <v>531</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>187</v>
+        <v>1052</v>
       </c>
       <c r="B479" t="s">
-        <v>532</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B480" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>928</v>
+        <v>803</v>
       </c>
       <c r="B481" t="s">
-        <v>1114</v>
+        <v>804</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>1439</v>
+        <v>187</v>
       </c>
       <c r="B482" t="s">
-        <v>1440</v>
+        <v>532</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>858</v>
+        <v>821</v>
       </c>
       <c r="B483" t="s">
-        <v>859</v>
+        <v>822</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>1427</v>
+        <v>927</v>
       </c>
       <c r="B484" t="s">
-        <v>1428</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>1037</v>
+        <v>1438</v>
       </c>
       <c r="B485" t="s">
-        <v>1038</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>793</v>
+        <v>857</v>
       </c>
       <c r="B486" t="s">
-        <v>1115</v>
+        <v>858</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>792</v>
+        <v>1426</v>
       </c>
       <c r="B487" t="s">
-        <v>1116</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>1482</v>
+        <v>1036</v>
       </c>
       <c r="B488" t="s">
-        <v>1483</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>1480</v>
+        <v>792</v>
       </c>
       <c r="B489" t="s">
-        <v>1481</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>13</v>
+        <v>791</v>
       </c>
       <c r="B490" t="s">
-        <v>14</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>812</v>
+        <v>1480</v>
       </c>
       <c r="B491" t="s">
-        <v>813</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>1217</v>
+        <v>1478</v>
       </c>
       <c r="B492" t="s">
-        <v>1218</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>186</v>
+        <v>13</v>
       </c>
       <c r="B493" t="s">
-        <v>533</v>
+        <v>14</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="B494" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>319</v>
+        <v>1216</v>
       </c>
       <c r="B495" t="s">
-        <v>534</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>651</v>
+        <v>186</v>
       </c>
       <c r="B496" t="s">
-        <v>732</v>
+        <v>533</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>850</v>
+        <v>805</v>
       </c>
       <c r="B497" t="s">
-        <v>851</v>
+        <v>806</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>653</v>
+        <v>319</v>
       </c>
       <c r="B498" t="s">
-        <v>733</v>
+        <v>534</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B499" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>1189</v>
+        <v>849</v>
       </c>
       <c r="B500" t="s">
-        <v>1190</v>
+        <v>850</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>256</v>
+        <v>652</v>
       </c>
       <c r="B501" t="s">
-        <v>535</v>
+        <v>732</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>260</v>
+        <v>647</v>
       </c>
       <c r="B502" t="s">
-        <v>536</v>
+        <v>733</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>261</v>
+        <v>1188</v>
       </c>
       <c r="B503" t="s">
-        <v>537</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="B504" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="B505" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>930</v>
+        <v>261</v>
       </c>
       <c r="B506" t="s">
-        <v>931</v>
+        <v>537</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>1024</v>
+        <v>188</v>
       </c>
       <c r="B507" t="s">
-        <v>1025</v>
+        <v>538</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>1205</v>
+        <v>190</v>
       </c>
       <c r="B508" t="s">
-        <v>1206</v>
+        <v>539</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>209</v>
+        <v>929</v>
       </c>
       <c r="B509" t="s">
-        <v>540</v>
+        <v>930</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>1406</v>
+        <v>1023</v>
       </c>
       <c r="B510" t="s">
-        <v>1407</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>1297</v>
+        <v>1204</v>
       </c>
       <c r="B511" t="s">
-        <v>1298</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>846</v>
+        <v>209</v>
       </c>
       <c r="B512" t="s">
-        <v>847</v>
+        <v>540</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>143</v>
+        <v>1405</v>
       </c>
       <c r="B513" t="s">
-        <v>541</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>140</v>
+        <v>1296</v>
       </c>
       <c r="B514" t="s">
-        <v>542</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>1185</v>
+        <v>845</v>
       </c>
       <c r="B515" t="s">
-        <v>1186</v>
+        <v>846</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>1285</v>
+        <v>143</v>
       </c>
       <c r="B516" t="s">
-        <v>1286</v>
+        <v>541</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>254</v>
+        <v>140</v>
       </c>
       <c r="B517" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>330</v>
+        <v>1184</v>
       </c>
       <c r="B518" t="s">
-        <v>544</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>210</v>
+        <v>1284</v>
       </c>
       <c r="B519" t="s">
-        <v>545</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="B520" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>73</v>
+        <v>330</v>
       </c>
       <c r="B521" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>341</v>
+        <v>210</v>
       </c>
       <c r="B522" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>308</v>
+        <v>234</v>
       </c>
       <c r="B523" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>838</v>
+        <v>73</v>
       </c>
       <c r="B524" t="s">
-        <v>839</v>
+        <v>547</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>840</v>
+        <v>341</v>
       </c>
       <c r="B525" t="s">
-        <v>841</v>
+        <v>548</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>220</v>
+        <v>308</v>
       </c>
       <c r="B526" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>903</v>
+        <v>837</v>
       </c>
       <c r="B527" t="s">
-        <v>904</v>
+        <v>838</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>1362</v>
+        <v>839</v>
       </c>
       <c r="B528" t="s">
-        <v>1363</v>
+        <v>840</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>957</v>
+        <v>220</v>
       </c>
       <c r="B529" t="s">
-        <v>958</v>
+        <v>550</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>1170</v>
+        <v>902</v>
       </c>
       <c r="B530" t="s">
-        <v>1171</v>
+        <v>903</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>227</v>
+        <v>1361</v>
       </c>
       <c r="B531" t="s">
-        <v>551</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>333</v>
+        <v>956</v>
       </c>
       <c r="B532" t="s">
-        <v>1143</v>
+        <v>957</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>965</v>
+        <v>1169</v>
       </c>
       <c r="B533" t="s">
-        <v>966</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>773</v>
+        <v>227</v>
       </c>
       <c r="B534" t="s">
-        <v>774</v>
+        <v>551</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>294</v>
+        <v>333</v>
       </c>
       <c r="B535" t="s">
-        <v>552</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>946</v>
+        <v>964</v>
       </c>
       <c r="B536" t="s">
-        <v>947</v>
+        <v>965</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>338</v>
+        <v>772</v>
       </c>
       <c r="B537" t="s">
-        <v>553</v>
+        <v>773</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>775</v>
+        <v>294</v>
       </c>
       <c r="B538" t="s">
-        <v>774</v>
+        <v>552</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>1301</v>
+        <v>945</v>
       </c>
       <c r="B539" t="s">
-        <v>1302</v>
+        <v>946</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B540" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>340</v>
+        <v>774</v>
       </c>
       <c r="B541" t="s">
-        <v>555</v>
+        <v>773</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>640</v>
+        <v>1300</v>
       </c>
       <c r="B542" t="s">
-        <v>735</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>39</v>
+        <v>339</v>
       </c>
       <c r="B543" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>38</v>
+        <v>340</v>
       </c>
       <c r="B544" t="s">
-        <v>1474</v>
+        <v>555</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>342</v>
+        <v>639</v>
       </c>
       <c r="B545" t="s">
-        <v>557</v>
+        <v>734</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="B546" t="s">
-        <v>558</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>1414</v>
+        <v>38</v>
       </c>
       <c r="B547" t="s">
-        <v>1415</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>1022</v>
+        <v>342</v>
       </c>
       <c r="B548" t="s">
-        <v>1023</v>
+        <v>556</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>897</v>
+        <v>107</v>
       </c>
       <c r="B549" t="s">
-        <v>898</v>
+        <v>557</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>117</v>
+        <v>1413</v>
       </c>
       <c r="B550" t="s">
-        <v>559</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="B551" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>98</v>
+        <v>896</v>
       </c>
       <c r="B552" t="s">
-        <v>560</v>
+        <v>897</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="B553" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>661</v>
+        <v>1017</v>
       </c>
       <c r="B554" t="s">
-        <v>736</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>1094</v>
+        <v>98</v>
       </c>
       <c r="B555" t="s">
-        <v>1017</v>
+        <v>559</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>818</v>
+        <v>99</v>
       </c>
       <c r="B556" t="s">
-        <v>819</v>
+        <v>560</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>113</v>
+        <v>660</v>
       </c>
       <c r="B557" t="s">
-        <v>562</v>
+        <v>735</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>884</v>
+        <v>1093</v>
       </c>
       <c r="B558" t="s">
-        <v>885</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>45</v>
+        <v>817</v>
       </c>
       <c r="B559" t="s">
-        <v>1113</v>
+        <v>818</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>290</v>
+        <v>113</v>
       </c>
       <c r="B560" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>299</v>
+        <v>883</v>
       </c>
       <c r="B561" t="s">
-        <v>564</v>
+        <v>884</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B562" t="s">
-        <v>565</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>842</v>
+        <v>290</v>
       </c>
       <c r="B563" t="s">
-        <v>843</v>
+        <v>562</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>51</v>
+        <v>299</v>
       </c>
       <c r="B564" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>866</v>
+        <v>47</v>
       </c>
       <c r="B565" t="s">
-        <v>867</v>
+        <v>564</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>114</v>
+        <v>841</v>
       </c>
       <c r="B566" t="s">
-        <v>567</v>
+        <v>842</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>848</v>
+        <v>51</v>
       </c>
       <c r="B567" t="s">
-        <v>849</v>
+        <v>565</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>144</v>
+        <v>865</v>
       </c>
       <c r="B568" t="s">
-        <v>568</v>
+        <v>866</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>1071</v>
+        <v>114</v>
       </c>
       <c r="B569" t="s">
-        <v>1072</v>
+        <v>566</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>176</v>
+        <v>847</v>
       </c>
       <c r="B570" t="s">
-        <v>569</v>
+        <v>848</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>315</v>
+        <v>144</v>
       </c>
       <c r="B571" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>29</v>
+        <v>1070</v>
       </c>
       <c r="B572" t="s">
-        <v>571</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>1011</v>
+        <v>176</v>
       </c>
       <c r="B573" t="s">
-        <v>1012</v>
+        <v>568</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>1213</v>
+        <v>315</v>
       </c>
       <c r="B574" t="s">
-        <v>1214</v>
+        <v>569</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>293</v>
+        <v>29</v>
       </c>
       <c r="B575" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>975</v>
+        <v>1010</v>
       </c>
       <c r="B576" t="s">
-        <v>976</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>1445</v>
+        <v>1212</v>
       </c>
       <c r="B577" t="s">
-        <v>1446</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B578" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>997</v>
+        <v>974</v>
       </c>
       <c r="B579" t="s">
-        <v>998</v>
+        <v>975</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>1001</v>
+        <v>1444</v>
       </c>
       <c r="B580" t="s">
-        <v>1002</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>75</v>
+        <v>301</v>
       </c>
       <c r="B581" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>76</v>
+        <v>996</v>
       </c>
       <c r="B582" t="s">
-        <v>575</v>
+        <v>997</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>78</v>
+        <v>1000</v>
       </c>
       <c r="B583" t="s">
-        <v>576</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>328</v>
+        <v>75</v>
       </c>
       <c r="B584" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>1393</v>
+        <v>76</v>
       </c>
       <c r="B585" t="s">
-        <v>1394</v>
+        <v>574</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>1291</v>
+        <v>78</v>
       </c>
       <c r="B586" t="s">
-        <v>1292</v>
+        <v>575</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>747</v>
+        <v>328</v>
       </c>
       <c r="B587" t="s">
-        <v>748</v>
+        <v>576</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>800</v>
+        <v>1392</v>
       </c>
       <c r="B588" t="s">
-        <v>801</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>1304</v>
+        <v>1290</v>
       </c>
       <c r="B589" t="s">
-        <v>1305</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>135</v>
+        <v>746</v>
       </c>
       <c r="B590" t="s">
-        <v>578</v>
+        <v>747</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>1168</v>
+        <v>799</v>
       </c>
       <c r="B591" t="s">
-        <v>1169</v>
+        <v>800</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>1031</v>
+        <v>1303</v>
       </c>
       <c r="B592" t="s">
-        <v>1032</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>215</v>
+        <v>135</v>
       </c>
       <c r="B593" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>929</v>
+        <v>1167</v>
       </c>
       <c r="B594" t="s">
-        <v>1128</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>216</v>
+        <v>1030</v>
       </c>
       <c r="B595" t="s">
-        <v>1111</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>316</v>
+        <v>215</v>
       </c>
       <c r="B596" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>1073</v>
+        <v>928</v>
       </c>
       <c r="B597" t="s">
-        <v>1074</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B598" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>993</v>
+        <v>316</v>
       </c>
       <c r="B599" t="s">
-        <v>994</v>
+        <v>579</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>995</v>
+        <v>1072</v>
       </c>
       <c r="B600" t="s">
-        <v>996</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="B601" t="s">
-        <v>581</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>1380</v>
+        <v>992</v>
       </c>
       <c r="B602" t="s">
-        <v>1381</v>
+        <v>993</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>942</v>
+        <v>994</v>
       </c>
       <c r="B603" t="s">
-        <v>943</v>
+        <v>995</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>1089</v>
+        <v>225</v>
       </c>
       <c r="B604" t="s">
-        <v>1090</v>
+        <v>580</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>1039</v>
+        <v>1379</v>
       </c>
       <c r="B605" t="s">
-        <v>1040</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>93</v>
+        <v>941</v>
       </c>
       <c r="B606" t="s">
-        <v>582</v>
+        <v>942</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>120</v>
+        <v>1088</v>
       </c>
       <c r="B607" t="s">
-        <v>583</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>778</v>
+        <v>1038</v>
       </c>
       <c r="B608" t="s">
-        <v>779</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="B609" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="B610" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>1293</v>
+        <v>777</v>
       </c>
       <c r="B611" t="s">
-        <v>1294</v>
+        <v>778</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="B612" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>820</v>
+        <v>62</v>
       </c>
       <c r="B613" t="s">
-        <v>821</v>
+        <v>584</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>944</v>
+        <v>1292</v>
       </c>
       <c r="B614" t="s">
-        <v>945</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>1197</v>
+        <v>66</v>
       </c>
       <c r="B615" t="s">
-        <v>1198</v>
+        <v>585</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>1306</v>
+        <v>819</v>
       </c>
       <c r="B616" t="s">
-        <v>1307</v>
+        <v>820</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>79</v>
+        <v>943</v>
       </c>
       <c r="B617" t="s">
-        <v>587</v>
+        <v>944</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>64</v>
+        <v>1196</v>
       </c>
       <c r="B618" t="s">
-        <v>588</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>122</v>
+        <v>1305</v>
       </c>
       <c r="B619" t="s">
-        <v>589</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>1166</v>
+        <v>79</v>
       </c>
       <c r="B620" t="s">
-        <v>1167</v>
+        <v>586</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>181</v>
+        <v>64</v>
       </c>
       <c r="B621" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
-        <v>796</v>
+        <v>122</v>
       </c>
       <c r="B622" t="s">
-        <v>797</v>
+        <v>588</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
-        <v>1271</v>
+        <v>1165</v>
       </c>
       <c r="B623" t="s">
-        <v>1276</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
-        <v>686</v>
+        <v>181</v>
       </c>
       <c r="B624" t="s">
-        <v>737</v>
+        <v>589</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
-        <v>1272</v>
+        <v>795</v>
       </c>
       <c r="B625" t="s">
-        <v>1277</v>
+        <v>796</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="B626" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>1274</v>
+        <v>685</v>
       </c>
       <c r="B627" t="s">
-        <v>1279</v>
+        <v>736</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="B628" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>1133</v>
+        <v>1272</v>
       </c>
       <c r="B629" t="s">
-        <v>1134</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>1131</v>
+        <v>1273</v>
       </c>
       <c r="B630" t="s">
-        <v>1132</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>284</v>
+        <v>1274</v>
       </c>
       <c r="B631" t="s">
-        <v>591</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>967</v>
+        <v>1132</v>
       </c>
       <c r="B632" t="s">
-        <v>968</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
-        <v>1201</v>
+        <v>1130</v>
       </c>
       <c r="B633" t="s">
-        <v>1202</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
-        <v>836</v>
+        <v>284</v>
       </c>
       <c r="B634" t="s">
-        <v>837</v>
+        <v>590</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
-        <v>283</v>
+        <v>966</v>
       </c>
       <c r="B635" t="s">
-        <v>592</v>
+        <v>967</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
-        <v>878</v>
+        <v>1200</v>
       </c>
       <c r="B636" t="s">
-        <v>879</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
-        <v>1162</v>
+        <v>835</v>
       </c>
       <c r="B637" t="s">
-        <v>1163</v>
+        <v>836</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
-        <v>751</v>
+        <v>283</v>
       </c>
       <c r="B638" t="s">
-        <v>752</v>
+        <v>591</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
-        <v>1069</v>
+        <v>877</v>
       </c>
       <c r="B639" t="s">
-        <v>1070</v>
+        <v>878</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
-        <v>67</v>
+        <v>1161</v>
       </c>
       <c r="B640" t="s">
-        <v>593</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>68</v>
+        <v>750</v>
       </c>
       <c r="B641" t="s">
-        <v>594</v>
+        <v>751</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
-        <v>1375</v>
+        <v>1068</v>
       </c>
       <c r="B642" t="s">
-        <v>1376</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="B643" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
-        <v>289</v>
+        <v>68</v>
       </c>
       <c r="B644" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
-        <v>297</v>
+        <v>1374</v>
       </c>
       <c r="B645" t="s">
-        <v>597</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
-        <v>264</v>
+        <v>95</v>
       </c>
       <c r="B646" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
-        <v>193</v>
+        <v>289</v>
       </c>
       <c r="B647" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
-        <v>1335</v>
+        <v>297</v>
       </c>
       <c r="B648" t="s">
-        <v>1336</v>
+        <v>596</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
-        <v>895</v>
+        <v>264</v>
       </c>
       <c r="B649" t="s">
-        <v>896</v>
+        <v>597</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
-        <v>44</v>
+        <v>193</v>
       </c>
       <c r="B650" t="s">
-        <v>1110</v>
+        <v>598</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
-        <v>1061</v>
+        <v>1334</v>
       </c>
       <c r="B651" t="s">
-        <v>1062</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>323</v>
+        <v>894</v>
       </c>
       <c r="B652" t="s">
-        <v>600</v>
+        <v>895</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
-        <v>324</v>
+        <v>44</v>
       </c>
       <c r="B653" t="s">
-        <v>601</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
-        <v>844</v>
+        <v>1060</v>
       </c>
       <c r="B654" t="s">
-        <v>845</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
-        <v>882</v>
+        <v>323</v>
       </c>
       <c r="B655" t="s">
-        <v>883</v>
+        <v>599</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
-        <v>1219</v>
+        <v>324</v>
       </c>
       <c r="B656" t="s">
-        <v>1220</v>
+        <v>600</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
-        <v>864</v>
+        <v>843</v>
       </c>
       <c r="B657" t="s">
-        <v>865</v>
+        <v>844</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
-        <v>33</v>
+        <v>881</v>
       </c>
       <c r="B658" t="s">
-        <v>602</v>
+        <v>882</v>
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
-        <v>36</v>
+        <v>1218</v>
       </c>
       <c r="B659" t="s">
-        <v>603</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
-        <v>1126</v>
+        <v>863</v>
       </c>
       <c r="B660" t="s">
-        <v>1127</v>
+        <v>864</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
-        <v>309</v>
+        <v>33</v>
       </c>
       <c r="B661" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
-        <v>257</v>
+        <v>36</v>
       </c>
       <c r="B662" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
-        <v>302</v>
+        <v>1125</v>
       </c>
       <c r="B663" t="s">
-        <v>606</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
-        <v>228</v>
+        <v>309</v>
       </c>
       <c r="B664" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
-        <v>17</v>
+        <v>257</v>
       </c>
       <c r="B665" t="s">
-        <v>18</v>
+        <v>604</v>
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
-        <v>650</v>
+        <v>302</v>
       </c>
       <c r="B666" t="s">
-        <v>738</v>
+        <v>605</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
-        <v>1402</v>
+        <v>228</v>
       </c>
       <c r="B667" t="s">
-        <v>1403</v>
+        <v>606</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
-        <v>780</v>
+        <v>17</v>
       </c>
       <c r="B668" t="s">
-        <v>781</v>
+        <v>18</v>
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
-        <v>142</v>
+        <v>649</v>
       </c>
       <c r="B669" t="s">
-        <v>608</v>
+        <v>737</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
-        <v>1160</v>
+        <v>1401</v>
       </c>
       <c r="B670" t="s">
-        <v>1161</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
-        <v>950</v>
+        <v>779</v>
       </c>
       <c r="B671" t="s">
-        <v>951</v>
+        <v>780</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="B672" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
-        <v>265</v>
+        <v>1159</v>
       </c>
       <c r="B673" t="s">
-        <v>610</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
-        <v>970</v>
+        <v>949</v>
       </c>
       <c r="B674" t="s">
-        <v>969</v>
+        <v>950</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
-        <v>1392</v>
+        <v>54</v>
       </c>
       <c r="B675" t="s">
-        <v>969</v>
+        <v>608</v>
       </c>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
-        <v>56</v>
+        <v>265</v>
       </c>
       <c r="B676" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
-        <v>1199</v>
+        <v>969</v>
       </c>
       <c r="B677" t="s">
-        <v>1200</v>
+        <v>968</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
-        <v>185</v>
+        <v>1391</v>
       </c>
       <c r="B678" t="s">
-        <v>612</v>
+        <v>968</v>
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="B679" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
-        <v>43</v>
+        <v>1198</v>
       </c>
       <c r="B680" t="s">
-        <v>1328</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
-        <v>1326</v>
+        <v>185</v>
       </c>
       <c r="B681" t="s">
-        <v>1327</v>
+        <v>611</v>
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
-        <v>1449</v>
+        <v>159</v>
       </c>
       <c r="B682" t="s">
-        <v>1451</v>
+        <v>612</v>
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
-        <v>1450</v>
+        <v>43</v>
       </c>
       <c r="B683" t="s">
-        <v>1452</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
-        <v>40</v>
+        <v>1325</v>
       </c>
       <c r="B684" t="s">
-        <v>1484</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
-        <v>1324</v>
+        <v>1448</v>
       </c>
       <c r="B685" t="s">
-        <v>1325</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
-        <v>1152</v>
+        <v>1449</v>
       </c>
       <c r="B686" t="s">
-        <v>1153</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
-        <v>165</v>
+        <v>40</v>
       </c>
       <c r="B687" t="s">
-        <v>614</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
-        <v>1281</v>
+        <v>1323</v>
       </c>
       <c r="B688" t="s">
-        <v>1282</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
-        <v>1283</v>
+        <v>1151</v>
       </c>
       <c r="B689" t="s">
-        <v>1284</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
-        <v>1470</v>
+        <v>165</v>
       </c>
       <c r="B690" t="s">
-        <v>1471</v>
+        <v>613</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
-        <v>1472</v>
+        <v>1280</v>
       </c>
       <c r="B691" t="s">
-        <v>1473</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
-        <v>12</v>
+        <v>1282</v>
       </c>
       <c r="B692" t="s">
-        <v>11</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
-        <v>250</v>
+        <v>1469</v>
       </c>
       <c r="B693" t="s">
-        <v>615</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
-        <v>27</v>
+        <v>1471</v>
       </c>
       <c r="B694" t="s">
-        <v>616</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
-        <v>1033</v>
+        <v>12</v>
       </c>
       <c r="B695" t="s">
-        <v>1034</v>
+        <v>11</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
-        <v>28</v>
+        <v>250</v>
       </c>
       <c r="B696" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
-        <v>1187</v>
+        <v>27</v>
       </c>
       <c r="B697" t="s">
-        <v>1188</v>
+        <v>615</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
-        <v>255</v>
+        <v>1032</v>
       </c>
       <c r="B698" t="s">
-        <v>618</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
-        <v>1316</v>
+        <v>28</v>
       </c>
       <c r="B699" t="s">
-        <v>1321</v>
+        <v>616</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
-        <v>790</v>
+        <v>1186</v>
       </c>
       <c r="B700" t="s">
-        <v>791</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="B701" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
-        <v>656</v>
+        <v>1315</v>
       </c>
       <c r="B702" t="s">
-        <v>739</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
-        <v>657</v>
+        <v>789</v>
       </c>
       <c r="B703" t="s">
-        <v>740</v>
+        <v>790</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
-        <v>139</v>
+        <v>267</v>
       </c>
       <c r="B704" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
-        <v>7</v>
+        <v>655</v>
       </c>
       <c r="B705" t="s">
-        <v>2</v>
+        <v>738</v>
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
-        <v>105</v>
+        <v>656</v>
       </c>
       <c r="B706" t="s">
-        <v>621</v>
+        <v>739</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
-        <v>1331</v>
+        <v>139</v>
       </c>
       <c r="B707" t="s">
-        <v>1332</v>
+        <v>619</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
-        <v>1027</v>
+        <v>7</v>
       </c>
       <c r="B708" t="s">
-        <v>1109</v>
+        <v>2</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
-        <v>860</v>
+        <v>105</v>
       </c>
       <c r="B709" t="s">
-        <v>861</v>
+        <v>620</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
-        <v>1431</v>
+        <v>1330</v>
       </c>
       <c r="B710" t="s">
-        <v>1432</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B711" t="s">
         <v>1108</v>
@@ -10548,330 +10566,354 @@
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
-        <v>292</v>
+        <v>859</v>
       </c>
       <c r="B712" t="s">
-        <v>622</v>
+        <v>860</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
-        <v>8</v>
+        <v>1430</v>
       </c>
       <c r="B713" t="s">
-        <v>11</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
-        <v>334</v>
+        <v>1027</v>
       </c>
       <c r="B714" t="s">
-        <v>623</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A715" t="s">
-        <v>1373</v>
+        <v>292</v>
       </c>
       <c r="B715" t="s">
-        <v>1374</v>
+        <v>621</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A716" t="s">
-        <v>1333</v>
+        <v>8</v>
       </c>
       <c r="B716" t="s">
-        <v>1334</v>
+        <v>11</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B717" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
-        <v>259</v>
+        <v>1372</v>
       </c>
       <c r="B718" t="s">
-        <v>625</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
-        <v>318</v>
+        <v>1332</v>
       </c>
       <c r="B719" t="s">
-        <v>626</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
-        <v>854</v>
+        <v>331</v>
       </c>
       <c r="B720" t="s">
-        <v>855</v>
+        <v>623</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
-        <v>1156</v>
+        <v>259</v>
       </c>
       <c r="B721" t="s">
-        <v>1157</v>
+        <v>624</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
-        <v>268</v>
+        <v>318</v>
       </c>
       <c r="B722" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
-        <v>271</v>
+        <v>853</v>
       </c>
       <c r="B723" t="s">
-        <v>1103</v>
+        <v>854</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
-        <v>274</v>
+        <v>1155</v>
       </c>
       <c r="B724" t="s">
-        <v>1104</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B725" t="s">
-        <v>1105</v>
+        <v>626</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B726" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B727" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B728" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
-        <v>92</v>
+        <v>273</v>
       </c>
       <c r="B729" t="s">
-        <v>628</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A730" t="s">
-        <v>200</v>
+        <v>269</v>
       </c>
       <c r="B730" t="s">
-        <v>629</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
-        <v>203</v>
+        <v>272</v>
       </c>
       <c r="B731" t="s">
-        <v>630</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
-        <v>1209</v>
+        <v>92</v>
       </c>
       <c r="B732" t="s">
-        <v>1210</v>
+        <v>627</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="B733" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
-        <v>1462</v>
+        <v>203</v>
       </c>
       <c r="B734" t="s">
-        <v>1463</v>
+        <v>629</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
-        <v>688</v>
+        <v>1208</v>
       </c>
       <c r="B735" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="736" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
-        <v>1457</v>
-      </c>
-      <c r="B736" s="1" t="s">
-        <v>1458</v>
+        <v>172</v>
+      </c>
+      <c r="B736" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A737" t="s">
-        <v>252</v>
+        <v>1461</v>
       </c>
       <c r="B737" t="s">
-        <v>632</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B738" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="739" spans="1:2" x14ac:dyDescent="0.35">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
-        <v>189</v>
-      </c>
-      <c r="B739" t="s">
-        <v>1401</v>
+        <v>1456</v>
+      </c>
+      <c r="B739" s="1" t="s">
+        <v>1457</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A740" t="s">
-        <v>983</v>
+        <v>252</v>
       </c>
       <c r="B740" t="s">
-        <v>984</v>
+        <v>631</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
-        <v>311</v>
+        <v>688</v>
       </c>
       <c r="B741" t="s">
-        <v>633</v>
+        <v>741</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
-        <v>312</v>
+        <v>189</v>
       </c>
       <c r="B742" t="s">
-        <v>634</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
-        <v>1026</v>
+        <v>982</v>
       </c>
       <c r="B743" t="s">
-        <v>1456</v>
+        <v>983</v>
       </c>
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A744" t="s">
-        <v>1455</v>
+        <v>311</v>
       </c>
       <c r="B744" t="s">
-        <v>1477</v>
+        <v>632</v>
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A745" t="s">
-        <v>999</v>
+        <v>312</v>
       </c>
       <c r="B745" t="s">
-        <v>1000</v>
+        <v>633</v>
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A746" t="s">
-        <v>81</v>
+        <v>1025</v>
       </c>
       <c r="B746" t="s">
-        <v>635</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A747" t="s">
-        <v>646</v>
+        <v>1454</v>
       </c>
       <c r="B747" t="s">
-        <v>743</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A748" t="s">
-        <v>916</v>
+        <v>998</v>
       </c>
       <c r="B748" t="s">
-        <v>917</v>
+        <v>999</v>
       </c>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A749" t="s">
-        <v>637</v>
+        <v>81</v>
       </c>
       <c r="B749" t="s">
-        <v>744</v>
+        <v>634</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A750" t="s">
-        <v>963</v>
+        <v>645</v>
       </c>
       <c r="B750" t="s">
-        <v>964</v>
+        <v>742</v>
       </c>
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A751" t="s">
-        <v>1144</v>
+        <v>915</v>
       </c>
       <c r="B751" t="s">
-        <v>1145</v>
+        <v>916</v>
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A752" t="s">
+        <v>636</v>
+      </c>
+      <c r="B752" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A753" t="s">
+        <v>962</v>
+      </c>
+      <c r="B753" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A754" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B754" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A755" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B755" t="s">
         <v>1371</v>
-      </c>
-      <c r="B752" t="s">
-        <v>1372</v>
       </c>
     </row>
   </sheetData>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F10EF7F-B81C-488F-8D25-531C3157DE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB95D235-A638-42DC-8F50-B86E9E19425F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1341,9 +1341,6 @@
     <t xml:space="preserve">features suggestive of </t>
   </si>
   <si>
-    <t>gall bladder</t>
-  </si>
-  <si>
     <t>gastroduodenal artery</t>
   </si>
   <si>
@@ -2586,9 +2583,6 @@
     <t>gbl</t>
   </si>
   <si>
-    <t>gall bladder lumen</t>
-  </si>
-  <si>
     <t>ts</t>
   </si>
   <si>
@@ -4525,6 +4519,12 @@
   </si>
   <si>
     <t>partial empty sella</t>
+  </si>
+  <si>
+    <t>gallbladder</t>
+  </si>
+  <si>
+    <t>gallbladder lumen</t>
   </si>
 </sst>
 </file>
@@ -4894,50 +4894,50 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="B3" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B4" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B5" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B6" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="B7" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B8" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -4950,18 +4950,18 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B10" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B11" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -4977,15 +4977,15 @@
         <v>307</v>
       </c>
       <c r="B13" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B14" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -4998,58 +4998,58 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B16" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>796</v>
+      </c>
+      <c r="B17" t="s">
         <v>797</v>
-      </c>
-      <c r="B17" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B18" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="B19" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B20" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>761</v>
+      </c>
+      <c r="B21" t="s">
         <v>762</v>
-      </c>
-      <c r="B21" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="B22" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
@@ -5086,26 +5086,26 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B27" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B28" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="B29" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
@@ -5118,18 +5118,18 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="B31" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="B32" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
@@ -5158,10 +5158,10 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="B36" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
@@ -5190,10 +5190,10 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B40" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
@@ -5206,42 +5206,42 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="B42" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="B43" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B44" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="B45" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B46" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
@@ -5289,15 +5289,15 @@
         <v>246</v>
       </c>
       <c r="B52" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B53" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
@@ -5310,34 +5310,34 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B55" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B56" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
+        <v>767</v>
+      </c>
+      <c r="B57" t="s">
         <v>768</v>
-      </c>
-      <c r="B57" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
+        <v>769</v>
+      </c>
+      <c r="B58" t="s">
         <v>770</v>
-      </c>
-      <c r="B58" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
@@ -5350,10 +5350,10 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B60" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
@@ -5382,10 +5382,10 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
+        <v>782</v>
+      </c>
+      <c r="B64" t="s">
         <v>783</v>
-      </c>
-      <c r="B64" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
@@ -5398,10 +5398,10 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
+        <v>755</v>
+      </c>
+      <c r="B66" t="s">
         <v>756</v>
-      </c>
-      <c r="B66" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
@@ -5430,50 +5430,50 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="B70" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="B71" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B72" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B73" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B74" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="B75" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
@@ -5486,10 +5486,10 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B77" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
@@ -5502,138 +5502,138 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B79" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="B80" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B81" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="B82" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B83" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B84" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B85" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="B86" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B87" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="B88" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B89" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="B90" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B91" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="B92" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B93" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="B94" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B95" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
@@ -5702,10 +5702,10 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B104" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
@@ -5726,10 +5726,10 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="B107" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
@@ -5761,23 +5761,23 @@
         <v>41</v>
       </c>
       <c r="B111" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B112" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="B113" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
@@ -5822,18 +5822,18 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="B119" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B120" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
@@ -5862,34 +5862,34 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="B124" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B125" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
+        <v>800</v>
+      </c>
+      <c r="B126" t="s">
         <v>801</v>
-      </c>
-      <c r="B126" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="B127" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
@@ -5902,10 +5902,10 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="B129" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
@@ -5934,10 +5934,10 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B133" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
@@ -5950,18 +5950,18 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B135" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="B136" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
@@ -5993,15 +5993,15 @@
         <v>104</v>
       </c>
       <c r="B140" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="B141" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
@@ -6025,12 +6025,12 @@
         <v>102</v>
       </c>
       <c r="B144" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="B145" t="s">
         <v>403</v>
@@ -6038,18 +6038,18 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B146" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B147" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
@@ -6062,274 +6062,274 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B149" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="B150" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
+        <v>830</v>
+      </c>
+      <c r="B151" t="s">
         <v>831</v>
-      </c>
-      <c r="B151" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
+        <v>832</v>
+      </c>
+      <c r="B152" t="s">
         <v>833</v>
-      </c>
-      <c r="B152" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="B153" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="B154" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B155" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B156" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B157" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="B158" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="B159" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="B160" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="B161" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B162" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B163" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B164" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B165" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B166" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="B167" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B168" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="B169" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B170" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="B171" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B172" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="B173" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B174" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="B175" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B176" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="B177" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B178" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="B179" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B180" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B181" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B182" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
@@ -6345,7 +6345,7 @@
         <v>211</v>
       </c>
       <c r="B184" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
@@ -6353,28 +6353,28 @@
         <v>213</v>
       </c>
       <c r="B185" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="B186" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="B187" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="B188" t="s">
         <v>406</v>
@@ -6385,7 +6385,7 @@
         <v>149</v>
       </c>
       <c r="B189" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
@@ -6401,7 +6401,7 @@
         <v>245</v>
       </c>
       <c r="B191" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
@@ -6414,10 +6414,10 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B193" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
@@ -6438,42 +6438,42 @@
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="B196" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="B197" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
+        <v>792</v>
+      </c>
+      <c r="B198" t="s">
         <v>793</v>
-      </c>
-      <c r="B198" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="B199" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="B200" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
@@ -6486,18 +6486,18 @@
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B202" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="B203" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
@@ -6510,58 +6510,58 @@
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B205" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
+        <v>806</v>
+      </c>
+      <c r="B206" t="s">
         <v>807</v>
-      </c>
-      <c r="B206" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B207" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
+        <v>826</v>
+      </c>
+      <c r="B208" t="s">
         <v>827</v>
-      </c>
-      <c r="B208" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
+        <v>786</v>
+      </c>
+      <c r="B209" t="s">
         <v>787</v>
-      </c>
-      <c r="B209" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="B210" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
+        <v>747</v>
+      </c>
+      <c r="B211" t="s">
         <v>748</v>
-      </c>
-      <c r="B211" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
@@ -6574,10 +6574,10 @@
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="B213" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
@@ -6601,47 +6601,47 @@
         <v>24</v>
       </c>
       <c r="B216" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="B217" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B218" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="B219" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="B220" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
+        <v>812</v>
+      </c>
+      <c r="B221" t="s">
         <v>813</v>
-      </c>
-      <c r="B221" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
@@ -6662,42 +6662,42 @@
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="B224" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B225" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="B226" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B227" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="B228" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
@@ -6710,50 +6710,50 @@
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="B230" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="B231" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="B232" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="B233" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="B234" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="B235" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
@@ -6774,26 +6774,26 @@
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B238" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="B239" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B240" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
@@ -6814,18 +6814,18 @@
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B243" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="B244" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
@@ -6878,18 +6878,18 @@
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B251" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="B252" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
@@ -6934,10 +6934,10 @@
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="B258" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
@@ -6950,50 +6950,50 @@
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B260" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B261" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="B262" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="B263" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="B264" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="B265" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
@@ -7014,10 +7014,10 @@
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
+        <v>780</v>
+      </c>
+      <c r="B268" t="s">
         <v>781</v>
-      </c>
-      <c r="B268" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
@@ -7030,26 +7030,26 @@
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="B270" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="B271" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="B272" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
@@ -7057,15 +7057,15 @@
         <v>275</v>
       </c>
       <c r="B273" t="s">
-        <v>437</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B274" t="s">
-        <v>852</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
@@ -7073,7 +7073,7 @@
         <v>116</v>
       </c>
       <c r="B275" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
@@ -7081,31 +7081,31 @@
         <v>208</v>
       </c>
       <c r="B276" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="B277" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="B278" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B279" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
@@ -7113,31 +7113,31 @@
         <v>118</v>
       </c>
       <c r="B280" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B281" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="B282" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
+        <v>808</v>
+      </c>
+      <c r="B283" t="s">
         <v>809</v>
-      </c>
-      <c r="B283" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
@@ -7145,31 +7145,31 @@
         <v>298</v>
       </c>
       <c r="B284" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B285" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B286" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B287" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
@@ -7177,7 +7177,7 @@
         <v>90</v>
       </c>
       <c r="B288" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
@@ -7185,7 +7185,7 @@
         <v>88</v>
       </c>
       <c r="B289" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
@@ -7193,15 +7193,15 @@
         <v>89</v>
       </c>
       <c r="B290" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B291" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
@@ -7209,15 +7209,15 @@
         <v>23</v>
       </c>
       <c r="B292" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="B293" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
@@ -7230,10 +7230,10 @@
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B295" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
@@ -7241,15 +7241,15 @@
         <v>126</v>
       </c>
       <c r="B296" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="B297" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
@@ -7257,7 +7257,7 @@
         <v>128</v>
       </c>
       <c r="B298" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
@@ -7265,7 +7265,7 @@
         <v>131</v>
       </c>
       <c r="B299" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
@@ -7273,7 +7273,7 @@
         <v>132</v>
       </c>
       <c r="B300" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
@@ -7281,7 +7281,7 @@
         <v>119</v>
       </c>
       <c r="B301" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
@@ -7289,15 +7289,15 @@
         <v>277</v>
       </c>
       <c r="B302" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="B303" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
@@ -7313,7 +7313,7 @@
         <v>129</v>
       </c>
       <c r="B305" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
@@ -7321,7 +7321,7 @@
         <v>127</v>
       </c>
       <c r="B306" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
@@ -7329,7 +7329,7 @@
         <v>173</v>
       </c>
       <c r="B307" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
@@ -7337,15 +7337,15 @@
         <v>262</v>
       </c>
       <c r="B308" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="B309" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
@@ -7353,23 +7353,23 @@
         <v>77</v>
       </c>
       <c r="B310" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B311" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="B312" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
@@ -7377,39 +7377,39 @@
         <v>168</v>
       </c>
       <c r="B313" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="B314" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="B315" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="B316" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="B317" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
@@ -7417,55 +7417,55 @@
         <v>167</v>
       </c>
       <c r="B318" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="B319" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="B320" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="B321" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="B322" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
+        <v>828</v>
+      </c>
+      <c r="B323" t="s">
         <v>829</v>
-      </c>
-      <c r="B323" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
+        <v>784</v>
+      </c>
+      <c r="B324" t="s">
         <v>785</v>
-      </c>
-      <c r="B324" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
@@ -7473,39 +7473,39 @@
         <v>304</v>
       </c>
       <c r="B325" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
+        <v>751</v>
+      </c>
+      <c r="B326" t="s">
         <v>752</v>
-      </c>
-      <c r="B326" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B327" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="B328" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B329" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
@@ -7513,7 +7513,7 @@
         <v>86</v>
       </c>
       <c r="B330" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
@@ -7521,7 +7521,7 @@
         <v>87</v>
       </c>
       <c r="B331" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
@@ -7529,7 +7529,7 @@
         <v>153</v>
       </c>
       <c r="B332" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
@@ -7537,7 +7537,7 @@
         <v>156</v>
       </c>
       <c r="B333" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
@@ -7545,7 +7545,7 @@
         <v>158</v>
       </c>
       <c r="B334" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
@@ -7553,7 +7553,7 @@
         <v>251</v>
       </c>
       <c r="B335" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
@@ -7561,7 +7561,7 @@
         <v>285</v>
       </c>
       <c r="B336" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
@@ -7569,15 +7569,15 @@
         <v>325</v>
       </c>
       <c r="B337" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B338" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
@@ -7585,7 +7585,7 @@
         <v>326</v>
       </c>
       <c r="B339" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
@@ -7593,7 +7593,7 @@
         <v>229</v>
       </c>
       <c r="B340" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
@@ -7601,15 +7601,15 @@
         <v>55</v>
       </c>
       <c r="B341" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B342" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
@@ -7617,7 +7617,7 @@
         <v>235</v>
       </c>
       <c r="B343" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
@@ -7625,7 +7625,7 @@
         <v>57</v>
       </c>
       <c r="B344" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
@@ -7633,23 +7633,23 @@
         <v>236</v>
       </c>
       <c r="B345" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
+        <v>759</v>
+      </c>
+      <c r="B346" t="s">
         <v>760</v>
-      </c>
-      <c r="B346" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B347" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
@@ -7657,15 +7657,15 @@
         <v>164</v>
       </c>
       <c r="B348" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B349" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
@@ -7673,7 +7673,7 @@
         <v>201</v>
       </c>
       <c r="B350" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
@@ -7681,7 +7681,7 @@
         <v>204</v>
       </c>
       <c r="B351" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
@@ -7689,31 +7689,31 @@
         <v>313</v>
       </c>
       <c r="B352" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B353" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="B354" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B355" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
@@ -7721,23 +7721,23 @@
         <v>258</v>
       </c>
       <c r="B356" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B357" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="B358" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
@@ -7745,47 +7745,47 @@
         <v>160</v>
       </c>
       <c r="B359" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B360" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="B361" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
+        <v>753</v>
+      </c>
+      <c r="B362" t="s">
         <v>754</v>
-      </c>
-      <c r="B362" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B363" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B364" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
@@ -7793,7 +7793,7 @@
         <v>184</v>
       </c>
       <c r="B365" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
@@ -7801,7 +7801,7 @@
         <v>244</v>
       </c>
       <c r="B366" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
@@ -7809,95 +7809,95 @@
         <v>243</v>
       </c>
       <c r="B367" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="B368" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B369" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="B370" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B371" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="B372" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B373" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="B374" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B375" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="B376" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B377" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="B378" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
@@ -7905,7 +7905,7 @@
         <v>280</v>
       </c>
       <c r="B379" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
@@ -7913,7 +7913,7 @@
         <v>281</v>
       </c>
       <c r="B380" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
@@ -7921,7 +7921,7 @@
         <v>49</v>
       </c>
       <c r="B381" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
@@ -7929,7 +7929,7 @@
         <v>53</v>
       </c>
       <c r="B382" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
@@ -7937,15 +7937,15 @@
         <v>136</v>
       </c>
       <c r="B383" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="B384" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
@@ -7953,15 +7953,15 @@
         <v>72</v>
       </c>
       <c r="B385" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="B386" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
@@ -7969,15 +7969,15 @@
         <v>221</v>
       </c>
       <c r="B387" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="B388" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
@@ -7990,18 +7990,18 @@
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="B390" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B391" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
@@ -8009,7 +8009,7 @@
         <v>108</v>
       </c>
       <c r="B392" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
@@ -8017,7 +8017,7 @@
         <v>241</v>
       </c>
       <c r="B393" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
@@ -8025,23 +8025,23 @@
         <v>327</v>
       </c>
       <c r="B394" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="B395" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="B396" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
@@ -8049,23 +8049,23 @@
         <v>121</v>
       </c>
       <c r="B397" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
+        <v>743</v>
+      </c>
+      <c r="B398" t="s">
         <v>744</v>
-      </c>
-      <c r="B398" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
+        <v>774</v>
+      </c>
+      <c r="B399" t="s">
         <v>775</v>
-      </c>
-      <c r="B399" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
@@ -8073,7 +8073,7 @@
         <v>134</v>
       </c>
       <c r="B400" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
@@ -8081,15 +8081,15 @@
         <v>63</v>
       </c>
       <c r="B401" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="B402" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
@@ -8097,7 +8097,7 @@
         <v>224</v>
       </c>
       <c r="B403" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
@@ -8105,7 +8105,7 @@
         <v>25</v>
       </c>
       <c r="B404" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
@@ -8113,7 +8113,7 @@
         <v>26</v>
       </c>
       <c r="B405" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
@@ -8121,23 +8121,23 @@
         <v>207</v>
       </c>
       <c r="B406" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B407" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="B408" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
@@ -8145,7 +8145,7 @@
         <v>206</v>
       </c>
       <c r="B409" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
@@ -8153,7 +8153,7 @@
         <v>202</v>
       </c>
       <c r="B410" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
@@ -8161,7 +8161,7 @@
         <v>205</v>
       </c>
       <c r="B411" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
@@ -8169,15 +8169,15 @@
         <v>145</v>
       </c>
       <c r="B412" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B413" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
@@ -8185,15 +8185,15 @@
         <v>171</v>
       </c>
       <c r="B414" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="B415" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
@@ -8201,15 +8201,15 @@
         <v>263</v>
       </c>
       <c r="B416" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="B417" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
@@ -8217,7 +8217,7 @@
         <v>80</v>
       </c>
       <c r="B418" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
@@ -8225,7 +8225,7 @@
         <v>65</v>
       </c>
       <c r="B419" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
@@ -8233,7 +8233,7 @@
         <v>191</v>
       </c>
       <c r="B420" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
@@ -8241,7 +8241,7 @@
         <v>123</v>
       </c>
       <c r="B421" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
@@ -8249,7 +8249,7 @@
         <v>192</v>
       </c>
       <c r="B422" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
@@ -8257,7 +8257,7 @@
         <v>231</v>
       </c>
       <c r="B423" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
@@ -8265,15 +8265,15 @@
         <v>233</v>
       </c>
       <c r="B424" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="B425" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
@@ -8281,15 +8281,15 @@
         <v>31</v>
       </c>
       <c r="B426" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="B427" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
@@ -8297,7 +8297,7 @@
         <v>30</v>
       </c>
       <c r="B428" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
@@ -8305,7 +8305,7 @@
         <v>37</v>
       </c>
       <c r="B429" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
@@ -8313,15 +8313,15 @@
         <v>71</v>
       </c>
       <c r="B430" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="B431" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
@@ -8329,7 +8329,7 @@
         <v>306</v>
       </c>
       <c r="B432" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
@@ -8337,7 +8337,7 @@
         <v>222</v>
       </c>
       <c r="B433" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
@@ -8345,7 +8345,7 @@
         <v>278</v>
       </c>
       <c r="B434" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
@@ -8353,23 +8353,23 @@
         <v>279</v>
       </c>
       <c r="B435" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="B436" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
+        <v>824</v>
+      </c>
+      <c r="B437" t="s">
         <v>825</v>
-      </c>
-      <c r="B437" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
@@ -8377,7 +8377,7 @@
         <v>48</v>
       </c>
       <c r="B438" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
@@ -8385,7 +8385,7 @@
         <v>146</v>
       </c>
       <c r="B439" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
@@ -8393,15 +8393,15 @@
         <v>52</v>
       </c>
       <c r="B440" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="B441" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
@@ -8409,31 +8409,31 @@
         <v>223</v>
       </c>
       <c r="B442" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="B443" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="B444" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="B445" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
@@ -8441,7 +8441,7 @@
         <v>96</v>
       </c>
       <c r="B446" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
@@ -8449,7 +8449,7 @@
         <v>248</v>
       </c>
       <c r="B447" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
@@ -8457,7 +8457,7 @@
         <v>249</v>
       </c>
       <c r="B448" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
@@ -8465,15 +8465,15 @@
         <v>94</v>
       </c>
       <c r="B449" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B450" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
@@ -8481,39 +8481,39 @@
         <v>212</v>
       </c>
       <c r="B451" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="B452" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B453" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="B454" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B455" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
@@ -8521,63 +8521,63 @@
         <v>329</v>
       </c>
       <c r="B456" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="B457" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="B458" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="B459" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="B460" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="B461" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B462" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="B463" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
@@ -8585,15 +8585,15 @@
         <v>82</v>
       </c>
       <c r="B464" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
+        <v>765</v>
+      </c>
+      <c r="B465" t="s">
         <v>766</v>
-      </c>
-      <c r="B465" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
@@ -8601,47 +8601,47 @@
         <v>197</v>
       </c>
       <c r="B466" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B467" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="B468" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="B469" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
+        <v>814</v>
+      </c>
+      <c r="B470" t="s">
         <v>815</v>
-      </c>
-      <c r="B470" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="B471" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
@@ -8654,7 +8654,7 @@
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B473" t="s">
         <v>4</v>
@@ -8662,7 +8662,7 @@
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B474" t="s">
         <v>4</v>
@@ -8670,26 +8670,26 @@
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B475" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B476" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
+        <v>763</v>
+      </c>
+      <c r="B477" t="s">
         <v>764</v>
-      </c>
-      <c r="B477" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
@@ -8697,31 +8697,31 @@
         <v>85</v>
       </c>
       <c r="B478" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="B479" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
+        <v>822</v>
+      </c>
+      <c r="B480" t="s">
         <v>823</v>
-      </c>
-      <c r="B480" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
+        <v>802</v>
+      </c>
+      <c r="B481" t="s">
         <v>803</v>
-      </c>
-      <c r="B481" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
@@ -8729,87 +8729,87 @@
         <v>187</v>
       </c>
       <c r="B482" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
+        <v>820</v>
+      </c>
+      <c r="B483" t="s">
         <v>821</v>
-      </c>
-      <c r="B483" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B484" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="B485" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B486" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="B487" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B488" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B489" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B490" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="B491" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="B492" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
@@ -8822,18 +8822,18 @@
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
+        <v>810</v>
+      </c>
+      <c r="B494" t="s">
         <v>811</v>
-      </c>
-      <c r="B494" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="B495" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
@@ -8841,15 +8841,15 @@
         <v>186</v>
       </c>
       <c r="B496" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
+        <v>804</v>
+      </c>
+      <c r="B497" t="s">
         <v>805</v>
-      </c>
-      <c r="B497" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
@@ -8857,47 +8857,47 @@
         <v>319</v>
       </c>
       <c r="B498" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B499" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
+        <v>848</v>
+      </c>
+      <c r="B500" t="s">
         <v>849</v>
-      </c>
-      <c r="B500" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B501" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B502" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="B503" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
@@ -8905,7 +8905,7 @@
         <v>256</v>
       </c>
       <c r="B504" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
@@ -8913,7 +8913,7 @@
         <v>260</v>
       </c>
       <c r="B505" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
@@ -8921,7 +8921,7 @@
         <v>261</v>
       </c>
       <c r="B506" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
@@ -8929,7 +8929,7 @@
         <v>188</v>
       </c>
       <c r="B507" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
@@ -8937,31 +8937,31 @@
         <v>190</v>
       </c>
       <c r="B508" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B509" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B510" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="B511" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
@@ -8969,31 +8969,31 @@
         <v>209</v>
       </c>
       <c r="B512" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="B513" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="B514" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
+        <v>844</v>
+      </c>
+      <c r="B515" t="s">
         <v>845</v>
-      </c>
-      <c r="B515" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
@@ -9001,7 +9001,7 @@
         <v>143</v>
       </c>
       <c r="B516" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
@@ -9009,23 +9009,23 @@
         <v>140</v>
       </c>
       <c r="B517" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="B518" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="B519" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
@@ -9033,7 +9033,7 @@
         <v>254</v>
       </c>
       <c r="B520" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
@@ -9041,7 +9041,7 @@
         <v>330</v>
       </c>
       <c r="B521" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
@@ -9049,7 +9049,7 @@
         <v>210</v>
       </c>
       <c r="B522" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
@@ -9057,7 +9057,7 @@
         <v>234</v>
       </c>
       <c r="B523" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
@@ -9065,7 +9065,7 @@
         <v>73</v>
       </c>
       <c r="B524" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
@@ -9073,7 +9073,7 @@
         <v>341</v>
       </c>
       <c r="B525" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
@@ -9081,23 +9081,23 @@
         <v>308</v>
       </c>
       <c r="B526" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
+        <v>836</v>
+      </c>
+      <c r="B527" t="s">
         <v>837</v>
-      </c>
-      <c r="B527" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
+        <v>838</v>
+      </c>
+      <c r="B528" t="s">
         <v>839</v>
-      </c>
-      <c r="B528" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
@@ -9105,39 +9105,39 @@
         <v>220</v>
       </c>
       <c r="B529" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B530" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="B531" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="B532" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B533" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
@@ -9145,7 +9145,7 @@
         <v>227</v>
       </c>
       <c r="B534" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
@@ -9153,23 +9153,23 @@
         <v>333</v>
       </c>
       <c r="B535" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B536" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
+        <v>771</v>
+      </c>
+      <c r="B537" t="s">
         <v>772</v>
-      </c>
-      <c r="B537" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
@@ -9177,15 +9177,15 @@
         <v>294</v>
       </c>
       <c r="B538" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="B539" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
@@ -9193,23 +9193,23 @@
         <v>338</v>
       </c>
       <c r="B540" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B541" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="B542" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
@@ -9217,7 +9217,7 @@
         <v>339</v>
       </c>
       <c r="B543" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
@@ -9225,15 +9225,15 @@
         <v>340</v>
       </c>
       <c r="B544" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B545" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
@@ -9241,7 +9241,7 @@
         <v>39</v>
       </c>
       <c r="B546" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
@@ -9249,7 +9249,7 @@
         <v>38</v>
       </c>
       <c r="B547" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
@@ -9257,7 +9257,7 @@
         <v>342</v>
       </c>
       <c r="B548" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
@@ -9265,31 +9265,31 @@
         <v>107</v>
       </c>
       <c r="B549" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="B550" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B551" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B552" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
@@ -9297,15 +9297,15 @@
         <v>117</v>
       </c>
       <c r="B553" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="B554" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
@@ -9313,7 +9313,7 @@
         <v>98</v>
       </c>
       <c r="B555" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
@@ -9321,31 +9321,31 @@
         <v>99</v>
       </c>
       <c r="B556" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B557" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="B558" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
+        <v>816</v>
+      </c>
+      <c r="B559" t="s">
         <v>817</v>
-      </c>
-      <c r="B559" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
@@ -9353,15 +9353,15 @@
         <v>113</v>
       </c>
       <c r="B560" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B561" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
@@ -9369,7 +9369,7 @@
         <v>45</v>
       </c>
       <c r="B562" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
@@ -9377,7 +9377,7 @@
         <v>290</v>
       </c>
       <c r="B563" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
@@ -9385,7 +9385,7 @@
         <v>299</v>
       </c>
       <c r="B564" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
@@ -9393,15 +9393,15 @@
         <v>47</v>
       </c>
       <c r="B565" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
+        <v>840</v>
+      </c>
+      <c r="B566" t="s">
         <v>841</v>
-      </c>
-      <c r="B566" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
@@ -9409,15 +9409,15 @@
         <v>51</v>
       </c>
       <c r="B567" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B568" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
@@ -9425,15 +9425,15 @@
         <v>114</v>
       </c>
       <c r="B569" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
+        <v>846</v>
+      </c>
+      <c r="B570" t="s">
         <v>847</v>
-      </c>
-      <c r="B570" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
@@ -9441,15 +9441,15 @@
         <v>144</v>
       </c>
       <c r="B571" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B572" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
@@ -9457,7 +9457,7 @@
         <v>176</v>
       </c>
       <c r="B573" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
@@ -9465,7 +9465,7 @@
         <v>315</v>
       </c>
       <c r="B574" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
@@ -9473,23 +9473,23 @@
         <v>29</v>
       </c>
       <c r="B575" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B576" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B577" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
@@ -9497,23 +9497,23 @@
         <v>293</v>
       </c>
       <c r="B578" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B579" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="B580" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
@@ -9521,23 +9521,23 @@
         <v>301</v>
       </c>
       <c r="B581" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="B582" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="B583" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
@@ -9545,7 +9545,7 @@
         <v>75</v>
       </c>
       <c r="B584" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
@@ -9553,7 +9553,7 @@
         <v>76</v>
       </c>
       <c r="B585" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
@@ -9561,7 +9561,7 @@
         <v>78</v>
       </c>
       <c r="B586" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
@@ -9569,47 +9569,47 @@
         <v>328</v>
       </c>
       <c r="B587" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="B588" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="B589" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
+        <v>745</v>
+      </c>
+      <c r="B590" t="s">
         <v>746</v>
-      </c>
-      <c r="B590" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
+        <v>798</v>
+      </c>
+      <c r="B591" t="s">
         <v>799</v>
-      </c>
-      <c r="B591" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="B592" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
@@ -9617,23 +9617,23 @@
         <v>135</v>
       </c>
       <c r="B593" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="B594" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="B595" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
@@ -9641,15 +9641,15 @@
         <v>215</v>
       </c>
       <c r="B596" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B597" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
@@ -9657,7 +9657,7 @@
         <v>216</v>
       </c>
       <c r="B598" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
@@ -9665,15 +9665,15 @@
         <v>316</v>
       </c>
       <c r="B599" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="B600" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
@@ -9681,23 +9681,23 @@
         <v>214</v>
       </c>
       <c r="B601" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B602" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="B603" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
@@ -9705,39 +9705,39 @@
         <v>225</v>
       </c>
       <c r="B604" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="B605" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="B606" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="B607" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="B608" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
@@ -9745,7 +9745,7 @@
         <v>93</v>
       </c>
       <c r="B609" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
@@ -9753,15 +9753,15 @@
         <v>120</v>
       </c>
       <c r="B610" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
+        <v>776</v>
+      </c>
+      <c r="B611" t="s">
         <v>777</v>
-      </c>
-      <c r="B611" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
@@ -9769,7 +9769,7 @@
         <v>133</v>
       </c>
       <c r="B612" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
@@ -9777,15 +9777,15 @@
         <v>62</v>
       </c>
       <c r="B613" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="B614" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
@@ -9793,39 +9793,39 @@
         <v>66</v>
       </c>
       <c r="B615" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
+        <v>818</v>
+      </c>
+      <c r="B616" t="s">
         <v>819</v>
-      </c>
-      <c r="B616" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="B617" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="B618" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="B619" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
@@ -9833,7 +9833,7 @@
         <v>79</v>
       </c>
       <c r="B620" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
@@ -9841,7 +9841,7 @@
         <v>64</v>
       </c>
       <c r="B621" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.35">
@@ -9849,15 +9849,15 @@
         <v>122</v>
       </c>
       <c r="B622" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="B623" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.35">
@@ -9865,79 +9865,79 @@
         <v>181</v>
       </c>
       <c r="B624" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
+        <v>794</v>
+      </c>
+      <c r="B625" t="s">
         <v>795</v>
-      </c>
-      <c r="B625" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B626" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B627" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B628" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="B629" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="B630" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="B631" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B632" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B633" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.35">
@@ -9945,31 +9945,31 @@
         <v>284</v>
       </c>
       <c r="B634" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B635" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="B636" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
+        <v>834</v>
+      </c>
+      <c r="B637" t="s">
         <v>835</v>
-      </c>
-      <c r="B637" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.35">
@@ -9977,39 +9977,39 @@
         <v>283</v>
       </c>
       <c r="B638" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B639" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="B640" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
+        <v>749</v>
+      </c>
+      <c r="B641" t="s">
         <v>750</v>
-      </c>
-      <c r="B641" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B642" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.35">
@@ -10017,7 +10017,7 @@
         <v>67</v>
       </c>
       <c r="B643" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.35">
@@ -10025,15 +10025,15 @@
         <v>68</v>
       </c>
       <c r="B644" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="B645" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.35">
@@ -10041,7 +10041,7 @@
         <v>95</v>
       </c>
       <c r="B646" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.35">
@@ -10049,7 +10049,7 @@
         <v>289</v>
       </c>
       <c r="B647" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.35">
@@ -10057,7 +10057,7 @@
         <v>297</v>
       </c>
       <c r="B648" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.35">
@@ -10065,7 +10065,7 @@
         <v>264</v>
       </c>
       <c r="B649" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.35">
@@ -10073,23 +10073,23 @@
         <v>193</v>
       </c>
       <c r="B650" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="B651" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B652" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.35">
@@ -10097,15 +10097,15 @@
         <v>44</v>
       </c>
       <c r="B653" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B654" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.35">
@@ -10113,7 +10113,7 @@
         <v>323</v>
       </c>
       <c r="B655" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.35">
@@ -10121,39 +10121,39 @@
         <v>324</v>
       </c>
       <c r="B656" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
+        <v>842</v>
+      </c>
+      <c r="B657" t="s">
         <v>843</v>
-      </c>
-      <c r="B657" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B658" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="B659" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B660" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.35">
@@ -10161,7 +10161,7 @@
         <v>33</v>
       </c>
       <c r="B661" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.35">
@@ -10169,15 +10169,15 @@
         <v>36</v>
       </c>
       <c r="B662" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="B663" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.35">
@@ -10185,7 +10185,7 @@
         <v>309</v>
       </c>
       <c r="B664" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.35">
@@ -10193,7 +10193,7 @@
         <v>257</v>
       </c>
       <c r="B665" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.35">
@@ -10201,7 +10201,7 @@
         <v>302</v>
       </c>
       <c r="B666" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.35">
@@ -10209,7 +10209,7 @@
         <v>228</v>
       </c>
       <c r="B667" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.35">
@@ -10222,26 +10222,26 @@
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B669" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="B670" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
+        <v>778</v>
+      </c>
+      <c r="B671" t="s">
         <v>779</v>
-      </c>
-      <c r="B671" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.35">
@@ -10249,23 +10249,23 @@
         <v>142</v>
       </c>
       <c r="B672" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="B673" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B674" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.35">
@@ -10273,7 +10273,7 @@
         <v>54</v>
       </c>
       <c r="B675" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.35">
@@ -10281,23 +10281,23 @@
         <v>265</v>
       </c>
       <c r="B676" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B677" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="B678" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.35">
@@ -10305,15 +10305,15 @@
         <v>56</v>
       </c>
       <c r="B679" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="B680" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.35">
@@ -10321,7 +10321,7 @@
         <v>185</v>
       </c>
       <c r="B681" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.35">
@@ -10329,7 +10329,7 @@
         <v>159</v>
       </c>
       <c r="B682" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.35">
@@ -10337,31 +10337,31 @@
         <v>43</v>
       </c>
       <c r="B683" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="B684" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B685" t="s">
         <v>1448</v>
-      </c>
-      <c r="B685" t="s">
-        <v>1450</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B686" t="s">
         <v>1449</v>
-      </c>
-      <c r="B686" t="s">
-        <v>1451</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.35">
@@ -10369,23 +10369,23 @@
         <v>40</v>
       </c>
       <c r="B687" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="B688" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="B689" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.35">
@@ -10393,39 +10393,39 @@
         <v>165</v>
       </c>
       <c r="B690" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="B691" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="B692" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="B693" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="B694" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.35">
@@ -10441,7 +10441,7 @@
         <v>250</v>
       </c>
       <c r="B696" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.35">
@@ -10449,15 +10449,15 @@
         <v>27</v>
       </c>
       <c r="B697" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B698" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.35">
@@ -10465,15 +10465,15 @@
         <v>28</v>
       </c>
       <c r="B699" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="B700" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.35">
@@ -10481,23 +10481,23 @@
         <v>255</v>
       </c>
       <c r="B701" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B702" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
+        <v>788</v>
+      </c>
+      <c r="B703" t="s">
         <v>789</v>
-      </c>
-      <c r="B703" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.35">
@@ -10505,23 +10505,23 @@
         <v>267</v>
       </c>
       <c r="B704" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B705" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B706" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.35">
@@ -10529,7 +10529,7 @@
         <v>139</v>
       </c>
       <c r="B707" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.35">
@@ -10545,47 +10545,47 @@
         <v>105</v>
       </c>
       <c r="B709" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="B710" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B711" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B712" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="B713" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B714" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.35">
@@ -10593,7 +10593,7 @@
         <v>292</v>
       </c>
       <c r="B715" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.35">
@@ -10609,23 +10609,23 @@
         <v>334</v>
       </c>
       <c r="B717" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="B718" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="B719" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.35">
@@ -10633,7 +10633,7 @@
         <v>331</v>
       </c>
       <c r="B720" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.35">
@@ -10641,7 +10641,7 @@
         <v>259</v>
       </c>
       <c r="B721" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.35">
@@ -10649,23 +10649,23 @@
         <v>318</v>
       </c>
       <c r="B722" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B723" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="B724" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.35">
@@ -10673,7 +10673,7 @@
         <v>268</v>
       </c>
       <c r="B725" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.35">
@@ -10681,7 +10681,7 @@
         <v>271</v>
       </c>
       <c r="B726" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.35">
@@ -10689,7 +10689,7 @@
         <v>274</v>
       </c>
       <c r="B727" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.35">
@@ -10697,7 +10697,7 @@
         <v>270</v>
       </c>
       <c r="B728" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.35">
@@ -10705,7 +10705,7 @@
         <v>273</v>
       </c>
       <c r="B729" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.35">
@@ -10713,7 +10713,7 @@
         <v>269</v>
       </c>
       <c r="B730" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.35">
@@ -10721,7 +10721,7 @@
         <v>272</v>
       </c>
       <c r="B731" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.35">
@@ -10729,7 +10729,7 @@
         <v>92</v>
       </c>
       <c r="B732" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.35">
@@ -10737,7 +10737,7 @@
         <v>200</v>
       </c>
       <c r="B733" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.35">
@@ -10745,15 +10745,15 @@
         <v>203</v>
       </c>
       <c r="B734" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B735" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.35">
@@ -10761,31 +10761,31 @@
         <v>172</v>
       </c>
       <c r="B736" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A737" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="B737" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B738" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="739" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="B739" s="1" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.35">
@@ -10793,15 +10793,15 @@
         <v>252</v>
       </c>
       <c r="B740" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B741" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.35">
@@ -10809,15 +10809,15 @@
         <v>189</v>
       </c>
       <c r="B742" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B743" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.35">
@@ -10825,7 +10825,7 @@
         <v>311</v>
       </c>
       <c r="B744" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.35">
@@ -10833,31 +10833,31 @@
         <v>312</v>
       </c>
       <c r="B745" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A746" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B746" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A747" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="B747" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A748" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B748" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.35">
@@ -10865,55 +10865,55 @@
         <v>81</v>
       </c>
       <c r="B749" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A750" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B750" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A751" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B751" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A752" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B752" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A753" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B753" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
     </row>
     <row r="754" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A754" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="B754" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A755" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="B755" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
     </row>
   </sheetData>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB95D235-A638-42DC-8F50-B86E9E19425F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B53FFCD-0853-4092-90B1-EEDA89A3A6F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="1499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="1501">
   <si>
     <t>trigger</t>
   </si>
@@ -4525,6 +4525,12 @@
   </si>
   <si>
     <t>gallbladder lumen</t>
+  </si>
+  <si>
+    <t>gbout</t>
+  </si>
+  <si>
+    <t>Gallbladder is not visualized with hyperdense clips in gallbladder fossa - suggestive of post-cholecystectomy status</t>
   </si>
 </sst>
 </file>
@@ -4593,10 +4599,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B755" totalsRowShown="0">
-  <autoFilter ref="A1:B755" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B755">
-    <sortCondition ref="A1:A755"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B756" totalsRowShown="0">
+  <autoFilter ref="A1:B756" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B756">
+    <sortCondition ref="A1:A756"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4869,7 +4875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B755"/>
+  <dimension ref="A1:B756"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -7070,343 +7076,343 @@
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>116</v>
+        <v>1499</v>
       </c>
       <c r="B275" t="s">
-        <v>437</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="B276" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>1401</v>
+        <v>208</v>
       </c>
       <c r="B277" t="s">
-        <v>1402</v>
+        <v>438</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>1200</v>
+        <v>1401</v>
       </c>
       <c r="B278" t="s">
-        <v>1201</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>1044</v>
+        <v>1200</v>
       </c>
       <c r="B279" t="s">
-        <v>1045</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>118</v>
+        <v>1044</v>
       </c>
       <c r="B280" t="s">
-        <v>439</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>634</v>
+        <v>118</v>
       </c>
       <c r="B281" t="s">
-        <v>716</v>
+        <v>439</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>1311</v>
+        <v>634</v>
       </c>
       <c r="B282" t="s">
-        <v>1312</v>
+        <v>716</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>808</v>
+        <v>1311</v>
       </c>
       <c r="B283" t="s">
-        <v>809</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>298</v>
+        <v>808</v>
       </c>
       <c r="B284" t="s">
-        <v>440</v>
+        <v>809</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>636</v>
+        <v>298</v>
       </c>
       <c r="B285" t="s">
-        <v>717</v>
+        <v>440</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B286" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>1026</v>
+        <v>637</v>
       </c>
       <c r="B287" t="s">
-        <v>1027</v>
+        <v>718</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>90</v>
+        <v>1026</v>
       </c>
       <c r="B288" t="s">
-        <v>441</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B289" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B290" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>1060</v>
+        <v>89</v>
       </c>
       <c r="B291" t="s">
-        <v>1061</v>
+        <v>443</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>23</v>
+        <v>1060</v>
       </c>
       <c r="B292" t="s">
-        <v>1117</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>1405</v>
+        <v>23</v>
       </c>
       <c r="B293" t="s">
-        <v>1406</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>5</v>
+        <v>1405</v>
       </c>
       <c r="B294" t="s">
-        <v>6</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>1121</v>
+        <v>5</v>
       </c>
       <c r="B295" t="s">
-        <v>1122</v>
+        <v>6</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>126</v>
+        <v>1121</v>
       </c>
       <c r="B296" t="s">
-        <v>444</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>1379</v>
+        <v>126</v>
       </c>
       <c r="B297" t="s">
-        <v>1380</v>
+        <v>444</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>128</v>
+        <v>1379</v>
       </c>
       <c r="B298" t="s">
-        <v>445</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B299" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B300" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B301" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>277</v>
+        <v>119</v>
       </c>
       <c r="B302" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>1062</v>
+        <v>277</v>
       </c>
       <c r="B303" t="s">
-        <v>1063</v>
+        <v>449</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>9</v>
+        <v>1062</v>
       </c>
       <c r="B304" t="s">
-        <v>10</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="B305" t="s">
-        <v>450</v>
+        <v>10</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B306" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="B307" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="B308" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>1366</v>
+        <v>262</v>
       </c>
       <c r="B309" t="s">
-        <v>1367</v>
+        <v>453</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>77</v>
+        <v>1366</v>
       </c>
       <c r="B310" t="s">
-        <v>454</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>929</v>
+        <v>77</v>
       </c>
       <c r="B311" t="s">
-        <v>930</v>
+        <v>454</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>1151</v>
+        <v>929</v>
       </c>
       <c r="B312" t="s">
-        <v>1152</v>
+        <v>930</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>168</v>
+        <v>1151</v>
       </c>
       <c r="B313" t="s">
-        <v>455</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>1339</v>
+        <v>168</v>
       </c>
       <c r="B314" t="s">
-        <v>1340</v>
+        <v>455</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>1349</v>
+        <v>1339</v>
       </c>
       <c r="B315" t="s">
-        <v>1350</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>1392</v>
+        <v>1349</v>
       </c>
       <c r="B316" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>1345</v>
+        <v>1392</v>
       </c>
       <c r="B317" t="s">
         <v>1346</v>
@@ -7414,39 +7420,39 @@
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>167</v>
+        <v>1345</v>
       </c>
       <c r="B318" t="s">
-        <v>456</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>1341</v>
+        <v>167</v>
       </c>
       <c r="B319" t="s">
-        <v>1342</v>
+        <v>456</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
       <c r="B320" t="s">
-        <v>1348</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>1374</v>
+        <v>1347</v>
       </c>
       <c r="B321" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>1343</v>
+        <v>1374</v>
       </c>
       <c r="B322" t="s">
         <v>1344</v>
@@ -7454,199 +7460,199 @@
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>828</v>
+        <v>1343</v>
       </c>
       <c r="B323" t="s">
-        <v>829</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>784</v>
+        <v>828</v>
       </c>
       <c r="B324" t="s">
-        <v>785</v>
+        <v>829</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>304</v>
+        <v>784</v>
       </c>
       <c r="B325" t="s">
-        <v>457</v>
+        <v>785</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>751</v>
+        <v>304</v>
       </c>
       <c r="B326" t="s">
-        <v>752</v>
+        <v>457</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>888</v>
+        <v>751</v>
       </c>
       <c r="B327" t="s">
-        <v>889</v>
+        <v>752</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>1381</v>
+        <v>888</v>
       </c>
       <c r="B328" t="s">
-        <v>1382</v>
+        <v>889</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>645</v>
+        <v>1381</v>
       </c>
       <c r="B329" t="s">
-        <v>719</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>86</v>
+        <v>645</v>
       </c>
       <c r="B330" t="s">
-        <v>458</v>
+        <v>719</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B331" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="B332" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B333" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B334" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>251</v>
+        <v>158</v>
       </c>
       <c r="B335" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="B336" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>325</v>
+        <v>285</v>
       </c>
       <c r="B337" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>1361</v>
+        <v>325</v>
       </c>
       <c r="B338" t="s">
-        <v>1362</v>
+        <v>465</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>326</v>
+        <v>1361</v>
       </c>
       <c r="B339" t="s">
-        <v>466</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>229</v>
+        <v>326</v>
       </c>
       <c r="B340" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>55</v>
+        <v>229</v>
       </c>
       <c r="B341" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>650</v>
+        <v>55</v>
       </c>
       <c r="B342" t="s">
-        <v>720</v>
+        <v>468</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>235</v>
+        <v>650</v>
       </c>
       <c r="B343" t="s">
-        <v>469</v>
+        <v>720</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="B344" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="B345" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>759</v>
+        <v>236</v>
       </c>
       <c r="B346" t="s">
-        <v>760</v>
+        <v>471</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>1002</v>
+        <v>759</v>
       </c>
       <c r="B347" t="s">
         <v>760</v>
@@ -7654,631 +7660,631 @@
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>164</v>
+        <v>1002</v>
       </c>
       <c r="B348" t="s">
-        <v>472</v>
+        <v>760</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>1458</v>
+        <v>164</v>
       </c>
       <c r="B349" t="s">
-        <v>1456</v>
+        <v>472</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>201</v>
+        <v>1458</v>
       </c>
       <c r="B350" t="s">
-        <v>473</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B351" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>313</v>
+        <v>204</v>
       </c>
       <c r="B352" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>865</v>
+        <v>313</v>
       </c>
       <c r="B353" t="s">
-        <v>866</v>
+        <v>475</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>988</v>
+        <v>865</v>
       </c>
       <c r="B354" t="s">
-        <v>989</v>
+        <v>866</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>1314</v>
+        <v>988</v>
       </c>
       <c r="B355" t="s">
-        <v>1315</v>
+        <v>989</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>258</v>
+        <v>1314</v>
       </c>
       <c r="B356" t="s">
-        <v>476</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>974</v>
+        <v>258</v>
       </c>
       <c r="B357" t="s">
-        <v>975</v>
+        <v>476</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>1353</v>
+        <v>974</v>
       </c>
       <c r="B358" t="s">
-        <v>1354</v>
+        <v>975</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>160</v>
+        <v>1353</v>
       </c>
       <c r="B359" t="s">
-        <v>477</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>685</v>
+        <v>160</v>
       </c>
       <c r="B360" t="s">
-        <v>721</v>
+        <v>477</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>1145</v>
+        <v>685</v>
       </c>
       <c r="B361" t="s">
-        <v>1146</v>
+        <v>721</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>753</v>
+        <v>1145</v>
       </c>
       <c r="B362" t="s">
-        <v>754</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>886</v>
+        <v>753</v>
       </c>
       <c r="B363" t="s">
-        <v>887</v>
+        <v>754</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B364" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>184</v>
+        <v>884</v>
       </c>
       <c r="B365" t="s">
-        <v>478</v>
+        <v>885</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>244</v>
+        <v>184</v>
       </c>
       <c r="B366" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B367" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>1258</v>
+        <v>243</v>
       </c>
       <c r="B368" t="s">
-        <v>1263</v>
+        <v>480</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>679</v>
+        <v>1258</v>
       </c>
       <c r="B369" t="s">
-        <v>722</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>1259</v>
+        <v>679</v>
       </c>
       <c r="B370" t="s">
-        <v>1264</v>
+        <v>722</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>680</v>
+        <v>1259</v>
       </c>
       <c r="B371" t="s">
-        <v>723</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>1260</v>
+        <v>680</v>
       </c>
       <c r="B372" t="s">
-        <v>1265</v>
+        <v>723</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>681</v>
+        <v>1260</v>
       </c>
       <c r="B373" t="s">
-        <v>724</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>1261</v>
+        <v>681</v>
       </c>
       <c r="B374" t="s">
-        <v>1266</v>
+        <v>724</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>682</v>
+        <v>1261</v>
       </c>
       <c r="B375" t="s">
-        <v>725</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>1262</v>
+        <v>682</v>
       </c>
       <c r="B376" t="s">
-        <v>1267</v>
+        <v>725</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>683</v>
+        <v>1262</v>
       </c>
       <c r="B377" t="s">
-        <v>726</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>1171</v>
+        <v>683</v>
       </c>
       <c r="B378" t="s">
-        <v>1172</v>
+        <v>726</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>280</v>
+        <v>1171</v>
       </c>
       <c r="B379" t="s">
-        <v>481</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B380" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>49</v>
+        <v>281</v>
       </c>
       <c r="B381" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B382" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="B383" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>1434</v>
+        <v>136</v>
       </c>
       <c r="B384" t="s">
-        <v>1435</v>
+        <v>486</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>72</v>
+        <v>1434</v>
       </c>
       <c r="B385" t="s">
-        <v>485</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>1169</v>
+        <v>72</v>
       </c>
       <c r="B386" t="s">
-        <v>1170</v>
+        <v>485</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>221</v>
+        <v>1169</v>
       </c>
       <c r="B387" t="s">
-        <v>487</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>1173</v>
+        <v>221</v>
       </c>
       <c r="B388" t="s">
-        <v>1174</v>
+        <v>487</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>15</v>
+        <v>1173</v>
       </c>
       <c r="B389" t="s">
-        <v>16</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>1048</v>
+        <v>15</v>
       </c>
       <c r="B390" t="s">
-        <v>1049</v>
+        <v>16</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>911</v>
+        <v>1048</v>
       </c>
       <c r="B391" t="s">
-        <v>912</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>108</v>
+        <v>911</v>
       </c>
       <c r="B392" t="s">
-        <v>488</v>
+        <v>912</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>241</v>
+        <v>108</v>
       </c>
       <c r="B393" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>327</v>
+        <v>241</v>
       </c>
       <c r="B394" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>1088</v>
+        <v>327</v>
       </c>
       <c r="B395" t="s">
-        <v>1089</v>
+        <v>490</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>1040</v>
+        <v>1088</v>
       </c>
       <c r="B396" t="s">
-        <v>1041</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>121</v>
+        <v>1040</v>
       </c>
       <c r="B397" t="s">
-        <v>491</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>743</v>
+        <v>121</v>
       </c>
       <c r="B398" t="s">
-        <v>744</v>
+        <v>491</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>774</v>
+        <v>743</v>
       </c>
       <c r="B399" t="s">
-        <v>775</v>
+        <v>744</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>134</v>
+        <v>774</v>
       </c>
       <c r="B400" t="s">
-        <v>492</v>
+        <v>775</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="B401" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>1292</v>
+        <v>63</v>
       </c>
       <c r="B402" t="s">
-        <v>1293</v>
+        <v>493</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>224</v>
+        <v>1292</v>
       </c>
       <c r="B403" t="s">
-        <v>494</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>25</v>
+        <v>224</v>
       </c>
       <c r="B404" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B405" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>207</v>
+        <v>26</v>
       </c>
       <c r="B406" t="s">
-        <v>1114</v>
+        <v>496</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>951</v>
+        <v>207</v>
       </c>
       <c r="B407" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>1097</v>
+        <v>951</v>
       </c>
       <c r="B408" t="s">
-        <v>1098</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>206</v>
+        <v>1097</v>
       </c>
       <c r="B409" t="s">
-        <v>1116</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B410" t="s">
-        <v>497</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B411" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="B412" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>656</v>
+        <v>145</v>
       </c>
       <c r="B413" t="s">
-        <v>727</v>
+        <v>499</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>171</v>
+        <v>656</v>
       </c>
       <c r="B414" t="s">
-        <v>500</v>
+        <v>727</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>1076</v>
+        <v>171</v>
       </c>
       <c r="B415" t="s">
-        <v>1077</v>
+        <v>500</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>263</v>
+        <v>1076</v>
       </c>
       <c r="B416" t="s">
-        <v>501</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>1078</v>
+        <v>263</v>
       </c>
       <c r="B417" t="s">
-        <v>1079</v>
+        <v>501</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>80</v>
+        <v>1078</v>
       </c>
       <c r="B418" t="s">
-        <v>502</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B419" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>191</v>
+        <v>65</v>
       </c>
       <c r="B420" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="B421" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>192</v>
+        <v>123</v>
       </c>
       <c r="B422" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="B423" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B424" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>1179</v>
+        <v>233</v>
       </c>
       <c r="B425" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>31</v>
+        <v>1179</v>
       </c>
       <c r="B426" t="s">
         <v>509</v>
@@ -8286,375 +8292,375 @@
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>1487</v>
+        <v>31</v>
       </c>
       <c r="B427" t="s">
-        <v>1488</v>
+        <v>509</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>30</v>
+        <v>1487</v>
       </c>
       <c r="B428" t="s">
-        <v>510</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B429" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B430" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>1432</v>
+        <v>71</v>
       </c>
       <c r="B431" t="s">
-        <v>1433</v>
+        <v>512</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>306</v>
+        <v>1432</v>
       </c>
       <c r="B432" t="s">
-        <v>513</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>222</v>
+        <v>306</v>
       </c>
       <c r="B433" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>278</v>
+        <v>222</v>
       </c>
       <c r="B434" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B435" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>1383</v>
+        <v>279</v>
       </c>
       <c r="B436" t="s">
-        <v>1384</v>
+        <v>517</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>824</v>
+        <v>1383</v>
       </c>
       <c r="B437" t="s">
-        <v>825</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>48</v>
+        <v>824</v>
       </c>
       <c r="B438" t="s">
-        <v>518</v>
+        <v>825</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="B439" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="B440" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>1365</v>
+        <v>52</v>
       </c>
       <c r="B441" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>223</v>
+        <v>1365</v>
       </c>
       <c r="B442" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>1082</v>
+        <v>223</v>
       </c>
       <c r="B443" t="s">
-        <v>1083</v>
+        <v>521</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>1093</v>
+        <v>1082</v>
       </c>
       <c r="B444" t="s">
-        <v>1096</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>1038</v>
+        <v>1093</v>
       </c>
       <c r="B445" t="s">
-        <v>1039</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>96</v>
+        <v>1038</v>
       </c>
       <c r="B446" t="s">
-        <v>522</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>248</v>
+        <v>96</v>
       </c>
       <c r="B447" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B448" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>94</v>
+        <v>249</v>
       </c>
       <c r="B449" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>1052</v>
+        <v>94</v>
       </c>
       <c r="B450" t="s">
-        <v>1053</v>
+        <v>525</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>212</v>
+        <v>1052</v>
       </c>
       <c r="B451" t="s">
-        <v>526</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>1204</v>
+        <v>212</v>
       </c>
       <c r="B452" t="s">
-        <v>1205</v>
+        <v>526</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>907</v>
+        <v>1204</v>
       </c>
       <c r="B453" t="s">
-        <v>908</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B454" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="B455" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>329</v>
+        <v>909</v>
       </c>
       <c r="B456" t="s">
-        <v>527</v>
+        <v>910</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>1407</v>
+        <v>329</v>
       </c>
       <c r="B457" t="s">
-        <v>1408</v>
+        <v>527</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="B458" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>1054</v>
+        <v>1409</v>
       </c>
       <c r="B459" t="s">
-        <v>1055</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>986</v>
+        <v>1054</v>
       </c>
       <c r="B460" t="s">
-        <v>987</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>1393</v>
+        <v>986</v>
       </c>
       <c r="B461" t="s">
-        <v>1394</v>
+        <v>987</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>982</v>
+        <v>1393</v>
       </c>
       <c r="B462" t="s">
-        <v>983</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B463" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>82</v>
+        <v>984</v>
       </c>
       <c r="B464" t="s">
-        <v>528</v>
+        <v>985</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>765</v>
+        <v>82</v>
       </c>
       <c r="B465" t="s">
-        <v>766</v>
+        <v>528</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>197</v>
+        <v>765</v>
       </c>
       <c r="B466" t="s">
-        <v>529</v>
+        <v>766</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>647</v>
+        <v>197</v>
       </c>
       <c r="B467" t="s">
-        <v>728</v>
+        <v>529</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>1430</v>
+        <v>647</v>
       </c>
       <c r="B468" t="s">
-        <v>1431</v>
+        <v>728</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>1336</v>
+        <v>1430</v>
       </c>
       <c r="B469" t="s">
-        <v>1337</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>814</v>
+        <v>1336</v>
       </c>
       <c r="B470" t="s">
-        <v>815</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>1056</v>
+        <v>814</v>
       </c>
       <c r="B471" t="s">
-        <v>1057</v>
+        <v>815</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>3</v>
+        <v>1056</v>
       </c>
       <c r="B472" t="s">
-        <v>4</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>949</v>
+        <v>3</v>
       </c>
       <c r="B473" t="s">
         <v>4</v>
@@ -8662,7 +8668,7 @@
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B474" t="s">
         <v>4</v>
@@ -8670,1631 +8676,1631 @@
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>657</v>
+        <v>950</v>
       </c>
       <c r="B475" t="s">
-        <v>729</v>
+        <v>4</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>1284</v>
+        <v>657</v>
       </c>
       <c r="B476" t="s">
-        <v>1285</v>
+        <v>729</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>763</v>
+        <v>1284</v>
       </c>
       <c r="B477" t="s">
-        <v>764</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>85</v>
+        <v>763</v>
       </c>
       <c r="B478" t="s">
-        <v>530</v>
+        <v>764</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>1050</v>
+        <v>85</v>
       </c>
       <c r="B479" t="s">
-        <v>1051</v>
+        <v>530</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>822</v>
+        <v>1050</v>
       </c>
       <c r="B480" t="s">
-        <v>823</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>802</v>
+        <v>822</v>
       </c>
       <c r="B481" t="s">
-        <v>803</v>
+        <v>823</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>187</v>
+        <v>802</v>
       </c>
       <c r="B482" t="s">
-        <v>531</v>
+        <v>803</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>820</v>
+        <v>187</v>
       </c>
       <c r="B483" t="s">
-        <v>821</v>
+        <v>531</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>925</v>
+        <v>820</v>
       </c>
       <c r="B484" t="s">
-        <v>1111</v>
+        <v>821</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>1436</v>
+        <v>925</v>
       </c>
       <c r="B485" t="s">
-        <v>1437</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>855</v>
+        <v>1436</v>
       </c>
       <c r="B486" t="s">
-        <v>856</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>1424</v>
+        <v>855</v>
       </c>
       <c r="B487" t="s">
-        <v>1425</v>
+        <v>856</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>1034</v>
+        <v>1424</v>
       </c>
       <c r="B488" t="s">
-        <v>1035</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>791</v>
+        <v>1034</v>
       </c>
       <c r="B489" t="s">
-        <v>1112</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B490" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>1478</v>
+        <v>790</v>
       </c>
       <c r="B491" t="s">
-        <v>1479</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="B492" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>13</v>
+        <v>1476</v>
       </c>
       <c r="B493" t="s">
-        <v>14</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>810</v>
+        <v>13</v>
       </c>
       <c r="B494" t="s">
-        <v>811</v>
+        <v>14</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>1214</v>
+        <v>810</v>
       </c>
       <c r="B495" t="s">
-        <v>1215</v>
+        <v>811</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>186</v>
+        <v>1214</v>
       </c>
       <c r="B496" t="s">
-        <v>532</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>804</v>
+        <v>186</v>
       </c>
       <c r="B497" t="s">
-        <v>805</v>
+        <v>532</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>319</v>
+        <v>804</v>
       </c>
       <c r="B498" t="s">
-        <v>533</v>
+        <v>805</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>649</v>
+        <v>319</v>
       </c>
       <c r="B499" t="s">
-        <v>730</v>
+        <v>533</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>848</v>
+        <v>649</v>
       </c>
       <c r="B500" t="s">
-        <v>849</v>
+        <v>730</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>651</v>
+        <v>848</v>
       </c>
       <c r="B501" t="s">
-        <v>731</v>
+        <v>849</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="B502" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>1186</v>
+        <v>646</v>
       </c>
       <c r="B503" t="s">
-        <v>1187</v>
+        <v>732</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>256</v>
+        <v>1186</v>
       </c>
       <c r="B504" t="s">
-        <v>534</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B505" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B506" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>188</v>
+        <v>261</v>
       </c>
       <c r="B507" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B508" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>927</v>
+        <v>190</v>
       </c>
       <c r="B509" t="s">
-        <v>928</v>
+        <v>538</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>1021</v>
+        <v>927</v>
       </c>
       <c r="B510" t="s">
-        <v>1022</v>
+        <v>928</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>1202</v>
+        <v>1021</v>
       </c>
       <c r="B511" t="s">
-        <v>1203</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>209</v>
+        <v>1202</v>
       </c>
       <c r="B512" t="s">
-        <v>539</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>1403</v>
+        <v>209</v>
       </c>
       <c r="B513" t="s">
-        <v>1404</v>
+        <v>539</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>1294</v>
+        <v>1403</v>
       </c>
       <c r="B514" t="s">
-        <v>1295</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>844</v>
+        <v>1294</v>
       </c>
       <c r="B515" t="s">
-        <v>845</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>143</v>
+        <v>844</v>
       </c>
       <c r="B516" t="s">
-        <v>540</v>
+        <v>845</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B517" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>1182</v>
+        <v>140</v>
       </c>
       <c r="B518" t="s">
-        <v>1183</v>
+        <v>541</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>1282</v>
+        <v>1182</v>
       </c>
       <c r="B519" t="s">
-        <v>1283</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>254</v>
+        <v>1282</v>
       </c>
       <c r="B520" t="s">
-        <v>542</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>330</v>
+        <v>254</v>
       </c>
       <c r="B521" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="B522" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="B523" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>73</v>
+        <v>234</v>
       </c>
       <c r="B524" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>341</v>
+        <v>73</v>
       </c>
       <c r="B525" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>308</v>
+        <v>341</v>
       </c>
       <c r="B526" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>836</v>
+        <v>308</v>
       </c>
       <c r="B527" t="s">
-        <v>837</v>
+        <v>548</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B528" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>220</v>
+        <v>838</v>
       </c>
       <c r="B529" t="s">
-        <v>549</v>
+        <v>839</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>900</v>
+        <v>220</v>
       </c>
       <c r="B530" t="s">
-        <v>901</v>
+        <v>549</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>1359</v>
+        <v>900</v>
       </c>
       <c r="B531" t="s">
-        <v>1360</v>
+        <v>901</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>954</v>
+        <v>1359</v>
       </c>
       <c r="B532" t="s">
-        <v>955</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>1167</v>
+        <v>954</v>
       </c>
       <c r="B533" t="s">
-        <v>1168</v>
+        <v>955</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>227</v>
+        <v>1167</v>
       </c>
       <c r="B534" t="s">
-        <v>550</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>333</v>
+        <v>227</v>
       </c>
       <c r="B535" t="s">
-        <v>1140</v>
+        <v>550</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>962</v>
+        <v>333</v>
       </c>
       <c r="B536" t="s">
-        <v>963</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>771</v>
+        <v>962</v>
       </c>
       <c r="B537" t="s">
-        <v>772</v>
+        <v>963</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>294</v>
+        <v>771</v>
       </c>
       <c r="B538" t="s">
-        <v>551</v>
+        <v>772</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>943</v>
+        <v>294</v>
       </c>
       <c r="B539" t="s">
-        <v>944</v>
+        <v>551</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>338</v>
+        <v>943</v>
       </c>
       <c r="B540" t="s">
-        <v>552</v>
+        <v>944</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>773</v>
+        <v>338</v>
       </c>
       <c r="B541" t="s">
-        <v>772</v>
+        <v>552</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>1298</v>
+        <v>773</v>
       </c>
       <c r="B542" t="s">
-        <v>1299</v>
+        <v>772</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>339</v>
+        <v>1298</v>
       </c>
       <c r="B543" t="s">
-        <v>553</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B544" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>638</v>
+        <v>340</v>
       </c>
       <c r="B545" t="s">
-        <v>733</v>
+        <v>554</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>39</v>
+        <v>638</v>
       </c>
       <c r="B546" t="s">
-        <v>1496</v>
+        <v>733</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B547" t="s">
-        <v>1489</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>342</v>
+        <v>38</v>
       </c>
       <c r="B548" t="s">
-        <v>555</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>107</v>
+        <v>342</v>
       </c>
       <c r="B549" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>1411</v>
+        <v>107</v>
       </c>
       <c r="B550" t="s">
-        <v>1412</v>
+        <v>556</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>1019</v>
+        <v>1411</v>
       </c>
       <c r="B551" t="s">
-        <v>1020</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>894</v>
+        <v>1019</v>
       </c>
       <c r="B552" t="s">
-        <v>895</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>117</v>
+        <v>894</v>
       </c>
       <c r="B553" t="s">
-        <v>557</v>
+        <v>895</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>1015</v>
+        <v>117</v>
       </c>
       <c r="B554" t="s">
-        <v>1016</v>
+        <v>557</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>98</v>
+        <v>1015</v>
       </c>
       <c r="B555" t="s">
-        <v>558</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B556" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>659</v>
+        <v>99</v>
       </c>
       <c r="B557" t="s">
-        <v>734</v>
+        <v>559</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>1091</v>
+        <v>659</v>
       </c>
       <c r="B558" t="s">
-        <v>1014</v>
+        <v>734</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>816</v>
+        <v>1091</v>
       </c>
       <c r="B559" t="s">
-        <v>817</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>113</v>
+        <v>816</v>
       </c>
       <c r="B560" t="s">
-        <v>560</v>
+        <v>817</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>881</v>
+        <v>113</v>
       </c>
       <c r="B561" t="s">
-        <v>882</v>
+        <v>560</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>45</v>
+        <v>881</v>
       </c>
       <c r="B562" t="s">
-        <v>1110</v>
+        <v>882</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>290</v>
+        <v>45</v>
       </c>
       <c r="B563" t="s">
-        <v>561</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B564" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>47</v>
+        <v>299</v>
       </c>
       <c r="B565" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>840</v>
+        <v>47</v>
       </c>
       <c r="B566" t="s">
-        <v>841</v>
+        <v>563</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>51</v>
+        <v>840</v>
       </c>
       <c r="B567" t="s">
-        <v>564</v>
+        <v>841</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>863</v>
+        <v>51</v>
       </c>
       <c r="B568" t="s">
-        <v>864</v>
+        <v>564</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>114</v>
+        <v>863</v>
       </c>
       <c r="B569" t="s">
-        <v>565</v>
+        <v>864</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>846</v>
+        <v>114</v>
       </c>
       <c r="B570" t="s">
-        <v>847</v>
+        <v>565</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>144</v>
+        <v>846</v>
       </c>
       <c r="B571" t="s">
-        <v>566</v>
+        <v>847</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>1068</v>
+        <v>144</v>
       </c>
       <c r="B572" t="s">
-        <v>1069</v>
+        <v>566</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>176</v>
+        <v>1068</v>
       </c>
       <c r="B573" t="s">
-        <v>567</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>315</v>
+        <v>176</v>
       </c>
       <c r="B574" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>29</v>
+        <v>315</v>
       </c>
       <c r="B575" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>1008</v>
+        <v>29</v>
       </c>
       <c r="B576" t="s">
-        <v>1009</v>
+        <v>569</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>1210</v>
+        <v>1008</v>
       </c>
       <c r="B577" t="s">
-        <v>1211</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>293</v>
+        <v>1210</v>
       </c>
       <c r="B578" t="s">
-        <v>570</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>972</v>
+        <v>293</v>
       </c>
       <c r="B579" t="s">
-        <v>973</v>
+        <v>570</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>1442</v>
+        <v>972</v>
       </c>
       <c r="B580" t="s">
-        <v>1443</v>
+        <v>973</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>301</v>
+        <v>1442</v>
       </c>
       <c r="B581" t="s">
-        <v>571</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>994</v>
+        <v>301</v>
       </c>
       <c r="B582" t="s">
-        <v>995</v>
+        <v>571</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="B583" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>75</v>
+        <v>998</v>
       </c>
       <c r="B584" t="s">
-        <v>572</v>
+        <v>999</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B585" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B586" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>328</v>
+        <v>78</v>
       </c>
       <c r="B587" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>1390</v>
+        <v>328</v>
       </c>
       <c r="B588" t="s">
-        <v>1391</v>
+        <v>575</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>1288</v>
+        <v>1390</v>
       </c>
       <c r="B589" t="s">
-        <v>1289</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>745</v>
+        <v>1288</v>
       </c>
       <c r="B590" t="s">
-        <v>746</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>798</v>
+        <v>745</v>
       </c>
       <c r="B591" t="s">
-        <v>799</v>
+        <v>746</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>1301</v>
+        <v>798</v>
       </c>
       <c r="B592" t="s">
-        <v>1302</v>
+        <v>799</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>135</v>
+        <v>1301</v>
       </c>
       <c r="B593" t="s">
-        <v>576</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>1165</v>
+        <v>135</v>
       </c>
       <c r="B594" t="s">
-        <v>1166</v>
+        <v>576</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>1028</v>
+        <v>1165</v>
       </c>
       <c r="B595" t="s">
-        <v>1029</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>215</v>
+        <v>1028</v>
       </c>
       <c r="B596" t="s">
-        <v>577</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>926</v>
+        <v>215</v>
       </c>
       <c r="B597" t="s">
-        <v>1125</v>
+        <v>577</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>216</v>
+        <v>926</v>
       </c>
       <c r="B598" t="s">
-        <v>1108</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>316</v>
+        <v>216</v>
       </c>
       <c r="B599" t="s">
-        <v>578</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>1070</v>
+        <v>316</v>
       </c>
       <c r="B600" t="s">
-        <v>1071</v>
+        <v>578</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>214</v>
+        <v>1070</v>
       </c>
       <c r="B601" t="s">
-        <v>1109</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>990</v>
+        <v>214</v>
       </c>
       <c r="B602" t="s">
-        <v>991</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B603" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>225</v>
+        <v>992</v>
       </c>
       <c r="B604" t="s">
-        <v>579</v>
+        <v>993</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>1377</v>
+        <v>225</v>
       </c>
       <c r="B605" t="s">
-        <v>1378</v>
+        <v>579</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>939</v>
+        <v>1377</v>
       </c>
       <c r="B606" t="s">
-        <v>940</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>1086</v>
+        <v>939</v>
       </c>
       <c r="B607" t="s">
-        <v>1087</v>
+        <v>940</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>1036</v>
+        <v>1086</v>
       </c>
       <c r="B608" t="s">
-        <v>1037</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>93</v>
+        <v>1036</v>
       </c>
       <c r="B609" t="s">
-        <v>580</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="B610" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>776</v>
+        <v>120</v>
       </c>
       <c r="B611" t="s">
-        <v>777</v>
+        <v>581</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>133</v>
+        <v>776</v>
       </c>
       <c r="B612" t="s">
-        <v>582</v>
+        <v>777</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="B613" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>1290</v>
+        <v>62</v>
       </c>
       <c r="B614" t="s">
-        <v>1291</v>
+        <v>583</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>66</v>
+        <v>1290</v>
       </c>
       <c r="B615" t="s">
-        <v>584</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>818</v>
+        <v>66</v>
       </c>
       <c r="B616" t="s">
-        <v>819</v>
+        <v>584</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>941</v>
+        <v>818</v>
       </c>
       <c r="B617" t="s">
-        <v>942</v>
+        <v>819</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>1194</v>
+        <v>941</v>
       </c>
       <c r="B618" t="s">
-        <v>1195</v>
+        <v>942</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>1303</v>
+        <v>1194</v>
       </c>
       <c r="B619" t="s">
-        <v>1304</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>79</v>
+        <v>1303</v>
       </c>
       <c r="B620" t="s">
-        <v>585</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B621" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="B622" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
-        <v>1163</v>
+        <v>122</v>
       </c>
       <c r="B623" t="s">
-        <v>1164</v>
+        <v>587</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
-        <v>181</v>
+        <v>1163</v>
       </c>
       <c r="B624" t="s">
-        <v>588</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
-        <v>794</v>
+        <v>181</v>
       </c>
       <c r="B625" t="s">
-        <v>795</v>
+        <v>588</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
-        <v>1268</v>
+        <v>794</v>
       </c>
       <c r="B626" t="s">
-        <v>1273</v>
+        <v>795</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>684</v>
+        <v>1268</v>
       </c>
       <c r="B627" t="s">
-        <v>735</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
-        <v>1269</v>
+        <v>684</v>
       </c>
       <c r="B628" t="s">
-        <v>1274</v>
+        <v>735</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B629" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="B630" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="B631" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>1130</v>
+        <v>1272</v>
       </c>
       <c r="B632" t="s">
-        <v>1131</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="B633" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
-        <v>284</v>
+        <v>1128</v>
       </c>
       <c r="B634" t="s">
-        <v>589</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
-        <v>964</v>
+        <v>284</v>
       </c>
       <c r="B635" t="s">
-        <v>965</v>
+        <v>589</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
-        <v>1198</v>
+        <v>964</v>
       </c>
       <c r="B636" t="s">
-        <v>1199</v>
+        <v>965</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
-        <v>834</v>
+        <v>1198</v>
       </c>
       <c r="B637" t="s">
-        <v>835</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
-        <v>283</v>
+        <v>834</v>
       </c>
       <c r="B638" t="s">
-        <v>590</v>
+        <v>835</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
-        <v>875</v>
+        <v>283</v>
       </c>
       <c r="B639" t="s">
-        <v>876</v>
+        <v>590</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
-        <v>1159</v>
+        <v>875</v>
       </c>
       <c r="B640" t="s">
-        <v>1160</v>
+        <v>876</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>749</v>
+        <v>1159</v>
       </c>
       <c r="B641" t="s">
-        <v>750</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
-        <v>1066</v>
+        <v>749</v>
       </c>
       <c r="B642" t="s">
-        <v>1067</v>
+        <v>750</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
-        <v>67</v>
+        <v>1066</v>
       </c>
       <c r="B643" t="s">
-        <v>591</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B644" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
-        <v>1372</v>
+        <v>68</v>
       </c>
       <c r="B645" t="s">
-        <v>1373</v>
+        <v>592</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
-        <v>95</v>
+        <v>1372</v>
       </c>
       <c r="B646" t="s">
-        <v>593</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
-        <v>289</v>
+        <v>95</v>
       </c>
       <c r="B647" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B648" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="B649" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
-        <v>193</v>
+        <v>264</v>
       </c>
       <c r="B650" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
-        <v>1332</v>
+        <v>193</v>
       </c>
       <c r="B651" t="s">
-        <v>1333</v>
+        <v>597</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>892</v>
+        <v>1332</v>
       </c>
       <c r="B652" t="s">
-        <v>893</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
-        <v>44</v>
+        <v>892</v>
       </c>
       <c r="B653" t="s">
-        <v>1107</v>
+        <v>893</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
-        <v>1058</v>
+        <v>44</v>
       </c>
       <c r="B654" t="s">
-        <v>1059</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
-        <v>323</v>
+        <v>1058</v>
       </c>
       <c r="B655" t="s">
-        <v>598</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B656" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
-        <v>842</v>
+        <v>324</v>
       </c>
       <c r="B657" t="s">
-        <v>843</v>
+        <v>599</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
-        <v>879</v>
+        <v>842</v>
       </c>
       <c r="B658" t="s">
-        <v>880</v>
+        <v>843</v>
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
-        <v>1216</v>
+        <v>879</v>
       </c>
       <c r="B659" t="s">
-        <v>1217</v>
+        <v>880</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
-        <v>861</v>
+        <v>1216</v>
       </c>
       <c r="B660" t="s">
-        <v>862</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
-        <v>33</v>
+        <v>861</v>
       </c>
       <c r="B661" t="s">
-        <v>600</v>
+        <v>862</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B662" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
-        <v>1123</v>
+        <v>36</v>
       </c>
       <c r="B663" t="s">
-        <v>1124</v>
+        <v>601</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
-        <v>309</v>
+        <v>1123</v>
       </c>
       <c r="B664" t="s">
-        <v>602</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
       <c r="B665" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
-        <v>302</v>
+        <v>257</v>
       </c>
       <c r="B666" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
-        <v>228</v>
+        <v>302</v>
       </c>
       <c r="B667" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c r="B668" t="s">
-        <v>18</v>
+        <v>605</v>
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
-        <v>648</v>
+        <v>17</v>
       </c>
       <c r="B669" t="s">
-        <v>736</v>
+        <v>18</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
-        <v>1399</v>
+        <v>648</v>
       </c>
       <c r="B670" t="s">
-        <v>1400</v>
+        <v>736</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
-        <v>778</v>
+        <v>1399</v>
       </c>
       <c r="B671" t="s">
-        <v>779</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
-        <v>142</v>
+        <v>778</v>
       </c>
       <c r="B672" t="s">
-        <v>606</v>
+        <v>779</v>
       </c>
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
-        <v>1157</v>
+        <v>142</v>
       </c>
       <c r="B673" t="s">
-        <v>1158</v>
+        <v>606</v>
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
-        <v>947</v>
+        <v>1157</v>
       </c>
       <c r="B674" t="s">
-        <v>948</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
-        <v>54</v>
+        <v>947</v>
       </c>
       <c r="B675" t="s">
-        <v>607</v>
+        <v>948</v>
       </c>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
-        <v>265</v>
+        <v>54</v>
       </c>
       <c r="B676" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
-        <v>967</v>
+        <v>265</v>
       </c>
       <c r="B677" t="s">
-        <v>966</v>
+        <v>608</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
-        <v>1389</v>
+        <v>967</v>
       </c>
       <c r="B678" t="s">
         <v>966</v>
@@ -10302,617 +10308,625 @@
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
-        <v>56</v>
+        <v>1389</v>
       </c>
       <c r="B679" t="s">
-        <v>609</v>
+        <v>966</v>
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
-        <v>1196</v>
+        <v>56</v>
       </c>
       <c r="B680" t="s">
-        <v>1197</v>
+        <v>609</v>
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
-        <v>185</v>
+        <v>1196</v>
       </c>
       <c r="B681" t="s">
-        <v>610</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="B682" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="B683" t="s">
-        <v>1325</v>
+        <v>611</v>
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
-        <v>1323</v>
+        <v>43</v>
       </c>
       <c r="B684" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
-        <v>1446</v>
+        <v>1323</v>
       </c>
       <c r="B685" t="s">
-        <v>1448</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B686" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
-        <v>40</v>
+        <v>1447</v>
       </c>
       <c r="B687" t="s">
-        <v>1480</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
-        <v>1321</v>
+        <v>40</v>
       </c>
       <c r="B688" t="s">
-        <v>1322</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
-        <v>1149</v>
+        <v>1321</v>
       </c>
       <c r="B689" t="s">
-        <v>1150</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
-        <v>165</v>
+        <v>1149</v>
       </c>
       <c r="B690" t="s">
-        <v>612</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
-        <v>1278</v>
+        <v>165</v>
       </c>
       <c r="B691" t="s">
-        <v>1279</v>
+        <v>612</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="B692" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
-        <v>1467</v>
+        <v>1280</v>
       </c>
       <c r="B693" t="s">
-        <v>1468</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="B694" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
-        <v>12</v>
+        <v>1469</v>
       </c>
       <c r="B695" t="s">
-        <v>11</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
-        <v>250</v>
+        <v>12</v>
       </c>
       <c r="B696" t="s">
-        <v>613</v>
+        <v>11</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="B697" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
-        <v>1030</v>
+        <v>27</v>
       </c>
       <c r="B698" t="s">
-        <v>1031</v>
+        <v>614</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
-        <v>28</v>
+        <v>1030</v>
       </c>
       <c r="B699" t="s">
-        <v>615</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
-        <v>1184</v>
+        <v>28</v>
       </c>
       <c r="B700" t="s">
-        <v>1185</v>
+        <v>615</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
-        <v>255</v>
+        <v>1184</v>
       </c>
       <c r="B701" t="s">
-        <v>616</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
-        <v>1313</v>
+        <v>255</v>
       </c>
       <c r="B702" t="s">
-        <v>1318</v>
+        <v>616</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
-        <v>788</v>
+        <v>1313</v>
       </c>
       <c r="B703" t="s">
-        <v>789</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
-        <v>267</v>
+        <v>788</v>
       </c>
       <c r="B704" t="s">
-        <v>617</v>
+        <v>789</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
-        <v>654</v>
+        <v>267</v>
       </c>
       <c r="B705" t="s">
-        <v>737</v>
+        <v>617</v>
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B706" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
-        <v>139</v>
+        <v>655</v>
       </c>
       <c r="B707" t="s">
-        <v>618</v>
+        <v>738</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="B708" t="s">
-        <v>2</v>
+        <v>618</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="B709" t="s">
-        <v>619</v>
+        <v>2</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
-        <v>1328</v>
+        <v>105</v>
       </c>
       <c r="B710" t="s">
-        <v>1329</v>
+        <v>619</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
-        <v>1024</v>
+        <v>1328</v>
       </c>
       <c r="B711" t="s">
-        <v>1106</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
-        <v>857</v>
+        <v>1024</v>
       </c>
       <c r="B712" t="s">
-        <v>858</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
-        <v>1428</v>
+        <v>857</v>
       </c>
       <c r="B713" t="s">
-        <v>1429</v>
+        <v>858</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
-        <v>1025</v>
+        <v>1428</v>
       </c>
       <c r="B714" t="s">
-        <v>1105</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A715" t="s">
-        <v>292</v>
+        <v>1025</v>
       </c>
       <c r="B715" t="s">
-        <v>620</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A716" t="s">
-        <v>8</v>
+        <v>292</v>
       </c>
       <c r="B716" t="s">
-        <v>11</v>
+        <v>620</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
-        <v>334</v>
+        <v>8</v>
       </c>
       <c r="B717" t="s">
-        <v>621</v>
+        <v>11</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
-        <v>1370</v>
+        <v>334</v>
       </c>
       <c r="B718" t="s">
-        <v>1371</v>
+        <v>621</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
-        <v>1330</v>
+        <v>1370</v>
       </c>
       <c r="B719" t="s">
-        <v>1331</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
-        <v>331</v>
+        <v>1330</v>
       </c>
       <c r="B720" t="s">
-        <v>622</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="B721" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
-        <v>318</v>
+        <v>259</v>
       </c>
       <c r="B722" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
-        <v>851</v>
+        <v>318</v>
       </c>
       <c r="B723" t="s">
-        <v>852</v>
+        <v>624</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
-        <v>1153</v>
+        <v>851</v>
       </c>
       <c r="B724" t="s">
-        <v>1154</v>
+        <v>852</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
-        <v>268</v>
+        <v>1153</v>
       </c>
       <c r="B725" t="s">
-        <v>625</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B726" t="s">
-        <v>1100</v>
+        <v>625</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B727" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B728" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B729" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A730" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B730" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B731" t="s">
-        <v>1099</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
-        <v>92</v>
+        <v>272</v>
       </c>
       <c r="B732" t="s">
-        <v>626</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
-        <v>200</v>
+        <v>92</v>
       </c>
       <c r="B733" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B734" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
-        <v>1206</v>
+        <v>203</v>
       </c>
       <c r="B735" t="s">
-        <v>1207</v>
+        <v>628</v>
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
-        <v>172</v>
+        <v>1206</v>
       </c>
       <c r="B736" t="s">
-        <v>629</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A737" t="s">
-        <v>1459</v>
+        <v>172</v>
       </c>
       <c r="B737" t="s">
-        <v>1460</v>
+        <v>629</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B738" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A739" t="s">
         <v>686</v>
       </c>
-      <c r="B738" t="s">
+      <c r="B739" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="739" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A739" t="s">
+    <row r="740" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A740" t="s">
         <v>1454</v>
       </c>
-      <c r="B739" s="1" t="s">
+      <c r="B740" s="1" t="s">
         <v>1455</v>
-      </c>
-    </row>
-    <row r="740" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A740" t="s">
-        <v>252</v>
-      </c>
-      <c r="B740" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
-        <v>687</v>
+        <v>252</v>
       </c>
       <c r="B741" t="s">
-        <v>740</v>
+        <v>630</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
-        <v>189</v>
+        <v>687</v>
       </c>
       <c r="B742" t="s">
-        <v>1398</v>
+        <v>740</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
-        <v>980</v>
+        <v>189</v>
       </c>
       <c r="B743" t="s">
-        <v>981</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A744" t="s">
-        <v>311</v>
+        <v>980</v>
       </c>
       <c r="B744" t="s">
-        <v>631</v>
+        <v>981</v>
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A745" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B745" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A746" t="s">
-        <v>1023</v>
+        <v>312</v>
       </c>
       <c r="B746" t="s">
-        <v>1453</v>
+        <v>632</v>
       </c>
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A747" t="s">
-        <v>1452</v>
+        <v>1023</v>
       </c>
       <c r="B747" t="s">
-        <v>1473</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A748" t="s">
-        <v>996</v>
+        <v>1452</v>
       </c>
       <c r="B748" t="s">
-        <v>997</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A749" t="s">
-        <v>81</v>
+        <v>996</v>
       </c>
       <c r="B749" t="s">
-        <v>633</v>
+        <v>997</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A750" t="s">
-        <v>644</v>
+        <v>81</v>
       </c>
       <c r="B750" t="s">
-        <v>741</v>
+        <v>633</v>
       </c>
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A751" t="s">
-        <v>913</v>
+        <v>644</v>
       </c>
       <c r="B751" t="s">
-        <v>914</v>
+        <v>741</v>
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A752" t="s">
-        <v>635</v>
+        <v>913</v>
       </c>
       <c r="B752" t="s">
-        <v>742</v>
+        <v>914</v>
       </c>
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A753" t="s">
-        <v>960</v>
+        <v>635</v>
       </c>
       <c r="B753" t="s">
-        <v>961</v>
+        <v>742</v>
       </c>
     </row>
     <row r="754" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A754" t="s">
-        <v>1141</v>
+        <v>960</v>
       </c>
       <c r="B754" t="s">
-        <v>1142</v>
+        <v>961</v>
       </c>
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A755" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B755" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A756" t="s">
         <v>1368</v>
       </c>
-      <c r="B755" t="s">
+      <c r="B756" t="s">
         <v>1369</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B53FFCD-0853-4092-90B1-EEDA89A3A6F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614EA563-069F-49FA-91A8-3FF46D573559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="1501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="1503">
   <si>
     <t>trigger</t>
   </si>
@@ -3327,24 +3327,12 @@
     <t>loss of fat plane</t>
   </si>
   <si>
-    <t>Urinary bladder is partially filled with Foley's in situ</t>
-  </si>
-  <si>
     <t>Urinary bladder is empty</t>
   </si>
   <si>
     <t>Urinary bladder is empty with Foley's in situ</t>
   </si>
   <si>
-    <t>Urinary bladder is minimally filled</t>
-  </si>
-  <si>
-    <t>Urinary bladder is minimally filled with Foley's in situ</t>
-  </si>
-  <si>
-    <t>Urinary bladder is partially filled</t>
-  </si>
-  <si>
     <t>T2 high signal intensity with convex free margin is noted in right maxillary sinus - polyp/ retention cyst</t>
   </si>
   <si>
@@ -4531,6 +4519,24 @@
   </si>
   <si>
     <t>Gallbladder is not visualized with hyperdense clips in gallbladder fossa - suggestive of post-cholecystectomy status</t>
+  </si>
+  <si>
+    <t>tg</t>
+  </si>
+  <si>
+    <t>thyroid gland</t>
+  </si>
+  <si>
+    <t>Urinary bladder is minimally distended</t>
+  </si>
+  <si>
+    <t>Urinary bladder is minimally distended with Foley's in situ</t>
+  </si>
+  <si>
+    <t>Urinary bladder is partially distended</t>
+  </si>
+  <si>
+    <t>Urinary bladder is partially distended with Foley's in situ</t>
   </si>
 </sst>
 </file>
@@ -4599,10 +4605,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B756" totalsRowShown="0">
-  <autoFilter ref="A1:B756" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B756">
-    <sortCondition ref="A1:A756"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B757" totalsRowShown="0">
+  <autoFilter ref="A1:B757" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B757">
+    <sortCondition ref="A1:A757"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4875,7 +4881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B756"/>
+  <dimension ref="A1:B757"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -4900,10 +4906,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="B3" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -5132,10 +5138,10 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="B32" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
@@ -5212,18 +5218,18 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="B42" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="B43" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
@@ -5236,10 +5242,10 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
       <c r="B45" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
@@ -5295,7 +5301,7 @@
         <v>246</v>
       </c>
       <c r="B52" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
@@ -5356,10 +5362,10 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="B60" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
@@ -5436,18 +5442,18 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>1485</v>
+        <v>1481</v>
       </c>
       <c r="B70" t="s">
-        <v>1486</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
       <c r="B71" t="s">
-        <v>1484</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
@@ -5460,10 +5466,10 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="B73" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
@@ -5476,10 +5482,10 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="B75" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
@@ -5492,10 +5498,10 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="B77" t="s">
-        <v>1209</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
@@ -5516,10 +5522,10 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="B80" t="s">
-        <v>1219</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
@@ -5532,10 +5538,10 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="B82" t="s">
-        <v>1221</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
@@ -5548,10 +5554,10 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
       <c r="B84" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
@@ -5564,10 +5570,10 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="B86" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
@@ -5580,10 +5586,10 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="B88" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
@@ -5596,10 +5602,10 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="B90" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
@@ -5612,10 +5618,10 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="B92" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
@@ -5628,10 +5634,10 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="B94" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
@@ -5732,10 +5738,10 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="B107" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
@@ -5767,7 +5773,7 @@
         <v>41</v>
       </c>
       <c r="B111" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
@@ -5780,10 +5786,10 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="B113" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
@@ -5828,10 +5834,10 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="B119" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
@@ -5868,10 +5874,10 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="B124" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
@@ -5892,10 +5898,10 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="B127" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
@@ -5908,10 +5914,10 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="B129" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
@@ -5964,10 +5970,10 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="B136" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
@@ -5999,15 +6005,15 @@
         <v>104</v>
       </c>
       <c r="B140" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>1494</v>
+        <v>1490</v>
       </c>
       <c r="B141" t="s">
-        <v>1495</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
@@ -6031,12 +6037,12 @@
         <v>102</v>
       </c>
       <c r="B144" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="B145" t="s">
         <v>403</v>
@@ -6068,18 +6074,18 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="B149" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="B150" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
@@ -6100,10 +6106,10 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="B153" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
@@ -6140,34 +6146,34 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="B158" t="s">
-        <v>1439</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="B159" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
       <c r="B160" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="B161" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
@@ -6180,10 +6186,10 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="B163" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
@@ -6196,10 +6202,10 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="B165" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
@@ -6212,10 +6218,10 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>1235</v>
+        <v>1231</v>
       </c>
       <c r="B167" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
@@ -6228,10 +6234,10 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="B169" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
@@ -6244,10 +6250,10 @@
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="B171" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
@@ -6260,10 +6266,10 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="B173" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
@@ -6276,10 +6282,10 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="B175" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
@@ -6292,10 +6298,10 @@
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="B177" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
@@ -6308,10 +6314,10 @@
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="B179" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
@@ -6324,10 +6330,10 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="B181" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
@@ -6351,7 +6357,7 @@
         <v>211</v>
       </c>
       <c r="B184" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
@@ -6359,28 +6365,28 @@
         <v>213</v>
       </c>
       <c r="B185" t="s">
-        <v>1441</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
       <c r="B186" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="B187" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="B188" t="s">
         <v>406</v>
@@ -6391,7 +6397,7 @@
         <v>149</v>
       </c>
       <c r="B189" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
@@ -6407,7 +6413,7 @@
         <v>245</v>
       </c>
       <c r="B191" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
@@ -6444,10 +6450,10 @@
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
       <c r="B196" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
@@ -6468,18 +6474,18 @@
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>1147</v>
+        <v>1143</v>
       </c>
       <c r="B199" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="B200" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
@@ -6556,10 +6562,10 @@
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="B210" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
@@ -6607,23 +6613,23 @@
         <v>24</v>
       </c>
       <c r="B216" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="B217" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="B218" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
@@ -6636,10 +6642,10 @@
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
       <c r="B220" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
@@ -6668,10 +6674,10 @@
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="B224" t="s">
-        <v>1423</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
@@ -6684,15 +6690,15 @@
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="B226" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
       <c r="B227" t="s">
         <v>883</v>
@@ -6700,10 +6706,10 @@
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="B228" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
@@ -6716,50 +6722,50 @@
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="B230" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="B231" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="B232" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
       <c r="B233" t="s">
-        <v>1491</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="B234" t="s">
-        <v>1376</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
       <c r="B235" t="s">
-        <v>1493</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
@@ -6780,18 +6786,18 @@
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="B238" t="s">
-        <v>1287</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="B239" t="s">
-        <v>1213</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
@@ -6828,10 +6834,10 @@
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="B244" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
@@ -6892,10 +6898,10 @@
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
       <c r="B252" t="s">
-        <v>1482</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
@@ -6940,10 +6946,10 @@
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>1413</v>
+        <v>1409</v>
       </c>
       <c r="B258" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
@@ -6980,26 +6986,26 @@
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="B263" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="B264" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="B265" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
@@ -7036,26 +7042,26 @@
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="B270" t="s">
-        <v>1396</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="B271" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="B272" t="s">
-        <v>1445</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
@@ -7063,7 +7069,7 @@
         <v>275</v>
       </c>
       <c r="B273" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
@@ -7071,15 +7077,15 @@
         <v>850</v>
       </c>
       <c r="B274" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="B275" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
@@ -7100,18 +7106,18 @@
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B278" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>1200</v>
+        <v>1196</v>
       </c>
       <c r="B279" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
@@ -7140,10 +7146,10 @@
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="B283" t="s">
-        <v>1312</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
@@ -7223,15 +7229,15 @@
         <v>23</v>
       </c>
       <c r="B293" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B294" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
@@ -7244,10 +7250,10 @@
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="B296" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
@@ -7260,10 +7266,10 @@
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
       <c r="B298" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
@@ -7356,10 +7362,10 @@
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
       <c r="B310" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
@@ -7380,10 +7386,10 @@
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="B313" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
@@ -7396,34 +7402,34 @@
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="B315" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
       <c r="B316" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
       <c r="B317" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="B318" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
@@ -7436,34 +7442,34 @@
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="B320" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>1347</v>
+        <v>1343</v>
       </c>
       <c r="B321" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="B322" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
       <c r="B323" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
@@ -7508,10 +7514,10 @@
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
       <c r="B329" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
@@ -7588,10 +7594,10 @@
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="B339" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
@@ -7676,10 +7682,10 @@
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="B350" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
@@ -7724,10 +7730,10 @@
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="B356" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
@@ -7748,10 +7754,10 @@
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="B359" t="s">
-        <v>1354</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
@@ -7772,10 +7778,10 @@
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="B362" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
@@ -7828,10 +7834,10 @@
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="B369" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
@@ -7844,10 +7850,10 @@
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="B371" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
@@ -7860,10 +7866,10 @@
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="B373" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
@@ -7876,10 +7882,10 @@
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="B375" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
@@ -7892,10 +7898,10 @@
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="B377" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
@@ -7908,10 +7914,10 @@
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="B379" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
@@ -7956,10 +7962,10 @@
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="B385" t="s">
-        <v>1435</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
@@ -7972,10 +7978,10 @@
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="B387" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
@@ -7988,10 +7994,10 @@
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>1173</v>
+        <v>1169</v>
       </c>
       <c r="B389" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
@@ -8100,10 +8106,10 @@
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="B403" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
@@ -8135,7 +8141,7 @@
         <v>207</v>
       </c>
       <c r="B407" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
@@ -8143,7 +8149,7 @@
         <v>951</v>
       </c>
       <c r="B408" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
@@ -8159,7 +8165,7 @@
         <v>206</v>
       </c>
       <c r="B410" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
@@ -8284,7 +8290,7 @@
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="B426" t="s">
         <v>509</v>
@@ -8300,10 +8306,10 @@
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
       <c r="B428" t="s">
-        <v>1488</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
@@ -8332,10 +8338,10 @@
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="B432" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
@@ -8372,10 +8378,10 @@
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="B437" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
@@ -8412,7 +8418,7 @@
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="B442" t="s">
         <v>515</v>
@@ -8500,10 +8506,10 @@
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="B453" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
@@ -8540,18 +8546,18 @@
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B458" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="B459" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
@@ -8572,10 +8578,10 @@
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>1393</v>
+        <v>1389</v>
       </c>
       <c r="B462" t="s">
-        <v>1394</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
@@ -8628,18 +8634,18 @@
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>1430</v>
+        <v>1426</v>
       </c>
       <c r="B469" t="s">
-        <v>1431</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="B470" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
@@ -8692,10 +8698,10 @@
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="B477" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
@@ -8759,15 +8765,15 @@
         <v>925</v>
       </c>
       <c r="B485" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
       <c r="B486" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
@@ -8780,10 +8786,10 @@
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>1424</v>
+        <v>1420</v>
       </c>
       <c r="B488" t="s">
-        <v>1425</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
@@ -8799,7 +8805,7 @@
         <v>791</v>
       </c>
       <c r="B490" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
@@ -8807,23 +8813,23 @@
         <v>790</v>
       </c>
       <c r="B491" t="s">
-        <v>1113</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>1478</v>
+        <v>1474</v>
       </c>
       <c r="B492" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
       <c r="B493" t="s">
-        <v>1477</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
@@ -8844,10 +8850,10 @@
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>1214</v>
+        <v>1210</v>
       </c>
       <c r="B496" t="s">
-        <v>1215</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
@@ -8908,10 +8914,10 @@
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="B504" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
@@ -8972,10 +8978,10 @@
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>1202</v>
+        <v>1198</v>
       </c>
       <c r="B512" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
@@ -8988,18 +8994,18 @@
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B514" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="B515" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
@@ -9028,18 +9034,18 @@
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="B519" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="B520" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
@@ -9132,10 +9138,10 @@
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="B532" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
@@ -9148,10 +9154,10 @@
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="B534" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
@@ -9167,7 +9173,7 @@
         <v>333</v>
       </c>
       <c r="B536" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
@@ -9220,10 +9226,10 @@
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="B543" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
@@ -9255,7 +9261,7 @@
         <v>39</v>
       </c>
       <c r="B547" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
@@ -9263,7 +9269,7 @@
         <v>38</v>
       </c>
       <c r="B548" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
@@ -9284,10 +9290,10 @@
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B551" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
@@ -9383,7 +9389,7 @@
         <v>45</v>
       </c>
       <c r="B563" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
@@ -9500,10 +9506,10 @@
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="B578" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
@@ -9524,10 +9530,10 @@
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
       <c r="B581" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
@@ -9588,18 +9594,18 @@
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
       <c r="B589" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="B590" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
@@ -9620,10 +9626,10 @@
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
       <c r="B593" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
@@ -9636,10 +9642,10 @@
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="B595" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
@@ -9663,7 +9669,7 @@
         <v>926</v>
       </c>
       <c r="B598" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
@@ -9671,7 +9677,7 @@
         <v>216</v>
       </c>
       <c r="B599" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
@@ -9695,7 +9701,7 @@
         <v>214</v>
       </c>
       <c r="B602" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
@@ -9724,10 +9730,10 @@
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
       <c r="B606" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
@@ -9796,10 +9802,10 @@
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="B615" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
@@ -9828,18 +9834,18 @@
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="B619" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="B620" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
@@ -9868,10 +9874,10 @@
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="B624" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.35">
@@ -9892,10 +9898,10 @@
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="B627" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.35">
@@ -9908,50 +9914,50 @@
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="B629" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="B630" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="B631" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="B632" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="B633" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="B634" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.35">
@@ -9972,10 +9978,10 @@
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
-        <v>1198</v>
+        <v>1194</v>
       </c>
       <c r="B637" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.35">
@@ -10004,10 +10010,10 @@
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="B641" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.35">
@@ -10044,10 +10050,10 @@
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
       <c r="B646" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.35">
@@ -10092,10 +10098,10 @@
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="B652" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.35">
@@ -10111,7 +10117,7 @@
         <v>44</v>
       </c>
       <c r="B654" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.35">
@@ -10156,10 +10162,10 @@
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="B660" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.35">
@@ -10188,10 +10194,10 @@
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="B664" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.35">
@@ -10244,10 +10250,10 @@
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B671" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.35">
@@ -10268,10 +10274,10 @@
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
       <c r="B674" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.35">
@@ -10308,7 +10314,7 @@
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
-        <v>1389</v>
+        <v>1385</v>
       </c>
       <c r="B679" t="s">
         <v>966</v>
@@ -10324,10 +10330,10 @@
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="B681" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.35">
@@ -10351,31 +10357,31 @@
         <v>43</v>
       </c>
       <c r="B684" t="s">
-        <v>1325</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="B685" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
-        <v>1446</v>
+        <v>1442</v>
       </c>
       <c r="B686" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="B687" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.35">
@@ -10383,23 +10389,23 @@
         <v>40</v>
       </c>
       <c r="B688" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="B689" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="B690" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.35">
@@ -10412,34 +10418,34 @@
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="B692" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="B693" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
-        <v>1467</v>
+        <v>1463</v>
       </c>
       <c r="B694" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
       <c r="B695" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.35">
@@ -10484,10 +10490,10 @@
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="B701" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.35">
@@ -10500,434 +10506,442 @@
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
-        <v>1313</v>
+        <v>1497</v>
       </c>
       <c r="B703" t="s">
-        <v>1318</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
-        <v>788</v>
+        <v>1309</v>
       </c>
       <c r="B704" t="s">
-        <v>789</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
-        <v>267</v>
+        <v>788</v>
       </c>
       <c r="B705" t="s">
-        <v>617</v>
+        <v>789</v>
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
-        <v>654</v>
+        <v>267</v>
       </c>
       <c r="B706" t="s">
-        <v>737</v>
+        <v>617</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B707" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
-        <v>139</v>
+        <v>655</v>
       </c>
       <c r="B708" t="s">
-        <v>618</v>
+        <v>738</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="B709" t="s">
-        <v>2</v>
+        <v>618</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="B710" t="s">
-        <v>619</v>
+        <v>2</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
-        <v>1328</v>
+        <v>105</v>
       </c>
       <c r="B711" t="s">
-        <v>1329</v>
+        <v>619</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
-        <v>1024</v>
+        <v>1324</v>
       </c>
       <c r="B712" t="s">
-        <v>1106</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
-        <v>857</v>
+        <v>1024</v>
       </c>
       <c r="B713" t="s">
-        <v>858</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
-        <v>1428</v>
+        <v>857</v>
       </c>
       <c r="B714" t="s">
-        <v>1429</v>
+        <v>858</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A715" t="s">
-        <v>1025</v>
+        <v>1424</v>
       </c>
       <c r="B715" t="s">
-        <v>1105</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A716" t="s">
-        <v>292</v>
+        <v>1025</v>
       </c>
       <c r="B716" t="s">
-        <v>620</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
-        <v>8</v>
+        <v>292</v>
       </c>
       <c r="B717" t="s">
-        <v>11</v>
+        <v>620</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
-        <v>334</v>
+        <v>8</v>
       </c>
       <c r="B718" t="s">
-        <v>621</v>
+        <v>11</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
-        <v>1370</v>
+        <v>334</v>
       </c>
       <c r="B719" t="s">
-        <v>1371</v>
+        <v>621</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
-        <v>1330</v>
+        <v>1366</v>
       </c>
       <c r="B720" t="s">
-        <v>1331</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
-        <v>331</v>
+        <v>1326</v>
       </c>
       <c r="B721" t="s">
-        <v>622</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="B722" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
-        <v>318</v>
+        <v>259</v>
       </c>
       <c r="B723" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
-        <v>851</v>
+        <v>318</v>
       </c>
       <c r="B724" t="s">
-        <v>852</v>
+        <v>624</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
-        <v>1153</v>
+        <v>851</v>
       </c>
       <c r="B725" t="s">
-        <v>1154</v>
+        <v>852</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
-        <v>268</v>
+        <v>1149</v>
       </c>
       <c r="B726" t="s">
-        <v>625</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B727" t="s">
-        <v>1100</v>
+        <v>625</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B728" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B729" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A730" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B730" t="s">
-        <v>1103</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B731" t="s">
-        <v>1104</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B732" t="s">
-        <v>1099</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
-        <v>92</v>
+        <v>272</v>
       </c>
       <c r="B733" t="s">
-        <v>626</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
-        <v>200</v>
+        <v>92</v>
       </c>
       <c r="B734" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B735" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
-        <v>1206</v>
+        <v>203</v>
       </c>
       <c r="B736" t="s">
-        <v>1207</v>
+        <v>628</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A737" t="s">
-        <v>172</v>
+        <v>1202</v>
       </c>
       <c r="B737" t="s">
-        <v>629</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
-        <v>1459</v>
+        <v>172</v>
       </c>
       <c r="B738" t="s">
-        <v>1460</v>
+        <v>629</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B739" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A740" t="s">
         <v>686</v>
       </c>
-      <c r="B739" t="s">
+      <c r="B740" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="740" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A740" t="s">
-        <v>1454</v>
-      </c>
-      <c r="B740" s="1" t="s">
-        <v>1455</v>
-      </c>
-    </row>
-    <row r="741" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
-        <v>252</v>
-      </c>
-      <c r="B741" t="s">
-        <v>630</v>
+        <v>1450</v>
+      </c>
+      <c r="B741" s="1" t="s">
+        <v>1451</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
-        <v>687</v>
+        <v>252</v>
       </c>
       <c r="B742" t="s">
-        <v>740</v>
+        <v>630</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
-        <v>189</v>
+        <v>687</v>
       </c>
       <c r="B743" t="s">
-        <v>1398</v>
+        <v>740</v>
       </c>
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A744" t="s">
-        <v>980</v>
+        <v>189</v>
       </c>
       <c r="B744" t="s">
-        <v>981</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A745" t="s">
-        <v>311</v>
+        <v>980</v>
       </c>
       <c r="B745" t="s">
-        <v>631</v>
+        <v>981</v>
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A746" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B746" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A747" t="s">
-        <v>1023</v>
+        <v>312</v>
       </c>
       <c r="B747" t="s">
-        <v>1453</v>
+        <v>632</v>
       </c>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A748" t="s">
-        <v>1452</v>
+        <v>1023</v>
       </c>
       <c r="B748" t="s">
-        <v>1473</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A749" t="s">
-        <v>996</v>
+        <v>1448</v>
       </c>
       <c r="B749" t="s">
-        <v>997</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A750" t="s">
-        <v>81</v>
+        <v>996</v>
       </c>
       <c r="B750" t="s">
-        <v>633</v>
+        <v>997</v>
       </c>
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A751" t="s">
-        <v>644</v>
+        <v>81</v>
       </c>
       <c r="B751" t="s">
-        <v>741</v>
+        <v>633</v>
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A752" t="s">
-        <v>913</v>
+        <v>644</v>
       </c>
       <c r="B752" t="s">
-        <v>914</v>
+        <v>741</v>
       </c>
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A753" t="s">
-        <v>635</v>
+        <v>913</v>
       </c>
       <c r="B753" t="s">
-        <v>742</v>
+        <v>914</v>
       </c>
     </row>
     <row r="754" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A754" t="s">
-        <v>960</v>
+        <v>635</v>
       </c>
       <c r="B754" t="s">
-        <v>961</v>
+        <v>742</v>
       </c>
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A755" t="s">
-        <v>1141</v>
+        <v>960</v>
       </c>
       <c r="B755" t="s">
-        <v>1142</v>
+        <v>961</v>
       </c>
     </row>
     <row r="756" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A756" t="s">
-        <v>1368</v>
+        <v>1137</v>
       </c>
       <c r="B756" t="s">
-        <v>1369</v>
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A757" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B757" t="s">
+        <v>1365</v>
       </c>
     </row>
   </sheetData>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614EA563-069F-49FA-91A8-3FF46D573559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88EEE51-053F-4A6F-9A08-3AED673D40A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3639,9 +3639,6 @@
     <t>usg</t>
   </si>
   <si>
-    <t>ultrasound</t>
-  </si>
-  <si>
     <t>bs</t>
   </si>
   <si>
@@ -4537,6 +4534,9 @@
   </si>
   <si>
     <t>Urinary bladder is partially distended with Foley's in situ</t>
+  </si>
+  <si>
+    <t>ultrasonography</t>
   </si>
 </sst>
 </file>
@@ -5242,10 +5242,10 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="B45" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
@@ -5442,18 +5442,18 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B70" t="s">
         <v>1481</v>
-      </c>
-      <c r="B70" t="s">
-        <v>1482</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B71" t="s">
         <v>1479</v>
-      </c>
-      <c r="B71" t="s">
-        <v>1480</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
@@ -5466,10 +5466,10 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B73" t="s">
         <v>1305</v>
-      </c>
-      <c r="B73" t="s">
-        <v>1306</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
@@ -5482,10 +5482,10 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B75" t="s">
         <v>1381</v>
-      </c>
-      <c r="B75" t="s">
-        <v>1382</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
@@ -5498,10 +5498,10 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B77" t="s">
         <v>1204</v>
-      </c>
-      <c r="B77" t="s">
-        <v>1205</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
@@ -5522,10 +5522,10 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B80" t="s">
         <v>1214</v>
-      </c>
-      <c r="B80" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
@@ -5538,10 +5538,10 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B82" t="s">
         <v>1216</v>
-      </c>
-      <c r="B82" t="s">
-        <v>1217</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
@@ -5554,10 +5554,10 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B84" t="s">
         <v>1218</v>
-      </c>
-      <c r="B84" t="s">
-        <v>1219</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
@@ -5570,10 +5570,10 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B86" t="s">
         <v>1220</v>
-      </c>
-      <c r="B86" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
@@ -5586,10 +5586,10 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B88" t="s">
         <v>1222</v>
-      </c>
-      <c r="B88" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
@@ -5602,10 +5602,10 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="B90" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
@@ -5618,10 +5618,10 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="B92" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
@@ -5634,10 +5634,10 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="B94" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
@@ -5786,10 +5786,10 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B113" t="s">
         <v>1446</v>
-      </c>
-      <c r="B113" t="s">
-        <v>1447</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
@@ -5834,10 +5834,10 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B119" t="s">
         <v>1417</v>
-      </c>
-      <c r="B119" t="s">
-        <v>1418</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
@@ -5898,10 +5898,10 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B127" t="s">
         <v>1470</v>
-      </c>
-      <c r="B127" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
@@ -5914,10 +5914,10 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="B129" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
@@ -5970,10 +5970,10 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B136" t="s">
         <v>1383</v>
-      </c>
-      <c r="B136" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
@@ -6005,15 +6005,15 @@
         <v>104</v>
       </c>
       <c r="B140" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B141" t="s">
         <v>1490</v>
-      </c>
-      <c r="B141" t="s">
-        <v>1491</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
@@ -6037,12 +6037,12 @@
         <v>102</v>
       </c>
       <c r="B144" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="B145" t="s">
         <v>403</v>
@@ -6082,10 +6082,10 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B150" t="s">
         <v>1359</v>
-      </c>
-      <c r="B150" t="s">
-        <v>1360</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
@@ -6106,10 +6106,10 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="B153" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
@@ -6146,34 +6146,34 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B158" t="s">
         <v>1434</v>
-      </c>
-      <c r="B158" t="s">
-        <v>1435</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B159" t="s">
         <v>1353</v>
-      </c>
-      <c r="B159" t="s">
-        <v>1354</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="B160" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="B161" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
@@ -6186,10 +6186,10 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="B163" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
@@ -6202,10 +6202,10 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B165" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
@@ -6218,10 +6218,10 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="B167" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
@@ -6234,10 +6234,10 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="B169" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
@@ -6250,10 +6250,10 @@
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="B171" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
@@ -6266,10 +6266,10 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="B173" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
@@ -6282,10 +6282,10 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="B175" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
@@ -6298,10 +6298,10 @@
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="B177" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
@@ -6314,10 +6314,10 @@
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="B179" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
@@ -6330,10 +6330,10 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="B181" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
@@ -6357,7 +6357,7 @@
         <v>211</v>
       </c>
       <c r="B184" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
@@ -6365,23 +6365,23 @@
         <v>213</v>
       </c>
       <c r="B185" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B186" t="s">
         <v>1312</v>
-      </c>
-      <c r="B186" t="s">
-        <v>1313</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B187" t="s">
         <v>1347</v>
-      </c>
-      <c r="B187" t="s">
-        <v>1348</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
@@ -6413,7 +6413,7 @@
         <v>245</v>
       </c>
       <c r="B191" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
@@ -6450,10 +6450,10 @@
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B196" t="s">
         <v>1467</v>
-      </c>
-      <c r="B196" t="s">
-        <v>1468</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
@@ -6482,10 +6482,10 @@
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B200" t="s">
         <v>1330</v>
-      </c>
-      <c r="B200" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
@@ -6562,10 +6562,10 @@
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B210" t="s">
         <v>1415</v>
-      </c>
-      <c r="B210" t="s">
-        <v>1416</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
@@ -6626,10 +6626,10 @@
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B218" t="s">
         <v>1303</v>
-      </c>
-      <c r="B218" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
@@ -6642,10 +6642,10 @@
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B220" t="s">
         <v>1459</v>
-      </c>
-      <c r="B220" t="s">
-        <v>1460</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
@@ -6674,10 +6674,10 @@
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="B224" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
@@ -6690,15 +6690,15 @@
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B226" t="s">
         <v>1422</v>
-      </c>
-      <c r="B226" t="s">
-        <v>1423</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="B227" t="s">
         <v>883</v>
@@ -6706,10 +6706,10 @@
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B228" t="s">
         <v>1292</v>
-      </c>
-      <c r="B228" t="s">
-        <v>1293</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
@@ -6738,34 +6738,34 @@
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B232" t="s">
         <v>1413</v>
-      </c>
-      <c r="B232" t="s">
-        <v>1414</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B233" t="s">
         <v>1486</v>
-      </c>
-      <c r="B233" t="s">
-        <v>1487</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B234" t="s">
         <v>1371</v>
-      </c>
-      <c r="B234" t="s">
-        <v>1372</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B235" t="s">
         <v>1488</v>
-      </c>
-      <c r="B235" t="s">
-        <v>1489</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
@@ -6786,18 +6786,18 @@
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B238" t="s">
         <v>1282</v>
-      </c>
-      <c r="B238" t="s">
-        <v>1283</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B239" t="s">
         <v>1208</v>
-      </c>
-      <c r="B239" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
@@ -6834,10 +6834,10 @@
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B244" t="s">
         <v>1411</v>
-      </c>
-      <c r="B244" t="s">
-        <v>1412</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
@@ -6898,10 +6898,10 @@
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B252" t="s">
         <v>1477</v>
-      </c>
-      <c r="B252" t="s">
-        <v>1478</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
@@ -6946,10 +6946,10 @@
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B258" t="s">
         <v>1409</v>
-      </c>
-      <c r="B258" t="s">
-        <v>1410</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
@@ -6994,10 +6994,10 @@
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B264" t="s">
         <v>1351</v>
-      </c>
-      <c r="B264" t="s">
-        <v>1352</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
@@ -7042,26 +7042,26 @@
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="B270" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B271" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B272" t="s">
         <v>1440</v>
-      </c>
-      <c r="B272" t="s">
-        <v>1441</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
@@ -7069,7 +7069,7 @@
         <v>275</v>
       </c>
       <c r="B273" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
@@ -7077,15 +7077,15 @@
         <v>850</v>
       </c>
       <c r="B274" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B275" t="s">
         <v>1495</v>
-      </c>
-      <c r="B275" t="s">
-        <v>1496</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
@@ -7106,10 +7106,10 @@
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B278" t="s">
         <v>1397</v>
-      </c>
-      <c r="B278" t="s">
-        <v>1398</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
@@ -7146,10 +7146,10 @@
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B283" t="s">
         <v>1307</v>
-      </c>
-      <c r="B283" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
@@ -7234,10 +7234,10 @@
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B294" t="s">
         <v>1401</v>
-      </c>
-      <c r="B294" t="s">
-        <v>1402</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
@@ -7266,10 +7266,10 @@
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B298" t="s">
         <v>1375</v>
-      </c>
-      <c r="B298" t="s">
-        <v>1376</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
@@ -7362,10 +7362,10 @@
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B310" t="s">
         <v>1362</v>
-      </c>
-      <c r="B310" t="s">
-        <v>1363</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
@@ -7402,34 +7402,34 @@
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B315" t="s">
         <v>1335</v>
-      </c>
-      <c r="B315" t="s">
-        <v>1336</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B316" t="s">
         <v>1345</v>
-      </c>
-      <c r="B316" t="s">
-        <v>1346</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B317" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B318" t="s">
         <v>1341</v>
-      </c>
-      <c r="B318" t="s">
-        <v>1342</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
@@ -7442,34 +7442,34 @@
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B320" t="s">
         <v>1337</v>
-      </c>
-      <c r="B320" t="s">
-        <v>1338</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B321" t="s">
         <v>1343</v>
-      </c>
-      <c r="B321" t="s">
-        <v>1344</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="B322" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B323" t="s">
         <v>1339</v>
-      </c>
-      <c r="B323" t="s">
-        <v>1340</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
@@ -7514,10 +7514,10 @@
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B329" t="s">
         <v>1377</v>
-      </c>
-      <c r="B329" t="s">
-        <v>1378</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
@@ -7594,10 +7594,10 @@
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B339" t="s">
         <v>1357</v>
-      </c>
-      <c r="B339" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
@@ -7682,10 +7682,10 @@
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B350" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
@@ -7730,10 +7730,10 @@
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B356" t="s">
         <v>1310</v>
-      </c>
-      <c r="B356" t="s">
-        <v>1311</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
@@ -7754,10 +7754,10 @@
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B359" t="s">
         <v>1349</v>
-      </c>
-      <c r="B359" t="s">
-        <v>1350</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
@@ -7834,10 +7834,10 @@
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B369" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
@@ -7850,10 +7850,10 @@
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B371" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
@@ -7866,10 +7866,10 @@
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="B373" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
@@ -7882,10 +7882,10 @@
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B375" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
@@ -7898,10 +7898,10 @@
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B377" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
@@ -7962,10 +7962,10 @@
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B385" t="s">
         <v>1430</v>
-      </c>
-      <c r="B385" t="s">
-        <v>1431</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
@@ -8106,10 +8106,10 @@
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B403" t="s">
         <v>1288</v>
-      </c>
-      <c r="B403" t="s">
-        <v>1289</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
@@ -8306,10 +8306,10 @@
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B428" t="s">
         <v>1483</v>
-      </c>
-      <c r="B428" t="s">
-        <v>1484</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
@@ -8338,10 +8338,10 @@
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B432" t="s">
         <v>1428</v>
-      </c>
-      <c r="B432" t="s">
-        <v>1429</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
@@ -8378,10 +8378,10 @@
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B437" t="s">
         <v>1379</v>
-      </c>
-      <c r="B437" t="s">
-        <v>1380</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
@@ -8418,7 +8418,7 @@
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="B442" t="s">
         <v>515</v>
@@ -8546,18 +8546,18 @@
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B458" t="s">
         <v>1403</v>
-      </c>
-      <c r="B458" t="s">
-        <v>1404</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B459" t="s">
         <v>1405</v>
-      </c>
-      <c r="B459" t="s">
-        <v>1406</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
@@ -8578,10 +8578,10 @@
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B462" t="s">
         <v>1389</v>
-      </c>
-      <c r="B462" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
@@ -8634,18 +8634,18 @@
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B469" t="s">
         <v>1426</v>
-      </c>
-      <c r="B469" t="s">
-        <v>1427</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B470" t="s">
         <v>1332</v>
-      </c>
-      <c r="B470" t="s">
-        <v>1333</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
@@ -8698,10 +8698,10 @@
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B477" t="s">
         <v>1280</v>
-      </c>
-      <c r="B477" t="s">
-        <v>1281</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
@@ -8770,10 +8770,10 @@
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B486" t="s">
         <v>1432</v>
-      </c>
-      <c r="B486" t="s">
-        <v>1433</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
@@ -8786,10 +8786,10 @@
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B488" t="s">
         <v>1420</v>
-      </c>
-      <c r="B488" t="s">
-        <v>1421</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
@@ -8818,18 +8818,18 @@
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B492" t="s">
         <v>1474</v>
-      </c>
-      <c r="B492" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B493" t="s">
         <v>1472</v>
-      </c>
-      <c r="B493" t="s">
-        <v>1473</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
@@ -8850,10 +8850,10 @@
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B496" t="s">
         <v>1210</v>
-      </c>
-      <c r="B496" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
@@ -8994,18 +8994,18 @@
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B514" t="s">
         <v>1399</v>
-      </c>
-      <c r="B514" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B515" t="s">
         <v>1290</v>
-      </c>
-      <c r="B515" t="s">
-        <v>1291</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
@@ -9042,10 +9042,10 @@
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B520" t="s">
         <v>1278</v>
-      </c>
-      <c r="B520" t="s">
-        <v>1279</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
@@ -9138,10 +9138,10 @@
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B532" t="s">
         <v>1355</v>
-      </c>
-      <c r="B532" t="s">
-        <v>1356</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
@@ -9226,10 +9226,10 @@
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B543" t="s">
         <v>1294</v>
-      </c>
-      <c r="B543" t="s">
-        <v>1295</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
@@ -9261,7 +9261,7 @@
         <v>39</v>
       </c>
       <c r="B547" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
@@ -9269,7 +9269,7 @@
         <v>38</v>
       </c>
       <c r="B548" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
@@ -9290,10 +9290,10 @@
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B551" t="s">
         <v>1407</v>
-      </c>
-      <c r="B551" t="s">
-        <v>1408</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
@@ -9506,10 +9506,10 @@
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B578" t="s">
         <v>1206</v>
-      </c>
-      <c r="B578" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
@@ -9530,10 +9530,10 @@
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B581" t="s">
         <v>1438</v>
-      </c>
-      <c r="B581" t="s">
-        <v>1439</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
@@ -9594,18 +9594,18 @@
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B589" t="s">
         <v>1386</v>
-      </c>
-      <c r="B589" t="s">
-        <v>1387</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B590" t="s">
         <v>1284</v>
-      </c>
-      <c r="B590" t="s">
-        <v>1285</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
@@ -9626,10 +9626,10 @@
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B593" t="s">
         <v>1297</v>
-      </c>
-      <c r="B593" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
@@ -9730,10 +9730,10 @@
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B606" t="s">
         <v>1373</v>
-      </c>
-      <c r="B606" t="s">
-        <v>1374</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
@@ -9802,10 +9802,10 @@
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B615" t="s">
         <v>1286</v>
-      </c>
-      <c r="B615" t="s">
-        <v>1287</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
@@ -9842,10 +9842,10 @@
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B620" t="s">
         <v>1299</v>
-      </c>
-      <c r="B620" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
@@ -9898,10 +9898,10 @@
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B627" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.35">
@@ -9914,34 +9914,34 @@
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="B629" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="B630" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="B631" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B632" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
@@ -10050,10 +10050,10 @@
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B646" t="s">
         <v>1368</v>
-      </c>
-      <c r="B646" t="s">
-        <v>1369</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.35">
@@ -10098,10 +10098,10 @@
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B652" t="s">
         <v>1328</v>
-      </c>
-      <c r="B652" t="s">
-        <v>1329</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.35">
@@ -10162,10 +10162,10 @@
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B660" t="s">
         <v>1212</v>
-      </c>
-      <c r="B660" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.35">
@@ -10250,10 +10250,10 @@
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B671" t="s">
         <v>1395</v>
-      </c>
-      <c r="B671" t="s">
-        <v>1396</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.35">
@@ -10314,7 +10314,7 @@
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="B679" t="s">
         <v>966</v>
@@ -10357,31 +10357,31 @@
         <v>43</v>
       </c>
       <c r="B684" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B685" t="s">
         <v>1319</v>
-      </c>
-      <c r="B685" t="s">
-        <v>1320</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B686" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B687" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.35">
@@ -10389,15 +10389,15 @@
         <v>40</v>
       </c>
       <c r="B688" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B689" t="s">
         <v>1317</v>
-      </c>
-      <c r="B689" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.35">
@@ -10418,34 +10418,34 @@
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B692" t="s">
         <v>1274</v>
-      </c>
-      <c r="B692" t="s">
-        <v>1275</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B693" t="s">
         <v>1276</v>
-      </c>
-      <c r="B693" t="s">
-        <v>1277</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B694" t="s">
         <v>1463</v>
-      </c>
-      <c r="B694" t="s">
-        <v>1464</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B695" t="s">
         <v>1465</v>
-      </c>
-      <c r="B695" t="s">
-        <v>1466</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.35">
@@ -10506,18 +10506,18 @@
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B703" t="s">
         <v>1497</v>
-      </c>
-      <c r="B703" t="s">
-        <v>1498</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="B704" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.35">
@@ -10578,10 +10578,10 @@
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B712" t="s">
         <v>1324</v>
-      </c>
-      <c r="B712" t="s">
-        <v>1325</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.35">
@@ -10602,10 +10602,10 @@
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A715" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B715" t="s">
         <v>1424</v>
-      </c>
-      <c r="B715" t="s">
-        <v>1425</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.35">
@@ -10642,18 +10642,18 @@
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B720" t="s">
         <v>1366</v>
-      </c>
-      <c r="B720" t="s">
-        <v>1367</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B721" t="s">
         <v>1326</v>
-      </c>
-      <c r="B721" t="s">
-        <v>1327</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.35">
@@ -10725,7 +10725,7 @@
         <v>270</v>
       </c>
       <c r="B730" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.35">
@@ -10733,7 +10733,7 @@
         <v>273</v>
       </c>
       <c r="B731" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.35">
@@ -10741,7 +10741,7 @@
         <v>269</v>
       </c>
       <c r="B732" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.35">
@@ -10749,7 +10749,7 @@
         <v>272</v>
       </c>
       <c r="B733" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.35">
@@ -10781,7 +10781,7 @@
         <v>1202</v>
       </c>
       <c r="B737" t="s">
-        <v>1203</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.35">
@@ -10794,10 +10794,10 @@
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B739" t="s">
         <v>1455</v>
-      </c>
-      <c r="B739" t="s">
-        <v>1456</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.35">
@@ -10810,10 +10810,10 @@
     </row>
     <row r="741" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B741" s="1" t="s">
         <v>1450</v>
-      </c>
-      <c r="B741" s="1" t="s">
-        <v>1451</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.35">
@@ -10837,7 +10837,7 @@
         <v>189</v>
       </c>
       <c r="B744" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.35">
@@ -10869,15 +10869,15 @@
         <v>1023</v>
       </c>
       <c r="B748" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A749" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B749" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.35">
@@ -10938,10 +10938,10 @@
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A757" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B757" t="s">
         <v>1364</v>
-      </c>
-      <c r="B757" t="s">
-        <v>1365</v>
       </c>
     </row>
   </sheetData>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88EEE51-053F-4A6F-9A08-3AED673D40A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A84A93-13F3-4353-B1E1-47585325323B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="1503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="1509">
   <si>
     <t>trigger</t>
   </si>
@@ -4537,6 +4537,24 @@
   </si>
   <si>
     <t>ultrasonography</t>
+  </si>
+  <si>
+    <t>atlc</t>
+  </si>
+  <si>
+    <t>atelectatic</t>
+  </si>
+  <si>
+    <t>lc</t>
+  </si>
+  <si>
+    <t>lesser curvature</t>
+  </si>
+  <si>
+    <t>gc</t>
+  </si>
+  <si>
+    <t>greater curvature</t>
   </si>
 </sst>
 </file>
@@ -4605,10 +4623,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B757" totalsRowShown="0">
-  <autoFilter ref="A1:B757" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B757">
-    <sortCondition ref="A1:A757"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B760" totalsRowShown="0">
+  <autoFilter ref="A1:B760" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B760">
+    <sortCondition ref="A1:A760"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4881,7 +4899,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B757"/>
+  <dimension ref="A1:B760"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -5322,1503 +5340,1503 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>853</v>
+        <v>1503</v>
       </c>
       <c r="B55" t="s">
-        <v>854</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>978</v>
+        <v>853</v>
       </c>
       <c r="B56" t="s">
-        <v>979</v>
+        <v>854</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>767</v>
+        <v>978</v>
       </c>
       <c r="B57" t="s">
-        <v>768</v>
+        <v>979</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B58" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>300</v>
+        <v>769</v>
       </c>
       <c r="B59" t="s">
-        <v>364</v>
+        <v>770</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>1122</v>
+        <v>300</v>
       </c>
       <c r="B60" t="s">
-        <v>1123</v>
+        <v>364</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>303</v>
+        <v>1122</v>
       </c>
       <c r="B61" t="s">
-        <v>365</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>230</v>
+        <v>303</v>
       </c>
       <c r="B62" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B63" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>782</v>
+        <v>232</v>
       </c>
       <c r="B64" t="s">
-        <v>783</v>
+        <v>367</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>317</v>
+        <v>782</v>
       </c>
       <c r="B65" t="s">
-        <v>368</v>
+        <v>783</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>755</v>
+        <v>317</v>
       </c>
       <c r="B66" t="s">
-        <v>756</v>
+        <v>368</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>61</v>
+        <v>755</v>
       </c>
       <c r="B67" t="s">
-        <v>369</v>
+        <v>756</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B68" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B69" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>1480</v>
+        <v>58</v>
       </c>
       <c r="B70" t="s">
-        <v>1481</v>
+        <v>371</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="B71" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>877</v>
+        <v>1478</v>
       </c>
       <c r="B72" t="s">
-        <v>878</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>1304</v>
+        <v>877</v>
       </c>
       <c r="B73" t="s">
-        <v>1305</v>
+        <v>878</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>652</v>
+        <v>1304</v>
       </c>
       <c r="B74" t="s">
-        <v>691</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>1380</v>
+        <v>652</v>
       </c>
       <c r="B75" t="s">
-        <v>1381</v>
+        <v>691</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>237</v>
+        <v>1380</v>
       </c>
       <c r="B76" t="s">
-        <v>372</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>1203</v>
+        <v>237</v>
       </c>
       <c r="B77" t="s">
-        <v>1204</v>
+        <v>372</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>60</v>
+        <v>1203</v>
       </c>
       <c r="B78" t="s">
-        <v>373</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>1004</v>
+        <v>60</v>
       </c>
       <c r="B79" t="s">
-        <v>1005</v>
+        <v>373</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>1213</v>
+        <v>1004</v>
       </c>
       <c r="B80" t="s">
-        <v>1214</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>661</v>
+        <v>1213</v>
       </c>
       <c r="B81" t="s">
-        <v>692</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>1215</v>
+        <v>661</v>
       </c>
       <c r="B82" t="s">
-        <v>1216</v>
+        <v>692</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>662</v>
+        <v>1215</v>
       </c>
       <c r="B83" t="s">
-        <v>693</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>1217</v>
+        <v>662</v>
       </c>
       <c r="B84" t="s">
-        <v>1218</v>
+        <v>693</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>663</v>
+        <v>1217</v>
       </c>
       <c r="B85" t="s">
-        <v>694</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>1219</v>
+        <v>663</v>
       </c>
       <c r="B86" t="s">
-        <v>1220</v>
+        <v>694</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>664</v>
+        <v>1219</v>
       </c>
       <c r="B87" t="s">
-        <v>695</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>1221</v>
+        <v>664</v>
       </c>
       <c r="B88" t="s">
-        <v>1222</v>
+        <v>695</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>665</v>
+        <v>1221</v>
       </c>
       <c r="B89" t="s">
-        <v>696</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>1223</v>
+        <v>665</v>
       </c>
       <c r="B90" t="s">
-        <v>1226</v>
+        <v>696</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>666</v>
+        <v>1223</v>
       </c>
       <c r="B91" t="s">
-        <v>697</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>1224</v>
+        <v>666</v>
       </c>
       <c r="B92" t="s">
-        <v>1227</v>
+        <v>697</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>667</v>
+        <v>1224</v>
       </c>
       <c r="B93" t="s">
-        <v>698</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>1225</v>
+        <v>667</v>
       </c>
       <c r="B94" t="s">
-        <v>1228</v>
+        <v>698</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>867</v>
+        <v>1225</v>
       </c>
       <c r="B95" t="s">
-        <v>868</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>320</v>
+        <v>867</v>
       </c>
       <c r="B96" t="s">
-        <v>374</v>
+        <v>868</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>194</v>
+        <v>320</v>
       </c>
       <c r="B97" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="B98" t="s">
-        <v>22</v>
+        <v>375</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B99" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="B100" t="s">
-        <v>376</v>
+        <v>20</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>287</v>
+        <v>196</v>
       </c>
       <c r="B101" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B102" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>336</v>
+        <v>286</v>
       </c>
       <c r="B103" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>890</v>
+        <v>336</v>
       </c>
       <c r="B104" t="s">
-        <v>891</v>
+        <v>379</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>305</v>
+        <v>890</v>
       </c>
       <c r="B105" t="s">
-        <v>380</v>
+        <v>891</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="B106" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>1134</v>
+        <v>322</v>
       </c>
       <c r="B107" t="s">
-        <v>1135</v>
+        <v>381</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>276</v>
+        <v>1134</v>
       </c>
       <c r="B108" t="s">
-        <v>382</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>332</v>
+        <v>276</v>
       </c>
       <c r="B109" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>42</v>
+        <v>332</v>
       </c>
       <c r="B110" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B111" t="s">
-        <v>1115</v>
+        <v>384</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>642</v>
+        <v>41</v>
       </c>
       <c r="B112" t="s">
-        <v>699</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>1445</v>
+        <v>642</v>
       </c>
       <c r="B113" t="s">
-        <v>1446</v>
+        <v>699</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>217</v>
+        <v>1445</v>
       </c>
       <c r="B114" t="s">
-        <v>385</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>288</v>
+        <v>217</v>
       </c>
       <c r="B115" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>218</v>
+        <v>288</v>
       </c>
       <c r="B116" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>296</v>
+        <v>218</v>
       </c>
       <c r="B117" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>199</v>
+        <v>296</v>
       </c>
       <c r="B118" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>1416</v>
+        <v>199</v>
       </c>
       <c r="B119" t="s">
-        <v>1417</v>
+        <v>389</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>641</v>
+        <v>1416</v>
       </c>
       <c r="B120" t="s">
-        <v>700</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>112</v>
+        <v>641</v>
       </c>
       <c r="B121" t="s">
-        <v>390</v>
+        <v>700</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="B122" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="B123" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>1151</v>
+        <v>115</v>
       </c>
       <c r="B124" t="s">
-        <v>1152</v>
+        <v>392</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>871</v>
+        <v>1151</v>
       </c>
       <c r="B125" t="s">
-        <v>872</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>800</v>
+        <v>871</v>
       </c>
       <c r="B126" t="s">
-        <v>801</v>
+        <v>872</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>1469</v>
+        <v>800</v>
       </c>
       <c r="B127" t="s">
-        <v>1470</v>
+        <v>801</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>152</v>
+        <v>1469</v>
       </c>
       <c r="B128" t="s">
-        <v>393</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>1295</v>
+        <v>152</v>
       </c>
       <c r="B129" t="s">
-        <v>1300</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>124</v>
+        <v>1295</v>
       </c>
       <c r="B130" t="s">
-        <v>395</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B131" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="B132" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>958</v>
+        <v>155</v>
       </c>
       <c r="B133" t="s">
-        <v>959</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>84</v>
+        <v>958</v>
       </c>
       <c r="B134" t="s">
-        <v>397</v>
+        <v>959</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>956</v>
+        <v>84</v>
       </c>
       <c r="B135" t="s">
-        <v>957</v>
+        <v>397</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>1382</v>
+        <v>956</v>
       </c>
       <c r="B136" t="s">
-        <v>1383</v>
+        <v>957</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>103</v>
+        <v>1382</v>
       </c>
       <c r="B137" t="s">
-        <v>398</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>198</v>
+        <v>103</v>
       </c>
       <c r="B138" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>314</v>
+        <v>198</v>
       </c>
       <c r="B139" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>104</v>
+        <v>314</v>
       </c>
       <c r="B140" t="s">
-        <v>1461</v>
+        <v>400</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>1489</v>
+        <v>104</v>
       </c>
       <c r="B141" t="s">
-        <v>1490</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>163</v>
+        <v>1489</v>
       </c>
       <c r="B142" t="s">
-        <v>401</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="B143" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B144" t="s">
-        <v>1315</v>
+        <v>402</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>1314</v>
+        <v>102</v>
       </c>
       <c r="B145" t="s">
-        <v>403</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>921</v>
+        <v>1314</v>
       </c>
       <c r="B146" t="s">
-        <v>922</v>
+        <v>403</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B147" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>162</v>
+        <v>919</v>
       </c>
       <c r="B148" t="s">
-        <v>404</v>
+        <v>920</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>1128</v>
+        <v>162</v>
       </c>
       <c r="B149" t="s">
-        <v>1129</v>
+        <v>404</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>1358</v>
+        <v>1128</v>
       </c>
       <c r="B150" t="s">
-        <v>1359</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>830</v>
+        <v>1358</v>
       </c>
       <c r="B151" t="s">
-        <v>831</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B152" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>1301</v>
+        <v>832</v>
       </c>
       <c r="B153" t="s">
-        <v>1460</v>
+        <v>833</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>1072</v>
+        <v>1301</v>
       </c>
       <c r="B154" t="s">
-        <v>1073</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>658</v>
+        <v>1072</v>
       </c>
       <c r="B155" t="s">
-        <v>701</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>639</v>
+        <v>658</v>
       </c>
       <c r="B156" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>931</v>
+        <v>639</v>
       </c>
       <c r="B157" t="s">
-        <v>932</v>
+        <v>702</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>1433</v>
+        <v>931</v>
       </c>
       <c r="B158" t="s">
-        <v>1434</v>
+        <v>932</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>1352</v>
+        <v>1433</v>
       </c>
       <c r="B159" t="s">
-        <v>1353</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>1229</v>
+        <v>1352</v>
       </c>
       <c r="B160" t="s">
-        <v>1241</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>1238</v>
+        <v>1229</v>
       </c>
       <c r="B161" t="s">
-        <v>1250</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>676</v>
+        <v>1238</v>
       </c>
       <c r="B162" t="s">
-        <v>703</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>1239</v>
+        <v>676</v>
       </c>
       <c r="B163" t="s">
-        <v>1251</v>
+        <v>703</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>677</v>
+        <v>1239</v>
       </c>
       <c r="B164" t="s">
-        <v>704</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>1240</v>
+        <v>677</v>
       </c>
       <c r="B165" t="s">
-        <v>1252</v>
+        <v>704</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>678</v>
+        <v>1240</v>
       </c>
       <c r="B166" t="s">
-        <v>705</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>1230</v>
+        <v>678</v>
       </c>
       <c r="B167" t="s">
-        <v>1242</v>
+        <v>705</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>668</v>
+        <v>1230</v>
       </c>
       <c r="B168" t="s">
-        <v>706</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>1231</v>
+        <v>668</v>
       </c>
       <c r="B169" t="s">
-        <v>1243</v>
+        <v>706</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>669</v>
+        <v>1231</v>
       </c>
       <c r="B170" t="s">
-        <v>707</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>1232</v>
+        <v>669</v>
       </c>
       <c r="B171" t="s">
-        <v>1244</v>
+        <v>707</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>670</v>
+        <v>1232</v>
       </c>
       <c r="B172" t="s">
-        <v>708</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>1233</v>
+        <v>670</v>
       </c>
       <c r="B173" t="s">
-        <v>1245</v>
+        <v>708</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>671</v>
+        <v>1233</v>
       </c>
       <c r="B174" t="s">
-        <v>709</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>1234</v>
+        <v>671</v>
       </c>
       <c r="B175" t="s">
-        <v>1246</v>
+        <v>709</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>672</v>
+        <v>1234</v>
       </c>
       <c r="B176" t="s">
-        <v>710</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>1235</v>
+        <v>672</v>
       </c>
       <c r="B177" t="s">
-        <v>1247</v>
+        <v>710</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>673</v>
+        <v>1235</v>
       </c>
       <c r="B178" t="s">
-        <v>711</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>1236</v>
+        <v>673</v>
       </c>
       <c r="B179" t="s">
-        <v>1248</v>
+        <v>711</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>674</v>
+        <v>1236</v>
       </c>
       <c r="B180" t="s">
-        <v>712</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>1237</v>
+        <v>674</v>
       </c>
       <c r="B181" t="s">
-        <v>1249</v>
+        <v>712</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>675</v>
+        <v>1237</v>
       </c>
       <c r="B182" t="s">
-        <v>713</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>175</v>
+        <v>675</v>
       </c>
       <c r="B183" t="s">
-        <v>405</v>
+        <v>713</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="B184" t="s">
-        <v>1435</v>
+        <v>405</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B185" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>1311</v>
+        <v>213</v>
       </c>
       <c r="B186" t="s">
-        <v>1312</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>1346</v>
+        <v>1311</v>
       </c>
       <c r="B187" t="s">
-        <v>1347</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>1184</v>
+        <v>1346</v>
       </c>
       <c r="B188" t="s">
-        <v>406</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>149</v>
+        <v>1184</v>
       </c>
       <c r="B189" t="s">
-        <v>1187</v>
+        <v>406</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>247</v>
+        <v>149</v>
       </c>
       <c r="B190" t="s">
-        <v>407</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B191" t="s">
-        <v>1390</v>
+        <v>407</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>335</v>
+        <v>245</v>
       </c>
       <c r="B192" t="s">
-        <v>408</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>643</v>
+        <v>335</v>
       </c>
       <c r="B193" t="s">
-        <v>714</v>
+        <v>408</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>91</v>
+        <v>643</v>
       </c>
       <c r="B194" t="s">
-        <v>409</v>
+        <v>714</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>266</v>
+        <v>91</v>
       </c>
       <c r="B195" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>1466</v>
+        <v>266</v>
       </c>
       <c r="B196" t="s">
-        <v>1467</v>
+        <v>410</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>1084</v>
+        <v>1466</v>
       </c>
       <c r="B197" t="s">
-        <v>1085</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>792</v>
+        <v>1084</v>
       </c>
       <c r="B198" t="s">
-        <v>793</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>1143</v>
+        <v>792</v>
       </c>
       <c r="B199" t="s">
-        <v>1144</v>
+        <v>793</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>1329</v>
+        <v>1143</v>
       </c>
       <c r="B200" t="s">
-        <v>1330</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>295</v>
+        <v>1329</v>
       </c>
       <c r="B201" t="s">
-        <v>411</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>1074</v>
+        <v>295</v>
       </c>
       <c r="B202" t="s">
-        <v>1075</v>
+        <v>411</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="B203" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>151</v>
+        <v>1080</v>
       </c>
       <c r="B204" t="s">
-        <v>412</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>952</v>
+        <v>151</v>
       </c>
       <c r="B205" t="s">
-        <v>953</v>
+        <v>412</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>806</v>
+        <v>952</v>
       </c>
       <c r="B206" t="s">
-        <v>807</v>
+        <v>953</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>923</v>
+        <v>806</v>
       </c>
       <c r="B207" t="s">
-        <v>924</v>
+        <v>807</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>826</v>
+        <v>923</v>
       </c>
       <c r="B208" t="s">
-        <v>827</v>
+        <v>924</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>786</v>
+        <v>826</v>
       </c>
       <c r="B209" t="s">
-        <v>787</v>
+        <v>827</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>1414</v>
+        <v>786</v>
       </c>
       <c r="B210" t="s">
-        <v>1415</v>
+        <v>787</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>747</v>
+        <v>1414</v>
       </c>
       <c r="B211" t="s">
-        <v>748</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>100</v>
+        <v>747</v>
       </c>
       <c r="B212" t="s">
-        <v>413</v>
+        <v>748</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>1032</v>
+        <v>100</v>
       </c>
       <c r="B213" t="s">
-        <v>1033</v>
+        <v>413</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>154</v>
+        <v>1032</v>
       </c>
       <c r="B214" t="s">
-        <v>414</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B215" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="B216" t="s">
-        <v>1114</v>
+        <v>415</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>1139</v>
+        <v>24</v>
       </c>
       <c r="B217" t="s">
-        <v>1140</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>1302</v>
+        <v>1139</v>
       </c>
       <c r="B218" t="s">
-        <v>1303</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>1064</v>
+        <v>1302</v>
       </c>
       <c r="B219" t="s">
-        <v>1065</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>1458</v>
+        <v>1064</v>
       </c>
       <c r="B220" t="s">
-        <v>1459</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>812</v>
+        <v>1458</v>
       </c>
       <c r="B221" t="s">
-        <v>813</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>130</v>
+        <v>812</v>
       </c>
       <c r="B222" t="s">
-        <v>416</v>
+        <v>813</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>321</v>
+        <v>130</v>
       </c>
       <c r="B223" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>1457</v>
+        <v>321</v>
       </c>
       <c r="B224" t="s">
-        <v>1418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>859</v>
+        <v>1457</v>
       </c>
       <c r="B225" t="s">
-        <v>860</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>1421</v>
+        <v>859</v>
       </c>
       <c r="B226" t="s">
-        <v>1422</v>
+        <v>860</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>1456</v>
+        <v>1421</v>
       </c>
       <c r="B227" t="s">
-        <v>883</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>1291</v>
+        <v>1456</v>
       </c>
       <c r="B228" t="s">
-        <v>1292</v>
+        <v>883</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>183</v>
+        <v>1291</v>
       </c>
       <c r="B229" t="s">
-        <v>418</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>1130</v>
+        <v>183</v>
       </c>
       <c r="B230" t="s">
-        <v>1131</v>
+        <v>418</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B231" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>1412</v>
+        <v>1132</v>
       </c>
       <c r="B232" t="s">
-        <v>1413</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>1485</v>
+        <v>1412</v>
       </c>
       <c r="B233" t="s">
-        <v>1486</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>1370</v>
+        <v>1485</v>
       </c>
       <c r="B234" t="s">
-        <v>1371</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>1487</v>
+        <v>1370</v>
       </c>
       <c r="B235" t="s">
-        <v>1488</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>32</v>
+        <v>1487</v>
       </c>
       <c r="B236" t="s">
-        <v>419</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B237" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>1281</v>
+        <v>35</v>
       </c>
       <c r="B238" t="s">
-        <v>1282</v>
+        <v>420</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>1207</v>
+        <v>1281</v>
       </c>
       <c r="B239" t="s">
-        <v>1208</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>757</v>
+        <v>1207</v>
       </c>
       <c r="B240" t="s">
-        <v>1000</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>169</v>
+        <v>757</v>
       </c>
       <c r="B241" t="s">
-        <v>421</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B242" t="s">
         <v>421</v>
@@ -6826,4121 +6844,4145 @@
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>1001</v>
+        <v>170</v>
       </c>
       <c r="B243" t="s">
-        <v>758</v>
+        <v>421</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>1410</v>
+        <v>1001</v>
       </c>
       <c r="B244" t="s">
-        <v>1411</v>
+        <v>758</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>178</v>
+        <v>1410</v>
       </c>
       <c r="B245" t="s">
-        <v>422</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="B246" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>238</v>
+        <v>111</v>
       </c>
       <c r="B247" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="B248" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B249" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="B250" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>660</v>
+        <v>179</v>
       </c>
       <c r="B251" t="s">
-        <v>715</v>
+        <v>427</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>1476</v>
+        <v>660</v>
       </c>
       <c r="B252" t="s">
-        <v>1477</v>
+        <v>715</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>97</v>
+        <v>1476</v>
       </c>
       <c r="B253" t="s">
-        <v>428</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B254" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>242</v>
+        <v>110</v>
       </c>
       <c r="B255" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B256" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="B257" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>1408</v>
+        <v>177</v>
       </c>
       <c r="B258" t="s">
-        <v>1409</v>
+        <v>432</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>182</v>
+        <v>1408</v>
       </c>
       <c r="B259" t="s">
-        <v>433</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>1094</v>
+        <v>182</v>
       </c>
       <c r="B260" t="s">
-        <v>1095</v>
+        <v>433</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>968</v>
+        <v>1094</v>
       </c>
       <c r="B261" t="s">
-        <v>969</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B262" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>1173</v>
+        <v>970</v>
       </c>
       <c r="B263" t="s">
-        <v>1174</v>
+        <v>971</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>1350</v>
+        <v>1173</v>
       </c>
       <c r="B264" t="s">
-        <v>1351</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>1176</v>
+        <v>1350</v>
       </c>
       <c r="B265" t="s">
-        <v>1177</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>253</v>
+        <v>1176</v>
       </c>
       <c r="B266" t="s">
-        <v>434</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="B267" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>780</v>
+        <v>34</v>
       </c>
       <c r="B268" t="s">
-        <v>781</v>
+        <v>435</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>180</v>
+        <v>780</v>
       </c>
       <c r="B269" t="s">
-        <v>436</v>
+        <v>781</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>1322</v>
+        <v>180</v>
       </c>
       <c r="B270" t="s">
-        <v>1391</v>
+        <v>436</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B271" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>1439</v>
+        <v>1321</v>
       </c>
       <c r="B272" t="s">
-        <v>1440</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>275</v>
+        <v>1439</v>
       </c>
       <c r="B273" t="s">
-        <v>1492</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>850</v>
+        <v>275</v>
       </c>
       <c r="B274" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>1494</v>
+        <v>850</v>
       </c>
       <c r="B275" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>116</v>
+        <v>1494</v>
       </c>
       <c r="B276" t="s">
-        <v>437</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>208</v>
+        <v>1507</v>
       </c>
       <c r="B277" t="s">
-        <v>438</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>1396</v>
+        <v>116</v>
       </c>
       <c r="B278" t="s">
-        <v>1397</v>
+        <v>437</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>1196</v>
+        <v>208</v>
       </c>
       <c r="B279" t="s">
-        <v>1197</v>
+        <v>438</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>1044</v>
+        <v>1396</v>
       </c>
       <c r="B280" t="s">
-        <v>1045</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>118</v>
+        <v>1196</v>
       </c>
       <c r="B281" t="s">
-        <v>439</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>634</v>
+        <v>1044</v>
       </c>
       <c r="B282" t="s">
-        <v>716</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>1306</v>
+        <v>118</v>
       </c>
       <c r="B283" t="s">
-        <v>1307</v>
+        <v>439</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>808</v>
+        <v>634</v>
       </c>
       <c r="B284" t="s">
-        <v>809</v>
+        <v>716</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>298</v>
+        <v>1306</v>
       </c>
       <c r="B285" t="s">
-        <v>440</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>636</v>
+        <v>808</v>
       </c>
       <c r="B286" t="s">
-        <v>717</v>
+        <v>809</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>637</v>
+        <v>298</v>
       </c>
       <c r="B287" t="s">
-        <v>718</v>
+        <v>440</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>1026</v>
+        <v>636</v>
       </c>
       <c r="B288" t="s">
-        <v>1027</v>
+        <v>717</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>90</v>
+        <v>637</v>
       </c>
       <c r="B289" t="s">
-        <v>441</v>
+        <v>718</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>88</v>
+        <v>1026</v>
       </c>
       <c r="B290" t="s">
-        <v>442</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B291" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>1060</v>
+        <v>88</v>
       </c>
       <c r="B292" t="s">
-        <v>1061</v>
+        <v>442</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="B293" t="s">
-        <v>1113</v>
+        <v>443</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>1400</v>
+        <v>1060</v>
       </c>
       <c r="B294" t="s">
-        <v>1401</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B295" t="s">
-        <v>6</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>1117</v>
+        <v>1400</v>
       </c>
       <c r="B296" t="s">
-        <v>1118</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>126</v>
+        <v>5</v>
       </c>
       <c r="B297" t="s">
-        <v>444</v>
+        <v>6</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>1374</v>
+        <v>1117</v>
       </c>
       <c r="B298" t="s">
-        <v>1375</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B299" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>131</v>
+        <v>1374</v>
       </c>
       <c r="B300" t="s">
-        <v>446</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B301" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="B302" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>277</v>
+        <v>132</v>
       </c>
       <c r="B303" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>1062</v>
+        <v>119</v>
       </c>
       <c r="B304" t="s">
-        <v>1063</v>
+        <v>448</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>9</v>
+        <v>277</v>
       </c>
       <c r="B305" t="s">
-        <v>10</v>
+        <v>449</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>129</v>
+        <v>1062</v>
       </c>
       <c r="B306" t="s">
-        <v>450</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>127</v>
+        <v>9</v>
       </c>
       <c r="B307" t="s">
-        <v>451</v>
+        <v>10</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>173</v>
+        <v>129</v>
       </c>
       <c r="B308" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>262</v>
+        <v>127</v>
       </c>
       <c r="B309" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>1361</v>
+        <v>173</v>
       </c>
       <c r="B310" t="s">
-        <v>1362</v>
+        <v>452</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>77</v>
+        <v>262</v>
       </c>
       <c r="B311" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>929</v>
+        <v>1361</v>
       </c>
       <c r="B312" t="s">
-        <v>930</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>1147</v>
+        <v>77</v>
       </c>
       <c r="B313" t="s">
-        <v>1148</v>
+        <v>454</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>168</v>
+        <v>929</v>
       </c>
       <c r="B314" t="s">
-        <v>455</v>
+        <v>930</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>1334</v>
+        <v>1147</v>
       </c>
       <c r="B315" t="s">
-        <v>1335</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>1344</v>
+        <v>168</v>
       </c>
       <c r="B316" t="s">
-        <v>1345</v>
+        <v>455</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>1387</v>
+        <v>1334</v>
       </c>
       <c r="B317" t="s">
-        <v>1341</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
       <c r="B318" t="s">
-        <v>1341</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>167</v>
+        <v>1387</v>
       </c>
       <c r="B319" t="s">
-        <v>456</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>1336</v>
+        <v>1340</v>
       </c>
       <c r="B320" t="s">
-        <v>1337</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>1342</v>
+        <v>167</v>
       </c>
       <c r="B321" t="s">
-        <v>1343</v>
+        <v>456</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>1369</v>
+        <v>1336</v>
       </c>
       <c r="B322" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
       <c r="B323" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>828</v>
+        <v>1369</v>
       </c>
       <c r="B324" t="s">
-        <v>829</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>784</v>
+        <v>1338</v>
       </c>
       <c r="B325" t="s">
-        <v>785</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>304</v>
+        <v>828</v>
       </c>
       <c r="B326" t="s">
-        <v>457</v>
+        <v>829</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>751</v>
+        <v>784</v>
       </c>
       <c r="B327" t="s">
-        <v>752</v>
+        <v>785</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>888</v>
+        <v>304</v>
       </c>
       <c r="B328" t="s">
-        <v>889</v>
+        <v>457</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>1376</v>
+        <v>751</v>
       </c>
       <c r="B329" t="s">
-        <v>1377</v>
+        <v>752</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>645</v>
+        <v>888</v>
       </c>
       <c r="B330" t="s">
-        <v>719</v>
+        <v>889</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>86</v>
+        <v>1376</v>
       </c>
       <c r="B331" t="s">
-        <v>458</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>87</v>
+        <v>645</v>
       </c>
       <c r="B332" t="s">
-        <v>459</v>
+        <v>719</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>153</v>
+        <v>86</v>
       </c>
       <c r="B333" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>156</v>
+        <v>87</v>
       </c>
       <c r="B334" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B335" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>251</v>
+        <v>156</v>
       </c>
       <c r="B336" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>285</v>
+        <v>158</v>
       </c>
       <c r="B337" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>325</v>
+        <v>251</v>
       </c>
       <c r="B338" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>1356</v>
+        <v>285</v>
       </c>
       <c r="B339" t="s">
-        <v>1357</v>
+        <v>464</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B340" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>229</v>
+        <v>1356</v>
       </c>
       <c r="B341" t="s">
-        <v>467</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>55</v>
+        <v>326</v>
       </c>
       <c r="B342" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>650</v>
+        <v>229</v>
       </c>
       <c r="B343" t="s">
-        <v>720</v>
+        <v>467</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>235</v>
+        <v>55</v>
       </c>
       <c r="B344" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>57</v>
+        <v>650</v>
       </c>
       <c r="B345" t="s">
-        <v>470</v>
+        <v>720</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B346" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>759</v>
+        <v>57</v>
       </c>
       <c r="B347" t="s">
-        <v>760</v>
+        <v>470</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>1002</v>
+        <v>236</v>
       </c>
       <c r="B348" t="s">
-        <v>760</v>
+        <v>471</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>164</v>
+        <v>759</v>
       </c>
       <c r="B349" t="s">
-        <v>472</v>
+        <v>760</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>1453</v>
+        <v>1002</v>
       </c>
       <c r="B350" t="s">
-        <v>1451</v>
+        <v>760</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="B351" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>204</v>
+        <v>1453</v>
       </c>
       <c r="B352" t="s">
-        <v>474</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>313</v>
+        <v>201</v>
       </c>
       <c r="B353" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>865</v>
+        <v>204</v>
       </c>
       <c r="B354" t="s">
-        <v>866</v>
+        <v>474</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>988</v>
+        <v>313</v>
       </c>
       <c r="B355" t="s">
-        <v>989</v>
+        <v>475</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>1309</v>
+        <v>865</v>
       </c>
       <c r="B356" t="s">
-        <v>1310</v>
+        <v>866</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>258</v>
+        <v>988</v>
       </c>
       <c r="B357" t="s">
-        <v>476</v>
+        <v>989</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>974</v>
+        <v>1309</v>
       </c>
       <c r="B358" t="s">
-        <v>975</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>1348</v>
+        <v>258</v>
       </c>
       <c r="B359" t="s">
-        <v>1349</v>
+        <v>476</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>160</v>
+        <v>974</v>
       </c>
       <c r="B360" t="s">
-        <v>477</v>
+        <v>975</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>685</v>
+        <v>1348</v>
       </c>
       <c r="B361" t="s">
-        <v>721</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>1141</v>
+        <v>160</v>
       </c>
       <c r="B362" t="s">
-        <v>1142</v>
+        <v>477</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>753</v>
+        <v>685</v>
       </c>
       <c r="B363" t="s">
-        <v>754</v>
+        <v>721</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>886</v>
+        <v>1141</v>
       </c>
       <c r="B364" t="s">
-        <v>887</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>884</v>
+        <v>753</v>
       </c>
       <c r="B365" t="s">
-        <v>885</v>
+        <v>754</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>184</v>
+        <v>886</v>
       </c>
       <c r="B366" t="s">
-        <v>478</v>
+        <v>887</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>244</v>
+        <v>884</v>
       </c>
       <c r="B367" t="s">
-        <v>479</v>
+        <v>885</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>243</v>
+        <v>184</v>
       </c>
       <c r="B368" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>1253</v>
+        <v>244</v>
       </c>
       <c r="B369" t="s">
-        <v>1258</v>
+        <v>479</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>679</v>
+        <v>243</v>
       </c>
       <c r="B370" t="s">
-        <v>722</v>
+        <v>480</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B371" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B372" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B373" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B374" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="B375" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B376" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B377" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B378" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>1167</v>
+        <v>1257</v>
       </c>
       <c r="B379" t="s">
-        <v>1168</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>280</v>
+        <v>683</v>
       </c>
       <c r="B380" t="s">
-        <v>481</v>
+        <v>726</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>281</v>
+        <v>1167</v>
       </c>
       <c r="B381" t="s">
-        <v>482</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>49</v>
+        <v>280</v>
       </c>
       <c r="B382" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>53</v>
+        <v>281</v>
       </c>
       <c r="B383" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="B384" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>1429</v>
+        <v>53</v>
       </c>
       <c r="B385" t="s">
-        <v>1430</v>
+        <v>484</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="B386" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>1165</v>
+        <v>1429</v>
       </c>
       <c r="B387" t="s">
-        <v>1166</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>221</v>
+        <v>72</v>
       </c>
       <c r="B388" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>1169</v>
+        <v>1505</v>
       </c>
       <c r="B389" t="s">
-        <v>1170</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>15</v>
+        <v>1165</v>
       </c>
       <c r="B390" t="s">
-        <v>16</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>1048</v>
+        <v>221</v>
       </c>
       <c r="B391" t="s">
-        <v>1049</v>
+        <v>487</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>911</v>
+        <v>1169</v>
       </c>
       <c r="B392" t="s">
-        <v>912</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="B393" t="s">
-        <v>488</v>
+        <v>16</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>241</v>
+        <v>1048</v>
       </c>
       <c r="B394" t="s">
-        <v>489</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>327</v>
+        <v>911</v>
       </c>
       <c r="B395" t="s">
-        <v>490</v>
+        <v>912</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>1088</v>
+        <v>108</v>
       </c>
       <c r="B396" t="s">
-        <v>1089</v>
+        <v>488</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>1040</v>
+        <v>241</v>
       </c>
       <c r="B397" t="s">
-        <v>1041</v>
+        <v>489</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>121</v>
+        <v>327</v>
       </c>
       <c r="B398" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>743</v>
+        <v>1088</v>
       </c>
       <c r="B399" t="s">
-        <v>744</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>774</v>
+        <v>1040</v>
       </c>
       <c r="B400" t="s">
-        <v>775</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="B401" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>63</v>
+        <v>743</v>
       </c>
       <c r="B402" t="s">
-        <v>493</v>
+        <v>744</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>1287</v>
+        <v>774</v>
       </c>
       <c r="B403" t="s">
-        <v>1288</v>
+        <v>775</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>224</v>
+        <v>134</v>
       </c>
       <c r="B404" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="B405" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>26</v>
+        <v>1287</v>
       </c>
       <c r="B406" t="s">
-        <v>496</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="B407" t="s">
-        <v>1110</v>
+        <v>494</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>951</v>
+        <v>25</v>
       </c>
       <c r="B408" t="s">
-        <v>1111</v>
+        <v>495</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>1097</v>
+        <v>26</v>
       </c>
       <c r="B409" t="s">
-        <v>1098</v>
+        <v>496</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B410" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>202</v>
+        <v>951</v>
       </c>
       <c r="B411" t="s">
-        <v>497</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>205</v>
+        <v>1097</v>
       </c>
       <c r="B412" t="s">
-        <v>498</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="B413" t="s">
-        <v>499</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>656</v>
+        <v>202</v>
       </c>
       <c r="B414" t="s">
-        <v>727</v>
+        <v>497</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="B415" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>1076</v>
+        <v>145</v>
       </c>
       <c r="B416" t="s">
-        <v>1077</v>
+        <v>499</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>263</v>
+        <v>656</v>
       </c>
       <c r="B417" t="s">
-        <v>501</v>
+        <v>727</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>1078</v>
+        <v>171</v>
       </c>
       <c r="B418" t="s">
-        <v>1079</v>
+        <v>500</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>80</v>
+        <v>1076</v>
       </c>
       <c r="B419" t="s">
-        <v>502</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>65</v>
+        <v>263</v>
       </c>
       <c r="B420" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>191</v>
+        <v>1078</v>
       </c>
       <c r="B421" t="s">
-        <v>504</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="B422" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>192</v>
+        <v>65</v>
       </c>
       <c r="B423" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="B424" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>233</v>
+        <v>123</v>
       </c>
       <c r="B425" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>1175</v>
+        <v>192</v>
       </c>
       <c r="B426" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>31</v>
+        <v>231</v>
       </c>
       <c r="B427" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>1482</v>
+        <v>233</v>
       </c>
       <c r="B428" t="s">
-        <v>1483</v>
+        <v>508</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>30</v>
+        <v>1175</v>
       </c>
       <c r="B429" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B430" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>71</v>
+        <v>1482</v>
       </c>
       <c r="B431" t="s">
-        <v>512</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>1427</v>
+        <v>30</v>
       </c>
       <c r="B432" t="s">
-        <v>1428</v>
+        <v>510</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>306</v>
+        <v>37</v>
       </c>
       <c r="B433" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>222</v>
+        <v>71</v>
       </c>
       <c r="B434" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>278</v>
+        <v>1427</v>
       </c>
       <c r="B435" t="s">
-        <v>516</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="B436" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>1378</v>
+        <v>222</v>
       </c>
       <c r="B437" t="s">
-        <v>1379</v>
+        <v>514</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>824</v>
+        <v>278</v>
       </c>
       <c r="B438" t="s">
-        <v>825</v>
+        <v>516</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>48</v>
+        <v>279</v>
       </c>
       <c r="B439" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>146</v>
+        <v>1378</v>
       </c>
       <c r="B440" t="s">
-        <v>519</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>52</v>
+        <v>824</v>
       </c>
       <c r="B441" t="s">
-        <v>520</v>
+        <v>825</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>1360</v>
+        <v>48</v>
       </c>
       <c r="B442" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>223</v>
+        <v>146</v>
       </c>
       <c r="B443" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>1082</v>
+        <v>52</v>
       </c>
       <c r="B444" t="s">
-        <v>1083</v>
+        <v>520</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>1093</v>
+        <v>1360</v>
       </c>
       <c r="B445" t="s">
-        <v>1096</v>
+        <v>515</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>1038</v>
+        <v>223</v>
       </c>
       <c r="B446" t="s">
-        <v>1039</v>
+        <v>521</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>96</v>
+        <v>1082</v>
       </c>
       <c r="B447" t="s">
-        <v>522</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>248</v>
+        <v>1093</v>
       </c>
       <c r="B448" t="s">
-        <v>523</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>249</v>
+        <v>1038</v>
       </c>
       <c r="B449" t="s">
-        <v>524</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B450" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>1052</v>
+        <v>248</v>
       </c>
       <c r="B451" t="s">
-        <v>1053</v>
+        <v>523</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="B452" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>1200</v>
+        <v>94</v>
       </c>
       <c r="B453" t="s">
-        <v>1201</v>
+        <v>525</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>907</v>
+        <v>1052</v>
       </c>
       <c r="B454" t="s">
-        <v>908</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>905</v>
+        <v>212</v>
       </c>
       <c r="B455" t="s">
-        <v>906</v>
+        <v>526</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>909</v>
+        <v>1200</v>
       </c>
       <c r="B456" t="s">
-        <v>910</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>329</v>
+        <v>907</v>
       </c>
       <c r="B457" t="s">
-        <v>527</v>
+        <v>908</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>1402</v>
+        <v>905</v>
       </c>
       <c r="B458" t="s">
-        <v>1403</v>
+        <v>906</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>1404</v>
+        <v>909</v>
       </c>
       <c r="B459" t="s">
-        <v>1405</v>
+        <v>910</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>1054</v>
+        <v>329</v>
       </c>
       <c r="B460" t="s">
-        <v>1055</v>
+        <v>527</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>986</v>
+        <v>1402</v>
       </c>
       <c r="B461" t="s">
-        <v>987</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="B462" t="s">
-        <v>1389</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>982</v>
+        <v>1054</v>
       </c>
       <c r="B463" t="s">
-        <v>983</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="B464" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>82</v>
+        <v>1388</v>
       </c>
       <c r="B465" t="s">
-        <v>528</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>765</v>
+        <v>982</v>
       </c>
       <c r="B466" t="s">
-        <v>766</v>
+        <v>983</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>197</v>
+        <v>984</v>
       </c>
       <c r="B467" t="s">
-        <v>529</v>
+        <v>985</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>647</v>
+        <v>82</v>
       </c>
       <c r="B468" t="s">
-        <v>728</v>
+        <v>528</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>1425</v>
+        <v>765</v>
       </c>
       <c r="B469" t="s">
-        <v>1426</v>
+        <v>766</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>1331</v>
+        <v>197</v>
       </c>
       <c r="B470" t="s">
-        <v>1332</v>
+        <v>529</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>814</v>
+        <v>647</v>
       </c>
       <c r="B471" t="s">
-        <v>815</v>
+        <v>728</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>1056</v>
+        <v>1425</v>
       </c>
       <c r="B472" t="s">
-        <v>1057</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>3</v>
+        <v>1331</v>
       </c>
       <c r="B473" t="s">
-        <v>4</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>949</v>
+        <v>814</v>
       </c>
       <c r="B474" t="s">
-        <v>4</v>
+        <v>815</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>950</v>
+        <v>1056</v>
       </c>
       <c r="B475" t="s">
-        <v>4</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>657</v>
+        <v>3</v>
       </c>
       <c r="B476" t="s">
-        <v>729</v>
+        <v>4</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>1279</v>
+        <v>949</v>
       </c>
       <c r="B477" t="s">
-        <v>1280</v>
+        <v>4</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>763</v>
+        <v>950</v>
       </c>
       <c r="B478" t="s">
-        <v>764</v>
+        <v>4</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>85</v>
+        <v>657</v>
       </c>
       <c r="B479" t="s">
-        <v>530</v>
+        <v>729</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>1050</v>
+        <v>1279</v>
       </c>
       <c r="B480" t="s">
-        <v>1051</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>822</v>
+        <v>763</v>
       </c>
       <c r="B481" t="s">
-        <v>823</v>
+        <v>764</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>802</v>
+        <v>85</v>
       </c>
       <c r="B482" t="s">
-        <v>803</v>
+        <v>530</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>187</v>
+        <v>1050</v>
       </c>
       <c r="B483" t="s">
-        <v>531</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B484" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>925</v>
+        <v>802</v>
       </c>
       <c r="B485" t="s">
-        <v>1107</v>
+        <v>803</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>1431</v>
+        <v>187</v>
       </c>
       <c r="B486" t="s">
-        <v>1432</v>
+        <v>531</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>855</v>
+        <v>820</v>
       </c>
       <c r="B487" t="s">
-        <v>856</v>
+        <v>821</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>1419</v>
+        <v>925</v>
       </c>
       <c r="B488" t="s">
-        <v>1420</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>1034</v>
+        <v>1431</v>
       </c>
       <c r="B489" t="s">
-        <v>1035</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>791</v>
+        <v>855</v>
       </c>
       <c r="B490" t="s">
-        <v>1108</v>
+        <v>856</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>790</v>
+        <v>1419</v>
       </c>
       <c r="B491" t="s">
-        <v>1109</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>1473</v>
+        <v>1034</v>
       </c>
       <c r="B492" t="s">
-        <v>1474</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>1471</v>
+        <v>791</v>
       </c>
       <c r="B493" t="s">
-        <v>1472</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>13</v>
+        <v>790</v>
       </c>
       <c r="B494" t="s">
-        <v>14</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>810</v>
+        <v>1473</v>
       </c>
       <c r="B495" t="s">
-        <v>811</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>1209</v>
+        <v>1471</v>
       </c>
       <c r="B496" t="s">
-        <v>1210</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>186</v>
+        <v>13</v>
       </c>
       <c r="B497" t="s">
-        <v>532</v>
+        <v>14</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="B498" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>319</v>
+        <v>1209</v>
       </c>
       <c r="B499" t="s">
-        <v>533</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>649</v>
+        <v>186</v>
       </c>
       <c r="B500" t="s">
-        <v>730</v>
+        <v>532</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>848</v>
+        <v>804</v>
       </c>
       <c r="B501" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>651</v>
+        <v>319</v>
       </c>
       <c r="B502" t="s">
-        <v>731</v>
+        <v>533</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B503" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>1182</v>
+        <v>848</v>
       </c>
       <c r="B504" t="s">
-        <v>1183</v>
+        <v>849</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>256</v>
+        <v>651</v>
       </c>
       <c r="B505" t="s">
-        <v>534</v>
+        <v>731</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>260</v>
+        <v>646</v>
       </c>
       <c r="B506" t="s">
-        <v>535</v>
+        <v>732</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>261</v>
+        <v>1182</v>
       </c>
       <c r="B507" t="s">
-        <v>536</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="B508" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="B509" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>927</v>
+        <v>261</v>
       </c>
       <c r="B510" t="s">
-        <v>928</v>
+        <v>536</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>1021</v>
+        <v>188</v>
       </c>
       <c r="B511" t="s">
-        <v>1022</v>
+        <v>537</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>1198</v>
+        <v>190</v>
       </c>
       <c r="B512" t="s">
-        <v>1199</v>
+        <v>538</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>209</v>
+        <v>927</v>
       </c>
       <c r="B513" t="s">
-        <v>539</v>
+        <v>928</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>1398</v>
+        <v>1021</v>
       </c>
       <c r="B514" t="s">
-        <v>1399</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>1289</v>
+        <v>1198</v>
       </c>
       <c r="B515" t="s">
-        <v>1290</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>844</v>
+        <v>209</v>
       </c>
       <c r="B516" t="s">
-        <v>845</v>
+        <v>539</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>143</v>
+        <v>1398</v>
       </c>
       <c r="B517" t="s">
-        <v>540</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>140</v>
+        <v>1289</v>
       </c>
       <c r="B518" t="s">
-        <v>541</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>1178</v>
+        <v>844</v>
       </c>
       <c r="B519" t="s">
-        <v>1179</v>
+        <v>845</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>1277</v>
+        <v>143</v>
       </c>
       <c r="B520" t="s">
-        <v>1278</v>
+        <v>540</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>254</v>
+        <v>140</v>
       </c>
       <c r="B521" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>330</v>
+        <v>1178</v>
       </c>
       <c r="B522" t="s">
-        <v>543</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>210</v>
+        <v>1277</v>
       </c>
       <c r="B523" t="s">
-        <v>544</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="B524" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>73</v>
+        <v>330</v>
       </c>
       <c r="B525" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>341</v>
+        <v>210</v>
       </c>
       <c r="B526" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>308</v>
+        <v>234</v>
       </c>
       <c r="B527" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>836</v>
+        <v>73</v>
       </c>
       <c r="B528" t="s">
-        <v>837</v>
+        <v>546</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>838</v>
+        <v>341</v>
       </c>
       <c r="B529" t="s">
-        <v>839</v>
+        <v>547</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>220</v>
+        <v>308</v>
       </c>
       <c r="B530" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>900</v>
+        <v>836</v>
       </c>
       <c r="B531" t="s">
-        <v>901</v>
+        <v>837</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>1354</v>
+        <v>838</v>
       </c>
       <c r="B532" t="s">
-        <v>1355</v>
+        <v>839</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>954</v>
+        <v>220</v>
       </c>
       <c r="B533" t="s">
-        <v>955</v>
+        <v>549</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>1163</v>
+        <v>900</v>
       </c>
       <c r="B534" t="s">
-        <v>1164</v>
+        <v>901</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>227</v>
+        <v>1354</v>
       </c>
       <c r="B535" t="s">
-        <v>550</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>333</v>
+        <v>954</v>
       </c>
       <c r="B536" t="s">
-        <v>1136</v>
+        <v>955</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>962</v>
+        <v>1163</v>
       </c>
       <c r="B537" t="s">
-        <v>963</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>771</v>
+        <v>227</v>
       </c>
       <c r="B538" t="s">
-        <v>772</v>
+        <v>550</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>294</v>
+        <v>333</v>
       </c>
       <c r="B539" t="s">
-        <v>551</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>943</v>
+        <v>962</v>
       </c>
       <c r="B540" t="s">
-        <v>944</v>
+        <v>963</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>338</v>
+        <v>771</v>
       </c>
       <c r="B541" t="s">
-        <v>552</v>
+        <v>772</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>773</v>
+        <v>294</v>
       </c>
       <c r="B542" t="s">
-        <v>772</v>
+        <v>551</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>1293</v>
+        <v>943</v>
       </c>
       <c r="B543" t="s">
-        <v>1294</v>
+        <v>944</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B544" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>340</v>
+        <v>773</v>
       </c>
       <c r="B545" t="s">
-        <v>554</v>
+        <v>772</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>638</v>
+        <v>1293</v>
       </c>
       <c r="B546" t="s">
-        <v>733</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>39</v>
+        <v>339</v>
       </c>
       <c r="B547" t="s">
-        <v>1491</v>
+        <v>553</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>38</v>
+        <v>340</v>
       </c>
       <c r="B548" t="s">
-        <v>1484</v>
+        <v>554</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>342</v>
+        <v>638</v>
       </c>
       <c r="B549" t="s">
-        <v>555</v>
+        <v>733</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="B550" t="s">
-        <v>556</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>1406</v>
+        <v>38</v>
       </c>
       <c r="B551" t="s">
-        <v>1407</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>1019</v>
+        <v>342</v>
       </c>
       <c r="B552" t="s">
-        <v>1020</v>
+        <v>555</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>894</v>
+        <v>107</v>
       </c>
       <c r="B553" t="s">
-        <v>895</v>
+        <v>556</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>117</v>
+        <v>1406</v>
       </c>
       <c r="B554" t="s">
-        <v>557</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="B555" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>98</v>
+        <v>894</v>
       </c>
       <c r="B556" t="s">
-        <v>558</v>
+        <v>895</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="B557" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>659</v>
+        <v>1015</v>
       </c>
       <c r="B558" t="s">
-        <v>734</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>1091</v>
+        <v>98</v>
       </c>
       <c r="B559" t="s">
-        <v>1014</v>
+        <v>558</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>816</v>
+        <v>99</v>
       </c>
       <c r="B560" t="s">
-        <v>817</v>
+        <v>559</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>113</v>
+        <v>659</v>
       </c>
       <c r="B561" t="s">
-        <v>560</v>
+        <v>734</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>881</v>
+        <v>1091</v>
       </c>
       <c r="B562" t="s">
-        <v>882</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>45</v>
+        <v>816</v>
       </c>
       <c r="B563" t="s">
-        <v>1106</v>
+        <v>817</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>290</v>
+        <v>113</v>
       </c>
       <c r="B564" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>299</v>
+        <v>881</v>
       </c>
       <c r="B565" t="s">
-        <v>562</v>
+        <v>882</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B566" t="s">
-        <v>563</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>840</v>
+        <v>290</v>
       </c>
       <c r="B567" t="s">
-        <v>841</v>
+        <v>561</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>51</v>
+        <v>299</v>
       </c>
       <c r="B568" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>863</v>
+        <v>47</v>
       </c>
       <c r="B569" t="s">
-        <v>864</v>
+        <v>563</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>114</v>
+        <v>840</v>
       </c>
       <c r="B570" t="s">
-        <v>565</v>
+        <v>841</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>846</v>
+        <v>51</v>
       </c>
       <c r="B571" t="s">
-        <v>847</v>
+        <v>564</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>144</v>
+        <v>863</v>
       </c>
       <c r="B572" t="s">
-        <v>566</v>
+        <v>864</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>1068</v>
+        <v>114</v>
       </c>
       <c r="B573" t="s">
-        <v>1069</v>
+        <v>565</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>176</v>
+        <v>846</v>
       </c>
       <c r="B574" t="s">
-        <v>567</v>
+        <v>847</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>315</v>
+        <v>144</v>
       </c>
       <c r="B575" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>29</v>
+        <v>1068</v>
       </c>
       <c r="B576" t="s">
-        <v>569</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>1008</v>
+        <v>176</v>
       </c>
       <c r="B577" t="s">
-        <v>1009</v>
+        <v>567</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>1205</v>
+        <v>315</v>
       </c>
       <c r="B578" t="s">
-        <v>1206</v>
+        <v>568</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>293</v>
+        <v>29</v>
       </c>
       <c r="B579" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>972</v>
+        <v>1008</v>
       </c>
       <c r="B580" t="s">
-        <v>973</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>1437</v>
+        <v>1205</v>
       </c>
       <c r="B581" t="s">
-        <v>1438</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B582" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>994</v>
+        <v>972</v>
       </c>
       <c r="B583" t="s">
-        <v>995</v>
+        <v>973</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>998</v>
+        <v>1437</v>
       </c>
       <c r="B584" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>75</v>
+        <v>301</v>
       </c>
       <c r="B585" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>76</v>
+        <v>994</v>
       </c>
       <c r="B586" t="s">
-        <v>573</v>
+        <v>995</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>78</v>
+        <v>998</v>
       </c>
       <c r="B587" t="s">
-        <v>574</v>
+        <v>999</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>328</v>
+        <v>75</v>
       </c>
       <c r="B588" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>1385</v>
+        <v>76</v>
       </c>
       <c r="B589" t="s">
-        <v>1386</v>
+        <v>573</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>1283</v>
+        <v>78</v>
       </c>
       <c r="B590" t="s">
-        <v>1284</v>
+        <v>574</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>745</v>
+        <v>328</v>
       </c>
       <c r="B591" t="s">
-        <v>746</v>
+        <v>575</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>798</v>
+        <v>1385</v>
       </c>
       <c r="B592" t="s">
-        <v>799</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>1296</v>
+        <v>1283</v>
       </c>
       <c r="B593" t="s">
-        <v>1297</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>135</v>
+        <v>745</v>
       </c>
       <c r="B594" t="s">
-        <v>576</v>
+        <v>746</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>1161</v>
+        <v>798</v>
       </c>
       <c r="B595" t="s">
-        <v>1162</v>
+        <v>799</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>1028</v>
+        <v>1296</v>
       </c>
       <c r="B596" t="s">
-        <v>1029</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>215</v>
+        <v>135</v>
       </c>
       <c r="B597" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>926</v>
+        <v>1161</v>
       </c>
       <c r="B598" t="s">
-        <v>1121</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>216</v>
+        <v>1028</v>
       </c>
       <c r="B599" t="s">
-        <v>1104</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>316</v>
+        <v>215</v>
       </c>
       <c r="B600" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>1070</v>
+        <v>926</v>
       </c>
       <c r="B601" t="s">
-        <v>1071</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B602" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>990</v>
+        <v>316</v>
       </c>
       <c r="B603" t="s">
-        <v>991</v>
+        <v>578</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>992</v>
+        <v>1070</v>
       </c>
       <c r="B604" t="s">
-        <v>993</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="B605" t="s">
-        <v>579</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>1372</v>
+        <v>990</v>
       </c>
       <c r="B606" t="s">
-        <v>1373</v>
+        <v>991</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>939</v>
+        <v>992</v>
       </c>
       <c r="B607" t="s">
-        <v>940</v>
+        <v>993</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>1086</v>
+        <v>225</v>
       </c>
       <c r="B608" t="s">
-        <v>1087</v>
+        <v>579</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>1036</v>
+        <v>1372</v>
       </c>
       <c r="B609" t="s">
-        <v>1037</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>93</v>
+        <v>939</v>
       </c>
       <c r="B610" t="s">
-        <v>580</v>
+        <v>940</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>120</v>
+        <v>1086</v>
       </c>
       <c r="B611" t="s">
-        <v>581</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>776</v>
+        <v>1036</v>
       </c>
       <c r="B612" t="s">
-        <v>777</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="B613" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="B614" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>1285</v>
+        <v>776</v>
       </c>
       <c r="B615" t="s">
-        <v>1286</v>
+        <v>777</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="B616" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>818</v>
+        <v>62</v>
       </c>
       <c r="B617" t="s">
-        <v>819</v>
+        <v>583</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>941</v>
+        <v>1285</v>
       </c>
       <c r="B618" t="s">
-        <v>942</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>1190</v>
+        <v>66</v>
       </c>
       <c r="B619" t="s">
-        <v>1191</v>
+        <v>584</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>1298</v>
+        <v>818</v>
       </c>
       <c r="B620" t="s">
-        <v>1299</v>
+        <v>819</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>79</v>
+        <v>941</v>
       </c>
       <c r="B621" t="s">
-        <v>585</v>
+        <v>942</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
-        <v>64</v>
+        <v>1190</v>
       </c>
       <c r="B622" t="s">
-        <v>586</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
-        <v>122</v>
+        <v>1298</v>
       </c>
       <c r="B623" t="s">
-        <v>587</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
-        <v>1159</v>
+        <v>79</v>
       </c>
       <c r="B624" t="s">
-        <v>1160</v>
+        <v>585</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
-        <v>181</v>
+        <v>64</v>
       </c>
       <c r="B625" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
-        <v>794</v>
+        <v>122</v>
       </c>
       <c r="B626" t="s">
-        <v>795</v>
+        <v>587</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>1263</v>
+        <v>1159</v>
       </c>
       <c r="B627" t="s">
-        <v>1268</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
-        <v>684</v>
+        <v>181</v>
       </c>
       <c r="B628" t="s">
-        <v>735</v>
+        <v>588</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>1264</v>
+        <v>794</v>
       </c>
       <c r="B629" t="s">
-        <v>1269</v>
+        <v>795</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="B630" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>1266</v>
+        <v>684</v>
       </c>
       <c r="B631" t="s">
-        <v>1271</v>
+        <v>735</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="B632" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
-        <v>1126</v>
+        <v>1265</v>
       </c>
       <c r="B633" t="s">
-        <v>1127</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
-        <v>1124</v>
+        <v>1266</v>
       </c>
       <c r="B634" t="s">
-        <v>1125</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
-        <v>284</v>
+        <v>1267</v>
       </c>
       <c r="B635" t="s">
-        <v>589</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
-        <v>964</v>
+        <v>1126</v>
       </c>
       <c r="B636" t="s">
-        <v>965</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
-        <v>1194</v>
+        <v>1124</v>
       </c>
       <c r="B637" t="s">
-        <v>1195</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
-        <v>834</v>
+        <v>284</v>
       </c>
       <c r="B638" t="s">
-        <v>835</v>
+        <v>589</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
-        <v>283</v>
+        <v>964</v>
       </c>
       <c r="B639" t="s">
-        <v>590</v>
+        <v>965</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
-        <v>875</v>
+        <v>1194</v>
       </c>
       <c r="B640" t="s">
-        <v>876</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>1155</v>
+        <v>834</v>
       </c>
       <c r="B641" t="s">
-        <v>1156</v>
+        <v>835</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
-        <v>749</v>
+        <v>283</v>
       </c>
       <c r="B642" t="s">
-        <v>750</v>
+        <v>590</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
-        <v>1066</v>
+        <v>875</v>
       </c>
       <c r="B643" t="s">
-        <v>1067</v>
+        <v>876</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
-        <v>67</v>
+        <v>1155</v>
       </c>
       <c r="B644" t="s">
-        <v>591</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
-        <v>68</v>
+        <v>749</v>
       </c>
       <c r="B645" t="s">
-        <v>592</v>
+        <v>750</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
-        <v>1367</v>
+        <v>1066</v>
       </c>
       <c r="B646" t="s">
-        <v>1368</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="B647" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
-        <v>289</v>
+        <v>68</v>
       </c>
       <c r="B648" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
-        <v>297</v>
+        <v>1367</v>
       </c>
       <c r="B649" t="s">
-        <v>595</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
-        <v>264</v>
+        <v>95</v>
       </c>
       <c r="B650" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
-        <v>193</v>
+        <v>289</v>
       </c>
       <c r="B651" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>1327</v>
+        <v>297</v>
       </c>
       <c r="B652" t="s">
-        <v>1328</v>
+        <v>595</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
-        <v>892</v>
+        <v>264</v>
       </c>
       <c r="B653" t="s">
-        <v>893</v>
+        <v>596</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
-        <v>44</v>
+        <v>193</v>
       </c>
       <c r="B654" t="s">
-        <v>1103</v>
+        <v>597</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
-        <v>1058</v>
+        <v>1327</v>
       </c>
       <c r="B655" t="s">
-        <v>1059</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
-        <v>323</v>
+        <v>892</v>
       </c>
       <c r="B656" t="s">
-        <v>598</v>
+        <v>893</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
-        <v>324</v>
+        <v>44</v>
       </c>
       <c r="B657" t="s">
-        <v>599</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
-        <v>842</v>
+        <v>1058</v>
       </c>
       <c r="B658" t="s">
-        <v>843</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
-        <v>879</v>
+        <v>323</v>
       </c>
       <c r="B659" t="s">
-        <v>880</v>
+        <v>598</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
-        <v>1211</v>
+        <v>324</v>
       </c>
       <c r="B660" t="s">
-        <v>1212</v>
+        <v>599</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
-        <v>861</v>
+        <v>842</v>
       </c>
       <c r="B661" t="s">
-        <v>862</v>
+        <v>843</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
-        <v>33</v>
+        <v>879</v>
       </c>
       <c r="B662" t="s">
-        <v>600</v>
+        <v>880</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
-        <v>36</v>
+        <v>1211</v>
       </c>
       <c r="B663" t="s">
-        <v>601</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
-        <v>1119</v>
+        <v>861</v>
       </c>
       <c r="B664" t="s">
-        <v>1120</v>
+        <v>862</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
-        <v>309</v>
+        <v>33</v>
       </c>
       <c r="B665" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
-        <v>257</v>
+        <v>36</v>
       </c>
       <c r="B666" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
-        <v>302</v>
+        <v>1119</v>
       </c>
       <c r="B667" t="s">
-        <v>604</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
-        <v>228</v>
+        <v>309</v>
       </c>
       <c r="B668" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
-        <v>17</v>
+        <v>257</v>
       </c>
       <c r="B669" t="s">
-        <v>18</v>
+        <v>603</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
-        <v>648</v>
+        <v>302</v>
       </c>
       <c r="B670" t="s">
-        <v>736</v>
+        <v>604</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
-        <v>1394</v>
+        <v>228</v>
       </c>
       <c r="B671" t="s">
-        <v>1395</v>
+        <v>605</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
-        <v>778</v>
+        <v>17</v>
       </c>
       <c r="B672" t="s">
-        <v>779</v>
+        <v>18</v>
       </c>
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
-        <v>142</v>
+        <v>648</v>
       </c>
       <c r="B673" t="s">
-        <v>606</v>
+        <v>736</v>
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
-        <v>1153</v>
+        <v>1394</v>
       </c>
       <c r="B674" t="s">
-        <v>1154</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
-        <v>947</v>
+        <v>778</v>
       </c>
       <c r="B675" t="s">
-        <v>948</v>
+        <v>779</v>
       </c>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="B676" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
-        <v>265</v>
+        <v>1153</v>
       </c>
       <c r="B677" t="s">
-        <v>608</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
-        <v>967</v>
+        <v>947</v>
       </c>
       <c r="B678" t="s">
-        <v>966</v>
+        <v>948</v>
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
-        <v>1384</v>
+        <v>54</v>
       </c>
       <c r="B679" t="s">
-        <v>966</v>
+        <v>607</v>
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
-        <v>56</v>
+        <v>265</v>
       </c>
       <c r="B680" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
-        <v>1192</v>
+        <v>967</v>
       </c>
       <c r="B681" t="s">
-        <v>1193</v>
+        <v>966</v>
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
-        <v>185</v>
+        <v>1384</v>
       </c>
       <c r="B682" t="s">
-        <v>610</v>
+        <v>966</v>
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="B683" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
-        <v>43</v>
+        <v>1192</v>
       </c>
       <c r="B684" t="s">
-        <v>1320</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
-        <v>1318</v>
+        <v>185</v>
       </c>
       <c r="B685" t="s">
-        <v>1319</v>
+        <v>610</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
-        <v>1441</v>
+        <v>159</v>
       </c>
       <c r="B686" t="s">
-        <v>1443</v>
+        <v>611</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
-        <v>1442</v>
+        <v>43</v>
       </c>
       <c r="B687" t="s">
-        <v>1444</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
-        <v>40</v>
+        <v>1318</v>
       </c>
       <c r="B688" t="s">
-        <v>1475</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
-        <v>1316</v>
+        <v>1441</v>
       </c>
       <c r="B689" t="s">
-        <v>1317</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
-        <v>1145</v>
+        <v>1442</v>
       </c>
       <c r="B690" t="s">
-        <v>1146</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
-        <v>165</v>
+        <v>40</v>
       </c>
       <c r="B691" t="s">
-        <v>612</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
-        <v>1273</v>
+        <v>1316</v>
       </c>
       <c r="B692" t="s">
-        <v>1274</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
-        <v>1275</v>
+        <v>1145</v>
       </c>
       <c r="B693" t="s">
-        <v>1276</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
-        <v>1462</v>
+        <v>165</v>
       </c>
       <c r="B694" t="s">
-        <v>1463</v>
+        <v>612</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
-        <v>1464</v>
+        <v>1273</v>
       </c>
       <c r="B695" t="s">
-        <v>1465</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
-        <v>12</v>
+        <v>1275</v>
       </c>
       <c r="B696" t="s">
-        <v>11</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
-        <v>250</v>
+        <v>1462</v>
       </c>
       <c r="B697" t="s">
-        <v>613</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
-        <v>27</v>
+        <v>1464</v>
       </c>
       <c r="B698" t="s">
-        <v>614</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
-        <v>1030</v>
+        <v>12</v>
       </c>
       <c r="B699" t="s">
-        <v>1031</v>
+        <v>11</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
-        <v>28</v>
+        <v>250</v>
       </c>
       <c r="B700" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
-        <v>1180</v>
+        <v>27</v>
       </c>
       <c r="B701" t="s">
-        <v>1181</v>
+        <v>614</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
-        <v>255</v>
+        <v>1030</v>
       </c>
       <c r="B702" t="s">
-        <v>616</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
-        <v>1496</v>
+        <v>28</v>
       </c>
       <c r="B703" t="s">
-        <v>1497</v>
+        <v>615</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
-        <v>1308</v>
+        <v>1180</v>
       </c>
       <c r="B704" t="s">
-        <v>1313</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
-        <v>788</v>
+        <v>255</v>
       </c>
       <c r="B705" t="s">
-        <v>789</v>
+        <v>616</v>
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
-        <v>267</v>
+        <v>1496</v>
       </c>
       <c r="B706" t="s">
-        <v>617</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
-        <v>654</v>
+        <v>1308</v>
       </c>
       <c r="B707" t="s">
-        <v>737</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
-        <v>655</v>
+        <v>788</v>
       </c>
       <c r="B708" t="s">
-        <v>738</v>
+        <v>789</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
-        <v>139</v>
+        <v>267</v>
       </c>
       <c r="B709" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
-        <v>7</v>
+        <v>654</v>
       </c>
       <c r="B710" t="s">
-        <v>2</v>
+        <v>737</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
-        <v>105</v>
+        <v>655</v>
       </c>
       <c r="B711" t="s">
-        <v>619</v>
+        <v>738</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
-        <v>1323</v>
+        <v>139</v>
       </c>
       <c r="B712" t="s">
-        <v>1324</v>
+        <v>618</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
-        <v>1024</v>
+        <v>7</v>
       </c>
       <c r="B713" t="s">
-        <v>1102</v>
+        <v>2</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
-        <v>857</v>
+        <v>105</v>
       </c>
       <c r="B714" t="s">
-        <v>858</v>
+        <v>619</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A715" t="s">
-        <v>1423</v>
+        <v>1323</v>
       </c>
       <c r="B715" t="s">
-        <v>1424</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A716" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B716" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
-        <v>292</v>
+        <v>857</v>
       </c>
       <c r="B717" t="s">
-        <v>620</v>
+        <v>858</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
-        <v>8</v>
+        <v>1423</v>
       </c>
       <c r="B718" t="s">
-        <v>11</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
-        <v>334</v>
+        <v>1025</v>
       </c>
       <c r="B719" t="s">
-        <v>621</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
-        <v>1365</v>
+        <v>292</v>
       </c>
       <c r="B720" t="s">
-        <v>1366</v>
+        <v>620</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
-        <v>1325</v>
+        <v>8</v>
       </c>
       <c r="B721" t="s">
-        <v>1326</v>
+        <v>11</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B722" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
-        <v>259</v>
+        <v>1365</v>
       </c>
       <c r="B723" t="s">
-        <v>623</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
-        <v>318</v>
+        <v>1325</v>
       </c>
       <c r="B724" t="s">
-        <v>624</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
-        <v>851</v>
+        <v>331</v>
       </c>
       <c r="B725" t="s">
-        <v>852</v>
+        <v>622</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
-        <v>1149</v>
+        <v>259</v>
       </c>
       <c r="B726" t="s">
-        <v>1150</v>
+        <v>623</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
-        <v>268</v>
+        <v>318</v>
       </c>
       <c r="B727" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
-        <v>271</v>
+        <v>851</v>
       </c>
       <c r="B728" t="s">
-        <v>1099</v>
+        <v>852</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
-        <v>274</v>
+        <v>1149</v>
       </c>
       <c r="B729" t="s">
-        <v>1100</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A730" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B730" t="s">
-        <v>1498</v>
+        <v>625</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B731" t="s">
-        <v>1499</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B732" t="s">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B733" t="s">
-        <v>1501</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
-        <v>92</v>
+        <v>273</v>
       </c>
       <c r="B734" t="s">
-        <v>626</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
-        <v>200</v>
+        <v>269</v>
       </c>
       <c r="B735" t="s">
-        <v>627</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
-        <v>203</v>
+        <v>272</v>
       </c>
       <c r="B736" t="s">
-        <v>628</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A737" t="s">
-        <v>1202</v>
+        <v>92</v>
       </c>
       <c r="B737" t="s">
-        <v>1502</v>
+        <v>626</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="B738" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
-        <v>1454</v>
+        <v>203</v>
       </c>
       <c r="B739" t="s">
-        <v>1455</v>
+        <v>628</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A740" t="s">
-        <v>686</v>
+        <v>1202</v>
       </c>
       <c r="B740" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="741" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
-        <v>1449</v>
-      </c>
-      <c r="B741" s="1" t="s">
-        <v>1450</v>
+        <v>172</v>
+      </c>
+      <c r="B741" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
-        <v>252</v>
+        <v>1454</v>
       </c>
       <c r="B742" t="s">
-        <v>630</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B743" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="744" spans="1:2" x14ac:dyDescent="0.35">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A744" t="s">
-        <v>189</v>
-      </c>
-      <c r="B744" t="s">
-        <v>1393</v>
+        <v>1449</v>
+      </c>
+      <c r="B744" s="1" t="s">
+        <v>1450</v>
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A745" t="s">
-        <v>980</v>
+        <v>252</v>
       </c>
       <c r="B745" t="s">
-        <v>981</v>
+        <v>630</v>
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A746" t="s">
-        <v>311</v>
+        <v>687</v>
       </c>
       <c r="B746" t="s">
-        <v>631</v>
+        <v>740</v>
       </c>
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A747" t="s">
-        <v>312</v>
+        <v>189</v>
       </c>
       <c r="B747" t="s">
-        <v>632</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A748" t="s">
-        <v>1023</v>
+        <v>980</v>
       </c>
       <c r="B748" t="s">
-        <v>1448</v>
+        <v>981</v>
       </c>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A749" t="s">
-        <v>1447</v>
+        <v>311</v>
       </c>
       <c r="B749" t="s">
-        <v>1468</v>
+        <v>631</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A750" t="s">
-        <v>996</v>
+        <v>312</v>
       </c>
       <c r="B750" t="s">
-        <v>997</v>
+        <v>632</v>
       </c>
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A751" t="s">
-        <v>81</v>
+        <v>1023</v>
       </c>
       <c r="B751" t="s">
-        <v>633</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A752" t="s">
-        <v>644</v>
+        <v>1447</v>
       </c>
       <c r="B752" t="s">
-        <v>741</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A753" t="s">
-        <v>913</v>
+        <v>996</v>
       </c>
       <c r="B753" t="s">
-        <v>914</v>
+        <v>997</v>
       </c>
     </row>
     <row r="754" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A754" t="s">
-        <v>635</v>
+        <v>81</v>
       </c>
       <c r="B754" t="s">
-        <v>742</v>
+        <v>633</v>
       </c>
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A755" t="s">
-        <v>960</v>
+        <v>644</v>
       </c>
       <c r="B755" t="s">
-        <v>961</v>
+        <v>741</v>
       </c>
     </row>
     <row r="756" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A756" t="s">
-        <v>1137</v>
+        <v>913</v>
       </c>
       <c r="B756" t="s">
-        <v>1138</v>
+        <v>914</v>
       </c>
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A757" t="s">
+        <v>635</v>
+      </c>
+      <c r="B757" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A758" t="s">
+        <v>960</v>
+      </c>
+      <c r="B758" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A759" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B759" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A760" t="s">
         <v>1363</v>
       </c>
-      <c r="B757" t="s">
+      <c r="B760" t="s">
         <v>1364</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A84A93-13F3-4353-B1E1-47585325323B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D33706E-DB0B-4477-B951-881D079F20D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="1509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="1511">
   <si>
     <t>trigger</t>
   </si>
@@ -3969,9 +3969,6 @@
     <t>degenerative</t>
   </si>
   <si>
-    <t>Geographic arterial phase hyperenhancement is seen in segment ... of the liver without associated mass effect or contour abnormality, becoming isodense on portal venous phase - suggestive of transient hepatic attenuation difference (THAD)</t>
-  </si>
-  <si>
     <t>colla</t>
   </si>
   <si>
@@ -4555,6 +4552,15 @@
   </si>
   <si>
     <t>greater curvature</t>
+  </si>
+  <si>
+    <t>thads</t>
+  </si>
+  <si>
+    <t>transient hepatic attenuation differences (THAD)</t>
+  </si>
+  <si>
+    <t>Geographic area of increased arterial phase enhancement is seen in segment ... of the liver without associated mass effect or contour abnormality, becoming isodense on portal venous phase - suggestive of transient hepatic attenuation differences (THAD)</t>
   </si>
 </sst>
 </file>
@@ -4623,10 +4629,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B760" totalsRowShown="0">
-  <autoFilter ref="A1:B760" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B760">
-    <sortCondition ref="A1:A760"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B761" totalsRowShown="0">
+  <autoFilter ref="A1:B761" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B761">
+    <sortCondition ref="A1:A761"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4899,7 +4905,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B760"/>
+  <dimension ref="A1:B761"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -5260,10 +5266,10 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="B45" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
@@ -5340,10 +5346,10 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B55" t="s">
         <v>1503</v>
-      </c>
-      <c r="B55" t="s">
-        <v>1504</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
@@ -5468,18 +5474,18 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B71" t="s">
         <v>1480</v>
-      </c>
-      <c r="B71" t="s">
-        <v>1481</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B72" t="s">
         <v>1478</v>
-      </c>
-      <c r="B72" t="s">
-        <v>1479</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
@@ -5508,10 +5514,10 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B76" t="s">
         <v>1380</v>
-      </c>
-      <c r="B76" t="s">
-        <v>1381</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
@@ -5812,10 +5818,10 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B114" t="s">
         <v>1445</v>
-      </c>
-      <c r="B114" t="s">
-        <v>1446</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
@@ -5860,10 +5866,10 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B120" t="s">
         <v>1416</v>
-      </c>
-      <c r="B120" t="s">
-        <v>1417</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
@@ -5924,10 +5930,10 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B128" t="s">
         <v>1469</v>
-      </c>
-      <c r="B128" t="s">
-        <v>1470</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
@@ -5996,10 +6002,10 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B137" t="s">
         <v>1382</v>
-      </c>
-      <c r="B137" t="s">
-        <v>1383</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
@@ -6031,15 +6037,15 @@
         <v>104</v>
       </c>
       <c r="B141" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B142" t="s">
         <v>1489</v>
-      </c>
-      <c r="B142" t="s">
-        <v>1490</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
@@ -6063,12 +6069,12 @@
         <v>102</v>
       </c>
       <c r="B145" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="B146" t="s">
         <v>403</v>
@@ -6108,10 +6114,10 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B151" t="s">
         <v>1358</v>
-      </c>
-      <c r="B151" t="s">
-        <v>1359</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
@@ -6135,7 +6141,7 @@
         <v>1301</v>
       </c>
       <c r="B154" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
@@ -6172,18 +6178,18 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B159" t="s">
         <v>1433</v>
-      </c>
-      <c r="B159" t="s">
-        <v>1434</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B160" t="s">
         <v>1352</v>
-      </c>
-      <c r="B160" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
@@ -6383,7 +6389,7 @@
         <v>211</v>
       </c>
       <c r="B185" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
@@ -6391,7 +6397,7 @@
         <v>213</v>
       </c>
       <c r="B186" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
@@ -6404,10 +6410,10 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B188" t="s">
         <v>1346</v>
-      </c>
-      <c r="B188" t="s">
-        <v>1347</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
@@ -6439,7 +6445,7 @@
         <v>245</v>
       </c>
       <c r="B192" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
@@ -6476,10 +6482,10 @@
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B197" t="s">
         <v>1466</v>
-      </c>
-      <c r="B197" t="s">
-        <v>1467</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
@@ -6508,10 +6514,10 @@
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B201" t="s">
         <v>1329</v>
-      </c>
-      <c r="B201" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
@@ -6588,10 +6594,10 @@
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B211" t="s">
         <v>1414</v>
-      </c>
-      <c r="B211" t="s">
-        <v>1415</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
@@ -6668,10 +6674,10 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B221" t="s">
         <v>1458</v>
-      </c>
-      <c r="B221" t="s">
-        <v>1459</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
@@ -6700,10 +6706,10 @@
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="B225" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
@@ -6716,15 +6722,15 @@
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B227" t="s">
         <v>1421</v>
-      </c>
-      <c r="B227" t="s">
-        <v>1422</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="B228" t="s">
         <v>883</v>
@@ -6764,34 +6770,34 @@
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B233" t="s">
         <v>1412</v>
-      </c>
-      <c r="B233" t="s">
-        <v>1413</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B234" t="s">
         <v>1485</v>
-      </c>
-      <c r="B234" t="s">
-        <v>1486</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B235" t="s">
         <v>1370</v>
-      </c>
-      <c r="B235" t="s">
-        <v>1371</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B236" t="s">
         <v>1487</v>
-      </c>
-      <c r="B236" t="s">
-        <v>1488</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
@@ -6860,10 +6866,10 @@
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B245" t="s">
         <v>1410</v>
-      </c>
-      <c r="B245" t="s">
-        <v>1411</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
@@ -6924,10 +6930,10 @@
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B253" t="s">
         <v>1476</v>
-      </c>
-      <c r="B253" t="s">
-        <v>1477</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
@@ -6972,10 +6978,10 @@
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B259" t="s">
         <v>1408</v>
-      </c>
-      <c r="B259" t="s">
-        <v>1409</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
@@ -7020,10 +7026,10 @@
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B265" t="s">
         <v>1350</v>
-      </c>
-      <c r="B265" t="s">
-        <v>1351</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
@@ -7068,26 +7074,26 @@
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B271" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="B272" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B273" t="s">
         <v>1439</v>
-      </c>
-      <c r="B273" t="s">
-        <v>1440</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
@@ -7095,7 +7101,7 @@
         <v>275</v>
       </c>
       <c r="B274" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
@@ -7103,23 +7109,23 @@
         <v>850</v>
       </c>
       <c r="B275" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B276" t="s">
         <v>1494</v>
-      </c>
-      <c r="B276" t="s">
-        <v>1495</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B277" t="s">
         <v>1507</v>
-      </c>
-      <c r="B277" t="s">
-        <v>1508</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
@@ -7140,10 +7146,10 @@
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B280" t="s">
         <v>1396</v>
-      </c>
-      <c r="B280" t="s">
-        <v>1397</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
@@ -7268,10 +7274,10 @@
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B296" t="s">
         <v>1400</v>
-      </c>
-      <c r="B296" t="s">
-        <v>1401</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
@@ -7300,10 +7306,10 @@
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B300" t="s">
         <v>1374</v>
-      </c>
-      <c r="B300" t="s">
-        <v>1375</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
@@ -7396,10 +7402,10 @@
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B312" t="s">
         <v>1361</v>
-      </c>
-      <c r="B312" t="s">
-        <v>1362</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
@@ -7436,34 +7442,34 @@
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B317" t="s">
         <v>1334</v>
-      </c>
-      <c r="B317" t="s">
-        <v>1335</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B318" t="s">
         <v>1344</v>
-      </c>
-      <c r="B318" t="s">
-        <v>1345</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="B319" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B320" t="s">
         <v>1340</v>
-      </c>
-      <c r="B320" t="s">
-        <v>1341</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
@@ -7476,34 +7482,34 @@
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B322" t="s">
         <v>1336</v>
-      </c>
-      <c r="B322" t="s">
-        <v>1337</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B323" t="s">
         <v>1342</v>
-      </c>
-      <c r="B323" t="s">
-        <v>1343</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="B324" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B325" t="s">
         <v>1338</v>
-      </c>
-      <c r="B325" t="s">
-        <v>1339</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
@@ -7548,10 +7554,10 @@
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B331" t="s">
         <v>1376</v>
-      </c>
-      <c r="B331" t="s">
-        <v>1377</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
@@ -7628,10 +7634,10 @@
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B341" t="s">
         <v>1356</v>
-      </c>
-      <c r="B341" t="s">
-        <v>1357</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
@@ -7716,10 +7722,10 @@
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="B352" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
@@ -7788,10 +7794,10 @@
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B361" t="s">
         <v>1348</v>
-      </c>
-      <c r="B361" t="s">
-        <v>1349</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
@@ -7996,10 +8002,10 @@
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B387" t="s">
         <v>1429</v>
-      </c>
-      <c r="B387" t="s">
-        <v>1430</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
@@ -8012,10 +8018,10 @@
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B389" t="s">
         <v>1505</v>
-      </c>
-      <c r="B389" t="s">
-        <v>1506</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
@@ -8348,10 +8354,10 @@
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B431" t="s">
         <v>1482</v>
-      </c>
-      <c r="B431" t="s">
-        <v>1483</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
@@ -8380,10 +8386,10 @@
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B435" t="s">
         <v>1427</v>
-      </c>
-      <c r="B435" t="s">
-        <v>1428</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
@@ -8420,10 +8426,10 @@
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B440" t="s">
         <v>1378</v>
-      </c>
-      <c r="B440" t="s">
-        <v>1379</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
@@ -8460,7 +8466,7 @@
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="B445" t="s">
         <v>515</v>
@@ -8588,18 +8594,18 @@
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B461" t="s">
         <v>1402</v>
-      </c>
-      <c r="B461" t="s">
-        <v>1403</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B462" t="s">
         <v>1404</v>
-      </c>
-      <c r="B462" t="s">
-        <v>1405</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
@@ -8620,10 +8626,10 @@
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B465" t="s">
         <v>1388</v>
-      </c>
-      <c r="B465" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
@@ -8676,18 +8682,18 @@
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B472" t="s">
         <v>1425</v>
-      </c>
-      <c r="B472" t="s">
-        <v>1426</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B473" t="s">
         <v>1331</v>
-      </c>
-      <c r="B473" t="s">
-        <v>1332</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
@@ -8812,10 +8818,10 @@
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B489" t="s">
         <v>1431</v>
-      </c>
-      <c r="B489" t="s">
-        <v>1432</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
@@ -8828,10 +8834,10 @@
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B491" t="s">
         <v>1419</v>
-      </c>
-      <c r="B491" t="s">
-        <v>1420</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
@@ -8860,18 +8866,18 @@
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B495" t="s">
         <v>1473</v>
-      </c>
-      <c r="B495" t="s">
-        <v>1474</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B496" t="s">
         <v>1471</v>
-      </c>
-      <c r="B496" t="s">
-        <v>1472</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
@@ -9036,10 +9042,10 @@
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B517" t="s">
         <v>1398</v>
-      </c>
-      <c r="B517" t="s">
-        <v>1399</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
@@ -9180,10 +9186,10 @@
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B535" t="s">
         <v>1354</v>
-      </c>
-      <c r="B535" t="s">
-        <v>1355</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
@@ -9303,7 +9309,7 @@
         <v>39</v>
       </c>
       <c r="B550" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
@@ -9311,7 +9317,7 @@
         <v>38</v>
       </c>
       <c r="B551" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
@@ -9332,10 +9338,10 @@
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B554" t="s">
         <v>1406</v>
-      </c>
-      <c r="B554" t="s">
-        <v>1407</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
@@ -9572,10 +9578,10 @@
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B584" t="s">
         <v>1437</v>
-      </c>
-      <c r="B584" t="s">
-        <v>1438</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
@@ -9636,10 +9642,10 @@
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B592" t="s">
         <v>1385</v>
-      </c>
-      <c r="B592" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
@@ -9772,10 +9778,10 @@
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B609" t="s">
         <v>1372</v>
-      </c>
-      <c r="B609" t="s">
-        <v>1373</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
@@ -10092,10 +10098,10 @@
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B649" t="s">
         <v>1367</v>
-      </c>
-      <c r="B649" t="s">
-        <v>1368</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.35">
@@ -10140,10 +10146,10 @@
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B655" t="s">
         <v>1327</v>
-      </c>
-      <c r="B655" t="s">
-        <v>1328</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.35">
@@ -10292,10 +10298,10 @@
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B674" t="s">
         <v>1394</v>
-      </c>
-      <c r="B674" t="s">
-        <v>1395</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.35">
@@ -10356,7 +10362,7 @@
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="B682" t="s">
         <v>966</v>
@@ -10399,31 +10405,31 @@
         <v>43</v>
       </c>
       <c r="B687" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B688" t="s">
         <v>1318</v>
-      </c>
-      <c r="B688" t="s">
-        <v>1319</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B689" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B690" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.35">
@@ -10431,15 +10437,15 @@
         <v>40</v>
       </c>
       <c r="B691" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B692" t="s">
         <v>1316</v>
-      </c>
-      <c r="B692" t="s">
-        <v>1317</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.35">
@@ -10476,18 +10482,18 @@
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B697" t="s">
         <v>1462</v>
-      </c>
-      <c r="B697" t="s">
-        <v>1463</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B698" t="s">
         <v>1464</v>
-      </c>
-      <c r="B698" t="s">
-        <v>1465</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.35">
@@ -10548,10 +10554,10 @@
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B706" t="s">
         <v>1496</v>
-      </c>
-      <c r="B706" t="s">
-        <v>1497</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.35">
@@ -10559,431 +10565,439 @@
         <v>1308</v>
       </c>
       <c r="B707" t="s">
-        <v>1313</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
-        <v>788</v>
+        <v>1508</v>
       </c>
       <c r="B708" t="s">
-        <v>789</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
-        <v>267</v>
+        <v>788</v>
       </c>
       <c r="B709" t="s">
-        <v>617</v>
+        <v>789</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
-        <v>654</v>
+        <v>267</v>
       </c>
       <c r="B710" t="s">
-        <v>737</v>
+        <v>617</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B711" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
-        <v>139</v>
+        <v>655</v>
       </c>
       <c r="B712" t="s">
-        <v>618</v>
+        <v>738</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="B713" t="s">
-        <v>2</v>
+        <v>618</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="B714" t="s">
-        <v>619</v>
+        <v>2</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A715" t="s">
-        <v>1323</v>
+        <v>105</v>
       </c>
       <c r="B715" t="s">
-        <v>1324</v>
+        <v>619</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A716" t="s">
-        <v>1024</v>
+        <v>1322</v>
       </c>
       <c r="B716" t="s">
-        <v>1102</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
-        <v>857</v>
+        <v>1024</v>
       </c>
       <c r="B717" t="s">
-        <v>858</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
-        <v>1423</v>
+        <v>857</v>
       </c>
       <c r="B718" t="s">
-        <v>1424</v>
+        <v>858</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
-        <v>1025</v>
+        <v>1422</v>
       </c>
       <c r="B719" t="s">
-        <v>1101</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
-        <v>292</v>
+        <v>1025</v>
       </c>
       <c r="B720" t="s">
-        <v>620</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
-        <v>8</v>
+        <v>292</v>
       </c>
       <c r="B721" t="s">
-        <v>11</v>
+        <v>620</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
-        <v>334</v>
+        <v>8</v>
       </c>
       <c r="B722" t="s">
-        <v>621</v>
+        <v>11</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
-        <v>1365</v>
+        <v>334</v>
       </c>
       <c r="B723" t="s">
-        <v>1366</v>
+        <v>621</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
-        <v>1325</v>
+        <v>1364</v>
       </c>
       <c r="B724" t="s">
-        <v>1326</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
-        <v>331</v>
+        <v>1324</v>
       </c>
       <c r="B725" t="s">
-        <v>622</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="B726" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
-        <v>318</v>
+        <v>259</v>
       </c>
       <c r="B727" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
-        <v>851</v>
+        <v>318</v>
       </c>
       <c r="B728" t="s">
-        <v>852</v>
+        <v>624</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
-        <v>1149</v>
+        <v>851</v>
       </c>
       <c r="B729" t="s">
-        <v>1150</v>
+        <v>852</v>
       </c>
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A730" t="s">
-        <v>268</v>
+        <v>1149</v>
       </c>
       <c r="B730" t="s">
-        <v>625</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B731" t="s">
-        <v>1099</v>
+        <v>625</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B732" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B733" t="s">
-        <v>1498</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B734" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B735" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B736" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A737" t="s">
-        <v>92</v>
+        <v>272</v>
       </c>
       <c r="B737" t="s">
-        <v>626</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
-        <v>200</v>
+        <v>92</v>
       </c>
       <c r="B738" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B739" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A740" t="s">
-        <v>1202</v>
+        <v>203</v>
       </c>
       <c r="B740" t="s">
-        <v>1502</v>
+        <v>628</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
-        <v>172</v>
+        <v>1202</v>
       </c>
       <c r="B741" t="s">
-        <v>629</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
-        <v>1454</v>
+        <v>172</v>
       </c>
       <c r="B742" t="s">
-        <v>1455</v>
+        <v>629</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B743" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A744" t="s">
         <v>686</v>
       </c>
-      <c r="B743" t="s">
+      <c r="B744" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="744" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A744" t="s">
+    <row r="745" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A745" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B745" s="1" t="s">
         <v>1449</v>
-      </c>
-      <c r="B744" s="1" t="s">
-        <v>1450</v>
-      </c>
-    </row>
-    <row r="745" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A745" t="s">
-        <v>252</v>
-      </c>
-      <c r="B745" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A746" t="s">
-        <v>687</v>
+        <v>252</v>
       </c>
       <c r="B746" t="s">
-        <v>740</v>
+        <v>630</v>
       </c>
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A747" t="s">
-        <v>189</v>
+        <v>687</v>
       </c>
       <c r="B747" t="s">
-        <v>1393</v>
+        <v>740</v>
       </c>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A748" t="s">
-        <v>980</v>
+        <v>189</v>
       </c>
       <c r="B748" t="s">
-        <v>981</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A749" t="s">
-        <v>311</v>
+        <v>980</v>
       </c>
       <c r="B749" t="s">
-        <v>631</v>
+        <v>981</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A750" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B750" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A751" t="s">
-        <v>1023</v>
+        <v>312</v>
       </c>
       <c r="B751" t="s">
-        <v>1448</v>
+        <v>632</v>
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A752" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B752" t="s">
         <v>1447</v>
-      </c>
-      <c r="B752" t="s">
-        <v>1468</v>
       </c>
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A753" t="s">
-        <v>996</v>
+        <v>1446</v>
       </c>
       <c r="B753" t="s">
-        <v>997</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="754" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A754" t="s">
-        <v>81</v>
+        <v>996</v>
       </c>
       <c r="B754" t="s">
-        <v>633</v>
+        <v>997</v>
       </c>
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A755" t="s">
-        <v>644</v>
+        <v>81</v>
       </c>
       <c r="B755" t="s">
-        <v>741</v>
+        <v>633</v>
       </c>
     </row>
     <row r="756" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A756" t="s">
-        <v>913</v>
+        <v>644</v>
       </c>
       <c r="B756" t="s">
-        <v>914</v>
+        <v>741</v>
       </c>
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A757" t="s">
-        <v>635</v>
+        <v>913</v>
       </c>
       <c r="B757" t="s">
-        <v>742</v>
+        <v>914</v>
       </c>
     </row>
     <row r="758" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A758" t="s">
-        <v>960</v>
+        <v>635</v>
       </c>
       <c r="B758" t="s">
-        <v>961</v>
+        <v>742</v>
       </c>
     </row>
     <row r="759" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A759" t="s">
-        <v>1137</v>
+        <v>960</v>
       </c>
       <c r="B759" t="s">
-        <v>1138</v>
+        <v>961</v>
       </c>
     </row>
     <row r="760" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A760" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B760" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A761" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B761" t="s">
         <v>1363</v>
-      </c>
-      <c r="B760" t="s">
-        <v>1364</v>
       </c>
     </row>
   </sheetData>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D33706E-DB0B-4477-B951-881D079F20D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB952ADD-D814-4A47-B0D1-D8CE51BAEE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="1511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="1513">
   <si>
     <t>trigger</t>
   </si>
@@ -4561,6 +4561,12 @@
   </si>
   <si>
     <t>Geographic area of increased arterial phase enhancement is seen in segment ... of the liver without associated mass effect or contour abnormality, becoming isodense on portal venous phase - suggestive of transient hepatic attenuation differences (THAD)</t>
+  </si>
+  <si>
+    <t>sp</t>
+  </si>
+  <si>
+    <t>ehng</t>
   </si>
 </sst>
 </file>
@@ -4629,10 +4635,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B761" totalsRowShown="0">
-  <autoFilter ref="A1:B761" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B761">
-    <sortCondition ref="A1:A761"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B763" totalsRowShown="0">
+  <autoFilter ref="A1:B763" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B763">
+    <sortCondition ref="A1:A763"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4905,7 +4911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B761"/>
+  <dimension ref="A1:B763"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -6618,239 +6624,239 @@
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>1032</v>
+        <v>1512</v>
       </c>
       <c r="B214" t="s">
-        <v>1033</v>
+        <v>416</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>154</v>
+        <v>1032</v>
       </c>
       <c r="B215" t="s">
-        <v>414</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B216" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="B217" t="s">
-        <v>1114</v>
+        <v>415</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>1139</v>
+        <v>24</v>
       </c>
       <c r="B218" t="s">
-        <v>1140</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>1302</v>
+        <v>1139</v>
       </c>
       <c r="B219" t="s">
-        <v>1303</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>1064</v>
+        <v>1302</v>
       </c>
       <c r="B220" t="s">
-        <v>1065</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>1457</v>
+        <v>1064</v>
       </c>
       <c r="B221" t="s">
-        <v>1458</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>812</v>
+        <v>1457</v>
       </c>
       <c r="B222" t="s">
-        <v>813</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>130</v>
+        <v>812</v>
       </c>
       <c r="B223" t="s">
-        <v>416</v>
+        <v>813</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>321</v>
+        <v>130</v>
       </c>
       <c r="B224" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>1456</v>
+        <v>321</v>
       </c>
       <c r="B225" t="s">
-        <v>1417</v>
+        <v>417</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>859</v>
+        <v>1456</v>
       </c>
       <c r="B226" t="s">
-        <v>860</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>1420</v>
+        <v>859</v>
       </c>
       <c r="B227" t="s">
-        <v>1421</v>
+        <v>860</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>1455</v>
+        <v>1420</v>
       </c>
       <c r="B228" t="s">
-        <v>883</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>1291</v>
+        <v>1455</v>
       </c>
       <c r="B229" t="s">
-        <v>1292</v>
+        <v>883</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>183</v>
+        <v>1291</v>
       </c>
       <c r="B230" t="s">
-        <v>418</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>1130</v>
+        <v>183</v>
       </c>
       <c r="B231" t="s">
-        <v>1131</v>
+        <v>418</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B232" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>1411</v>
+        <v>1132</v>
       </c>
       <c r="B233" t="s">
-        <v>1412</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>1484</v>
+        <v>1411</v>
       </c>
       <c r="B234" t="s">
-        <v>1485</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>1369</v>
+        <v>1484</v>
       </c>
       <c r="B235" t="s">
-        <v>1370</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>1486</v>
+        <v>1369</v>
       </c>
       <c r="B236" t="s">
-        <v>1487</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>32</v>
+        <v>1486</v>
       </c>
       <c r="B237" t="s">
-        <v>419</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B238" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>1281</v>
+        <v>35</v>
       </c>
       <c r="B239" t="s">
-        <v>1282</v>
+        <v>420</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>1207</v>
+        <v>1281</v>
       </c>
       <c r="B240" t="s">
-        <v>1208</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>757</v>
+        <v>1207</v>
       </c>
       <c r="B241" t="s">
-        <v>1000</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>169</v>
+        <v>757</v>
       </c>
       <c r="B242" t="s">
-        <v>421</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B243" t="s">
         <v>421</v>
@@ -6858,615 +6864,615 @@
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>1001</v>
+        <v>170</v>
       </c>
       <c r="B244" t="s">
-        <v>758</v>
+        <v>421</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>1409</v>
+        <v>1001</v>
       </c>
       <c r="B245" t="s">
-        <v>1410</v>
+        <v>758</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>178</v>
+        <v>1409</v>
       </c>
       <c r="B246" t="s">
-        <v>422</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="B247" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>238</v>
+        <v>111</v>
       </c>
       <c r="B248" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="B249" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B250" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="B251" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>660</v>
+        <v>179</v>
       </c>
       <c r="B252" t="s">
-        <v>715</v>
+        <v>427</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>1475</v>
+        <v>660</v>
       </c>
       <c r="B253" t="s">
-        <v>1476</v>
+        <v>715</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>97</v>
+        <v>1475</v>
       </c>
       <c r="B254" t="s">
-        <v>428</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B255" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>242</v>
+        <v>110</v>
       </c>
       <c r="B256" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B257" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="B258" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>1407</v>
+        <v>177</v>
       </c>
       <c r="B259" t="s">
-        <v>1408</v>
+        <v>432</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>182</v>
+        <v>1407</v>
       </c>
       <c r="B260" t="s">
-        <v>433</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>1094</v>
+        <v>182</v>
       </c>
       <c r="B261" t="s">
-        <v>1095</v>
+        <v>433</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>968</v>
+        <v>1094</v>
       </c>
       <c r="B262" t="s">
-        <v>969</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B263" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>1173</v>
+        <v>970</v>
       </c>
       <c r="B264" t="s">
-        <v>1174</v>
+        <v>971</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>1349</v>
+        <v>1173</v>
       </c>
       <c r="B265" t="s">
-        <v>1350</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>1176</v>
+        <v>1349</v>
       </c>
       <c r="B266" t="s">
-        <v>1177</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>253</v>
+        <v>1176</v>
       </c>
       <c r="B267" t="s">
-        <v>434</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="B268" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>780</v>
+        <v>34</v>
       </c>
       <c r="B269" t="s">
-        <v>781</v>
+        <v>435</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>180</v>
+        <v>780</v>
       </c>
       <c r="B270" t="s">
-        <v>436</v>
+        <v>781</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>1321</v>
+        <v>180</v>
       </c>
       <c r="B271" t="s">
-        <v>1390</v>
+        <v>436</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B272" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>1438</v>
+        <v>1320</v>
       </c>
       <c r="B273" t="s">
-        <v>1439</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>275</v>
+        <v>1438</v>
       </c>
       <c r="B274" t="s">
-        <v>1491</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>850</v>
+        <v>275</v>
       </c>
       <c r="B275" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>1493</v>
+        <v>850</v>
       </c>
       <c r="B276" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>1506</v>
+        <v>1493</v>
       </c>
       <c r="B277" t="s">
-        <v>1507</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>116</v>
+        <v>1506</v>
       </c>
       <c r="B278" t="s">
-        <v>437</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="B279" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>1395</v>
+        <v>208</v>
       </c>
       <c r="B280" t="s">
-        <v>1396</v>
+        <v>438</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>1196</v>
+        <v>1395</v>
       </c>
       <c r="B281" t="s">
-        <v>1197</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>1044</v>
+        <v>1196</v>
       </c>
       <c r="B282" t="s">
-        <v>1045</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>118</v>
+        <v>1044</v>
       </c>
       <c r="B283" t="s">
-        <v>439</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>634</v>
+        <v>118</v>
       </c>
       <c r="B284" t="s">
-        <v>716</v>
+        <v>439</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>1306</v>
+        <v>634</v>
       </c>
       <c r="B285" t="s">
-        <v>1307</v>
+        <v>716</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>808</v>
+        <v>1306</v>
       </c>
       <c r="B286" t="s">
-        <v>809</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>298</v>
+        <v>808</v>
       </c>
       <c r="B287" t="s">
-        <v>440</v>
+        <v>809</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>636</v>
+        <v>298</v>
       </c>
       <c r="B288" t="s">
-        <v>717</v>
+        <v>440</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B289" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>1026</v>
+        <v>637</v>
       </c>
       <c r="B290" t="s">
-        <v>1027</v>
+        <v>718</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>90</v>
+        <v>1026</v>
       </c>
       <c r="B291" t="s">
-        <v>441</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B292" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B293" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>1060</v>
+        <v>89</v>
       </c>
       <c r="B294" t="s">
-        <v>1061</v>
+        <v>443</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>23</v>
+        <v>1060</v>
       </c>
       <c r="B295" t="s">
-        <v>1113</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>1399</v>
+        <v>23</v>
       </c>
       <c r="B296" t="s">
-        <v>1400</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>5</v>
+        <v>1399</v>
       </c>
       <c r="B297" t="s">
-        <v>6</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>1117</v>
+        <v>5</v>
       </c>
       <c r="B298" t="s">
-        <v>1118</v>
+        <v>6</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>126</v>
+        <v>1117</v>
       </c>
       <c r="B299" t="s">
-        <v>444</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>1373</v>
+        <v>126</v>
       </c>
       <c r="B300" t="s">
-        <v>1374</v>
+        <v>444</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>128</v>
+        <v>1373</v>
       </c>
       <c r="B301" t="s">
-        <v>445</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B302" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B303" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B304" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>277</v>
+        <v>119</v>
       </c>
       <c r="B305" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>1062</v>
+        <v>277</v>
       </c>
       <c r="B306" t="s">
-        <v>1063</v>
+        <v>449</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>9</v>
+        <v>1062</v>
       </c>
       <c r="B307" t="s">
-        <v>10</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="B308" t="s">
-        <v>450</v>
+        <v>10</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B309" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="B310" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="B311" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>1360</v>
+        <v>262</v>
       </c>
       <c r="B312" t="s">
-        <v>1361</v>
+        <v>453</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>77</v>
+        <v>1360</v>
       </c>
       <c r="B313" t="s">
-        <v>454</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>929</v>
+        <v>77</v>
       </c>
       <c r="B314" t="s">
-        <v>930</v>
+        <v>454</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>1147</v>
+        <v>929</v>
       </c>
       <c r="B315" t="s">
-        <v>1148</v>
+        <v>930</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>168</v>
+        <v>1147</v>
       </c>
       <c r="B316" t="s">
-        <v>455</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>1333</v>
+        <v>168</v>
       </c>
       <c r="B317" t="s">
-        <v>1334</v>
+        <v>455</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>1343</v>
+        <v>1333</v>
       </c>
       <c r="B318" t="s">
-        <v>1344</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>1386</v>
+        <v>1343</v>
       </c>
       <c r="B319" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>1339</v>
+        <v>1386</v>
       </c>
       <c r="B320" t="s">
         <v>1340</v>
@@ -7474,39 +7480,39 @@
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>167</v>
+        <v>1339</v>
       </c>
       <c r="B321" t="s">
-        <v>456</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>1335</v>
+        <v>167</v>
       </c>
       <c r="B322" t="s">
-        <v>1336</v>
+        <v>456</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>1341</v>
+        <v>1335</v>
       </c>
       <c r="B323" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>1368</v>
+        <v>1341</v>
       </c>
       <c r="B324" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>1337</v>
+        <v>1368</v>
       </c>
       <c r="B325" t="s">
         <v>1338</v>
@@ -7514,199 +7520,199 @@
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>828</v>
+        <v>1337</v>
       </c>
       <c r="B326" t="s">
-        <v>829</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>784</v>
+        <v>828</v>
       </c>
       <c r="B327" t="s">
-        <v>785</v>
+        <v>829</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>304</v>
+        <v>784</v>
       </c>
       <c r="B328" t="s">
-        <v>457</v>
+        <v>785</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>751</v>
+        <v>304</v>
       </c>
       <c r="B329" t="s">
-        <v>752</v>
+        <v>457</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>888</v>
+        <v>751</v>
       </c>
       <c r="B330" t="s">
-        <v>889</v>
+        <v>752</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>1375</v>
+        <v>888</v>
       </c>
       <c r="B331" t="s">
-        <v>1376</v>
+        <v>889</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>645</v>
+        <v>1375</v>
       </c>
       <c r="B332" t="s">
-        <v>719</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>86</v>
+        <v>645</v>
       </c>
       <c r="B333" t="s">
-        <v>458</v>
+        <v>719</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B334" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="B335" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B336" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B337" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>251</v>
+        <v>158</v>
       </c>
       <c r="B338" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="B339" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>325</v>
+        <v>285</v>
       </c>
       <c r="B340" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>1355</v>
+        <v>325</v>
       </c>
       <c r="B341" t="s">
-        <v>1356</v>
+        <v>465</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>326</v>
+        <v>1355</v>
       </c>
       <c r="B342" t="s">
-        <v>466</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>229</v>
+        <v>326</v>
       </c>
       <c r="B343" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>55</v>
+        <v>229</v>
       </c>
       <c r="B344" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>650</v>
+        <v>55</v>
       </c>
       <c r="B345" t="s">
-        <v>720</v>
+        <v>468</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>235</v>
+        <v>650</v>
       </c>
       <c r="B346" t="s">
-        <v>469</v>
+        <v>720</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="B347" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="B348" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>759</v>
+        <v>236</v>
       </c>
       <c r="B349" t="s">
-        <v>760</v>
+        <v>471</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>1002</v>
+        <v>759</v>
       </c>
       <c r="B350" t="s">
         <v>760</v>
@@ -7714,639 +7720,639 @@
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>164</v>
+        <v>1002</v>
       </c>
       <c r="B351" t="s">
-        <v>472</v>
+        <v>760</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>1452</v>
+        <v>164</v>
       </c>
       <c r="B352" t="s">
-        <v>1450</v>
+        <v>472</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>201</v>
+        <v>1452</v>
       </c>
       <c r="B353" t="s">
-        <v>473</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B354" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>313</v>
+        <v>204</v>
       </c>
       <c r="B355" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>865</v>
+        <v>313</v>
       </c>
       <c r="B356" t="s">
-        <v>866</v>
+        <v>475</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>988</v>
+        <v>865</v>
       </c>
       <c r="B357" t="s">
-        <v>989</v>
+        <v>866</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>1309</v>
+        <v>988</v>
       </c>
       <c r="B358" t="s">
-        <v>1310</v>
+        <v>989</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>258</v>
+        <v>1309</v>
       </c>
       <c r="B359" t="s">
-        <v>476</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>974</v>
+        <v>258</v>
       </c>
       <c r="B360" t="s">
-        <v>975</v>
+        <v>476</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>1347</v>
+        <v>974</v>
       </c>
       <c r="B361" t="s">
-        <v>1348</v>
+        <v>975</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>160</v>
+        <v>1347</v>
       </c>
       <c r="B362" t="s">
-        <v>477</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>685</v>
+        <v>160</v>
       </c>
       <c r="B363" t="s">
-        <v>721</v>
+        <v>477</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>1141</v>
+        <v>685</v>
       </c>
       <c r="B364" t="s">
-        <v>1142</v>
+        <v>721</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>753</v>
+        <v>1141</v>
       </c>
       <c r="B365" t="s">
-        <v>754</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>886</v>
+        <v>753</v>
       </c>
       <c r="B366" t="s">
-        <v>887</v>
+        <v>754</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B367" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>184</v>
+        <v>884</v>
       </c>
       <c r="B368" t="s">
-        <v>478</v>
+        <v>885</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>244</v>
+        <v>184</v>
       </c>
       <c r="B369" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B370" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>1253</v>
+        <v>243</v>
       </c>
       <c r="B371" t="s">
-        <v>1258</v>
+        <v>480</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>679</v>
+        <v>1253</v>
       </c>
       <c r="B372" t="s">
-        <v>722</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>1254</v>
+        <v>679</v>
       </c>
       <c r="B373" t="s">
-        <v>1259</v>
+        <v>722</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>680</v>
+        <v>1254</v>
       </c>
       <c r="B374" t="s">
-        <v>723</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>1255</v>
+        <v>680</v>
       </c>
       <c r="B375" t="s">
-        <v>1260</v>
+        <v>723</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>681</v>
+        <v>1255</v>
       </c>
       <c r="B376" t="s">
-        <v>724</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>1256</v>
+        <v>681</v>
       </c>
       <c r="B377" t="s">
-        <v>1261</v>
+        <v>724</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>682</v>
+        <v>1256</v>
       </c>
       <c r="B378" t="s">
-        <v>725</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>1257</v>
+        <v>682</v>
       </c>
       <c r="B379" t="s">
-        <v>1262</v>
+        <v>725</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>683</v>
+        <v>1257</v>
       </c>
       <c r="B380" t="s">
-        <v>726</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>1167</v>
+        <v>683</v>
       </c>
       <c r="B381" t="s">
-        <v>1168</v>
+        <v>726</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>280</v>
+        <v>1167</v>
       </c>
       <c r="B382" t="s">
-        <v>481</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B383" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>49</v>
+        <v>281</v>
       </c>
       <c r="B384" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B385" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="B386" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>1428</v>
+        <v>136</v>
       </c>
       <c r="B387" t="s">
-        <v>1429</v>
+        <v>486</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>72</v>
+        <v>1428</v>
       </c>
       <c r="B388" t="s">
-        <v>485</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>1504</v>
+        <v>72</v>
       </c>
       <c r="B389" t="s">
-        <v>1505</v>
+        <v>485</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>1165</v>
+        <v>1504</v>
       </c>
       <c r="B390" t="s">
-        <v>1166</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>221</v>
+        <v>1165</v>
       </c>
       <c r="B391" t="s">
-        <v>487</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>1169</v>
+        <v>221</v>
       </c>
       <c r="B392" t="s">
-        <v>1170</v>
+        <v>487</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>15</v>
+        <v>1169</v>
       </c>
       <c r="B393" t="s">
-        <v>16</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>1048</v>
+        <v>15</v>
       </c>
       <c r="B394" t="s">
-        <v>1049</v>
+        <v>16</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>911</v>
+        <v>1048</v>
       </c>
       <c r="B395" t="s">
-        <v>912</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>108</v>
+        <v>911</v>
       </c>
       <c r="B396" t="s">
-        <v>488</v>
+        <v>912</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>241</v>
+        <v>108</v>
       </c>
       <c r="B397" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>327</v>
+        <v>241</v>
       </c>
       <c r="B398" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>1088</v>
+        <v>327</v>
       </c>
       <c r="B399" t="s">
-        <v>1089</v>
+        <v>490</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>1040</v>
+        <v>1088</v>
       </c>
       <c r="B400" t="s">
-        <v>1041</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>121</v>
+        <v>1040</v>
       </c>
       <c r="B401" t="s">
-        <v>491</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>743</v>
+        <v>121</v>
       </c>
       <c r="B402" t="s">
-        <v>744</v>
+        <v>491</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>774</v>
+        <v>743</v>
       </c>
       <c r="B403" t="s">
-        <v>775</v>
+        <v>744</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>134</v>
+        <v>774</v>
       </c>
       <c r="B404" t="s">
-        <v>492</v>
+        <v>775</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="B405" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>1287</v>
+        <v>63</v>
       </c>
       <c r="B406" t="s">
-        <v>1288</v>
+        <v>493</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>224</v>
+        <v>1287</v>
       </c>
       <c r="B407" t="s">
-        <v>494</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>25</v>
+        <v>224</v>
       </c>
       <c r="B408" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B409" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>207</v>
+        <v>26</v>
       </c>
       <c r="B410" t="s">
-        <v>1110</v>
+        <v>496</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>951</v>
+        <v>207</v>
       </c>
       <c r="B411" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>1097</v>
+        <v>951</v>
       </c>
       <c r="B412" t="s">
-        <v>1098</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>206</v>
+        <v>1097</v>
       </c>
       <c r="B413" t="s">
-        <v>1112</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B414" t="s">
-        <v>497</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B415" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="B416" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>656</v>
+        <v>145</v>
       </c>
       <c r="B417" t="s">
-        <v>727</v>
+        <v>499</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>171</v>
+        <v>656</v>
       </c>
       <c r="B418" t="s">
-        <v>500</v>
+        <v>727</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>1076</v>
+        <v>171</v>
       </c>
       <c r="B419" t="s">
-        <v>1077</v>
+        <v>500</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>263</v>
+        <v>1076</v>
       </c>
       <c r="B420" t="s">
-        <v>501</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>1078</v>
+        <v>263</v>
       </c>
       <c r="B421" t="s">
-        <v>1079</v>
+        <v>501</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>80</v>
+        <v>1078</v>
       </c>
       <c r="B422" t="s">
-        <v>502</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B423" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>191</v>
+        <v>65</v>
       </c>
       <c r="B424" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="B425" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>192</v>
+        <v>123</v>
       </c>
       <c r="B426" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="B427" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B428" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>1175</v>
+        <v>233</v>
       </c>
       <c r="B429" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>31</v>
+        <v>1175</v>
       </c>
       <c r="B430" t="s">
         <v>509</v>
@@ -8354,375 +8360,375 @@
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>1481</v>
+        <v>31</v>
       </c>
       <c r="B431" t="s">
-        <v>1482</v>
+        <v>509</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>30</v>
+        <v>1481</v>
       </c>
       <c r="B432" t="s">
-        <v>510</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B433" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B434" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>1426</v>
+        <v>71</v>
       </c>
       <c r="B435" t="s">
-        <v>1427</v>
+        <v>512</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>306</v>
+        <v>1426</v>
       </c>
       <c r="B436" t="s">
-        <v>513</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>222</v>
+        <v>306</v>
       </c>
       <c r="B437" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>278</v>
+        <v>222</v>
       </c>
       <c r="B438" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B439" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>1377</v>
+        <v>279</v>
       </c>
       <c r="B440" t="s">
-        <v>1378</v>
+        <v>517</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>824</v>
+        <v>1377</v>
       </c>
       <c r="B441" t="s">
-        <v>825</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>48</v>
+        <v>824</v>
       </c>
       <c r="B442" t="s">
-        <v>518</v>
+        <v>825</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="B443" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="B444" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>1359</v>
+        <v>52</v>
       </c>
       <c r="B445" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>223</v>
+        <v>1359</v>
       </c>
       <c r="B446" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>1082</v>
+        <v>223</v>
       </c>
       <c r="B447" t="s">
-        <v>1083</v>
+        <v>521</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>1093</v>
+        <v>1082</v>
       </c>
       <c r="B448" t="s">
-        <v>1096</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>1038</v>
+        <v>1093</v>
       </c>
       <c r="B449" t="s">
-        <v>1039</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>96</v>
+        <v>1038</v>
       </c>
       <c r="B450" t="s">
-        <v>522</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>248</v>
+        <v>96</v>
       </c>
       <c r="B451" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B452" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>94</v>
+        <v>249</v>
       </c>
       <c r="B453" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>1052</v>
+        <v>94</v>
       </c>
       <c r="B454" t="s">
-        <v>1053</v>
+        <v>525</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>212</v>
+        <v>1052</v>
       </c>
       <c r="B455" t="s">
-        <v>526</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>1200</v>
+        <v>212</v>
       </c>
       <c r="B456" t="s">
-        <v>1201</v>
+        <v>526</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>907</v>
+        <v>1200</v>
       </c>
       <c r="B457" t="s">
-        <v>908</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B458" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="B459" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>329</v>
+        <v>909</v>
       </c>
       <c r="B460" t="s">
-        <v>527</v>
+        <v>910</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>1401</v>
+        <v>329</v>
       </c>
       <c r="B461" t="s">
-        <v>1402</v>
+        <v>527</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="B462" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>1054</v>
+        <v>1403</v>
       </c>
       <c r="B463" t="s">
-        <v>1055</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>986</v>
+        <v>1054</v>
       </c>
       <c r="B464" t="s">
-        <v>987</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>1387</v>
+        <v>986</v>
       </c>
       <c r="B465" t="s">
-        <v>1388</v>
+        <v>987</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>982</v>
+        <v>1387</v>
       </c>
       <c r="B466" t="s">
-        <v>983</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B467" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>82</v>
+        <v>984</v>
       </c>
       <c r="B468" t="s">
-        <v>528</v>
+        <v>985</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>765</v>
+        <v>82</v>
       </c>
       <c r="B469" t="s">
-        <v>766</v>
+        <v>528</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>197</v>
+        <v>765</v>
       </c>
       <c r="B470" t="s">
-        <v>529</v>
+        <v>766</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>647</v>
+        <v>197</v>
       </c>
       <c r="B471" t="s">
-        <v>728</v>
+        <v>529</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>1424</v>
+        <v>647</v>
       </c>
       <c r="B472" t="s">
-        <v>1425</v>
+        <v>728</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>1330</v>
+        <v>1424</v>
       </c>
       <c r="B473" t="s">
-        <v>1331</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>814</v>
+        <v>1330</v>
       </c>
       <c r="B474" t="s">
-        <v>815</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>1056</v>
+        <v>814</v>
       </c>
       <c r="B475" t="s">
-        <v>1057</v>
+        <v>815</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>3</v>
+        <v>1056</v>
       </c>
       <c r="B476" t="s">
-        <v>4</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>949</v>
+        <v>3</v>
       </c>
       <c r="B477" t="s">
         <v>4</v>
@@ -8730,7 +8736,7 @@
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B478" t="s">
         <v>4</v>
@@ -8738,2265 +8744,2281 @@
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>657</v>
+        <v>950</v>
       </c>
       <c r="B479" t="s">
-        <v>729</v>
+        <v>4</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>1279</v>
+        <v>657</v>
       </c>
       <c r="B480" t="s">
-        <v>1280</v>
+        <v>729</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>763</v>
+        <v>1279</v>
       </c>
       <c r="B481" t="s">
-        <v>764</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>85</v>
+        <v>763</v>
       </c>
       <c r="B482" t="s">
-        <v>530</v>
+        <v>764</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>1050</v>
+        <v>85</v>
       </c>
       <c r="B483" t="s">
-        <v>1051</v>
+        <v>530</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>822</v>
+        <v>1050</v>
       </c>
       <c r="B484" t="s">
-        <v>823</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>802</v>
+        <v>822</v>
       </c>
       <c r="B485" t="s">
-        <v>803</v>
+        <v>823</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>187</v>
+        <v>802</v>
       </c>
       <c r="B486" t="s">
-        <v>531</v>
+        <v>803</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>820</v>
+        <v>187</v>
       </c>
       <c r="B487" t="s">
-        <v>821</v>
+        <v>531</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>925</v>
+        <v>820</v>
       </c>
       <c r="B488" t="s">
-        <v>1107</v>
+        <v>821</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>1430</v>
+        <v>925</v>
       </c>
       <c r="B489" t="s">
-        <v>1431</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>855</v>
+        <v>1430</v>
       </c>
       <c r="B490" t="s">
-        <v>856</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>1418</v>
+        <v>855</v>
       </c>
       <c r="B491" t="s">
-        <v>1419</v>
+        <v>856</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>1034</v>
+        <v>1418</v>
       </c>
       <c r="B492" t="s">
-        <v>1035</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>791</v>
+        <v>1034</v>
       </c>
       <c r="B493" t="s">
-        <v>1108</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B494" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>1472</v>
+        <v>790</v>
       </c>
       <c r="B495" t="s">
-        <v>1473</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="B496" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>13</v>
+        <v>1470</v>
       </c>
       <c r="B497" t="s">
-        <v>14</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>810</v>
+        <v>13</v>
       </c>
       <c r="B498" t="s">
-        <v>811</v>
+        <v>14</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>1209</v>
+        <v>810</v>
       </c>
       <c r="B499" t="s">
-        <v>1210</v>
+        <v>811</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>186</v>
+        <v>1209</v>
       </c>
       <c r="B500" t="s">
-        <v>532</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>804</v>
+        <v>186</v>
       </c>
       <c r="B501" t="s">
-        <v>805</v>
+        <v>532</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>319</v>
+        <v>804</v>
       </c>
       <c r="B502" t="s">
-        <v>533</v>
+        <v>805</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>649</v>
+        <v>319</v>
       </c>
       <c r="B503" t="s">
-        <v>730</v>
+        <v>533</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>848</v>
+        <v>649</v>
       </c>
       <c r="B504" t="s">
-        <v>849</v>
+        <v>730</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>651</v>
+        <v>848</v>
       </c>
       <c r="B505" t="s">
-        <v>731</v>
+        <v>849</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="B506" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>1182</v>
+        <v>646</v>
       </c>
       <c r="B507" t="s">
-        <v>1183</v>
+        <v>732</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>256</v>
+        <v>1182</v>
       </c>
       <c r="B508" t="s">
-        <v>534</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B509" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B510" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>188</v>
+        <v>261</v>
       </c>
       <c r="B511" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B512" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>927</v>
+        <v>190</v>
       </c>
       <c r="B513" t="s">
-        <v>928</v>
+        <v>538</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>1021</v>
+        <v>927</v>
       </c>
       <c r="B514" t="s">
-        <v>1022</v>
+        <v>928</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>1198</v>
+        <v>1021</v>
       </c>
       <c r="B515" t="s">
-        <v>1199</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>209</v>
+        <v>1198</v>
       </c>
       <c r="B516" t="s">
-        <v>539</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>1397</v>
+        <v>209</v>
       </c>
       <c r="B517" t="s">
-        <v>1398</v>
+        <v>539</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>1289</v>
+        <v>1397</v>
       </c>
       <c r="B518" t="s">
-        <v>1290</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>844</v>
+        <v>1289</v>
       </c>
       <c r="B519" t="s">
-        <v>845</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>143</v>
+        <v>844</v>
       </c>
       <c r="B520" t="s">
-        <v>540</v>
+        <v>845</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B521" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>1178</v>
+        <v>140</v>
       </c>
       <c r="B522" t="s">
-        <v>1179</v>
+        <v>541</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>1277</v>
+        <v>1178</v>
       </c>
       <c r="B523" t="s">
-        <v>1278</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>254</v>
+        <v>1277</v>
       </c>
       <c r="B524" t="s">
-        <v>542</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>330</v>
+        <v>254</v>
       </c>
       <c r="B525" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="B526" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="B527" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>73</v>
+        <v>234</v>
       </c>
       <c r="B528" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>341</v>
+        <v>73</v>
       </c>
       <c r="B529" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>308</v>
+        <v>341</v>
       </c>
       <c r="B530" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>836</v>
+        <v>308</v>
       </c>
       <c r="B531" t="s">
-        <v>837</v>
+        <v>548</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B532" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>220</v>
+        <v>838</v>
       </c>
       <c r="B533" t="s">
-        <v>549</v>
+        <v>839</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>900</v>
+        <v>220</v>
       </c>
       <c r="B534" t="s">
-        <v>901</v>
+        <v>549</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>1353</v>
+        <v>900</v>
       </c>
       <c r="B535" t="s">
-        <v>1354</v>
+        <v>901</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>954</v>
+        <v>1353</v>
       </c>
       <c r="B536" t="s">
-        <v>955</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>1163</v>
+        <v>954</v>
       </c>
       <c r="B537" t="s">
-        <v>1164</v>
+        <v>955</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>227</v>
+        <v>1163</v>
       </c>
       <c r="B538" t="s">
-        <v>550</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>333</v>
+        <v>227</v>
       </c>
       <c r="B539" t="s">
-        <v>1136</v>
+        <v>550</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>962</v>
+        <v>333</v>
       </c>
       <c r="B540" t="s">
-        <v>963</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>771</v>
+        <v>962</v>
       </c>
       <c r="B541" t="s">
-        <v>772</v>
+        <v>963</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>294</v>
+        <v>771</v>
       </c>
       <c r="B542" t="s">
-        <v>551</v>
+        <v>772</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>943</v>
+        <v>294</v>
       </c>
       <c r="B543" t="s">
-        <v>944</v>
+        <v>551</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>338</v>
+        <v>943</v>
       </c>
       <c r="B544" t="s">
-        <v>552</v>
+        <v>944</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>773</v>
+        <v>338</v>
       </c>
       <c r="B545" t="s">
-        <v>772</v>
+        <v>552</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>1293</v>
+        <v>773</v>
       </c>
       <c r="B546" t="s">
-        <v>1294</v>
+        <v>772</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>339</v>
+        <v>1293</v>
       </c>
       <c r="B547" t="s">
-        <v>553</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B548" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>638</v>
+        <v>340</v>
       </c>
       <c r="B549" t="s">
-        <v>733</v>
+        <v>554</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>39</v>
+        <v>638</v>
       </c>
       <c r="B550" t="s">
-        <v>1490</v>
+        <v>733</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B551" t="s">
-        <v>1483</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>342</v>
+        <v>38</v>
       </c>
       <c r="B552" t="s">
-        <v>555</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>107</v>
+        <v>342</v>
       </c>
       <c r="B553" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>1405</v>
+        <v>107</v>
       </c>
       <c r="B554" t="s">
-        <v>1406</v>
+        <v>556</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>1019</v>
+        <v>1405</v>
       </c>
       <c r="B555" t="s">
-        <v>1020</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>894</v>
+        <v>1019</v>
       </c>
       <c r="B556" t="s">
-        <v>895</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>117</v>
+        <v>894</v>
       </c>
       <c r="B557" t="s">
-        <v>557</v>
+        <v>895</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>1015</v>
+        <v>117</v>
       </c>
       <c r="B558" t="s">
-        <v>1016</v>
+        <v>557</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>98</v>
+        <v>1015</v>
       </c>
       <c r="B559" t="s">
-        <v>558</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B560" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>659</v>
+        <v>99</v>
       </c>
       <c r="B561" t="s">
-        <v>734</v>
+        <v>559</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>1091</v>
+        <v>659</v>
       </c>
       <c r="B562" t="s">
-        <v>1014</v>
+        <v>734</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>816</v>
+        <v>1091</v>
       </c>
       <c r="B563" t="s">
-        <v>817</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>113</v>
+        <v>816</v>
       </c>
       <c r="B564" t="s">
-        <v>560</v>
+        <v>817</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>881</v>
+        <v>113</v>
       </c>
       <c r="B565" t="s">
-        <v>882</v>
+        <v>560</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>45</v>
+        <v>881</v>
       </c>
       <c r="B566" t="s">
-        <v>1106</v>
+        <v>882</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>290</v>
+        <v>45</v>
       </c>
       <c r="B567" t="s">
-        <v>561</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B568" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>47</v>
+        <v>299</v>
       </c>
       <c r="B569" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>840</v>
+        <v>47</v>
       </c>
       <c r="B570" t="s">
-        <v>841</v>
+        <v>563</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>51</v>
+        <v>840</v>
       </c>
       <c r="B571" t="s">
-        <v>564</v>
+        <v>841</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>863</v>
+        <v>51</v>
       </c>
       <c r="B572" t="s">
-        <v>864</v>
+        <v>564</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>114</v>
+        <v>863</v>
       </c>
       <c r="B573" t="s">
-        <v>565</v>
+        <v>864</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>846</v>
+        <v>114</v>
       </c>
       <c r="B574" t="s">
-        <v>847</v>
+        <v>565</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>144</v>
+        <v>846</v>
       </c>
       <c r="B575" t="s">
-        <v>566</v>
+        <v>847</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>1068</v>
+        <v>144</v>
       </c>
       <c r="B576" t="s">
-        <v>1069</v>
+        <v>566</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>176</v>
+        <v>1068</v>
       </c>
       <c r="B577" t="s">
-        <v>567</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>315</v>
+        <v>176</v>
       </c>
       <c r="B578" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>29</v>
+        <v>315</v>
       </c>
       <c r="B579" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>1008</v>
+        <v>29</v>
       </c>
       <c r="B580" t="s">
-        <v>1009</v>
+        <v>569</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>1205</v>
+        <v>1008</v>
       </c>
       <c r="B581" t="s">
-        <v>1206</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>293</v>
+        <v>1205</v>
       </c>
       <c r="B582" t="s">
-        <v>570</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>972</v>
+        <v>293</v>
       </c>
       <c r="B583" t="s">
-        <v>973</v>
+        <v>570</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>1436</v>
+        <v>972</v>
       </c>
       <c r="B584" t="s">
-        <v>1437</v>
+        <v>973</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>301</v>
+        <v>1436</v>
       </c>
       <c r="B585" t="s">
-        <v>571</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>994</v>
+        <v>301</v>
       </c>
       <c r="B586" t="s">
-        <v>995</v>
+        <v>571</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="B587" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>75</v>
+        <v>998</v>
       </c>
       <c r="B588" t="s">
-        <v>572</v>
+        <v>999</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B589" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B590" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>328</v>
+        <v>78</v>
       </c>
       <c r="B591" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>1384</v>
+        <v>328</v>
       </c>
       <c r="B592" t="s">
-        <v>1385</v>
+        <v>575</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>1283</v>
+        <v>1384</v>
       </c>
       <c r="B593" t="s">
-        <v>1284</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>745</v>
+        <v>1283</v>
       </c>
       <c r="B594" t="s">
-        <v>746</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>798</v>
+        <v>745</v>
       </c>
       <c r="B595" t="s">
-        <v>799</v>
+        <v>746</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>1296</v>
+        <v>798</v>
       </c>
       <c r="B596" t="s">
-        <v>1297</v>
+        <v>799</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>135</v>
+        <v>1296</v>
       </c>
       <c r="B597" t="s">
-        <v>576</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>1161</v>
+        <v>135</v>
       </c>
       <c r="B598" t="s">
-        <v>1162</v>
+        <v>576</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>1028</v>
+        <v>1161</v>
       </c>
       <c r="B599" t="s">
-        <v>1029</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>215</v>
+        <v>1028</v>
       </c>
       <c r="B600" t="s">
-        <v>577</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>926</v>
+        <v>215</v>
       </c>
       <c r="B601" t="s">
-        <v>1121</v>
+        <v>577</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>216</v>
+        <v>926</v>
       </c>
       <c r="B602" t="s">
-        <v>1104</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>316</v>
+        <v>216</v>
       </c>
       <c r="B603" t="s">
-        <v>578</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>1070</v>
+        <v>316</v>
       </c>
       <c r="B604" t="s">
-        <v>1071</v>
+        <v>578</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>214</v>
+        <v>1070</v>
       </c>
       <c r="B605" t="s">
-        <v>1105</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>990</v>
+        <v>214</v>
       </c>
       <c r="B606" t="s">
-        <v>991</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B607" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>225</v>
+        <v>992</v>
       </c>
       <c r="B608" t="s">
-        <v>579</v>
+        <v>993</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>1371</v>
+        <v>225</v>
       </c>
       <c r="B609" t="s">
-        <v>1372</v>
+        <v>579</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>939</v>
+        <v>1371</v>
       </c>
       <c r="B610" t="s">
-        <v>940</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>1086</v>
+        <v>939</v>
       </c>
       <c r="B611" t="s">
-        <v>1087</v>
+        <v>940</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>1036</v>
+        <v>1086</v>
       </c>
       <c r="B612" t="s">
-        <v>1037</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>93</v>
+        <v>1036</v>
       </c>
       <c r="B613" t="s">
-        <v>580</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="B614" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>776</v>
+        <v>120</v>
       </c>
       <c r="B615" t="s">
-        <v>777</v>
+        <v>581</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>133</v>
+        <v>776</v>
       </c>
       <c r="B616" t="s">
-        <v>582</v>
+        <v>777</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="B617" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>1285</v>
+        <v>62</v>
       </c>
       <c r="B618" t="s">
-        <v>1286</v>
+        <v>583</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>66</v>
+        <v>1285</v>
       </c>
       <c r="B619" t="s">
-        <v>584</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>818</v>
+        <v>66</v>
       </c>
       <c r="B620" t="s">
-        <v>819</v>
+        <v>584</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>941</v>
+        <v>818</v>
       </c>
       <c r="B621" t="s">
-        <v>942</v>
+        <v>819</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
-        <v>1190</v>
+        <v>941</v>
       </c>
       <c r="B622" t="s">
-        <v>1191</v>
+        <v>942</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
-        <v>1298</v>
+        <v>1190</v>
       </c>
       <c r="B623" t="s">
-        <v>1299</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
-        <v>79</v>
+        <v>1298</v>
       </c>
       <c r="B624" t="s">
-        <v>585</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B625" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="B626" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>1159</v>
+        <v>122</v>
       </c>
       <c r="B627" t="s">
-        <v>1160</v>
+        <v>587</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
-        <v>181</v>
+        <v>1159</v>
       </c>
       <c r="B628" t="s">
-        <v>588</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>794</v>
+        <v>181</v>
       </c>
       <c r="B629" t="s">
-        <v>795</v>
+        <v>588</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>1263</v>
+        <v>794</v>
       </c>
       <c r="B630" t="s">
-        <v>1268</v>
+        <v>795</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>684</v>
+        <v>1263</v>
       </c>
       <c r="B631" t="s">
-        <v>735</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>1264</v>
+        <v>684</v>
       </c>
       <c r="B632" t="s">
-        <v>1269</v>
+        <v>735</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="B633" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="B634" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="B635" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
-        <v>1126</v>
+        <v>1267</v>
       </c>
       <c r="B636" t="s">
-        <v>1127</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="B637" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
-        <v>284</v>
+        <v>1124</v>
       </c>
       <c r="B638" t="s">
-        <v>589</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
-        <v>964</v>
+        <v>284</v>
       </c>
       <c r="B639" t="s">
-        <v>965</v>
+        <v>589</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
-        <v>1194</v>
+        <v>964</v>
       </c>
       <c r="B640" t="s">
-        <v>1195</v>
+        <v>965</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>834</v>
+        <v>1194</v>
       </c>
       <c r="B641" t="s">
-        <v>835</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
-        <v>283</v>
+        <v>834</v>
       </c>
       <c r="B642" t="s">
-        <v>590</v>
+        <v>835</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
-        <v>875</v>
+        <v>283</v>
       </c>
       <c r="B643" t="s">
-        <v>876</v>
+        <v>590</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
-        <v>1155</v>
+        <v>875</v>
       </c>
       <c r="B644" t="s">
-        <v>1156</v>
+        <v>876</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
-        <v>749</v>
+        <v>1155</v>
       </c>
       <c r="B645" t="s">
-        <v>750</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
-        <v>1066</v>
+        <v>749</v>
       </c>
       <c r="B646" t="s">
-        <v>1067</v>
+        <v>750</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
-        <v>67</v>
+        <v>1066</v>
       </c>
       <c r="B647" t="s">
-        <v>591</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B648" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
-        <v>1366</v>
+        <v>68</v>
       </c>
       <c r="B649" t="s">
-        <v>1367</v>
+        <v>592</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
-        <v>95</v>
+        <v>1366</v>
       </c>
       <c r="B650" t="s">
-        <v>593</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
-        <v>289</v>
+        <v>95</v>
       </c>
       <c r="B651" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B652" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="B653" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
-        <v>193</v>
+        <v>264</v>
       </c>
       <c r="B654" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
-        <v>1326</v>
+        <v>193</v>
       </c>
       <c r="B655" t="s">
-        <v>1327</v>
+        <v>597</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
-        <v>892</v>
+        <v>1326</v>
       </c>
       <c r="B656" t="s">
-        <v>893</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
-        <v>44</v>
+        <v>892</v>
       </c>
       <c r="B657" t="s">
-        <v>1103</v>
+        <v>893</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
-        <v>1058</v>
+        <v>44</v>
       </c>
       <c r="B658" t="s">
-        <v>1059</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
-        <v>323</v>
+        <v>1058</v>
       </c>
       <c r="B659" t="s">
-        <v>598</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B660" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
-        <v>842</v>
+        <v>324</v>
       </c>
       <c r="B661" t="s">
-        <v>843</v>
+        <v>599</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
-        <v>879</v>
+        <v>842</v>
       </c>
       <c r="B662" t="s">
-        <v>880</v>
+        <v>843</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
-        <v>1211</v>
+        <v>879</v>
       </c>
       <c r="B663" t="s">
-        <v>1212</v>
+        <v>880</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
-        <v>861</v>
+        <v>1211</v>
       </c>
       <c r="B664" t="s">
-        <v>862</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
-        <v>33</v>
+        <v>1511</v>
       </c>
       <c r="B665" t="s">
-        <v>600</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
-        <v>36</v>
+        <v>861</v>
       </c>
       <c r="B666" t="s">
-        <v>601</v>
+        <v>862</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
-        <v>1119</v>
+        <v>33</v>
       </c>
       <c r="B667" t="s">
-        <v>1120</v>
+        <v>600</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
-        <v>309</v>
+        <v>36</v>
       </c>
       <c r="B668" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
-        <v>257</v>
+        <v>1119</v>
       </c>
       <c r="B669" t="s">
-        <v>603</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B670" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="B671" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
-        <v>17</v>
+        <v>302</v>
       </c>
       <c r="B672" t="s">
-        <v>18</v>
+        <v>604</v>
       </c>
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
-        <v>648</v>
+        <v>228</v>
       </c>
       <c r="B673" t="s">
-        <v>736</v>
+        <v>605</v>
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
-        <v>1393</v>
+        <v>17</v>
       </c>
       <c r="B674" t="s">
-        <v>1394</v>
+        <v>18</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
-        <v>778</v>
+        <v>648</v>
       </c>
       <c r="B675" t="s">
-        <v>779</v>
+        <v>736</v>
       </c>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
-        <v>142</v>
+        <v>1393</v>
       </c>
       <c r="B676" t="s">
-        <v>606</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
-        <v>1153</v>
+        <v>778</v>
       </c>
       <c r="B677" t="s">
-        <v>1154</v>
+        <v>779</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
-        <v>947</v>
+        <v>142</v>
       </c>
       <c r="B678" t="s">
-        <v>948</v>
+        <v>606</v>
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
-        <v>54</v>
+        <v>1153</v>
       </c>
       <c r="B679" t="s">
-        <v>607</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
-        <v>265</v>
+        <v>947</v>
       </c>
       <c r="B680" t="s">
-        <v>608</v>
+        <v>948</v>
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
-        <v>967</v>
+        <v>54</v>
       </c>
       <c r="B681" t="s">
-        <v>966</v>
+        <v>607</v>
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
-        <v>1383</v>
+        <v>265</v>
       </c>
       <c r="B682" t="s">
-        <v>966</v>
+        <v>608</v>
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
-        <v>56</v>
+        <v>967</v>
       </c>
       <c r="B683" t="s">
-        <v>609</v>
+        <v>966</v>
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
-        <v>1192</v>
+        <v>1383</v>
       </c>
       <c r="B684" t="s">
-        <v>1193</v>
+        <v>966</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
-        <v>185</v>
+        <v>56</v>
       </c>
       <c r="B685" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
-        <v>159</v>
+        <v>1192</v>
       </c>
       <c r="B686" t="s">
-        <v>611</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
-        <v>43</v>
+        <v>185</v>
       </c>
       <c r="B687" t="s">
-        <v>1319</v>
+        <v>610</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
-        <v>1317</v>
+        <v>159</v>
       </c>
       <c r="B688" t="s">
-        <v>1318</v>
+        <v>611</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
-        <v>1440</v>
+        <v>43</v>
       </c>
       <c r="B689" t="s">
-        <v>1442</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
-        <v>1441</v>
+        <v>1317</v>
       </c>
       <c r="B690" t="s">
-        <v>1443</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
-        <v>40</v>
+        <v>1440</v>
       </c>
       <c r="B691" t="s">
-        <v>1474</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
-        <v>1315</v>
+        <v>1441</v>
       </c>
       <c r="B692" t="s">
-        <v>1316</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
-        <v>1145</v>
+        <v>40</v>
       </c>
       <c r="B693" t="s">
-        <v>1146</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
-        <v>165</v>
+        <v>1315</v>
       </c>
       <c r="B694" t="s">
-        <v>612</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
-        <v>1273</v>
+        <v>1145</v>
       </c>
       <c r="B695" t="s">
-        <v>1274</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
-        <v>1275</v>
+        <v>165</v>
       </c>
       <c r="B696" t="s">
-        <v>1276</v>
+        <v>612</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
-        <v>1461</v>
+        <v>1273</v>
       </c>
       <c r="B697" t="s">
-        <v>1462</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
-        <v>1463</v>
+        <v>1275</v>
       </c>
       <c r="B698" t="s">
-        <v>1464</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
-        <v>12</v>
+        <v>1461</v>
       </c>
       <c r="B699" t="s">
-        <v>11</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
-        <v>250</v>
+        <v>1463</v>
       </c>
       <c r="B700" t="s">
-        <v>613</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B701" t="s">
-        <v>614</v>
+        <v>11</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
-        <v>1030</v>
+        <v>250</v>
       </c>
       <c r="B702" t="s">
-        <v>1031</v>
+        <v>613</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B703" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
-        <v>1180</v>
+        <v>1030</v>
       </c>
       <c r="B704" t="s">
-        <v>1181</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
-        <v>255</v>
+        <v>28</v>
       </c>
       <c r="B705" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
-        <v>1495</v>
+        <v>1180</v>
       </c>
       <c r="B706" t="s">
-        <v>1496</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
-        <v>1308</v>
+        <v>255</v>
       </c>
       <c r="B707" t="s">
-        <v>1509</v>
+        <v>616</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
-        <v>1508</v>
+        <v>1495</v>
       </c>
       <c r="B708" t="s">
-        <v>1510</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
-        <v>788</v>
+        <v>1308</v>
       </c>
       <c r="B709" t="s">
-        <v>789</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
-        <v>267</v>
+        <v>1508</v>
       </c>
       <c r="B710" t="s">
-        <v>617</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
-        <v>654</v>
+        <v>788</v>
       </c>
       <c r="B711" t="s">
-        <v>737</v>
+        <v>789</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
-        <v>655</v>
+        <v>267</v>
       </c>
       <c r="B712" t="s">
-        <v>738</v>
+        <v>617</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
-        <v>139</v>
+        <v>654</v>
       </c>
       <c r="B713" t="s">
-        <v>618</v>
+        <v>737</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
-        <v>7</v>
+        <v>655</v>
       </c>
       <c r="B714" t="s">
-        <v>2</v>
+        <v>738</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A715" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="B715" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A716" t="s">
-        <v>1322</v>
+        <v>7</v>
       </c>
       <c r="B716" t="s">
-        <v>1323</v>
+        <v>2</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
-        <v>1024</v>
+        <v>105</v>
       </c>
       <c r="B717" t="s">
-        <v>1102</v>
+        <v>619</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
-        <v>857</v>
+        <v>1322</v>
       </c>
       <c r="B718" t="s">
-        <v>858</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
-        <v>1422</v>
+        <v>1024</v>
       </c>
       <c r="B719" t="s">
-        <v>1423</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
-        <v>1025</v>
+        <v>857</v>
       </c>
       <c r="B720" t="s">
-        <v>1101</v>
+        <v>858</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
-        <v>292</v>
+        <v>1422</v>
       </c>
       <c r="B721" t="s">
-        <v>620</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
-        <v>8</v>
+        <v>1025</v>
       </c>
       <c r="B722" t="s">
-        <v>11</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
-        <v>334</v>
+        <v>292</v>
       </c>
       <c r="B723" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
-        <v>1364</v>
+        <v>8</v>
       </c>
       <c r="B724" t="s">
-        <v>1365</v>
+        <v>11</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
-        <v>1324</v>
+        <v>334</v>
       </c>
       <c r="B725" t="s">
-        <v>1325</v>
+        <v>621</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
-        <v>331</v>
+        <v>1364</v>
       </c>
       <c r="B726" t="s">
-        <v>622</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
-        <v>259</v>
+        <v>1324</v>
       </c>
       <c r="B727" t="s">
-        <v>623</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="B728" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
-        <v>851</v>
+        <v>259</v>
       </c>
       <c r="B729" t="s">
-        <v>852</v>
+        <v>623</v>
       </c>
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A730" t="s">
-        <v>1149</v>
+        <v>318</v>
       </c>
       <c r="B730" t="s">
-        <v>1150</v>
+        <v>624</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
-        <v>268</v>
+        <v>851</v>
       </c>
       <c r="B731" t="s">
-        <v>625</v>
+        <v>852</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
-        <v>271</v>
+        <v>1149</v>
       </c>
       <c r="B732" t="s">
-        <v>1099</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B733" t="s">
-        <v>1100</v>
+        <v>625</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B734" t="s">
-        <v>1497</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B735" t="s">
-        <v>1498</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B736" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A737" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B737" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
-        <v>92</v>
+        <v>269</v>
       </c>
       <c r="B738" t="s">
-        <v>626</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
-        <v>200</v>
+        <v>272</v>
       </c>
       <c r="B739" t="s">
-        <v>627</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A740" t="s">
-        <v>203</v>
+        <v>92</v>
       </c>
       <c r="B740" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
-        <v>1202</v>
+        <v>200</v>
       </c>
       <c r="B741" t="s">
-        <v>1501</v>
+        <v>627</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="B742" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
-        <v>1453</v>
+        <v>1202</v>
       </c>
       <c r="B743" t="s">
-        <v>1454</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A744" t="s">
-        <v>686</v>
+        <v>172</v>
       </c>
       <c r="B744" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="745" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A745" t="s">
-        <v>1448</v>
-      </c>
-      <c r="B745" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
+      </c>
+      <c r="B745" t="s">
+        <v>1454</v>
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A746" t="s">
-        <v>252</v>
+        <v>686</v>
       </c>
       <c r="B746" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="747" spans="1:2" x14ac:dyDescent="0.35">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A747" t="s">
-        <v>687</v>
-      </c>
-      <c r="B747" t="s">
-        <v>740</v>
+        <v>1448</v>
+      </c>
+      <c r="B747" s="1" t="s">
+        <v>1449</v>
       </c>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A748" t="s">
-        <v>189</v>
+        <v>252</v>
       </c>
       <c r="B748" t="s">
-        <v>1392</v>
+        <v>630</v>
       </c>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A749" t="s">
-        <v>980</v>
+        <v>687</v>
       </c>
       <c r="B749" t="s">
-        <v>981</v>
+        <v>740</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A750" t="s">
-        <v>311</v>
+        <v>189</v>
       </c>
       <c r="B750" t="s">
-        <v>631</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A751" t="s">
-        <v>312</v>
+        <v>980</v>
       </c>
       <c r="B751" t="s">
-        <v>632</v>
+        <v>981</v>
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A752" t="s">
-        <v>1023</v>
+        <v>311</v>
       </c>
       <c r="B752" t="s">
-        <v>1447</v>
+        <v>631</v>
       </c>
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A753" t="s">
-        <v>1446</v>
+        <v>312</v>
       </c>
       <c r="B753" t="s">
-        <v>1467</v>
+        <v>632</v>
       </c>
     </row>
     <row r="754" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A754" t="s">
-        <v>996</v>
+        <v>1023</v>
       </c>
       <c r="B754" t="s">
-        <v>997</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A755" t="s">
-        <v>81</v>
+        <v>1446</v>
       </c>
       <c r="B755" t="s">
-        <v>633</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="756" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A756" t="s">
-        <v>644</v>
+        <v>996</v>
       </c>
       <c r="B756" t="s">
-        <v>741</v>
+        <v>997</v>
       </c>
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A757" t="s">
-        <v>913</v>
+        <v>81</v>
       </c>
       <c r="B757" t="s">
-        <v>914</v>
+        <v>633</v>
       </c>
     </row>
     <row r="758" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A758" t="s">
-        <v>635</v>
+        <v>644</v>
       </c>
       <c r="B758" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="759" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A759" t="s">
-        <v>960</v>
+        <v>913</v>
       </c>
       <c r="B759" t="s">
-        <v>961</v>
+        <v>914</v>
       </c>
     </row>
     <row r="760" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A760" t="s">
-        <v>1137</v>
+        <v>635</v>
       </c>
       <c r="B760" t="s">
-        <v>1138</v>
+        <v>742</v>
       </c>
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A761" t="s">
+        <v>960</v>
+      </c>
+      <c r="B761" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A762" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B762" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A763" t="s">
         <v>1362</v>
       </c>
-      <c r="B761" t="s">
+      <c r="B763" t="s">
         <v>1363</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB952ADD-D814-4A47-B0D1-D8CE51BAEE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE1B8283-D6C8-4DA9-91D8-AA3F5B71827A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="1513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="1515">
   <si>
     <t>trigger</t>
   </si>
@@ -4567,6 +4567,12 @@
   </si>
   <si>
     <t>ehng</t>
+  </si>
+  <si>
+    <t>aml</t>
+  </si>
+  <si>
+    <t>angiomyolipoma</t>
   </si>
 </sst>
 </file>
@@ -4635,10 +4641,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B763" totalsRowShown="0">
-  <autoFilter ref="A1:B763" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B763">
-    <sortCondition ref="A1:A763"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B764" totalsRowShown="0">
+  <autoFilter ref="A1:B764" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B764">
+    <sortCondition ref="A1:A764"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4911,7 +4917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B763"/>
+  <dimension ref="A1:B764"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -5168,1703 +5174,1703 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>1157</v>
+        <v>1513</v>
       </c>
       <c r="B32" t="s">
-        <v>1158</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>1157</v>
       </c>
       <c r="B33" t="s">
-        <v>352</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B34" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="B35" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>1012</v>
+        <v>150</v>
       </c>
       <c r="B36" t="s">
-        <v>1013</v>
+        <v>354</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>69</v>
+        <v>1012</v>
       </c>
       <c r="B37" t="s">
-        <v>355</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>282</v>
+        <v>69</v>
       </c>
       <c r="B38" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>141</v>
+        <v>282</v>
       </c>
       <c r="B39" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>902</v>
+        <v>141</v>
       </c>
       <c r="B40" t="s">
-        <v>903</v>
+        <v>357</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>148</v>
+        <v>902</v>
       </c>
       <c r="B41" t="s">
-        <v>358</v>
+        <v>903</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>1188</v>
+        <v>148</v>
       </c>
       <c r="B42" t="s">
-        <v>1189</v>
+        <v>358</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="B43" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>653</v>
+        <v>1185</v>
       </c>
       <c r="B44" t="s">
-        <v>689</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>1451</v>
+        <v>653</v>
       </c>
       <c r="B45" t="s">
-        <v>1332</v>
+        <v>689</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>1006</v>
+        <v>1451</v>
       </c>
       <c r="B46" t="s">
-        <v>1007</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>166</v>
+        <v>1006</v>
       </c>
       <c r="B47" t="s">
-        <v>359</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>291</v>
+        <v>166</v>
       </c>
       <c r="B48" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="B49" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>239</v>
+        <v>310</v>
       </c>
       <c r="B50" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>195</v>
+        <v>239</v>
       </c>
       <c r="B51" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>246</v>
+        <v>195</v>
       </c>
       <c r="B52" t="s">
-        <v>1116</v>
+        <v>363</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>640</v>
+        <v>246</v>
       </c>
       <c r="B53" t="s">
-        <v>690</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>240</v>
+        <v>640</v>
       </c>
       <c r="B54" t="s">
-        <v>362</v>
+        <v>690</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>1502</v>
+        <v>240</v>
       </c>
       <c r="B55" t="s">
-        <v>1503</v>
+        <v>362</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>853</v>
+        <v>1502</v>
       </c>
       <c r="B56" t="s">
-        <v>854</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>978</v>
+        <v>853</v>
       </c>
       <c r="B57" t="s">
-        <v>979</v>
+        <v>854</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>767</v>
+        <v>978</v>
       </c>
       <c r="B58" t="s">
-        <v>768</v>
+        <v>979</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B59" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>300</v>
+        <v>769</v>
       </c>
       <c r="B60" t="s">
-        <v>364</v>
+        <v>770</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>1122</v>
+        <v>300</v>
       </c>
       <c r="B61" t="s">
-        <v>1123</v>
+        <v>364</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>303</v>
+        <v>1122</v>
       </c>
       <c r="B62" t="s">
-        <v>365</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>230</v>
+        <v>303</v>
       </c>
       <c r="B63" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B64" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>782</v>
+        <v>232</v>
       </c>
       <c r="B65" t="s">
-        <v>783</v>
+        <v>367</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>317</v>
+        <v>782</v>
       </c>
       <c r="B66" t="s">
-        <v>368</v>
+        <v>783</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>755</v>
+        <v>317</v>
       </c>
       <c r="B67" t="s">
-        <v>756</v>
+        <v>368</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>61</v>
+        <v>755</v>
       </c>
       <c r="B68" t="s">
-        <v>369</v>
+        <v>756</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B69" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B70" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>1479</v>
+        <v>58</v>
       </c>
       <c r="B71" t="s">
-        <v>1480</v>
+        <v>371</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="B72" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>877</v>
+        <v>1477</v>
       </c>
       <c r="B73" t="s">
-        <v>878</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>1304</v>
+        <v>877</v>
       </c>
       <c r="B74" t="s">
-        <v>1305</v>
+        <v>878</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>652</v>
+        <v>1304</v>
       </c>
       <c r="B75" t="s">
-        <v>691</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>1379</v>
+        <v>652</v>
       </c>
       <c r="B76" t="s">
-        <v>1380</v>
+        <v>691</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>237</v>
+        <v>1379</v>
       </c>
       <c r="B77" t="s">
-        <v>372</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>1203</v>
+        <v>237</v>
       </c>
       <c r="B78" t="s">
-        <v>1204</v>
+        <v>372</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>60</v>
+        <v>1203</v>
       </c>
       <c r="B79" t="s">
-        <v>373</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>1004</v>
+        <v>60</v>
       </c>
       <c r="B80" t="s">
-        <v>1005</v>
+        <v>373</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>1213</v>
+        <v>1004</v>
       </c>
       <c r="B81" t="s">
-        <v>1214</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>661</v>
+        <v>1213</v>
       </c>
       <c r="B82" t="s">
-        <v>692</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>1215</v>
+        <v>661</v>
       </c>
       <c r="B83" t="s">
-        <v>1216</v>
+        <v>692</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>662</v>
+        <v>1215</v>
       </c>
       <c r="B84" t="s">
-        <v>693</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>1217</v>
+        <v>662</v>
       </c>
       <c r="B85" t="s">
-        <v>1218</v>
+        <v>693</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>663</v>
+        <v>1217</v>
       </c>
       <c r="B86" t="s">
-        <v>694</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>1219</v>
+        <v>663</v>
       </c>
       <c r="B87" t="s">
-        <v>1220</v>
+        <v>694</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>664</v>
+        <v>1219</v>
       </c>
       <c r="B88" t="s">
-        <v>695</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>1221</v>
+        <v>664</v>
       </c>
       <c r="B89" t="s">
-        <v>1222</v>
+        <v>695</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>665</v>
+        <v>1221</v>
       </c>
       <c r="B90" t="s">
-        <v>696</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>1223</v>
+        <v>665</v>
       </c>
       <c r="B91" t="s">
-        <v>1226</v>
+        <v>696</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>666</v>
+        <v>1223</v>
       </c>
       <c r="B92" t="s">
-        <v>697</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>1224</v>
+        <v>666</v>
       </c>
       <c r="B93" t="s">
-        <v>1227</v>
+        <v>697</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>667</v>
+        <v>1224</v>
       </c>
       <c r="B94" t="s">
-        <v>698</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>1225</v>
+        <v>667</v>
       </c>
       <c r="B95" t="s">
-        <v>1228</v>
+        <v>698</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>867</v>
+        <v>1225</v>
       </c>
       <c r="B96" t="s">
-        <v>868</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>320</v>
+        <v>867</v>
       </c>
       <c r="B97" t="s">
-        <v>374</v>
+        <v>868</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>194</v>
+        <v>320</v>
       </c>
       <c r="B98" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="B99" t="s">
-        <v>22</v>
+        <v>375</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B100" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="B101" t="s">
-        <v>376</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>287</v>
+        <v>196</v>
       </c>
       <c r="B102" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B103" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>336</v>
+        <v>286</v>
       </c>
       <c r="B104" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>890</v>
+        <v>336</v>
       </c>
       <c r="B105" t="s">
-        <v>891</v>
+        <v>379</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>305</v>
+        <v>890</v>
       </c>
       <c r="B106" t="s">
-        <v>380</v>
+        <v>891</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="B107" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>1134</v>
+        <v>322</v>
       </c>
       <c r="B108" t="s">
-        <v>1135</v>
+        <v>381</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>276</v>
+        <v>1134</v>
       </c>
       <c r="B109" t="s">
-        <v>382</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>332</v>
+        <v>276</v>
       </c>
       <c r="B110" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>42</v>
+        <v>332</v>
       </c>
       <c r="B111" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B112" t="s">
-        <v>1115</v>
+        <v>384</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>642</v>
+        <v>41</v>
       </c>
       <c r="B113" t="s">
-        <v>699</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>1444</v>
+        <v>642</v>
       </c>
       <c r="B114" t="s">
-        <v>1445</v>
+        <v>699</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>217</v>
+        <v>1444</v>
       </c>
       <c r="B115" t="s">
-        <v>385</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>288</v>
+        <v>217</v>
       </c>
       <c r="B116" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>218</v>
+        <v>288</v>
       </c>
       <c r="B117" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>296</v>
+        <v>218</v>
       </c>
       <c r="B118" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>199</v>
+        <v>296</v>
       </c>
       <c r="B119" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>1415</v>
+        <v>199</v>
       </c>
       <c r="B120" t="s">
-        <v>1416</v>
+        <v>389</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>641</v>
+        <v>1415</v>
       </c>
       <c r="B121" t="s">
-        <v>700</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>112</v>
+        <v>641</v>
       </c>
       <c r="B122" t="s">
-        <v>390</v>
+        <v>700</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="B123" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="B124" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>1151</v>
+        <v>115</v>
       </c>
       <c r="B125" t="s">
-        <v>1152</v>
+        <v>392</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>871</v>
+        <v>1151</v>
       </c>
       <c r="B126" t="s">
-        <v>872</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>800</v>
+        <v>871</v>
       </c>
       <c r="B127" t="s">
-        <v>801</v>
+        <v>872</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>1468</v>
+        <v>800</v>
       </c>
       <c r="B128" t="s">
-        <v>1469</v>
+        <v>801</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>152</v>
+        <v>1468</v>
       </c>
       <c r="B129" t="s">
-        <v>393</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>1295</v>
+        <v>152</v>
       </c>
       <c r="B130" t="s">
-        <v>1300</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>124</v>
+        <v>1295</v>
       </c>
       <c r="B131" t="s">
-        <v>395</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="B133" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>958</v>
+        <v>155</v>
       </c>
       <c r="B134" t="s">
-        <v>959</v>
+        <v>396</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>84</v>
+        <v>958</v>
       </c>
       <c r="B135" t="s">
-        <v>397</v>
+        <v>959</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>956</v>
+        <v>84</v>
       </c>
       <c r="B136" t="s">
-        <v>957</v>
+        <v>397</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>1381</v>
+        <v>956</v>
       </c>
       <c r="B137" t="s">
-        <v>1382</v>
+        <v>957</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>103</v>
+        <v>1381</v>
       </c>
       <c r="B138" t="s">
-        <v>398</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>198</v>
+        <v>103</v>
       </c>
       <c r="B139" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>314</v>
+        <v>198</v>
       </c>
       <c r="B140" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>104</v>
+        <v>314</v>
       </c>
       <c r="B141" t="s">
-        <v>1460</v>
+        <v>400</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>1488</v>
+        <v>104</v>
       </c>
       <c r="B142" t="s">
-        <v>1489</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>163</v>
+        <v>1488</v>
       </c>
       <c r="B143" t="s">
-        <v>401</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="B144" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B145" t="s">
-        <v>1314</v>
+        <v>402</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>1313</v>
+        <v>102</v>
       </c>
       <c r="B146" t="s">
-        <v>403</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>921</v>
+        <v>1313</v>
       </c>
       <c r="B147" t="s">
-        <v>922</v>
+        <v>403</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B148" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>162</v>
+        <v>919</v>
       </c>
       <c r="B149" t="s">
-        <v>404</v>
+        <v>920</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>1128</v>
+        <v>162</v>
       </c>
       <c r="B150" t="s">
-        <v>1129</v>
+        <v>404</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>1357</v>
+        <v>1128</v>
       </c>
       <c r="B151" t="s">
-        <v>1358</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>830</v>
+        <v>1357</v>
       </c>
       <c r="B152" t="s">
-        <v>831</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B153" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>1301</v>
+        <v>832</v>
       </c>
       <c r="B154" t="s">
-        <v>1459</v>
+        <v>833</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>1072</v>
+        <v>1301</v>
       </c>
       <c r="B155" t="s">
-        <v>1073</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>658</v>
+        <v>1072</v>
       </c>
       <c r="B156" t="s">
-        <v>701</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>639</v>
+        <v>658</v>
       </c>
       <c r="B157" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>931</v>
+        <v>639</v>
       </c>
       <c r="B158" t="s">
-        <v>932</v>
+        <v>702</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>1432</v>
+        <v>931</v>
       </c>
       <c r="B159" t="s">
-        <v>1433</v>
+        <v>932</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>1351</v>
+        <v>1432</v>
       </c>
       <c r="B160" t="s">
-        <v>1352</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>1229</v>
+        <v>1351</v>
       </c>
       <c r="B161" t="s">
-        <v>1241</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>1238</v>
+        <v>1229</v>
       </c>
       <c r="B162" t="s">
-        <v>1250</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>676</v>
+        <v>1238</v>
       </c>
       <c r="B163" t="s">
-        <v>703</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>1239</v>
+        <v>676</v>
       </c>
       <c r="B164" t="s">
-        <v>1251</v>
+        <v>703</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>677</v>
+        <v>1239</v>
       </c>
       <c r="B165" t="s">
-        <v>704</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>1240</v>
+        <v>677</v>
       </c>
       <c r="B166" t="s">
-        <v>1252</v>
+        <v>704</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>678</v>
+        <v>1240</v>
       </c>
       <c r="B167" t="s">
-        <v>705</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>1230</v>
+        <v>678</v>
       </c>
       <c r="B168" t="s">
-        <v>1242</v>
+        <v>705</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>668</v>
+        <v>1230</v>
       </c>
       <c r="B169" t="s">
-        <v>706</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>1231</v>
+        <v>668</v>
       </c>
       <c r="B170" t="s">
-        <v>1243</v>
+        <v>706</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>669</v>
+        <v>1231</v>
       </c>
       <c r="B171" t="s">
-        <v>707</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>1232</v>
+        <v>669</v>
       </c>
       <c r="B172" t="s">
-        <v>1244</v>
+        <v>707</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>670</v>
+        <v>1232</v>
       </c>
       <c r="B173" t="s">
-        <v>708</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>1233</v>
+        <v>670</v>
       </c>
       <c r="B174" t="s">
-        <v>1245</v>
+        <v>708</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>671</v>
+        <v>1233</v>
       </c>
       <c r="B175" t="s">
-        <v>709</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>1234</v>
+        <v>671</v>
       </c>
       <c r="B176" t="s">
-        <v>1246</v>
+        <v>709</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>672</v>
+        <v>1234</v>
       </c>
       <c r="B177" t="s">
-        <v>710</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>1235</v>
+        <v>672</v>
       </c>
       <c r="B178" t="s">
-        <v>1247</v>
+        <v>710</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>673</v>
+        <v>1235</v>
       </c>
       <c r="B179" t="s">
-        <v>711</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>1236</v>
+        <v>673</v>
       </c>
       <c r="B180" t="s">
-        <v>1248</v>
+        <v>711</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>674</v>
+        <v>1236</v>
       </c>
       <c r="B181" t="s">
-        <v>712</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>1237</v>
+        <v>674</v>
       </c>
       <c r="B182" t="s">
-        <v>1249</v>
+        <v>712</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>675</v>
+        <v>1237</v>
       </c>
       <c r="B183" t="s">
-        <v>713</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>175</v>
+        <v>675</v>
       </c>
       <c r="B184" t="s">
-        <v>405</v>
+        <v>713</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="B185" t="s">
-        <v>1434</v>
+        <v>405</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B186" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>1311</v>
+        <v>213</v>
       </c>
       <c r="B187" t="s">
-        <v>1312</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>1345</v>
+        <v>1311</v>
       </c>
       <c r="B188" t="s">
-        <v>1346</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>1184</v>
+        <v>1345</v>
       </c>
       <c r="B189" t="s">
-        <v>406</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>149</v>
+        <v>1184</v>
       </c>
       <c r="B190" t="s">
-        <v>1187</v>
+        <v>406</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>247</v>
+        <v>149</v>
       </c>
       <c r="B191" t="s">
-        <v>407</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B192" t="s">
-        <v>1389</v>
+        <v>407</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>335</v>
+        <v>245</v>
       </c>
       <c r="B193" t="s">
-        <v>408</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>643</v>
+        <v>335</v>
       </c>
       <c r="B194" t="s">
-        <v>714</v>
+        <v>408</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>91</v>
+        <v>643</v>
       </c>
       <c r="B195" t="s">
-        <v>409</v>
+        <v>714</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>266</v>
+        <v>91</v>
       </c>
       <c r="B196" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>1465</v>
+        <v>266</v>
       </c>
       <c r="B197" t="s">
-        <v>1466</v>
+        <v>410</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>1084</v>
+        <v>1465</v>
       </c>
       <c r="B198" t="s">
-        <v>1085</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>792</v>
+        <v>1084</v>
       </c>
       <c r="B199" t="s">
-        <v>793</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>1143</v>
+        <v>792</v>
       </c>
       <c r="B200" t="s">
-        <v>1144</v>
+        <v>793</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>1328</v>
+        <v>1143</v>
       </c>
       <c r="B201" t="s">
-        <v>1329</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>295</v>
+        <v>1328</v>
       </c>
       <c r="B202" t="s">
-        <v>411</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>1074</v>
+        <v>295</v>
       </c>
       <c r="B203" t="s">
-        <v>1075</v>
+        <v>411</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="B204" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>151</v>
+        <v>1080</v>
       </c>
       <c r="B205" t="s">
-        <v>412</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>952</v>
+        <v>151</v>
       </c>
       <c r="B206" t="s">
-        <v>953</v>
+        <v>412</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>806</v>
+        <v>952</v>
       </c>
       <c r="B207" t="s">
-        <v>807</v>
+        <v>953</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>923</v>
+        <v>806</v>
       </c>
       <c r="B208" t="s">
-        <v>924</v>
+        <v>807</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>826</v>
+        <v>923</v>
       </c>
       <c r="B209" t="s">
-        <v>827</v>
+        <v>924</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>786</v>
+        <v>826</v>
       </c>
       <c r="B210" t="s">
-        <v>787</v>
+        <v>827</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>1413</v>
+        <v>786</v>
       </c>
       <c r="B211" t="s">
-        <v>1414</v>
+        <v>787</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>747</v>
+        <v>1413</v>
       </c>
       <c r="B212" t="s">
-        <v>748</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>100</v>
+        <v>747</v>
       </c>
       <c r="B213" t="s">
-        <v>413</v>
+        <v>748</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>1512</v>
+        <v>100</v>
       </c>
       <c r="B214" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>1032</v>
+        <v>1512</v>
       </c>
       <c r="B215" t="s">
-        <v>1033</v>
+        <v>416</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>154</v>
+        <v>1032</v>
       </c>
       <c r="B216" t="s">
-        <v>414</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B217" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="B218" t="s">
-        <v>1114</v>
+        <v>415</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>1139</v>
+        <v>24</v>
       </c>
       <c r="B219" t="s">
-        <v>1140</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>1302</v>
+        <v>1139</v>
       </c>
       <c r="B220" t="s">
-        <v>1303</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>1064</v>
+        <v>1302</v>
       </c>
       <c r="B221" t="s">
-        <v>1065</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>1457</v>
+        <v>1064</v>
       </c>
       <c r="B222" t="s">
-        <v>1458</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>812</v>
+        <v>1457</v>
       </c>
       <c r="B223" t="s">
-        <v>813</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>130</v>
+        <v>812</v>
       </c>
       <c r="B224" t="s">
-        <v>416</v>
+        <v>813</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>321</v>
+        <v>130</v>
       </c>
       <c r="B225" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>1456</v>
+        <v>321</v>
       </c>
       <c r="B226" t="s">
-        <v>1417</v>
+        <v>417</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>859</v>
+        <v>1456</v>
       </c>
       <c r="B227" t="s">
-        <v>860</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>1420</v>
+        <v>859</v>
       </c>
       <c r="B228" t="s">
-        <v>1421</v>
+        <v>860</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>1455</v>
+        <v>1420</v>
       </c>
       <c r="B229" t="s">
-        <v>883</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>1291</v>
+        <v>1455</v>
       </c>
       <c r="B230" t="s">
-        <v>1292</v>
+        <v>883</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>183</v>
+        <v>1291</v>
       </c>
       <c r="B231" t="s">
-        <v>418</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>1130</v>
+        <v>183</v>
       </c>
       <c r="B232" t="s">
-        <v>1131</v>
+        <v>418</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B233" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>1411</v>
+        <v>1132</v>
       </c>
       <c r="B234" t="s">
-        <v>1412</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>1484</v>
+        <v>1411</v>
       </c>
       <c r="B235" t="s">
-        <v>1485</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>1369</v>
+        <v>1484</v>
       </c>
       <c r="B236" t="s">
-        <v>1370</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>1486</v>
+        <v>1369</v>
       </c>
       <c r="B237" t="s">
-        <v>1487</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>32</v>
+        <v>1486</v>
       </c>
       <c r="B238" t="s">
-        <v>419</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B239" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>1281</v>
+        <v>35</v>
       </c>
       <c r="B240" t="s">
-        <v>1282</v>
+        <v>420</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>1207</v>
+        <v>1281</v>
       </c>
       <c r="B241" t="s">
-        <v>1208</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>757</v>
+        <v>1207</v>
       </c>
       <c r="B242" t="s">
-        <v>1000</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>169</v>
+        <v>757</v>
       </c>
       <c r="B243" t="s">
-        <v>421</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B244" t="s">
         <v>421</v>
@@ -6872,615 +6878,615 @@
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>1001</v>
+        <v>170</v>
       </c>
       <c r="B245" t="s">
-        <v>758</v>
+        <v>421</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>1409</v>
+        <v>1001</v>
       </c>
       <c r="B246" t="s">
-        <v>1410</v>
+        <v>758</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>178</v>
+        <v>1409</v>
       </c>
       <c r="B247" t="s">
-        <v>422</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="B248" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>238</v>
+        <v>111</v>
       </c>
       <c r="B249" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="B250" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B251" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="B252" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>660</v>
+        <v>179</v>
       </c>
       <c r="B253" t="s">
-        <v>715</v>
+        <v>427</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>1475</v>
+        <v>660</v>
       </c>
       <c r="B254" t="s">
-        <v>1476</v>
+        <v>715</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>97</v>
+        <v>1475</v>
       </c>
       <c r="B255" t="s">
-        <v>428</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B256" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>242</v>
+        <v>110</v>
       </c>
       <c r="B257" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B258" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="B259" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>1407</v>
+        <v>177</v>
       </c>
       <c r="B260" t="s">
-        <v>1408</v>
+        <v>432</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>182</v>
+        <v>1407</v>
       </c>
       <c r="B261" t="s">
-        <v>433</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>1094</v>
+        <v>182</v>
       </c>
       <c r="B262" t="s">
-        <v>1095</v>
+        <v>433</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>968</v>
+        <v>1094</v>
       </c>
       <c r="B263" t="s">
-        <v>969</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B264" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>1173</v>
+        <v>970</v>
       </c>
       <c r="B265" t="s">
-        <v>1174</v>
+        <v>971</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>1349</v>
+        <v>1173</v>
       </c>
       <c r="B266" t="s">
-        <v>1350</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>1176</v>
+        <v>1349</v>
       </c>
       <c r="B267" t="s">
-        <v>1177</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>253</v>
+        <v>1176</v>
       </c>
       <c r="B268" t="s">
-        <v>434</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="B269" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>780</v>
+        <v>34</v>
       </c>
       <c r="B270" t="s">
-        <v>781</v>
+        <v>435</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>180</v>
+        <v>780</v>
       </c>
       <c r="B271" t="s">
-        <v>436</v>
+        <v>781</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>1321</v>
+        <v>180</v>
       </c>
       <c r="B272" t="s">
-        <v>1390</v>
+        <v>436</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B273" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>1438</v>
+        <v>1320</v>
       </c>
       <c r="B274" t="s">
-        <v>1439</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>275</v>
+        <v>1438</v>
       </c>
       <c r="B275" t="s">
-        <v>1491</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>850</v>
+        <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>1493</v>
+        <v>850</v>
       </c>
       <c r="B277" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>1506</v>
+        <v>1493</v>
       </c>
       <c r="B278" t="s">
-        <v>1507</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>116</v>
+        <v>1506</v>
       </c>
       <c r="B279" t="s">
-        <v>437</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="B280" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>1395</v>
+        <v>208</v>
       </c>
       <c r="B281" t="s">
-        <v>1396</v>
+        <v>438</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>1196</v>
+        <v>1395</v>
       </c>
       <c r="B282" t="s">
-        <v>1197</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>1044</v>
+        <v>1196</v>
       </c>
       <c r="B283" t="s">
-        <v>1045</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>118</v>
+        <v>1044</v>
       </c>
       <c r="B284" t="s">
-        <v>439</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>634</v>
+        <v>118</v>
       </c>
       <c r="B285" t="s">
-        <v>716</v>
+        <v>439</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>1306</v>
+        <v>634</v>
       </c>
       <c r="B286" t="s">
-        <v>1307</v>
+        <v>716</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>808</v>
+        <v>1306</v>
       </c>
       <c r="B287" t="s">
-        <v>809</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>298</v>
+        <v>808</v>
       </c>
       <c r="B288" t="s">
-        <v>440</v>
+        <v>809</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>636</v>
+        <v>298</v>
       </c>
       <c r="B289" t="s">
-        <v>717</v>
+        <v>440</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B290" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>1026</v>
+        <v>637</v>
       </c>
       <c r="B291" t="s">
-        <v>1027</v>
+        <v>718</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>90</v>
+        <v>1026</v>
       </c>
       <c r="B292" t="s">
-        <v>441</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B293" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B294" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>1060</v>
+        <v>89</v>
       </c>
       <c r="B295" t="s">
-        <v>1061</v>
+        <v>443</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>23</v>
+        <v>1060</v>
       </c>
       <c r="B296" t="s">
-        <v>1113</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>1399</v>
+        <v>23</v>
       </c>
       <c r="B297" t="s">
-        <v>1400</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>5</v>
+        <v>1399</v>
       </c>
       <c r="B298" t="s">
-        <v>6</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>1117</v>
+        <v>5</v>
       </c>
       <c r="B299" t="s">
-        <v>1118</v>
+        <v>6</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>126</v>
+        <v>1117</v>
       </c>
       <c r="B300" t="s">
-        <v>444</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>1373</v>
+        <v>126</v>
       </c>
       <c r="B301" t="s">
-        <v>1374</v>
+        <v>444</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>128</v>
+        <v>1373</v>
       </c>
       <c r="B302" t="s">
-        <v>445</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B303" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B304" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B305" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>277</v>
+        <v>119</v>
       </c>
       <c r="B306" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>1062</v>
+        <v>277</v>
       </c>
       <c r="B307" t="s">
-        <v>1063</v>
+        <v>449</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>9</v>
+        <v>1062</v>
       </c>
       <c r="B308" t="s">
-        <v>10</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="B309" t="s">
-        <v>450</v>
+        <v>10</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B310" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="B311" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="B312" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>1360</v>
+        <v>262</v>
       </c>
       <c r="B313" t="s">
-        <v>1361</v>
+        <v>453</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>77</v>
+        <v>1360</v>
       </c>
       <c r="B314" t="s">
-        <v>454</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>929</v>
+        <v>77</v>
       </c>
       <c r="B315" t="s">
-        <v>930</v>
+        <v>454</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>1147</v>
+        <v>929</v>
       </c>
       <c r="B316" t="s">
-        <v>1148</v>
+        <v>930</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>168</v>
+        <v>1147</v>
       </c>
       <c r="B317" t="s">
-        <v>455</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>1333</v>
+        <v>168</v>
       </c>
       <c r="B318" t="s">
-        <v>1334</v>
+        <v>455</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>1343</v>
+        <v>1333</v>
       </c>
       <c r="B319" t="s">
-        <v>1344</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>1386</v>
+        <v>1343</v>
       </c>
       <c r="B320" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>1339</v>
+        <v>1386</v>
       </c>
       <c r="B321" t="s">
         <v>1340</v>
@@ -7488,39 +7494,39 @@
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>167</v>
+        <v>1339</v>
       </c>
       <c r="B322" t="s">
-        <v>456</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>1335</v>
+        <v>167</v>
       </c>
       <c r="B323" t="s">
-        <v>1336</v>
+        <v>456</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>1341</v>
+        <v>1335</v>
       </c>
       <c r="B324" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>1368</v>
+        <v>1341</v>
       </c>
       <c r="B325" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>1337</v>
+        <v>1368</v>
       </c>
       <c r="B326" t="s">
         <v>1338</v>
@@ -7528,199 +7534,199 @@
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>828</v>
+        <v>1337</v>
       </c>
       <c r="B327" t="s">
-        <v>829</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>784</v>
+        <v>828</v>
       </c>
       <c r="B328" t="s">
-        <v>785</v>
+        <v>829</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>304</v>
+        <v>784</v>
       </c>
       <c r="B329" t="s">
-        <v>457</v>
+        <v>785</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>751</v>
+        <v>304</v>
       </c>
       <c r="B330" t="s">
-        <v>752</v>
+        <v>457</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>888</v>
+        <v>751</v>
       </c>
       <c r="B331" t="s">
-        <v>889</v>
+        <v>752</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>1375</v>
+        <v>888</v>
       </c>
       <c r="B332" t="s">
-        <v>1376</v>
+        <v>889</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>645</v>
+        <v>1375</v>
       </c>
       <c r="B333" t="s">
-        <v>719</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>86</v>
+        <v>645</v>
       </c>
       <c r="B334" t="s">
-        <v>458</v>
+        <v>719</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B335" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="B336" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B337" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B338" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>251</v>
+        <v>158</v>
       </c>
       <c r="B339" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="B340" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>325</v>
+        <v>285</v>
       </c>
       <c r="B341" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>1355</v>
+        <v>325</v>
       </c>
       <c r="B342" t="s">
-        <v>1356</v>
+        <v>465</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>326</v>
+        <v>1355</v>
       </c>
       <c r="B343" t="s">
-        <v>466</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>229</v>
+        <v>326</v>
       </c>
       <c r="B344" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>55</v>
+        <v>229</v>
       </c>
       <c r="B345" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>650</v>
+        <v>55</v>
       </c>
       <c r="B346" t="s">
-        <v>720</v>
+        <v>468</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>235</v>
+        <v>650</v>
       </c>
       <c r="B347" t="s">
-        <v>469</v>
+        <v>720</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="B348" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="B349" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>759</v>
+        <v>236</v>
       </c>
       <c r="B350" t="s">
-        <v>760</v>
+        <v>471</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>1002</v>
+        <v>759</v>
       </c>
       <c r="B351" t="s">
         <v>760</v>
@@ -7728,639 +7734,639 @@
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>164</v>
+        <v>1002</v>
       </c>
       <c r="B352" t="s">
-        <v>472</v>
+        <v>760</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>1452</v>
+        <v>164</v>
       </c>
       <c r="B353" t="s">
-        <v>1450</v>
+        <v>472</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>201</v>
+        <v>1452</v>
       </c>
       <c r="B354" t="s">
-        <v>473</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B355" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>313</v>
+        <v>204</v>
       </c>
       <c r="B356" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>865</v>
+        <v>313</v>
       </c>
       <c r="B357" t="s">
-        <v>866</v>
+        <v>475</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>988</v>
+        <v>865</v>
       </c>
       <c r="B358" t="s">
-        <v>989</v>
+        <v>866</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>1309</v>
+        <v>988</v>
       </c>
       <c r="B359" t="s">
-        <v>1310</v>
+        <v>989</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>258</v>
+        <v>1309</v>
       </c>
       <c r="B360" t="s">
-        <v>476</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>974</v>
+        <v>258</v>
       </c>
       <c r="B361" t="s">
-        <v>975</v>
+        <v>476</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>1347</v>
+        <v>974</v>
       </c>
       <c r="B362" t="s">
-        <v>1348</v>
+        <v>975</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>160</v>
+        <v>1347</v>
       </c>
       <c r="B363" t="s">
-        <v>477</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>685</v>
+        <v>160</v>
       </c>
       <c r="B364" t="s">
-        <v>721</v>
+        <v>477</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>1141</v>
+        <v>685</v>
       </c>
       <c r="B365" t="s">
-        <v>1142</v>
+        <v>721</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>753</v>
+        <v>1141</v>
       </c>
       <c r="B366" t="s">
-        <v>754</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>886</v>
+        <v>753</v>
       </c>
       <c r="B367" t="s">
-        <v>887</v>
+        <v>754</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B368" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>184</v>
+        <v>884</v>
       </c>
       <c r="B369" t="s">
-        <v>478</v>
+        <v>885</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>244</v>
+        <v>184</v>
       </c>
       <c r="B370" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B371" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>1253</v>
+        <v>243</v>
       </c>
       <c r="B372" t="s">
-        <v>1258</v>
+        <v>480</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>679</v>
+        <v>1253</v>
       </c>
       <c r="B373" t="s">
-        <v>722</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>1254</v>
+        <v>679</v>
       </c>
       <c r="B374" t="s">
-        <v>1259</v>
+        <v>722</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>680</v>
+        <v>1254</v>
       </c>
       <c r="B375" t="s">
-        <v>723</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>1255</v>
+        <v>680</v>
       </c>
       <c r="B376" t="s">
-        <v>1260</v>
+        <v>723</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>681</v>
+        <v>1255</v>
       </c>
       <c r="B377" t="s">
-        <v>724</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>1256</v>
+        <v>681</v>
       </c>
       <c r="B378" t="s">
-        <v>1261</v>
+        <v>724</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>682</v>
+        <v>1256</v>
       </c>
       <c r="B379" t="s">
-        <v>725</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>1257</v>
+        <v>682</v>
       </c>
       <c r="B380" t="s">
-        <v>1262</v>
+        <v>725</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>683</v>
+        <v>1257</v>
       </c>
       <c r="B381" t="s">
-        <v>726</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>1167</v>
+        <v>683</v>
       </c>
       <c r="B382" t="s">
-        <v>1168</v>
+        <v>726</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>280</v>
+        <v>1167</v>
       </c>
       <c r="B383" t="s">
-        <v>481</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B384" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>49</v>
+        <v>281</v>
       </c>
       <c r="B385" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B386" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="B387" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>1428</v>
+        <v>136</v>
       </c>
       <c r="B388" t="s">
-        <v>1429</v>
+        <v>486</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>72</v>
+        <v>1428</v>
       </c>
       <c r="B389" t="s">
-        <v>485</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>1504</v>
+        <v>72</v>
       </c>
       <c r="B390" t="s">
-        <v>1505</v>
+        <v>485</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>1165</v>
+        <v>1504</v>
       </c>
       <c r="B391" t="s">
-        <v>1166</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>221</v>
+        <v>1165</v>
       </c>
       <c r="B392" t="s">
-        <v>487</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>1169</v>
+        <v>221</v>
       </c>
       <c r="B393" t="s">
-        <v>1170</v>
+        <v>487</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>15</v>
+        <v>1169</v>
       </c>
       <c r="B394" t="s">
-        <v>16</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>1048</v>
+        <v>15</v>
       </c>
       <c r="B395" t="s">
-        <v>1049</v>
+        <v>16</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>911</v>
+        <v>1048</v>
       </c>
       <c r="B396" t="s">
-        <v>912</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>108</v>
+        <v>911</v>
       </c>
       <c r="B397" t="s">
-        <v>488</v>
+        <v>912</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>241</v>
+        <v>108</v>
       </c>
       <c r="B398" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>327</v>
+        <v>241</v>
       </c>
       <c r="B399" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>1088</v>
+        <v>327</v>
       </c>
       <c r="B400" t="s">
-        <v>1089</v>
+        <v>490</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>1040</v>
+        <v>1088</v>
       </c>
       <c r="B401" t="s">
-        <v>1041</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>121</v>
+        <v>1040</v>
       </c>
       <c r="B402" t="s">
-        <v>491</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>743</v>
+        <v>121</v>
       </c>
       <c r="B403" t="s">
-        <v>744</v>
+        <v>491</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>774</v>
+        <v>743</v>
       </c>
       <c r="B404" t="s">
-        <v>775</v>
+        <v>744</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>134</v>
+        <v>774</v>
       </c>
       <c r="B405" t="s">
-        <v>492</v>
+        <v>775</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="B406" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>1287</v>
+        <v>63</v>
       </c>
       <c r="B407" t="s">
-        <v>1288</v>
+        <v>493</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>224</v>
+        <v>1287</v>
       </c>
       <c r="B408" t="s">
-        <v>494</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>25</v>
+        <v>224</v>
       </c>
       <c r="B409" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B410" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>207</v>
+        <v>26</v>
       </c>
       <c r="B411" t="s">
-        <v>1110</v>
+        <v>496</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>951</v>
+        <v>207</v>
       </c>
       <c r="B412" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>1097</v>
+        <v>951</v>
       </c>
       <c r="B413" t="s">
-        <v>1098</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>206</v>
+        <v>1097</v>
       </c>
       <c r="B414" t="s">
-        <v>1112</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B415" t="s">
-        <v>497</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B416" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="B417" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>656</v>
+        <v>145</v>
       </c>
       <c r="B418" t="s">
-        <v>727</v>
+        <v>499</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>171</v>
+        <v>656</v>
       </c>
       <c r="B419" t="s">
-        <v>500</v>
+        <v>727</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>1076</v>
+        <v>171</v>
       </c>
       <c r="B420" t="s">
-        <v>1077</v>
+        <v>500</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>263</v>
+        <v>1076</v>
       </c>
       <c r="B421" t="s">
-        <v>501</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>1078</v>
+        <v>263</v>
       </c>
       <c r="B422" t="s">
-        <v>1079</v>
+        <v>501</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>80</v>
+        <v>1078</v>
       </c>
       <c r="B423" t="s">
-        <v>502</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B424" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>191</v>
+        <v>65</v>
       </c>
       <c r="B425" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="B426" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>192</v>
+        <v>123</v>
       </c>
       <c r="B427" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="B428" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B429" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>1175</v>
+        <v>233</v>
       </c>
       <c r="B430" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>31</v>
+        <v>1175</v>
       </c>
       <c r="B431" t="s">
         <v>509</v>
@@ -8368,375 +8374,375 @@
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>1481</v>
+        <v>31</v>
       </c>
       <c r="B432" t="s">
-        <v>1482</v>
+        <v>509</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>30</v>
+        <v>1481</v>
       </c>
       <c r="B433" t="s">
-        <v>510</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B434" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B435" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>1426</v>
+        <v>71</v>
       </c>
       <c r="B436" t="s">
-        <v>1427</v>
+        <v>512</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>306</v>
+        <v>1426</v>
       </c>
       <c r="B437" t="s">
-        <v>513</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>222</v>
+        <v>306</v>
       </c>
       <c r="B438" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>278</v>
+        <v>222</v>
       </c>
       <c r="B439" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B440" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>1377</v>
+        <v>279</v>
       </c>
       <c r="B441" t="s">
-        <v>1378</v>
+        <v>517</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>824</v>
+        <v>1377</v>
       </c>
       <c r="B442" t="s">
-        <v>825</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>48</v>
+        <v>824</v>
       </c>
       <c r="B443" t="s">
-        <v>518</v>
+        <v>825</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="B444" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="B445" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>1359</v>
+        <v>52</v>
       </c>
       <c r="B446" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>223</v>
+        <v>1359</v>
       </c>
       <c r="B447" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>1082</v>
+        <v>223</v>
       </c>
       <c r="B448" t="s">
-        <v>1083</v>
+        <v>521</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>1093</v>
+        <v>1082</v>
       </c>
       <c r="B449" t="s">
-        <v>1096</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>1038</v>
+        <v>1093</v>
       </c>
       <c r="B450" t="s">
-        <v>1039</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>96</v>
+        <v>1038</v>
       </c>
       <c r="B451" t="s">
-        <v>522</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>248</v>
+        <v>96</v>
       </c>
       <c r="B452" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B453" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>94</v>
+        <v>249</v>
       </c>
       <c r="B454" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>1052</v>
+        <v>94</v>
       </c>
       <c r="B455" t="s">
-        <v>1053</v>
+        <v>525</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>212</v>
+        <v>1052</v>
       </c>
       <c r="B456" t="s">
-        <v>526</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>1200</v>
+        <v>212</v>
       </c>
       <c r="B457" t="s">
-        <v>1201</v>
+        <v>526</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>907</v>
+        <v>1200</v>
       </c>
       <c r="B458" t="s">
-        <v>908</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B459" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="B460" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>329</v>
+        <v>909</v>
       </c>
       <c r="B461" t="s">
-        <v>527</v>
+        <v>910</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>1401</v>
+        <v>329</v>
       </c>
       <c r="B462" t="s">
-        <v>1402</v>
+        <v>527</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="B463" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>1054</v>
+        <v>1403</v>
       </c>
       <c r="B464" t="s">
-        <v>1055</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>986</v>
+        <v>1054</v>
       </c>
       <c r="B465" t="s">
-        <v>987</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>1387</v>
+        <v>986</v>
       </c>
       <c r="B466" t="s">
-        <v>1388</v>
+        <v>987</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>982</v>
+        <v>1387</v>
       </c>
       <c r="B467" t="s">
-        <v>983</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B468" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>82</v>
+        <v>984</v>
       </c>
       <c r="B469" t="s">
-        <v>528</v>
+        <v>985</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>765</v>
+        <v>82</v>
       </c>
       <c r="B470" t="s">
-        <v>766</v>
+        <v>528</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>197</v>
+        <v>765</v>
       </c>
       <c r="B471" t="s">
-        <v>529</v>
+        <v>766</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>647</v>
+        <v>197</v>
       </c>
       <c r="B472" t="s">
-        <v>728</v>
+        <v>529</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>1424</v>
+        <v>647</v>
       </c>
       <c r="B473" t="s">
-        <v>1425</v>
+        <v>728</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>1330</v>
+        <v>1424</v>
       </c>
       <c r="B474" t="s">
-        <v>1331</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>814</v>
+        <v>1330</v>
       </c>
       <c r="B475" t="s">
-        <v>815</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>1056</v>
+        <v>814</v>
       </c>
       <c r="B476" t="s">
-        <v>1057</v>
+        <v>815</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>3</v>
+        <v>1056</v>
       </c>
       <c r="B477" t="s">
-        <v>4</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>949</v>
+        <v>3</v>
       </c>
       <c r="B478" t="s">
         <v>4</v>
@@ -8744,7 +8750,7 @@
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B479" t="s">
         <v>4</v>
@@ -8752,1639 +8758,1639 @@
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>657</v>
+        <v>950</v>
       </c>
       <c r="B480" t="s">
-        <v>729</v>
+        <v>4</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>1279</v>
+        <v>657</v>
       </c>
       <c r="B481" t="s">
-        <v>1280</v>
+        <v>729</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>763</v>
+        <v>1279</v>
       </c>
       <c r="B482" t="s">
-        <v>764</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>85</v>
+        <v>763</v>
       </c>
       <c r="B483" t="s">
-        <v>530</v>
+        <v>764</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>1050</v>
+        <v>85</v>
       </c>
       <c r="B484" t="s">
-        <v>1051</v>
+        <v>530</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>822</v>
+        <v>1050</v>
       </c>
       <c r="B485" t="s">
-        <v>823</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>802</v>
+        <v>822</v>
       </c>
       <c r="B486" t="s">
-        <v>803</v>
+        <v>823</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>187</v>
+        <v>802</v>
       </c>
       <c r="B487" t="s">
-        <v>531</v>
+        <v>803</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>820</v>
+        <v>187</v>
       </c>
       <c r="B488" t="s">
-        <v>821</v>
+        <v>531</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>925</v>
+        <v>820</v>
       </c>
       <c r="B489" t="s">
-        <v>1107</v>
+        <v>821</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>1430</v>
+        <v>925</v>
       </c>
       <c r="B490" t="s">
-        <v>1431</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>855</v>
+        <v>1430</v>
       </c>
       <c r="B491" t="s">
-        <v>856</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>1418</v>
+        <v>855</v>
       </c>
       <c r="B492" t="s">
-        <v>1419</v>
+        <v>856</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>1034</v>
+        <v>1418</v>
       </c>
       <c r="B493" t="s">
-        <v>1035</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>791</v>
+        <v>1034</v>
       </c>
       <c r="B494" t="s">
-        <v>1108</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B495" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>1472</v>
+        <v>790</v>
       </c>
       <c r="B496" t="s">
-        <v>1473</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="B497" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>13</v>
+        <v>1470</v>
       </c>
       <c r="B498" t="s">
-        <v>14</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>810</v>
+        <v>13</v>
       </c>
       <c r="B499" t="s">
-        <v>811</v>
+        <v>14</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>1209</v>
+        <v>810</v>
       </c>
       <c r="B500" t="s">
-        <v>1210</v>
+        <v>811</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>186</v>
+        <v>1209</v>
       </c>
       <c r="B501" t="s">
-        <v>532</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>804</v>
+        <v>186</v>
       </c>
       <c r="B502" t="s">
-        <v>805</v>
+        <v>532</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>319</v>
+        <v>804</v>
       </c>
       <c r="B503" t="s">
-        <v>533</v>
+        <v>805</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>649</v>
+        <v>319</v>
       </c>
       <c r="B504" t="s">
-        <v>730</v>
+        <v>533</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>848</v>
+        <v>649</v>
       </c>
       <c r="B505" t="s">
-        <v>849</v>
+        <v>730</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>651</v>
+        <v>848</v>
       </c>
       <c r="B506" t="s">
-        <v>731</v>
+        <v>849</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="B507" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>1182</v>
+        <v>646</v>
       </c>
       <c r="B508" t="s">
-        <v>1183</v>
+        <v>732</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>256</v>
+        <v>1182</v>
       </c>
       <c r="B509" t="s">
-        <v>534</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B510" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B511" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>188</v>
+        <v>261</v>
       </c>
       <c r="B512" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B513" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>927</v>
+        <v>190</v>
       </c>
       <c r="B514" t="s">
-        <v>928</v>
+        <v>538</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>1021</v>
+        <v>927</v>
       </c>
       <c r="B515" t="s">
-        <v>1022</v>
+        <v>928</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>1198</v>
+        <v>1021</v>
       </c>
       <c r="B516" t="s">
-        <v>1199</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>209</v>
+        <v>1198</v>
       </c>
       <c r="B517" t="s">
-        <v>539</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>1397</v>
+        <v>209</v>
       </c>
       <c r="B518" t="s">
-        <v>1398</v>
+        <v>539</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>1289</v>
+        <v>1397</v>
       </c>
       <c r="B519" t="s">
-        <v>1290</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>844</v>
+        <v>1289</v>
       </c>
       <c r="B520" t="s">
-        <v>845</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>143</v>
+        <v>844</v>
       </c>
       <c r="B521" t="s">
-        <v>540</v>
+        <v>845</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B522" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>1178</v>
+        <v>140</v>
       </c>
       <c r="B523" t="s">
-        <v>1179</v>
+        <v>541</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>1277</v>
+        <v>1178</v>
       </c>
       <c r="B524" t="s">
-        <v>1278</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>254</v>
+        <v>1277</v>
       </c>
       <c r="B525" t="s">
-        <v>542</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>330</v>
+        <v>254</v>
       </c>
       <c r="B526" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="B527" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="B528" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>73</v>
+        <v>234</v>
       </c>
       <c r="B529" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>341</v>
+        <v>73</v>
       </c>
       <c r="B530" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>308</v>
+        <v>341</v>
       </c>
       <c r="B531" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>836</v>
+        <v>308</v>
       </c>
       <c r="B532" t="s">
-        <v>837</v>
+        <v>548</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B533" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>220</v>
+        <v>838</v>
       </c>
       <c r="B534" t="s">
-        <v>549</v>
+        <v>839</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>900</v>
+        <v>220</v>
       </c>
       <c r="B535" t="s">
-        <v>901</v>
+        <v>549</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>1353</v>
+        <v>900</v>
       </c>
       <c r="B536" t="s">
-        <v>1354</v>
+        <v>901</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>954</v>
+        <v>1353</v>
       </c>
       <c r="B537" t="s">
-        <v>955</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>1163</v>
+        <v>954</v>
       </c>
       <c r="B538" t="s">
-        <v>1164</v>
+        <v>955</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>227</v>
+        <v>1163</v>
       </c>
       <c r="B539" t="s">
-        <v>550</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>333</v>
+        <v>227</v>
       </c>
       <c r="B540" t="s">
-        <v>1136</v>
+        <v>550</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>962</v>
+        <v>333</v>
       </c>
       <c r="B541" t="s">
-        <v>963</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>771</v>
+        <v>962</v>
       </c>
       <c r="B542" t="s">
-        <v>772</v>
+        <v>963</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>294</v>
+        <v>771</v>
       </c>
       <c r="B543" t="s">
-        <v>551</v>
+        <v>772</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>943</v>
+        <v>294</v>
       </c>
       <c r="B544" t="s">
-        <v>944</v>
+        <v>551</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>338</v>
+        <v>943</v>
       </c>
       <c r="B545" t="s">
-        <v>552</v>
+        <v>944</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>773</v>
+        <v>338</v>
       </c>
       <c r="B546" t="s">
-        <v>772</v>
+        <v>552</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>1293</v>
+        <v>773</v>
       </c>
       <c r="B547" t="s">
-        <v>1294</v>
+        <v>772</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>339</v>
+        <v>1293</v>
       </c>
       <c r="B548" t="s">
-        <v>553</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B549" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>638</v>
+        <v>340</v>
       </c>
       <c r="B550" t="s">
-        <v>733</v>
+        <v>554</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>39</v>
+        <v>638</v>
       </c>
       <c r="B551" t="s">
-        <v>1490</v>
+        <v>733</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B552" t="s">
-        <v>1483</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>342</v>
+        <v>38</v>
       </c>
       <c r="B553" t="s">
-        <v>555</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>107</v>
+        <v>342</v>
       </c>
       <c r="B554" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>1405</v>
+        <v>107</v>
       </c>
       <c r="B555" t="s">
-        <v>1406</v>
+        <v>556</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>1019</v>
+        <v>1405</v>
       </c>
       <c r="B556" t="s">
-        <v>1020</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>894</v>
+        <v>1019</v>
       </c>
       <c r="B557" t="s">
-        <v>895</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>117</v>
+        <v>894</v>
       </c>
       <c r="B558" t="s">
-        <v>557</v>
+        <v>895</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>1015</v>
+        <v>117</v>
       </c>
       <c r="B559" t="s">
-        <v>1016</v>
+        <v>557</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>98</v>
+        <v>1015</v>
       </c>
       <c r="B560" t="s">
-        <v>558</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B561" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>659</v>
+        <v>99</v>
       </c>
       <c r="B562" t="s">
-        <v>734</v>
+        <v>559</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>1091</v>
+        <v>659</v>
       </c>
       <c r="B563" t="s">
-        <v>1014</v>
+        <v>734</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>816</v>
+        <v>1091</v>
       </c>
       <c r="B564" t="s">
-        <v>817</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>113</v>
+        <v>816</v>
       </c>
       <c r="B565" t="s">
-        <v>560</v>
+        <v>817</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>881</v>
+        <v>113</v>
       </c>
       <c r="B566" t="s">
-        <v>882</v>
+        <v>560</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>45</v>
+        <v>881</v>
       </c>
       <c r="B567" t="s">
-        <v>1106</v>
+        <v>882</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>290</v>
+        <v>45</v>
       </c>
       <c r="B568" t="s">
-        <v>561</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B569" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>47</v>
+        <v>299</v>
       </c>
       <c r="B570" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>840</v>
+        <v>47</v>
       </c>
       <c r="B571" t="s">
-        <v>841</v>
+        <v>563</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>51</v>
+        <v>840</v>
       </c>
       <c r="B572" t="s">
-        <v>564</v>
+        <v>841</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>863</v>
+        <v>51</v>
       </c>
       <c r="B573" t="s">
-        <v>864</v>
+        <v>564</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>114</v>
+        <v>863</v>
       </c>
       <c r="B574" t="s">
-        <v>565</v>
+        <v>864</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>846</v>
+        <v>114</v>
       </c>
       <c r="B575" t="s">
-        <v>847</v>
+        <v>565</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>144</v>
+        <v>846</v>
       </c>
       <c r="B576" t="s">
-        <v>566</v>
+        <v>847</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>1068</v>
+        <v>144</v>
       </c>
       <c r="B577" t="s">
-        <v>1069</v>
+        <v>566</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>176</v>
+        <v>1068</v>
       </c>
       <c r="B578" t="s">
-        <v>567</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>315</v>
+        <v>176</v>
       </c>
       <c r="B579" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>29</v>
+        <v>315</v>
       </c>
       <c r="B580" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>1008</v>
+        <v>29</v>
       </c>
       <c r="B581" t="s">
-        <v>1009</v>
+        <v>569</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>1205</v>
+        <v>1008</v>
       </c>
       <c r="B582" t="s">
-        <v>1206</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>293</v>
+        <v>1205</v>
       </c>
       <c r="B583" t="s">
-        <v>570</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>972</v>
+        <v>293</v>
       </c>
       <c r="B584" t="s">
-        <v>973</v>
+        <v>570</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>1436</v>
+        <v>972</v>
       </c>
       <c r="B585" t="s">
-        <v>1437</v>
+        <v>973</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>301</v>
+        <v>1436</v>
       </c>
       <c r="B586" t="s">
-        <v>571</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>994</v>
+        <v>301</v>
       </c>
       <c r="B587" t="s">
-        <v>995</v>
+        <v>571</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="B588" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>75</v>
+        <v>998</v>
       </c>
       <c r="B589" t="s">
-        <v>572</v>
+        <v>999</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B590" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B591" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>328</v>
+        <v>78</v>
       </c>
       <c r="B592" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>1384</v>
+        <v>328</v>
       </c>
       <c r="B593" t="s">
-        <v>1385</v>
+        <v>575</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>1283</v>
+        <v>1384</v>
       </c>
       <c r="B594" t="s">
-        <v>1284</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>745</v>
+        <v>1283</v>
       </c>
       <c r="B595" t="s">
-        <v>746</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>798</v>
+        <v>745</v>
       </c>
       <c r="B596" t="s">
-        <v>799</v>
+        <v>746</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>1296</v>
+        <v>798</v>
       </c>
       <c r="B597" t="s">
-        <v>1297</v>
+        <v>799</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>135</v>
+        <v>1296</v>
       </c>
       <c r="B598" t="s">
-        <v>576</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>1161</v>
+        <v>135</v>
       </c>
       <c r="B599" t="s">
-        <v>1162</v>
+        <v>576</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>1028</v>
+        <v>1161</v>
       </c>
       <c r="B600" t="s">
-        <v>1029</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>215</v>
+        <v>1028</v>
       </c>
       <c r="B601" t="s">
-        <v>577</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>926</v>
+        <v>215</v>
       </c>
       <c r="B602" t="s">
-        <v>1121</v>
+        <v>577</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>216</v>
+        <v>926</v>
       </c>
       <c r="B603" t="s">
-        <v>1104</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>316</v>
+        <v>216</v>
       </c>
       <c r="B604" t="s">
-        <v>578</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>1070</v>
+        <v>316</v>
       </c>
       <c r="B605" t="s">
-        <v>1071</v>
+        <v>578</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>214</v>
+        <v>1070</v>
       </c>
       <c r="B606" t="s">
-        <v>1105</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>990</v>
+        <v>214</v>
       </c>
       <c r="B607" t="s">
-        <v>991</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B608" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>225</v>
+        <v>992</v>
       </c>
       <c r="B609" t="s">
-        <v>579</v>
+        <v>993</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>1371</v>
+        <v>225</v>
       </c>
       <c r="B610" t="s">
-        <v>1372</v>
+        <v>579</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>939</v>
+        <v>1371</v>
       </c>
       <c r="B611" t="s">
-        <v>940</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>1086</v>
+        <v>939</v>
       </c>
       <c r="B612" t="s">
-        <v>1087</v>
+        <v>940</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>1036</v>
+        <v>1086</v>
       </c>
       <c r="B613" t="s">
-        <v>1037</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>93</v>
+        <v>1036</v>
       </c>
       <c r="B614" t="s">
-        <v>580</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="B615" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>776</v>
+        <v>120</v>
       </c>
       <c r="B616" t="s">
-        <v>777</v>
+        <v>581</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>133</v>
+        <v>776</v>
       </c>
       <c r="B617" t="s">
-        <v>582</v>
+        <v>777</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="B618" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>1285</v>
+        <v>62</v>
       </c>
       <c r="B619" t="s">
-        <v>1286</v>
+        <v>583</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>66</v>
+        <v>1285</v>
       </c>
       <c r="B620" t="s">
-        <v>584</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>818</v>
+        <v>66</v>
       </c>
       <c r="B621" t="s">
-        <v>819</v>
+        <v>584</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
-        <v>941</v>
+        <v>818</v>
       </c>
       <c r="B622" t="s">
-        <v>942</v>
+        <v>819</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
-        <v>1190</v>
+        <v>941</v>
       </c>
       <c r="B623" t="s">
-        <v>1191</v>
+        <v>942</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
-        <v>1298</v>
+        <v>1190</v>
       </c>
       <c r="B624" t="s">
-        <v>1299</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
-        <v>79</v>
+        <v>1298</v>
       </c>
       <c r="B625" t="s">
-        <v>585</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B626" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="B627" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
-        <v>1159</v>
+        <v>122</v>
       </c>
       <c r="B628" t="s">
-        <v>1160</v>
+        <v>587</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>181</v>
+        <v>1159</v>
       </c>
       <c r="B629" t="s">
-        <v>588</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>794</v>
+        <v>181</v>
       </c>
       <c r="B630" t="s">
-        <v>795</v>
+        <v>588</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>1263</v>
+        <v>794</v>
       </c>
       <c r="B631" t="s">
-        <v>1268</v>
+        <v>795</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>684</v>
+        <v>1263</v>
       </c>
       <c r="B632" t="s">
-        <v>735</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
-        <v>1264</v>
+        <v>684</v>
       </c>
       <c r="B633" t="s">
-        <v>1269</v>
+        <v>735</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="B634" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="B635" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="B636" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
-        <v>1126</v>
+        <v>1267</v>
       </c>
       <c r="B637" t="s">
-        <v>1127</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="B638" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
-        <v>284</v>
+        <v>1124</v>
       </c>
       <c r="B639" t="s">
-        <v>589</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
-        <v>964</v>
+        <v>284</v>
       </c>
       <c r="B640" t="s">
-        <v>965</v>
+        <v>589</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>1194</v>
+        <v>964</v>
       </c>
       <c r="B641" t="s">
-        <v>1195</v>
+        <v>965</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
-        <v>834</v>
+        <v>1194</v>
       </c>
       <c r="B642" t="s">
-        <v>835</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
-        <v>283</v>
+        <v>834</v>
       </c>
       <c r="B643" t="s">
-        <v>590</v>
+        <v>835</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
-        <v>875</v>
+        <v>283</v>
       </c>
       <c r="B644" t="s">
-        <v>876</v>
+        <v>590</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
-        <v>1155</v>
+        <v>875</v>
       </c>
       <c r="B645" t="s">
-        <v>1156</v>
+        <v>876</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
-        <v>749</v>
+        <v>1155</v>
       </c>
       <c r="B646" t="s">
-        <v>750</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
-        <v>1066</v>
+        <v>749</v>
       </c>
       <c r="B647" t="s">
-        <v>1067</v>
+        <v>750</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
-        <v>67</v>
+        <v>1066</v>
       </c>
       <c r="B648" t="s">
-        <v>591</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B649" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
-        <v>1366</v>
+        <v>68</v>
       </c>
       <c r="B650" t="s">
-        <v>1367</v>
+        <v>592</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
-        <v>95</v>
+        <v>1366</v>
       </c>
       <c r="B651" t="s">
-        <v>593</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>289</v>
+        <v>95</v>
       </c>
       <c r="B652" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B653" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="B654" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
-        <v>193</v>
+        <v>264</v>
       </c>
       <c r="B655" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
-        <v>1326</v>
+        <v>193</v>
       </c>
       <c r="B656" t="s">
-        <v>1327</v>
+        <v>597</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
-        <v>892</v>
+        <v>1326</v>
       </c>
       <c r="B657" t="s">
-        <v>893</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
-        <v>44</v>
+        <v>892</v>
       </c>
       <c r="B658" t="s">
-        <v>1103</v>
+        <v>893</v>
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
-        <v>1058</v>
+        <v>44</v>
       </c>
       <c r="B659" t="s">
-        <v>1059</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
-        <v>323</v>
+        <v>1058</v>
       </c>
       <c r="B660" t="s">
-        <v>598</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B661" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
-        <v>842</v>
+        <v>324</v>
       </c>
       <c r="B662" t="s">
-        <v>843</v>
+        <v>599</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
-        <v>879</v>
+        <v>842</v>
       </c>
       <c r="B663" t="s">
-        <v>880</v>
+        <v>843</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
-        <v>1211</v>
+        <v>879</v>
       </c>
       <c r="B664" t="s">
-        <v>1212</v>
+        <v>880</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
-        <v>1511</v>
+        <v>1211</v>
       </c>
       <c r="B665" t="s">
-        <v>1156</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
-        <v>861</v>
+        <v>1511</v>
       </c>
       <c r="B666" t="s">
-        <v>862</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
-        <v>33</v>
+        <v>861</v>
       </c>
       <c r="B667" t="s">
-        <v>600</v>
+        <v>862</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B668" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
-        <v>1119</v>
+        <v>36</v>
       </c>
       <c r="B669" t="s">
-        <v>1120</v>
+        <v>601</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
-        <v>309</v>
+        <v>1119</v>
       </c>
       <c r="B670" t="s">
-        <v>602</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
       <c r="B671" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
-        <v>302</v>
+        <v>257</v>
       </c>
       <c r="B672" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
-        <v>228</v>
+        <v>302</v>
       </c>
       <c r="B673" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c r="B674" t="s">
-        <v>18</v>
+        <v>605</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
-        <v>648</v>
+        <v>17</v>
       </c>
       <c r="B675" t="s">
-        <v>736</v>
+        <v>18</v>
       </c>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
-        <v>1393</v>
+        <v>648</v>
       </c>
       <c r="B676" t="s">
-        <v>1394</v>
+        <v>736</v>
       </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
-        <v>778</v>
+        <v>1393</v>
       </c>
       <c r="B677" t="s">
-        <v>779</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
-        <v>142</v>
+        <v>778</v>
       </c>
       <c r="B678" t="s">
-        <v>606</v>
+        <v>779</v>
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
-        <v>1153</v>
+        <v>142</v>
       </c>
       <c r="B679" t="s">
-        <v>1154</v>
+        <v>606</v>
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
-        <v>947</v>
+        <v>1153</v>
       </c>
       <c r="B680" t="s">
-        <v>948</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
-        <v>54</v>
+        <v>947</v>
       </c>
       <c r="B681" t="s">
-        <v>607</v>
+        <v>948</v>
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
-        <v>265</v>
+        <v>54</v>
       </c>
       <c r="B682" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
-        <v>967</v>
+        <v>265</v>
       </c>
       <c r="B683" t="s">
-        <v>966</v>
+        <v>608</v>
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
-        <v>1383</v>
+        <v>967</v>
       </c>
       <c r="B684" t="s">
         <v>966</v>
@@ -10392,633 +10398,641 @@
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
-        <v>56</v>
+        <v>1383</v>
       </c>
       <c r="B685" t="s">
-        <v>609</v>
+        <v>966</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
-        <v>1192</v>
+        <v>56</v>
       </c>
       <c r="B686" t="s">
-        <v>1193</v>
+        <v>609</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
-        <v>185</v>
+        <v>1192</v>
       </c>
       <c r="B687" t="s">
-        <v>610</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="B688" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="B689" t="s">
-        <v>1319</v>
+        <v>611</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
-        <v>1317</v>
+        <v>43</v>
       </c>
       <c r="B690" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
-        <v>1440</v>
+        <v>1317</v>
       </c>
       <c r="B691" t="s">
-        <v>1442</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B692" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
-        <v>40</v>
+        <v>1441</v>
       </c>
       <c r="B693" t="s">
-        <v>1474</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
-        <v>1315</v>
+        <v>40</v>
       </c>
       <c r="B694" t="s">
-        <v>1316</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
-        <v>1145</v>
+        <v>1315</v>
       </c>
       <c r="B695" t="s">
-        <v>1146</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
-        <v>165</v>
+        <v>1145</v>
       </c>
       <c r="B696" t="s">
-        <v>612</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
-        <v>1273</v>
+        <v>165</v>
       </c>
       <c r="B697" t="s">
-        <v>1274</v>
+        <v>612</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="B698" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
-        <v>1461</v>
+        <v>1275</v>
       </c>
       <c r="B699" t="s">
-        <v>1462</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B700" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
-        <v>12</v>
+        <v>1463</v>
       </c>
       <c r="B701" t="s">
-        <v>11</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
-        <v>250</v>
+        <v>12</v>
       </c>
       <c r="B702" t="s">
-        <v>613</v>
+        <v>11</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="B703" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
-        <v>1030</v>
+        <v>27</v>
       </c>
       <c r="B704" t="s">
-        <v>1031</v>
+        <v>614</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
-        <v>28</v>
+        <v>1030</v>
       </c>
       <c r="B705" t="s">
-        <v>615</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
-        <v>1180</v>
+        <v>28</v>
       </c>
       <c r="B706" t="s">
-        <v>1181</v>
+        <v>615</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
-        <v>255</v>
+        <v>1180</v>
       </c>
       <c r="B707" t="s">
-        <v>616</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
-        <v>1495</v>
+        <v>255</v>
       </c>
       <c r="B708" t="s">
-        <v>1496</v>
+        <v>616</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
-        <v>1308</v>
+        <v>1495</v>
       </c>
       <c r="B709" t="s">
-        <v>1509</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
-        <v>1508</v>
+        <v>1308</v>
       </c>
       <c r="B710" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
-        <v>788</v>
+        <v>1508</v>
       </c>
       <c r="B711" t="s">
-        <v>789</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
-        <v>267</v>
+        <v>788</v>
       </c>
       <c r="B712" t="s">
-        <v>617</v>
+        <v>789</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
-        <v>654</v>
+        <v>267</v>
       </c>
       <c r="B713" t="s">
-        <v>737</v>
+        <v>617</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B714" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A715" t="s">
-        <v>139</v>
+        <v>655</v>
       </c>
       <c r="B715" t="s">
-        <v>618</v>
+        <v>738</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A716" t="s">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="B716" t="s">
-        <v>2</v>
+        <v>618</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="B717" t="s">
-        <v>619</v>
+        <v>2</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
-        <v>1322</v>
+        <v>105</v>
       </c>
       <c r="B718" t="s">
-        <v>1323</v>
+        <v>619</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
-        <v>1024</v>
+        <v>1322</v>
       </c>
       <c r="B719" t="s">
-        <v>1102</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
-        <v>857</v>
+        <v>1024</v>
       </c>
       <c r="B720" t="s">
-        <v>858</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
-        <v>1422</v>
+        <v>857</v>
       </c>
       <c r="B721" t="s">
-        <v>1423</v>
+        <v>858</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
-        <v>1025</v>
+        <v>1422</v>
       </c>
       <c r="B722" t="s">
-        <v>1101</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
-        <v>292</v>
+        <v>1025</v>
       </c>
       <c r="B723" t="s">
-        <v>620</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
-        <v>8</v>
+        <v>292</v>
       </c>
       <c r="B724" t="s">
-        <v>11</v>
+        <v>620</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
-        <v>334</v>
+        <v>8</v>
       </c>
       <c r="B725" t="s">
-        <v>621</v>
+        <v>11</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
-        <v>1364</v>
+        <v>334</v>
       </c>
       <c r="B726" t="s">
-        <v>1365</v>
+        <v>621</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
-        <v>1324</v>
+        <v>1364</v>
       </c>
       <c r="B727" t="s">
-        <v>1325</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
-        <v>331</v>
+        <v>1324</v>
       </c>
       <c r="B728" t="s">
-        <v>622</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="B729" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A730" t="s">
-        <v>318</v>
+        <v>259</v>
       </c>
       <c r="B730" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
-        <v>851</v>
+        <v>318</v>
       </c>
       <c r="B731" t="s">
-        <v>852</v>
+        <v>624</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
-        <v>1149</v>
+        <v>851</v>
       </c>
       <c r="B732" t="s">
-        <v>1150</v>
+        <v>852</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
-        <v>268</v>
+        <v>1149</v>
       </c>
       <c r="B733" t="s">
-        <v>625</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B734" t="s">
-        <v>1099</v>
+        <v>625</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B735" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B736" t="s">
-        <v>1497</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A737" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B737" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B738" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B739" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A740" t="s">
-        <v>92</v>
+        <v>272</v>
       </c>
       <c r="B740" t="s">
-        <v>626</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
-        <v>200</v>
+        <v>92</v>
       </c>
       <c r="B741" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B742" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
-        <v>1202</v>
+        <v>203</v>
       </c>
       <c r="B743" t="s">
-        <v>1501</v>
+        <v>628</v>
       </c>
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A744" t="s">
-        <v>172</v>
+        <v>1202</v>
       </c>
       <c r="B744" t="s">
-        <v>629</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A745" t="s">
-        <v>1453</v>
+        <v>172</v>
       </c>
       <c r="B745" t="s">
-        <v>1454</v>
+        <v>629</v>
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A746" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B746" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A747" t="s">
         <v>686</v>
       </c>
-      <c r="B746" t="s">
+      <c r="B747" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="747" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A747" t="s">
+    <row r="748" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A748" t="s">
         <v>1448</v>
       </c>
-      <c r="B747" s="1" t="s">
+      <c r="B748" s="1" t="s">
         <v>1449</v>
-      </c>
-    </row>
-    <row r="748" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A748" t="s">
-        <v>252</v>
-      </c>
-      <c r="B748" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A749" t="s">
-        <v>687</v>
+        <v>252</v>
       </c>
       <c r="B749" t="s">
-        <v>740</v>
+        <v>630</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A750" t="s">
-        <v>189</v>
+        <v>687</v>
       </c>
       <c r="B750" t="s">
-        <v>1392</v>
+        <v>740</v>
       </c>
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A751" t="s">
-        <v>980</v>
+        <v>189</v>
       </c>
       <c r="B751" t="s">
-        <v>981</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A752" t="s">
-        <v>311</v>
+        <v>980</v>
       </c>
       <c r="B752" t="s">
-        <v>631</v>
+        <v>981</v>
       </c>
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A753" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B753" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="754" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A754" t="s">
-        <v>1023</v>
+        <v>312</v>
       </c>
       <c r="B754" t="s">
-        <v>1447</v>
+        <v>632</v>
       </c>
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A755" t="s">
-        <v>1446</v>
+        <v>1023</v>
       </c>
       <c r="B755" t="s">
-        <v>1467</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="756" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A756" t="s">
-        <v>996</v>
+        <v>1446</v>
       </c>
       <c r="B756" t="s">
-        <v>997</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A757" t="s">
-        <v>81</v>
+        <v>996</v>
       </c>
       <c r="B757" t="s">
-        <v>633</v>
+        <v>997</v>
       </c>
     </row>
     <row r="758" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A758" t="s">
-        <v>644</v>
+        <v>81</v>
       </c>
       <c r="B758" t="s">
-        <v>741</v>
+        <v>633</v>
       </c>
     </row>
     <row r="759" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A759" t="s">
-        <v>913</v>
+        <v>644</v>
       </c>
       <c r="B759" t="s">
-        <v>914</v>
+        <v>741</v>
       </c>
     </row>
     <row r="760" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A760" t="s">
-        <v>635</v>
+        <v>913</v>
       </c>
       <c r="B760" t="s">
-        <v>742</v>
+        <v>914</v>
       </c>
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A761" t="s">
-        <v>960</v>
+        <v>635</v>
       </c>
       <c r="B761" t="s">
-        <v>961</v>
+        <v>742</v>
       </c>
     </row>
     <row r="762" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A762" t="s">
-        <v>1137</v>
+        <v>960</v>
       </c>
       <c r="B762" t="s">
-        <v>1138</v>
+        <v>961</v>
       </c>
     </row>
     <row r="763" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A763" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B763" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A764" t="s">
         <v>1362</v>
       </c>
-      <c r="B763" t="s">
+      <c r="B764" t="s">
         <v>1363</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE1B8283-D6C8-4DA9-91D8-AA3F5B71827A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB3AB0B2-6520-4F79-90F6-81281A9907B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="1515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="1534">
   <si>
     <t>trigger</t>
   </si>
@@ -4573,6 +4573,63 @@
   </si>
   <si>
     <t>angiomyolipoma</t>
+  </si>
+  <si>
+    <t>cem</t>
+  </si>
+  <si>
+    <t>centrilobular emphysematous changes</t>
+  </si>
+  <si>
+    <t>pem</t>
+  </si>
+  <si>
+    <t>paraseptal emhysematous changes</t>
+  </si>
+  <si>
+    <t>ulr</t>
+  </si>
+  <si>
+    <t>upper lobe of right lung</t>
+  </si>
+  <si>
+    <t>mlr</t>
+  </si>
+  <si>
+    <t>middle lobe of right lung</t>
+  </si>
+  <si>
+    <t>llr</t>
+  </si>
+  <si>
+    <t>lower lobe of right lung</t>
+  </si>
+  <si>
+    <t>ull</t>
+  </si>
+  <si>
+    <t>upper lobe of left lung</t>
+  </si>
+  <si>
+    <t>llol</t>
+  </si>
+  <si>
+    <t>lower lobe of left lung</t>
+  </si>
+  <si>
+    <t>ulb</t>
+  </si>
+  <si>
+    <t>upper lobe of bilateral lungs</t>
+  </si>
+  <si>
+    <t>llb</t>
+  </si>
+  <si>
+    <t>lower lobe of bilateral lungs</t>
+  </si>
+  <si>
+    <t>subcut</t>
   </si>
 </sst>
 </file>
@@ -4641,10 +4698,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B764" totalsRowShown="0">
-  <autoFilter ref="A1:B764" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B764">
-    <sortCondition ref="A1:A764"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B774" totalsRowShown="0">
+  <autoFilter ref="A1:B774" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B774">
+    <sortCondition ref="A1:A774"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4917,7 +4974,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B764"/>
+  <dimension ref="A1:B774"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -5838,1047 +5895,1047 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>1444</v>
+        <v>1515</v>
       </c>
       <c r="B115" t="s">
-        <v>1445</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>217</v>
+        <v>1444</v>
       </c>
       <c r="B116" t="s">
-        <v>385</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>288</v>
+        <v>217</v>
       </c>
       <c r="B117" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>218</v>
+        <v>288</v>
       </c>
       <c r="B118" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>296</v>
+        <v>218</v>
       </c>
       <c r="B119" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>199</v>
+        <v>296</v>
       </c>
       <c r="B120" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>1415</v>
+        <v>199</v>
       </c>
       <c r="B121" t="s">
-        <v>1416</v>
+        <v>389</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>641</v>
+        <v>1415</v>
       </c>
       <c r="B122" t="s">
-        <v>700</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>112</v>
+        <v>641</v>
       </c>
       <c r="B123" t="s">
-        <v>390</v>
+        <v>700</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="B124" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="B125" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>1151</v>
+        <v>115</v>
       </c>
       <c r="B126" t="s">
-        <v>1152</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>871</v>
+        <v>1151</v>
       </c>
       <c r="B127" t="s">
-        <v>872</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>800</v>
+        <v>871</v>
       </c>
       <c r="B128" t="s">
-        <v>801</v>
+        <v>872</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>1468</v>
+        <v>800</v>
       </c>
       <c r="B129" t="s">
-        <v>1469</v>
+        <v>801</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>152</v>
+        <v>1468</v>
       </c>
       <c r="B130" t="s">
-        <v>393</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>1295</v>
+        <v>152</v>
       </c>
       <c r="B131" t="s">
-        <v>1300</v>
+        <v>393</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>124</v>
+        <v>1295</v>
       </c>
       <c r="B132" t="s">
-        <v>395</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B133" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="B134" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>958</v>
+        <v>155</v>
       </c>
       <c r="B135" t="s">
-        <v>959</v>
+        <v>396</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>84</v>
+        <v>958</v>
       </c>
       <c r="B136" t="s">
-        <v>397</v>
+        <v>959</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>956</v>
+        <v>84</v>
       </c>
       <c r="B137" t="s">
-        <v>957</v>
+        <v>397</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>1381</v>
+        <v>956</v>
       </c>
       <c r="B138" t="s">
-        <v>1382</v>
+        <v>957</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>103</v>
+        <v>1381</v>
       </c>
       <c r="B139" t="s">
-        <v>398</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>198</v>
+        <v>103</v>
       </c>
       <c r="B140" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>314</v>
+        <v>198</v>
       </c>
       <c r="B141" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>104</v>
+        <v>314</v>
       </c>
       <c r="B142" t="s">
-        <v>1460</v>
+        <v>400</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>1488</v>
+        <v>104</v>
       </c>
       <c r="B143" t="s">
-        <v>1489</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>163</v>
+        <v>1488</v>
       </c>
       <c r="B144" t="s">
-        <v>401</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="B145" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B146" t="s">
-        <v>1314</v>
+        <v>402</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>1313</v>
+        <v>102</v>
       </c>
       <c r="B147" t="s">
-        <v>403</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>921</v>
+        <v>1313</v>
       </c>
       <c r="B148" t="s">
-        <v>922</v>
+        <v>403</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B149" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>162</v>
+        <v>919</v>
       </c>
       <c r="B150" t="s">
-        <v>404</v>
+        <v>920</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>1128</v>
+        <v>162</v>
       </c>
       <c r="B151" t="s">
-        <v>1129</v>
+        <v>404</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>1357</v>
+        <v>1128</v>
       </c>
       <c r="B152" t="s">
-        <v>1358</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>830</v>
+        <v>1357</v>
       </c>
       <c r="B153" t="s">
-        <v>831</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B154" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>1301</v>
+        <v>832</v>
       </c>
       <c r="B155" t="s">
-        <v>1459</v>
+        <v>833</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>1072</v>
+        <v>1301</v>
       </c>
       <c r="B156" t="s">
-        <v>1073</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>658</v>
+        <v>1072</v>
       </c>
       <c r="B157" t="s">
-        <v>701</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>639</v>
+        <v>658</v>
       </c>
       <c r="B158" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>931</v>
+        <v>639</v>
       </c>
       <c r="B159" t="s">
-        <v>932</v>
+        <v>702</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>1432</v>
+        <v>931</v>
       </c>
       <c r="B160" t="s">
-        <v>1433</v>
+        <v>932</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>1351</v>
+        <v>1432</v>
       </c>
       <c r="B161" t="s">
-        <v>1352</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>1229</v>
+        <v>1351</v>
       </c>
       <c r="B162" t="s">
-        <v>1241</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>1238</v>
+        <v>1229</v>
       </c>
       <c r="B163" t="s">
-        <v>1250</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>676</v>
+        <v>1238</v>
       </c>
       <c r="B164" t="s">
-        <v>703</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>1239</v>
+        <v>676</v>
       </c>
       <c r="B165" t="s">
-        <v>1251</v>
+        <v>703</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>677</v>
+        <v>1239</v>
       </c>
       <c r="B166" t="s">
-        <v>704</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>1240</v>
+        <v>677</v>
       </c>
       <c r="B167" t="s">
-        <v>1252</v>
+        <v>704</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>678</v>
+        <v>1240</v>
       </c>
       <c r="B168" t="s">
-        <v>705</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>1230</v>
+        <v>678</v>
       </c>
       <c r="B169" t="s">
-        <v>1242</v>
+        <v>705</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>668</v>
+        <v>1230</v>
       </c>
       <c r="B170" t="s">
-        <v>706</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>1231</v>
+        <v>668</v>
       </c>
       <c r="B171" t="s">
-        <v>1243</v>
+        <v>706</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>669</v>
+        <v>1231</v>
       </c>
       <c r="B172" t="s">
-        <v>707</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>1232</v>
+        <v>669</v>
       </c>
       <c r="B173" t="s">
-        <v>1244</v>
+        <v>707</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>670</v>
+        <v>1232</v>
       </c>
       <c r="B174" t="s">
-        <v>708</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>1233</v>
+        <v>670</v>
       </c>
       <c r="B175" t="s">
-        <v>1245</v>
+        <v>708</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>671</v>
+        <v>1233</v>
       </c>
       <c r="B176" t="s">
-        <v>709</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>1234</v>
+        <v>671</v>
       </c>
       <c r="B177" t="s">
-        <v>1246</v>
+        <v>709</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>672</v>
+        <v>1234</v>
       </c>
       <c r="B178" t="s">
-        <v>710</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>1235</v>
+        <v>672</v>
       </c>
       <c r="B179" t="s">
-        <v>1247</v>
+        <v>710</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>673</v>
+        <v>1235</v>
       </c>
       <c r="B180" t="s">
-        <v>711</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>1236</v>
+        <v>673</v>
       </c>
       <c r="B181" t="s">
-        <v>1248</v>
+        <v>711</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>674</v>
+        <v>1236</v>
       </c>
       <c r="B182" t="s">
-        <v>712</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>1237</v>
+        <v>674</v>
       </c>
       <c r="B183" t="s">
-        <v>1249</v>
+        <v>712</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>675</v>
+        <v>1237</v>
       </c>
       <c r="B184" t="s">
-        <v>713</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>175</v>
+        <v>675</v>
       </c>
       <c r="B185" t="s">
-        <v>405</v>
+        <v>713</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="B186" t="s">
-        <v>1434</v>
+        <v>405</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B187" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>1311</v>
+        <v>213</v>
       </c>
       <c r="B188" t="s">
-        <v>1312</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>1345</v>
+        <v>1311</v>
       </c>
       <c r="B189" t="s">
-        <v>1346</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>1184</v>
+        <v>1345</v>
       </c>
       <c r="B190" t="s">
-        <v>406</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>149</v>
+        <v>1184</v>
       </c>
       <c r="B191" t="s">
-        <v>1187</v>
+        <v>406</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>247</v>
+        <v>149</v>
       </c>
       <c r="B192" t="s">
-        <v>407</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B193" t="s">
-        <v>1389</v>
+        <v>407</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>335</v>
+        <v>245</v>
       </c>
       <c r="B194" t="s">
-        <v>408</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>643</v>
+        <v>335</v>
       </c>
       <c r="B195" t="s">
-        <v>714</v>
+        <v>408</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>91</v>
+        <v>643</v>
       </c>
       <c r="B196" t="s">
-        <v>409</v>
+        <v>714</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>266</v>
+        <v>91</v>
       </c>
       <c r="B197" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>1465</v>
+        <v>266</v>
       </c>
       <c r="B198" t="s">
-        <v>1466</v>
+        <v>410</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>1084</v>
+        <v>1465</v>
       </c>
       <c r="B199" t="s">
-        <v>1085</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>792</v>
+        <v>1084</v>
       </c>
       <c r="B200" t="s">
-        <v>793</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>1143</v>
+        <v>792</v>
       </c>
       <c r="B201" t="s">
-        <v>1144</v>
+        <v>793</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>1328</v>
+        <v>1143</v>
       </c>
       <c r="B202" t="s">
-        <v>1329</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>295</v>
+        <v>1328</v>
       </c>
       <c r="B203" t="s">
-        <v>411</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>1074</v>
+        <v>295</v>
       </c>
       <c r="B204" t="s">
-        <v>1075</v>
+        <v>411</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="B205" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>151</v>
+        <v>1080</v>
       </c>
       <c r="B206" t="s">
-        <v>412</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>952</v>
+        <v>151</v>
       </c>
       <c r="B207" t="s">
-        <v>953</v>
+        <v>412</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>806</v>
+        <v>952</v>
       </c>
       <c r="B208" t="s">
-        <v>807</v>
+        <v>953</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>923</v>
+        <v>806</v>
       </c>
       <c r="B209" t="s">
-        <v>924</v>
+        <v>807</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>826</v>
+        <v>923</v>
       </c>
       <c r="B210" t="s">
-        <v>827</v>
+        <v>924</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>786</v>
+        <v>826</v>
       </c>
       <c r="B211" t="s">
-        <v>787</v>
+        <v>827</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>1413</v>
+        <v>786</v>
       </c>
       <c r="B212" t="s">
-        <v>1414</v>
+        <v>787</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>747</v>
+        <v>1413</v>
       </c>
       <c r="B213" t="s">
-        <v>748</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>100</v>
+        <v>747</v>
       </c>
       <c r="B214" t="s">
-        <v>413</v>
+        <v>748</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>1512</v>
+        <v>100</v>
       </c>
       <c r="B215" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>1032</v>
+        <v>1512</v>
       </c>
       <c r="B216" t="s">
-        <v>1033</v>
+        <v>416</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>154</v>
+        <v>1032</v>
       </c>
       <c r="B217" t="s">
-        <v>414</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B218" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="B219" t="s">
-        <v>1114</v>
+        <v>415</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>1139</v>
+        <v>24</v>
       </c>
       <c r="B220" t="s">
-        <v>1140</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>1302</v>
+        <v>1139</v>
       </c>
       <c r="B221" t="s">
-        <v>1303</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>1064</v>
+        <v>1302</v>
       </c>
       <c r="B222" t="s">
-        <v>1065</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>1457</v>
+        <v>1064</v>
       </c>
       <c r="B223" t="s">
-        <v>1458</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>812</v>
+        <v>1457</v>
       </c>
       <c r="B224" t="s">
-        <v>813</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>130</v>
+        <v>812</v>
       </c>
       <c r="B225" t="s">
-        <v>416</v>
+        <v>813</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>321</v>
+        <v>130</v>
       </c>
       <c r="B226" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>1456</v>
+        <v>321</v>
       </c>
       <c r="B227" t="s">
-        <v>1417</v>
+        <v>417</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>859</v>
+        <v>1456</v>
       </c>
       <c r="B228" t="s">
-        <v>860</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>1420</v>
+        <v>859</v>
       </c>
       <c r="B229" t="s">
-        <v>1421</v>
+        <v>860</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>1455</v>
+        <v>1420</v>
       </c>
       <c r="B230" t="s">
-        <v>883</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>1291</v>
+        <v>1455</v>
       </c>
       <c r="B231" t="s">
-        <v>1292</v>
+        <v>883</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>183</v>
+        <v>1291</v>
       </c>
       <c r="B232" t="s">
-        <v>418</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>1130</v>
+        <v>183</v>
       </c>
       <c r="B233" t="s">
-        <v>1131</v>
+        <v>418</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B234" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>1411</v>
+        <v>1132</v>
       </c>
       <c r="B235" t="s">
-        <v>1412</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>1484</v>
+        <v>1411</v>
       </c>
       <c r="B236" t="s">
-        <v>1485</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>1369</v>
+        <v>1484</v>
       </c>
       <c r="B237" t="s">
-        <v>1370</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>1486</v>
+        <v>1369</v>
       </c>
       <c r="B238" t="s">
-        <v>1487</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>32</v>
+        <v>1486</v>
       </c>
       <c r="B239" t="s">
-        <v>419</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B240" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>1281</v>
+        <v>35</v>
       </c>
       <c r="B241" t="s">
-        <v>1282</v>
+        <v>420</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>1207</v>
+        <v>1281</v>
       </c>
       <c r="B242" t="s">
-        <v>1208</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>757</v>
+        <v>1207</v>
       </c>
       <c r="B243" t="s">
-        <v>1000</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>169</v>
+        <v>757</v>
       </c>
       <c r="B244" t="s">
-        <v>421</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B245" t="s">
         <v>421</v>
@@ -6886,615 +6943,615 @@
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>1001</v>
+        <v>170</v>
       </c>
       <c r="B246" t="s">
-        <v>758</v>
+        <v>421</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>1409</v>
+        <v>1001</v>
       </c>
       <c r="B247" t="s">
-        <v>1410</v>
+        <v>758</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>178</v>
+        <v>1409</v>
       </c>
       <c r="B248" t="s">
-        <v>422</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="B249" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>238</v>
+        <v>111</v>
       </c>
       <c r="B250" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="B251" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B252" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="B253" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>660</v>
+        <v>179</v>
       </c>
       <c r="B254" t="s">
-        <v>715</v>
+        <v>427</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>1475</v>
+        <v>660</v>
       </c>
       <c r="B255" t="s">
-        <v>1476</v>
+        <v>715</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>97</v>
+        <v>1475</v>
       </c>
       <c r="B256" t="s">
-        <v>428</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B257" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>242</v>
+        <v>110</v>
       </c>
       <c r="B258" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B259" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="B260" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>1407</v>
+        <v>177</v>
       </c>
       <c r="B261" t="s">
-        <v>1408</v>
+        <v>432</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>182</v>
+        <v>1407</v>
       </c>
       <c r="B262" t="s">
-        <v>433</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>1094</v>
+        <v>182</v>
       </c>
       <c r="B263" t="s">
-        <v>1095</v>
+        <v>433</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>968</v>
+        <v>1094</v>
       </c>
       <c r="B264" t="s">
-        <v>969</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B265" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>1173</v>
+        <v>970</v>
       </c>
       <c r="B266" t="s">
-        <v>1174</v>
+        <v>971</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>1349</v>
+        <v>1173</v>
       </c>
       <c r="B267" t="s">
-        <v>1350</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>1176</v>
+        <v>1349</v>
       </c>
       <c r="B268" t="s">
-        <v>1177</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>253</v>
+        <v>1176</v>
       </c>
       <c r="B269" t="s">
-        <v>434</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="B270" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>780</v>
+        <v>34</v>
       </c>
       <c r="B271" t="s">
-        <v>781</v>
+        <v>435</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>180</v>
+        <v>780</v>
       </c>
       <c r="B272" t="s">
-        <v>436</v>
+        <v>781</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>1321</v>
+        <v>180</v>
       </c>
       <c r="B273" t="s">
-        <v>1390</v>
+        <v>436</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B274" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>1438</v>
+        <v>1320</v>
       </c>
       <c r="B275" t="s">
-        <v>1439</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>275</v>
+        <v>1438</v>
       </c>
       <c r="B276" t="s">
-        <v>1491</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>850</v>
+        <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>1493</v>
+        <v>850</v>
       </c>
       <c r="B278" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>1506</v>
+        <v>1493</v>
       </c>
       <c r="B279" t="s">
-        <v>1507</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>116</v>
+        <v>1506</v>
       </c>
       <c r="B280" t="s">
-        <v>437</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="B281" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>1395</v>
+        <v>208</v>
       </c>
       <c r="B282" t="s">
-        <v>1396</v>
+        <v>438</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>1196</v>
+        <v>1395</v>
       </c>
       <c r="B283" t="s">
-        <v>1197</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>1044</v>
+        <v>1196</v>
       </c>
       <c r="B284" t="s">
-        <v>1045</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>118</v>
+        <v>1044</v>
       </c>
       <c r="B285" t="s">
-        <v>439</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>634</v>
+        <v>118</v>
       </c>
       <c r="B286" t="s">
-        <v>716</v>
+        <v>439</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>1306</v>
+        <v>634</v>
       </c>
       <c r="B287" t="s">
-        <v>1307</v>
+        <v>716</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>808</v>
+        <v>1306</v>
       </c>
       <c r="B288" t="s">
-        <v>809</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>298</v>
+        <v>808</v>
       </c>
       <c r="B289" t="s">
-        <v>440</v>
+        <v>809</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>636</v>
+        <v>298</v>
       </c>
       <c r="B290" t="s">
-        <v>717</v>
+        <v>440</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B291" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>1026</v>
+        <v>637</v>
       </c>
       <c r="B292" t="s">
-        <v>1027</v>
+        <v>718</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>90</v>
+        <v>1026</v>
       </c>
       <c r="B293" t="s">
-        <v>441</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B294" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B295" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>1060</v>
+        <v>89</v>
       </c>
       <c r="B296" t="s">
-        <v>1061</v>
+        <v>443</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>23</v>
+        <v>1060</v>
       </c>
       <c r="B297" t="s">
-        <v>1113</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>1399</v>
+        <v>23</v>
       </c>
       <c r="B298" t="s">
-        <v>1400</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>5</v>
+        <v>1399</v>
       </c>
       <c r="B299" t="s">
-        <v>6</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>1117</v>
+        <v>5</v>
       </c>
       <c r="B300" t="s">
-        <v>1118</v>
+        <v>6</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>126</v>
+        <v>1117</v>
       </c>
       <c r="B301" t="s">
-        <v>444</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>1373</v>
+        <v>126</v>
       </c>
       <c r="B302" t="s">
-        <v>1374</v>
+        <v>444</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>128</v>
+        <v>1373</v>
       </c>
       <c r="B303" t="s">
-        <v>445</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B304" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B305" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B306" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>277</v>
+        <v>119</v>
       </c>
       <c r="B307" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>1062</v>
+        <v>277</v>
       </c>
       <c r="B308" t="s">
-        <v>1063</v>
+        <v>449</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>9</v>
+        <v>1062</v>
       </c>
       <c r="B309" t="s">
-        <v>10</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="B310" t="s">
-        <v>450</v>
+        <v>10</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B311" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="B312" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="B313" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>1360</v>
+        <v>262</v>
       </c>
       <c r="B314" t="s">
-        <v>1361</v>
+        <v>453</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>77</v>
+        <v>1360</v>
       </c>
       <c r="B315" t="s">
-        <v>454</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>929</v>
+        <v>77</v>
       </c>
       <c r="B316" t="s">
-        <v>930</v>
+        <v>454</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>1147</v>
+        <v>929</v>
       </c>
       <c r="B317" t="s">
-        <v>1148</v>
+        <v>930</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>168</v>
+        <v>1147</v>
       </c>
       <c r="B318" t="s">
-        <v>455</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>1333</v>
+        <v>168</v>
       </c>
       <c r="B319" t="s">
-        <v>1334</v>
+        <v>455</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>1343</v>
+        <v>1333</v>
       </c>
       <c r="B320" t="s">
-        <v>1344</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>1386</v>
+        <v>1343</v>
       </c>
       <c r="B321" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>1339</v>
+        <v>1386</v>
       </c>
       <c r="B322" t="s">
         <v>1340</v>
@@ -7502,39 +7559,39 @@
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>167</v>
+        <v>1339</v>
       </c>
       <c r="B323" t="s">
-        <v>456</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>1335</v>
+        <v>167</v>
       </c>
       <c r="B324" t="s">
-        <v>1336</v>
+        <v>456</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>1341</v>
+        <v>1335</v>
       </c>
       <c r="B325" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>1368</v>
+        <v>1341</v>
       </c>
       <c r="B326" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>1337</v>
+        <v>1368</v>
       </c>
       <c r="B327" t="s">
         <v>1338</v>
@@ -7542,199 +7599,199 @@
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>828</v>
+        <v>1337</v>
       </c>
       <c r="B328" t="s">
-        <v>829</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>784</v>
+        <v>828</v>
       </c>
       <c r="B329" t="s">
-        <v>785</v>
+        <v>829</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>304</v>
+        <v>784</v>
       </c>
       <c r="B330" t="s">
-        <v>457</v>
+        <v>785</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>751</v>
+        <v>304</v>
       </c>
       <c r="B331" t="s">
-        <v>752</v>
+        <v>457</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>888</v>
+        <v>751</v>
       </c>
       <c r="B332" t="s">
-        <v>889</v>
+        <v>752</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>1375</v>
+        <v>888</v>
       </c>
       <c r="B333" t="s">
-        <v>1376</v>
+        <v>889</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>645</v>
+        <v>1375</v>
       </c>
       <c r="B334" t="s">
-        <v>719</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>86</v>
+        <v>645</v>
       </c>
       <c r="B335" t="s">
-        <v>458</v>
+        <v>719</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B336" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="B337" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B338" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B339" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>251</v>
+        <v>158</v>
       </c>
       <c r="B340" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="B341" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>325</v>
+        <v>285</v>
       </c>
       <c r="B342" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>1355</v>
+        <v>325</v>
       </c>
       <c r="B343" t="s">
-        <v>1356</v>
+        <v>465</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>326</v>
+        <v>1355</v>
       </c>
       <c r="B344" t="s">
-        <v>466</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>229</v>
+        <v>326</v>
       </c>
       <c r="B345" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>55</v>
+        <v>229</v>
       </c>
       <c r="B346" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>650</v>
+        <v>55</v>
       </c>
       <c r="B347" t="s">
-        <v>720</v>
+        <v>468</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>235</v>
+        <v>650</v>
       </c>
       <c r="B348" t="s">
-        <v>469</v>
+        <v>720</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="B349" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="B350" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>759</v>
+        <v>236</v>
       </c>
       <c r="B351" t="s">
-        <v>760</v>
+        <v>471</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>1002</v>
+        <v>759</v>
       </c>
       <c r="B352" t="s">
         <v>760</v>
@@ -7742,3297 +7799,3377 @@
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>164</v>
+        <v>1002</v>
       </c>
       <c r="B353" t="s">
-        <v>472</v>
+        <v>760</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>1452</v>
+        <v>164</v>
       </c>
       <c r="B354" t="s">
-        <v>1450</v>
+        <v>472</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>201</v>
+        <v>1452</v>
       </c>
       <c r="B355" t="s">
-        <v>473</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B356" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>313</v>
+        <v>204</v>
       </c>
       <c r="B357" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>865</v>
+        <v>313</v>
       </c>
       <c r="B358" t="s">
-        <v>866</v>
+        <v>475</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>988</v>
+        <v>865</v>
       </c>
       <c r="B359" t="s">
-        <v>989</v>
+        <v>866</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>1309</v>
+        <v>988</v>
       </c>
       <c r="B360" t="s">
-        <v>1310</v>
+        <v>989</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>258</v>
+        <v>1309</v>
       </c>
       <c r="B361" t="s">
-        <v>476</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>974</v>
+        <v>258</v>
       </c>
       <c r="B362" t="s">
-        <v>975</v>
+        <v>476</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>1347</v>
+        <v>974</v>
       </c>
       <c r="B363" t="s">
-        <v>1348</v>
+        <v>975</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>160</v>
+        <v>1347</v>
       </c>
       <c r="B364" t="s">
-        <v>477</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>685</v>
+        <v>160</v>
       </c>
       <c r="B365" t="s">
-        <v>721</v>
+        <v>477</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>1141</v>
+        <v>685</v>
       </c>
       <c r="B366" t="s">
-        <v>1142</v>
+        <v>721</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>753</v>
+        <v>1141</v>
       </c>
       <c r="B367" t="s">
-        <v>754</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>886</v>
+        <v>753</v>
       </c>
       <c r="B368" t="s">
-        <v>887</v>
+        <v>754</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B369" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>184</v>
+        <v>884</v>
       </c>
       <c r="B370" t="s">
-        <v>478</v>
+        <v>885</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>244</v>
+        <v>184</v>
       </c>
       <c r="B371" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B372" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>1253</v>
+        <v>243</v>
       </c>
       <c r="B373" t="s">
-        <v>1258</v>
+        <v>480</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>679</v>
+        <v>1253</v>
       </c>
       <c r="B374" t="s">
-        <v>722</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>1254</v>
+        <v>679</v>
       </c>
       <c r="B375" t="s">
-        <v>1259</v>
+        <v>722</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>680</v>
+        <v>1254</v>
       </c>
       <c r="B376" t="s">
-        <v>723</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>1255</v>
+        <v>680</v>
       </c>
       <c r="B377" t="s">
-        <v>1260</v>
+        <v>723</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>681</v>
+        <v>1255</v>
       </c>
       <c r="B378" t="s">
-        <v>724</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>1256</v>
+        <v>681</v>
       </c>
       <c r="B379" t="s">
-        <v>1261</v>
+        <v>724</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>682</v>
+        <v>1256</v>
       </c>
       <c r="B380" t="s">
-        <v>725</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>1257</v>
+        <v>682</v>
       </c>
       <c r="B381" t="s">
-        <v>1262</v>
+        <v>725</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>683</v>
+        <v>1257</v>
       </c>
       <c r="B382" t="s">
-        <v>726</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>1167</v>
+        <v>683</v>
       </c>
       <c r="B383" t="s">
-        <v>1168</v>
+        <v>726</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>280</v>
+        <v>1167</v>
       </c>
       <c r="B384" t="s">
-        <v>481</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B385" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>49</v>
+        <v>281</v>
       </c>
       <c r="B386" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B387" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="B388" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>1428</v>
+        <v>136</v>
       </c>
       <c r="B389" t="s">
-        <v>1429</v>
+        <v>486</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>72</v>
+        <v>1428</v>
       </c>
       <c r="B390" t="s">
-        <v>485</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>1504</v>
+        <v>72</v>
       </c>
       <c r="B391" t="s">
-        <v>1505</v>
+        <v>485</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>1165</v>
+        <v>1504</v>
       </c>
       <c r="B392" t="s">
-        <v>1166</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>221</v>
+        <v>1165</v>
       </c>
       <c r="B393" t="s">
-        <v>487</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>1169</v>
+        <v>221</v>
       </c>
       <c r="B394" t="s">
-        <v>1170</v>
+        <v>487</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>15</v>
+        <v>1169</v>
       </c>
       <c r="B395" t="s">
-        <v>16</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>1048</v>
+        <v>15</v>
       </c>
       <c r="B396" t="s">
-        <v>1049</v>
+        <v>16</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>911</v>
+        <v>1048</v>
       </c>
       <c r="B397" t="s">
-        <v>912</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>108</v>
+        <v>911</v>
       </c>
       <c r="B398" t="s">
-        <v>488</v>
+        <v>912</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>241</v>
+        <v>108</v>
       </c>
       <c r="B399" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>327</v>
+        <v>241</v>
       </c>
       <c r="B400" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>1088</v>
+        <v>327</v>
       </c>
       <c r="B401" t="s">
-        <v>1089</v>
+        <v>490</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>1040</v>
+        <v>1088</v>
       </c>
       <c r="B402" t="s">
-        <v>1041</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>121</v>
+        <v>1040</v>
       </c>
       <c r="B403" t="s">
-        <v>491</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>743</v>
+        <v>121</v>
       </c>
       <c r="B404" t="s">
-        <v>744</v>
+        <v>491</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>774</v>
+        <v>743</v>
       </c>
       <c r="B405" t="s">
-        <v>775</v>
+        <v>744</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>134</v>
+        <v>774</v>
       </c>
       <c r="B406" t="s">
-        <v>492</v>
+        <v>775</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="B407" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>1287</v>
+        <v>1531</v>
       </c>
       <c r="B408" t="s">
-        <v>1288</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>224</v>
+        <v>63</v>
       </c>
       <c r="B409" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>25</v>
+        <v>1527</v>
       </c>
       <c r="B410" t="s">
-        <v>495</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>26</v>
+        <v>1287</v>
       </c>
       <c r="B411" t="s">
-        <v>496</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>207</v>
+        <v>1523</v>
       </c>
       <c r="B412" t="s">
-        <v>1110</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>951</v>
+        <v>224</v>
       </c>
       <c r="B413" t="s">
-        <v>1111</v>
+        <v>494</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>1097</v>
+        <v>25</v>
       </c>
       <c r="B414" t="s">
-        <v>1098</v>
+        <v>495</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>206</v>
+        <v>26</v>
       </c>
       <c r="B415" t="s">
-        <v>1112</v>
+        <v>496</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B416" t="s">
-        <v>497</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>205</v>
+        <v>951</v>
       </c>
       <c r="B417" t="s">
-        <v>498</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>145</v>
+        <v>1097</v>
       </c>
       <c r="B418" t="s">
-        <v>499</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>656</v>
+        <v>206</v>
       </c>
       <c r="B419" t="s">
-        <v>727</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="B420" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>1076</v>
+        <v>205</v>
       </c>
       <c r="B421" t="s">
-        <v>1077</v>
+        <v>498</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>263</v>
+        <v>145</v>
       </c>
       <c r="B422" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>1078</v>
+        <v>656</v>
       </c>
       <c r="B423" t="s">
-        <v>1079</v>
+        <v>727</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>80</v>
+        <v>171</v>
       </c>
       <c r="B424" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>65</v>
+        <v>1076</v>
       </c>
       <c r="B425" t="s">
-        <v>503</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>191</v>
+        <v>263</v>
       </c>
       <c r="B426" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>123</v>
+        <v>1078</v>
       </c>
       <c r="B427" t="s">
-        <v>505</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>192</v>
+        <v>80</v>
       </c>
       <c r="B428" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>231</v>
+        <v>65</v>
       </c>
       <c r="B429" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="B430" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>1175</v>
+        <v>123</v>
       </c>
       <c r="B431" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>31</v>
+        <v>192</v>
       </c>
       <c r="B432" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>1481</v>
+        <v>231</v>
       </c>
       <c r="B433" t="s">
-        <v>1482</v>
+        <v>507</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>30</v>
+        <v>233</v>
       </c>
       <c r="B434" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>37</v>
+        <v>1175</v>
       </c>
       <c r="B435" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="B436" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>1426</v>
+        <v>1481</v>
       </c>
       <c r="B437" t="s">
-        <v>1427</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>306</v>
+        <v>30</v>
       </c>
       <c r="B438" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>222</v>
+        <v>37</v>
       </c>
       <c r="B439" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>278</v>
+        <v>71</v>
       </c>
       <c r="B440" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>279</v>
+        <v>1426</v>
       </c>
       <c r="B441" t="s">
-        <v>517</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>1377</v>
+        <v>306</v>
       </c>
       <c r="B442" t="s">
-        <v>1378</v>
+        <v>513</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>824</v>
+        <v>222</v>
       </c>
       <c r="B443" t="s">
-        <v>825</v>
+        <v>514</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>48</v>
+        <v>278</v>
       </c>
       <c r="B444" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>146</v>
+        <v>279</v>
       </c>
       <c r="B445" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>52</v>
+        <v>1377</v>
       </c>
       <c r="B446" t="s">
-        <v>520</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>1359</v>
+        <v>824</v>
       </c>
       <c r="B447" t="s">
-        <v>515</v>
+        <v>825</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>223</v>
+        <v>48</v>
       </c>
       <c r="B448" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>1082</v>
+        <v>146</v>
       </c>
       <c r="B449" t="s">
-        <v>1083</v>
+        <v>519</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>1093</v>
+        <v>52</v>
       </c>
       <c r="B450" t="s">
-        <v>1096</v>
+        <v>520</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>1038</v>
+        <v>1359</v>
       </c>
       <c r="B451" t="s">
-        <v>1039</v>
+        <v>515</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>96</v>
+        <v>223</v>
       </c>
       <c r="B452" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>248</v>
+        <v>1082</v>
       </c>
       <c r="B453" t="s">
-        <v>523</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>249</v>
+        <v>1093</v>
       </c>
       <c r="B454" t="s">
-        <v>524</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>94</v>
+        <v>1038</v>
       </c>
       <c r="B455" t="s">
-        <v>525</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>1052</v>
+        <v>96</v>
       </c>
       <c r="B456" t="s">
-        <v>1053</v>
+        <v>522</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>212</v>
+        <v>1521</v>
       </c>
       <c r="B457" t="s">
-        <v>526</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>1200</v>
+        <v>248</v>
       </c>
       <c r="B458" t="s">
-        <v>1201</v>
+        <v>523</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>907</v>
+        <v>249</v>
       </c>
       <c r="B459" t="s">
-        <v>908</v>
+        <v>524</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>905</v>
+        <v>94</v>
       </c>
       <c r="B460" t="s">
-        <v>906</v>
+        <v>525</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>909</v>
+        <v>1052</v>
       </c>
       <c r="B461" t="s">
-        <v>910</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>329</v>
+        <v>212</v>
       </c>
       <c r="B462" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>1401</v>
+        <v>1200</v>
       </c>
       <c r="B463" t="s">
-        <v>1402</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>1403</v>
+        <v>907</v>
       </c>
       <c r="B464" t="s">
-        <v>1404</v>
+        <v>908</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>1054</v>
+        <v>905</v>
       </c>
       <c r="B465" t="s">
-        <v>1055</v>
+        <v>906</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>986</v>
+        <v>909</v>
       </c>
       <c r="B466" t="s">
-        <v>987</v>
+        <v>910</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>1387</v>
+        <v>329</v>
       </c>
       <c r="B467" t="s">
-        <v>1388</v>
+        <v>527</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>982</v>
+        <v>1401</v>
       </c>
       <c r="B468" t="s">
-        <v>983</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>984</v>
+        <v>1403</v>
       </c>
       <c r="B469" t="s">
-        <v>985</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>82</v>
+        <v>1054</v>
       </c>
       <c r="B470" t="s">
-        <v>528</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>765</v>
+        <v>986</v>
       </c>
       <c r="B471" t="s">
-        <v>766</v>
+        <v>987</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>197</v>
+        <v>1387</v>
       </c>
       <c r="B472" t="s">
-        <v>529</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>647</v>
+        <v>982</v>
       </c>
       <c r="B473" t="s">
-        <v>728</v>
+        <v>983</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>1424</v>
+        <v>984</v>
       </c>
       <c r="B474" t="s">
-        <v>1425</v>
+        <v>985</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>1330</v>
+        <v>82</v>
       </c>
       <c r="B475" t="s">
-        <v>1331</v>
+        <v>528</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>814</v>
+        <v>765</v>
       </c>
       <c r="B476" t="s">
-        <v>815</v>
+        <v>766</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>1056</v>
+        <v>197</v>
       </c>
       <c r="B477" t="s">
-        <v>1057</v>
+        <v>529</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>3</v>
+        <v>647</v>
       </c>
       <c r="B478" t="s">
-        <v>4</v>
+        <v>728</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>949</v>
+        <v>1424</v>
       </c>
       <c r="B479" t="s">
-        <v>4</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>950</v>
+        <v>1330</v>
       </c>
       <c r="B480" t="s">
-        <v>4</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>657</v>
+        <v>814</v>
       </c>
       <c r="B481" t="s">
-        <v>729</v>
+        <v>815</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>1279</v>
+        <v>1056</v>
       </c>
       <c r="B482" t="s">
-        <v>1280</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>763</v>
+        <v>3</v>
       </c>
       <c r="B483" t="s">
-        <v>764</v>
+        <v>4</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>85</v>
+        <v>949</v>
       </c>
       <c r="B484" t="s">
-        <v>530</v>
+        <v>4</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>1050</v>
+        <v>950</v>
       </c>
       <c r="B485" t="s">
-        <v>1051</v>
+        <v>4</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>822</v>
+        <v>657</v>
       </c>
       <c r="B486" t="s">
-        <v>823</v>
+        <v>729</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>802</v>
+        <v>1279</v>
       </c>
       <c r="B487" t="s">
-        <v>803</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>187</v>
+        <v>763</v>
       </c>
       <c r="B488" t="s">
-        <v>531</v>
+        <v>764</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>820</v>
+        <v>85</v>
       </c>
       <c r="B489" t="s">
-        <v>821</v>
+        <v>530</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>925</v>
+        <v>1050</v>
       </c>
       <c r="B490" t="s">
-        <v>1107</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>1430</v>
+        <v>822</v>
       </c>
       <c r="B491" t="s">
-        <v>1431</v>
+        <v>823</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>855</v>
+        <v>802</v>
       </c>
       <c r="B492" t="s">
-        <v>856</v>
+        <v>803</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>1418</v>
+        <v>187</v>
       </c>
       <c r="B493" t="s">
-        <v>1419</v>
+        <v>531</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>1034</v>
+        <v>820</v>
       </c>
       <c r="B494" t="s">
-        <v>1035</v>
+        <v>821</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>791</v>
+        <v>925</v>
       </c>
       <c r="B495" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>790</v>
+        <v>1430</v>
       </c>
       <c r="B496" t="s">
-        <v>1109</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>1472</v>
+        <v>855</v>
       </c>
       <c r="B497" t="s">
-        <v>1473</v>
+        <v>856</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>1470</v>
+        <v>1418</v>
       </c>
       <c r="B498" t="s">
-        <v>1471</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>13</v>
+        <v>1034</v>
       </c>
       <c r="B499" t="s">
-        <v>14</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>810</v>
+        <v>791</v>
       </c>
       <c r="B500" t="s">
-        <v>811</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>1209</v>
+        <v>790</v>
       </c>
       <c r="B501" t="s">
-        <v>1210</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>186</v>
+        <v>1472</v>
       </c>
       <c r="B502" t="s">
-        <v>532</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>804</v>
+        <v>1470</v>
       </c>
       <c r="B503" t="s">
-        <v>805</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>319</v>
+        <v>13</v>
       </c>
       <c r="B504" t="s">
-        <v>533</v>
+        <v>14</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>649</v>
+        <v>810</v>
       </c>
       <c r="B505" t="s">
-        <v>730</v>
+        <v>811</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>848</v>
+        <v>1209</v>
       </c>
       <c r="B506" t="s">
-        <v>849</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>651</v>
+        <v>186</v>
       </c>
       <c r="B507" t="s">
-        <v>731</v>
+        <v>532</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>646</v>
+        <v>804</v>
       </c>
       <c r="B508" t="s">
-        <v>732</v>
+        <v>805</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>1182</v>
+        <v>319</v>
       </c>
       <c r="B509" t="s">
-        <v>1183</v>
+        <v>533</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>256</v>
+        <v>649</v>
       </c>
       <c r="B510" t="s">
-        <v>534</v>
+        <v>730</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>260</v>
+        <v>848</v>
       </c>
       <c r="B511" t="s">
-        <v>535</v>
+        <v>849</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>261</v>
+        <v>651</v>
       </c>
       <c r="B512" t="s">
-        <v>536</v>
+        <v>731</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>188</v>
+        <v>646</v>
       </c>
       <c r="B513" t="s">
-        <v>537</v>
+        <v>732</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>190</v>
+        <v>1182</v>
       </c>
       <c r="B514" t="s">
-        <v>538</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>927</v>
+        <v>256</v>
       </c>
       <c r="B515" t="s">
-        <v>928</v>
+        <v>534</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>1021</v>
+        <v>260</v>
       </c>
       <c r="B516" t="s">
-        <v>1022</v>
+        <v>535</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>1198</v>
+        <v>261</v>
       </c>
       <c r="B517" t="s">
-        <v>1199</v>
+        <v>536</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="B518" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>1397</v>
+        <v>190</v>
       </c>
       <c r="B519" t="s">
-        <v>1398</v>
+        <v>538</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>1289</v>
+        <v>927</v>
       </c>
       <c r="B520" t="s">
-        <v>1290</v>
+        <v>928</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>844</v>
+        <v>1021</v>
       </c>
       <c r="B521" t="s">
-        <v>845</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>143</v>
+        <v>1198</v>
       </c>
       <c r="B522" t="s">
-        <v>540</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>140</v>
+        <v>209</v>
       </c>
       <c r="B523" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>1178</v>
+        <v>1397</v>
       </c>
       <c r="B524" t="s">
-        <v>1179</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>1277</v>
+        <v>1289</v>
       </c>
       <c r="B525" t="s">
-        <v>1278</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>254</v>
+        <v>844</v>
       </c>
       <c r="B526" t="s">
-        <v>542</v>
+        <v>845</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>330</v>
+        <v>143</v>
       </c>
       <c r="B527" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="B528" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>234</v>
+        <v>1178</v>
       </c>
       <c r="B529" t="s">
-        <v>545</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>73</v>
+        <v>1277</v>
       </c>
       <c r="B530" t="s">
-        <v>546</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>341</v>
+        <v>254</v>
       </c>
       <c r="B531" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="B532" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>836</v>
+        <v>210</v>
       </c>
       <c r="B533" t="s">
-        <v>837</v>
+        <v>544</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>838</v>
+        <v>234</v>
       </c>
       <c r="B534" t="s">
-        <v>839</v>
+        <v>545</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>220</v>
+        <v>73</v>
       </c>
       <c r="B535" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>900</v>
+        <v>341</v>
       </c>
       <c r="B536" t="s">
-        <v>901</v>
+        <v>547</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>1353</v>
+        <v>308</v>
       </c>
       <c r="B537" t="s">
-        <v>1354</v>
+        <v>548</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>954</v>
+        <v>836</v>
       </c>
       <c r="B538" t="s">
-        <v>955</v>
+        <v>837</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>1163</v>
+        <v>838</v>
       </c>
       <c r="B539" t="s">
-        <v>1164</v>
+        <v>839</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B540" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>333</v>
+        <v>900</v>
       </c>
       <c r="B541" t="s">
-        <v>1136</v>
+        <v>901</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>962</v>
+        <v>1353</v>
       </c>
       <c r="B542" t="s">
-        <v>963</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>771</v>
+        <v>954</v>
       </c>
       <c r="B543" t="s">
-        <v>772</v>
+        <v>955</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>294</v>
+        <v>1163</v>
       </c>
       <c r="B544" t="s">
-        <v>551</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>943</v>
+        <v>227</v>
       </c>
       <c r="B545" t="s">
-        <v>944</v>
+        <v>550</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B546" t="s">
-        <v>552</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>773</v>
+        <v>962</v>
       </c>
       <c r="B547" t="s">
-        <v>772</v>
+        <v>963</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>1293</v>
+        <v>771</v>
       </c>
       <c r="B548" t="s">
-        <v>1294</v>
+        <v>772</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>339</v>
+        <v>1517</v>
       </c>
       <c r="B549" t="s">
-        <v>553</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>340</v>
+        <v>294</v>
       </c>
       <c r="B550" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>638</v>
+        <v>943</v>
       </c>
       <c r="B551" t="s">
-        <v>733</v>
+        <v>944</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>39</v>
+        <v>338</v>
       </c>
       <c r="B552" t="s">
-        <v>1490</v>
+        <v>552</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>38</v>
+        <v>773</v>
       </c>
       <c r="B553" t="s">
-        <v>1483</v>
+        <v>772</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>342</v>
+        <v>1293</v>
       </c>
       <c r="B554" t="s">
-        <v>555</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>107</v>
+        <v>339</v>
       </c>
       <c r="B555" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>1405</v>
+        <v>340</v>
       </c>
       <c r="B556" t="s">
-        <v>1406</v>
+        <v>554</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>1019</v>
+        <v>638</v>
       </c>
       <c r="B557" t="s">
-        <v>1020</v>
+        <v>733</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>894</v>
+        <v>39</v>
       </c>
       <c r="B558" t="s">
-        <v>895</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="B559" t="s">
-        <v>557</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>1015</v>
+        <v>342</v>
       </c>
       <c r="B560" t="s">
-        <v>1016</v>
+        <v>555</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B561" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>99</v>
+        <v>1405</v>
       </c>
       <c r="B562" t="s">
-        <v>559</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>659</v>
+        <v>1019</v>
       </c>
       <c r="B563" t="s">
-        <v>734</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>1091</v>
+        <v>894</v>
       </c>
       <c r="B564" t="s">
-        <v>1014</v>
+        <v>895</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>816</v>
+        <v>117</v>
       </c>
       <c r="B565" t="s">
-        <v>817</v>
+        <v>557</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>113</v>
+        <v>1015</v>
       </c>
       <c r="B566" t="s">
-        <v>560</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>881</v>
+        <v>98</v>
       </c>
       <c r="B567" t="s">
-        <v>882</v>
+        <v>558</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="B568" t="s">
-        <v>1106</v>
+        <v>559</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>290</v>
+        <v>659</v>
       </c>
       <c r="B569" t="s">
-        <v>561</v>
+        <v>734</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>299</v>
+        <v>1091</v>
       </c>
       <c r="B570" t="s">
-        <v>562</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>47</v>
+        <v>816</v>
       </c>
       <c r="B571" t="s">
-        <v>563</v>
+        <v>817</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>840</v>
+        <v>113</v>
       </c>
       <c r="B572" t="s">
-        <v>841</v>
+        <v>560</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>51</v>
+        <v>881</v>
       </c>
       <c r="B573" t="s">
-        <v>564</v>
+        <v>882</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>863</v>
+        <v>45</v>
       </c>
       <c r="B574" t="s">
-        <v>864</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>114</v>
+        <v>290</v>
       </c>
       <c r="B575" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>846</v>
+        <v>299</v>
       </c>
       <c r="B576" t="s">
-        <v>847</v>
+        <v>562</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>144</v>
+        <v>47</v>
       </c>
       <c r="B577" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>1068</v>
+        <v>840</v>
       </c>
       <c r="B578" t="s">
-        <v>1069</v>
+        <v>841</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>176</v>
+        <v>51</v>
       </c>
       <c r="B579" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>315</v>
+        <v>863</v>
       </c>
       <c r="B580" t="s">
-        <v>568</v>
+        <v>864</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="B581" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>1008</v>
+        <v>846</v>
       </c>
       <c r="B582" t="s">
-        <v>1009</v>
+        <v>847</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>1205</v>
+        <v>144</v>
       </c>
       <c r="B583" t="s">
-        <v>1206</v>
+        <v>566</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>293</v>
+        <v>1068</v>
       </c>
       <c r="B584" t="s">
-        <v>570</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>972</v>
+        <v>176</v>
       </c>
       <c r="B585" t="s">
-        <v>973</v>
+        <v>567</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>1436</v>
+        <v>315</v>
       </c>
       <c r="B586" t="s">
-        <v>1437</v>
+        <v>568</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>301</v>
+        <v>29</v>
       </c>
       <c r="B587" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>994</v>
+        <v>1008</v>
       </c>
       <c r="B588" t="s">
-        <v>995</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>998</v>
+        <v>1205</v>
       </c>
       <c r="B589" t="s">
-        <v>999</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>75</v>
+        <v>293</v>
       </c>
       <c r="B590" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>76</v>
+        <v>972</v>
       </c>
       <c r="B591" t="s">
-        <v>573</v>
+        <v>973</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>78</v>
+        <v>1436</v>
       </c>
       <c r="B592" t="s">
-        <v>574</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>328</v>
+        <v>301</v>
       </c>
       <c r="B593" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>1384</v>
+        <v>994</v>
       </c>
       <c r="B594" t="s">
-        <v>1385</v>
+        <v>995</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>1283</v>
+        <v>998</v>
       </c>
       <c r="B595" t="s">
-        <v>1284</v>
+        <v>999</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>745</v>
+        <v>75</v>
       </c>
       <c r="B596" t="s">
-        <v>746</v>
+        <v>572</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>798</v>
+        <v>76</v>
       </c>
       <c r="B597" t="s">
-        <v>799</v>
+        <v>573</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>1296</v>
+        <v>78</v>
       </c>
       <c r="B598" t="s">
-        <v>1297</v>
+        <v>574</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>135</v>
+        <v>328</v>
       </c>
       <c r="B599" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>1161</v>
+        <v>1384</v>
       </c>
       <c r="B600" t="s">
-        <v>11